--- a/PublicCustomerApp/src/python/translation.xlsx
+++ b/PublicCustomerApp/src/python/translation.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="828">
   <si>
     <t>key</t>
   </si>
@@ -2323,6 +2323,186 @@
   </si>
   <si>
     <t>Refreshing....</t>
+  </si>
+  <si>
+    <t>view_detailed</t>
+  </si>
+  <si>
+    <t>View Detailed</t>
+  </si>
+  <si>
+    <t>my_account</t>
+  </si>
+  <si>
+    <t>My Account</t>
+  </si>
+  <si>
+    <t>price_chart</t>
+  </si>
+  <si>
+    <t>Price Chart</t>
+  </si>
+  <si>
+    <t>permission_screen</t>
+  </si>
+  <si>
+    <t>Permission Screen</t>
+  </si>
+  <si>
+    <t>permission_screen_info</t>
+  </si>
+  <si>
+    <t>We need location, background tracking, and notification permissions for real-time trip monitoring, passenger alerts, and seamless navigation updates while driving.</t>
+  </si>
+  <si>
+    <t>notification_permission</t>
+  </si>
+  <si>
+    <t>Notification Permission</t>
+  </si>
+  <si>
+    <t>location_permission</t>
+  </si>
+  <si>
+    <t>Location Permission</t>
+  </si>
+  <si>
+    <t>bg_loc_permission</t>
+  </si>
+  <si>
+    <t>Background location Permission</t>
+  </si>
+  <si>
+    <t>not_tracking_info</t>
+  </si>
+  <si>
+    <t>NOT needs background location permission to track your location even when the app is not open. This allows for continuous tracking and ensures accurate location data is collected at all times.</t>
+  </si>
+  <si>
+    <t>display_over_other_apps</t>
+  </si>
+  <si>
+    <t>Display Over Other Apps</t>
+  </si>
+  <si>
+    <t>display_over_other_apps_info</t>
+  </si>
+  <si>
+    <t>Display Over Other Apps this permission is required to display the overlay over other apps. This ensures drivers can promptly respond to new ride requests. The overlay is not used for advertising or unrelated content.</t>
+  </si>
+  <si>
+    <t>disable_battery_optim</t>
+  </si>
+  <si>
+    <t>Disable Battery Optimization</t>
+  </si>
+  <si>
+    <t>disable_battery_info</t>
+  </si>
+  <si>
+    <t>Disabling battery optimization enables continuous tracking for better accuracy even when app is not actively in use, but may slightly increase battery usage. We recommend you to disable battery optimization from app settings for optimal tracking  performance</t>
+  </si>
+  <si>
+    <t>you_can_enable_in_this_screen</t>
+  </si>
+  <si>
+    <t>In this screen you can only enable permissions, for disabling permission manually disable it on mobile settings</t>
+  </si>
+  <si>
+    <t>enable_disable_manually</t>
+  </si>
+  <si>
+    <t>Disable / Enable Permissions Manually</t>
+  </si>
+  <si>
+    <t>delete_account</t>
+  </si>
+  <si>
+    <t>Delete Account</t>
+  </si>
+  <si>
+    <t>history</t>
+  </si>
+  <si>
+    <t>History</t>
+  </si>
+  <si>
+    <t>today</t>
+  </si>
+  <si>
+    <t>Today</t>
+  </si>
+  <si>
+    <t>yesterday</t>
+  </si>
+  <si>
+    <t>Yesterday</t>
+  </si>
+  <si>
+    <t>this_week</t>
+  </si>
+  <si>
+    <t>This week</t>
+  </si>
+  <si>
+    <t>last_week</t>
+  </si>
+  <si>
+    <t>Last week</t>
+  </si>
+  <si>
+    <t>this_month</t>
+  </si>
+  <si>
+    <t>This Month</t>
+  </si>
+  <si>
+    <t>call_support</t>
+  </si>
+  <si>
+    <t>Call Support</t>
+  </si>
+  <si>
+    <t>send_email</t>
+  </si>
+  <si>
+    <t>Send Email</t>
+  </si>
+  <si>
+    <t>whatsapp</t>
+  </si>
+  <si>
+    <t>WhatsApp</t>
+  </si>
+  <si>
+    <t>call</t>
+  </si>
+  <si>
+    <t>Call</t>
+  </si>
+  <si>
+    <t>mail</t>
+  </si>
+  <si>
+    <t>Mail</t>
+  </si>
+  <si>
+    <t>home</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>accept</t>
+  </si>
+  <si>
+    <t>Accept</t>
+  </si>
+  <si>
+    <t>settings</t>
+  </si>
+  <si>
+    <t>Settings</t>
   </si>
 </sst>
 </file>
@@ -2377,7 +2557,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2404,6 +2584,12 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
@@ -2625,8 +2811,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="39.0"/>
-    <col customWidth="1" min="2" max="2" width="46.75"/>
+    <col customWidth="1" min="1" max="1" width="47.0"/>
+    <col customWidth="1" min="2" max="2" width="52.63"/>
     <col customWidth="1" min="3" max="3" width="54.88"/>
     <col customWidth="1" min="4" max="4" width="60.88"/>
     <col customWidth="1" min="5" max="5" width="54.88"/>
@@ -3003,8 +3189,8 @@
         <v>54</v>
       </c>
       <c r="C27" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B27, ""en"", ""ta"")"),"செல்லுபடியாகும் உரிம எண்ணை (TN01 20110012345) உள்ளிடவும்.")</f>
-        <v>செல்லுபடியாகும் உரிம எண்ணை (TN01 20110012345) உள்ளிடவும்.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B27, ""en"", ""ta"")"),"தயவுசெய்து செல்லுபடியாகும் உரிம எண்ணை உள்ளிடவும் (TN01 20110012345)")</f>
+        <v>தயவுசெய்து செல்லுபடியாகும் உரிம எண்ணை உள்ளிடவும் (TN01 20110012345)</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
@@ -3607,8 +3793,8 @@
         <v>140</v>
       </c>
       <c r="C70" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B70, ""en"", ""ta"")"),"நிறத்தைத் தேர்ந்தெடுக்கவும்")</f>
-        <v>நிறத்தைத் தேர்ந்தெடுக்கவும்</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B70, ""en"", ""ta"")"),"வண்ணத்தைத் தேர்ந்தெடுக்கவும்")</f>
+        <v>வண்ணத்தைத் தேர்ந்தெடுக்கவும்</v>
       </c>
       <c r="D70" s="5"/>
       <c r="E70" s="5"/>
@@ -5685,8 +5871,8 @@
         <v>422</v>
       </c>
       <c r="C218" s="5" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B218, ""en"", ""ta"")"),"முடிவு இடம்")</f>
-        <v>முடிவு இடம்</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B218, ""en"", ""ta"")"),"இருப்பிடம் முடிவு")</f>
+        <v>இருப்பிடம் முடிவு</v>
       </c>
       <c r="D218" s="5"/>
       <c r="E218" s="5"/>
@@ -8212,226 +8398,450 @@
       <c r="E398" s="5"/>
     </row>
     <row r="399">
-      <c r="A399" s="3"/>
-      <c r="B399" s="4"/>
-      <c r="C399" s="5"/>
+      <c r="A399" s="9" t="s">
+        <v>768</v>
+      </c>
+      <c r="B399" s="10" t="s">
+        <v>769</v>
+      </c>
+      <c r="C399" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B399, ""en"", ""ta"")"),"விரிவாகக் காண்க")</f>
+        <v>விரிவாகக் காண்க</v>
+      </c>
       <c r="D399" s="5"/>
       <c r="E399" s="5"/>
     </row>
     <row r="400">
-      <c r="A400" s="3"/>
-      <c r="B400" s="4"/>
-      <c r="C400" s="5"/>
+      <c r="A400" s="9" t="s">
+        <v>770</v>
+      </c>
+      <c r="B400" s="10" t="s">
+        <v>771</v>
+      </c>
+      <c r="C400" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B400, ""en"", ""ta"")"),"எனது கணக்கு")</f>
+        <v>எனது கணக்கு</v>
+      </c>
       <c r="D400" s="5"/>
       <c r="E400" s="5"/>
     </row>
     <row r="401">
-      <c r="A401" s="3"/>
-      <c r="B401" s="4"/>
-      <c r="C401" s="5"/>
+      <c r="A401" s="9" t="s">
+        <v>772</v>
+      </c>
+      <c r="B401" s="10" t="s">
+        <v>773</v>
+      </c>
+      <c r="C401" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B401, ""en"", ""ta"")"),"விலை விளக்கப்படம்")</f>
+        <v>விலை விளக்கப்படம்</v>
+      </c>
       <c r="D401" s="5"/>
       <c r="E401" s="5"/>
     </row>
     <row r="402">
-      <c r="A402" s="3"/>
-      <c r="B402" s="4"/>
-      <c r="C402" s="5"/>
+      <c r="A402" s="9" t="s">
+        <v>774</v>
+      </c>
+      <c r="B402" s="10" t="s">
+        <v>775</v>
+      </c>
+      <c r="C402" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B402, ""en"", ""ta"")"),"அனுமதித் திரை")</f>
+        <v>அனுமதித் திரை</v>
+      </c>
       <c r="D402" s="5"/>
       <c r="E402" s="5"/>
     </row>
     <row r="403">
-      <c r="A403" s="3"/>
-      <c r="B403" s="4"/>
-      <c r="C403" s="5"/>
+      <c r="A403" s="9" t="s">
+        <v>776</v>
+      </c>
+      <c r="B403" s="10" t="s">
+        <v>777</v>
+      </c>
+      <c r="C403" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B403, ""en"", ""ta"")"),"வாகனம் ஓட்டும்போது நிகழ்நேர பயணக் கண்காணிப்பு, பயணிகள் எச்சரிக்கைகள் மற்றும் தடையற்ற வழிசெலுத்தல் புதுப்பிப்புகளுக்கு இருப்பிடம், பின்னணி கண்காணிப்பு மற்றும் அறிவிப்பு அனுமதிகள் நமக்குத் தேவை.")</f>
+        <v>வாகனம் ஓட்டும்போது நிகழ்நேர பயணக் கண்காணிப்பு, பயணிகள் எச்சரிக்கைகள் மற்றும் தடையற்ற வழிசெலுத்தல் புதுப்பிப்புகளுக்கு இருப்பிடம், பின்னணி கண்காணிப்பு மற்றும் அறிவிப்பு அனுமதிகள் நமக்குத் தேவை.</v>
+      </c>
       <c r="D403" s="5"/>
       <c r="E403" s="5"/>
     </row>
     <row r="404">
-      <c r="A404" s="3"/>
-      <c r="B404" s="4"/>
-      <c r="C404" s="5"/>
+      <c r="A404" s="9" t="s">
+        <v>778</v>
+      </c>
+      <c r="B404" s="10" t="s">
+        <v>779</v>
+      </c>
+      <c r="C404" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B404, ""en"", ""ta"")"),"அறிவிப்பு அனுமதி")</f>
+        <v>அறிவிப்பு அனுமதி</v>
+      </c>
       <c r="D404" s="5"/>
       <c r="E404" s="5"/>
     </row>
     <row r="405">
-      <c r="A405" s="3"/>
-      <c r="B405" s="4"/>
-      <c r="C405" s="5"/>
+      <c r="A405" s="9" t="s">
+        <v>780</v>
+      </c>
+      <c r="B405" s="10" t="s">
+        <v>781</v>
+      </c>
+      <c r="C405" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B405, ""en"", ""ta"")"),"இருப்பிட அனுமதி")</f>
+        <v>இருப்பிட அனுமதி</v>
+      </c>
       <c r="D405" s="5"/>
       <c r="E405" s="5"/>
     </row>
     <row r="406">
-      <c r="A406" s="3"/>
-      <c r="B406" s="4"/>
-      <c r="C406" s="5"/>
+      <c r="A406" s="9" t="s">
+        <v>782</v>
+      </c>
+      <c r="B406" s="10" t="s">
+        <v>783</v>
+      </c>
+      <c r="C406" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B406, ""en"", ""ta"")"),"பின்னணி இருப்பிட அனுமதி")</f>
+        <v>பின்னணி இருப்பிட அனுமதி</v>
+      </c>
       <c r="D406" s="5"/>
       <c r="E406" s="5"/>
     </row>
     <row r="407">
-      <c r="A407" s="3"/>
-      <c r="B407" s="4"/>
-      <c r="C407" s="5"/>
+      <c r="A407" s="9" t="s">
+        <v>784</v>
+      </c>
+      <c r="B407" s="10" t="s">
+        <v>785</v>
+      </c>
+      <c r="C407" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B407, ""en"", ""ta"")"),"பயன்பாடு திறக்கப்படாதபோதும் கூட உங்கள் இருப்பிடத்தைக் கண்காணிக்க NOT க்கு பின்னணி இருப்பிட அனுமதி தேவையில்லை. இது தொடர்ச்சியான கண்காணிப்பை அனுமதிக்கிறது மற்றும் எல்லா நேரங்களிலும் துல்லியமான இருப்பிடத் தரவு சேகரிக்கப்படுவதை உறுதி செய்கிறது.")</f>
+        <v>பயன்பாடு திறக்கப்படாதபோதும் கூட உங்கள் இருப்பிடத்தைக் கண்காணிக்க NOT க்கு பின்னணி இருப்பிட அனுமதி தேவையில்லை. இது தொடர்ச்சியான கண்காணிப்பை அனுமதிக்கிறது மற்றும் எல்லா நேரங்களிலும் துல்லியமான இருப்பிடத் தரவு சேகரிக்கப்படுவதை உறுதி செய்கிறது.</v>
+      </c>
       <c r="D407" s="5"/>
       <c r="E407" s="5"/>
     </row>
     <row r="408">
-      <c r="A408" s="3"/>
-      <c r="B408" s="4"/>
-      <c r="C408" s="5"/>
+      <c r="A408" s="9" t="s">
+        <v>786</v>
+      </c>
+      <c r="B408" s="10" t="s">
+        <v>787</v>
+      </c>
+      <c r="C408" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B408, ""en"", ""ta"")"),"பிற பயன்பாடுகளின் மேல் காட்டு")</f>
+        <v>பிற பயன்பாடுகளின் மேல் காட்டு</v>
+      </c>
       <c r="D408" s="5"/>
       <c r="E408" s="5"/>
     </row>
     <row r="409">
-      <c r="A409" s="3"/>
-      <c r="B409" s="4"/>
-      <c r="C409" s="5"/>
+      <c r="A409" s="9" t="s">
+        <v>788</v>
+      </c>
+      <c r="B409" s="10" t="s">
+        <v>789</v>
+      </c>
+      <c r="C409" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B409, ""en"", ""ta"")"),"மற்ற பயன்பாடுகளின் மேல் காட்சிப்படுத்தல் மற்ற பயன்பாடுகளின் மேல் காட்சிப்படுத்த இந்த அனுமதி தேவை. இது ஓட்டுநர்கள் புதிய சவாரி கோரிக்கைகளுக்கு உடனடியாக பதிலளிக்க முடியும் என்பதை உறுதி செய்கிறது. விளம்பரம் அல்லது தொடர்பில்லாத உள்ளடக்கத்திற்கு இந்த மேலடுக்கு"&amp;" பயன்படுத்தப்படாது.")</f>
+        <v>மற்ற பயன்பாடுகளின் மேல் காட்சிப்படுத்தல் மற்ற பயன்பாடுகளின் மேல் காட்சிப்படுத்த இந்த அனுமதி தேவை. இது ஓட்டுநர்கள் புதிய சவாரி கோரிக்கைகளுக்கு உடனடியாக பதிலளிக்க முடியும் என்பதை உறுதி செய்கிறது. விளம்பரம் அல்லது தொடர்பில்லாத உள்ளடக்கத்திற்கு இந்த மேலடுக்கு பயன்படுத்தப்படாது.</v>
+      </c>
       <c r="D409" s="5"/>
       <c r="E409" s="5"/>
     </row>
     <row r="410">
-      <c r="A410" s="3"/>
-      <c r="B410" s="4"/>
-      <c r="C410" s="5"/>
+      <c r="A410" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="B410" s="4" t="s">
+        <v>791</v>
+      </c>
+      <c r="C410" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B410, ""en"", ""ta"")"),"பேட்டரி உகப்பாக்கத்தை முடக்கு")</f>
+        <v>பேட்டரி உகப்பாக்கத்தை முடக்கு</v>
+      </c>
       <c r="D410" s="5"/>
       <c r="E410" s="5"/>
     </row>
     <row r="411">
-      <c r="A411" s="3"/>
-      <c r="B411" s="4"/>
-      <c r="C411" s="5"/>
+      <c r="A411" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="B411" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="C411" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B411, ""en"", ""ta"")"),"பேட்டரி ஆப்டிமைசேஷனை முடக்குவது, ஆப்ஸ் தீவிரமாகப் பயன்பாட்டில் இல்லாதபோதும் சிறந்த துல்லியத்திற்காக தொடர்ச்சியான கண்காணிப்பை செயல்படுத்துகிறது, ஆனால் பேட்டரி பயன்பாட்டை சற்று அதிகரிக்கக்கூடும். உகந்த கண்காணிப்பு செயல்திறனுக்காக ஆப்ஸ் அமைப்புகளில் இருந்து "&amp;"பேட்டரி ஆப்டிமைசேஷனை முடக்குமாறு நாங்கள் பரிந்துரைக்கிறோம்.")</f>
+        <v>பேட்டரி ஆப்டிமைசேஷனை முடக்குவது, ஆப்ஸ் தீவிரமாகப் பயன்பாட்டில் இல்லாதபோதும் சிறந்த துல்லியத்திற்காக தொடர்ச்சியான கண்காணிப்பை செயல்படுத்துகிறது, ஆனால் பேட்டரி பயன்பாட்டை சற்று அதிகரிக்கக்கூடும். உகந்த கண்காணிப்பு செயல்திறனுக்காக ஆப்ஸ் அமைப்புகளில் இருந்து பேட்டரி ஆப்டிமைசேஷனை முடக்குமாறு நாங்கள் பரிந்துரைக்கிறோம்.</v>
+      </c>
       <c r="D411" s="5"/>
       <c r="E411" s="5"/>
     </row>
     <row r="412">
-      <c r="A412" s="3"/>
-      <c r="B412" s="4"/>
-      <c r="C412" s="5"/>
+      <c r="A412" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="B412" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="C412" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B412, ""en"", ""ta"")"),"இந்தத் திரையில் நீங்கள் அனுமதிகளை மட்டுமே இயக்க முடியும், அனுமதியை முடக்குவதற்கு மொபைல் அமைப்புகளில் அதை கைமுறையாக முடக்கவும்.")</f>
+        <v>இந்தத் திரையில் நீங்கள் அனுமதிகளை மட்டுமே இயக்க முடியும், அனுமதியை முடக்குவதற்கு மொபைல் அமைப்புகளில் அதை கைமுறையாக முடக்கவும்.</v>
+      </c>
       <c r="D412" s="5"/>
       <c r="E412" s="5"/>
     </row>
     <row r="413">
-      <c r="A413" s="3"/>
-      <c r="B413" s="4"/>
-      <c r="C413" s="5"/>
+      <c r="A413" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="B413" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="C413" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B413, ""en"", ""ta"")"),"அனுமதிகளை கைமுறையாக முடக்கு / இயக்கு")</f>
+        <v>அனுமதிகளை கைமுறையாக முடக்கு / இயக்கு</v>
+      </c>
       <c r="D413" s="5"/>
       <c r="E413" s="5"/>
     </row>
     <row r="414">
-      <c r="A414" s="3"/>
-      <c r="B414" s="4"/>
-      <c r="C414" s="5"/>
+      <c r="A414" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="B414" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="C414" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B414, ""en"", ""ta"")"),"கணக்கை நீக்கு")</f>
+        <v>கணக்கை நீக்கு</v>
+      </c>
       <c r="D414" s="5"/>
       <c r="E414" s="5"/>
     </row>
     <row r="415">
-      <c r="A415" s="3"/>
-      <c r="B415" s="4"/>
-      <c r="C415" s="5"/>
+      <c r="A415" s="9" t="s">
+        <v>800</v>
+      </c>
+      <c r="B415" s="10" t="s">
+        <v>801</v>
+      </c>
+      <c r="C415" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B415, ""en"", ""ta"")"),"வரலாறு")</f>
+        <v>வரலாறு</v>
+      </c>
       <c r="D415" s="5"/>
       <c r="E415" s="5"/>
     </row>
     <row r="416">
-      <c r="A416" s="3"/>
-      <c r="B416" s="4"/>
-      <c r="C416" s="5"/>
+      <c r="A416" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="B416" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="C416" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B416, ""en"", ""ta"")"),"இன்று")</f>
+        <v>இன்று</v>
+      </c>
       <c r="D416" s="5"/>
       <c r="E416" s="5"/>
     </row>
     <row r="417">
-      <c r="A417" s="3"/>
-      <c r="B417" s="4"/>
-      <c r="C417" s="5"/>
+      <c r="A417" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="B417" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="C417" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B417, ""en"", ""ta"")"),"நேற்று")</f>
+        <v>நேற்று</v>
+      </c>
       <c r="D417" s="5"/>
       <c r="E417" s="5"/>
     </row>
     <row r="418">
-      <c r="A418" s="3"/>
-      <c r="B418" s="4"/>
-      <c r="C418" s="5"/>
+      <c r="A418" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="B418" s="4" t="s">
+        <v>807</v>
+      </c>
+      <c r="C418" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B418, ""en"", ""ta"")"),"இந்த வாரம்")</f>
+        <v>இந்த வாரம்</v>
+      </c>
       <c r="D418" s="5"/>
       <c r="E418" s="5"/>
     </row>
     <row r="419">
-      <c r="A419" s="3"/>
-      <c r="B419" s="4"/>
-      <c r="C419" s="5"/>
+      <c r="A419" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="B419" s="4" t="s">
+        <v>809</v>
+      </c>
+      <c r="C419" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B419, ""en"", ""ta"")"),"கடந்த வாரம்")</f>
+        <v>கடந்த வாரம்</v>
+      </c>
       <c r="D419" s="5"/>
       <c r="E419" s="5"/>
     </row>
     <row r="420">
-      <c r="A420" s="3"/>
-      <c r="B420" s="4"/>
-      <c r="C420" s="5"/>
+      <c r="A420" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="B420" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="C420" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B420, ""en"", ""ta"")"),"இந்த மாதம்")</f>
+        <v>இந்த மாதம்</v>
+      </c>
       <c r="D420" s="5"/>
       <c r="E420" s="5"/>
     </row>
     <row r="421">
-      <c r="A421" s="3"/>
-      <c r="B421" s="4"/>
-      <c r="C421" s="5"/>
+      <c r="A421" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="B421" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="C421" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B421, ""en"", ""ta"")"),"ஆதரவை அழைக்கவும்")</f>
+        <v>ஆதரவை அழைக்கவும்</v>
+      </c>
       <c r="D421" s="5"/>
       <c r="E421" s="5"/>
     </row>
     <row r="422">
-      <c r="A422" s="3"/>
-      <c r="B422" s="4"/>
-      <c r="C422" s="5"/>
+      <c r="A422" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="B422" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="C422" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B422, ""en"", ""ta"")"),"மின்னஞ்சல் அனுப்பு")</f>
+        <v>மின்னஞ்சல் அனுப்பு</v>
+      </c>
       <c r="D422" s="5"/>
       <c r="E422" s="5"/>
     </row>
     <row r="423">
-      <c r="A423" s="3"/>
-      <c r="B423" s="4"/>
-      <c r="C423" s="5"/>
+      <c r="A423" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="B423" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="C423" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B423, ""en"", ""ta"")"),"வாட்ஸ்அப்")</f>
+        <v>வாட்ஸ்அப்</v>
+      </c>
       <c r="D423" s="5"/>
       <c r="E423" s="5"/>
     </row>
     <row r="424">
-      <c r="A424" s="3"/>
-      <c r="B424" s="4"/>
-      <c r="C424" s="5"/>
+      <c r="A424" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="B424" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="C424" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B424, ""en"", ""ta"")"),"அழைப்பு")</f>
+        <v>அழைப்பு</v>
+      </c>
       <c r="D424" s="5"/>
       <c r="E424" s="5"/>
     </row>
     <row r="425">
-      <c r="A425" s="3"/>
-      <c r="B425" s="4"/>
-      <c r="C425" s="5"/>
+      <c r="A425" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="B425" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="C425" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B425, ""en"", ""ta"")"),"அஞ்சல்")</f>
+        <v>அஞ்சல்</v>
+      </c>
       <c r="D425" s="5"/>
       <c r="E425" s="5"/>
     </row>
     <row r="426">
-      <c r="A426" s="3"/>
-      <c r="B426" s="4"/>
-      <c r="C426" s="5"/>
+      <c r="A426" s="9" t="s">
+        <v>822</v>
+      </c>
+      <c r="B426" s="10" t="s">
+        <v>823</v>
+      </c>
+      <c r="C426" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B426, ""en"", ""ta"")"),"முகப்புப் பக்கம்")</f>
+        <v>முகப்புப் பக்கம்</v>
+      </c>
       <c r="D426" s="5"/>
       <c r="E426" s="5"/>
     </row>
     <row r="427">
-      <c r="A427" s="3"/>
-      <c r="B427" s="4"/>
-      <c r="C427" s="5"/>
+      <c r="A427" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B427" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="C427" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B427, ""en"", ""ta"")"),"டிக்கெட்டை உயர்த்தவும்")</f>
+        <v>டிக்கெட்டை உயர்த்தவும்</v>
+      </c>
       <c r="D427" s="5"/>
       <c r="E427" s="5"/>
     </row>
     <row r="428">
-      <c r="A428" s="3"/>
-      <c r="B428" s="4"/>
-      <c r="C428" s="5"/>
+      <c r="A428" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="B428" s="10" t="s">
+        <v>699</v>
+      </c>
+      <c r="C428" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B428, ""en"", ""ta"")"),"நிராகரி")</f>
+        <v>நிராகரி</v>
+      </c>
       <c r="D428" s="5"/>
       <c r="E428" s="5"/>
     </row>
     <row r="429">
-      <c r="A429" s="3"/>
-      <c r="B429" s="4"/>
-      <c r="C429" s="5"/>
+      <c r="A429" s="9" t="s">
+        <v>824</v>
+      </c>
+      <c r="B429" s="10" t="s">
+        <v>825</v>
+      </c>
+      <c r="C429" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B429, ""en"", ""ta"")"),"ஏற்றுக்கொள்")</f>
+        <v>ஏற்றுக்கொள்</v>
+      </c>
       <c r="D429" s="5"/>
       <c r="E429" s="5"/>
     </row>
     <row r="430">
-      <c r="A430" s="3"/>
-      <c r="B430" s="4"/>
-      <c r="C430" s="5"/>
+      <c r="A430" s="9" t="s">
+        <v>826</v>
+      </c>
+      <c r="B430" s="10" t="s">
+        <v>827</v>
+      </c>
+      <c r="C430" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B430, ""en"", ""ta"")"),"அமைப்புகள்")</f>
+        <v>அமைப்புகள்</v>
+      </c>
       <c r="D430" s="5"/>
       <c r="E430" s="5"/>
     </row>
@@ -9563,7 +9973,7 @@
       <c r="E591" s="5"/>
     </row>
     <row r="592">
-      <c r="A592" s="9"/>
+      <c r="A592" s="11"/>
       <c r="B592" s="4"/>
       <c r="C592" s="5"/>
       <c r="D592" s="5"/>
@@ -10761,7 +11171,7 @@
     </row>
     <row r="763">
       <c r="A763" s="3"/>
-      <c r="B763" s="10"/>
+      <c r="B763" s="12"/>
       <c r="C763" s="5"/>
       <c r="D763" s="5"/>
       <c r="E763" s="5"/>
@@ -11216,7 +11626,7 @@
     </row>
     <row r="828">
       <c r="A828" s="7"/>
-      <c r="B828" s="11"/>
+      <c r="B828" s="13"/>
       <c r="C828" s="5"/>
       <c r="D828" s="5"/>
       <c r="E828" s="5"/>
@@ -14968,4830 +15378,4830 @@
     </row>
     <row r="1364">
       <c r="A1364" s="6"/>
-      <c r="B1364" s="11"/>
+      <c r="B1364" s="13"/>
       <c r="C1364" s="6"/>
       <c r="D1364" s="6"/>
       <c r="E1364" s="6"/>
     </row>
     <row r="1365">
       <c r="A1365" s="6"/>
-      <c r="B1365" s="11"/>
+      <c r="B1365" s="13"/>
       <c r="C1365" s="6"/>
       <c r="D1365" s="6"/>
       <c r="E1365" s="6"/>
     </row>
     <row r="1366">
       <c r="A1366" s="6"/>
-      <c r="B1366" s="11"/>
+      <c r="B1366" s="13"/>
       <c r="C1366" s="6"/>
       <c r="D1366" s="6"/>
       <c r="E1366" s="6"/>
     </row>
     <row r="1367">
       <c r="A1367" s="6"/>
-      <c r="B1367" s="11"/>
+      <c r="B1367" s="13"/>
       <c r="C1367" s="6"/>
       <c r="D1367" s="6"/>
       <c r="E1367" s="6"/>
     </row>
     <row r="1368">
       <c r="A1368" s="6"/>
-      <c r="B1368" s="11"/>
+      <c r="B1368" s="13"/>
       <c r="C1368" s="6"/>
       <c r="D1368" s="6"/>
       <c r="E1368" s="6"/>
     </row>
     <row r="1369">
       <c r="A1369" s="6"/>
-      <c r="B1369" s="11"/>
+      <c r="B1369" s="13"/>
       <c r="C1369" s="6"/>
       <c r="D1369" s="6"/>
       <c r="E1369" s="6"/>
     </row>
     <row r="1370">
       <c r="A1370" s="6"/>
-      <c r="B1370" s="11"/>
+      <c r="B1370" s="13"/>
       <c r="C1370" s="6"/>
       <c r="D1370" s="6"/>
       <c r="E1370" s="6"/>
     </row>
     <row r="1371">
       <c r="A1371" s="6"/>
-      <c r="B1371" s="11"/>
+      <c r="B1371" s="13"/>
       <c r="C1371" s="6"/>
       <c r="D1371" s="6"/>
       <c r="E1371" s="6"/>
     </row>
     <row r="1372">
       <c r="A1372" s="6"/>
-      <c r="B1372" s="11"/>
+      <c r="B1372" s="13"/>
       <c r="C1372" s="6"/>
       <c r="D1372" s="6"/>
       <c r="E1372" s="6"/>
     </row>
     <row r="1373">
       <c r="A1373" s="6"/>
-      <c r="B1373" s="11"/>
+      <c r="B1373" s="13"/>
       <c r="C1373" s="6"/>
       <c r="D1373" s="6"/>
       <c r="E1373" s="6"/>
     </row>
     <row r="1374">
       <c r="A1374" s="6"/>
-      <c r="B1374" s="11"/>
+      <c r="B1374" s="13"/>
       <c r="C1374" s="6"/>
       <c r="D1374" s="6"/>
       <c r="E1374" s="6"/>
     </row>
     <row r="1375">
       <c r="A1375" s="6"/>
-      <c r="B1375" s="11"/>
+      <c r="B1375" s="13"/>
       <c r="C1375" s="6"/>
       <c r="D1375" s="6"/>
       <c r="E1375" s="6"/>
     </row>
     <row r="1376">
       <c r="A1376" s="6"/>
-      <c r="B1376" s="11"/>
+      <c r="B1376" s="13"/>
       <c r="C1376" s="6"/>
       <c r="D1376" s="6"/>
       <c r="E1376" s="6"/>
     </row>
     <row r="1377">
       <c r="A1377" s="6"/>
-      <c r="B1377" s="11"/>
+      <c r="B1377" s="13"/>
       <c r="C1377" s="6"/>
       <c r="D1377" s="6"/>
       <c r="E1377" s="6"/>
     </row>
     <row r="1378">
       <c r="A1378" s="6"/>
-      <c r="B1378" s="11"/>
+      <c r="B1378" s="13"/>
       <c r="C1378" s="6"/>
       <c r="D1378" s="6"/>
       <c r="E1378" s="6"/>
     </row>
     <row r="1379">
       <c r="A1379" s="6"/>
-      <c r="B1379" s="11"/>
+      <c r="B1379" s="13"/>
       <c r="C1379" s="6"/>
       <c r="D1379" s="6"/>
       <c r="E1379" s="6"/>
     </row>
     <row r="1380">
       <c r="A1380" s="6"/>
-      <c r="B1380" s="11"/>
+      <c r="B1380" s="13"/>
       <c r="C1380" s="6"/>
       <c r="D1380" s="6"/>
       <c r="E1380" s="6"/>
     </row>
     <row r="1381">
       <c r="A1381" s="6"/>
-      <c r="B1381" s="11"/>
+      <c r="B1381" s="13"/>
       <c r="C1381" s="6"/>
       <c r="D1381" s="6"/>
       <c r="E1381" s="6"/>
     </row>
     <row r="1382">
       <c r="A1382" s="6"/>
-      <c r="B1382" s="11"/>
+      <c r="B1382" s="13"/>
       <c r="C1382" s="6"/>
       <c r="D1382" s="6"/>
       <c r="E1382" s="6"/>
     </row>
     <row r="1383">
       <c r="A1383" s="6"/>
-      <c r="B1383" s="11"/>
+      <c r="B1383" s="13"/>
       <c r="C1383" s="6"/>
       <c r="D1383" s="6"/>
       <c r="E1383" s="6"/>
     </row>
     <row r="1384">
       <c r="A1384" s="6"/>
-      <c r="B1384" s="11"/>
+      <c r="B1384" s="13"/>
       <c r="C1384" s="6"/>
       <c r="D1384" s="6"/>
       <c r="E1384" s="6"/>
     </row>
     <row r="1385">
       <c r="A1385" s="6"/>
-      <c r="B1385" s="11"/>
+      <c r="B1385" s="13"/>
       <c r="C1385" s="6"/>
       <c r="D1385" s="6"/>
       <c r="E1385" s="6"/>
     </row>
     <row r="1386">
       <c r="A1386" s="6"/>
-      <c r="B1386" s="11"/>
+      <c r="B1386" s="13"/>
       <c r="C1386" s="6"/>
       <c r="D1386" s="6"/>
       <c r="E1386" s="6"/>
     </row>
     <row r="1387">
       <c r="A1387" s="6"/>
-      <c r="B1387" s="11"/>
+      <c r="B1387" s="13"/>
       <c r="C1387" s="6"/>
       <c r="D1387" s="6"/>
       <c r="E1387" s="6"/>
     </row>
     <row r="1388">
       <c r="A1388" s="6"/>
-      <c r="B1388" s="11"/>
+      <c r="B1388" s="13"/>
       <c r="C1388" s="6"/>
       <c r="D1388" s="6"/>
       <c r="E1388" s="6"/>
     </row>
     <row r="1389">
       <c r="A1389" s="6"/>
-      <c r="B1389" s="11"/>
+      <c r="B1389" s="13"/>
       <c r="C1389" s="6"/>
       <c r="D1389" s="6"/>
       <c r="E1389" s="6"/>
     </row>
     <row r="1390">
       <c r="A1390" s="6"/>
-      <c r="B1390" s="11"/>
+      <c r="B1390" s="13"/>
       <c r="C1390" s="6"/>
       <c r="D1390" s="6"/>
       <c r="E1390" s="6"/>
     </row>
     <row r="1391">
       <c r="A1391" s="6"/>
-      <c r="B1391" s="11"/>
+      <c r="B1391" s="13"/>
       <c r="C1391" s="6"/>
       <c r="D1391" s="6"/>
       <c r="E1391" s="6"/>
     </row>
     <row r="1392">
       <c r="A1392" s="6"/>
-      <c r="B1392" s="11"/>
+      <c r="B1392" s="13"/>
       <c r="C1392" s="6"/>
       <c r="D1392" s="6"/>
       <c r="E1392" s="6"/>
     </row>
     <row r="1393">
       <c r="A1393" s="6"/>
-      <c r="B1393" s="11"/>
+      <c r="B1393" s="13"/>
       <c r="C1393" s="6"/>
       <c r="D1393" s="6"/>
       <c r="E1393" s="6"/>
     </row>
     <row r="1394">
       <c r="A1394" s="6"/>
-      <c r="B1394" s="11"/>
+      <c r="B1394" s="13"/>
       <c r="C1394" s="6"/>
       <c r="D1394" s="6"/>
       <c r="E1394" s="6"/>
     </row>
     <row r="1395">
       <c r="A1395" s="6"/>
-      <c r="B1395" s="11"/>
+      <c r="B1395" s="13"/>
       <c r="C1395" s="6"/>
       <c r="D1395" s="6"/>
       <c r="E1395" s="6"/>
     </row>
     <row r="1396">
       <c r="A1396" s="6"/>
-      <c r="B1396" s="11"/>
+      <c r="B1396" s="13"/>
       <c r="C1396" s="6"/>
       <c r="D1396" s="6"/>
       <c r="E1396" s="6"/>
     </row>
     <row r="1397">
       <c r="A1397" s="6"/>
-      <c r="B1397" s="11"/>
+      <c r="B1397" s="13"/>
       <c r="C1397" s="6"/>
       <c r="D1397" s="6"/>
       <c r="E1397" s="6"/>
     </row>
     <row r="1398">
       <c r="A1398" s="6"/>
-      <c r="B1398" s="11"/>
+      <c r="B1398" s="13"/>
       <c r="C1398" s="6"/>
       <c r="D1398" s="6"/>
       <c r="E1398" s="6"/>
     </row>
     <row r="1399">
       <c r="A1399" s="6"/>
-      <c r="B1399" s="11"/>
+      <c r="B1399" s="13"/>
       <c r="C1399" s="6"/>
       <c r="D1399" s="6"/>
       <c r="E1399" s="6"/>
     </row>
     <row r="1400">
       <c r="A1400" s="6"/>
-      <c r="B1400" s="11"/>
+      <c r="B1400" s="13"/>
       <c r="C1400" s="6"/>
       <c r="D1400" s="6"/>
       <c r="E1400" s="6"/>
     </row>
     <row r="1401">
       <c r="A1401" s="6"/>
-      <c r="B1401" s="11"/>
+      <c r="B1401" s="13"/>
       <c r="C1401" s="6"/>
       <c r="D1401" s="6"/>
       <c r="E1401" s="6"/>
     </row>
     <row r="1402">
       <c r="A1402" s="6"/>
-      <c r="B1402" s="11"/>
+      <c r="B1402" s="13"/>
       <c r="C1402" s="6"/>
       <c r="D1402" s="6"/>
       <c r="E1402" s="6"/>
     </row>
     <row r="1403">
       <c r="A1403" s="6"/>
-      <c r="B1403" s="11"/>
+      <c r="B1403" s="13"/>
       <c r="C1403" s="6"/>
       <c r="D1403" s="6"/>
       <c r="E1403" s="6"/>
     </row>
     <row r="1404">
       <c r="A1404" s="6"/>
-      <c r="B1404" s="11"/>
+      <c r="B1404" s="13"/>
       <c r="C1404" s="6"/>
       <c r="D1404" s="6"/>
       <c r="E1404" s="6"/>
     </row>
     <row r="1405">
       <c r="A1405" s="6"/>
-      <c r="B1405" s="11"/>
+      <c r="B1405" s="13"/>
       <c r="C1405" s="6"/>
       <c r="D1405" s="6"/>
       <c r="E1405" s="6"/>
     </row>
     <row r="1406">
       <c r="A1406" s="6"/>
-      <c r="B1406" s="11"/>
+      <c r="B1406" s="13"/>
       <c r="C1406" s="6"/>
       <c r="D1406" s="6"/>
       <c r="E1406" s="6"/>
     </row>
     <row r="1407">
       <c r="A1407" s="6"/>
-      <c r="B1407" s="11"/>
+      <c r="B1407" s="13"/>
       <c r="C1407" s="6"/>
       <c r="D1407" s="6"/>
       <c r="E1407" s="6"/>
     </row>
     <row r="1408">
       <c r="A1408" s="6"/>
-      <c r="B1408" s="11"/>
+      <c r="B1408" s="13"/>
       <c r="C1408" s="6"/>
       <c r="D1408" s="6"/>
       <c r="E1408" s="6"/>
     </row>
     <row r="1409">
       <c r="A1409" s="6"/>
-      <c r="B1409" s="11"/>
+      <c r="B1409" s="13"/>
       <c r="C1409" s="6"/>
       <c r="D1409" s="6"/>
       <c r="E1409" s="6"/>
     </row>
     <row r="1410">
       <c r="A1410" s="6"/>
-      <c r="B1410" s="11"/>
+      <c r="B1410" s="13"/>
       <c r="C1410" s="6"/>
       <c r="D1410" s="6"/>
       <c r="E1410" s="6"/>
     </row>
     <row r="1411">
       <c r="A1411" s="6"/>
-      <c r="B1411" s="11"/>
+      <c r="B1411" s="13"/>
       <c r="C1411" s="6"/>
       <c r="D1411" s="6"/>
       <c r="E1411" s="6"/>
     </row>
     <row r="1412">
       <c r="A1412" s="6"/>
-      <c r="B1412" s="11"/>
+      <c r="B1412" s="13"/>
       <c r="C1412" s="6"/>
       <c r="D1412" s="6"/>
       <c r="E1412" s="6"/>
     </row>
     <row r="1413">
       <c r="A1413" s="6"/>
-      <c r="B1413" s="11"/>
+      <c r="B1413" s="13"/>
       <c r="C1413" s="6"/>
       <c r="D1413" s="6"/>
       <c r="E1413" s="6"/>
     </row>
     <row r="1414">
       <c r="A1414" s="6"/>
-      <c r="B1414" s="11"/>
+      <c r="B1414" s="13"/>
       <c r="C1414" s="6"/>
       <c r="D1414" s="6"/>
       <c r="E1414" s="6"/>
     </row>
     <row r="1415">
       <c r="A1415" s="6"/>
-      <c r="B1415" s="11"/>
+      <c r="B1415" s="13"/>
       <c r="C1415" s="6"/>
       <c r="D1415" s="6"/>
       <c r="E1415" s="6"/>
     </row>
     <row r="1416">
       <c r="A1416" s="6"/>
-      <c r="B1416" s="11"/>
+      <c r="B1416" s="13"/>
       <c r="C1416" s="6"/>
       <c r="D1416" s="6"/>
       <c r="E1416" s="6"/>
     </row>
     <row r="1417">
       <c r="A1417" s="6"/>
-      <c r="B1417" s="11"/>
+      <c r="B1417" s="13"/>
       <c r="C1417" s="6"/>
       <c r="D1417" s="6"/>
       <c r="E1417" s="6"/>
     </row>
     <row r="1418">
       <c r="A1418" s="6"/>
-      <c r="B1418" s="11"/>
+      <c r="B1418" s="13"/>
       <c r="C1418" s="6"/>
       <c r="D1418" s="6"/>
       <c r="E1418" s="6"/>
     </row>
     <row r="1419">
       <c r="A1419" s="6"/>
-      <c r="B1419" s="11"/>
+      <c r="B1419" s="13"/>
       <c r="C1419" s="6"/>
       <c r="D1419" s="6"/>
       <c r="E1419" s="6"/>
     </row>
     <row r="1420">
       <c r="A1420" s="6"/>
-      <c r="B1420" s="11"/>
+      <c r="B1420" s="13"/>
       <c r="C1420" s="6"/>
       <c r="D1420" s="6"/>
       <c r="E1420" s="6"/>
     </row>
     <row r="1421">
       <c r="A1421" s="6"/>
-      <c r="B1421" s="11"/>
+      <c r="B1421" s="13"/>
       <c r="C1421" s="6"/>
       <c r="D1421" s="6"/>
       <c r="E1421" s="6"/>
     </row>
     <row r="1422">
       <c r="A1422" s="6"/>
-      <c r="B1422" s="11"/>
+      <c r="B1422" s="13"/>
       <c r="C1422" s="6"/>
       <c r="D1422" s="6"/>
       <c r="E1422" s="6"/>
     </row>
     <row r="1423">
       <c r="A1423" s="6"/>
-      <c r="B1423" s="11"/>
+      <c r="B1423" s="13"/>
       <c r="C1423" s="6"/>
       <c r="D1423" s="6"/>
       <c r="E1423" s="6"/>
     </row>
     <row r="1424">
       <c r="A1424" s="6"/>
-      <c r="B1424" s="11"/>
+      <c r="B1424" s="13"/>
       <c r="C1424" s="6"/>
       <c r="D1424" s="6"/>
       <c r="E1424" s="6"/>
     </row>
     <row r="1425">
       <c r="A1425" s="6"/>
-      <c r="B1425" s="11"/>
+      <c r="B1425" s="13"/>
       <c r="C1425" s="6"/>
       <c r="D1425" s="6"/>
       <c r="E1425" s="6"/>
     </row>
     <row r="1426">
       <c r="A1426" s="6"/>
-      <c r="B1426" s="11"/>
+      <c r="B1426" s="13"/>
       <c r="C1426" s="6"/>
       <c r="D1426" s="6"/>
       <c r="E1426" s="6"/>
     </row>
     <row r="1427">
       <c r="A1427" s="6"/>
-      <c r="B1427" s="11"/>
+      <c r="B1427" s="13"/>
       <c r="C1427" s="6"/>
       <c r="D1427" s="6"/>
       <c r="E1427" s="6"/>
     </row>
     <row r="1428">
       <c r="A1428" s="6"/>
-      <c r="B1428" s="11"/>
+      <c r="B1428" s="13"/>
       <c r="C1428" s="6"/>
       <c r="D1428" s="6"/>
       <c r="E1428" s="6"/>
     </row>
     <row r="1429">
       <c r="A1429" s="6"/>
-      <c r="B1429" s="11"/>
+      <c r="B1429" s="13"/>
       <c r="C1429" s="6"/>
       <c r="D1429" s="6"/>
       <c r="E1429" s="6"/>
     </row>
     <row r="1430">
       <c r="A1430" s="6"/>
-      <c r="B1430" s="11"/>
+      <c r="B1430" s="13"/>
       <c r="C1430" s="6"/>
       <c r="D1430" s="6"/>
       <c r="E1430" s="6"/>
     </row>
     <row r="1431">
       <c r="A1431" s="6"/>
-      <c r="B1431" s="11"/>
+      <c r="B1431" s="13"/>
       <c r="C1431" s="6"/>
       <c r="D1431" s="6"/>
       <c r="E1431" s="6"/>
     </row>
     <row r="1432">
       <c r="A1432" s="6"/>
-      <c r="B1432" s="11"/>
+      <c r="B1432" s="13"/>
       <c r="C1432" s="6"/>
       <c r="D1432" s="6"/>
       <c r="E1432" s="6"/>
     </row>
     <row r="1433">
       <c r="A1433" s="6"/>
-      <c r="B1433" s="11"/>
+      <c r="B1433" s="13"/>
       <c r="C1433" s="6"/>
       <c r="D1433" s="6"/>
       <c r="E1433" s="6"/>
     </row>
     <row r="1434">
       <c r="A1434" s="6"/>
-      <c r="B1434" s="11"/>
+      <c r="B1434" s="13"/>
       <c r="C1434" s="6"/>
       <c r="D1434" s="6"/>
       <c r="E1434" s="6"/>
     </row>
     <row r="1435">
       <c r="A1435" s="6"/>
-      <c r="B1435" s="11"/>
+      <c r="B1435" s="13"/>
       <c r="C1435" s="6"/>
       <c r="D1435" s="6"/>
       <c r="E1435" s="6"/>
     </row>
     <row r="1436">
       <c r="A1436" s="6"/>
-      <c r="B1436" s="11"/>
+      <c r="B1436" s="13"/>
       <c r="C1436" s="6"/>
       <c r="D1436" s="6"/>
       <c r="E1436" s="6"/>
     </row>
     <row r="1437">
       <c r="A1437" s="6"/>
-      <c r="B1437" s="11"/>
+      <c r="B1437" s="13"/>
       <c r="C1437" s="6"/>
       <c r="D1437" s="6"/>
       <c r="E1437" s="6"/>
     </row>
     <row r="1438">
       <c r="A1438" s="6"/>
-      <c r="B1438" s="11"/>
+      <c r="B1438" s="13"/>
       <c r="C1438" s="6"/>
       <c r="D1438" s="6"/>
       <c r="E1438" s="6"/>
     </row>
     <row r="1439">
       <c r="A1439" s="6"/>
-      <c r="B1439" s="11"/>
+      <c r="B1439" s="13"/>
       <c r="C1439" s="6"/>
       <c r="D1439" s="6"/>
       <c r="E1439" s="6"/>
     </row>
     <row r="1440">
       <c r="A1440" s="6"/>
-      <c r="B1440" s="11"/>
+      <c r="B1440" s="13"/>
       <c r="C1440" s="6"/>
       <c r="D1440" s="6"/>
       <c r="E1440" s="6"/>
     </row>
     <row r="1441">
       <c r="A1441" s="6"/>
-      <c r="B1441" s="11"/>
+      <c r="B1441" s="13"/>
       <c r="C1441" s="6"/>
       <c r="D1441" s="6"/>
       <c r="E1441" s="6"/>
     </row>
     <row r="1442">
       <c r="A1442" s="6"/>
-      <c r="B1442" s="11"/>
+      <c r="B1442" s="13"/>
       <c r="C1442" s="6"/>
       <c r="D1442" s="6"/>
       <c r="E1442" s="6"/>
     </row>
     <row r="1443">
       <c r="A1443" s="6"/>
-      <c r="B1443" s="11"/>
+      <c r="B1443" s="13"/>
       <c r="C1443" s="6"/>
       <c r="D1443" s="6"/>
       <c r="E1443" s="6"/>
     </row>
     <row r="1444">
       <c r="A1444" s="6"/>
-      <c r="B1444" s="11"/>
+      <c r="B1444" s="13"/>
       <c r="C1444" s="6"/>
       <c r="D1444" s="6"/>
       <c r="E1444" s="6"/>
     </row>
     <row r="1445">
       <c r="A1445" s="6"/>
-      <c r="B1445" s="11"/>
+      <c r="B1445" s="13"/>
       <c r="C1445" s="6"/>
       <c r="D1445" s="6"/>
       <c r="E1445" s="6"/>
     </row>
     <row r="1446">
       <c r="A1446" s="6"/>
-      <c r="B1446" s="11"/>
+      <c r="B1446" s="13"/>
       <c r="C1446" s="6"/>
       <c r="D1446" s="6"/>
       <c r="E1446" s="6"/>
     </row>
     <row r="1447">
       <c r="A1447" s="6"/>
-      <c r="B1447" s="11"/>
+      <c r="B1447" s="13"/>
       <c r="C1447" s="6"/>
       <c r="D1447" s="6"/>
       <c r="E1447" s="6"/>
     </row>
     <row r="1448">
       <c r="A1448" s="6"/>
-      <c r="B1448" s="11"/>
+      <c r="B1448" s="13"/>
       <c r="C1448" s="6"/>
       <c r="D1448" s="6"/>
       <c r="E1448" s="6"/>
     </row>
     <row r="1449">
       <c r="A1449" s="6"/>
-      <c r="B1449" s="11"/>
+      <c r="B1449" s="13"/>
       <c r="C1449" s="6"/>
       <c r="D1449" s="6"/>
       <c r="E1449" s="6"/>
     </row>
     <row r="1450">
       <c r="A1450" s="6"/>
-      <c r="B1450" s="11"/>
+      <c r="B1450" s="13"/>
       <c r="C1450" s="6"/>
       <c r="D1450" s="6"/>
       <c r="E1450" s="6"/>
     </row>
     <row r="1451">
       <c r="A1451" s="6"/>
-      <c r="B1451" s="11"/>
+      <c r="B1451" s="13"/>
       <c r="C1451" s="6"/>
       <c r="D1451" s="6"/>
       <c r="E1451" s="6"/>
     </row>
     <row r="1452">
       <c r="A1452" s="6"/>
-      <c r="B1452" s="11"/>
+      <c r="B1452" s="13"/>
       <c r="C1452" s="6"/>
       <c r="D1452" s="6"/>
       <c r="E1452" s="6"/>
     </row>
     <row r="1453">
       <c r="A1453" s="6"/>
-      <c r="B1453" s="11"/>
+      <c r="B1453" s="13"/>
       <c r="C1453" s="6"/>
       <c r="D1453" s="6"/>
       <c r="E1453" s="6"/>
     </row>
     <row r="1454">
       <c r="A1454" s="6"/>
-      <c r="B1454" s="11"/>
+      <c r="B1454" s="13"/>
       <c r="C1454" s="6"/>
       <c r="D1454" s="6"/>
       <c r="E1454" s="6"/>
     </row>
     <row r="1455">
       <c r="A1455" s="6"/>
-      <c r="B1455" s="11"/>
+      <c r="B1455" s="13"/>
       <c r="C1455" s="6"/>
       <c r="D1455" s="6"/>
       <c r="E1455" s="6"/>
     </row>
     <row r="1456">
       <c r="A1456" s="6"/>
-      <c r="B1456" s="11"/>
+      <c r="B1456" s="13"/>
       <c r="C1456" s="6"/>
       <c r="D1456" s="6"/>
       <c r="E1456" s="6"/>
     </row>
     <row r="1457">
       <c r="A1457" s="6"/>
-      <c r="B1457" s="11"/>
+      <c r="B1457" s="13"/>
       <c r="C1457" s="6"/>
       <c r="D1457" s="6"/>
       <c r="E1457" s="6"/>
     </row>
     <row r="1458">
       <c r="A1458" s="6"/>
-      <c r="B1458" s="11"/>
+      <c r="B1458" s="13"/>
       <c r="C1458" s="6"/>
       <c r="D1458" s="6"/>
       <c r="E1458" s="6"/>
     </row>
     <row r="1459">
       <c r="A1459" s="6"/>
-      <c r="B1459" s="11"/>
+      <c r="B1459" s="13"/>
       <c r="C1459" s="6"/>
       <c r="D1459" s="6"/>
       <c r="E1459" s="6"/>
     </row>
     <row r="1460">
       <c r="A1460" s="6"/>
-      <c r="B1460" s="11"/>
+      <c r="B1460" s="13"/>
       <c r="C1460" s="6"/>
       <c r="D1460" s="6"/>
       <c r="E1460" s="6"/>
     </row>
     <row r="1461">
       <c r="A1461" s="6"/>
-      <c r="B1461" s="11"/>
+      <c r="B1461" s="13"/>
       <c r="C1461" s="6"/>
       <c r="D1461" s="6"/>
       <c r="E1461" s="6"/>
     </row>
     <row r="1462">
       <c r="A1462" s="6"/>
-      <c r="B1462" s="11"/>
+      <c r="B1462" s="13"/>
       <c r="C1462" s="6"/>
       <c r="D1462" s="6"/>
       <c r="E1462" s="6"/>
     </row>
     <row r="1463">
       <c r="A1463" s="6"/>
-      <c r="B1463" s="11"/>
+      <c r="B1463" s="13"/>
       <c r="C1463" s="6"/>
       <c r="D1463" s="6"/>
       <c r="E1463" s="6"/>
     </row>
     <row r="1464">
       <c r="A1464" s="6"/>
-      <c r="B1464" s="11"/>
+      <c r="B1464" s="13"/>
       <c r="C1464" s="6"/>
       <c r="D1464" s="6"/>
       <c r="E1464" s="6"/>
     </row>
     <row r="1465">
       <c r="A1465" s="6"/>
-      <c r="B1465" s="11"/>
+      <c r="B1465" s="13"/>
       <c r="C1465" s="6"/>
       <c r="D1465" s="6"/>
       <c r="E1465" s="6"/>
     </row>
     <row r="1466">
       <c r="A1466" s="6"/>
-      <c r="B1466" s="11"/>
+      <c r="B1466" s="13"/>
       <c r="C1466" s="6"/>
       <c r="D1466" s="6"/>
       <c r="E1466" s="6"/>
     </row>
     <row r="1467">
       <c r="A1467" s="6"/>
-      <c r="B1467" s="11"/>
+      <c r="B1467" s="13"/>
       <c r="C1467" s="6"/>
       <c r="D1467" s="6"/>
       <c r="E1467" s="6"/>
     </row>
     <row r="1468">
       <c r="A1468" s="6"/>
-      <c r="B1468" s="11"/>
+      <c r="B1468" s="13"/>
       <c r="C1468" s="6"/>
       <c r="D1468" s="6"/>
       <c r="E1468" s="6"/>
     </row>
     <row r="1469">
       <c r="A1469" s="6"/>
-      <c r="B1469" s="11"/>
+      <c r="B1469" s="13"/>
       <c r="C1469" s="6"/>
       <c r="D1469" s="6"/>
       <c r="E1469" s="6"/>
     </row>
     <row r="1470">
       <c r="A1470" s="6"/>
-      <c r="B1470" s="11"/>
+      <c r="B1470" s="13"/>
       <c r="C1470" s="6"/>
       <c r="D1470" s="6"/>
       <c r="E1470" s="6"/>
     </row>
     <row r="1471">
       <c r="A1471" s="6"/>
-      <c r="B1471" s="11"/>
+      <c r="B1471" s="13"/>
       <c r="C1471" s="6"/>
       <c r="D1471" s="6"/>
       <c r="E1471" s="6"/>
     </row>
     <row r="1472">
       <c r="A1472" s="6"/>
-      <c r="B1472" s="11"/>
+      <c r="B1472" s="13"/>
       <c r="C1472" s="6"/>
       <c r="D1472" s="6"/>
       <c r="E1472" s="6"/>
     </row>
     <row r="1473">
       <c r="A1473" s="6"/>
-      <c r="B1473" s="11"/>
+      <c r="B1473" s="13"/>
       <c r="C1473" s="6"/>
       <c r="D1473" s="6"/>
       <c r="E1473" s="6"/>
     </row>
     <row r="1474">
       <c r="A1474" s="6"/>
-      <c r="B1474" s="11"/>
+      <c r="B1474" s="13"/>
       <c r="C1474" s="6"/>
       <c r="D1474" s="6"/>
       <c r="E1474" s="6"/>
     </row>
     <row r="1475">
       <c r="A1475" s="6"/>
-      <c r="B1475" s="11"/>
+      <c r="B1475" s="13"/>
       <c r="C1475" s="6"/>
       <c r="D1475" s="6"/>
       <c r="E1475" s="6"/>
     </row>
     <row r="1476">
       <c r="A1476" s="6"/>
-      <c r="B1476" s="11"/>
+      <c r="B1476" s="13"/>
       <c r="C1476" s="6"/>
       <c r="D1476" s="6"/>
       <c r="E1476" s="6"/>
     </row>
     <row r="1477">
       <c r="A1477" s="6"/>
-      <c r="B1477" s="11"/>
+      <c r="B1477" s="13"/>
       <c r="C1477" s="6"/>
       <c r="D1477" s="6"/>
       <c r="E1477" s="6"/>
     </row>
     <row r="1478">
       <c r="A1478" s="6"/>
-      <c r="B1478" s="11"/>
+      <c r="B1478" s="13"/>
       <c r="C1478" s="6"/>
       <c r="D1478" s="6"/>
       <c r="E1478" s="6"/>
     </row>
     <row r="1479">
       <c r="A1479" s="6"/>
-      <c r="B1479" s="11"/>
+      <c r="B1479" s="13"/>
       <c r="C1479" s="6"/>
       <c r="D1479" s="6"/>
       <c r="E1479" s="6"/>
     </row>
     <row r="1480">
       <c r="A1480" s="6"/>
-      <c r="B1480" s="11"/>
+      <c r="B1480" s="13"/>
       <c r="C1480" s="6"/>
       <c r="D1480" s="6"/>
       <c r="E1480" s="6"/>
     </row>
     <row r="1481">
       <c r="A1481" s="6"/>
-      <c r="B1481" s="11"/>
+      <c r="B1481" s="13"/>
       <c r="C1481" s="6"/>
       <c r="D1481" s="6"/>
       <c r="E1481" s="6"/>
     </row>
     <row r="1482">
       <c r="A1482" s="6"/>
-      <c r="B1482" s="11"/>
+      <c r="B1482" s="13"/>
       <c r="C1482" s="6"/>
       <c r="D1482" s="6"/>
       <c r="E1482" s="6"/>
     </row>
     <row r="1483">
       <c r="A1483" s="6"/>
-      <c r="B1483" s="11"/>
+      <c r="B1483" s="13"/>
       <c r="C1483" s="6"/>
       <c r="D1483" s="6"/>
       <c r="E1483" s="6"/>
     </row>
     <row r="1484">
       <c r="A1484" s="6"/>
-      <c r="B1484" s="11"/>
+      <c r="B1484" s="13"/>
       <c r="C1484" s="6"/>
       <c r="D1484" s="6"/>
       <c r="E1484" s="6"/>
     </row>
     <row r="1485">
       <c r="A1485" s="6"/>
-      <c r="B1485" s="11"/>
+      <c r="B1485" s="13"/>
       <c r="C1485" s="6"/>
       <c r="D1485" s="6"/>
       <c r="E1485" s="6"/>
     </row>
     <row r="1486">
       <c r="A1486" s="6"/>
-      <c r="B1486" s="11"/>
+      <c r="B1486" s="13"/>
       <c r="C1486" s="6"/>
       <c r="D1486" s="6"/>
       <c r="E1486" s="6"/>
     </row>
     <row r="1487">
       <c r="A1487" s="6"/>
-      <c r="B1487" s="11"/>
+      <c r="B1487" s="13"/>
       <c r="C1487" s="6"/>
       <c r="D1487" s="6"/>
       <c r="E1487" s="6"/>
     </row>
     <row r="1488">
       <c r="A1488" s="6"/>
-      <c r="B1488" s="11"/>
+      <c r="B1488" s="13"/>
       <c r="C1488" s="6"/>
       <c r="D1488" s="6"/>
       <c r="E1488" s="6"/>
     </row>
     <row r="1489">
       <c r="A1489" s="6"/>
-      <c r="B1489" s="11"/>
+      <c r="B1489" s="13"/>
       <c r="C1489" s="6"/>
       <c r="D1489" s="6"/>
       <c r="E1489" s="6"/>
     </row>
     <row r="1490">
       <c r="A1490" s="6"/>
-      <c r="B1490" s="11"/>
+      <c r="B1490" s="13"/>
       <c r="C1490" s="6"/>
       <c r="D1490" s="6"/>
       <c r="E1490" s="6"/>
     </row>
     <row r="1491">
       <c r="A1491" s="6"/>
-      <c r="B1491" s="11"/>
+      <c r="B1491" s="13"/>
       <c r="C1491" s="6"/>
       <c r="D1491" s="6"/>
       <c r="E1491" s="6"/>
     </row>
     <row r="1492">
       <c r="A1492" s="6"/>
-      <c r="B1492" s="11"/>
+      <c r="B1492" s="13"/>
       <c r="C1492" s="6"/>
       <c r="D1492" s="6"/>
       <c r="E1492" s="6"/>
     </row>
     <row r="1493">
       <c r="A1493" s="6"/>
-      <c r="B1493" s="11"/>
+      <c r="B1493" s="13"/>
       <c r="C1493" s="6"/>
       <c r="D1493" s="6"/>
       <c r="E1493" s="6"/>
     </row>
     <row r="1494">
       <c r="A1494" s="6"/>
-      <c r="B1494" s="11"/>
+      <c r="B1494" s="13"/>
       <c r="C1494" s="6"/>
       <c r="D1494" s="6"/>
       <c r="E1494" s="6"/>
     </row>
     <row r="1495">
       <c r="A1495" s="6"/>
-      <c r="B1495" s="11"/>
+      <c r="B1495" s="13"/>
       <c r="C1495" s="6"/>
       <c r="D1495" s="6"/>
       <c r="E1495" s="6"/>
     </row>
     <row r="1496">
       <c r="A1496" s="6"/>
-      <c r="B1496" s="11"/>
+      <c r="B1496" s="13"/>
       <c r="C1496" s="6"/>
       <c r="D1496" s="6"/>
       <c r="E1496" s="6"/>
     </row>
     <row r="1497">
       <c r="A1497" s="6"/>
-      <c r="B1497" s="11"/>
+      <c r="B1497" s="13"/>
       <c r="C1497" s="6"/>
       <c r="D1497" s="6"/>
       <c r="E1497" s="6"/>
     </row>
     <row r="1498">
       <c r="A1498" s="6"/>
-      <c r="B1498" s="11"/>
+      <c r="B1498" s="13"/>
       <c r="C1498" s="6"/>
       <c r="D1498" s="6"/>
       <c r="E1498" s="6"/>
     </row>
     <row r="1499">
       <c r="A1499" s="6"/>
-      <c r="B1499" s="11"/>
+      <c r="B1499" s="13"/>
       <c r="C1499" s="6"/>
       <c r="D1499" s="6"/>
       <c r="E1499" s="6"/>
     </row>
     <row r="1500">
       <c r="A1500" s="6"/>
-      <c r="B1500" s="11"/>
+      <c r="B1500" s="13"/>
       <c r="C1500" s="6"/>
       <c r="D1500" s="6"/>
       <c r="E1500" s="6"/>
     </row>
     <row r="1501">
       <c r="A1501" s="6"/>
-      <c r="B1501" s="11"/>
+      <c r="B1501" s="13"/>
       <c r="C1501" s="6"/>
       <c r="D1501" s="6"/>
       <c r="E1501" s="6"/>
     </row>
     <row r="1502">
       <c r="A1502" s="6"/>
-      <c r="B1502" s="11"/>
+      <c r="B1502" s="13"/>
       <c r="C1502" s="6"/>
       <c r="D1502" s="6"/>
       <c r="E1502" s="6"/>
     </row>
     <row r="1503">
       <c r="A1503" s="6"/>
-      <c r="B1503" s="11"/>
+      <c r="B1503" s="13"/>
       <c r="C1503" s="6"/>
       <c r="D1503" s="6"/>
       <c r="E1503" s="6"/>
     </row>
     <row r="1504">
       <c r="A1504" s="6"/>
-      <c r="B1504" s="11"/>
+      <c r="B1504" s="13"/>
       <c r="C1504" s="6"/>
       <c r="D1504" s="6"/>
       <c r="E1504" s="6"/>
     </row>
     <row r="1505">
       <c r="A1505" s="6"/>
-      <c r="B1505" s="11"/>
+      <c r="B1505" s="13"/>
       <c r="C1505" s="6"/>
       <c r="D1505" s="6"/>
       <c r="E1505" s="6"/>
     </row>
     <row r="1506">
       <c r="A1506" s="6"/>
-      <c r="B1506" s="11"/>
+      <c r="B1506" s="13"/>
       <c r="C1506" s="6"/>
       <c r="D1506" s="6"/>
       <c r="E1506" s="6"/>
     </row>
     <row r="1507">
       <c r="A1507" s="6"/>
-      <c r="B1507" s="11"/>
+      <c r="B1507" s="13"/>
       <c r="C1507" s="6"/>
       <c r="D1507" s="6"/>
       <c r="E1507" s="6"/>
     </row>
     <row r="1508">
       <c r="A1508" s="6"/>
-      <c r="B1508" s="11"/>
+      <c r="B1508" s="13"/>
       <c r="C1508" s="6"/>
       <c r="D1508" s="6"/>
       <c r="E1508" s="6"/>
     </row>
     <row r="1509">
       <c r="A1509" s="6"/>
-      <c r="B1509" s="11"/>
+      <c r="B1509" s="13"/>
       <c r="C1509" s="6"/>
       <c r="D1509" s="6"/>
       <c r="E1509" s="6"/>
     </row>
     <row r="1510">
       <c r="A1510" s="6"/>
-      <c r="B1510" s="11"/>
+      <c r="B1510" s="13"/>
       <c r="C1510" s="6"/>
       <c r="D1510" s="6"/>
       <c r="E1510" s="6"/>
     </row>
     <row r="1511">
       <c r="A1511" s="6"/>
-      <c r="B1511" s="11"/>
+      <c r="B1511" s="13"/>
       <c r="C1511" s="6"/>
       <c r="D1511" s="6"/>
       <c r="E1511" s="6"/>
     </row>
     <row r="1512">
       <c r="A1512" s="6"/>
-      <c r="B1512" s="11"/>
+      <c r="B1512" s="13"/>
       <c r="C1512" s="6"/>
       <c r="D1512" s="6"/>
       <c r="E1512" s="6"/>
     </row>
     <row r="1513">
       <c r="A1513" s="6"/>
-      <c r="B1513" s="11"/>
+      <c r="B1513" s="13"/>
       <c r="C1513" s="6"/>
       <c r="D1513" s="6"/>
       <c r="E1513" s="6"/>
     </row>
     <row r="1514">
       <c r="A1514" s="6"/>
-      <c r="B1514" s="11"/>
+      <c r="B1514" s="13"/>
       <c r="C1514" s="6"/>
       <c r="D1514" s="6"/>
       <c r="E1514" s="6"/>
     </row>
     <row r="1515">
       <c r="A1515" s="6"/>
-      <c r="B1515" s="11"/>
+      <c r="B1515" s="13"/>
       <c r="C1515" s="6"/>
       <c r="D1515" s="6"/>
       <c r="E1515" s="6"/>
     </row>
     <row r="1516">
       <c r="A1516" s="6"/>
-      <c r="B1516" s="11"/>
+      <c r="B1516" s="13"/>
       <c r="C1516" s="6"/>
       <c r="D1516" s="6"/>
       <c r="E1516" s="6"/>
     </row>
     <row r="1517">
       <c r="A1517" s="6"/>
-      <c r="B1517" s="11"/>
+      <c r="B1517" s="13"/>
       <c r="C1517" s="6"/>
       <c r="D1517" s="6"/>
       <c r="E1517" s="6"/>
     </row>
     <row r="1518">
       <c r="A1518" s="6"/>
-      <c r="B1518" s="11"/>
+      <c r="B1518" s="13"/>
       <c r="C1518" s="6"/>
       <c r="D1518" s="6"/>
       <c r="E1518" s="6"/>
     </row>
     <row r="1519">
       <c r="A1519" s="6"/>
-      <c r="B1519" s="11"/>
+      <c r="B1519" s="13"/>
       <c r="C1519" s="6"/>
       <c r="D1519" s="6"/>
       <c r="E1519" s="6"/>
     </row>
     <row r="1520">
       <c r="A1520" s="6"/>
-      <c r="B1520" s="11"/>
+      <c r="B1520" s="13"/>
       <c r="C1520" s="6"/>
       <c r="D1520" s="6"/>
       <c r="E1520" s="6"/>
     </row>
     <row r="1521">
       <c r="A1521" s="6"/>
-      <c r="B1521" s="11"/>
+      <c r="B1521" s="13"/>
       <c r="C1521" s="6"/>
       <c r="D1521" s="6"/>
       <c r="E1521" s="6"/>
     </row>
     <row r="1522">
       <c r="A1522" s="6"/>
-      <c r="B1522" s="11"/>
+      <c r="B1522" s="13"/>
       <c r="C1522" s="6"/>
       <c r="D1522" s="6"/>
       <c r="E1522" s="6"/>
     </row>
     <row r="1523">
       <c r="A1523" s="6"/>
-      <c r="B1523" s="11"/>
+      <c r="B1523" s="13"/>
       <c r="C1523" s="6"/>
       <c r="D1523" s="6"/>
       <c r="E1523" s="6"/>
     </row>
     <row r="1524">
       <c r="A1524" s="6"/>
-      <c r="B1524" s="11"/>
+      <c r="B1524" s="13"/>
       <c r="C1524" s="6"/>
       <c r="D1524" s="6"/>
       <c r="E1524" s="6"/>
     </row>
     <row r="1525">
       <c r="A1525" s="6"/>
-      <c r="B1525" s="11"/>
+      <c r="B1525" s="13"/>
       <c r="C1525" s="6"/>
       <c r="D1525" s="6"/>
       <c r="E1525" s="6"/>
     </row>
     <row r="1526">
       <c r="A1526" s="6"/>
-      <c r="B1526" s="11"/>
+      <c r="B1526" s="13"/>
       <c r="C1526" s="6"/>
       <c r="D1526" s="6"/>
       <c r="E1526" s="6"/>
     </row>
     <row r="1527">
       <c r="A1527" s="6"/>
-      <c r="B1527" s="11"/>
+      <c r="B1527" s="13"/>
       <c r="C1527" s="6"/>
       <c r="D1527" s="6"/>
       <c r="E1527" s="6"/>
     </row>
     <row r="1528">
       <c r="A1528" s="6"/>
-      <c r="B1528" s="11"/>
+      <c r="B1528" s="13"/>
       <c r="C1528" s="6"/>
       <c r="D1528" s="6"/>
       <c r="E1528" s="6"/>
     </row>
     <row r="1529">
       <c r="A1529" s="6"/>
-      <c r="B1529" s="11"/>
+      <c r="B1529" s="13"/>
       <c r="C1529" s="6"/>
       <c r="D1529" s="6"/>
       <c r="E1529" s="6"/>
     </row>
     <row r="1530">
       <c r="A1530" s="6"/>
-      <c r="B1530" s="11"/>
+      <c r="B1530" s="13"/>
       <c r="C1530" s="6"/>
       <c r="D1530" s="6"/>
       <c r="E1530" s="6"/>
     </row>
     <row r="1531">
       <c r="A1531" s="6"/>
-      <c r="B1531" s="11"/>
+      <c r="B1531" s="13"/>
       <c r="C1531" s="6"/>
       <c r="D1531" s="6"/>
       <c r="E1531" s="6"/>
     </row>
     <row r="1532">
       <c r="A1532" s="6"/>
-      <c r="B1532" s="11"/>
+      <c r="B1532" s="13"/>
       <c r="C1532" s="6"/>
       <c r="D1532" s="6"/>
       <c r="E1532" s="6"/>
     </row>
     <row r="1533">
       <c r="A1533" s="6"/>
-      <c r="B1533" s="11"/>
+      <c r="B1533" s="13"/>
       <c r="C1533" s="6"/>
       <c r="D1533" s="6"/>
       <c r="E1533" s="6"/>
     </row>
     <row r="1534">
       <c r="A1534" s="6"/>
-      <c r="B1534" s="11"/>
+      <c r="B1534" s="13"/>
       <c r="C1534" s="6"/>
       <c r="D1534" s="6"/>
       <c r="E1534" s="6"/>
     </row>
     <row r="1535">
       <c r="A1535" s="6"/>
-      <c r="B1535" s="11"/>
+      <c r="B1535" s="13"/>
       <c r="C1535" s="6"/>
       <c r="D1535" s="6"/>
       <c r="E1535" s="6"/>
     </row>
     <row r="1536">
       <c r="A1536" s="6"/>
-      <c r="B1536" s="11"/>
+      <c r="B1536" s="13"/>
       <c r="C1536" s="6"/>
       <c r="D1536" s="6"/>
       <c r="E1536" s="6"/>
     </row>
     <row r="1537">
       <c r="A1537" s="6"/>
-      <c r="B1537" s="11"/>
+      <c r="B1537" s="13"/>
       <c r="C1537" s="6"/>
       <c r="D1537" s="6"/>
       <c r="E1537" s="6"/>
     </row>
     <row r="1538">
       <c r="A1538" s="6"/>
-      <c r="B1538" s="11"/>
+      <c r="B1538" s="13"/>
       <c r="C1538" s="6"/>
       <c r="D1538" s="6"/>
       <c r="E1538" s="6"/>
     </row>
     <row r="1539">
       <c r="A1539" s="6"/>
-      <c r="B1539" s="11"/>
+      <c r="B1539" s="13"/>
       <c r="C1539" s="6"/>
       <c r="D1539" s="6"/>
       <c r="E1539" s="6"/>
     </row>
     <row r="1540">
       <c r="A1540" s="6"/>
-      <c r="B1540" s="11"/>
+      <c r="B1540" s="13"/>
       <c r="C1540" s="6"/>
       <c r="D1540" s="6"/>
       <c r="E1540" s="6"/>
     </row>
     <row r="1541">
       <c r="A1541" s="6"/>
-      <c r="B1541" s="11"/>
+      <c r="B1541" s="13"/>
       <c r="C1541" s="6"/>
       <c r="D1541" s="6"/>
       <c r="E1541" s="6"/>
     </row>
     <row r="1542">
       <c r="A1542" s="6"/>
-      <c r="B1542" s="11"/>
+      <c r="B1542" s="13"/>
       <c r="C1542" s="6"/>
       <c r="D1542" s="6"/>
       <c r="E1542" s="6"/>
     </row>
     <row r="1543">
       <c r="A1543" s="6"/>
-      <c r="B1543" s="11"/>
+      <c r="B1543" s="13"/>
       <c r="C1543" s="6"/>
       <c r="D1543" s="6"/>
       <c r="E1543" s="6"/>
     </row>
     <row r="1544">
       <c r="A1544" s="6"/>
-      <c r="B1544" s="11"/>
+      <c r="B1544" s="13"/>
       <c r="C1544" s="6"/>
       <c r="D1544" s="6"/>
       <c r="E1544" s="6"/>
     </row>
     <row r="1545">
       <c r="A1545" s="6"/>
-      <c r="B1545" s="11"/>
+      <c r="B1545" s="13"/>
       <c r="C1545" s="6"/>
       <c r="D1545" s="6"/>
       <c r="E1545" s="6"/>
     </row>
     <row r="1546">
       <c r="A1546" s="6"/>
-      <c r="B1546" s="11"/>
+      <c r="B1546" s="13"/>
       <c r="C1546" s="6"/>
       <c r="D1546" s="6"/>
       <c r="E1546" s="6"/>
     </row>
     <row r="1547">
       <c r="A1547" s="6"/>
-      <c r="B1547" s="11"/>
+      <c r="B1547" s="13"/>
       <c r="C1547" s="6"/>
       <c r="D1547" s="6"/>
       <c r="E1547" s="6"/>
     </row>
     <row r="1548">
       <c r="A1548" s="6"/>
-      <c r="B1548" s="11"/>
+      <c r="B1548" s="13"/>
       <c r="C1548" s="6"/>
       <c r="D1548" s="6"/>
       <c r="E1548" s="6"/>
     </row>
     <row r="1549">
       <c r="A1549" s="6"/>
-      <c r="B1549" s="11"/>
+      <c r="B1549" s="13"/>
       <c r="C1549" s="6"/>
       <c r="D1549" s="6"/>
       <c r="E1549" s="6"/>
     </row>
     <row r="1550">
       <c r="A1550" s="6"/>
-      <c r="B1550" s="11"/>
+      <c r="B1550" s="13"/>
       <c r="C1550" s="6"/>
       <c r="D1550" s="6"/>
       <c r="E1550" s="6"/>
     </row>
     <row r="1551">
       <c r="A1551" s="6"/>
-      <c r="B1551" s="11"/>
+      <c r="B1551" s="13"/>
       <c r="C1551" s="6"/>
       <c r="D1551" s="6"/>
       <c r="E1551" s="6"/>
     </row>
     <row r="1552">
       <c r="A1552" s="6"/>
-      <c r="B1552" s="11"/>
+      <c r="B1552" s="13"/>
       <c r="C1552" s="6"/>
       <c r="D1552" s="6"/>
       <c r="E1552" s="6"/>
     </row>
     <row r="1553">
       <c r="A1553" s="6"/>
-      <c r="B1553" s="11"/>
+      <c r="B1553" s="13"/>
       <c r="C1553" s="6"/>
       <c r="D1553" s="6"/>
       <c r="E1553" s="6"/>
     </row>
     <row r="1554">
       <c r="A1554" s="6"/>
-      <c r="B1554" s="11"/>
+      <c r="B1554" s="13"/>
       <c r="C1554" s="6"/>
       <c r="D1554" s="6"/>
       <c r="E1554" s="6"/>
     </row>
     <row r="1555">
       <c r="A1555" s="6"/>
-      <c r="B1555" s="11"/>
+      <c r="B1555" s="13"/>
       <c r="C1555" s="6"/>
       <c r="D1555" s="6"/>
       <c r="E1555" s="6"/>
     </row>
     <row r="1556">
       <c r="A1556" s="6"/>
-      <c r="B1556" s="11"/>
+      <c r="B1556" s="13"/>
       <c r="C1556" s="6"/>
       <c r="D1556" s="6"/>
       <c r="E1556" s="6"/>
     </row>
     <row r="1557">
       <c r="A1557" s="6"/>
-      <c r="B1557" s="11"/>
+      <c r="B1557" s="13"/>
       <c r="C1557" s="6"/>
       <c r="D1557" s="6"/>
       <c r="E1557" s="6"/>
     </row>
     <row r="1558">
       <c r="A1558" s="6"/>
-      <c r="B1558" s="11"/>
+      <c r="B1558" s="13"/>
       <c r="C1558" s="6"/>
       <c r="D1558" s="6"/>
       <c r="E1558" s="6"/>
     </row>
     <row r="1559">
       <c r="A1559" s="6"/>
-      <c r="B1559" s="11"/>
+      <c r="B1559" s="13"/>
       <c r="C1559" s="6"/>
       <c r="D1559" s="6"/>
       <c r="E1559" s="6"/>
     </row>
     <row r="1560">
       <c r="A1560" s="6"/>
-      <c r="B1560" s="11"/>
+      <c r="B1560" s="13"/>
       <c r="C1560" s="6"/>
       <c r="D1560" s="6"/>
       <c r="E1560" s="6"/>
     </row>
     <row r="1561">
       <c r="A1561" s="6"/>
-      <c r="B1561" s="11"/>
+      <c r="B1561" s="13"/>
       <c r="C1561" s="6"/>
       <c r="D1561" s="6"/>
       <c r="E1561" s="6"/>
     </row>
     <row r="1562">
       <c r="A1562" s="6"/>
-      <c r="B1562" s="11"/>
+      <c r="B1562" s="13"/>
       <c r="C1562" s="6"/>
       <c r="D1562" s="6"/>
       <c r="E1562" s="6"/>
     </row>
     <row r="1563">
       <c r="A1563" s="6"/>
-      <c r="B1563" s="11"/>
+      <c r="B1563" s="13"/>
       <c r="C1563" s="6"/>
       <c r="D1563" s="6"/>
       <c r="E1563" s="6"/>
     </row>
     <row r="1564">
       <c r="A1564" s="6"/>
-      <c r="B1564" s="11"/>
+      <c r="B1564" s="13"/>
       <c r="C1564" s="6"/>
       <c r="D1564" s="6"/>
       <c r="E1564" s="6"/>
     </row>
     <row r="1565">
       <c r="A1565" s="6"/>
-      <c r="B1565" s="11"/>
+      <c r="B1565" s="13"/>
       <c r="C1565" s="6"/>
       <c r="D1565" s="6"/>
       <c r="E1565" s="6"/>
     </row>
     <row r="1566">
       <c r="A1566" s="6"/>
-      <c r="B1566" s="11"/>
+      <c r="B1566" s="13"/>
       <c r="C1566" s="6"/>
       <c r="D1566" s="6"/>
       <c r="E1566" s="6"/>
     </row>
     <row r="1567">
       <c r="A1567" s="6"/>
-      <c r="B1567" s="11"/>
+      <c r="B1567" s="13"/>
       <c r="C1567" s="6"/>
       <c r="D1567" s="6"/>
       <c r="E1567" s="6"/>
     </row>
     <row r="1568">
       <c r="A1568" s="6"/>
-      <c r="B1568" s="11"/>
+      <c r="B1568" s="13"/>
       <c r="C1568" s="6"/>
       <c r="D1568" s="6"/>
       <c r="E1568" s="6"/>
     </row>
     <row r="1569">
       <c r="A1569" s="6"/>
-      <c r="B1569" s="11"/>
+      <c r="B1569" s="13"/>
       <c r="C1569" s="6"/>
       <c r="D1569" s="6"/>
       <c r="E1569" s="6"/>
     </row>
     <row r="1570">
       <c r="A1570" s="6"/>
-      <c r="B1570" s="11"/>
+      <c r="B1570" s="13"/>
       <c r="C1570" s="6"/>
       <c r="D1570" s="6"/>
       <c r="E1570" s="6"/>
     </row>
     <row r="1571">
       <c r="A1571" s="6"/>
-      <c r="B1571" s="11"/>
+      <c r="B1571" s="13"/>
       <c r="C1571" s="6"/>
       <c r="D1571" s="6"/>
       <c r="E1571" s="6"/>
     </row>
     <row r="1572">
       <c r="A1572" s="6"/>
-      <c r="B1572" s="11"/>
+      <c r="B1572" s="13"/>
       <c r="C1572" s="6"/>
       <c r="D1572" s="6"/>
       <c r="E1572" s="6"/>
     </row>
     <row r="1573">
       <c r="A1573" s="6"/>
-      <c r="B1573" s="11"/>
+      <c r="B1573" s="13"/>
       <c r="C1573" s="6"/>
       <c r="D1573" s="6"/>
       <c r="E1573" s="6"/>
     </row>
     <row r="1574">
       <c r="A1574" s="6"/>
-      <c r="B1574" s="11"/>
+      <c r="B1574" s="13"/>
       <c r="C1574" s="6"/>
       <c r="D1574" s="6"/>
       <c r="E1574" s="6"/>
     </row>
     <row r="1575">
       <c r="A1575" s="6"/>
-      <c r="B1575" s="11"/>
+      <c r="B1575" s="13"/>
       <c r="C1575" s="6"/>
       <c r="D1575" s="6"/>
       <c r="E1575" s="6"/>
     </row>
     <row r="1576">
       <c r="A1576" s="6"/>
-      <c r="B1576" s="11"/>
+      <c r="B1576" s="13"/>
       <c r="C1576" s="6"/>
       <c r="D1576" s="6"/>
       <c r="E1576" s="6"/>
     </row>
     <row r="1577">
       <c r="A1577" s="6"/>
-      <c r="B1577" s="11"/>
+      <c r="B1577" s="13"/>
       <c r="C1577" s="6"/>
       <c r="D1577" s="6"/>
       <c r="E1577" s="6"/>
     </row>
     <row r="1578">
       <c r="A1578" s="6"/>
-      <c r="B1578" s="11"/>
+      <c r="B1578" s="13"/>
       <c r="C1578" s="6"/>
       <c r="D1578" s="6"/>
       <c r="E1578" s="6"/>
     </row>
     <row r="1579">
       <c r="A1579" s="6"/>
-      <c r="B1579" s="11"/>
+      <c r="B1579" s="13"/>
       <c r="C1579" s="6"/>
       <c r="D1579" s="6"/>
       <c r="E1579" s="6"/>
     </row>
     <row r="1580">
       <c r="A1580" s="6"/>
-      <c r="B1580" s="11"/>
+      <c r="B1580" s="13"/>
       <c r="C1580" s="6"/>
       <c r="D1580" s="6"/>
       <c r="E1580" s="6"/>
     </row>
     <row r="1581">
       <c r="A1581" s="6"/>
-      <c r="B1581" s="11"/>
+      <c r="B1581" s="13"/>
       <c r="C1581" s="6"/>
       <c r="D1581" s="6"/>
       <c r="E1581" s="6"/>
     </row>
     <row r="1582">
       <c r="A1582" s="6"/>
-      <c r="B1582" s="11"/>
+      <c r="B1582" s="13"/>
       <c r="C1582" s="6"/>
       <c r="D1582" s="6"/>
       <c r="E1582" s="6"/>
     </row>
     <row r="1583">
       <c r="A1583" s="6"/>
-      <c r="B1583" s="11"/>
+      <c r="B1583" s="13"/>
       <c r="C1583" s="6"/>
       <c r="D1583" s="6"/>
       <c r="E1583" s="6"/>
     </row>
     <row r="1584">
       <c r="A1584" s="6"/>
-      <c r="B1584" s="11"/>
+      <c r="B1584" s="13"/>
       <c r="C1584" s="6"/>
       <c r="D1584" s="6"/>
       <c r="E1584" s="6"/>
     </row>
     <row r="1585">
       <c r="A1585" s="6"/>
-      <c r="B1585" s="11"/>
+      <c r="B1585" s="13"/>
       <c r="C1585" s="6"/>
       <c r="D1585" s="6"/>
       <c r="E1585" s="6"/>
     </row>
     <row r="1586">
       <c r="A1586" s="6"/>
-      <c r="B1586" s="11"/>
+      <c r="B1586" s="13"/>
       <c r="C1586" s="6"/>
       <c r="D1586" s="6"/>
       <c r="E1586" s="6"/>
     </row>
     <row r="1587">
       <c r="A1587" s="6"/>
-      <c r="B1587" s="11"/>
+      <c r="B1587" s="13"/>
       <c r="C1587" s="6"/>
       <c r="D1587" s="6"/>
       <c r="E1587" s="6"/>
     </row>
     <row r="1588">
       <c r="A1588" s="6"/>
-      <c r="B1588" s="11"/>
+      <c r="B1588" s="13"/>
       <c r="C1588" s="6"/>
       <c r="D1588" s="6"/>
       <c r="E1588" s="6"/>
     </row>
     <row r="1589">
       <c r="A1589" s="6"/>
-      <c r="B1589" s="11"/>
+      <c r="B1589" s="13"/>
       <c r="C1589" s="6"/>
       <c r="D1589" s="6"/>
       <c r="E1589" s="6"/>
     </row>
     <row r="1590">
       <c r="A1590" s="6"/>
-      <c r="B1590" s="11"/>
+      <c r="B1590" s="13"/>
       <c r="C1590" s="6"/>
       <c r="D1590" s="6"/>
       <c r="E1590" s="6"/>
     </row>
     <row r="1591">
       <c r="A1591" s="6"/>
-      <c r="B1591" s="11"/>
+      <c r="B1591" s="13"/>
       <c r="C1591" s="6"/>
       <c r="D1591" s="6"/>
       <c r="E1591" s="6"/>
     </row>
     <row r="1592">
       <c r="A1592" s="6"/>
-      <c r="B1592" s="11"/>
+      <c r="B1592" s="13"/>
       <c r="C1592" s="6"/>
       <c r="D1592" s="6"/>
       <c r="E1592" s="6"/>
     </row>
     <row r="1593">
       <c r="A1593" s="6"/>
-      <c r="B1593" s="11"/>
+      <c r="B1593" s="13"/>
       <c r="C1593" s="6"/>
       <c r="D1593" s="6"/>
       <c r="E1593" s="6"/>
     </row>
     <row r="1594">
       <c r="A1594" s="6"/>
-      <c r="B1594" s="11"/>
+      <c r="B1594" s="13"/>
       <c r="C1594" s="6"/>
       <c r="D1594" s="6"/>
       <c r="E1594" s="6"/>
     </row>
     <row r="1595">
       <c r="A1595" s="6"/>
-      <c r="B1595" s="11"/>
+      <c r="B1595" s="13"/>
       <c r="C1595" s="6"/>
       <c r="D1595" s="6"/>
       <c r="E1595" s="6"/>
     </row>
     <row r="1596">
       <c r="A1596" s="6"/>
-      <c r="B1596" s="11"/>
+      <c r="B1596" s="13"/>
       <c r="C1596" s="6"/>
       <c r="D1596" s="6"/>
       <c r="E1596" s="6"/>
     </row>
     <row r="1597">
       <c r="A1597" s="6"/>
-      <c r="B1597" s="11"/>
+      <c r="B1597" s="13"/>
       <c r="C1597" s="6"/>
       <c r="D1597" s="6"/>
       <c r="E1597" s="6"/>
     </row>
     <row r="1598">
       <c r="A1598" s="6"/>
-      <c r="B1598" s="11"/>
+      <c r="B1598" s="13"/>
       <c r="C1598" s="6"/>
       <c r="D1598" s="6"/>
       <c r="E1598" s="6"/>
     </row>
     <row r="1599">
       <c r="A1599" s="6"/>
-      <c r="B1599" s="11"/>
+      <c r="B1599" s="13"/>
       <c r="C1599" s="6"/>
       <c r="D1599" s="6"/>
       <c r="E1599" s="6"/>
     </row>
     <row r="1600">
       <c r="A1600" s="6"/>
-      <c r="B1600" s="11"/>
+      <c r="B1600" s="13"/>
       <c r="C1600" s="6"/>
       <c r="D1600" s="6"/>
       <c r="E1600" s="6"/>
     </row>
     <row r="1601">
       <c r="A1601" s="6"/>
-      <c r="B1601" s="11"/>
+      <c r="B1601" s="13"/>
       <c r="C1601" s="6"/>
       <c r="D1601" s="6"/>
       <c r="E1601" s="6"/>
     </row>
     <row r="1602">
       <c r="A1602" s="6"/>
-      <c r="B1602" s="11"/>
+      <c r="B1602" s="13"/>
       <c r="C1602" s="6"/>
       <c r="D1602" s="6"/>
       <c r="E1602" s="6"/>
     </row>
     <row r="1603">
       <c r="A1603" s="6"/>
-      <c r="B1603" s="11"/>
+      <c r="B1603" s="13"/>
       <c r="C1603" s="6"/>
       <c r="D1603" s="6"/>
       <c r="E1603" s="6"/>
     </row>
     <row r="1604">
       <c r="A1604" s="6"/>
-      <c r="B1604" s="11"/>
+      <c r="B1604" s="13"/>
       <c r="C1604" s="6"/>
       <c r="D1604" s="6"/>
       <c r="E1604" s="6"/>
     </row>
     <row r="1605">
       <c r="A1605" s="6"/>
-      <c r="B1605" s="11"/>
+      <c r="B1605" s="13"/>
       <c r="C1605" s="6"/>
       <c r="D1605" s="6"/>
       <c r="E1605" s="6"/>
     </row>
     <row r="1606">
       <c r="A1606" s="6"/>
-      <c r="B1606" s="11"/>
+      <c r="B1606" s="13"/>
       <c r="C1606" s="6"/>
       <c r="D1606" s="6"/>
       <c r="E1606" s="6"/>
     </row>
     <row r="1607">
       <c r="A1607" s="6"/>
-      <c r="B1607" s="11"/>
+      <c r="B1607" s="13"/>
       <c r="C1607" s="6"/>
       <c r="D1607" s="6"/>
       <c r="E1607" s="6"/>
     </row>
     <row r="1608">
       <c r="A1608" s="6"/>
-      <c r="B1608" s="11"/>
+      <c r="B1608" s="13"/>
       <c r="C1608" s="6"/>
       <c r="D1608" s="6"/>
       <c r="E1608" s="6"/>
     </row>
     <row r="1609">
       <c r="A1609" s="6"/>
-      <c r="B1609" s="11"/>
+      <c r="B1609" s="13"/>
       <c r="C1609" s="6"/>
       <c r="D1609" s="6"/>
       <c r="E1609" s="6"/>
     </row>
     <row r="1610">
       <c r="A1610" s="6"/>
-      <c r="B1610" s="11"/>
+      <c r="B1610" s="13"/>
       <c r="C1610" s="6"/>
       <c r="D1610" s="6"/>
       <c r="E1610" s="6"/>
     </row>
     <row r="1611">
       <c r="A1611" s="6"/>
-      <c r="B1611" s="11"/>
+      <c r="B1611" s="13"/>
       <c r="C1611" s="6"/>
       <c r="D1611" s="6"/>
       <c r="E1611" s="6"/>
     </row>
     <row r="1612">
       <c r="A1612" s="6"/>
-      <c r="B1612" s="11"/>
+      <c r="B1612" s="13"/>
       <c r="C1612" s="6"/>
       <c r="D1612" s="6"/>
       <c r="E1612" s="6"/>
     </row>
     <row r="1613">
       <c r="A1613" s="6"/>
-      <c r="B1613" s="11"/>
+      <c r="B1613" s="13"/>
       <c r="C1613" s="6"/>
       <c r="D1613" s="6"/>
       <c r="E1613" s="6"/>
     </row>
     <row r="1614">
       <c r="A1614" s="6"/>
-      <c r="B1614" s="11"/>
+      <c r="B1614" s="13"/>
       <c r="C1614" s="6"/>
       <c r="D1614" s="6"/>
       <c r="E1614" s="6"/>
     </row>
     <row r="1615">
       <c r="A1615" s="6"/>
-      <c r="B1615" s="11"/>
+      <c r="B1615" s="13"/>
       <c r="C1615" s="6"/>
       <c r="D1615" s="6"/>
       <c r="E1615" s="6"/>
     </row>
     <row r="1616">
       <c r="A1616" s="6"/>
-      <c r="B1616" s="11"/>
+      <c r="B1616" s="13"/>
       <c r="C1616" s="6"/>
       <c r="D1616" s="6"/>
       <c r="E1616" s="6"/>
     </row>
     <row r="1617">
       <c r="A1617" s="6"/>
-      <c r="B1617" s="11"/>
+      <c r="B1617" s="13"/>
       <c r="C1617" s="6"/>
       <c r="D1617" s="6"/>
       <c r="E1617" s="6"/>
     </row>
     <row r="1618">
       <c r="A1618" s="6"/>
-      <c r="B1618" s="11"/>
+      <c r="B1618" s="13"/>
       <c r="C1618" s="6"/>
       <c r="D1618" s="6"/>
       <c r="E1618" s="6"/>
     </row>
     <row r="1619">
       <c r="A1619" s="6"/>
-      <c r="B1619" s="11"/>
+      <c r="B1619" s="13"/>
       <c r="C1619" s="6"/>
       <c r="D1619" s="6"/>
       <c r="E1619" s="6"/>
     </row>
     <row r="1620">
       <c r="A1620" s="6"/>
-      <c r="B1620" s="11"/>
+      <c r="B1620" s="13"/>
       <c r="C1620" s="6"/>
       <c r="D1620" s="6"/>
       <c r="E1620" s="6"/>
     </row>
     <row r="1621">
       <c r="A1621" s="6"/>
-      <c r="B1621" s="11"/>
+      <c r="B1621" s="13"/>
       <c r="C1621" s="6"/>
       <c r="D1621" s="6"/>
       <c r="E1621" s="6"/>
     </row>
     <row r="1622">
       <c r="A1622" s="6"/>
-      <c r="B1622" s="11"/>
+      <c r="B1622" s="13"/>
       <c r="C1622" s="6"/>
       <c r="D1622" s="6"/>
       <c r="E1622" s="6"/>
     </row>
     <row r="1623">
       <c r="A1623" s="6"/>
-      <c r="B1623" s="11"/>
+      <c r="B1623" s="13"/>
       <c r="C1623" s="6"/>
       <c r="D1623" s="6"/>
       <c r="E1623" s="6"/>
     </row>
     <row r="1624">
       <c r="A1624" s="6"/>
-      <c r="B1624" s="11"/>
+      <c r="B1624" s="13"/>
       <c r="C1624" s="6"/>
       <c r="D1624" s="6"/>
       <c r="E1624" s="6"/>
     </row>
     <row r="1625">
       <c r="A1625" s="6"/>
-      <c r="B1625" s="11"/>
+      <c r="B1625" s="13"/>
       <c r="C1625" s="6"/>
       <c r="D1625" s="6"/>
       <c r="E1625" s="6"/>
     </row>
     <row r="1626">
       <c r="A1626" s="6"/>
-      <c r="B1626" s="11"/>
+      <c r="B1626" s="13"/>
       <c r="C1626" s="6"/>
       <c r="D1626" s="6"/>
       <c r="E1626" s="6"/>
     </row>
     <row r="1627">
       <c r="A1627" s="6"/>
-      <c r="B1627" s="11"/>
+      <c r="B1627" s="13"/>
       <c r="C1627" s="6"/>
       <c r="D1627" s="6"/>
       <c r="E1627" s="6"/>
     </row>
     <row r="1628">
       <c r="A1628" s="6"/>
-      <c r="B1628" s="11"/>
+      <c r="B1628" s="13"/>
       <c r="C1628" s="6"/>
       <c r="D1628" s="6"/>
       <c r="E1628" s="6"/>
     </row>
     <row r="1629">
       <c r="A1629" s="6"/>
-      <c r="B1629" s="11"/>
+      <c r="B1629" s="13"/>
       <c r="C1629" s="6"/>
       <c r="D1629" s="6"/>
       <c r="E1629" s="6"/>
     </row>
     <row r="1630">
       <c r="A1630" s="6"/>
-      <c r="B1630" s="11"/>
+      <c r="B1630" s="13"/>
       <c r="C1630" s="6"/>
       <c r="D1630" s="6"/>
       <c r="E1630" s="6"/>
     </row>
     <row r="1631">
       <c r="A1631" s="6"/>
-      <c r="B1631" s="11"/>
+      <c r="B1631" s="13"/>
       <c r="C1631" s="6"/>
       <c r="D1631" s="6"/>
       <c r="E1631" s="6"/>
     </row>
     <row r="1632">
       <c r="A1632" s="6"/>
-      <c r="B1632" s="11"/>
+      <c r="B1632" s="13"/>
       <c r="C1632" s="6"/>
       <c r="D1632" s="6"/>
       <c r="E1632" s="6"/>
     </row>
     <row r="1633">
       <c r="A1633" s="6"/>
-      <c r="B1633" s="11"/>
+      <c r="B1633" s="13"/>
       <c r="C1633" s="6"/>
       <c r="D1633" s="6"/>
       <c r="E1633" s="6"/>
     </row>
     <row r="1634">
       <c r="A1634" s="6"/>
-      <c r="B1634" s="11"/>
+      <c r="B1634" s="13"/>
       <c r="C1634" s="6"/>
       <c r="D1634" s="6"/>
       <c r="E1634" s="6"/>
     </row>
     <row r="1635">
       <c r="A1635" s="6"/>
-      <c r="B1635" s="11"/>
+      <c r="B1635" s="13"/>
       <c r="C1635" s="6"/>
       <c r="D1635" s="6"/>
       <c r="E1635" s="6"/>
     </row>
     <row r="1636">
       <c r="A1636" s="6"/>
-      <c r="B1636" s="11"/>
+      <c r="B1636" s="13"/>
       <c r="C1636" s="6"/>
       <c r="D1636" s="6"/>
       <c r="E1636" s="6"/>
     </row>
     <row r="1637">
       <c r="A1637" s="6"/>
-      <c r="B1637" s="11"/>
+      <c r="B1637" s="13"/>
       <c r="C1637" s="6"/>
       <c r="D1637" s="6"/>
       <c r="E1637" s="6"/>
     </row>
     <row r="1638">
       <c r="A1638" s="6"/>
-      <c r="B1638" s="11"/>
+      <c r="B1638" s="13"/>
       <c r="C1638" s="6"/>
       <c r="D1638" s="6"/>
       <c r="E1638" s="6"/>
     </row>
     <row r="1639">
       <c r="A1639" s="6"/>
-      <c r="B1639" s="11"/>
+      <c r="B1639" s="13"/>
       <c r="C1639" s="6"/>
       <c r="D1639" s="6"/>
       <c r="E1639" s="6"/>
     </row>
     <row r="1640">
       <c r="A1640" s="6"/>
-      <c r="B1640" s="11"/>
+      <c r="B1640" s="13"/>
       <c r="C1640" s="6"/>
       <c r="D1640" s="6"/>
       <c r="E1640" s="6"/>
     </row>
     <row r="1641">
       <c r="A1641" s="6"/>
-      <c r="B1641" s="11"/>
+      <c r="B1641" s="13"/>
       <c r="C1641" s="6"/>
       <c r="D1641" s="6"/>
       <c r="E1641" s="6"/>
     </row>
     <row r="1642">
       <c r="A1642" s="6"/>
-      <c r="B1642" s="11"/>
+      <c r="B1642" s="13"/>
       <c r="C1642" s="6"/>
       <c r="D1642" s="6"/>
       <c r="E1642" s="6"/>
     </row>
     <row r="1643">
       <c r="A1643" s="6"/>
-      <c r="B1643" s="11"/>
+      <c r="B1643" s="13"/>
       <c r="C1643" s="6"/>
       <c r="D1643" s="6"/>
       <c r="E1643" s="6"/>
     </row>
     <row r="1644">
       <c r="A1644" s="6"/>
-      <c r="B1644" s="11"/>
+      <c r="B1644" s="13"/>
       <c r="C1644" s="6"/>
       <c r="D1644" s="6"/>
       <c r="E1644" s="6"/>
     </row>
     <row r="1645">
       <c r="A1645" s="6"/>
-      <c r="B1645" s="11"/>
+      <c r="B1645" s="13"/>
       <c r="C1645" s="6"/>
       <c r="D1645" s="6"/>
       <c r="E1645" s="6"/>
     </row>
     <row r="1646">
       <c r="A1646" s="6"/>
-      <c r="B1646" s="11"/>
+      <c r="B1646" s="13"/>
       <c r="C1646" s="6"/>
       <c r="D1646" s="6"/>
       <c r="E1646" s="6"/>
     </row>
     <row r="1647">
       <c r="A1647" s="6"/>
-      <c r="B1647" s="11"/>
+      <c r="B1647" s="13"/>
       <c r="C1647" s="6"/>
       <c r="D1647" s="6"/>
       <c r="E1647" s="6"/>
     </row>
     <row r="1648">
       <c r="A1648" s="6"/>
-      <c r="B1648" s="11"/>
+      <c r="B1648" s="13"/>
       <c r="C1648" s="6"/>
       <c r="D1648" s="6"/>
       <c r="E1648" s="6"/>
     </row>
     <row r="1649">
       <c r="A1649" s="6"/>
-      <c r="B1649" s="11"/>
+      <c r="B1649" s="13"/>
       <c r="C1649" s="6"/>
       <c r="D1649" s="6"/>
       <c r="E1649" s="6"/>
     </row>
     <row r="1650">
       <c r="A1650" s="6"/>
-      <c r="B1650" s="11"/>
+      <c r="B1650" s="13"/>
       <c r="C1650" s="6"/>
       <c r="D1650" s="6"/>
       <c r="E1650" s="6"/>
     </row>
     <row r="1651">
       <c r="A1651" s="6"/>
-      <c r="B1651" s="11"/>
+      <c r="B1651" s="13"/>
       <c r="C1651" s="6"/>
       <c r="D1651" s="6"/>
       <c r="E1651" s="6"/>
     </row>
     <row r="1652">
       <c r="A1652" s="6"/>
-      <c r="B1652" s="11"/>
+      <c r="B1652" s="13"/>
       <c r="C1652" s="6"/>
       <c r="D1652" s="6"/>
       <c r="E1652" s="6"/>
     </row>
     <row r="1653">
       <c r="A1653" s="6"/>
-      <c r="B1653" s="11"/>
+      <c r="B1653" s="13"/>
       <c r="C1653" s="6"/>
       <c r="D1653" s="6"/>
       <c r="E1653" s="6"/>
     </row>
     <row r="1654">
       <c r="A1654" s="6"/>
-      <c r="B1654" s="11"/>
+      <c r="B1654" s="13"/>
       <c r="C1654" s="6"/>
       <c r="D1654" s="6"/>
       <c r="E1654" s="6"/>
     </row>
     <row r="1655">
       <c r="A1655" s="6"/>
-      <c r="B1655" s="11"/>
+      <c r="B1655" s="13"/>
       <c r="C1655" s="6"/>
       <c r="D1655" s="6"/>
       <c r="E1655" s="6"/>
     </row>
     <row r="1656">
       <c r="A1656" s="6"/>
-      <c r="B1656" s="11"/>
+      <c r="B1656" s="13"/>
       <c r="C1656" s="6"/>
       <c r="D1656" s="6"/>
       <c r="E1656" s="6"/>
     </row>
     <row r="1657">
       <c r="A1657" s="6"/>
-      <c r="B1657" s="11"/>
+      <c r="B1657" s="13"/>
       <c r="C1657" s="6"/>
       <c r="D1657" s="6"/>
       <c r="E1657" s="6"/>
     </row>
     <row r="1658">
       <c r="A1658" s="6"/>
-      <c r="B1658" s="11"/>
+      <c r="B1658" s="13"/>
       <c r="C1658" s="6"/>
       <c r="D1658" s="6"/>
       <c r="E1658" s="6"/>
     </row>
     <row r="1659">
       <c r="A1659" s="6"/>
-      <c r="B1659" s="11"/>
+      <c r="B1659" s="13"/>
       <c r="C1659" s="6"/>
       <c r="D1659" s="6"/>
       <c r="E1659" s="6"/>
     </row>
     <row r="1660">
       <c r="A1660" s="6"/>
-      <c r="B1660" s="11"/>
+      <c r="B1660" s="13"/>
       <c r="C1660" s="6"/>
       <c r="D1660" s="6"/>
       <c r="E1660" s="6"/>
     </row>
     <row r="1661">
       <c r="A1661" s="6"/>
-      <c r="B1661" s="11"/>
+      <c r="B1661" s="13"/>
       <c r="C1661" s="6"/>
       <c r="D1661" s="6"/>
       <c r="E1661" s="6"/>
     </row>
     <row r="1662">
       <c r="A1662" s="6"/>
-      <c r="B1662" s="11"/>
+      <c r="B1662" s="13"/>
       <c r="C1662" s="6"/>
       <c r="D1662" s="6"/>
       <c r="E1662" s="6"/>
     </row>
     <row r="1663">
       <c r="A1663" s="6"/>
-      <c r="B1663" s="11"/>
+      <c r="B1663" s="13"/>
       <c r="C1663" s="6"/>
       <c r="D1663" s="6"/>
       <c r="E1663" s="6"/>
     </row>
     <row r="1664">
       <c r="A1664" s="6"/>
-      <c r="B1664" s="11"/>
+      <c r="B1664" s="13"/>
       <c r="C1664" s="6"/>
       <c r="D1664" s="6"/>
       <c r="E1664" s="6"/>
     </row>
     <row r="1665">
       <c r="A1665" s="6"/>
-      <c r="B1665" s="11"/>
+      <c r="B1665" s="13"/>
       <c r="C1665" s="6"/>
       <c r="D1665" s="6"/>
       <c r="E1665" s="6"/>
     </row>
     <row r="1666">
       <c r="A1666" s="6"/>
-      <c r="B1666" s="11"/>
+      <c r="B1666" s="13"/>
       <c r="C1666" s="6"/>
       <c r="D1666" s="6"/>
       <c r="E1666" s="6"/>
     </row>
     <row r="1667">
       <c r="A1667" s="6"/>
-      <c r="B1667" s="11"/>
+      <c r="B1667" s="13"/>
       <c r="C1667" s="6"/>
       <c r="D1667" s="6"/>
       <c r="E1667" s="6"/>
     </row>
     <row r="1668">
       <c r="A1668" s="6"/>
-      <c r="B1668" s="11"/>
+      <c r="B1668" s="13"/>
       <c r="C1668" s="6"/>
       <c r="D1668" s="6"/>
       <c r="E1668" s="6"/>
     </row>
     <row r="1669">
       <c r="A1669" s="6"/>
-      <c r="B1669" s="11"/>
+      <c r="B1669" s="13"/>
       <c r="C1669" s="6"/>
       <c r="D1669" s="6"/>
       <c r="E1669" s="6"/>
     </row>
     <row r="1670">
       <c r="A1670" s="6"/>
-      <c r="B1670" s="11"/>
+      <c r="B1670" s="13"/>
       <c r="C1670" s="6"/>
       <c r="D1670" s="6"/>
       <c r="E1670" s="6"/>
     </row>
     <row r="1671">
       <c r="A1671" s="6"/>
-      <c r="B1671" s="11"/>
+      <c r="B1671" s="13"/>
       <c r="C1671" s="6"/>
       <c r="D1671" s="6"/>
       <c r="E1671" s="6"/>
     </row>
     <row r="1672">
       <c r="A1672" s="6"/>
-      <c r="B1672" s="11"/>
+      <c r="B1672" s="13"/>
       <c r="C1672" s="6"/>
       <c r="D1672" s="6"/>
       <c r="E1672" s="6"/>
     </row>
     <row r="1673">
       <c r="A1673" s="6"/>
-      <c r="B1673" s="11"/>
+      <c r="B1673" s="13"/>
       <c r="C1673" s="6"/>
       <c r="D1673" s="6"/>
       <c r="E1673" s="6"/>
     </row>
     <row r="1674">
       <c r="A1674" s="6"/>
-      <c r="B1674" s="11"/>
+      <c r="B1674" s="13"/>
       <c r="C1674" s="6"/>
       <c r="D1674" s="6"/>
       <c r="E1674" s="6"/>
     </row>
     <row r="1675">
       <c r="A1675" s="6"/>
-      <c r="B1675" s="11"/>
+      <c r="B1675" s="13"/>
       <c r="C1675" s="6"/>
       <c r="D1675" s="6"/>
       <c r="E1675" s="6"/>
     </row>
     <row r="1676">
       <c r="A1676" s="6"/>
-      <c r="B1676" s="11"/>
+      <c r="B1676" s="13"/>
       <c r="C1676" s="6"/>
       <c r="D1676" s="6"/>
       <c r="E1676" s="6"/>
     </row>
     <row r="1677">
       <c r="A1677" s="6"/>
-      <c r="B1677" s="11"/>
+      <c r="B1677" s="13"/>
       <c r="C1677" s="6"/>
       <c r="D1677" s="6"/>
       <c r="E1677" s="6"/>
     </row>
     <row r="1678">
       <c r="A1678" s="6"/>
-      <c r="B1678" s="11"/>
+      <c r="B1678" s="13"/>
       <c r="C1678" s="6"/>
       <c r="D1678" s="6"/>
       <c r="E1678" s="6"/>
     </row>
     <row r="1679">
       <c r="A1679" s="6"/>
-      <c r="B1679" s="11"/>
+      <c r="B1679" s="13"/>
       <c r="C1679" s="6"/>
       <c r="D1679" s="6"/>
       <c r="E1679" s="6"/>
     </row>
     <row r="1680">
       <c r="A1680" s="6"/>
-      <c r="B1680" s="11"/>
+      <c r="B1680" s="13"/>
       <c r="C1680" s="6"/>
       <c r="D1680" s="6"/>
       <c r="E1680" s="6"/>
     </row>
     <row r="1681">
       <c r="A1681" s="6"/>
-      <c r="B1681" s="11"/>
+      <c r="B1681" s="13"/>
       <c r="C1681" s="6"/>
       <c r="D1681" s="6"/>
       <c r="E1681" s="6"/>
     </row>
     <row r="1682">
       <c r="A1682" s="6"/>
-      <c r="B1682" s="11"/>
+      <c r="B1682" s="13"/>
       <c r="C1682" s="6"/>
       <c r="D1682" s="6"/>
       <c r="E1682" s="6"/>
     </row>
     <row r="1683">
       <c r="A1683" s="6"/>
-      <c r="B1683" s="11"/>
+      <c r="B1683" s="13"/>
       <c r="C1683" s="6"/>
       <c r="D1683" s="6"/>
       <c r="E1683" s="6"/>
     </row>
     <row r="1684">
       <c r="A1684" s="6"/>
-      <c r="B1684" s="11"/>
+      <c r="B1684" s="13"/>
       <c r="C1684" s="6"/>
       <c r="D1684" s="6"/>
       <c r="E1684" s="6"/>
     </row>
     <row r="1685">
       <c r="A1685" s="6"/>
-      <c r="B1685" s="11"/>
+      <c r="B1685" s="13"/>
       <c r="C1685" s="6"/>
       <c r="D1685" s="6"/>
       <c r="E1685" s="6"/>
     </row>
     <row r="1686">
       <c r="A1686" s="6"/>
-      <c r="B1686" s="11"/>
+      <c r="B1686" s="13"/>
       <c r="C1686" s="6"/>
       <c r="D1686" s="6"/>
       <c r="E1686" s="6"/>
     </row>
     <row r="1687">
       <c r="A1687" s="6"/>
-      <c r="B1687" s="11"/>
+      <c r="B1687" s="13"/>
       <c r="C1687" s="6"/>
       <c r="D1687" s="6"/>
       <c r="E1687" s="6"/>
     </row>
     <row r="1688">
       <c r="A1688" s="6"/>
-      <c r="B1688" s="11"/>
+      <c r="B1688" s="13"/>
       <c r="C1688" s="6"/>
       <c r="D1688" s="6"/>
       <c r="E1688" s="6"/>
     </row>
     <row r="1689">
       <c r="A1689" s="6"/>
-      <c r="B1689" s="11"/>
+      <c r="B1689" s="13"/>
       <c r="C1689" s="6"/>
       <c r="D1689" s="6"/>
       <c r="E1689" s="6"/>
     </row>
     <row r="1690">
       <c r="A1690" s="6"/>
-      <c r="B1690" s="11"/>
+      <c r="B1690" s="13"/>
       <c r="C1690" s="6"/>
       <c r="D1690" s="6"/>
       <c r="E1690" s="6"/>
     </row>
     <row r="1691">
       <c r="A1691" s="6"/>
-      <c r="B1691" s="11"/>
+      <c r="B1691" s="13"/>
       <c r="C1691" s="6"/>
       <c r="D1691" s="6"/>
       <c r="E1691" s="6"/>
     </row>
     <row r="1692">
       <c r="A1692" s="6"/>
-      <c r="B1692" s="11"/>
+      <c r="B1692" s="13"/>
       <c r="C1692" s="6"/>
       <c r="D1692" s="6"/>
       <c r="E1692" s="6"/>
     </row>
     <row r="1693">
       <c r="A1693" s="6"/>
-      <c r="B1693" s="11"/>
+      <c r="B1693" s="13"/>
       <c r="C1693" s="6"/>
       <c r="D1693" s="6"/>
       <c r="E1693" s="6"/>
     </row>
     <row r="1694">
       <c r="A1694" s="6"/>
-      <c r="B1694" s="11"/>
+      <c r="B1694" s="13"/>
       <c r="C1694" s="6"/>
       <c r="D1694" s="6"/>
       <c r="E1694" s="6"/>
     </row>
     <row r="1695">
       <c r="A1695" s="6"/>
-      <c r="B1695" s="11"/>
+      <c r="B1695" s="13"/>
       <c r="C1695" s="6"/>
       <c r="D1695" s="6"/>
       <c r="E1695" s="6"/>
     </row>
     <row r="1696">
       <c r="A1696" s="6"/>
-      <c r="B1696" s="11"/>
+      <c r="B1696" s="13"/>
       <c r="C1696" s="6"/>
       <c r="D1696" s="6"/>
       <c r="E1696" s="6"/>
     </row>
     <row r="1697">
       <c r="A1697" s="6"/>
-      <c r="B1697" s="11"/>
+      <c r="B1697" s="13"/>
       <c r="C1697" s="6"/>
       <c r="D1697" s="6"/>
       <c r="E1697" s="6"/>
     </row>
     <row r="1698">
       <c r="A1698" s="6"/>
-      <c r="B1698" s="11"/>
+      <c r="B1698" s="13"/>
       <c r="C1698" s="6"/>
       <c r="D1698" s="6"/>
       <c r="E1698" s="6"/>
     </row>
     <row r="1699">
       <c r="A1699" s="6"/>
-      <c r="B1699" s="11"/>
+      <c r="B1699" s="13"/>
       <c r="C1699" s="6"/>
       <c r="D1699" s="6"/>
       <c r="E1699" s="6"/>
     </row>
     <row r="1700">
       <c r="A1700" s="6"/>
-      <c r="B1700" s="11"/>
+      <c r="B1700" s="13"/>
       <c r="C1700" s="6"/>
       <c r="D1700" s="6"/>
       <c r="E1700" s="6"/>
     </row>
     <row r="1701">
       <c r="A1701" s="6"/>
-      <c r="B1701" s="11"/>
+      <c r="B1701" s="13"/>
       <c r="C1701" s="6"/>
       <c r="D1701" s="6"/>
       <c r="E1701" s="6"/>
     </row>
     <row r="1702">
       <c r="A1702" s="6"/>
-      <c r="B1702" s="11"/>
+      <c r="B1702" s="13"/>
       <c r="C1702" s="6"/>
       <c r="D1702" s="6"/>
       <c r="E1702" s="6"/>
     </row>
     <row r="1703">
       <c r="A1703" s="6"/>
-      <c r="B1703" s="11"/>
+      <c r="B1703" s="13"/>
       <c r="C1703" s="6"/>
       <c r="D1703" s="6"/>
       <c r="E1703" s="6"/>
     </row>
     <row r="1704">
       <c r="A1704" s="6"/>
-      <c r="B1704" s="11"/>
+      <c r="B1704" s="13"/>
       <c r="C1704" s="6"/>
       <c r="D1704" s="6"/>
       <c r="E1704" s="6"/>
     </row>
     <row r="1705">
       <c r="A1705" s="6"/>
-      <c r="B1705" s="11"/>
+      <c r="B1705" s="13"/>
       <c r="C1705" s="6"/>
       <c r="D1705" s="6"/>
       <c r="E1705" s="6"/>
     </row>
     <row r="1706">
       <c r="A1706" s="6"/>
-      <c r="B1706" s="11"/>
+      <c r="B1706" s="13"/>
       <c r="C1706" s="6"/>
       <c r="D1706" s="6"/>
       <c r="E1706" s="6"/>
     </row>
     <row r="1707">
       <c r="A1707" s="6"/>
-      <c r="B1707" s="11"/>
+      <c r="B1707" s="13"/>
       <c r="C1707" s="6"/>
       <c r="D1707" s="6"/>
       <c r="E1707" s="6"/>
     </row>
     <row r="1708">
       <c r="A1708" s="6"/>
-      <c r="B1708" s="11"/>
+      <c r="B1708" s="13"/>
       <c r="C1708" s="6"/>
       <c r="D1708" s="6"/>
       <c r="E1708" s="6"/>
     </row>
     <row r="1709">
       <c r="A1709" s="6"/>
-      <c r="B1709" s="11"/>
+      <c r="B1709" s="13"/>
       <c r="C1709" s="6"/>
       <c r="D1709" s="6"/>
       <c r="E1709" s="6"/>
     </row>
     <row r="1710">
       <c r="A1710" s="6"/>
-      <c r="B1710" s="11"/>
+      <c r="B1710" s="13"/>
       <c r="C1710" s="6"/>
       <c r="D1710" s="6"/>
       <c r="E1710" s="6"/>
     </row>
     <row r="1711">
       <c r="A1711" s="6"/>
-      <c r="B1711" s="11"/>
+      <c r="B1711" s="13"/>
       <c r="C1711" s="6"/>
       <c r="D1711" s="6"/>
       <c r="E1711" s="6"/>
     </row>
     <row r="1712">
       <c r="A1712" s="6"/>
-      <c r="B1712" s="11"/>
+      <c r="B1712" s="13"/>
       <c r="C1712" s="6"/>
       <c r="D1712" s="6"/>
       <c r="E1712" s="6"/>
     </row>
     <row r="1713">
       <c r="A1713" s="6"/>
-      <c r="B1713" s="11"/>
+      <c r="B1713" s="13"/>
       <c r="C1713" s="6"/>
       <c r="D1713" s="6"/>
       <c r="E1713" s="6"/>
     </row>
     <row r="1714">
       <c r="A1714" s="6"/>
-      <c r="B1714" s="11"/>
+      <c r="B1714" s="13"/>
       <c r="C1714" s="6"/>
       <c r="D1714" s="6"/>
       <c r="E1714" s="6"/>
     </row>
     <row r="1715">
       <c r="A1715" s="6"/>
-      <c r="B1715" s="11"/>
+      <c r="B1715" s="13"/>
       <c r="C1715" s="6"/>
       <c r="D1715" s="6"/>
       <c r="E1715" s="6"/>
     </row>
     <row r="1716">
       <c r="A1716" s="6"/>
-      <c r="B1716" s="11"/>
+      <c r="B1716" s="13"/>
       <c r="C1716" s="6"/>
       <c r="D1716" s="6"/>
       <c r="E1716" s="6"/>
     </row>
     <row r="1717">
       <c r="A1717" s="6"/>
-      <c r="B1717" s="11"/>
+      <c r="B1717" s="13"/>
       <c r="C1717" s="6"/>
       <c r="D1717" s="6"/>
       <c r="E1717" s="6"/>
     </row>
     <row r="1718">
       <c r="A1718" s="6"/>
-      <c r="B1718" s="11"/>
+      <c r="B1718" s="13"/>
       <c r="C1718" s="6"/>
       <c r="D1718" s="6"/>
       <c r="E1718" s="6"/>
     </row>
     <row r="1719">
       <c r="A1719" s="6"/>
-      <c r="B1719" s="11"/>
+      <c r="B1719" s="13"/>
       <c r="C1719" s="6"/>
       <c r="D1719" s="6"/>
       <c r="E1719" s="6"/>
     </row>
     <row r="1720">
       <c r="A1720" s="6"/>
-      <c r="B1720" s="11"/>
+      <c r="B1720" s="13"/>
       <c r="C1720" s="6"/>
       <c r="D1720" s="6"/>
       <c r="E1720" s="6"/>
     </row>
     <row r="1721">
       <c r="A1721" s="6"/>
-      <c r="B1721" s="11"/>
+      <c r="B1721" s="13"/>
       <c r="C1721" s="6"/>
       <c r="D1721" s="6"/>
       <c r="E1721" s="6"/>
     </row>
     <row r="1722">
       <c r="A1722" s="6"/>
-      <c r="B1722" s="11"/>
+      <c r="B1722" s="13"/>
       <c r="C1722" s="6"/>
       <c r="D1722" s="6"/>
       <c r="E1722" s="6"/>
     </row>
     <row r="1723">
       <c r="A1723" s="6"/>
-      <c r="B1723" s="11"/>
+      <c r="B1723" s="13"/>
       <c r="C1723" s="6"/>
       <c r="D1723" s="6"/>
       <c r="E1723" s="6"/>
     </row>
     <row r="1724">
       <c r="A1724" s="6"/>
-      <c r="B1724" s="11"/>
+      <c r="B1724" s="13"/>
       <c r="C1724" s="6"/>
       <c r="D1724" s="6"/>
       <c r="E1724" s="6"/>
     </row>
     <row r="1725">
       <c r="A1725" s="6"/>
-      <c r="B1725" s="11"/>
+      <c r="B1725" s="13"/>
       <c r="C1725" s="6"/>
       <c r="D1725" s="6"/>
       <c r="E1725" s="6"/>
     </row>
     <row r="1726">
       <c r="A1726" s="6"/>
-      <c r="B1726" s="11"/>
+      <c r="B1726" s="13"/>
       <c r="C1726" s="6"/>
       <c r="D1726" s="6"/>
       <c r="E1726" s="6"/>
     </row>
     <row r="1727">
       <c r="A1727" s="6"/>
-      <c r="B1727" s="11"/>
+      <c r="B1727" s="13"/>
       <c r="C1727" s="6"/>
       <c r="D1727" s="6"/>
       <c r="E1727" s="6"/>
     </row>
     <row r="1728">
       <c r="A1728" s="6"/>
-      <c r="B1728" s="11"/>
+      <c r="B1728" s="13"/>
       <c r="C1728" s="6"/>
       <c r="D1728" s="6"/>
       <c r="E1728" s="6"/>
     </row>
     <row r="1729">
       <c r="A1729" s="6"/>
-      <c r="B1729" s="11"/>
+      <c r="B1729" s="13"/>
       <c r="C1729" s="6"/>
       <c r="D1729" s="6"/>
       <c r="E1729" s="6"/>
     </row>
     <row r="1730">
       <c r="A1730" s="6"/>
-      <c r="B1730" s="11"/>
+      <c r="B1730" s="13"/>
       <c r="C1730" s="6"/>
       <c r="D1730" s="6"/>
       <c r="E1730" s="6"/>
     </row>
     <row r="1731">
       <c r="A1731" s="6"/>
-      <c r="B1731" s="11"/>
+      <c r="B1731" s="13"/>
       <c r="C1731" s="6"/>
       <c r="D1731" s="6"/>
       <c r="E1731" s="6"/>
     </row>
     <row r="1732">
       <c r="A1732" s="6"/>
-      <c r="B1732" s="11"/>
+      <c r="B1732" s="13"/>
       <c r="C1732" s="6"/>
       <c r="D1732" s="6"/>
       <c r="E1732" s="6"/>
     </row>
     <row r="1733">
       <c r="A1733" s="6"/>
-      <c r="B1733" s="11"/>
+      <c r="B1733" s="13"/>
       <c r="C1733" s="6"/>
       <c r="D1733" s="6"/>
       <c r="E1733" s="6"/>
     </row>
     <row r="1734">
       <c r="A1734" s="6"/>
-      <c r="B1734" s="11"/>
+      <c r="B1734" s="13"/>
       <c r="C1734" s="6"/>
       <c r="D1734" s="6"/>
       <c r="E1734" s="6"/>
     </row>
     <row r="1735">
       <c r="A1735" s="6"/>
-      <c r="B1735" s="11"/>
+      <c r="B1735" s="13"/>
       <c r="C1735" s="6"/>
       <c r="D1735" s="6"/>
       <c r="E1735" s="6"/>
     </row>
     <row r="1736">
       <c r="A1736" s="6"/>
-      <c r="B1736" s="11"/>
+      <c r="B1736" s="13"/>
       <c r="C1736" s="6"/>
       <c r="D1736" s="6"/>
       <c r="E1736" s="6"/>
     </row>
     <row r="1737">
       <c r="A1737" s="6"/>
-      <c r="B1737" s="11"/>
+      <c r="B1737" s="13"/>
       <c r="C1737" s="6"/>
       <c r="D1737" s="6"/>
       <c r="E1737" s="6"/>
     </row>
     <row r="1738">
       <c r="A1738" s="6"/>
-      <c r="B1738" s="11"/>
+      <c r="B1738" s="13"/>
       <c r="C1738" s="6"/>
       <c r="D1738" s="6"/>
       <c r="E1738" s="6"/>
     </row>
     <row r="1739">
       <c r="A1739" s="6"/>
-      <c r="B1739" s="11"/>
+      <c r="B1739" s="13"/>
       <c r="C1739" s="6"/>
       <c r="D1739" s="6"/>
       <c r="E1739" s="6"/>
     </row>
     <row r="1740">
       <c r="A1740" s="6"/>
-      <c r="B1740" s="11"/>
+      <c r="B1740" s="13"/>
       <c r="C1740" s="6"/>
       <c r="D1740" s="6"/>
       <c r="E1740" s="6"/>
     </row>
     <row r="1741">
       <c r="A1741" s="6"/>
-      <c r="B1741" s="11"/>
+      <c r="B1741" s="13"/>
       <c r="C1741" s="6"/>
       <c r="D1741" s="6"/>
       <c r="E1741" s="6"/>
     </row>
     <row r="1742">
       <c r="A1742" s="6"/>
-      <c r="B1742" s="11"/>
+      <c r="B1742" s="13"/>
       <c r="C1742" s="6"/>
       <c r="D1742" s="6"/>
       <c r="E1742" s="6"/>
     </row>
     <row r="1743">
       <c r="A1743" s="6"/>
-      <c r="B1743" s="11"/>
+      <c r="B1743" s="13"/>
       <c r="C1743" s="6"/>
       <c r="D1743" s="6"/>
       <c r="E1743" s="6"/>
     </row>
     <row r="1744">
       <c r="A1744" s="6"/>
-      <c r="B1744" s="11"/>
+      <c r="B1744" s="13"/>
       <c r="C1744" s="6"/>
       <c r="D1744" s="6"/>
       <c r="E1744" s="6"/>
     </row>
     <row r="1745">
       <c r="A1745" s="6"/>
-      <c r="B1745" s="11"/>
+      <c r="B1745" s="13"/>
       <c r="C1745" s="6"/>
       <c r="D1745" s="6"/>
       <c r="E1745" s="6"/>
     </row>
     <row r="1746">
       <c r="A1746" s="6"/>
-      <c r="B1746" s="11"/>
+      <c r="B1746" s="13"/>
       <c r="C1746" s="6"/>
       <c r="D1746" s="6"/>
       <c r="E1746" s="6"/>
     </row>
     <row r="1747">
       <c r="A1747" s="6"/>
-      <c r="B1747" s="11"/>
+      <c r="B1747" s="13"/>
       <c r="C1747" s="6"/>
       <c r="D1747" s="6"/>
       <c r="E1747" s="6"/>
     </row>
     <row r="1748">
       <c r="A1748" s="6"/>
-      <c r="B1748" s="11"/>
+      <c r="B1748" s="13"/>
       <c r="C1748" s="6"/>
       <c r="D1748" s="6"/>
       <c r="E1748" s="6"/>
     </row>
     <row r="1749">
       <c r="A1749" s="6"/>
-      <c r="B1749" s="11"/>
+      <c r="B1749" s="13"/>
       <c r="C1749" s="6"/>
       <c r="D1749" s="6"/>
       <c r="E1749" s="6"/>
     </row>
     <row r="1750">
       <c r="A1750" s="6"/>
-      <c r="B1750" s="11"/>
+      <c r="B1750" s="13"/>
       <c r="C1750" s="6"/>
       <c r="D1750" s="6"/>
       <c r="E1750" s="6"/>
     </row>
     <row r="1751">
       <c r="A1751" s="6"/>
-      <c r="B1751" s="11"/>
+      <c r="B1751" s="13"/>
       <c r="C1751" s="6"/>
       <c r="D1751" s="6"/>
       <c r="E1751" s="6"/>
     </row>
     <row r="1752">
       <c r="A1752" s="6"/>
-      <c r="B1752" s="11"/>
+      <c r="B1752" s="13"/>
       <c r="C1752" s="6"/>
       <c r="D1752" s="6"/>
       <c r="E1752" s="6"/>
     </row>
     <row r="1753">
       <c r="A1753" s="6"/>
-      <c r="B1753" s="11"/>
+      <c r="B1753" s="13"/>
       <c r="C1753" s="6"/>
       <c r="D1753" s="6"/>
       <c r="E1753" s="6"/>
     </row>
     <row r="1754">
       <c r="A1754" s="6"/>
-      <c r="B1754" s="11"/>
+      <c r="B1754" s="13"/>
       <c r="C1754" s="6"/>
       <c r="D1754" s="6"/>
       <c r="E1754" s="6"/>
     </row>
     <row r="1755">
       <c r="A1755" s="6"/>
-      <c r="B1755" s="11"/>
+      <c r="B1755" s="13"/>
       <c r="C1755" s="6"/>
       <c r="D1755" s="6"/>
       <c r="E1755" s="6"/>
     </row>
     <row r="1756">
       <c r="A1756" s="6"/>
-      <c r="B1756" s="11"/>
+      <c r="B1756" s="13"/>
       <c r="C1756" s="6"/>
       <c r="D1756" s="6"/>
       <c r="E1756" s="6"/>
     </row>
     <row r="1757">
       <c r="A1757" s="6"/>
-      <c r="B1757" s="11"/>
+      <c r="B1757" s="13"/>
       <c r="C1757" s="6"/>
       <c r="D1757" s="6"/>
       <c r="E1757" s="6"/>
     </row>
     <row r="1758">
       <c r="A1758" s="6"/>
-      <c r="B1758" s="11"/>
+      <c r="B1758" s="13"/>
       <c r="C1758" s="6"/>
       <c r="D1758" s="6"/>
       <c r="E1758" s="6"/>
     </row>
     <row r="1759">
       <c r="A1759" s="6"/>
-      <c r="B1759" s="11"/>
+      <c r="B1759" s="13"/>
       <c r="C1759" s="6"/>
       <c r="D1759" s="6"/>
       <c r="E1759" s="6"/>
     </row>
     <row r="1760">
       <c r="A1760" s="6"/>
-      <c r="B1760" s="11"/>
+      <c r="B1760" s="13"/>
       <c r="C1760" s="6"/>
       <c r="D1760" s="6"/>
       <c r="E1760" s="6"/>
     </row>
     <row r="1761">
       <c r="A1761" s="6"/>
-      <c r="B1761" s="11"/>
+      <c r="B1761" s="13"/>
       <c r="C1761" s="6"/>
       <c r="D1761" s="6"/>
       <c r="E1761" s="6"/>
     </row>
     <row r="1762">
       <c r="A1762" s="6"/>
-      <c r="B1762" s="11"/>
+      <c r="B1762" s="13"/>
       <c r="C1762" s="6"/>
       <c r="D1762" s="6"/>
       <c r="E1762" s="6"/>
     </row>
     <row r="1763">
       <c r="A1763" s="6"/>
-      <c r="B1763" s="11"/>
+      <c r="B1763" s="13"/>
       <c r="C1763" s="6"/>
       <c r="D1763" s="6"/>
       <c r="E1763" s="6"/>
     </row>
     <row r="1764">
       <c r="A1764" s="6"/>
-      <c r="B1764" s="11"/>
+      <c r="B1764" s="13"/>
       <c r="C1764" s="6"/>
       <c r="D1764" s="6"/>
       <c r="E1764" s="6"/>
     </row>
     <row r="1765">
       <c r="A1765" s="6"/>
-      <c r="B1765" s="11"/>
+      <c r="B1765" s="13"/>
       <c r="C1765" s="6"/>
       <c r="D1765" s="6"/>
       <c r="E1765" s="6"/>
     </row>
     <row r="1766">
       <c r="A1766" s="6"/>
-      <c r="B1766" s="11"/>
+      <c r="B1766" s="13"/>
       <c r="C1766" s="6"/>
       <c r="D1766" s="6"/>
       <c r="E1766" s="6"/>
     </row>
     <row r="1767">
       <c r="A1767" s="6"/>
-      <c r="B1767" s="11"/>
+      <c r="B1767" s="13"/>
       <c r="C1767" s="6"/>
       <c r="D1767" s="6"/>
       <c r="E1767" s="6"/>
     </row>
     <row r="1768">
       <c r="A1768" s="6"/>
-      <c r="B1768" s="11"/>
+      <c r="B1768" s="13"/>
       <c r="C1768" s="6"/>
       <c r="D1768" s="6"/>
       <c r="E1768" s="6"/>
     </row>
     <row r="1769">
       <c r="A1769" s="6"/>
-      <c r="B1769" s="11"/>
+      <c r="B1769" s="13"/>
       <c r="C1769" s="6"/>
       <c r="D1769" s="6"/>
       <c r="E1769" s="6"/>
     </row>
     <row r="1770">
       <c r="A1770" s="6"/>
-      <c r="B1770" s="11"/>
+      <c r="B1770" s="13"/>
       <c r="C1770" s="6"/>
       <c r="D1770" s="6"/>
       <c r="E1770" s="6"/>
     </row>
     <row r="1771">
       <c r="A1771" s="6"/>
-      <c r="B1771" s="11"/>
+      <c r="B1771" s="13"/>
       <c r="C1771" s="6"/>
       <c r="D1771" s="6"/>
       <c r="E1771" s="6"/>
     </row>
     <row r="1772">
       <c r="A1772" s="6"/>
-      <c r="B1772" s="11"/>
+      <c r="B1772" s="13"/>
       <c r="C1772" s="6"/>
       <c r="D1772" s="6"/>
       <c r="E1772" s="6"/>
     </row>
     <row r="1773">
       <c r="A1773" s="6"/>
-      <c r="B1773" s="11"/>
+      <c r="B1773" s="13"/>
       <c r="C1773" s="6"/>
       <c r="D1773" s="6"/>
       <c r="E1773" s="6"/>
     </row>
     <row r="1774">
       <c r="A1774" s="6"/>
-      <c r="B1774" s="11"/>
+      <c r="B1774" s="13"/>
       <c r="C1774" s="6"/>
       <c r="D1774" s="6"/>
       <c r="E1774" s="6"/>
     </row>
     <row r="1775">
       <c r="A1775" s="6"/>
-      <c r="B1775" s="11"/>
+      <c r="B1775" s="13"/>
       <c r="C1775" s="6"/>
       <c r="D1775" s="6"/>
       <c r="E1775" s="6"/>
     </row>
     <row r="1776">
       <c r="A1776" s="6"/>
-      <c r="B1776" s="11"/>
+      <c r="B1776" s="13"/>
       <c r="C1776" s="6"/>
       <c r="D1776" s="6"/>
       <c r="E1776" s="6"/>
     </row>
     <row r="1777">
       <c r="A1777" s="6"/>
-      <c r="B1777" s="11"/>
+      <c r="B1777" s="13"/>
       <c r="C1777" s="6"/>
       <c r="D1777" s="6"/>
       <c r="E1777" s="6"/>
     </row>
     <row r="1778">
       <c r="A1778" s="6"/>
-      <c r="B1778" s="11"/>
+      <c r="B1778" s="13"/>
       <c r="C1778" s="6"/>
       <c r="D1778" s="6"/>
       <c r="E1778" s="6"/>
     </row>
     <row r="1779">
       <c r="A1779" s="6"/>
-      <c r="B1779" s="11"/>
+      <c r="B1779" s="13"/>
       <c r="C1779" s="6"/>
       <c r="D1779" s="6"/>
       <c r="E1779" s="6"/>
     </row>
     <row r="1780">
       <c r="A1780" s="6"/>
-      <c r="B1780" s="11"/>
+      <c r="B1780" s="13"/>
       <c r="C1780" s="6"/>
       <c r="D1780" s="6"/>
       <c r="E1780" s="6"/>
     </row>
     <row r="1781">
       <c r="A1781" s="6"/>
-      <c r="B1781" s="11"/>
+      <c r="B1781" s="13"/>
       <c r="C1781" s="6"/>
       <c r="D1781" s="6"/>
       <c r="E1781" s="6"/>
     </row>
     <row r="1782">
       <c r="A1782" s="6"/>
-      <c r="B1782" s="11"/>
+      <c r="B1782" s="13"/>
       <c r="C1782" s="6"/>
       <c r="D1782" s="6"/>
       <c r="E1782" s="6"/>
     </row>
     <row r="1783">
       <c r="A1783" s="6"/>
-      <c r="B1783" s="11"/>
+      <c r="B1783" s="13"/>
       <c r="C1783" s="6"/>
       <c r="D1783" s="6"/>
       <c r="E1783" s="6"/>
     </row>
     <row r="1784">
       <c r="A1784" s="6"/>
-      <c r="B1784" s="11"/>
+      <c r="B1784" s="13"/>
       <c r="C1784" s="6"/>
       <c r="D1784" s="6"/>
       <c r="E1784" s="6"/>
     </row>
     <row r="1785">
       <c r="A1785" s="6"/>
-      <c r="B1785" s="11"/>
+      <c r="B1785" s="13"/>
       <c r="C1785" s="6"/>
       <c r="D1785" s="6"/>
       <c r="E1785" s="6"/>
     </row>
     <row r="1786">
       <c r="A1786" s="6"/>
-      <c r="B1786" s="11"/>
+      <c r="B1786" s="13"/>
       <c r="C1786" s="6"/>
       <c r="D1786" s="6"/>
       <c r="E1786" s="6"/>
     </row>
     <row r="1787">
       <c r="A1787" s="6"/>
-      <c r="B1787" s="11"/>
+      <c r="B1787" s="13"/>
       <c r="C1787" s="6"/>
       <c r="D1787" s="6"/>
       <c r="E1787" s="6"/>
     </row>
     <row r="1788">
       <c r="A1788" s="6"/>
-      <c r="B1788" s="11"/>
+      <c r="B1788" s="13"/>
       <c r="C1788" s="6"/>
       <c r="D1788" s="6"/>
       <c r="E1788" s="6"/>
     </row>
     <row r="1789">
       <c r="A1789" s="6"/>
-      <c r="B1789" s="11"/>
+      <c r="B1789" s="13"/>
       <c r="C1789" s="6"/>
       <c r="D1789" s="6"/>
       <c r="E1789" s="6"/>
     </row>
     <row r="1790">
       <c r="A1790" s="6"/>
-      <c r="B1790" s="11"/>
+      <c r="B1790" s="13"/>
       <c r="C1790" s="6"/>
       <c r="D1790" s="6"/>
       <c r="E1790" s="6"/>
     </row>
     <row r="1791">
       <c r="A1791" s="6"/>
-      <c r="B1791" s="11"/>
+      <c r="B1791" s="13"/>
       <c r="C1791" s="6"/>
       <c r="D1791" s="6"/>
       <c r="E1791" s="6"/>
     </row>
     <row r="1792">
       <c r="A1792" s="6"/>
-      <c r="B1792" s="11"/>
+      <c r="B1792" s="13"/>
       <c r="C1792" s="6"/>
       <c r="D1792" s="6"/>
       <c r="E1792" s="6"/>
     </row>
     <row r="1793">
       <c r="A1793" s="6"/>
-      <c r="B1793" s="11"/>
+      <c r="B1793" s="13"/>
       <c r="C1793" s="6"/>
       <c r="D1793" s="6"/>
       <c r="E1793" s="6"/>
     </row>
     <row r="1794">
       <c r="A1794" s="6"/>
-      <c r="B1794" s="11"/>
+      <c r="B1794" s="13"/>
       <c r="C1794" s="6"/>
       <c r="D1794" s="6"/>
       <c r="E1794" s="6"/>
     </row>
     <row r="1795">
       <c r="A1795" s="6"/>
-      <c r="B1795" s="11"/>
+      <c r="B1795" s="13"/>
       <c r="C1795" s="6"/>
       <c r="D1795" s="6"/>
       <c r="E1795" s="6"/>
     </row>
     <row r="1796">
       <c r="A1796" s="6"/>
-      <c r="B1796" s="11"/>
+      <c r="B1796" s="13"/>
       <c r="C1796" s="6"/>
       <c r="D1796" s="6"/>
       <c r="E1796" s="6"/>
     </row>
     <row r="1797">
       <c r="A1797" s="6"/>
-      <c r="B1797" s="11"/>
+      <c r="B1797" s="13"/>
       <c r="C1797" s="6"/>
       <c r="D1797" s="6"/>
       <c r="E1797" s="6"/>
     </row>
     <row r="1798">
       <c r="A1798" s="6"/>
-      <c r="B1798" s="11"/>
+      <c r="B1798" s="13"/>
       <c r="C1798" s="6"/>
       <c r="D1798" s="6"/>
       <c r="E1798" s="6"/>
     </row>
     <row r="1799">
       <c r="A1799" s="6"/>
-      <c r="B1799" s="11"/>
+      <c r="B1799" s="13"/>
       <c r="C1799" s="6"/>
       <c r="D1799" s="6"/>
       <c r="E1799" s="6"/>
     </row>
     <row r="1800">
       <c r="A1800" s="6"/>
-      <c r="B1800" s="11"/>
+      <c r="B1800" s="13"/>
       <c r="C1800" s="6"/>
       <c r="D1800" s="6"/>
       <c r="E1800" s="6"/>
     </row>
     <row r="1801">
       <c r="A1801" s="6"/>
-      <c r="B1801" s="11"/>
+      <c r="B1801" s="13"/>
       <c r="C1801" s="6"/>
       <c r="D1801" s="6"/>
       <c r="E1801" s="6"/>
     </row>
     <row r="1802">
       <c r="A1802" s="6"/>
-      <c r="B1802" s="11"/>
+      <c r="B1802" s="13"/>
       <c r="C1802" s="6"/>
       <c r="D1802" s="6"/>
       <c r="E1802" s="6"/>
     </row>
     <row r="1803">
       <c r="A1803" s="6"/>
-      <c r="B1803" s="11"/>
+      <c r="B1803" s="13"/>
       <c r="C1803" s="6"/>
       <c r="D1803" s="6"/>
       <c r="E1803" s="6"/>
     </row>
     <row r="1804">
       <c r="A1804" s="6"/>
-      <c r="B1804" s="11"/>
+      <c r="B1804" s="13"/>
       <c r="C1804" s="6"/>
       <c r="D1804" s="6"/>
       <c r="E1804" s="6"/>
     </row>
     <row r="1805">
       <c r="A1805" s="6"/>
-      <c r="B1805" s="11"/>
+      <c r="B1805" s="13"/>
       <c r="C1805" s="6"/>
       <c r="D1805" s="6"/>
       <c r="E1805" s="6"/>
     </row>
     <row r="1806">
       <c r="A1806" s="6"/>
-      <c r="B1806" s="11"/>
+      <c r="B1806" s="13"/>
       <c r="C1806" s="6"/>
       <c r="D1806" s="6"/>
       <c r="E1806" s="6"/>
     </row>
     <row r="1807">
       <c r="A1807" s="6"/>
-      <c r="B1807" s="11"/>
+      <c r="B1807" s="13"/>
       <c r="C1807" s="6"/>
       <c r="D1807" s="6"/>
       <c r="E1807" s="6"/>
     </row>
     <row r="1808">
       <c r="A1808" s="6"/>
-      <c r="B1808" s="11"/>
+      <c r="B1808" s="13"/>
       <c r="C1808" s="6"/>
       <c r="D1808" s="6"/>
       <c r="E1808" s="6"/>
     </row>
     <row r="1809">
       <c r="A1809" s="6"/>
-      <c r="B1809" s="11"/>
+      <c r="B1809" s="13"/>
       <c r="C1809" s="6"/>
       <c r="D1809" s="6"/>
       <c r="E1809" s="6"/>
     </row>
     <row r="1810">
       <c r="A1810" s="6"/>
-      <c r="B1810" s="11"/>
+      <c r="B1810" s="13"/>
       <c r="C1810" s="6"/>
       <c r="D1810" s="6"/>
       <c r="E1810" s="6"/>
     </row>
     <row r="1811">
       <c r="A1811" s="6"/>
-      <c r="B1811" s="11"/>
+      <c r="B1811" s="13"/>
       <c r="C1811" s="6"/>
       <c r="D1811" s="6"/>
       <c r="E1811" s="6"/>
     </row>
     <row r="1812">
       <c r="A1812" s="6"/>
-      <c r="B1812" s="11"/>
+      <c r="B1812" s="13"/>
       <c r="C1812" s="6"/>
       <c r="D1812" s="6"/>
       <c r="E1812" s="6"/>
     </row>
     <row r="1813">
       <c r="A1813" s="6"/>
-      <c r="B1813" s="11"/>
+      <c r="B1813" s="13"/>
       <c r="C1813" s="6"/>
       <c r="D1813" s="6"/>
       <c r="E1813" s="6"/>
     </row>
     <row r="1814">
       <c r="A1814" s="6"/>
-      <c r="B1814" s="11"/>
+      <c r="B1814" s="13"/>
       <c r="C1814" s="6"/>
       <c r="D1814" s="6"/>
       <c r="E1814" s="6"/>
     </row>
     <row r="1815">
       <c r="A1815" s="6"/>
-      <c r="B1815" s="11"/>
+      <c r="B1815" s="13"/>
       <c r="C1815" s="6"/>
       <c r="D1815" s="6"/>
       <c r="E1815" s="6"/>
     </row>
     <row r="1816">
       <c r="A1816" s="6"/>
-      <c r="B1816" s="11"/>
+      <c r="B1816" s="13"/>
       <c r="C1816" s="6"/>
       <c r="D1816" s="6"/>
       <c r="E1816" s="6"/>
     </row>
     <row r="1817">
       <c r="A1817" s="6"/>
-      <c r="B1817" s="11"/>
+      <c r="B1817" s="13"/>
       <c r="C1817" s="6"/>
       <c r="D1817" s="6"/>
       <c r="E1817" s="6"/>
     </row>
     <row r="1818">
       <c r="A1818" s="6"/>
-      <c r="B1818" s="11"/>
+      <c r="B1818" s="13"/>
       <c r="C1818" s="6"/>
       <c r="D1818" s="6"/>
       <c r="E1818" s="6"/>
     </row>
     <row r="1819">
       <c r="A1819" s="6"/>
-      <c r="B1819" s="11"/>
+      <c r="B1819" s="13"/>
       <c r="C1819" s="6"/>
       <c r="D1819" s="6"/>
       <c r="E1819" s="6"/>
     </row>
     <row r="1820">
       <c r="A1820" s="6"/>
-      <c r="B1820" s="11"/>
+      <c r="B1820" s="13"/>
       <c r="C1820" s="6"/>
       <c r="D1820" s="6"/>
       <c r="E1820" s="6"/>
     </row>
     <row r="1821">
       <c r="A1821" s="6"/>
-      <c r="B1821" s="11"/>
+      <c r="B1821" s="13"/>
       <c r="C1821" s="6"/>
       <c r="D1821" s="6"/>
       <c r="E1821" s="6"/>
     </row>
     <row r="1822">
       <c r="A1822" s="6"/>
-      <c r="B1822" s="11"/>
+      <c r="B1822" s="13"/>
       <c r="C1822" s="6"/>
       <c r="D1822" s="6"/>
       <c r="E1822" s="6"/>
     </row>
     <row r="1823">
       <c r="A1823" s="6"/>
-      <c r="B1823" s="11"/>
+      <c r="B1823" s="13"/>
       <c r="C1823" s="6"/>
       <c r="D1823" s="6"/>
       <c r="E1823" s="6"/>
     </row>
     <row r="1824">
       <c r="A1824" s="6"/>
-      <c r="B1824" s="11"/>
+      <c r="B1824" s="13"/>
       <c r="C1824" s="6"/>
       <c r="D1824" s="6"/>
       <c r="E1824" s="6"/>
     </row>
     <row r="1825">
       <c r="A1825" s="6"/>
-      <c r="B1825" s="11"/>
+      <c r="B1825" s="13"/>
       <c r="C1825" s="6"/>
       <c r="D1825" s="6"/>
       <c r="E1825" s="6"/>
     </row>
     <row r="1826">
       <c r="A1826" s="6"/>
-      <c r="B1826" s="11"/>
+      <c r="B1826" s="13"/>
       <c r="C1826" s="6"/>
       <c r="D1826" s="6"/>
       <c r="E1826" s="6"/>
     </row>
     <row r="1827">
       <c r="A1827" s="6"/>
-      <c r="B1827" s="11"/>
+      <c r="B1827" s="13"/>
       <c r="C1827" s="6"/>
       <c r="D1827" s="6"/>
       <c r="E1827" s="6"/>
     </row>
     <row r="1828">
       <c r="A1828" s="6"/>
-      <c r="B1828" s="11"/>
+      <c r="B1828" s="13"/>
       <c r="C1828" s="6"/>
       <c r="D1828" s="6"/>
       <c r="E1828" s="6"/>
     </row>
     <row r="1829">
       <c r="A1829" s="6"/>
-      <c r="B1829" s="11"/>
+      <c r="B1829" s="13"/>
       <c r="C1829" s="6"/>
       <c r="D1829" s="6"/>
       <c r="E1829" s="6"/>
     </row>
     <row r="1830">
       <c r="A1830" s="6"/>
-      <c r="B1830" s="11"/>
+      <c r="B1830" s="13"/>
       <c r="C1830" s="6"/>
       <c r="D1830" s="6"/>
       <c r="E1830" s="6"/>
     </row>
     <row r="1831">
       <c r="A1831" s="6"/>
-      <c r="B1831" s="11"/>
+      <c r="B1831" s="13"/>
       <c r="C1831" s="6"/>
       <c r="D1831" s="6"/>
       <c r="E1831" s="6"/>
     </row>
     <row r="1832">
       <c r="A1832" s="6"/>
-      <c r="B1832" s="11"/>
+      <c r="B1832" s="13"/>
       <c r="C1832" s="6"/>
       <c r="D1832" s="6"/>
       <c r="E1832" s="6"/>
     </row>
     <row r="1833">
       <c r="A1833" s="6"/>
-      <c r="B1833" s="11"/>
+      <c r="B1833" s="13"/>
       <c r="C1833" s="6"/>
       <c r="D1833" s="6"/>
       <c r="E1833" s="6"/>
     </row>
     <row r="1834">
       <c r="A1834" s="6"/>
-      <c r="B1834" s="11"/>
+      <c r="B1834" s="13"/>
       <c r="C1834" s="6"/>
       <c r="D1834" s="6"/>
       <c r="E1834" s="6"/>
     </row>
     <row r="1835">
       <c r="A1835" s="6"/>
-      <c r="B1835" s="11"/>
+      <c r="B1835" s="13"/>
       <c r="C1835" s="6"/>
       <c r="D1835" s="6"/>
       <c r="E1835" s="6"/>
     </row>
     <row r="1836">
       <c r="A1836" s="6"/>
-      <c r="B1836" s="11"/>
+      <c r="B1836" s="13"/>
       <c r="C1836" s="6"/>
       <c r="D1836" s="6"/>
       <c r="E1836" s="6"/>
     </row>
     <row r="1837">
       <c r="A1837" s="6"/>
-      <c r="B1837" s="11"/>
+      <c r="B1837" s="13"/>
       <c r="C1837" s="6"/>
       <c r="D1837" s="6"/>
       <c r="E1837" s="6"/>
     </row>
     <row r="1838">
       <c r="A1838" s="6"/>
-      <c r="B1838" s="11"/>
+      <c r="B1838" s="13"/>
       <c r="C1838" s="6"/>
       <c r="D1838" s="6"/>
       <c r="E1838" s="6"/>
     </row>
     <row r="1839">
       <c r="A1839" s="6"/>
-      <c r="B1839" s="11"/>
+      <c r="B1839" s="13"/>
       <c r="C1839" s="6"/>
       <c r="D1839" s="6"/>
       <c r="E1839" s="6"/>
     </row>
     <row r="1840">
       <c r="A1840" s="6"/>
-      <c r="B1840" s="11"/>
+      <c r="B1840" s="13"/>
       <c r="C1840" s="6"/>
       <c r="D1840" s="6"/>
       <c r="E1840" s="6"/>
     </row>
     <row r="1841">
       <c r="A1841" s="6"/>
-      <c r="B1841" s="11"/>
+      <c r="B1841" s="13"/>
       <c r="C1841" s="6"/>
       <c r="D1841" s="6"/>
       <c r="E1841" s="6"/>
     </row>
     <row r="1842">
       <c r="A1842" s="6"/>
-      <c r="B1842" s="11"/>
+      <c r="B1842" s="13"/>
       <c r="C1842" s="6"/>
       <c r="D1842" s="6"/>
       <c r="E1842" s="6"/>
     </row>
     <row r="1843">
       <c r="A1843" s="6"/>
-      <c r="B1843" s="11"/>
+      <c r="B1843" s="13"/>
       <c r="C1843" s="6"/>
       <c r="D1843" s="6"/>
       <c r="E1843" s="6"/>
     </row>
     <row r="1844">
       <c r="A1844" s="6"/>
-      <c r="B1844" s="11"/>
+      <c r="B1844" s="13"/>
       <c r="C1844" s="6"/>
       <c r="D1844" s="6"/>
       <c r="E1844" s="6"/>
     </row>
     <row r="1845">
       <c r="A1845" s="6"/>
-      <c r="B1845" s="11"/>
+      <c r="B1845" s="13"/>
       <c r="C1845" s="6"/>
       <c r="D1845" s="6"/>
       <c r="E1845" s="6"/>
     </row>
     <row r="1846">
       <c r="A1846" s="6"/>
-      <c r="B1846" s="11"/>
+      <c r="B1846" s="13"/>
       <c r="C1846" s="6"/>
       <c r="D1846" s="6"/>
       <c r="E1846" s="6"/>
     </row>
     <row r="1847">
       <c r="A1847" s="6"/>
-      <c r="B1847" s="11"/>
+      <c r="B1847" s="13"/>
       <c r="C1847" s="6"/>
       <c r="D1847" s="6"/>
       <c r="E1847" s="6"/>
     </row>
     <row r="1848">
       <c r="A1848" s="6"/>
-      <c r="B1848" s="11"/>
+      <c r="B1848" s="13"/>
       <c r="C1848" s="6"/>
       <c r="D1848" s="6"/>
       <c r="E1848" s="6"/>
     </row>
     <row r="1849">
       <c r="A1849" s="6"/>
-      <c r="B1849" s="11"/>
+      <c r="B1849" s="13"/>
       <c r="C1849" s="6"/>
       <c r="D1849" s="6"/>
       <c r="E1849" s="6"/>
     </row>
     <row r="1850">
       <c r="A1850" s="6"/>
-      <c r="B1850" s="11"/>
+      <c r="B1850" s="13"/>
       <c r="C1850" s="6"/>
       <c r="D1850" s="6"/>
       <c r="E1850" s="6"/>
     </row>
     <row r="1851">
       <c r="A1851" s="6"/>
-      <c r="B1851" s="11"/>
+      <c r="B1851" s="13"/>
       <c r="C1851" s="6"/>
       <c r="D1851" s="6"/>
       <c r="E1851" s="6"/>
     </row>
     <row r="1852">
       <c r="A1852" s="6"/>
-      <c r="B1852" s="11"/>
+      <c r="B1852" s="13"/>
       <c r="C1852" s="6"/>
       <c r="D1852" s="6"/>
       <c r="E1852" s="6"/>
     </row>
     <row r="1853">
       <c r="A1853" s="6"/>
-      <c r="B1853" s="11"/>
+      <c r="B1853" s="13"/>
       <c r="C1853" s="6"/>
       <c r="D1853" s="6"/>
       <c r="E1853" s="6"/>
     </row>
     <row r="1854">
       <c r="A1854" s="6"/>
-      <c r="B1854" s="11"/>
+      <c r="B1854" s="13"/>
       <c r="C1854" s="6"/>
       <c r="D1854" s="6"/>
       <c r="E1854" s="6"/>
     </row>
     <row r="1855">
       <c r="A1855" s="6"/>
-      <c r="B1855" s="11"/>
+      <c r="B1855" s="13"/>
       <c r="C1855" s="6"/>
       <c r="D1855" s="6"/>
       <c r="E1855" s="6"/>
     </row>
     <row r="1856">
       <c r="A1856" s="6"/>
-      <c r="B1856" s="11"/>
+      <c r="B1856" s="13"/>
       <c r="C1856" s="6"/>
       <c r="D1856" s="6"/>
       <c r="E1856" s="6"/>
     </row>
     <row r="1857">
       <c r="A1857" s="6"/>
-      <c r="B1857" s="11"/>
+      <c r="B1857" s="13"/>
       <c r="C1857" s="6"/>
       <c r="D1857" s="6"/>
       <c r="E1857" s="6"/>
     </row>
     <row r="1858">
       <c r="A1858" s="6"/>
-      <c r="B1858" s="11"/>
+      <c r="B1858" s="13"/>
       <c r="C1858" s="6"/>
       <c r="D1858" s="6"/>
       <c r="E1858" s="6"/>
     </row>
     <row r="1859">
       <c r="A1859" s="6"/>
-      <c r="B1859" s="11"/>
+      <c r="B1859" s="13"/>
       <c r="C1859" s="6"/>
       <c r="D1859" s="6"/>
       <c r="E1859" s="6"/>
     </row>
     <row r="1860">
       <c r="A1860" s="6"/>
-      <c r="B1860" s="11"/>
+      <c r="B1860" s="13"/>
       <c r="C1860" s="6"/>
       <c r="D1860" s="6"/>
       <c r="E1860" s="6"/>
     </row>
     <row r="1861">
       <c r="A1861" s="6"/>
-      <c r="B1861" s="11"/>
+      <c r="B1861" s="13"/>
       <c r="C1861" s="6"/>
       <c r="D1861" s="6"/>
       <c r="E1861" s="6"/>
     </row>
     <row r="1862">
       <c r="A1862" s="6"/>
-      <c r="B1862" s="11"/>
+      <c r="B1862" s="13"/>
       <c r="C1862" s="6"/>
       <c r="D1862" s="6"/>
       <c r="E1862" s="6"/>
     </row>
     <row r="1863">
       <c r="A1863" s="6"/>
-      <c r="B1863" s="11"/>
+      <c r="B1863" s="13"/>
       <c r="C1863" s="6"/>
       <c r="D1863" s="6"/>
       <c r="E1863" s="6"/>
     </row>
     <row r="1864">
       <c r="A1864" s="6"/>
-      <c r="B1864" s="11"/>
+      <c r="B1864" s="13"/>
       <c r="C1864" s="6"/>
       <c r="D1864" s="6"/>
       <c r="E1864" s="6"/>
     </row>
     <row r="1865">
       <c r="A1865" s="6"/>
-      <c r="B1865" s="11"/>
+      <c r="B1865" s="13"/>
       <c r="C1865" s="6"/>
       <c r="D1865" s="6"/>
       <c r="E1865" s="6"/>
     </row>
     <row r="1866">
       <c r="A1866" s="6"/>
-      <c r="B1866" s="11"/>
+      <c r="B1866" s="13"/>
       <c r="C1866" s="6"/>
       <c r="D1866" s="6"/>
       <c r="E1866" s="6"/>
     </row>
     <row r="1867">
       <c r="A1867" s="6"/>
-      <c r="B1867" s="11"/>
+      <c r="B1867" s="13"/>
       <c r="C1867" s="6"/>
       <c r="D1867" s="6"/>
       <c r="E1867" s="6"/>
     </row>
     <row r="1868">
       <c r="A1868" s="6"/>
-      <c r="B1868" s="11"/>
+      <c r="B1868" s="13"/>
       <c r="C1868" s="6"/>
       <c r="D1868" s="6"/>
       <c r="E1868" s="6"/>
     </row>
     <row r="1869">
       <c r="A1869" s="6"/>
-      <c r="B1869" s="11"/>
+      <c r="B1869" s="13"/>
       <c r="C1869" s="6"/>
       <c r="D1869" s="6"/>
       <c r="E1869" s="6"/>
     </row>
     <row r="1870">
       <c r="A1870" s="6"/>
-      <c r="B1870" s="11"/>
+      <c r="B1870" s="13"/>
       <c r="C1870" s="6"/>
       <c r="D1870" s="6"/>
       <c r="E1870" s="6"/>
     </row>
     <row r="1871">
       <c r="A1871" s="6"/>
-      <c r="B1871" s="11"/>
+      <c r="B1871" s="13"/>
       <c r="C1871" s="6"/>
       <c r="D1871" s="6"/>
       <c r="E1871" s="6"/>
     </row>
     <row r="1872">
       <c r="A1872" s="6"/>
-      <c r="B1872" s="11"/>
+      <c r="B1872" s="13"/>
       <c r="C1872" s="6"/>
       <c r="D1872" s="6"/>
       <c r="E1872" s="6"/>
     </row>
     <row r="1873">
       <c r="A1873" s="6"/>
-      <c r="B1873" s="11"/>
+      <c r="B1873" s="13"/>
       <c r="C1873" s="6"/>
       <c r="D1873" s="6"/>
       <c r="E1873" s="6"/>
     </row>
     <row r="1874">
       <c r="A1874" s="6"/>
-      <c r="B1874" s="11"/>
+      <c r="B1874" s="13"/>
       <c r="C1874" s="6"/>
       <c r="D1874" s="6"/>
       <c r="E1874" s="6"/>
     </row>
     <row r="1875">
       <c r="A1875" s="6"/>
-      <c r="B1875" s="11"/>
+      <c r="B1875" s="13"/>
       <c r="C1875" s="6"/>
       <c r="D1875" s="6"/>
       <c r="E1875" s="6"/>
     </row>
     <row r="1876">
       <c r="A1876" s="6"/>
-      <c r="B1876" s="11"/>
+      <c r="B1876" s="13"/>
       <c r="C1876" s="6"/>
       <c r="D1876" s="6"/>
       <c r="E1876" s="6"/>
     </row>
     <row r="1877">
       <c r="A1877" s="6"/>
-      <c r="B1877" s="11"/>
+      <c r="B1877" s="13"/>
       <c r="C1877" s="6"/>
       <c r="D1877" s="6"/>
       <c r="E1877" s="6"/>
     </row>
     <row r="1878">
       <c r="A1878" s="6"/>
-      <c r="B1878" s="11"/>
+      <c r="B1878" s="13"/>
       <c r="C1878" s="6"/>
       <c r="D1878" s="6"/>
       <c r="E1878" s="6"/>
     </row>
     <row r="1879">
       <c r="A1879" s="6"/>
-      <c r="B1879" s="11"/>
+      <c r="B1879" s="13"/>
       <c r="C1879" s="6"/>
       <c r="D1879" s="6"/>
       <c r="E1879" s="6"/>
     </row>
     <row r="1880">
       <c r="A1880" s="6"/>
-      <c r="B1880" s="11"/>
+      <c r="B1880" s="13"/>
       <c r="C1880" s="6"/>
       <c r="D1880" s="6"/>
       <c r="E1880" s="6"/>
     </row>
     <row r="1881">
       <c r="A1881" s="6"/>
-      <c r="B1881" s="11"/>
+      <c r="B1881" s="13"/>
       <c r="C1881" s="6"/>
       <c r="D1881" s="6"/>
       <c r="E1881" s="6"/>
     </row>
     <row r="1882">
       <c r="A1882" s="6"/>
-      <c r="B1882" s="11"/>
+      <c r="B1882" s="13"/>
       <c r="C1882" s="6"/>
       <c r="D1882" s="6"/>
       <c r="E1882" s="6"/>
     </row>
     <row r="1883">
       <c r="A1883" s="6"/>
-      <c r="B1883" s="11"/>
+      <c r="B1883" s="13"/>
       <c r="C1883" s="6"/>
       <c r="D1883" s="6"/>
       <c r="E1883" s="6"/>
     </row>
     <row r="1884">
       <c r="A1884" s="6"/>
-      <c r="B1884" s="11"/>
+      <c r="B1884" s="13"/>
       <c r="C1884" s="6"/>
       <c r="D1884" s="6"/>
       <c r="E1884" s="6"/>
     </row>
     <row r="1885">
       <c r="A1885" s="6"/>
-      <c r="B1885" s="11"/>
+      <c r="B1885" s="13"/>
       <c r="C1885" s="6"/>
       <c r="D1885" s="6"/>
       <c r="E1885" s="6"/>
     </row>
     <row r="1886">
       <c r="A1886" s="6"/>
-      <c r="B1886" s="11"/>
+      <c r="B1886" s="13"/>
       <c r="C1886" s="6"/>
       <c r="D1886" s="6"/>
       <c r="E1886" s="6"/>
     </row>
     <row r="1887">
       <c r="A1887" s="6"/>
-      <c r="B1887" s="11"/>
+      <c r="B1887" s="13"/>
       <c r="C1887" s="6"/>
       <c r="D1887" s="6"/>
       <c r="E1887" s="6"/>
     </row>
     <row r="1888">
       <c r="A1888" s="6"/>
-      <c r="B1888" s="11"/>
+      <c r="B1888" s="13"/>
       <c r="C1888" s="6"/>
       <c r="D1888" s="6"/>
       <c r="E1888" s="6"/>
     </row>
     <row r="1889">
       <c r="A1889" s="6"/>
-      <c r="B1889" s="11"/>
+      <c r="B1889" s="13"/>
       <c r="C1889" s="6"/>
       <c r="D1889" s="6"/>
       <c r="E1889" s="6"/>
     </row>
     <row r="1890">
       <c r="A1890" s="6"/>
-      <c r="B1890" s="11"/>
+      <c r="B1890" s="13"/>
       <c r="C1890" s="6"/>
       <c r="D1890" s="6"/>
       <c r="E1890" s="6"/>
     </row>
     <row r="1891">
       <c r="A1891" s="6"/>
-      <c r="B1891" s="11"/>
+      <c r="B1891" s="13"/>
       <c r="C1891" s="6"/>
       <c r="D1891" s="6"/>
       <c r="E1891" s="6"/>
     </row>
     <row r="1892">
       <c r="A1892" s="6"/>
-      <c r="B1892" s="11"/>
+      <c r="B1892" s="13"/>
       <c r="C1892" s="6"/>
       <c r="D1892" s="6"/>
       <c r="E1892" s="6"/>
     </row>
     <row r="1893">
       <c r="A1893" s="6"/>
-      <c r="B1893" s="11"/>
+      <c r="B1893" s="13"/>
       <c r="C1893" s="6"/>
       <c r="D1893" s="6"/>
       <c r="E1893" s="6"/>
     </row>
     <row r="1894">
       <c r="A1894" s="6"/>
-      <c r="B1894" s="11"/>
+      <c r="B1894" s="13"/>
       <c r="C1894" s="6"/>
       <c r="D1894" s="6"/>
       <c r="E1894" s="6"/>
     </row>
     <row r="1895">
       <c r="A1895" s="6"/>
-      <c r="B1895" s="11"/>
+      <c r="B1895" s="13"/>
       <c r="C1895" s="6"/>
       <c r="D1895" s="6"/>
       <c r="E1895" s="6"/>
     </row>
     <row r="1896">
       <c r="A1896" s="6"/>
-      <c r="B1896" s="11"/>
+      <c r="B1896" s="13"/>
       <c r="C1896" s="6"/>
       <c r="D1896" s="6"/>
       <c r="E1896" s="6"/>
     </row>
     <row r="1897">
       <c r="A1897" s="6"/>
-      <c r="B1897" s="11"/>
+      <c r="B1897" s="13"/>
       <c r="C1897" s="6"/>
       <c r="D1897" s="6"/>
       <c r="E1897" s="6"/>
     </row>
     <row r="1898">
       <c r="A1898" s="6"/>
-      <c r="B1898" s="11"/>
+      <c r="B1898" s="13"/>
       <c r="C1898" s="6"/>
       <c r="D1898" s="6"/>
       <c r="E1898" s="6"/>
     </row>
     <row r="1899">
       <c r="A1899" s="6"/>
-      <c r="B1899" s="11"/>
+      <c r="B1899" s="13"/>
       <c r="C1899" s="6"/>
       <c r="D1899" s="6"/>
       <c r="E1899" s="6"/>
     </row>
     <row r="1900">
       <c r="A1900" s="6"/>
-      <c r="B1900" s="11"/>
+      <c r="B1900" s="13"/>
       <c r="C1900" s="6"/>
       <c r="D1900" s="6"/>
       <c r="E1900" s="6"/>
     </row>
     <row r="1901">
       <c r="A1901" s="6"/>
-      <c r="B1901" s="11"/>
+      <c r="B1901" s="13"/>
       <c r="C1901" s="6"/>
       <c r="D1901" s="6"/>
       <c r="E1901" s="6"/>
     </row>
     <row r="1902">
       <c r="A1902" s="6"/>
-      <c r="B1902" s="11"/>
+      <c r="B1902" s="13"/>
       <c r="C1902" s="6"/>
       <c r="D1902" s="6"/>
       <c r="E1902" s="6"/>
     </row>
     <row r="1903">
       <c r="A1903" s="6"/>
-      <c r="B1903" s="11"/>
+      <c r="B1903" s="13"/>
       <c r="C1903" s="6"/>
       <c r="D1903" s="6"/>
       <c r="E1903" s="6"/>
     </row>
     <row r="1904">
       <c r="A1904" s="6"/>
-      <c r="B1904" s="11"/>
+      <c r="B1904" s="13"/>
       <c r="C1904" s="6"/>
       <c r="D1904" s="6"/>
       <c r="E1904" s="6"/>
     </row>
     <row r="1905">
       <c r="A1905" s="6"/>
-      <c r="B1905" s="11"/>
+      <c r="B1905" s="13"/>
       <c r="C1905" s="6"/>
       <c r="D1905" s="6"/>
       <c r="E1905" s="6"/>
     </row>
     <row r="1906">
       <c r="A1906" s="6"/>
-      <c r="B1906" s="11"/>
+      <c r="B1906" s="13"/>
       <c r="C1906" s="6"/>
       <c r="D1906" s="6"/>
       <c r="E1906" s="6"/>
     </row>
     <row r="1907">
       <c r="A1907" s="6"/>
-      <c r="B1907" s="11"/>
+      <c r="B1907" s="13"/>
       <c r="C1907" s="6"/>
       <c r="D1907" s="6"/>
       <c r="E1907" s="6"/>
     </row>
     <row r="1908">
       <c r="A1908" s="6"/>
-      <c r="B1908" s="11"/>
+      <c r="B1908" s="13"/>
       <c r="C1908" s="6"/>
       <c r="D1908" s="6"/>
       <c r="E1908" s="6"/>
     </row>
     <row r="1909">
       <c r="A1909" s="6"/>
-      <c r="B1909" s="11"/>
+      <c r="B1909" s="13"/>
       <c r="C1909" s="6"/>
       <c r="D1909" s="6"/>
       <c r="E1909" s="6"/>
     </row>
     <row r="1910">
       <c r="A1910" s="6"/>
-      <c r="B1910" s="11"/>
+      <c r="B1910" s="13"/>
       <c r="C1910" s="6"/>
       <c r="D1910" s="6"/>
       <c r="E1910" s="6"/>
     </row>
     <row r="1911">
       <c r="A1911" s="6"/>
-      <c r="B1911" s="11"/>
+      <c r="B1911" s="13"/>
       <c r="C1911" s="6"/>
       <c r="D1911" s="6"/>
       <c r="E1911" s="6"/>
     </row>
     <row r="1912">
       <c r="A1912" s="6"/>
-      <c r="B1912" s="11"/>
+      <c r="B1912" s="13"/>
       <c r="C1912" s="6"/>
       <c r="D1912" s="6"/>
       <c r="E1912" s="6"/>
     </row>
     <row r="1913">
       <c r="A1913" s="6"/>
-      <c r="B1913" s="11"/>
+      <c r="B1913" s="13"/>
       <c r="C1913" s="6"/>
       <c r="D1913" s="6"/>
       <c r="E1913" s="6"/>
     </row>
     <row r="1914">
       <c r="A1914" s="6"/>
-      <c r="B1914" s="11"/>
+      <c r="B1914" s="13"/>
       <c r="C1914" s="6"/>
       <c r="D1914" s="6"/>
       <c r="E1914" s="6"/>
     </row>
     <row r="1915">
       <c r="A1915" s="6"/>
-      <c r="B1915" s="11"/>
+      <c r="B1915" s="13"/>
       <c r="C1915" s="6"/>
       <c r="D1915" s="6"/>
       <c r="E1915" s="6"/>
     </row>
     <row r="1916">
       <c r="A1916" s="6"/>
-      <c r="B1916" s="11"/>
+      <c r="B1916" s="13"/>
       <c r="C1916" s="6"/>
       <c r="D1916" s="6"/>
       <c r="E1916" s="6"/>
     </row>
     <row r="1917">
       <c r="A1917" s="6"/>
-      <c r="B1917" s="11"/>
+      <c r="B1917" s="13"/>
       <c r="C1917" s="6"/>
       <c r="D1917" s="6"/>
       <c r="E1917" s="6"/>
     </row>
     <row r="1918">
       <c r="A1918" s="6"/>
-      <c r="B1918" s="11"/>
+      <c r="B1918" s="13"/>
       <c r="C1918" s="6"/>
       <c r="D1918" s="6"/>
       <c r="E1918" s="6"/>
     </row>
     <row r="1919">
       <c r="A1919" s="6"/>
-      <c r="B1919" s="11"/>
+      <c r="B1919" s="13"/>
       <c r="C1919" s="6"/>
       <c r="D1919" s="6"/>
       <c r="E1919" s="6"/>
     </row>
     <row r="1920">
       <c r="A1920" s="6"/>
-      <c r="B1920" s="11"/>
+      <c r="B1920" s="13"/>
       <c r="C1920" s="6"/>
       <c r="D1920" s="6"/>
       <c r="E1920" s="6"/>
     </row>
     <row r="1921">
       <c r="A1921" s="6"/>
-      <c r="B1921" s="11"/>
+      <c r="B1921" s="13"/>
       <c r="C1921" s="6"/>
       <c r="D1921" s="6"/>
       <c r="E1921" s="6"/>
     </row>
     <row r="1922">
       <c r="A1922" s="6"/>
-      <c r="B1922" s="11"/>
+      <c r="B1922" s="13"/>
       <c r="C1922" s="6"/>
       <c r="D1922" s="6"/>
       <c r="E1922" s="6"/>
     </row>
     <row r="1923">
       <c r="A1923" s="6"/>
-      <c r="B1923" s="11"/>
+      <c r="B1923" s="13"/>
       <c r="C1923" s="6"/>
       <c r="D1923" s="6"/>
       <c r="E1923" s="6"/>
     </row>
     <row r="1924">
       <c r="A1924" s="6"/>
-      <c r="B1924" s="11"/>
+      <c r="B1924" s="13"/>
       <c r="C1924" s="6"/>
       <c r="D1924" s="6"/>
       <c r="E1924" s="6"/>
     </row>
     <row r="1925">
       <c r="A1925" s="6"/>
-      <c r="B1925" s="11"/>
+      <c r="B1925" s="13"/>
       <c r="C1925" s="6"/>
       <c r="D1925" s="6"/>
       <c r="E1925" s="6"/>
     </row>
     <row r="1926">
       <c r="A1926" s="6"/>
-      <c r="B1926" s="11"/>
+      <c r="B1926" s="13"/>
       <c r="C1926" s="6"/>
       <c r="D1926" s="6"/>
       <c r="E1926" s="6"/>
     </row>
     <row r="1927">
       <c r="A1927" s="6"/>
-      <c r="B1927" s="11"/>
+      <c r="B1927" s="13"/>
       <c r="C1927" s="6"/>
       <c r="D1927" s="6"/>
       <c r="E1927" s="6"/>
     </row>
     <row r="1928">
       <c r="A1928" s="6"/>
-      <c r="B1928" s="11"/>
+      <c r="B1928" s="13"/>
       <c r="C1928" s="6"/>
       <c r="D1928" s="6"/>
       <c r="E1928" s="6"/>
     </row>
     <row r="1929">
       <c r="A1929" s="6"/>
-      <c r="B1929" s="11"/>
+      <c r="B1929" s="13"/>
       <c r="C1929" s="6"/>
       <c r="D1929" s="6"/>
       <c r="E1929" s="6"/>
     </row>
     <row r="1930">
       <c r="A1930" s="6"/>
-      <c r="B1930" s="11"/>
+      <c r="B1930" s="13"/>
       <c r="C1930" s="6"/>
       <c r="D1930" s="6"/>
       <c r="E1930" s="6"/>
     </row>
     <row r="1931">
       <c r="A1931" s="6"/>
-      <c r="B1931" s="11"/>
+      <c r="B1931" s="13"/>
       <c r="C1931" s="6"/>
       <c r="D1931" s="6"/>
       <c r="E1931" s="6"/>
     </row>
     <row r="1932">
       <c r="A1932" s="6"/>
-      <c r="B1932" s="11"/>
+      <c r="B1932" s="13"/>
       <c r="C1932" s="6"/>
       <c r="D1932" s="6"/>
       <c r="E1932" s="6"/>
     </row>
     <row r="1933">
       <c r="A1933" s="6"/>
-      <c r="B1933" s="11"/>
+      <c r="B1933" s="13"/>
       <c r="C1933" s="6"/>
       <c r="D1933" s="6"/>
       <c r="E1933" s="6"/>
     </row>
     <row r="1934">
       <c r="A1934" s="6"/>
-      <c r="B1934" s="11"/>
+      <c r="B1934" s="13"/>
       <c r="C1934" s="6"/>
       <c r="D1934" s="6"/>
       <c r="E1934" s="6"/>
     </row>
     <row r="1935">
       <c r="A1935" s="6"/>
-      <c r="B1935" s="11"/>
+      <c r="B1935" s="13"/>
       <c r="C1935" s="6"/>
       <c r="D1935" s="6"/>
       <c r="E1935" s="6"/>
     </row>
     <row r="1936">
       <c r="A1936" s="6"/>
-      <c r="B1936" s="11"/>
+      <c r="B1936" s="13"/>
       <c r="C1936" s="6"/>
       <c r="D1936" s="6"/>
       <c r="E1936" s="6"/>
     </row>
     <row r="1937">
       <c r="A1937" s="6"/>
-      <c r="B1937" s="11"/>
+      <c r="B1937" s="13"/>
       <c r="C1937" s="6"/>
       <c r="D1937" s="6"/>
       <c r="E1937" s="6"/>
     </row>
     <row r="1938">
       <c r="A1938" s="6"/>
-      <c r="B1938" s="11"/>
+      <c r="B1938" s="13"/>
       <c r="C1938" s="6"/>
       <c r="D1938" s="6"/>
       <c r="E1938" s="6"/>
     </row>
     <row r="1939">
       <c r="A1939" s="6"/>
-      <c r="B1939" s="11"/>
+      <c r="B1939" s="13"/>
       <c r="C1939" s="6"/>
       <c r="D1939" s="6"/>
       <c r="E1939" s="6"/>
     </row>
     <row r="1940">
       <c r="A1940" s="6"/>
-      <c r="B1940" s="11"/>
+      <c r="B1940" s="13"/>
       <c r="C1940" s="6"/>
       <c r="D1940" s="6"/>
       <c r="E1940" s="6"/>
     </row>
     <row r="1941">
       <c r="A1941" s="6"/>
-      <c r="B1941" s="11"/>
+      <c r="B1941" s="13"/>
       <c r="C1941" s="6"/>
       <c r="D1941" s="6"/>
       <c r="E1941" s="6"/>
     </row>
     <row r="1942">
       <c r="A1942" s="6"/>
-      <c r="B1942" s="11"/>
+      <c r="B1942" s="13"/>
       <c r="C1942" s="6"/>
       <c r="D1942" s="6"/>
       <c r="E1942" s="6"/>
     </row>
     <row r="1943">
       <c r="A1943" s="6"/>
-      <c r="B1943" s="11"/>
+      <c r="B1943" s="13"/>
       <c r="C1943" s="6"/>
       <c r="D1943" s="6"/>
       <c r="E1943" s="6"/>
     </row>
     <row r="1944">
       <c r="A1944" s="6"/>
-      <c r="B1944" s="11"/>
+      <c r="B1944" s="13"/>
       <c r="C1944" s="6"/>
       <c r="D1944" s="6"/>
       <c r="E1944" s="6"/>
     </row>
     <row r="1945">
       <c r="A1945" s="6"/>
-      <c r="B1945" s="11"/>
+      <c r="B1945" s="13"/>
       <c r="C1945" s="6"/>
       <c r="D1945" s="6"/>
       <c r="E1945" s="6"/>
     </row>
     <row r="1946">
       <c r="A1946" s="6"/>
-      <c r="B1946" s="11"/>
+      <c r="B1946" s="13"/>
       <c r="C1946" s="6"/>
       <c r="D1946" s="6"/>
       <c r="E1946" s="6"/>
     </row>
     <row r="1947">
       <c r="A1947" s="6"/>
-      <c r="B1947" s="11"/>
+      <c r="B1947" s="13"/>
       <c r="C1947" s="6"/>
       <c r="D1947" s="6"/>
       <c r="E1947" s="6"/>
     </row>
     <row r="1948">
       <c r="A1948" s="6"/>
-      <c r="B1948" s="11"/>
+      <c r="B1948" s="13"/>
       <c r="C1948" s="6"/>
       <c r="D1948" s="6"/>
       <c r="E1948" s="6"/>
     </row>
     <row r="1949">
       <c r="A1949" s="6"/>
-      <c r="B1949" s="11"/>
+      <c r="B1949" s="13"/>
       <c r="C1949" s="6"/>
       <c r="D1949" s="6"/>
       <c r="E1949" s="6"/>
     </row>
     <row r="1950">
       <c r="A1950" s="6"/>
-      <c r="B1950" s="11"/>
+      <c r="B1950" s="13"/>
       <c r="C1950" s="6"/>
       <c r="D1950" s="6"/>
       <c r="E1950" s="6"/>
     </row>
     <row r="1951">
       <c r="A1951" s="6"/>
-      <c r="B1951" s="11"/>
+      <c r="B1951" s="13"/>
       <c r="C1951" s="6"/>
       <c r="D1951" s="6"/>
       <c r="E1951" s="6"/>
     </row>
     <row r="1952">
       <c r="A1952" s="6"/>
-      <c r="B1952" s="11"/>
+      <c r="B1952" s="13"/>
       <c r="C1952" s="6"/>
       <c r="D1952" s="6"/>
       <c r="E1952" s="6"/>
     </row>
     <row r="1953">
       <c r="A1953" s="6"/>
-      <c r="B1953" s="11"/>
+      <c r="B1953" s="13"/>
       <c r="C1953" s="6"/>
       <c r="D1953" s="6"/>
       <c r="E1953" s="6"/>
     </row>
     <row r="1954">
       <c r="A1954" s="6"/>
-      <c r="B1954" s="11"/>
+      <c r="B1954" s="13"/>
       <c r="C1954" s="6"/>
       <c r="D1954" s="6"/>
       <c r="E1954" s="6"/>
     </row>
     <row r="1955">
       <c r="A1955" s="6"/>
-      <c r="B1955" s="11"/>
+      <c r="B1955" s="13"/>
       <c r="C1955" s="6"/>
       <c r="D1955" s="6"/>
       <c r="E1955" s="6"/>
     </row>
     <row r="1956">
       <c r="A1956" s="6"/>
-      <c r="B1956" s="11"/>
+      <c r="B1956" s="13"/>
       <c r="C1956" s="6"/>
       <c r="D1956" s="6"/>
       <c r="E1956" s="6"/>
     </row>
     <row r="1957">
       <c r="A1957" s="6"/>
-      <c r="B1957" s="11"/>
+      <c r="B1957" s="13"/>
       <c r="C1957" s="6"/>
       <c r="D1957" s="6"/>
       <c r="E1957" s="6"/>
     </row>
     <row r="1958">
       <c r="A1958" s="6"/>
-      <c r="B1958" s="11"/>
+      <c r="B1958" s="13"/>
       <c r="C1958" s="6"/>
       <c r="D1958" s="6"/>
       <c r="E1958" s="6"/>
     </row>
     <row r="1959">
       <c r="A1959" s="6"/>
-      <c r="B1959" s="11"/>
+      <c r="B1959" s="13"/>
       <c r="C1959" s="6"/>
       <c r="D1959" s="6"/>
       <c r="E1959" s="6"/>
     </row>
     <row r="1960">
       <c r="A1960" s="6"/>
-      <c r="B1960" s="11"/>
+      <c r="B1960" s="13"/>
       <c r="C1960" s="6"/>
       <c r="D1960" s="6"/>
       <c r="E1960" s="6"/>
     </row>
     <row r="1961">
       <c r="A1961" s="6"/>
-      <c r="B1961" s="11"/>
+      <c r="B1961" s="13"/>
       <c r="C1961" s="6"/>
       <c r="D1961" s="6"/>
       <c r="E1961" s="6"/>
     </row>
     <row r="1962">
       <c r="A1962" s="6"/>
-      <c r="B1962" s="11"/>
+      <c r="B1962" s="13"/>
       <c r="C1962" s="6"/>
       <c r="D1962" s="6"/>
       <c r="E1962" s="6"/>
     </row>
     <row r="1963">
       <c r="A1963" s="6"/>
-      <c r="B1963" s="11"/>
+      <c r="B1963" s="13"/>
       <c r="C1963" s="6"/>
       <c r="D1963" s="6"/>
       <c r="E1963" s="6"/>
     </row>
     <row r="1964">
       <c r="A1964" s="6"/>
-      <c r="B1964" s="11"/>
+      <c r="B1964" s="13"/>
       <c r="C1964" s="6"/>
       <c r="D1964" s="6"/>
       <c r="E1964" s="6"/>
     </row>
     <row r="1965">
       <c r="A1965" s="6"/>
-      <c r="B1965" s="11"/>
+      <c r="B1965" s="13"/>
       <c r="C1965" s="6"/>
       <c r="D1965" s="6"/>
       <c r="E1965" s="6"/>
     </row>
     <row r="1966">
       <c r="A1966" s="6"/>
-      <c r="B1966" s="11"/>
+      <c r="B1966" s="13"/>
       <c r="C1966" s="6"/>
       <c r="D1966" s="6"/>
       <c r="E1966" s="6"/>
     </row>
     <row r="1967">
       <c r="A1967" s="6"/>
-      <c r="B1967" s="11"/>
+      <c r="B1967" s="13"/>
       <c r="C1967" s="6"/>
       <c r="D1967" s="6"/>
       <c r="E1967" s="6"/>
     </row>
     <row r="1968">
       <c r="A1968" s="6"/>
-      <c r="B1968" s="11"/>
+      <c r="B1968" s="13"/>
       <c r="C1968" s="6"/>
       <c r="D1968" s="6"/>
       <c r="E1968" s="6"/>
     </row>
     <row r="1969">
       <c r="A1969" s="6"/>
-      <c r="B1969" s="11"/>
+      <c r="B1969" s="13"/>
       <c r="C1969" s="6"/>
       <c r="D1969" s="6"/>
       <c r="E1969" s="6"/>
     </row>
     <row r="1970">
       <c r="A1970" s="6"/>
-      <c r="B1970" s="11"/>
+      <c r="B1970" s="13"/>
       <c r="C1970" s="6"/>
       <c r="D1970" s="6"/>
       <c r="E1970" s="6"/>
     </row>
     <row r="1971">
       <c r="A1971" s="6"/>
-      <c r="B1971" s="11"/>
+      <c r="B1971" s="13"/>
       <c r="C1971" s="6"/>
       <c r="D1971" s="6"/>
       <c r="E1971" s="6"/>
     </row>
     <row r="1972">
       <c r="A1972" s="6"/>
-      <c r="B1972" s="11"/>
+      <c r="B1972" s="13"/>
       <c r="C1972" s="6"/>
       <c r="D1972" s="6"/>
       <c r="E1972" s="6"/>
     </row>
     <row r="1973">
       <c r="A1973" s="6"/>
-      <c r="B1973" s="11"/>
+      <c r="B1973" s="13"/>
       <c r="C1973" s="6"/>
       <c r="D1973" s="6"/>
       <c r="E1973" s="6"/>
     </row>
     <row r="1974">
       <c r="A1974" s="6"/>
-      <c r="B1974" s="11"/>
+      <c r="B1974" s="13"/>
       <c r="C1974" s="6"/>
       <c r="D1974" s="6"/>
       <c r="E1974" s="6"/>
     </row>
     <row r="1975">
       <c r="A1975" s="6"/>
-      <c r="B1975" s="11"/>
+      <c r="B1975" s="13"/>
       <c r="C1975" s="6"/>
       <c r="D1975" s="6"/>
       <c r="E1975" s="6"/>
     </row>
     <row r="1976">
       <c r="A1976" s="6"/>
-      <c r="B1976" s="11"/>
+      <c r="B1976" s="13"/>
       <c r="C1976" s="6"/>
       <c r="D1976" s="6"/>
       <c r="E1976" s="6"/>
     </row>
     <row r="1977">
       <c r="A1977" s="6"/>
-      <c r="B1977" s="11"/>
+      <c r="B1977" s="13"/>
       <c r="C1977" s="6"/>
       <c r="D1977" s="6"/>
       <c r="E1977" s="6"/>
     </row>
     <row r="1978">
       <c r="A1978" s="6"/>
-      <c r="B1978" s="11"/>
+      <c r="B1978" s="13"/>
       <c r="C1978" s="6"/>
       <c r="D1978" s="6"/>
       <c r="E1978" s="6"/>
     </row>
     <row r="1979">
       <c r="A1979" s="6"/>
-      <c r="B1979" s="11"/>
+      <c r="B1979" s="13"/>
       <c r="C1979" s="6"/>
       <c r="D1979" s="6"/>
       <c r="E1979" s="6"/>
     </row>
     <row r="1980">
       <c r="A1980" s="6"/>
-      <c r="B1980" s="11"/>
+      <c r="B1980" s="13"/>
       <c r="C1980" s="6"/>
       <c r="D1980" s="6"/>
       <c r="E1980" s="6"/>
     </row>
     <row r="1981">
       <c r="A1981" s="6"/>
-      <c r="B1981" s="11"/>
+      <c r="B1981" s="13"/>
       <c r="C1981" s="6"/>
       <c r="D1981" s="6"/>
       <c r="E1981" s="6"/>
     </row>
     <row r="1982">
       <c r="A1982" s="6"/>
-      <c r="B1982" s="11"/>
+      <c r="B1982" s="13"/>
       <c r="C1982" s="6"/>
       <c r="D1982" s="6"/>
       <c r="E1982" s="6"/>
     </row>
     <row r="1983">
       <c r="A1983" s="6"/>
-      <c r="B1983" s="11"/>
+      <c r="B1983" s="13"/>
       <c r="C1983" s="6"/>
       <c r="D1983" s="6"/>
       <c r="E1983" s="6"/>
     </row>
     <row r="1984">
       <c r="A1984" s="6"/>
-      <c r="B1984" s="11"/>
+      <c r="B1984" s="13"/>
       <c r="C1984" s="6"/>
       <c r="D1984" s="6"/>
       <c r="E1984" s="6"/>
     </row>
     <row r="1985">
       <c r="A1985" s="6"/>
-      <c r="B1985" s="11"/>
+      <c r="B1985" s="13"/>
       <c r="C1985" s="6"/>
       <c r="D1985" s="6"/>
       <c r="E1985" s="6"/>
     </row>
     <row r="1986">
       <c r="A1986" s="6"/>
-      <c r="B1986" s="11"/>
+      <c r="B1986" s="13"/>
       <c r="C1986" s="6"/>
       <c r="D1986" s="6"/>
       <c r="E1986" s="6"/>
     </row>
     <row r="1987">
       <c r="A1987" s="6"/>
-      <c r="B1987" s="11"/>
+      <c r="B1987" s="13"/>
       <c r="C1987" s="6"/>
       <c r="D1987" s="6"/>
       <c r="E1987" s="6"/>
     </row>
     <row r="1988">
       <c r="A1988" s="6"/>
-      <c r="B1988" s="11"/>
+      <c r="B1988" s="13"/>
       <c r="C1988" s="6"/>
       <c r="D1988" s="6"/>
       <c r="E1988" s="6"/>
     </row>
     <row r="1989">
       <c r="A1989" s="6"/>
-      <c r="B1989" s="11"/>
+      <c r="B1989" s="13"/>
       <c r="C1989" s="6"/>
       <c r="D1989" s="6"/>
       <c r="E1989" s="6"/>
     </row>
     <row r="1990">
       <c r="A1990" s="6"/>
-      <c r="B1990" s="11"/>
+      <c r="B1990" s="13"/>
       <c r="C1990" s="6"/>
       <c r="D1990" s="6"/>
       <c r="E1990" s="6"/>
     </row>
     <row r="1991">
       <c r="A1991" s="6"/>
-      <c r="B1991" s="11"/>
+      <c r="B1991" s="13"/>
       <c r="C1991" s="6"/>
       <c r="D1991" s="6"/>
       <c r="E1991" s="6"/>
     </row>
     <row r="1992">
       <c r="A1992" s="6"/>
-      <c r="B1992" s="11"/>
+      <c r="B1992" s="13"/>
       <c r="C1992" s="6"/>
       <c r="D1992" s="6"/>
       <c r="E1992" s="6"/>
     </row>
     <row r="1993">
       <c r="A1993" s="6"/>
-      <c r="B1993" s="11"/>
+      <c r="B1993" s="13"/>
       <c r="C1993" s="6"/>
       <c r="D1993" s="6"/>
       <c r="E1993" s="6"/>
     </row>
     <row r="1994">
       <c r="A1994" s="6"/>
-      <c r="B1994" s="11"/>
+      <c r="B1994" s="13"/>
       <c r="C1994" s="6"/>
       <c r="D1994" s="6"/>
       <c r="E1994" s="6"/>
     </row>
     <row r="1995">
       <c r="A1995" s="6"/>
-      <c r="B1995" s="11"/>
+      <c r="B1995" s="13"/>
       <c r="C1995" s="6"/>
       <c r="D1995" s="6"/>
       <c r="E1995" s="6"/>
     </row>
     <row r="1996">
       <c r="A1996" s="6"/>
-      <c r="B1996" s="11"/>
+      <c r="B1996" s="13"/>
       <c r="C1996" s="6"/>
       <c r="D1996" s="6"/>
       <c r="E1996" s="6"/>
     </row>
     <row r="1997">
       <c r="A1997" s="6"/>
-      <c r="B1997" s="11"/>
+      <c r="B1997" s="13"/>
       <c r="C1997" s="6"/>
       <c r="D1997" s="6"/>
       <c r="E1997" s="6"/>
     </row>
     <row r="1998">
       <c r="A1998" s="6"/>
-      <c r="B1998" s="11"/>
+      <c r="B1998" s="13"/>
       <c r="C1998" s="6"/>
       <c r="D1998" s="6"/>
       <c r="E1998" s="6"/>
     </row>
     <row r="1999">
       <c r="A1999" s="6"/>
-      <c r="B1999" s="11"/>
+      <c r="B1999" s="13"/>
       <c r="C1999" s="6"/>
       <c r="D1999" s="6"/>
       <c r="E1999" s="6"/>
     </row>
     <row r="2000">
       <c r="A2000" s="6"/>
-      <c r="B2000" s="11"/>
+      <c r="B2000" s="13"/>
       <c r="C2000" s="6"/>
       <c r="D2000" s="6"/>
       <c r="E2000" s="6"/>
     </row>
     <row r="2001">
       <c r="A2001" s="6"/>
-      <c r="B2001" s="11"/>
+      <c r="B2001" s="13"/>
       <c r="C2001" s="6"/>
       <c r="D2001" s="6"/>
       <c r="E2001" s="6"/>
     </row>
     <row r="2002">
       <c r="A2002" s="6"/>
-      <c r="B2002" s="11"/>
+      <c r="B2002" s="13"/>
       <c r="C2002" s="6"/>
       <c r="D2002" s="6"/>
       <c r="E2002" s="6"/>
     </row>
     <row r="2003">
       <c r="A2003" s="6"/>
-      <c r="B2003" s="11"/>
+      <c r="B2003" s="13"/>
       <c r="C2003" s="6"/>
       <c r="D2003" s="6"/>
       <c r="E2003" s="6"/>
     </row>
     <row r="2004">
       <c r="A2004" s="6"/>
-      <c r="B2004" s="11"/>
+      <c r="B2004" s="13"/>
       <c r="C2004" s="6"/>
       <c r="D2004" s="6"/>
       <c r="E2004" s="6"/>
     </row>
     <row r="2005">
       <c r="A2005" s="6"/>
-      <c r="B2005" s="11"/>
+      <c r="B2005" s="13"/>
       <c r="C2005" s="6"/>
       <c r="D2005" s="6"/>
       <c r="E2005" s="6"/>
     </row>
     <row r="2006">
       <c r="A2006" s="6"/>
-      <c r="B2006" s="11"/>
+      <c r="B2006" s="13"/>
       <c r="C2006" s="6"/>
       <c r="D2006" s="6"/>
       <c r="E2006" s="6"/>
     </row>
     <row r="2007">
       <c r="A2007" s="6"/>
-      <c r="B2007" s="11"/>
+      <c r="B2007" s="13"/>
       <c r="C2007" s="6"/>
       <c r="D2007" s="6"/>
       <c r="E2007" s="6"/>
     </row>
     <row r="2008">
       <c r="A2008" s="6"/>
-      <c r="B2008" s="11"/>
+      <c r="B2008" s="13"/>
       <c r="C2008" s="6"/>
       <c r="D2008" s="6"/>
       <c r="E2008" s="6"/>
     </row>
     <row r="2009">
       <c r="A2009" s="6"/>
-      <c r="B2009" s="11"/>
+      <c r="B2009" s="13"/>
       <c r="C2009" s="6"/>
       <c r="D2009" s="6"/>
       <c r="E2009" s="6"/>
     </row>
     <row r="2010">
       <c r="A2010" s="6"/>
-      <c r="B2010" s="11"/>
+      <c r="B2010" s="13"/>
       <c r="C2010" s="6"/>
       <c r="D2010" s="6"/>
       <c r="E2010" s="6"/>
     </row>
     <row r="2011">
       <c r="A2011" s="6"/>
-      <c r="B2011" s="11"/>
+      <c r="B2011" s="13"/>
       <c r="C2011" s="6"/>
       <c r="D2011" s="6"/>
       <c r="E2011" s="6"/>
     </row>
     <row r="2012">
       <c r="A2012" s="6"/>
-      <c r="B2012" s="11"/>
+      <c r="B2012" s="13"/>
       <c r="C2012" s="6"/>
       <c r="D2012" s="6"/>
       <c r="E2012" s="6"/>
     </row>
     <row r="2013">
       <c r="A2013" s="6"/>
-      <c r="B2013" s="11"/>
+      <c r="B2013" s="13"/>
       <c r="C2013" s="6"/>
       <c r="D2013" s="6"/>
       <c r="E2013" s="6"/>
     </row>
     <row r="2014">
       <c r="A2014" s="6"/>
-      <c r="B2014" s="11"/>
+      <c r="B2014" s="13"/>
       <c r="C2014" s="6"/>
       <c r="D2014" s="6"/>
       <c r="E2014" s="6"/>
     </row>
     <row r="2015">
       <c r="A2015" s="6"/>
-      <c r="B2015" s="11"/>
+      <c r="B2015" s="13"/>
       <c r="C2015" s="6"/>
       <c r="D2015" s="6"/>
       <c r="E2015" s="6"/>
     </row>
     <row r="2016">
       <c r="A2016" s="6"/>
-      <c r="B2016" s="11"/>
+      <c r="B2016" s="13"/>
       <c r="C2016" s="6"/>
       <c r="D2016" s="6"/>
       <c r="E2016" s="6"/>
     </row>
     <row r="2017">
       <c r="A2017" s="6"/>
-      <c r="B2017" s="11"/>
+      <c r="B2017" s="13"/>
       <c r="C2017" s="6"/>
       <c r="D2017" s="6"/>
       <c r="E2017" s="6"/>
     </row>
     <row r="2018">
       <c r="A2018" s="6"/>
-      <c r="B2018" s="11"/>
+      <c r="B2018" s="13"/>
       <c r="C2018" s="6"/>
       <c r="D2018" s="6"/>
       <c r="E2018" s="6"/>
     </row>
     <row r="2019">
       <c r="A2019" s="6"/>
-      <c r="B2019" s="11"/>
+      <c r="B2019" s="13"/>
       <c r="C2019" s="6"/>
       <c r="D2019" s="6"/>
       <c r="E2019" s="6"/>
     </row>
     <row r="2020">
       <c r="A2020" s="6"/>
-      <c r="B2020" s="11"/>
+      <c r="B2020" s="13"/>
       <c r="C2020" s="6"/>
       <c r="D2020" s="6"/>
       <c r="E2020" s="6"/>
     </row>
     <row r="2021">
       <c r="A2021" s="6"/>
-      <c r="B2021" s="11"/>
+      <c r="B2021" s="13"/>
       <c r="C2021" s="6"/>
       <c r="D2021" s="6"/>
       <c r="E2021" s="6"/>
     </row>
     <row r="2022">
       <c r="A2022" s="6"/>
-      <c r="B2022" s="11"/>
+      <c r="B2022" s="13"/>
       <c r="C2022" s="6"/>
       <c r="D2022" s="6"/>
       <c r="E2022" s="6"/>
     </row>
     <row r="2023">
       <c r="A2023" s="6"/>
-      <c r="B2023" s="11"/>
+      <c r="B2023" s="13"/>
       <c r="C2023" s="6"/>
       <c r="D2023" s="6"/>
       <c r="E2023" s="6"/>
     </row>
     <row r="2024">
       <c r="A2024" s="6"/>
-      <c r="B2024" s="11"/>
+      <c r="B2024" s="13"/>
       <c r="C2024" s="6"/>
       <c r="D2024" s="6"/>
       <c r="E2024" s="6"/>
     </row>
     <row r="2025">
       <c r="A2025" s="6"/>
-      <c r="B2025" s="11"/>
+      <c r="B2025" s="13"/>
       <c r="C2025" s="6"/>
       <c r="D2025" s="6"/>
       <c r="E2025" s="6"/>
     </row>
     <row r="2026">
       <c r="A2026" s="6"/>
-      <c r="B2026" s="11"/>
+      <c r="B2026" s="13"/>
       <c r="C2026" s="6"/>
       <c r="D2026" s="6"/>
       <c r="E2026" s="6"/>
     </row>
     <row r="2027">
       <c r="A2027" s="6"/>
-      <c r="B2027" s="11"/>
+      <c r="B2027" s="13"/>
       <c r="C2027" s="6"/>
       <c r="D2027" s="6"/>
       <c r="E2027" s="6"/>
     </row>
     <row r="2028">
       <c r="A2028" s="6"/>
-      <c r="B2028" s="11"/>
+      <c r="B2028" s="13"/>
       <c r="C2028" s="6"/>
       <c r="D2028" s="6"/>
       <c r="E2028" s="6"/>
     </row>
     <row r="2029">
       <c r="A2029" s="6"/>
-      <c r="B2029" s="11"/>
+      <c r="B2029" s="13"/>
       <c r="C2029" s="6"/>
       <c r="D2029" s="6"/>
       <c r="E2029" s="6"/>
     </row>
     <row r="2030">
       <c r="A2030" s="6"/>
-      <c r="B2030" s="11"/>
+      <c r="B2030" s="13"/>
       <c r="C2030" s="6"/>
       <c r="D2030" s="6"/>
       <c r="E2030" s="6"/>
     </row>
     <row r="2031">
       <c r="A2031" s="6"/>
-      <c r="B2031" s="11"/>
+      <c r="B2031" s="13"/>
       <c r="C2031" s="6"/>
       <c r="D2031" s="6"/>
       <c r="E2031" s="6"/>
     </row>
     <row r="2032">
       <c r="A2032" s="6"/>
-      <c r="B2032" s="11"/>
+      <c r="B2032" s="13"/>
       <c r="C2032" s="6"/>
       <c r="D2032" s="6"/>
       <c r="E2032" s="6"/>
     </row>
     <row r="2033">
       <c r="A2033" s="6"/>
-      <c r="B2033" s="11"/>
+      <c r="B2033" s="13"/>
       <c r="C2033" s="6"/>
       <c r="D2033" s="6"/>
       <c r="E2033" s="6"/>
     </row>
     <row r="2034">
       <c r="A2034" s="6"/>
-      <c r="B2034" s="11"/>
+      <c r="B2034" s="13"/>
       <c r="C2034" s="6"/>
       <c r="D2034" s="6"/>
       <c r="E2034" s="6"/>
     </row>
     <row r="2035">
       <c r="A2035" s="6"/>
-      <c r="B2035" s="11"/>
+      <c r="B2035" s="13"/>
       <c r="C2035" s="6"/>
       <c r="D2035" s="6"/>
       <c r="E2035" s="6"/>
     </row>
     <row r="2036">
       <c r="A2036" s="6"/>
-      <c r="B2036" s="11"/>
+      <c r="B2036" s="13"/>
       <c r="C2036" s="6"/>
       <c r="D2036" s="6"/>
       <c r="E2036" s="6"/>
     </row>
     <row r="2037">
       <c r="A2037" s="6"/>
-      <c r="B2037" s="11"/>
+      <c r="B2037" s="13"/>
       <c r="C2037" s="6"/>
       <c r="D2037" s="6"/>
       <c r="E2037" s="6"/>
     </row>
     <row r="2038">
       <c r="A2038" s="6"/>
-      <c r="B2038" s="11"/>
+      <c r="B2038" s="13"/>
       <c r="C2038" s="6"/>
       <c r="D2038" s="6"/>
       <c r="E2038" s="6"/>
     </row>
     <row r="2039">
       <c r="A2039" s="6"/>
-      <c r="B2039" s="11"/>
+      <c r="B2039" s="13"/>
       <c r="C2039" s="6"/>
       <c r="D2039" s="6"/>
       <c r="E2039" s="6"/>
     </row>
     <row r="2040">
       <c r="A2040" s="6"/>
-      <c r="B2040" s="11"/>
+      <c r="B2040" s="13"/>
       <c r="C2040" s="6"/>
       <c r="D2040" s="6"/>
       <c r="E2040" s="6"/>
     </row>
     <row r="2041">
       <c r="A2041" s="6"/>
-      <c r="B2041" s="11"/>
+      <c r="B2041" s="13"/>
       <c r="C2041" s="6"/>
       <c r="D2041" s="6"/>
       <c r="E2041" s="6"/>
     </row>
     <row r="2042">
       <c r="A2042" s="6"/>
-      <c r="B2042" s="11"/>
+      <c r="B2042" s="13"/>
       <c r="C2042" s="6"/>
       <c r="D2042" s="6"/>
       <c r="E2042" s="6"/>
     </row>
     <row r="2043">
       <c r="A2043" s="6"/>
-      <c r="B2043" s="11"/>
+      <c r="B2043" s="13"/>
       <c r="C2043" s="6"/>
       <c r="D2043" s="6"/>
       <c r="E2043" s="6"/>
     </row>
     <row r="2044">
       <c r="A2044" s="6"/>
-      <c r="B2044" s="11"/>
+      <c r="B2044" s="13"/>
       <c r="C2044" s="6"/>
       <c r="D2044" s="6"/>
       <c r="E2044" s="6"/>
     </row>
     <row r="2045">
       <c r="A2045" s="6"/>
-      <c r="B2045" s="11"/>
+      <c r="B2045" s="13"/>
       <c r="C2045" s="6"/>
       <c r="D2045" s="6"/>
       <c r="E2045" s="6"/>
     </row>
     <row r="2046">
       <c r="A2046" s="6"/>
-      <c r="B2046" s="11"/>
+      <c r="B2046" s="13"/>
       <c r="C2046" s="6"/>
       <c r="D2046" s="6"/>
       <c r="E2046" s="6"/>
     </row>
     <row r="2047">
       <c r="A2047" s="6"/>
-      <c r="B2047" s="11"/>
+      <c r="B2047" s="13"/>
       <c r="C2047" s="6"/>
       <c r="D2047" s="6"/>
       <c r="E2047" s="6"/>
     </row>
     <row r="2048">
       <c r="A2048" s="6"/>
-      <c r="B2048" s="11"/>
+      <c r="B2048" s="13"/>
       <c r="C2048" s="6"/>
       <c r="D2048" s="6"/>
       <c r="E2048" s="6"/>
     </row>
     <row r="2049">
       <c r="A2049" s="6"/>
-      <c r="B2049" s="11"/>
+      <c r="B2049" s="13"/>
       <c r="C2049" s="6"/>
       <c r="D2049" s="6"/>
       <c r="E2049" s="6"/>
     </row>
     <row r="2050">
       <c r="A2050" s="6"/>
-      <c r="B2050" s="11"/>
+      <c r="B2050" s="13"/>
       <c r="C2050" s="6"/>
       <c r="D2050" s="6"/>
       <c r="E2050" s="6"/>
     </row>
     <row r="2051">
       <c r="A2051" s="6"/>
-      <c r="B2051" s="11"/>
+      <c r="B2051" s="13"/>
       <c r="C2051" s="6"/>
       <c r="D2051" s="6"/>
       <c r="E2051" s="6"/>
     </row>
     <row r="2052">
       <c r="A2052" s="6"/>
-      <c r="B2052" s="11"/>
+      <c r="B2052" s="13"/>
       <c r="C2052" s="6"/>
       <c r="D2052" s="6"/>
       <c r="E2052" s="6"/>
     </row>
     <row r="2053">
       <c r="A2053" s="6"/>
-      <c r="B2053" s="11"/>
+      <c r="B2053" s="13"/>
       <c r="C2053" s="6"/>
       <c r="D2053" s="6"/>
       <c r="E2053" s="6"/>

--- a/PublicCustomerApp/src/python/translation.xlsx
+++ b/PublicCustomerApp/src/python/translation.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="861" uniqueCount="828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="889" uniqueCount="854">
   <si>
     <t>key</t>
   </si>
@@ -2503,13 +2503,91 @@
   </si>
   <si>
     <t>Settings</t>
+  </si>
+  <si>
+    <t>driver_login</t>
+  </si>
+  <si>
+    <t>Driver Login</t>
+  </si>
+  <si>
+    <t>customer_login</t>
+  </si>
+  <si>
+    <t>Customer Login</t>
+  </si>
+  <si>
+    <t>sign_in_by_mobile</t>
+  </si>
+  <si>
+    <t>Sign In By Mobile</t>
+  </si>
+  <si>
+    <t>mobile_number</t>
+  </si>
+  <si>
+    <t>Mobile Number</t>
+  </si>
+  <si>
+    <t>request_otp</t>
+  </si>
+  <si>
+    <t>Request OTP</t>
+  </si>
+  <si>
+    <t>one_time_password_otp</t>
+  </si>
+  <si>
+    <t>One Time Password(OTP)</t>
+  </si>
+  <si>
+    <t>enter_otp_sent_to_mobile</t>
+  </si>
+  <si>
+    <t>Enter the OTP sent to your mobile number</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
+    <t>Welcome to Namma Ooru Taxi</t>
+  </si>
+  <si>
+    <t>subtitle</t>
+  </si>
+  <si>
+    <t>Choose how you would like to continue.</t>
+  </si>
+  <si>
+    <t>continue_as</t>
+  </si>
+  <si>
+    <t>Continue as</t>
+  </si>
+  <si>
+    <t>customer</t>
+  </si>
+  <si>
+    <t>Passenger</t>
+  </si>
+  <si>
+    <t>become_a</t>
+  </si>
+  <si>
+    <t>Become a</t>
+  </si>
+  <si>
+    <t>and_earn_money</t>
+  </si>
+  <si>
+    <t>&amp; earn money</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -2523,6 +2601,11 @@
     </font>
     <font>
       <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -2557,7 +2640,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -2592,6 +2675,9 @@
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -8846,105 +8932,202 @@
       <c r="E430" s="5"/>
     </row>
     <row r="431">
-      <c r="A431" s="3"/>
-      <c r="B431" s="4"/>
-      <c r="C431" s="5"/>
+      <c r="A431" s="9" t="s">
+        <v>828</v>
+      </c>
+      <c r="B431" s="10" t="s">
+        <v>829</v>
+      </c>
+      <c r="C431" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B431, ""en"", ""ta"")"),"இயக்கி உள்நுழைவு")</f>
+        <v>இயக்கி உள்நுழைவு</v>
+      </c>
       <c r="D431" s="5"/>
       <c r="E431" s="5"/>
     </row>
     <row r="432">
-      <c r="A432" s="3"/>
-      <c r="B432" s="4"/>
-      <c r="C432" s="5"/>
+      <c r="A432" s="9" t="s">
+        <v>830</v>
+      </c>
+      <c r="B432" s="10" t="s">
+        <v>831</v>
+      </c>
+      <c r="C432" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B432, ""en"", ""ta"")"),"வாடிக்கையாளர் உள்நுழைவு")</f>
+        <v>வாடிக்கையாளர் உள்நுழைவு</v>
+      </c>
       <c r="D432" s="5"/>
       <c r="E432" s="5"/>
     </row>
     <row r="433">
-      <c r="A433" s="3"/>
-      <c r="B433" s="4"/>
-      <c r="C433" s="5"/>
+      <c r="A433" s="9" t="s">
+        <v>832</v>
+      </c>
+      <c r="B433" s="10" t="s">
+        <v>833</v>
+      </c>
+      <c r="C433" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B433, ""en"", ""ta"")"),"மொபைல் மூலம் உள்நுழையவும்")</f>
+        <v>மொபைல் மூலம் உள்நுழையவும்</v>
+      </c>
       <c r="D433" s="5"/>
       <c r="E433" s="5"/>
     </row>
     <row r="434">
-      <c r="A434" s="3"/>
-      <c r="B434" s="4"/>
-      <c r="C434" s="5"/>
+      <c r="A434" s="9" t="s">
+        <v>834</v>
+      </c>
+      <c r="B434" s="10" t="s">
+        <v>835</v>
+      </c>
+      <c r="C434" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B434, ""en"", ""ta"")"),"மொபைல் எண்")</f>
+        <v>மொபைல் எண்</v>
+      </c>
       <c r="D434" s="5"/>
       <c r="E434" s="5"/>
     </row>
     <row r="435">
-      <c r="A435" s="3"/>
-      <c r="B435" s="4"/>
-      <c r="C435" s="5"/>
+      <c r="A435" s="9" t="s">
+        <v>836</v>
+      </c>
+      <c r="B435" s="10" t="s">
+        <v>837</v>
+      </c>
+      <c r="C435" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B435, ""en"", ""ta"")"),"OTP-யைக் கோருங்கள்")</f>
+        <v>OTP-யைக் கோருங்கள்</v>
+      </c>
       <c r="D435" s="5"/>
       <c r="E435" s="5"/>
     </row>
     <row r="436">
-      <c r="A436" s="3"/>
-      <c r="B436" s="4"/>
-      <c r="C436" s="5"/>
+      <c r="A436" s="9" t="s">
+        <v>838</v>
+      </c>
+      <c r="B436" s="10" t="s">
+        <v>839</v>
+      </c>
+      <c r="C436" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B436, ""en"", ""ta"")"),"ஒரு முறை கடவுச்சொல் (OTP)")</f>
+        <v>ஒரு முறை கடவுச்சொல் (OTP)</v>
+      </c>
       <c r="D436" s="5"/>
       <c r="E436" s="5"/>
     </row>
     <row r="437">
-      <c r="A437" s="3"/>
-      <c r="B437" s="4"/>
-      <c r="C437" s="5"/>
+      <c r="A437" s="9" t="s">
+        <v>840</v>
+      </c>
+      <c r="B437" s="10" t="s">
+        <v>841</v>
+      </c>
+      <c r="C437" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B437, ""en"", ""ta"")"),"உங்கள் மொபைல் எண்ணுக்கு அனுப்பப்பட்ட OTP ஐ உள்ளிடவும்.")</f>
+        <v>உங்கள் மொபைல் எண்ணுக்கு அனுப்பப்பட்ட OTP ஐ உள்ளிடவும்.</v>
+      </c>
       <c r="D437" s="5"/>
       <c r="E437" s="5"/>
     </row>
     <row r="438">
-      <c r="A438" s="3"/>
-      <c r="B438" s="4"/>
-      <c r="C438" s="5"/>
+      <c r="A438" s="11" t="s">
+        <v>842</v>
+      </c>
+      <c r="B438" s="10" t="s">
+        <v>843</v>
+      </c>
+      <c r="C438" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B438, ""en"", ""ta"")"),"நம்ம ஊரு டாக்ஸிக்கு வருக.")</f>
+        <v>நம்ம ஊரு டாக்ஸிக்கு வருக.</v>
+      </c>
       <c r="D438" s="5"/>
       <c r="E438" s="5"/>
     </row>
     <row r="439">
-      <c r="A439" s="3"/>
-      <c r="B439" s="4"/>
-      <c r="C439" s="5"/>
+      <c r="A439" s="11" t="s">
+        <v>844</v>
+      </c>
+      <c r="B439" s="10" t="s">
+        <v>845</v>
+      </c>
+      <c r="C439" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B439, ""en"", ""ta"")"),"நீங்கள் எப்படித் தொடர விரும்புகிறீர்கள் என்பதைத் தேர்வுசெய்யவும்.")</f>
+        <v>நீங்கள் எப்படித் தொடர விரும்புகிறீர்கள் என்பதைத் தேர்வுசெய்யவும்.</v>
+      </c>
       <c r="D439" s="5"/>
       <c r="E439" s="5"/>
     </row>
     <row r="440">
-      <c r="A440" s="3"/>
-      <c r="B440" s="4"/>
-      <c r="C440" s="5"/>
+      <c r="A440" s="11" t="s">
+        <v>846</v>
+      </c>
+      <c r="B440" s="10" t="s">
+        <v>847</v>
+      </c>
+      <c r="C440" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B440, ""en"", ""ta"")"),"எனத் தொடரவும்")</f>
+        <v>எனத் தொடரவும்</v>
+      </c>
       <c r="D440" s="5"/>
       <c r="E440" s="5"/>
     </row>
     <row r="441">
-      <c r="A441" s="3"/>
-      <c r="B441" s="4"/>
-      <c r="C441" s="5"/>
+      <c r="A441" s="11" t="s">
+        <v>848</v>
+      </c>
+      <c r="B441" s="10" t="s">
+        <v>849</v>
+      </c>
+      <c r="C441" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B441, ""en"", ""ta"")"),"பயணிகள்")</f>
+        <v>பயணிகள்</v>
+      </c>
       <c r="D441" s="5"/>
       <c r="E441" s="5"/>
     </row>
     <row r="442">
-      <c r="A442" s="3"/>
-      <c r="B442" s="4"/>
-      <c r="C442" s="5"/>
+      <c r="A442" s="11" t="s">
+        <v>676</v>
+      </c>
+      <c r="B442" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="C442" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B442, ""en"", ""ta"")"),"டிரைவர்")</f>
+        <v>டிரைவர்</v>
+      </c>
       <c r="D442" s="5"/>
       <c r="E442" s="5"/>
     </row>
     <row r="443">
-      <c r="A443" s="3"/>
-      <c r="B443" s="4"/>
-      <c r="C443" s="5"/>
+      <c r="A443" s="11" t="s">
+        <v>850</v>
+      </c>
+      <c r="B443" s="10" t="s">
+        <v>851</v>
+      </c>
+      <c r="C443" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B443, ""en"", ""ta"")"),"ஆகுங்கள்")</f>
+        <v>ஆகுங்கள்</v>
+      </c>
       <c r="D443" s="5"/>
       <c r="E443" s="5"/>
     </row>
     <row r="444">
-      <c r="A444" s="3"/>
-      <c r="B444" s="4"/>
-      <c r="C444" s="5"/>
+      <c r="A444" s="11" t="s">
+        <v>852</v>
+      </c>
+      <c r="B444" s="10" t="s">
+        <v>853</v>
+      </c>
+      <c r="C444" s="5" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B444, ""en"", ""ta"")"),"&amp; பணம் சம்பாதிக்கவும்")</f>
+        <v>&amp; பணம் சம்பாதிக்கவும்</v>
+      </c>
       <c r="D444" s="5"/>
       <c r="E444" s="5"/>
     </row>
     <row r="445">
-      <c r="A445" s="3"/>
       <c r="B445" s="4"/>
       <c r="C445" s="5"/>
       <c r="D445" s="5"/>
@@ -9973,7 +10156,7 @@
       <c r="E591" s="5"/>
     </row>
     <row r="592">
-      <c r="A592" s="11"/>
+      <c r="A592" s="12"/>
       <c r="B592" s="4"/>
       <c r="C592" s="5"/>
       <c r="D592" s="5"/>
@@ -11171,7 +11354,7 @@
     </row>
     <row r="763">
       <c r="A763" s="3"/>
-      <c r="B763" s="12"/>
+      <c r="B763" s="13"/>
       <c r="C763" s="5"/>
       <c r="D763" s="5"/>
       <c r="E763" s="5"/>
@@ -11626,7 +11809,7 @@
     </row>
     <row r="828">
       <c r="A828" s="7"/>
-      <c r="B828" s="13"/>
+      <c r="B828" s="14"/>
       <c r="C828" s="5"/>
       <c r="D828" s="5"/>
       <c r="E828" s="5"/>
@@ -15378,4830 +15561,4830 @@
     </row>
     <row r="1364">
       <c r="A1364" s="6"/>
-      <c r="B1364" s="13"/>
+      <c r="B1364" s="14"/>
       <c r="C1364" s="6"/>
       <c r="D1364" s="6"/>
       <c r="E1364" s="6"/>
     </row>
     <row r="1365">
       <c r="A1365" s="6"/>
-      <c r="B1365" s="13"/>
+      <c r="B1365" s="14"/>
       <c r="C1365" s="6"/>
       <c r="D1365" s="6"/>
       <c r="E1365" s="6"/>
     </row>
     <row r="1366">
       <c r="A1366" s="6"/>
-      <c r="B1366" s="13"/>
+      <c r="B1366" s="14"/>
       <c r="C1366" s="6"/>
       <c r="D1366" s="6"/>
       <c r="E1366" s="6"/>
     </row>
     <row r="1367">
       <c r="A1367" s="6"/>
-      <c r="B1367" s="13"/>
+      <c r="B1367" s="14"/>
       <c r="C1367" s="6"/>
       <c r="D1367" s="6"/>
       <c r="E1367" s="6"/>
     </row>
     <row r="1368">
       <c r="A1368" s="6"/>
-      <c r="B1368" s="13"/>
+      <c r="B1368" s="14"/>
       <c r="C1368" s="6"/>
       <c r="D1368" s="6"/>
       <c r="E1368" s="6"/>
     </row>
     <row r="1369">
       <c r="A1369" s="6"/>
-      <c r="B1369" s="13"/>
+      <c r="B1369" s="14"/>
       <c r="C1369" s="6"/>
       <c r="D1369" s="6"/>
       <c r="E1369" s="6"/>
     </row>
     <row r="1370">
       <c r="A1370" s="6"/>
-      <c r="B1370" s="13"/>
+      <c r="B1370" s="14"/>
       <c r="C1370" s="6"/>
       <c r="D1370" s="6"/>
       <c r="E1370" s="6"/>
     </row>
     <row r="1371">
       <c r="A1371" s="6"/>
-      <c r="B1371" s="13"/>
+      <c r="B1371" s="14"/>
       <c r="C1371" s="6"/>
       <c r="D1371" s="6"/>
       <c r="E1371" s="6"/>
     </row>
     <row r="1372">
       <c r="A1372" s="6"/>
-      <c r="B1372" s="13"/>
+      <c r="B1372" s="14"/>
       <c r="C1372" s="6"/>
       <c r="D1372" s="6"/>
       <c r="E1372" s="6"/>
     </row>
     <row r="1373">
       <c r="A1373" s="6"/>
-      <c r="B1373" s="13"/>
+      <c r="B1373" s="14"/>
       <c r="C1373" s="6"/>
       <c r="D1373" s="6"/>
       <c r="E1373" s="6"/>
     </row>
     <row r="1374">
       <c r="A1374" s="6"/>
-      <c r="B1374" s="13"/>
+      <c r="B1374" s="14"/>
       <c r="C1374" s="6"/>
       <c r="D1374" s="6"/>
       <c r="E1374" s="6"/>
     </row>
     <row r="1375">
       <c r="A1375" s="6"/>
-      <c r="B1375" s="13"/>
+      <c r="B1375" s="14"/>
       <c r="C1375" s="6"/>
       <c r="D1375" s="6"/>
       <c r="E1375" s="6"/>
     </row>
     <row r="1376">
       <c r="A1376" s="6"/>
-      <c r="B1376" s="13"/>
+      <c r="B1376" s="14"/>
       <c r="C1376" s="6"/>
       <c r="D1376" s="6"/>
       <c r="E1376" s="6"/>
     </row>
     <row r="1377">
       <c r="A1377" s="6"/>
-      <c r="B1377" s="13"/>
+      <c r="B1377" s="14"/>
       <c r="C1377" s="6"/>
       <c r="D1377" s="6"/>
       <c r="E1377" s="6"/>
     </row>
     <row r="1378">
       <c r="A1378" s="6"/>
-      <c r="B1378" s="13"/>
+      <c r="B1378" s="14"/>
       <c r="C1378" s="6"/>
       <c r="D1378" s="6"/>
       <c r="E1378" s="6"/>
     </row>
     <row r="1379">
       <c r="A1379" s="6"/>
-      <c r="B1379" s="13"/>
+      <c r="B1379" s="14"/>
       <c r="C1379" s="6"/>
       <c r="D1379" s="6"/>
       <c r="E1379" s="6"/>
     </row>
     <row r="1380">
       <c r="A1380" s="6"/>
-      <c r="B1380" s="13"/>
+      <c r="B1380" s="14"/>
       <c r="C1380" s="6"/>
       <c r="D1380" s="6"/>
       <c r="E1380" s="6"/>
     </row>
     <row r="1381">
       <c r="A1381" s="6"/>
-      <c r="B1381" s="13"/>
+      <c r="B1381" s="14"/>
       <c r="C1381" s="6"/>
       <c r="D1381" s="6"/>
       <c r="E1381" s="6"/>
     </row>
     <row r="1382">
       <c r="A1382" s="6"/>
-      <c r="B1382" s="13"/>
+      <c r="B1382" s="14"/>
       <c r="C1382" s="6"/>
       <c r="D1382" s="6"/>
       <c r="E1382" s="6"/>
     </row>
     <row r="1383">
       <c r="A1383" s="6"/>
-      <c r="B1383" s="13"/>
+      <c r="B1383" s="14"/>
       <c r="C1383" s="6"/>
       <c r="D1383" s="6"/>
       <c r="E1383" s="6"/>
     </row>
     <row r="1384">
       <c r="A1384" s="6"/>
-      <c r="B1384" s="13"/>
+      <c r="B1384" s="14"/>
       <c r="C1384" s="6"/>
       <c r="D1384" s="6"/>
       <c r="E1384" s="6"/>
     </row>
     <row r="1385">
       <c r="A1385" s="6"/>
-      <c r="B1385" s="13"/>
+      <c r="B1385" s="14"/>
       <c r="C1385" s="6"/>
       <c r="D1385" s="6"/>
       <c r="E1385" s="6"/>
     </row>
     <row r="1386">
       <c r="A1386" s="6"/>
-      <c r="B1386" s="13"/>
+      <c r="B1386" s="14"/>
       <c r="C1386" s="6"/>
       <c r="D1386" s="6"/>
       <c r="E1386" s="6"/>
     </row>
     <row r="1387">
       <c r="A1387" s="6"/>
-      <c r="B1387" s="13"/>
+      <c r="B1387" s="14"/>
       <c r="C1387" s="6"/>
       <c r="D1387" s="6"/>
       <c r="E1387" s="6"/>
     </row>
     <row r="1388">
       <c r="A1388" s="6"/>
-      <c r="B1388" s="13"/>
+      <c r="B1388" s="14"/>
       <c r="C1388" s="6"/>
       <c r="D1388" s="6"/>
       <c r="E1388" s="6"/>
     </row>
     <row r="1389">
       <c r="A1389" s="6"/>
-      <c r="B1389" s="13"/>
+      <c r="B1389" s="14"/>
       <c r="C1389" s="6"/>
       <c r="D1389" s="6"/>
       <c r="E1389" s="6"/>
     </row>
     <row r="1390">
       <c r="A1390" s="6"/>
-      <c r="B1390" s="13"/>
+      <c r="B1390" s="14"/>
       <c r="C1390" s="6"/>
       <c r="D1390" s="6"/>
       <c r="E1390" s="6"/>
     </row>
     <row r="1391">
       <c r="A1391" s="6"/>
-      <c r="B1391" s="13"/>
+      <c r="B1391" s="14"/>
       <c r="C1391" s="6"/>
       <c r="D1391" s="6"/>
       <c r="E1391" s="6"/>
     </row>
     <row r="1392">
       <c r="A1392" s="6"/>
-      <c r="B1392" s="13"/>
+      <c r="B1392" s="14"/>
       <c r="C1392" s="6"/>
       <c r="D1392" s="6"/>
       <c r="E1392" s="6"/>
     </row>
     <row r="1393">
       <c r="A1393" s="6"/>
-      <c r="B1393" s="13"/>
+      <c r="B1393" s="14"/>
       <c r="C1393" s="6"/>
       <c r="D1393" s="6"/>
       <c r="E1393" s="6"/>
     </row>
     <row r="1394">
       <c r="A1394" s="6"/>
-      <c r="B1394" s="13"/>
+      <c r="B1394" s="14"/>
       <c r="C1394" s="6"/>
       <c r="D1394" s="6"/>
       <c r="E1394" s="6"/>
     </row>
     <row r="1395">
       <c r="A1395" s="6"/>
-      <c r="B1395" s="13"/>
+      <c r="B1395" s="14"/>
       <c r="C1395" s="6"/>
       <c r="D1395" s="6"/>
       <c r="E1395" s="6"/>
     </row>
     <row r="1396">
       <c r="A1396" s="6"/>
-      <c r="B1396" s="13"/>
+      <c r="B1396" s="14"/>
       <c r="C1396" s="6"/>
       <c r="D1396" s="6"/>
       <c r="E1396" s="6"/>
     </row>
     <row r="1397">
       <c r="A1397" s="6"/>
-      <c r="B1397" s="13"/>
+      <c r="B1397" s="14"/>
       <c r="C1397" s="6"/>
       <c r="D1397" s="6"/>
       <c r="E1397" s="6"/>
     </row>
     <row r="1398">
       <c r="A1398" s="6"/>
-      <c r="B1398" s="13"/>
+      <c r="B1398" s="14"/>
       <c r="C1398" s="6"/>
       <c r="D1398" s="6"/>
       <c r="E1398" s="6"/>
     </row>
     <row r="1399">
       <c r="A1399" s="6"/>
-      <c r="B1399" s="13"/>
+      <c r="B1399" s="14"/>
       <c r="C1399" s="6"/>
       <c r="D1399" s="6"/>
       <c r="E1399" s="6"/>
     </row>
     <row r="1400">
       <c r="A1400" s="6"/>
-      <c r="B1400" s="13"/>
+      <c r="B1400" s="14"/>
       <c r="C1400" s="6"/>
       <c r="D1400" s="6"/>
       <c r="E1400" s="6"/>
     </row>
     <row r="1401">
       <c r="A1401" s="6"/>
-      <c r="B1401" s="13"/>
+      <c r="B1401" s="14"/>
       <c r="C1401" s="6"/>
       <c r="D1401" s="6"/>
       <c r="E1401" s="6"/>
     </row>
     <row r="1402">
       <c r="A1402" s="6"/>
-      <c r="B1402" s="13"/>
+      <c r="B1402" s="14"/>
       <c r="C1402" s="6"/>
       <c r="D1402" s="6"/>
       <c r="E1402" s="6"/>
     </row>
     <row r="1403">
       <c r="A1403" s="6"/>
-      <c r="B1403" s="13"/>
+      <c r="B1403" s="14"/>
       <c r="C1403" s="6"/>
       <c r="D1403" s="6"/>
       <c r="E1403" s="6"/>
     </row>
     <row r="1404">
       <c r="A1404" s="6"/>
-      <c r="B1404" s="13"/>
+      <c r="B1404" s="14"/>
       <c r="C1404" s="6"/>
       <c r="D1404" s="6"/>
       <c r="E1404" s="6"/>
     </row>
     <row r="1405">
       <c r="A1405" s="6"/>
-      <c r="B1405" s="13"/>
+      <c r="B1405" s="14"/>
       <c r="C1405" s="6"/>
       <c r="D1405" s="6"/>
       <c r="E1405" s="6"/>
     </row>
     <row r="1406">
       <c r="A1406" s="6"/>
-      <c r="B1406" s="13"/>
+      <c r="B1406" s="14"/>
       <c r="C1406" s="6"/>
       <c r="D1406" s="6"/>
       <c r="E1406" s="6"/>
     </row>
     <row r="1407">
       <c r="A1407" s="6"/>
-      <c r="B1407" s="13"/>
+      <c r="B1407" s="14"/>
       <c r="C1407" s="6"/>
       <c r="D1407" s="6"/>
       <c r="E1407" s="6"/>
     </row>
     <row r="1408">
       <c r="A1408" s="6"/>
-      <c r="B1408" s="13"/>
+      <c r="B1408" s="14"/>
       <c r="C1408" s="6"/>
       <c r="D1408" s="6"/>
       <c r="E1408" s="6"/>
     </row>
     <row r="1409">
       <c r="A1409" s="6"/>
-      <c r="B1409" s="13"/>
+      <c r="B1409" s="14"/>
       <c r="C1409" s="6"/>
       <c r="D1409" s="6"/>
       <c r="E1409" s="6"/>
     </row>
     <row r="1410">
       <c r="A1410" s="6"/>
-      <c r="B1410" s="13"/>
+      <c r="B1410" s="14"/>
       <c r="C1410" s="6"/>
       <c r="D1410" s="6"/>
       <c r="E1410" s="6"/>
     </row>
     <row r="1411">
       <c r="A1411" s="6"/>
-      <c r="B1411" s="13"/>
+      <c r="B1411" s="14"/>
       <c r="C1411" s="6"/>
       <c r="D1411" s="6"/>
       <c r="E1411" s="6"/>
     </row>
     <row r="1412">
       <c r="A1412" s="6"/>
-      <c r="B1412" s="13"/>
+      <c r="B1412" s="14"/>
       <c r="C1412" s="6"/>
       <c r="D1412" s="6"/>
       <c r="E1412" s="6"/>
     </row>
     <row r="1413">
       <c r="A1413" s="6"/>
-      <c r="B1413" s="13"/>
+      <c r="B1413" s="14"/>
       <c r="C1413" s="6"/>
       <c r="D1413" s="6"/>
       <c r="E1413" s="6"/>
     </row>
     <row r="1414">
       <c r="A1414" s="6"/>
-      <c r="B1414" s="13"/>
+      <c r="B1414" s="14"/>
       <c r="C1414" s="6"/>
       <c r="D1414" s="6"/>
       <c r="E1414" s="6"/>
     </row>
     <row r="1415">
       <c r="A1415" s="6"/>
-      <c r="B1415" s="13"/>
+      <c r="B1415" s="14"/>
       <c r="C1415" s="6"/>
       <c r="D1415" s="6"/>
       <c r="E1415" s="6"/>
     </row>
     <row r="1416">
       <c r="A1416" s="6"/>
-      <c r="B1416" s="13"/>
+      <c r="B1416" s="14"/>
       <c r="C1416" s="6"/>
       <c r="D1416" s="6"/>
       <c r="E1416" s="6"/>
     </row>
     <row r="1417">
       <c r="A1417" s="6"/>
-      <c r="B1417" s="13"/>
+      <c r="B1417" s="14"/>
       <c r="C1417" s="6"/>
       <c r="D1417" s="6"/>
       <c r="E1417" s="6"/>
     </row>
     <row r="1418">
       <c r="A1418" s="6"/>
-      <c r="B1418" s="13"/>
+      <c r="B1418" s="14"/>
       <c r="C1418" s="6"/>
       <c r="D1418" s="6"/>
       <c r="E1418" s="6"/>
     </row>
     <row r="1419">
       <c r="A1419" s="6"/>
-      <c r="B1419" s="13"/>
+      <c r="B1419" s="14"/>
       <c r="C1419" s="6"/>
       <c r="D1419" s="6"/>
       <c r="E1419" s="6"/>
     </row>
     <row r="1420">
       <c r="A1420" s="6"/>
-      <c r="B1420" s="13"/>
+      <c r="B1420" s="14"/>
       <c r="C1420" s="6"/>
       <c r="D1420" s="6"/>
       <c r="E1420" s="6"/>
     </row>
     <row r="1421">
       <c r="A1421" s="6"/>
-      <c r="B1421" s="13"/>
+      <c r="B1421" s="14"/>
       <c r="C1421" s="6"/>
       <c r="D1421" s="6"/>
       <c r="E1421" s="6"/>
     </row>
     <row r="1422">
       <c r="A1422" s="6"/>
-      <c r="B1422" s="13"/>
+      <c r="B1422" s="14"/>
       <c r="C1422" s="6"/>
       <c r="D1422" s="6"/>
       <c r="E1422" s="6"/>
     </row>
     <row r="1423">
       <c r="A1423" s="6"/>
-      <c r="B1423" s="13"/>
+      <c r="B1423" s="14"/>
       <c r="C1423" s="6"/>
       <c r="D1423" s="6"/>
       <c r="E1423" s="6"/>
     </row>
     <row r="1424">
       <c r="A1424" s="6"/>
-      <c r="B1424" s="13"/>
+      <c r="B1424" s="14"/>
       <c r="C1424" s="6"/>
       <c r="D1424" s="6"/>
       <c r="E1424" s="6"/>
     </row>
     <row r="1425">
       <c r="A1425" s="6"/>
-      <c r="B1425" s="13"/>
+      <c r="B1425" s="14"/>
       <c r="C1425" s="6"/>
       <c r="D1425" s="6"/>
       <c r="E1425" s="6"/>
     </row>
     <row r="1426">
       <c r="A1426" s="6"/>
-      <c r="B1426" s="13"/>
+      <c r="B1426" s="14"/>
       <c r="C1426" s="6"/>
       <c r="D1426" s="6"/>
       <c r="E1426" s="6"/>
     </row>
     <row r="1427">
       <c r="A1427" s="6"/>
-      <c r="B1427" s="13"/>
+      <c r="B1427" s="14"/>
       <c r="C1427" s="6"/>
       <c r="D1427" s="6"/>
       <c r="E1427" s="6"/>
     </row>
     <row r="1428">
       <c r="A1428" s="6"/>
-      <c r="B1428" s="13"/>
+      <c r="B1428" s="14"/>
       <c r="C1428" s="6"/>
       <c r="D1428" s="6"/>
       <c r="E1428" s="6"/>
     </row>
     <row r="1429">
       <c r="A1429" s="6"/>
-      <c r="B1429" s="13"/>
+      <c r="B1429" s="14"/>
       <c r="C1429" s="6"/>
       <c r="D1429" s="6"/>
       <c r="E1429" s="6"/>
     </row>
     <row r="1430">
       <c r="A1430" s="6"/>
-      <c r="B1430" s="13"/>
+      <c r="B1430" s="14"/>
       <c r="C1430" s="6"/>
       <c r="D1430" s="6"/>
       <c r="E1430" s="6"/>
     </row>
     <row r="1431">
       <c r="A1431" s="6"/>
-      <c r="B1431" s="13"/>
+      <c r="B1431" s="14"/>
       <c r="C1431" s="6"/>
       <c r="D1431" s="6"/>
       <c r="E1431" s="6"/>
     </row>
     <row r="1432">
       <c r="A1432" s="6"/>
-      <c r="B1432" s="13"/>
+      <c r="B1432" s="14"/>
       <c r="C1432" s="6"/>
       <c r="D1432" s="6"/>
       <c r="E1432" s="6"/>
     </row>
     <row r="1433">
       <c r="A1433" s="6"/>
-      <c r="B1433" s="13"/>
+      <c r="B1433" s="14"/>
       <c r="C1433" s="6"/>
       <c r="D1433" s="6"/>
       <c r="E1433" s="6"/>
     </row>
     <row r="1434">
       <c r="A1434" s="6"/>
-      <c r="B1434" s="13"/>
+      <c r="B1434" s="14"/>
       <c r="C1434" s="6"/>
       <c r="D1434" s="6"/>
       <c r="E1434" s="6"/>
     </row>
     <row r="1435">
       <c r="A1435" s="6"/>
-      <c r="B1435" s="13"/>
+      <c r="B1435" s="14"/>
       <c r="C1435" s="6"/>
       <c r="D1435" s="6"/>
       <c r="E1435" s="6"/>
     </row>
     <row r="1436">
       <c r="A1436" s="6"/>
-      <c r="B1436" s="13"/>
+      <c r="B1436" s="14"/>
       <c r="C1436" s="6"/>
       <c r="D1436" s="6"/>
       <c r="E1436" s="6"/>
     </row>
     <row r="1437">
       <c r="A1437" s="6"/>
-      <c r="B1437" s="13"/>
+      <c r="B1437" s="14"/>
       <c r="C1437" s="6"/>
       <c r="D1437" s="6"/>
       <c r="E1437" s="6"/>
     </row>
     <row r="1438">
       <c r="A1438" s="6"/>
-      <c r="B1438" s="13"/>
+      <c r="B1438" s="14"/>
       <c r="C1438" s="6"/>
       <c r="D1438" s="6"/>
       <c r="E1438" s="6"/>
     </row>
     <row r="1439">
       <c r="A1439" s="6"/>
-      <c r="B1439" s="13"/>
+      <c r="B1439" s="14"/>
       <c r="C1439" s="6"/>
       <c r="D1439" s="6"/>
       <c r="E1439" s="6"/>
     </row>
     <row r="1440">
       <c r="A1440" s="6"/>
-      <c r="B1440" s="13"/>
+      <c r="B1440" s="14"/>
       <c r="C1440" s="6"/>
       <c r="D1440" s="6"/>
       <c r="E1440" s="6"/>
     </row>
     <row r="1441">
       <c r="A1441" s="6"/>
-      <c r="B1441" s="13"/>
+      <c r="B1441" s="14"/>
       <c r="C1441" s="6"/>
       <c r="D1441" s="6"/>
       <c r="E1441" s="6"/>
     </row>
     <row r="1442">
       <c r="A1442" s="6"/>
-      <c r="B1442" s="13"/>
+      <c r="B1442" s="14"/>
       <c r="C1442" s="6"/>
       <c r="D1442" s="6"/>
       <c r="E1442" s="6"/>
     </row>
     <row r="1443">
       <c r="A1443" s="6"/>
-      <c r="B1443" s="13"/>
+      <c r="B1443" s="14"/>
       <c r="C1443" s="6"/>
       <c r="D1443" s="6"/>
       <c r="E1443" s="6"/>
     </row>
     <row r="1444">
       <c r="A1444" s="6"/>
-      <c r="B1444" s="13"/>
+      <c r="B1444" s="14"/>
       <c r="C1444" s="6"/>
       <c r="D1444" s="6"/>
       <c r="E1444" s="6"/>
     </row>
     <row r="1445">
       <c r="A1445" s="6"/>
-      <c r="B1445" s="13"/>
+      <c r="B1445" s="14"/>
       <c r="C1445" s="6"/>
       <c r="D1445" s="6"/>
       <c r="E1445" s="6"/>
     </row>
     <row r="1446">
       <c r="A1446" s="6"/>
-      <c r="B1446" s="13"/>
+      <c r="B1446" s="14"/>
       <c r="C1446" s="6"/>
       <c r="D1446" s="6"/>
       <c r="E1446" s="6"/>
     </row>
     <row r="1447">
       <c r="A1447" s="6"/>
-      <c r="B1447" s="13"/>
+      <c r="B1447" s="14"/>
       <c r="C1447" s="6"/>
       <c r="D1447" s="6"/>
       <c r="E1447" s="6"/>
     </row>
     <row r="1448">
       <c r="A1448" s="6"/>
-      <c r="B1448" s="13"/>
+      <c r="B1448" s="14"/>
       <c r="C1448" s="6"/>
       <c r="D1448" s="6"/>
       <c r="E1448" s="6"/>
     </row>
     <row r="1449">
       <c r="A1449" s="6"/>
-      <c r="B1449" s="13"/>
+      <c r="B1449" s="14"/>
       <c r="C1449" s="6"/>
       <c r="D1449" s="6"/>
       <c r="E1449" s="6"/>
     </row>
     <row r="1450">
       <c r="A1450" s="6"/>
-      <c r="B1450" s="13"/>
+      <c r="B1450" s="14"/>
       <c r="C1450" s="6"/>
       <c r="D1450" s="6"/>
       <c r="E1450" s="6"/>
     </row>
     <row r="1451">
       <c r="A1451" s="6"/>
-      <c r="B1451" s="13"/>
+      <c r="B1451" s="14"/>
       <c r="C1451" s="6"/>
       <c r="D1451" s="6"/>
       <c r="E1451" s="6"/>
     </row>
     <row r="1452">
       <c r="A1452" s="6"/>
-      <c r="B1452" s="13"/>
+      <c r="B1452" s="14"/>
       <c r="C1452" s="6"/>
       <c r="D1452" s="6"/>
       <c r="E1452" s="6"/>
     </row>
     <row r="1453">
       <c r="A1453" s="6"/>
-      <c r="B1453" s="13"/>
+      <c r="B1453" s="14"/>
       <c r="C1453" s="6"/>
       <c r="D1453" s="6"/>
       <c r="E1453" s="6"/>
     </row>
     <row r="1454">
       <c r="A1454" s="6"/>
-      <c r="B1454" s="13"/>
+      <c r="B1454" s="14"/>
       <c r="C1454" s="6"/>
       <c r="D1454" s="6"/>
       <c r="E1454" s="6"/>
     </row>
     <row r="1455">
       <c r="A1455" s="6"/>
-      <c r="B1455" s="13"/>
+      <c r="B1455" s="14"/>
       <c r="C1455" s="6"/>
       <c r="D1455" s="6"/>
       <c r="E1455" s="6"/>
     </row>
     <row r="1456">
       <c r="A1456" s="6"/>
-      <c r="B1456" s="13"/>
+      <c r="B1456" s="14"/>
       <c r="C1456" s="6"/>
       <c r="D1456" s="6"/>
       <c r="E1456" s="6"/>
     </row>
     <row r="1457">
       <c r="A1457" s="6"/>
-      <c r="B1457" s="13"/>
+      <c r="B1457" s="14"/>
       <c r="C1457" s="6"/>
       <c r="D1457" s="6"/>
       <c r="E1457" s="6"/>
     </row>
     <row r="1458">
       <c r="A1458" s="6"/>
-      <c r="B1458" s="13"/>
+      <c r="B1458" s="14"/>
       <c r="C1458" s="6"/>
       <c r="D1458" s="6"/>
       <c r="E1458" s="6"/>
     </row>
     <row r="1459">
       <c r="A1459" s="6"/>
-      <c r="B1459" s="13"/>
+      <c r="B1459" s="14"/>
       <c r="C1459" s="6"/>
       <c r="D1459" s="6"/>
       <c r="E1459" s="6"/>
     </row>
     <row r="1460">
       <c r="A1460" s="6"/>
-      <c r="B1460" s="13"/>
+      <c r="B1460" s="14"/>
       <c r="C1460" s="6"/>
       <c r="D1460" s="6"/>
       <c r="E1460" s="6"/>
     </row>
     <row r="1461">
       <c r="A1461" s="6"/>
-      <c r="B1461" s="13"/>
+      <c r="B1461" s="14"/>
       <c r="C1461" s="6"/>
       <c r="D1461" s="6"/>
       <c r="E1461" s="6"/>
     </row>
     <row r="1462">
       <c r="A1462" s="6"/>
-      <c r="B1462" s="13"/>
+      <c r="B1462" s="14"/>
       <c r="C1462" s="6"/>
       <c r="D1462" s="6"/>
       <c r="E1462" s="6"/>
     </row>
     <row r="1463">
       <c r="A1463" s="6"/>
-      <c r="B1463" s="13"/>
+      <c r="B1463" s="14"/>
       <c r="C1463" s="6"/>
       <c r="D1463" s="6"/>
       <c r="E1463" s="6"/>
     </row>
     <row r="1464">
       <c r="A1464" s="6"/>
-      <c r="B1464" s="13"/>
+      <c r="B1464" s="14"/>
       <c r="C1464" s="6"/>
       <c r="D1464" s="6"/>
       <c r="E1464" s="6"/>
     </row>
     <row r="1465">
       <c r="A1465" s="6"/>
-      <c r="B1465" s="13"/>
+      <c r="B1465" s="14"/>
       <c r="C1465" s="6"/>
       <c r="D1465" s="6"/>
       <c r="E1465" s="6"/>
     </row>
     <row r="1466">
       <c r="A1466" s="6"/>
-      <c r="B1466" s="13"/>
+      <c r="B1466" s="14"/>
       <c r="C1466" s="6"/>
       <c r="D1466" s="6"/>
       <c r="E1466" s="6"/>
     </row>
     <row r="1467">
       <c r="A1467" s="6"/>
-      <c r="B1467" s="13"/>
+      <c r="B1467" s="14"/>
       <c r="C1467" s="6"/>
       <c r="D1467" s="6"/>
       <c r="E1467" s="6"/>
     </row>
     <row r="1468">
       <c r="A1468" s="6"/>
-      <c r="B1468" s="13"/>
+      <c r="B1468" s="14"/>
       <c r="C1468" s="6"/>
       <c r="D1468" s="6"/>
       <c r="E1468" s="6"/>
     </row>
     <row r="1469">
       <c r="A1469" s="6"/>
-      <c r="B1469" s="13"/>
+      <c r="B1469" s="14"/>
       <c r="C1469" s="6"/>
       <c r="D1469" s="6"/>
       <c r="E1469" s="6"/>
     </row>
     <row r="1470">
       <c r="A1470" s="6"/>
-      <c r="B1470" s="13"/>
+      <c r="B1470" s="14"/>
       <c r="C1470" s="6"/>
       <c r="D1470" s="6"/>
       <c r="E1470" s="6"/>
     </row>
     <row r="1471">
       <c r="A1471" s="6"/>
-      <c r="B1471" s="13"/>
+      <c r="B1471" s="14"/>
       <c r="C1471" s="6"/>
       <c r="D1471" s="6"/>
       <c r="E1471" s="6"/>
     </row>
     <row r="1472">
       <c r="A1472" s="6"/>
-      <c r="B1472" s="13"/>
+      <c r="B1472" s="14"/>
       <c r="C1472" s="6"/>
       <c r="D1472" s="6"/>
       <c r="E1472" s="6"/>
     </row>
     <row r="1473">
       <c r="A1473" s="6"/>
-      <c r="B1473" s="13"/>
+      <c r="B1473" s="14"/>
       <c r="C1473" s="6"/>
       <c r="D1473" s="6"/>
       <c r="E1473" s="6"/>
     </row>
     <row r="1474">
       <c r="A1474" s="6"/>
-      <c r="B1474" s="13"/>
+      <c r="B1474" s="14"/>
       <c r="C1474" s="6"/>
       <c r="D1474" s="6"/>
       <c r="E1474" s="6"/>
     </row>
     <row r="1475">
       <c r="A1475" s="6"/>
-      <c r="B1475" s="13"/>
+      <c r="B1475" s="14"/>
       <c r="C1475" s="6"/>
       <c r="D1475" s="6"/>
       <c r="E1475" s="6"/>
     </row>
     <row r="1476">
       <c r="A1476" s="6"/>
-      <c r="B1476" s="13"/>
+      <c r="B1476" s="14"/>
       <c r="C1476" s="6"/>
       <c r="D1476" s="6"/>
       <c r="E1476" s="6"/>
     </row>
     <row r="1477">
       <c r="A1477" s="6"/>
-      <c r="B1477" s="13"/>
+      <c r="B1477" s="14"/>
       <c r="C1477" s="6"/>
       <c r="D1477" s="6"/>
       <c r="E1477" s="6"/>
     </row>
     <row r="1478">
       <c r="A1478" s="6"/>
-      <c r="B1478" s="13"/>
+      <c r="B1478" s="14"/>
       <c r="C1478" s="6"/>
       <c r="D1478" s="6"/>
       <c r="E1478" s="6"/>
     </row>
     <row r="1479">
       <c r="A1479" s="6"/>
-      <c r="B1479" s="13"/>
+      <c r="B1479" s="14"/>
       <c r="C1479" s="6"/>
       <c r="D1479" s="6"/>
       <c r="E1479" s="6"/>
     </row>
     <row r="1480">
       <c r="A1480" s="6"/>
-      <c r="B1480" s="13"/>
+      <c r="B1480" s="14"/>
       <c r="C1480" s="6"/>
       <c r="D1480" s="6"/>
       <c r="E1480" s="6"/>
     </row>
     <row r="1481">
       <c r="A1481" s="6"/>
-      <c r="B1481" s="13"/>
+      <c r="B1481" s="14"/>
       <c r="C1481" s="6"/>
       <c r="D1481" s="6"/>
       <c r="E1481" s="6"/>
     </row>
     <row r="1482">
       <c r="A1482" s="6"/>
-      <c r="B1482" s="13"/>
+      <c r="B1482" s="14"/>
       <c r="C1482" s="6"/>
       <c r="D1482" s="6"/>
       <c r="E1482" s="6"/>
     </row>
     <row r="1483">
       <c r="A1483" s="6"/>
-      <c r="B1483" s="13"/>
+      <c r="B1483" s="14"/>
       <c r="C1483" s="6"/>
       <c r="D1483" s="6"/>
       <c r="E1483" s="6"/>
     </row>
     <row r="1484">
       <c r="A1484" s="6"/>
-      <c r="B1484" s="13"/>
+      <c r="B1484" s="14"/>
       <c r="C1484" s="6"/>
       <c r="D1484" s="6"/>
       <c r="E1484" s="6"/>
     </row>
     <row r="1485">
       <c r="A1485" s="6"/>
-      <c r="B1485" s="13"/>
+      <c r="B1485" s="14"/>
       <c r="C1485" s="6"/>
       <c r="D1485" s="6"/>
       <c r="E1485" s="6"/>
     </row>
     <row r="1486">
       <c r="A1486" s="6"/>
-      <c r="B1486" s="13"/>
+      <c r="B1486" s="14"/>
       <c r="C1486" s="6"/>
       <c r="D1486" s="6"/>
       <c r="E1486" s="6"/>
     </row>
     <row r="1487">
       <c r="A1487" s="6"/>
-      <c r="B1487" s="13"/>
+      <c r="B1487" s="14"/>
       <c r="C1487" s="6"/>
       <c r="D1487" s="6"/>
       <c r="E1487" s="6"/>
     </row>
     <row r="1488">
       <c r="A1488" s="6"/>
-      <c r="B1488" s="13"/>
+      <c r="B1488" s="14"/>
       <c r="C1488" s="6"/>
       <c r="D1488" s="6"/>
       <c r="E1488" s="6"/>
     </row>
     <row r="1489">
       <c r="A1489" s="6"/>
-      <c r="B1489" s="13"/>
+      <c r="B1489" s="14"/>
       <c r="C1489" s="6"/>
       <c r="D1489" s="6"/>
       <c r="E1489" s="6"/>
     </row>
     <row r="1490">
       <c r="A1490" s="6"/>
-      <c r="B1490" s="13"/>
+      <c r="B1490" s="14"/>
       <c r="C1490" s="6"/>
       <c r="D1490" s="6"/>
       <c r="E1490" s="6"/>
     </row>
     <row r="1491">
       <c r="A1491" s="6"/>
-      <c r="B1491" s="13"/>
+      <c r="B1491" s="14"/>
       <c r="C1491" s="6"/>
       <c r="D1491" s="6"/>
       <c r="E1491" s="6"/>
     </row>
     <row r="1492">
       <c r="A1492" s="6"/>
-      <c r="B1492" s="13"/>
+      <c r="B1492" s="14"/>
       <c r="C1492" s="6"/>
       <c r="D1492" s="6"/>
       <c r="E1492" s="6"/>
     </row>
     <row r="1493">
       <c r="A1493" s="6"/>
-      <c r="B1493" s="13"/>
+      <c r="B1493" s="14"/>
       <c r="C1493" s="6"/>
       <c r="D1493" s="6"/>
       <c r="E1493" s="6"/>
     </row>
     <row r="1494">
       <c r="A1494" s="6"/>
-      <c r="B1494" s="13"/>
+      <c r="B1494" s="14"/>
       <c r="C1494" s="6"/>
       <c r="D1494" s="6"/>
       <c r="E1494" s="6"/>
     </row>
     <row r="1495">
       <c r="A1495" s="6"/>
-      <c r="B1495" s="13"/>
+      <c r="B1495" s="14"/>
       <c r="C1495" s="6"/>
       <c r="D1495" s="6"/>
       <c r="E1495" s="6"/>
     </row>
     <row r="1496">
       <c r="A1496" s="6"/>
-      <c r="B1496" s="13"/>
+      <c r="B1496" s="14"/>
       <c r="C1496" s="6"/>
       <c r="D1496" s="6"/>
       <c r="E1496" s="6"/>
     </row>
     <row r="1497">
       <c r="A1497" s="6"/>
-      <c r="B1497" s="13"/>
+      <c r="B1497" s="14"/>
       <c r="C1497" s="6"/>
       <c r="D1497" s="6"/>
       <c r="E1497" s="6"/>
     </row>
     <row r="1498">
       <c r="A1498" s="6"/>
-      <c r="B1498" s="13"/>
+      <c r="B1498" s="14"/>
       <c r="C1498" s="6"/>
       <c r="D1498" s="6"/>
       <c r="E1498" s="6"/>
     </row>
     <row r="1499">
       <c r="A1499" s="6"/>
-      <c r="B1499" s="13"/>
+      <c r="B1499" s="14"/>
       <c r="C1499" s="6"/>
       <c r="D1499" s="6"/>
       <c r="E1499" s="6"/>
     </row>
     <row r="1500">
       <c r="A1500" s="6"/>
-      <c r="B1500" s="13"/>
+      <c r="B1500" s="14"/>
       <c r="C1500" s="6"/>
       <c r="D1500" s="6"/>
       <c r="E1500" s="6"/>
     </row>
     <row r="1501">
       <c r="A1501" s="6"/>
-      <c r="B1501" s="13"/>
+      <c r="B1501" s="14"/>
       <c r="C1501" s="6"/>
       <c r="D1501" s="6"/>
       <c r="E1501" s="6"/>
     </row>
     <row r="1502">
       <c r="A1502" s="6"/>
-      <c r="B1502" s="13"/>
+      <c r="B1502" s="14"/>
       <c r="C1502" s="6"/>
       <c r="D1502" s="6"/>
       <c r="E1502" s="6"/>
     </row>
     <row r="1503">
       <c r="A1503" s="6"/>
-      <c r="B1503" s="13"/>
+      <c r="B1503" s="14"/>
       <c r="C1503" s="6"/>
       <c r="D1503" s="6"/>
       <c r="E1503" s="6"/>
     </row>
     <row r="1504">
       <c r="A1504" s="6"/>
-      <c r="B1504" s="13"/>
+      <c r="B1504" s="14"/>
       <c r="C1504" s="6"/>
       <c r="D1504" s="6"/>
       <c r="E1504" s="6"/>
     </row>
     <row r="1505">
       <c r="A1505" s="6"/>
-      <c r="B1505" s="13"/>
+      <c r="B1505" s="14"/>
       <c r="C1505" s="6"/>
       <c r="D1505" s="6"/>
       <c r="E1505" s="6"/>
     </row>
     <row r="1506">
       <c r="A1506" s="6"/>
-      <c r="B1506" s="13"/>
+      <c r="B1506" s="14"/>
       <c r="C1506" s="6"/>
       <c r="D1506" s="6"/>
       <c r="E1506" s="6"/>
     </row>
     <row r="1507">
       <c r="A1507" s="6"/>
-      <c r="B1507" s="13"/>
+      <c r="B1507" s="14"/>
       <c r="C1507" s="6"/>
       <c r="D1507" s="6"/>
       <c r="E1507" s="6"/>
     </row>
     <row r="1508">
       <c r="A1508" s="6"/>
-      <c r="B1508" s="13"/>
+      <c r="B1508" s="14"/>
       <c r="C1508" s="6"/>
       <c r="D1508" s="6"/>
       <c r="E1508" s="6"/>
     </row>
     <row r="1509">
       <c r="A1509" s="6"/>
-      <c r="B1509" s="13"/>
+      <c r="B1509" s="14"/>
       <c r="C1509" s="6"/>
       <c r="D1509" s="6"/>
       <c r="E1509" s="6"/>
     </row>
     <row r="1510">
       <c r="A1510" s="6"/>
-      <c r="B1510" s="13"/>
+      <c r="B1510" s="14"/>
       <c r="C1510" s="6"/>
       <c r="D1510" s="6"/>
       <c r="E1510" s="6"/>
     </row>
     <row r="1511">
       <c r="A1511" s="6"/>
-      <c r="B1511" s="13"/>
+      <c r="B1511" s="14"/>
       <c r="C1511" s="6"/>
       <c r="D1511" s="6"/>
       <c r="E1511" s="6"/>
     </row>
     <row r="1512">
       <c r="A1512" s="6"/>
-      <c r="B1512" s="13"/>
+      <c r="B1512" s="14"/>
       <c r="C1512" s="6"/>
       <c r="D1512" s="6"/>
       <c r="E1512" s="6"/>
     </row>
     <row r="1513">
       <c r="A1513" s="6"/>
-      <c r="B1513" s="13"/>
+      <c r="B1513" s="14"/>
       <c r="C1513" s="6"/>
       <c r="D1513" s="6"/>
       <c r="E1513" s="6"/>
     </row>
     <row r="1514">
       <c r="A1514" s="6"/>
-      <c r="B1514" s="13"/>
+      <c r="B1514" s="14"/>
       <c r="C1514" s="6"/>
       <c r="D1514" s="6"/>
       <c r="E1514" s="6"/>
     </row>
     <row r="1515">
       <c r="A1515" s="6"/>
-      <c r="B1515" s="13"/>
+      <c r="B1515" s="14"/>
       <c r="C1515" s="6"/>
       <c r="D1515" s="6"/>
       <c r="E1515" s="6"/>
     </row>
     <row r="1516">
       <c r="A1516" s="6"/>
-      <c r="B1516" s="13"/>
+      <c r="B1516" s="14"/>
       <c r="C1516" s="6"/>
       <c r="D1516" s="6"/>
       <c r="E1516" s="6"/>
     </row>
     <row r="1517">
       <c r="A1517" s="6"/>
-      <c r="B1517" s="13"/>
+      <c r="B1517" s="14"/>
       <c r="C1517" s="6"/>
       <c r="D1517" s="6"/>
       <c r="E1517" s="6"/>
     </row>
     <row r="1518">
       <c r="A1518" s="6"/>
-      <c r="B1518" s="13"/>
+      <c r="B1518" s="14"/>
       <c r="C1518" s="6"/>
       <c r="D1518" s="6"/>
       <c r="E1518" s="6"/>
     </row>
     <row r="1519">
       <c r="A1519" s="6"/>
-      <c r="B1519" s="13"/>
+      <c r="B1519" s="14"/>
       <c r="C1519" s="6"/>
       <c r="D1519" s="6"/>
       <c r="E1519" s="6"/>
     </row>
     <row r="1520">
       <c r="A1520" s="6"/>
-      <c r="B1520" s="13"/>
+      <c r="B1520" s="14"/>
       <c r="C1520" s="6"/>
       <c r="D1520" s="6"/>
       <c r="E1520" s="6"/>
     </row>
     <row r="1521">
       <c r="A1521" s="6"/>
-      <c r="B1521" s="13"/>
+      <c r="B1521" s="14"/>
       <c r="C1521" s="6"/>
       <c r="D1521" s="6"/>
       <c r="E1521" s="6"/>
     </row>
     <row r="1522">
       <c r="A1522" s="6"/>
-      <c r="B1522" s="13"/>
+      <c r="B1522" s="14"/>
       <c r="C1522" s="6"/>
       <c r="D1522" s="6"/>
       <c r="E1522" s="6"/>
     </row>
     <row r="1523">
       <c r="A1523" s="6"/>
-      <c r="B1523" s="13"/>
+      <c r="B1523" s="14"/>
       <c r="C1523" s="6"/>
       <c r="D1523" s="6"/>
       <c r="E1523" s="6"/>
     </row>
     <row r="1524">
       <c r="A1524" s="6"/>
-      <c r="B1524" s="13"/>
+      <c r="B1524" s="14"/>
       <c r="C1524" s="6"/>
       <c r="D1524" s="6"/>
       <c r="E1524" s="6"/>
     </row>
     <row r="1525">
       <c r="A1525" s="6"/>
-      <c r="B1525" s="13"/>
+      <c r="B1525" s="14"/>
       <c r="C1525" s="6"/>
       <c r="D1525" s="6"/>
       <c r="E1525" s="6"/>
     </row>
     <row r="1526">
       <c r="A1526" s="6"/>
-      <c r="B1526" s="13"/>
+      <c r="B1526" s="14"/>
       <c r="C1526" s="6"/>
       <c r="D1526" s="6"/>
       <c r="E1526" s="6"/>
     </row>
     <row r="1527">
       <c r="A1527" s="6"/>
-      <c r="B1527" s="13"/>
+      <c r="B1527" s="14"/>
       <c r="C1527" s="6"/>
       <c r="D1527" s="6"/>
       <c r="E1527" s="6"/>
     </row>
     <row r="1528">
       <c r="A1528" s="6"/>
-      <c r="B1528" s="13"/>
+      <c r="B1528" s="14"/>
       <c r="C1528" s="6"/>
       <c r="D1528" s="6"/>
       <c r="E1528" s="6"/>
     </row>
     <row r="1529">
       <c r="A1529" s="6"/>
-      <c r="B1529" s="13"/>
+      <c r="B1529" s="14"/>
       <c r="C1529" s="6"/>
       <c r="D1529" s="6"/>
       <c r="E1529" s="6"/>
     </row>
     <row r="1530">
       <c r="A1530" s="6"/>
-      <c r="B1530" s="13"/>
+      <c r="B1530" s="14"/>
       <c r="C1530" s="6"/>
       <c r="D1530" s="6"/>
       <c r="E1530" s="6"/>
     </row>
     <row r="1531">
       <c r="A1531" s="6"/>
-      <c r="B1531" s="13"/>
+      <c r="B1531" s="14"/>
       <c r="C1531" s="6"/>
       <c r="D1531" s="6"/>
       <c r="E1531" s="6"/>
     </row>
     <row r="1532">
       <c r="A1532" s="6"/>
-      <c r="B1532" s="13"/>
+      <c r="B1532" s="14"/>
       <c r="C1532" s="6"/>
       <c r="D1532" s="6"/>
       <c r="E1532" s="6"/>
     </row>
     <row r="1533">
       <c r="A1533" s="6"/>
-      <c r="B1533" s="13"/>
+      <c r="B1533" s="14"/>
       <c r="C1533" s="6"/>
       <c r="D1533" s="6"/>
       <c r="E1533" s="6"/>
     </row>
     <row r="1534">
       <c r="A1534" s="6"/>
-      <c r="B1534" s="13"/>
+      <c r="B1534" s="14"/>
       <c r="C1534" s="6"/>
       <c r="D1534" s="6"/>
       <c r="E1534" s="6"/>
     </row>
     <row r="1535">
       <c r="A1535" s="6"/>
-      <c r="B1535" s="13"/>
+      <c r="B1535" s="14"/>
       <c r="C1535" s="6"/>
       <c r="D1535" s="6"/>
       <c r="E1535" s="6"/>
     </row>
     <row r="1536">
       <c r="A1536" s="6"/>
-      <c r="B1536" s="13"/>
+      <c r="B1536" s="14"/>
       <c r="C1536" s="6"/>
       <c r="D1536" s="6"/>
       <c r="E1536" s="6"/>
     </row>
     <row r="1537">
       <c r="A1537" s="6"/>
-      <c r="B1537" s="13"/>
+      <c r="B1537" s="14"/>
       <c r="C1537" s="6"/>
       <c r="D1537" s="6"/>
       <c r="E1537" s="6"/>
     </row>
     <row r="1538">
       <c r="A1538" s="6"/>
-      <c r="B1538" s="13"/>
+      <c r="B1538" s="14"/>
       <c r="C1538" s="6"/>
       <c r="D1538" s="6"/>
       <c r="E1538" s="6"/>
     </row>
     <row r="1539">
       <c r="A1539" s="6"/>
-      <c r="B1539" s="13"/>
+      <c r="B1539" s="14"/>
       <c r="C1539" s="6"/>
       <c r="D1539" s="6"/>
       <c r="E1539" s="6"/>
     </row>
     <row r="1540">
       <c r="A1540" s="6"/>
-      <c r="B1540" s="13"/>
+      <c r="B1540" s="14"/>
       <c r="C1540" s="6"/>
       <c r="D1540" s="6"/>
       <c r="E1540" s="6"/>
     </row>
     <row r="1541">
       <c r="A1541" s="6"/>
-      <c r="B1541" s="13"/>
+      <c r="B1541" s="14"/>
       <c r="C1541" s="6"/>
       <c r="D1541" s="6"/>
       <c r="E1541" s="6"/>
     </row>
     <row r="1542">
       <c r="A1542" s="6"/>
-      <c r="B1542" s="13"/>
+      <c r="B1542" s="14"/>
       <c r="C1542" s="6"/>
       <c r="D1542" s="6"/>
       <c r="E1542" s="6"/>
     </row>
     <row r="1543">
       <c r="A1543" s="6"/>
-      <c r="B1543" s="13"/>
+      <c r="B1543" s="14"/>
       <c r="C1543" s="6"/>
       <c r="D1543" s="6"/>
       <c r="E1543" s="6"/>
     </row>
     <row r="1544">
       <c r="A1544" s="6"/>
-      <c r="B1544" s="13"/>
+      <c r="B1544" s="14"/>
       <c r="C1544" s="6"/>
       <c r="D1544" s="6"/>
       <c r="E1544" s="6"/>
     </row>
     <row r="1545">
       <c r="A1545" s="6"/>
-      <c r="B1545" s="13"/>
+      <c r="B1545" s="14"/>
       <c r="C1545" s="6"/>
       <c r="D1545" s="6"/>
       <c r="E1545" s="6"/>
     </row>
     <row r="1546">
       <c r="A1546" s="6"/>
-      <c r="B1546" s="13"/>
+      <c r="B1546" s="14"/>
       <c r="C1546" s="6"/>
       <c r="D1546" s="6"/>
       <c r="E1546" s="6"/>
     </row>
     <row r="1547">
       <c r="A1547" s="6"/>
-      <c r="B1547" s="13"/>
+      <c r="B1547" s="14"/>
       <c r="C1547" s="6"/>
       <c r="D1547" s="6"/>
       <c r="E1547" s="6"/>
     </row>
     <row r="1548">
       <c r="A1548" s="6"/>
-      <c r="B1548" s="13"/>
+      <c r="B1548" s="14"/>
       <c r="C1548" s="6"/>
       <c r="D1548" s="6"/>
       <c r="E1548" s="6"/>
     </row>
     <row r="1549">
       <c r="A1549" s="6"/>
-      <c r="B1549" s="13"/>
+      <c r="B1549" s="14"/>
       <c r="C1549" s="6"/>
       <c r="D1549" s="6"/>
       <c r="E1549" s="6"/>
     </row>
     <row r="1550">
       <c r="A1550" s="6"/>
-      <c r="B1550" s="13"/>
+      <c r="B1550" s="14"/>
       <c r="C1550" s="6"/>
       <c r="D1550" s="6"/>
       <c r="E1550" s="6"/>
     </row>
     <row r="1551">
       <c r="A1551" s="6"/>
-      <c r="B1551" s="13"/>
+      <c r="B1551" s="14"/>
       <c r="C1551" s="6"/>
       <c r="D1551" s="6"/>
       <c r="E1551" s="6"/>
     </row>
     <row r="1552">
       <c r="A1552" s="6"/>
-      <c r="B1552" s="13"/>
+      <c r="B1552" s="14"/>
       <c r="C1552" s="6"/>
       <c r="D1552" s="6"/>
       <c r="E1552" s="6"/>
     </row>
     <row r="1553">
       <c r="A1553" s="6"/>
-      <c r="B1553" s="13"/>
+      <c r="B1553" s="14"/>
       <c r="C1553" s="6"/>
       <c r="D1553" s="6"/>
       <c r="E1553" s="6"/>
     </row>
     <row r="1554">
       <c r="A1554" s="6"/>
-      <c r="B1554" s="13"/>
+      <c r="B1554" s="14"/>
       <c r="C1554" s="6"/>
       <c r="D1554" s="6"/>
       <c r="E1554" s="6"/>
     </row>
     <row r="1555">
       <c r="A1555" s="6"/>
-      <c r="B1555" s="13"/>
+      <c r="B1555" s="14"/>
       <c r="C1555" s="6"/>
       <c r="D1555" s="6"/>
       <c r="E1555" s="6"/>
     </row>
     <row r="1556">
       <c r="A1556" s="6"/>
-      <c r="B1556" s="13"/>
+      <c r="B1556" s="14"/>
       <c r="C1556" s="6"/>
       <c r="D1556" s="6"/>
       <c r="E1556" s="6"/>
     </row>
     <row r="1557">
       <c r="A1557" s="6"/>
-      <c r="B1557" s="13"/>
+      <c r="B1557" s="14"/>
       <c r="C1557" s="6"/>
       <c r="D1557" s="6"/>
       <c r="E1557" s="6"/>
     </row>
     <row r="1558">
       <c r="A1558" s="6"/>
-      <c r="B1558" s="13"/>
+      <c r="B1558" s="14"/>
       <c r="C1558" s="6"/>
       <c r="D1558" s="6"/>
       <c r="E1558" s="6"/>
     </row>
     <row r="1559">
       <c r="A1559" s="6"/>
-      <c r="B1559" s="13"/>
+      <c r="B1559" s="14"/>
       <c r="C1559" s="6"/>
       <c r="D1559" s="6"/>
       <c r="E1559" s="6"/>
     </row>
     <row r="1560">
       <c r="A1560" s="6"/>
-      <c r="B1560" s="13"/>
+      <c r="B1560" s="14"/>
       <c r="C1560" s="6"/>
       <c r="D1560" s="6"/>
       <c r="E1560" s="6"/>
     </row>
     <row r="1561">
       <c r="A1561" s="6"/>
-      <c r="B1561" s="13"/>
+      <c r="B1561" s="14"/>
       <c r="C1561" s="6"/>
       <c r="D1561" s="6"/>
       <c r="E1561" s="6"/>
     </row>
     <row r="1562">
       <c r="A1562" s="6"/>
-      <c r="B1562" s="13"/>
+      <c r="B1562" s="14"/>
       <c r="C1562" s="6"/>
       <c r="D1562" s="6"/>
       <c r="E1562" s="6"/>
     </row>
     <row r="1563">
       <c r="A1563" s="6"/>
-      <c r="B1563" s="13"/>
+      <c r="B1563" s="14"/>
       <c r="C1563" s="6"/>
       <c r="D1563" s="6"/>
       <c r="E1563" s="6"/>
     </row>
     <row r="1564">
       <c r="A1564" s="6"/>
-      <c r="B1564" s="13"/>
+      <c r="B1564" s="14"/>
       <c r="C1564" s="6"/>
       <c r="D1564" s="6"/>
       <c r="E1564" s="6"/>
     </row>
     <row r="1565">
       <c r="A1565" s="6"/>
-      <c r="B1565" s="13"/>
+      <c r="B1565" s="14"/>
       <c r="C1565" s="6"/>
       <c r="D1565" s="6"/>
       <c r="E1565" s="6"/>
     </row>
     <row r="1566">
       <c r="A1566" s="6"/>
-      <c r="B1566" s="13"/>
+      <c r="B1566" s="14"/>
       <c r="C1566" s="6"/>
       <c r="D1566" s="6"/>
       <c r="E1566" s="6"/>
     </row>
     <row r="1567">
       <c r="A1567" s="6"/>
-      <c r="B1567" s="13"/>
+      <c r="B1567" s="14"/>
       <c r="C1567" s="6"/>
       <c r="D1567" s="6"/>
       <c r="E1567" s="6"/>
     </row>
     <row r="1568">
       <c r="A1568" s="6"/>
-      <c r="B1568" s="13"/>
+      <c r="B1568" s="14"/>
       <c r="C1568" s="6"/>
       <c r="D1568" s="6"/>
       <c r="E1568" s="6"/>
     </row>
     <row r="1569">
       <c r="A1569" s="6"/>
-      <c r="B1569" s="13"/>
+      <c r="B1569" s="14"/>
       <c r="C1569" s="6"/>
       <c r="D1569" s="6"/>
       <c r="E1569" s="6"/>
     </row>
     <row r="1570">
       <c r="A1570" s="6"/>
-      <c r="B1570" s="13"/>
+      <c r="B1570" s="14"/>
       <c r="C1570" s="6"/>
       <c r="D1570" s="6"/>
       <c r="E1570" s="6"/>
     </row>
     <row r="1571">
       <c r="A1571" s="6"/>
-      <c r="B1571" s="13"/>
+      <c r="B1571" s="14"/>
       <c r="C1571" s="6"/>
       <c r="D1571" s="6"/>
       <c r="E1571" s="6"/>
     </row>
     <row r="1572">
       <c r="A1572" s="6"/>
-      <c r="B1572" s="13"/>
+      <c r="B1572" s="14"/>
       <c r="C1572" s="6"/>
       <c r="D1572" s="6"/>
       <c r="E1572" s="6"/>
     </row>
     <row r="1573">
       <c r="A1573" s="6"/>
-      <c r="B1573" s="13"/>
+      <c r="B1573" s="14"/>
       <c r="C1573" s="6"/>
       <c r="D1573" s="6"/>
       <c r="E1573" s="6"/>
     </row>
     <row r="1574">
       <c r="A1574" s="6"/>
-      <c r="B1574" s="13"/>
+      <c r="B1574" s="14"/>
       <c r="C1574" s="6"/>
       <c r="D1574" s="6"/>
       <c r="E1574" s="6"/>
     </row>
     <row r="1575">
       <c r="A1575" s="6"/>
-      <c r="B1575" s="13"/>
+      <c r="B1575" s="14"/>
       <c r="C1575" s="6"/>
       <c r="D1575" s="6"/>
       <c r="E1575" s="6"/>
     </row>
     <row r="1576">
       <c r="A1576" s="6"/>
-      <c r="B1576" s="13"/>
+      <c r="B1576" s="14"/>
       <c r="C1576" s="6"/>
       <c r="D1576" s="6"/>
       <c r="E1576" s="6"/>
     </row>
     <row r="1577">
       <c r="A1577" s="6"/>
-      <c r="B1577" s="13"/>
+      <c r="B1577" s="14"/>
       <c r="C1577" s="6"/>
       <c r="D1577" s="6"/>
       <c r="E1577" s="6"/>
     </row>
     <row r="1578">
       <c r="A1578" s="6"/>
-      <c r="B1578" s="13"/>
+      <c r="B1578" s="14"/>
       <c r="C1578" s="6"/>
       <c r="D1578" s="6"/>
       <c r="E1578" s="6"/>
     </row>
     <row r="1579">
       <c r="A1579" s="6"/>
-      <c r="B1579" s="13"/>
+      <c r="B1579" s="14"/>
       <c r="C1579" s="6"/>
       <c r="D1579" s="6"/>
       <c r="E1579" s="6"/>
     </row>
     <row r="1580">
       <c r="A1580" s="6"/>
-      <c r="B1580" s="13"/>
+      <c r="B1580" s="14"/>
       <c r="C1580" s="6"/>
       <c r="D1580" s="6"/>
       <c r="E1580" s="6"/>
     </row>
     <row r="1581">
       <c r="A1581" s="6"/>
-      <c r="B1581" s="13"/>
+      <c r="B1581" s="14"/>
       <c r="C1581" s="6"/>
       <c r="D1581" s="6"/>
       <c r="E1581" s="6"/>
     </row>
     <row r="1582">
       <c r="A1582" s="6"/>
-      <c r="B1582" s="13"/>
+      <c r="B1582" s="14"/>
       <c r="C1582" s="6"/>
       <c r="D1582" s="6"/>
       <c r="E1582" s="6"/>
     </row>
     <row r="1583">
       <c r="A1583" s="6"/>
-      <c r="B1583" s="13"/>
+      <c r="B1583" s="14"/>
       <c r="C1583" s="6"/>
       <c r="D1583" s="6"/>
       <c r="E1583" s="6"/>
     </row>
     <row r="1584">
       <c r="A1584" s="6"/>
-      <c r="B1584" s="13"/>
+      <c r="B1584" s="14"/>
       <c r="C1584" s="6"/>
       <c r="D1584" s="6"/>
       <c r="E1584" s="6"/>
     </row>
     <row r="1585">
       <c r="A1585" s="6"/>
-      <c r="B1585" s="13"/>
+      <c r="B1585" s="14"/>
       <c r="C1585" s="6"/>
       <c r="D1585" s="6"/>
       <c r="E1585" s="6"/>
     </row>
     <row r="1586">
       <c r="A1586" s="6"/>
-      <c r="B1586" s="13"/>
+      <c r="B1586" s="14"/>
       <c r="C1586" s="6"/>
       <c r="D1586" s="6"/>
       <c r="E1586" s="6"/>
     </row>
     <row r="1587">
       <c r="A1587" s="6"/>
-      <c r="B1587" s="13"/>
+      <c r="B1587" s="14"/>
       <c r="C1587" s="6"/>
       <c r="D1587" s="6"/>
       <c r="E1587" s="6"/>
     </row>
     <row r="1588">
       <c r="A1588" s="6"/>
-      <c r="B1588" s="13"/>
+      <c r="B1588" s="14"/>
       <c r="C1588" s="6"/>
       <c r="D1588" s="6"/>
       <c r="E1588" s="6"/>
     </row>
     <row r="1589">
       <c r="A1589" s="6"/>
-      <c r="B1589" s="13"/>
+      <c r="B1589" s="14"/>
       <c r="C1589" s="6"/>
       <c r="D1589" s="6"/>
       <c r="E1589" s="6"/>
     </row>
     <row r="1590">
       <c r="A1590" s="6"/>
-      <c r="B1590" s="13"/>
+      <c r="B1590" s="14"/>
       <c r="C1590" s="6"/>
       <c r="D1590" s="6"/>
       <c r="E1590" s="6"/>
     </row>
     <row r="1591">
       <c r="A1591" s="6"/>
-      <c r="B1591" s="13"/>
+      <c r="B1591" s="14"/>
       <c r="C1591" s="6"/>
       <c r="D1591" s="6"/>
       <c r="E1591" s="6"/>
     </row>
     <row r="1592">
       <c r="A1592" s="6"/>
-      <c r="B1592" s="13"/>
+      <c r="B1592" s="14"/>
       <c r="C1592" s="6"/>
       <c r="D1592" s="6"/>
       <c r="E1592" s="6"/>
     </row>
     <row r="1593">
       <c r="A1593" s="6"/>
-      <c r="B1593" s="13"/>
+      <c r="B1593" s="14"/>
       <c r="C1593" s="6"/>
       <c r="D1593" s="6"/>
       <c r="E1593" s="6"/>
     </row>
     <row r="1594">
       <c r="A1594" s="6"/>
-      <c r="B1594" s="13"/>
+      <c r="B1594" s="14"/>
       <c r="C1594" s="6"/>
       <c r="D1594" s="6"/>
       <c r="E1594" s="6"/>
     </row>
     <row r="1595">
       <c r="A1595" s="6"/>
-      <c r="B1595" s="13"/>
+      <c r="B1595" s="14"/>
       <c r="C1595" s="6"/>
       <c r="D1595" s="6"/>
       <c r="E1595" s="6"/>
     </row>
     <row r="1596">
       <c r="A1596" s="6"/>
-      <c r="B1596" s="13"/>
+      <c r="B1596" s="14"/>
       <c r="C1596" s="6"/>
       <c r="D1596" s="6"/>
       <c r="E1596" s="6"/>
     </row>
     <row r="1597">
       <c r="A1597" s="6"/>
-      <c r="B1597" s="13"/>
+      <c r="B1597" s="14"/>
       <c r="C1597" s="6"/>
       <c r="D1597" s="6"/>
       <c r="E1597" s="6"/>
     </row>
     <row r="1598">
       <c r="A1598" s="6"/>
-      <c r="B1598" s="13"/>
+      <c r="B1598" s="14"/>
       <c r="C1598" s="6"/>
       <c r="D1598" s="6"/>
       <c r="E1598" s="6"/>
     </row>
     <row r="1599">
       <c r="A1599" s="6"/>
-      <c r="B1599" s="13"/>
+      <c r="B1599" s="14"/>
       <c r="C1599" s="6"/>
       <c r="D1599" s="6"/>
       <c r="E1599" s="6"/>
     </row>
     <row r="1600">
       <c r="A1600" s="6"/>
-      <c r="B1600" s="13"/>
+      <c r="B1600" s="14"/>
       <c r="C1600" s="6"/>
       <c r="D1600" s="6"/>
       <c r="E1600" s="6"/>
     </row>
     <row r="1601">
       <c r="A1601" s="6"/>
-      <c r="B1601" s="13"/>
+      <c r="B1601" s="14"/>
       <c r="C1601" s="6"/>
       <c r="D1601" s="6"/>
       <c r="E1601" s="6"/>
     </row>
     <row r="1602">
       <c r="A1602" s="6"/>
-      <c r="B1602" s="13"/>
+      <c r="B1602" s="14"/>
       <c r="C1602" s="6"/>
       <c r="D1602" s="6"/>
       <c r="E1602" s="6"/>
     </row>
     <row r="1603">
       <c r="A1603" s="6"/>
-      <c r="B1603" s="13"/>
+      <c r="B1603" s="14"/>
       <c r="C1603" s="6"/>
       <c r="D1603" s="6"/>
       <c r="E1603" s="6"/>
     </row>
     <row r="1604">
       <c r="A1604" s="6"/>
-      <c r="B1604" s="13"/>
+      <c r="B1604" s="14"/>
       <c r="C1604" s="6"/>
       <c r="D1604" s="6"/>
       <c r="E1604" s="6"/>
     </row>
     <row r="1605">
       <c r="A1605" s="6"/>
-      <c r="B1605" s="13"/>
+      <c r="B1605" s="14"/>
       <c r="C1605" s="6"/>
       <c r="D1605" s="6"/>
       <c r="E1605" s="6"/>
     </row>
     <row r="1606">
       <c r="A1606" s="6"/>
-      <c r="B1606" s="13"/>
+      <c r="B1606" s="14"/>
       <c r="C1606" s="6"/>
       <c r="D1606" s="6"/>
       <c r="E1606" s="6"/>
     </row>
     <row r="1607">
       <c r="A1607" s="6"/>
-      <c r="B1607" s="13"/>
+      <c r="B1607" s="14"/>
       <c r="C1607" s="6"/>
       <c r="D1607" s="6"/>
       <c r="E1607" s="6"/>
     </row>
     <row r="1608">
       <c r="A1608" s="6"/>
-      <c r="B1608" s="13"/>
+      <c r="B1608" s="14"/>
       <c r="C1608" s="6"/>
       <c r="D1608" s="6"/>
       <c r="E1608" s="6"/>
     </row>
     <row r="1609">
       <c r="A1609" s="6"/>
-      <c r="B1609" s="13"/>
+      <c r="B1609" s="14"/>
       <c r="C1609" s="6"/>
       <c r="D1609" s="6"/>
       <c r="E1609" s="6"/>
     </row>
     <row r="1610">
       <c r="A1610" s="6"/>
-      <c r="B1610" s="13"/>
+      <c r="B1610" s="14"/>
       <c r="C1610" s="6"/>
       <c r="D1610" s="6"/>
       <c r="E1610" s="6"/>
     </row>
     <row r="1611">
       <c r="A1611" s="6"/>
-      <c r="B1611" s="13"/>
+      <c r="B1611" s="14"/>
       <c r="C1611" s="6"/>
       <c r="D1611" s="6"/>
       <c r="E1611" s="6"/>
     </row>
     <row r="1612">
       <c r="A1612" s="6"/>
-      <c r="B1612" s="13"/>
+      <c r="B1612" s="14"/>
       <c r="C1612" s="6"/>
       <c r="D1612" s="6"/>
       <c r="E1612" s="6"/>
     </row>
     <row r="1613">
       <c r="A1613" s="6"/>
-      <c r="B1613" s="13"/>
+      <c r="B1613" s="14"/>
       <c r="C1613" s="6"/>
       <c r="D1613" s="6"/>
       <c r="E1613" s="6"/>
     </row>
     <row r="1614">
       <c r="A1614" s="6"/>
-      <c r="B1614" s="13"/>
+      <c r="B1614" s="14"/>
       <c r="C1614" s="6"/>
       <c r="D1614" s="6"/>
       <c r="E1614" s="6"/>
     </row>
     <row r="1615">
       <c r="A1615" s="6"/>
-      <c r="B1615" s="13"/>
+      <c r="B1615" s="14"/>
       <c r="C1615" s="6"/>
       <c r="D1615" s="6"/>
       <c r="E1615" s="6"/>
     </row>
     <row r="1616">
       <c r="A1616" s="6"/>
-      <c r="B1616" s="13"/>
+      <c r="B1616" s="14"/>
       <c r="C1616" s="6"/>
       <c r="D1616" s="6"/>
       <c r="E1616" s="6"/>
     </row>
     <row r="1617">
       <c r="A1617" s="6"/>
-      <c r="B1617" s="13"/>
+      <c r="B1617" s="14"/>
       <c r="C1617" s="6"/>
       <c r="D1617" s="6"/>
       <c r="E1617" s="6"/>
     </row>
     <row r="1618">
       <c r="A1618" s="6"/>
-      <c r="B1618" s="13"/>
+      <c r="B1618" s="14"/>
       <c r="C1618" s="6"/>
       <c r="D1618" s="6"/>
       <c r="E1618" s="6"/>
     </row>
     <row r="1619">
       <c r="A1619" s="6"/>
-      <c r="B1619" s="13"/>
+      <c r="B1619" s="14"/>
       <c r="C1619" s="6"/>
       <c r="D1619" s="6"/>
       <c r="E1619" s="6"/>
     </row>
     <row r="1620">
       <c r="A1620" s="6"/>
-      <c r="B1620" s="13"/>
+      <c r="B1620" s="14"/>
       <c r="C1620" s="6"/>
       <c r="D1620" s="6"/>
       <c r="E1620" s="6"/>
     </row>
     <row r="1621">
       <c r="A1621" s="6"/>
-      <c r="B1621" s="13"/>
+      <c r="B1621" s="14"/>
       <c r="C1621" s="6"/>
       <c r="D1621" s="6"/>
       <c r="E1621" s="6"/>
     </row>
     <row r="1622">
       <c r="A1622" s="6"/>
-      <c r="B1622" s="13"/>
+      <c r="B1622" s="14"/>
       <c r="C1622" s="6"/>
       <c r="D1622" s="6"/>
       <c r="E1622" s="6"/>
     </row>
     <row r="1623">
       <c r="A1623" s="6"/>
-      <c r="B1623" s="13"/>
+      <c r="B1623" s="14"/>
       <c r="C1623" s="6"/>
       <c r="D1623" s="6"/>
       <c r="E1623" s="6"/>
     </row>
     <row r="1624">
       <c r="A1624" s="6"/>
-      <c r="B1624" s="13"/>
+      <c r="B1624" s="14"/>
       <c r="C1624" s="6"/>
       <c r="D1624" s="6"/>
       <c r="E1624" s="6"/>
     </row>
     <row r="1625">
       <c r="A1625" s="6"/>
-      <c r="B1625" s="13"/>
+      <c r="B1625" s="14"/>
       <c r="C1625" s="6"/>
       <c r="D1625" s="6"/>
       <c r="E1625" s="6"/>
     </row>
     <row r="1626">
       <c r="A1626" s="6"/>
-      <c r="B1626" s="13"/>
+      <c r="B1626" s="14"/>
       <c r="C1626" s="6"/>
       <c r="D1626" s="6"/>
       <c r="E1626" s="6"/>
     </row>
     <row r="1627">
       <c r="A1627" s="6"/>
-      <c r="B1627" s="13"/>
+      <c r="B1627" s="14"/>
       <c r="C1627" s="6"/>
       <c r="D1627" s="6"/>
       <c r="E1627" s="6"/>
     </row>
     <row r="1628">
       <c r="A1628" s="6"/>
-      <c r="B1628" s="13"/>
+      <c r="B1628" s="14"/>
       <c r="C1628" s="6"/>
       <c r="D1628" s="6"/>
       <c r="E1628" s="6"/>
     </row>
     <row r="1629">
       <c r="A1629" s="6"/>
-      <c r="B1629" s="13"/>
+      <c r="B1629" s="14"/>
       <c r="C1629" s="6"/>
       <c r="D1629" s="6"/>
       <c r="E1629" s="6"/>
     </row>
     <row r="1630">
       <c r="A1630" s="6"/>
-      <c r="B1630" s="13"/>
+      <c r="B1630" s="14"/>
       <c r="C1630" s="6"/>
       <c r="D1630" s="6"/>
       <c r="E1630" s="6"/>
     </row>
     <row r="1631">
       <c r="A1631" s="6"/>
-      <c r="B1631" s="13"/>
+      <c r="B1631" s="14"/>
       <c r="C1631" s="6"/>
       <c r="D1631" s="6"/>
       <c r="E1631" s="6"/>
     </row>
     <row r="1632">
       <c r="A1632" s="6"/>
-      <c r="B1632" s="13"/>
+      <c r="B1632" s="14"/>
       <c r="C1632" s="6"/>
       <c r="D1632" s="6"/>
       <c r="E1632" s="6"/>
     </row>
     <row r="1633">
       <c r="A1633" s="6"/>
-      <c r="B1633" s="13"/>
+      <c r="B1633" s="14"/>
       <c r="C1633" s="6"/>
       <c r="D1633" s="6"/>
       <c r="E1633" s="6"/>
     </row>
     <row r="1634">
       <c r="A1634" s="6"/>
-      <c r="B1634" s="13"/>
+      <c r="B1634" s="14"/>
       <c r="C1634" s="6"/>
       <c r="D1634" s="6"/>
       <c r="E1634" s="6"/>
     </row>
     <row r="1635">
       <c r="A1635" s="6"/>
-      <c r="B1635" s="13"/>
+      <c r="B1635" s="14"/>
       <c r="C1635" s="6"/>
       <c r="D1635" s="6"/>
       <c r="E1635" s="6"/>
     </row>
     <row r="1636">
       <c r="A1636" s="6"/>
-      <c r="B1636" s="13"/>
+      <c r="B1636" s="14"/>
       <c r="C1636" s="6"/>
       <c r="D1636" s="6"/>
       <c r="E1636" s="6"/>
     </row>
     <row r="1637">
       <c r="A1637" s="6"/>
-      <c r="B1637" s="13"/>
+      <c r="B1637" s="14"/>
       <c r="C1637" s="6"/>
       <c r="D1637" s="6"/>
       <c r="E1637" s="6"/>
     </row>
     <row r="1638">
       <c r="A1638" s="6"/>
-      <c r="B1638" s="13"/>
+      <c r="B1638" s="14"/>
       <c r="C1638" s="6"/>
       <c r="D1638" s="6"/>
       <c r="E1638" s="6"/>
     </row>
     <row r="1639">
       <c r="A1639" s="6"/>
-      <c r="B1639" s="13"/>
+      <c r="B1639" s="14"/>
       <c r="C1639" s="6"/>
       <c r="D1639" s="6"/>
       <c r="E1639" s="6"/>
     </row>
     <row r="1640">
       <c r="A1640" s="6"/>
-      <c r="B1640" s="13"/>
+      <c r="B1640" s="14"/>
       <c r="C1640" s="6"/>
       <c r="D1640" s="6"/>
       <c r="E1640" s="6"/>
     </row>
     <row r="1641">
       <c r="A1641" s="6"/>
-      <c r="B1641" s="13"/>
+      <c r="B1641" s="14"/>
       <c r="C1641" s="6"/>
       <c r="D1641" s="6"/>
       <c r="E1641" s="6"/>
     </row>
     <row r="1642">
       <c r="A1642" s="6"/>
-      <c r="B1642" s="13"/>
+      <c r="B1642" s="14"/>
       <c r="C1642" s="6"/>
       <c r="D1642" s="6"/>
       <c r="E1642" s="6"/>
     </row>
     <row r="1643">
       <c r="A1643" s="6"/>
-      <c r="B1643" s="13"/>
+      <c r="B1643" s="14"/>
       <c r="C1643" s="6"/>
       <c r="D1643" s="6"/>
       <c r="E1643" s="6"/>
     </row>
     <row r="1644">
       <c r="A1644" s="6"/>
-      <c r="B1644" s="13"/>
+      <c r="B1644" s="14"/>
       <c r="C1644" s="6"/>
       <c r="D1644" s="6"/>
       <c r="E1644" s="6"/>
     </row>
     <row r="1645">
       <c r="A1645" s="6"/>
-      <c r="B1645" s="13"/>
+      <c r="B1645" s="14"/>
       <c r="C1645" s="6"/>
       <c r="D1645" s="6"/>
       <c r="E1645" s="6"/>
     </row>
     <row r="1646">
       <c r="A1646" s="6"/>
-      <c r="B1646" s="13"/>
+      <c r="B1646" s="14"/>
       <c r="C1646" s="6"/>
       <c r="D1646" s="6"/>
       <c r="E1646" s="6"/>
     </row>
     <row r="1647">
       <c r="A1647" s="6"/>
-      <c r="B1647" s="13"/>
+      <c r="B1647" s="14"/>
       <c r="C1647" s="6"/>
       <c r="D1647" s="6"/>
       <c r="E1647" s="6"/>
     </row>
     <row r="1648">
       <c r="A1648" s="6"/>
-      <c r="B1648" s="13"/>
+      <c r="B1648" s="14"/>
       <c r="C1648" s="6"/>
       <c r="D1648" s="6"/>
       <c r="E1648" s="6"/>
     </row>
     <row r="1649">
       <c r="A1649" s="6"/>
-      <c r="B1649" s="13"/>
+      <c r="B1649" s="14"/>
       <c r="C1649" s="6"/>
       <c r="D1649" s="6"/>
       <c r="E1649" s="6"/>
     </row>
     <row r="1650">
       <c r="A1650" s="6"/>
-      <c r="B1650" s="13"/>
+      <c r="B1650" s="14"/>
       <c r="C1650" s="6"/>
       <c r="D1650" s="6"/>
       <c r="E1650" s="6"/>
     </row>
     <row r="1651">
       <c r="A1651" s="6"/>
-      <c r="B1651" s="13"/>
+      <c r="B1651" s="14"/>
       <c r="C1651" s="6"/>
       <c r="D1651" s="6"/>
       <c r="E1651" s="6"/>
     </row>
     <row r="1652">
       <c r="A1652" s="6"/>
-      <c r="B1652" s="13"/>
+      <c r="B1652" s="14"/>
       <c r="C1652" s="6"/>
       <c r="D1652" s="6"/>
       <c r="E1652" s="6"/>
     </row>
     <row r="1653">
       <c r="A1653" s="6"/>
-      <c r="B1653" s="13"/>
+      <c r="B1653" s="14"/>
       <c r="C1653" s="6"/>
       <c r="D1653" s="6"/>
       <c r="E1653" s="6"/>
     </row>
     <row r="1654">
       <c r="A1654" s="6"/>
-      <c r="B1654" s="13"/>
+      <c r="B1654" s="14"/>
       <c r="C1654" s="6"/>
       <c r="D1654" s="6"/>
       <c r="E1654" s="6"/>
     </row>
     <row r="1655">
       <c r="A1655" s="6"/>
-      <c r="B1655" s="13"/>
+      <c r="B1655" s="14"/>
       <c r="C1655" s="6"/>
       <c r="D1655" s="6"/>
       <c r="E1655" s="6"/>
     </row>
     <row r="1656">
       <c r="A1656" s="6"/>
-      <c r="B1656" s="13"/>
+      <c r="B1656" s="14"/>
       <c r="C1656" s="6"/>
       <c r="D1656" s="6"/>
       <c r="E1656" s="6"/>
     </row>
     <row r="1657">
       <c r="A1657" s="6"/>
-      <c r="B1657" s="13"/>
+      <c r="B1657" s="14"/>
       <c r="C1657" s="6"/>
       <c r="D1657" s="6"/>
       <c r="E1657" s="6"/>
     </row>
     <row r="1658">
       <c r="A1658" s="6"/>
-      <c r="B1658" s="13"/>
+      <c r="B1658" s="14"/>
       <c r="C1658" s="6"/>
       <c r="D1658" s="6"/>
       <c r="E1658" s="6"/>
     </row>
     <row r="1659">
       <c r="A1659" s="6"/>
-      <c r="B1659" s="13"/>
+      <c r="B1659" s="14"/>
       <c r="C1659" s="6"/>
       <c r="D1659" s="6"/>
       <c r="E1659" s="6"/>
     </row>
     <row r="1660">
       <c r="A1660" s="6"/>
-      <c r="B1660" s="13"/>
+      <c r="B1660" s="14"/>
       <c r="C1660" s="6"/>
       <c r="D1660" s="6"/>
       <c r="E1660" s="6"/>
     </row>
     <row r="1661">
       <c r="A1661" s="6"/>
-      <c r="B1661" s="13"/>
+      <c r="B1661" s="14"/>
       <c r="C1661" s="6"/>
       <c r="D1661" s="6"/>
       <c r="E1661" s="6"/>
     </row>
     <row r="1662">
       <c r="A1662" s="6"/>
-      <c r="B1662" s="13"/>
+      <c r="B1662" s="14"/>
       <c r="C1662" s="6"/>
       <c r="D1662" s="6"/>
       <c r="E1662" s="6"/>
     </row>
     <row r="1663">
       <c r="A1663" s="6"/>
-      <c r="B1663" s="13"/>
+      <c r="B1663" s="14"/>
       <c r="C1663" s="6"/>
       <c r="D1663" s="6"/>
       <c r="E1663" s="6"/>
     </row>
     <row r="1664">
       <c r="A1664" s="6"/>
-      <c r="B1664" s="13"/>
+      <c r="B1664" s="14"/>
       <c r="C1664" s="6"/>
       <c r="D1664" s="6"/>
       <c r="E1664" s="6"/>
     </row>
     <row r="1665">
       <c r="A1665" s="6"/>
-      <c r="B1665" s="13"/>
+      <c r="B1665" s="14"/>
       <c r="C1665" s="6"/>
       <c r="D1665" s="6"/>
       <c r="E1665" s="6"/>
     </row>
     <row r="1666">
       <c r="A1666" s="6"/>
-      <c r="B1666" s="13"/>
+      <c r="B1666" s="14"/>
       <c r="C1666" s="6"/>
       <c r="D1666" s="6"/>
       <c r="E1666" s="6"/>
     </row>
     <row r="1667">
       <c r="A1667" s="6"/>
-      <c r="B1667" s="13"/>
+      <c r="B1667" s="14"/>
       <c r="C1667" s="6"/>
       <c r="D1667" s="6"/>
       <c r="E1667" s="6"/>
     </row>
     <row r="1668">
       <c r="A1668" s="6"/>
-      <c r="B1668" s="13"/>
+      <c r="B1668" s="14"/>
       <c r="C1668" s="6"/>
       <c r="D1668" s="6"/>
       <c r="E1668" s="6"/>
     </row>
     <row r="1669">
       <c r="A1669" s="6"/>
-      <c r="B1669" s="13"/>
+      <c r="B1669" s="14"/>
       <c r="C1669" s="6"/>
       <c r="D1669" s="6"/>
       <c r="E1669" s="6"/>
     </row>
     <row r="1670">
       <c r="A1670" s="6"/>
-      <c r="B1670" s="13"/>
+      <c r="B1670" s="14"/>
       <c r="C1670" s="6"/>
       <c r="D1670" s="6"/>
       <c r="E1670" s="6"/>
     </row>
     <row r="1671">
       <c r="A1671" s="6"/>
-      <c r="B1671" s="13"/>
+      <c r="B1671" s="14"/>
       <c r="C1671" s="6"/>
       <c r="D1671" s="6"/>
       <c r="E1671" s="6"/>
     </row>
     <row r="1672">
       <c r="A1672" s="6"/>
-      <c r="B1672" s="13"/>
+      <c r="B1672" s="14"/>
       <c r="C1672" s="6"/>
       <c r="D1672" s="6"/>
       <c r="E1672" s="6"/>
     </row>
     <row r="1673">
       <c r="A1673" s="6"/>
-      <c r="B1673" s="13"/>
+      <c r="B1673" s="14"/>
       <c r="C1673" s="6"/>
       <c r="D1673" s="6"/>
       <c r="E1673" s="6"/>
     </row>
     <row r="1674">
       <c r="A1674" s="6"/>
-      <c r="B1674" s="13"/>
+      <c r="B1674" s="14"/>
       <c r="C1674" s="6"/>
       <c r="D1674" s="6"/>
       <c r="E1674" s="6"/>
     </row>
     <row r="1675">
       <c r="A1675" s="6"/>
-      <c r="B1675" s="13"/>
+      <c r="B1675" s="14"/>
       <c r="C1675" s="6"/>
       <c r="D1675" s="6"/>
       <c r="E1675" s="6"/>
     </row>
     <row r="1676">
       <c r="A1676" s="6"/>
-      <c r="B1676" s="13"/>
+      <c r="B1676" s="14"/>
       <c r="C1676" s="6"/>
       <c r="D1676" s="6"/>
       <c r="E1676" s="6"/>
     </row>
     <row r="1677">
       <c r="A1677" s="6"/>
-      <c r="B1677" s="13"/>
+      <c r="B1677" s="14"/>
       <c r="C1677" s="6"/>
       <c r="D1677" s="6"/>
       <c r="E1677" s="6"/>
     </row>
     <row r="1678">
       <c r="A1678" s="6"/>
-      <c r="B1678" s="13"/>
+      <c r="B1678" s="14"/>
       <c r="C1678" s="6"/>
       <c r="D1678" s="6"/>
       <c r="E1678" s="6"/>
     </row>
     <row r="1679">
       <c r="A1679" s="6"/>
-      <c r="B1679" s="13"/>
+      <c r="B1679" s="14"/>
       <c r="C1679" s="6"/>
       <c r="D1679" s="6"/>
       <c r="E1679" s="6"/>
     </row>
     <row r="1680">
       <c r="A1680" s="6"/>
-      <c r="B1680" s="13"/>
+      <c r="B1680" s="14"/>
       <c r="C1680" s="6"/>
       <c r="D1680" s="6"/>
       <c r="E1680" s="6"/>
     </row>
     <row r="1681">
       <c r="A1681" s="6"/>
-      <c r="B1681" s="13"/>
+      <c r="B1681" s="14"/>
       <c r="C1681" s="6"/>
       <c r="D1681" s="6"/>
       <c r="E1681" s="6"/>
     </row>
     <row r="1682">
       <c r="A1682" s="6"/>
-      <c r="B1682" s="13"/>
+      <c r="B1682" s="14"/>
       <c r="C1682" s="6"/>
       <c r="D1682" s="6"/>
       <c r="E1682" s="6"/>
     </row>
     <row r="1683">
       <c r="A1683" s="6"/>
-      <c r="B1683" s="13"/>
+      <c r="B1683" s="14"/>
       <c r="C1683" s="6"/>
       <c r="D1683" s="6"/>
       <c r="E1683" s="6"/>
     </row>
     <row r="1684">
       <c r="A1684" s="6"/>
-      <c r="B1684" s="13"/>
+      <c r="B1684" s="14"/>
       <c r="C1684" s="6"/>
       <c r="D1684" s="6"/>
       <c r="E1684" s="6"/>
     </row>
     <row r="1685">
       <c r="A1685" s="6"/>
-      <c r="B1685" s="13"/>
+      <c r="B1685" s="14"/>
       <c r="C1685" s="6"/>
       <c r="D1685" s="6"/>
       <c r="E1685" s="6"/>
     </row>
     <row r="1686">
       <c r="A1686" s="6"/>
-      <c r="B1686" s="13"/>
+      <c r="B1686" s="14"/>
       <c r="C1686" s="6"/>
       <c r="D1686" s="6"/>
       <c r="E1686" s="6"/>
     </row>
     <row r="1687">
       <c r="A1687" s="6"/>
-      <c r="B1687" s="13"/>
+      <c r="B1687" s="14"/>
       <c r="C1687" s="6"/>
       <c r="D1687" s="6"/>
       <c r="E1687" s="6"/>
     </row>
     <row r="1688">
       <c r="A1688" s="6"/>
-      <c r="B1688" s="13"/>
+      <c r="B1688" s="14"/>
       <c r="C1688" s="6"/>
       <c r="D1688" s="6"/>
       <c r="E1688" s="6"/>
     </row>
     <row r="1689">
       <c r="A1689" s="6"/>
-      <c r="B1689" s="13"/>
+      <c r="B1689" s="14"/>
       <c r="C1689" s="6"/>
       <c r="D1689" s="6"/>
       <c r="E1689" s="6"/>
     </row>
     <row r="1690">
       <c r="A1690" s="6"/>
-      <c r="B1690" s="13"/>
+      <c r="B1690" s="14"/>
       <c r="C1690" s="6"/>
       <c r="D1690" s="6"/>
       <c r="E1690" s="6"/>
     </row>
     <row r="1691">
       <c r="A1691" s="6"/>
-      <c r="B1691" s="13"/>
+      <c r="B1691" s="14"/>
       <c r="C1691" s="6"/>
       <c r="D1691" s="6"/>
       <c r="E1691" s="6"/>
     </row>
     <row r="1692">
       <c r="A1692" s="6"/>
-      <c r="B1692" s="13"/>
+      <c r="B1692" s="14"/>
       <c r="C1692" s="6"/>
       <c r="D1692" s="6"/>
       <c r="E1692" s="6"/>
     </row>
     <row r="1693">
       <c r="A1693" s="6"/>
-      <c r="B1693" s="13"/>
+      <c r="B1693" s="14"/>
       <c r="C1693" s="6"/>
       <c r="D1693" s="6"/>
       <c r="E1693" s="6"/>
     </row>
     <row r="1694">
       <c r="A1694" s="6"/>
-      <c r="B1694" s="13"/>
+      <c r="B1694" s="14"/>
       <c r="C1694" s="6"/>
       <c r="D1694" s="6"/>
       <c r="E1694" s="6"/>
     </row>
     <row r="1695">
       <c r="A1695" s="6"/>
-      <c r="B1695" s="13"/>
+      <c r="B1695" s="14"/>
       <c r="C1695" s="6"/>
       <c r="D1695" s="6"/>
       <c r="E1695" s="6"/>
     </row>
     <row r="1696">
       <c r="A1696" s="6"/>
-      <c r="B1696" s="13"/>
+      <c r="B1696" s="14"/>
       <c r="C1696" s="6"/>
       <c r="D1696" s="6"/>
       <c r="E1696" s="6"/>
     </row>
     <row r="1697">
       <c r="A1697" s="6"/>
-      <c r="B1697" s="13"/>
+      <c r="B1697" s="14"/>
       <c r="C1697" s="6"/>
       <c r="D1697" s="6"/>
       <c r="E1697" s="6"/>
     </row>
     <row r="1698">
       <c r="A1698" s="6"/>
-      <c r="B1698" s="13"/>
+      <c r="B1698" s="14"/>
       <c r="C1698" s="6"/>
       <c r="D1698" s="6"/>
       <c r="E1698" s="6"/>
     </row>
     <row r="1699">
       <c r="A1699" s="6"/>
-      <c r="B1699" s="13"/>
+      <c r="B1699" s="14"/>
       <c r="C1699" s="6"/>
       <c r="D1699" s="6"/>
       <c r="E1699" s="6"/>
     </row>
     <row r="1700">
       <c r="A1700" s="6"/>
-      <c r="B1700" s="13"/>
+      <c r="B1700" s="14"/>
       <c r="C1700" s="6"/>
       <c r="D1700" s="6"/>
       <c r="E1700" s="6"/>
     </row>
     <row r="1701">
       <c r="A1701" s="6"/>
-      <c r="B1701" s="13"/>
+      <c r="B1701" s="14"/>
       <c r="C1701" s="6"/>
       <c r="D1701" s="6"/>
       <c r="E1701" s="6"/>
     </row>
     <row r="1702">
       <c r="A1702" s="6"/>
-      <c r="B1702" s="13"/>
+      <c r="B1702" s="14"/>
       <c r="C1702" s="6"/>
       <c r="D1702" s="6"/>
       <c r="E1702" s="6"/>
     </row>
     <row r="1703">
       <c r="A1703" s="6"/>
-      <c r="B1703" s="13"/>
+      <c r="B1703" s="14"/>
       <c r="C1703" s="6"/>
       <c r="D1703" s="6"/>
       <c r="E1703" s="6"/>
     </row>
     <row r="1704">
       <c r="A1704" s="6"/>
-      <c r="B1704" s="13"/>
+      <c r="B1704" s="14"/>
       <c r="C1704" s="6"/>
       <c r="D1704" s="6"/>
       <c r="E1704" s="6"/>
     </row>
     <row r="1705">
       <c r="A1705" s="6"/>
-      <c r="B1705" s="13"/>
+      <c r="B1705" s="14"/>
       <c r="C1705" s="6"/>
       <c r="D1705" s="6"/>
       <c r="E1705" s="6"/>
     </row>
     <row r="1706">
       <c r="A1706" s="6"/>
-      <c r="B1706" s="13"/>
+      <c r="B1706" s="14"/>
       <c r="C1706" s="6"/>
       <c r="D1706" s="6"/>
       <c r="E1706" s="6"/>
     </row>
     <row r="1707">
       <c r="A1707" s="6"/>
-      <c r="B1707" s="13"/>
+      <c r="B1707" s="14"/>
       <c r="C1707" s="6"/>
       <c r="D1707" s="6"/>
       <c r="E1707" s="6"/>
     </row>
     <row r="1708">
       <c r="A1708" s="6"/>
-      <c r="B1708" s="13"/>
+      <c r="B1708" s="14"/>
       <c r="C1708" s="6"/>
       <c r="D1708" s="6"/>
       <c r="E1708" s="6"/>
     </row>
     <row r="1709">
       <c r="A1709" s="6"/>
-      <c r="B1709" s="13"/>
+      <c r="B1709" s="14"/>
       <c r="C1709" s="6"/>
       <c r="D1709" s="6"/>
       <c r="E1709" s="6"/>
     </row>
     <row r="1710">
       <c r="A1710" s="6"/>
-      <c r="B1710" s="13"/>
+      <c r="B1710" s="14"/>
       <c r="C1710" s="6"/>
       <c r="D1710" s="6"/>
       <c r="E1710" s="6"/>
     </row>
     <row r="1711">
       <c r="A1711" s="6"/>
-      <c r="B1711" s="13"/>
+      <c r="B1711" s="14"/>
       <c r="C1711" s="6"/>
       <c r="D1711" s="6"/>
       <c r="E1711" s="6"/>
     </row>
     <row r="1712">
       <c r="A1712" s="6"/>
-      <c r="B1712" s="13"/>
+      <c r="B1712" s="14"/>
       <c r="C1712" s="6"/>
       <c r="D1712" s="6"/>
       <c r="E1712" s="6"/>
     </row>
     <row r="1713">
       <c r="A1713" s="6"/>
-      <c r="B1713" s="13"/>
+      <c r="B1713" s="14"/>
       <c r="C1713" s="6"/>
       <c r="D1713" s="6"/>
       <c r="E1713" s="6"/>
     </row>
     <row r="1714">
       <c r="A1714" s="6"/>
-      <c r="B1714" s="13"/>
+      <c r="B1714" s="14"/>
       <c r="C1714" s="6"/>
       <c r="D1714" s="6"/>
       <c r="E1714" s="6"/>
     </row>
     <row r="1715">
       <c r="A1715" s="6"/>
-      <c r="B1715" s="13"/>
+      <c r="B1715" s="14"/>
       <c r="C1715" s="6"/>
       <c r="D1715" s="6"/>
       <c r="E1715" s="6"/>
     </row>
     <row r="1716">
       <c r="A1716" s="6"/>
-      <c r="B1716" s="13"/>
+      <c r="B1716" s="14"/>
       <c r="C1716" s="6"/>
       <c r="D1716" s="6"/>
       <c r="E1716" s="6"/>
     </row>
     <row r="1717">
       <c r="A1717" s="6"/>
-      <c r="B1717" s="13"/>
+      <c r="B1717" s="14"/>
       <c r="C1717" s="6"/>
       <c r="D1717" s="6"/>
       <c r="E1717" s="6"/>
     </row>
     <row r="1718">
       <c r="A1718" s="6"/>
-      <c r="B1718" s="13"/>
+      <c r="B1718" s="14"/>
       <c r="C1718" s="6"/>
       <c r="D1718" s="6"/>
       <c r="E1718" s="6"/>
     </row>
     <row r="1719">
       <c r="A1719" s="6"/>
-      <c r="B1719" s="13"/>
+      <c r="B1719" s="14"/>
       <c r="C1719" s="6"/>
       <c r="D1719" s="6"/>
       <c r="E1719" s="6"/>
     </row>
     <row r="1720">
       <c r="A1720" s="6"/>
-      <c r="B1720" s="13"/>
+      <c r="B1720" s="14"/>
       <c r="C1720" s="6"/>
       <c r="D1720" s="6"/>
       <c r="E1720" s="6"/>
     </row>
     <row r="1721">
       <c r="A1721" s="6"/>
-      <c r="B1721" s="13"/>
+      <c r="B1721" s="14"/>
       <c r="C1721" s="6"/>
       <c r="D1721" s="6"/>
       <c r="E1721" s="6"/>
     </row>
     <row r="1722">
       <c r="A1722" s="6"/>
-      <c r="B1722" s="13"/>
+      <c r="B1722" s="14"/>
       <c r="C1722" s="6"/>
       <c r="D1722" s="6"/>
       <c r="E1722" s="6"/>
     </row>
     <row r="1723">
       <c r="A1723" s="6"/>
-      <c r="B1723" s="13"/>
+      <c r="B1723" s="14"/>
       <c r="C1723" s="6"/>
       <c r="D1723" s="6"/>
       <c r="E1723" s="6"/>
     </row>
     <row r="1724">
       <c r="A1724" s="6"/>
-      <c r="B1724" s="13"/>
+      <c r="B1724" s="14"/>
       <c r="C1724" s="6"/>
       <c r="D1724" s="6"/>
       <c r="E1724" s="6"/>
     </row>
     <row r="1725">
       <c r="A1725" s="6"/>
-      <c r="B1725" s="13"/>
+      <c r="B1725" s="14"/>
       <c r="C1725" s="6"/>
       <c r="D1725" s="6"/>
       <c r="E1725" s="6"/>
     </row>
     <row r="1726">
       <c r="A1726" s="6"/>
-      <c r="B1726" s="13"/>
+      <c r="B1726" s="14"/>
       <c r="C1726" s="6"/>
       <c r="D1726" s="6"/>
       <c r="E1726" s="6"/>
     </row>
     <row r="1727">
       <c r="A1727" s="6"/>
-      <c r="B1727" s="13"/>
+      <c r="B1727" s="14"/>
       <c r="C1727" s="6"/>
       <c r="D1727" s="6"/>
       <c r="E1727" s="6"/>
     </row>
     <row r="1728">
       <c r="A1728" s="6"/>
-      <c r="B1728" s="13"/>
+      <c r="B1728" s="14"/>
       <c r="C1728" s="6"/>
       <c r="D1728" s="6"/>
       <c r="E1728" s="6"/>
     </row>
     <row r="1729">
       <c r="A1729" s="6"/>
-      <c r="B1729" s="13"/>
+      <c r="B1729" s="14"/>
       <c r="C1729" s="6"/>
       <c r="D1729" s="6"/>
       <c r="E1729" s="6"/>
     </row>
     <row r="1730">
       <c r="A1730" s="6"/>
-      <c r="B1730" s="13"/>
+      <c r="B1730" s="14"/>
       <c r="C1730" s="6"/>
       <c r="D1730" s="6"/>
       <c r="E1730" s="6"/>
     </row>
     <row r="1731">
       <c r="A1731" s="6"/>
-      <c r="B1731" s="13"/>
+      <c r="B1731" s="14"/>
       <c r="C1731" s="6"/>
       <c r="D1731" s="6"/>
       <c r="E1731" s="6"/>
     </row>
     <row r="1732">
       <c r="A1732" s="6"/>
-      <c r="B1732" s="13"/>
+      <c r="B1732" s="14"/>
       <c r="C1732" s="6"/>
       <c r="D1732" s="6"/>
       <c r="E1732" s="6"/>
     </row>
     <row r="1733">
       <c r="A1733" s="6"/>
-      <c r="B1733" s="13"/>
+      <c r="B1733" s="14"/>
       <c r="C1733" s="6"/>
       <c r="D1733" s="6"/>
       <c r="E1733" s="6"/>
     </row>
     <row r="1734">
       <c r="A1734" s="6"/>
-      <c r="B1734" s="13"/>
+      <c r="B1734" s="14"/>
       <c r="C1734" s="6"/>
       <c r="D1734" s="6"/>
       <c r="E1734" s="6"/>
     </row>
     <row r="1735">
       <c r="A1735" s="6"/>
-      <c r="B1735" s="13"/>
+      <c r="B1735" s="14"/>
       <c r="C1735" s="6"/>
       <c r="D1735" s="6"/>
       <c r="E1735" s="6"/>
     </row>
     <row r="1736">
       <c r="A1736" s="6"/>
-      <c r="B1736" s="13"/>
+      <c r="B1736" s="14"/>
       <c r="C1736" s="6"/>
       <c r="D1736" s="6"/>
       <c r="E1736" s="6"/>
     </row>
     <row r="1737">
       <c r="A1737" s="6"/>
-      <c r="B1737" s="13"/>
+      <c r="B1737" s="14"/>
       <c r="C1737" s="6"/>
       <c r="D1737" s="6"/>
       <c r="E1737" s="6"/>
     </row>
     <row r="1738">
       <c r="A1738" s="6"/>
-      <c r="B1738" s="13"/>
+      <c r="B1738" s="14"/>
       <c r="C1738" s="6"/>
       <c r="D1738" s="6"/>
       <c r="E1738" s="6"/>
     </row>
     <row r="1739">
       <c r="A1739" s="6"/>
-      <c r="B1739" s="13"/>
+      <c r="B1739" s="14"/>
       <c r="C1739" s="6"/>
       <c r="D1739" s="6"/>
       <c r="E1739" s="6"/>
     </row>
     <row r="1740">
       <c r="A1740" s="6"/>
-      <c r="B1740" s="13"/>
+      <c r="B1740" s="14"/>
       <c r="C1740" s="6"/>
       <c r="D1740" s="6"/>
       <c r="E1740" s="6"/>
     </row>
     <row r="1741">
       <c r="A1741" s="6"/>
-      <c r="B1741" s="13"/>
+      <c r="B1741" s="14"/>
       <c r="C1741" s="6"/>
       <c r="D1741" s="6"/>
       <c r="E1741" s="6"/>
     </row>
     <row r="1742">
       <c r="A1742" s="6"/>
-      <c r="B1742" s="13"/>
+      <c r="B1742" s="14"/>
       <c r="C1742" s="6"/>
       <c r="D1742" s="6"/>
       <c r="E1742" s="6"/>
     </row>
     <row r="1743">
       <c r="A1743" s="6"/>
-      <c r="B1743" s="13"/>
+      <c r="B1743" s="14"/>
       <c r="C1743" s="6"/>
       <c r="D1743" s="6"/>
       <c r="E1743" s="6"/>
     </row>
     <row r="1744">
       <c r="A1744" s="6"/>
-      <c r="B1744" s="13"/>
+      <c r="B1744" s="14"/>
       <c r="C1744" s="6"/>
       <c r="D1744" s="6"/>
       <c r="E1744" s="6"/>
     </row>
     <row r="1745">
       <c r="A1745" s="6"/>
-      <c r="B1745" s="13"/>
+      <c r="B1745" s="14"/>
       <c r="C1745" s="6"/>
       <c r="D1745" s="6"/>
       <c r="E1745" s="6"/>
     </row>
     <row r="1746">
       <c r="A1746" s="6"/>
-      <c r="B1746" s="13"/>
+      <c r="B1746" s="14"/>
       <c r="C1746" s="6"/>
       <c r="D1746" s="6"/>
       <c r="E1746" s="6"/>
     </row>
     <row r="1747">
       <c r="A1747" s="6"/>
-      <c r="B1747" s="13"/>
+      <c r="B1747" s="14"/>
       <c r="C1747" s="6"/>
       <c r="D1747" s="6"/>
       <c r="E1747" s="6"/>
     </row>
     <row r="1748">
       <c r="A1748" s="6"/>
-      <c r="B1748" s="13"/>
+      <c r="B1748" s="14"/>
       <c r="C1748" s="6"/>
       <c r="D1748" s="6"/>
       <c r="E1748" s="6"/>
     </row>
     <row r="1749">
       <c r="A1749" s="6"/>
-      <c r="B1749" s="13"/>
+      <c r="B1749" s="14"/>
       <c r="C1749" s="6"/>
       <c r="D1749" s="6"/>
       <c r="E1749" s="6"/>
     </row>
     <row r="1750">
       <c r="A1750" s="6"/>
-      <c r="B1750" s="13"/>
+      <c r="B1750" s="14"/>
       <c r="C1750" s="6"/>
       <c r="D1750" s="6"/>
       <c r="E1750" s="6"/>
     </row>
     <row r="1751">
       <c r="A1751" s="6"/>
-      <c r="B1751" s="13"/>
+      <c r="B1751" s="14"/>
       <c r="C1751" s="6"/>
       <c r="D1751" s="6"/>
       <c r="E1751" s="6"/>
     </row>
     <row r="1752">
       <c r="A1752" s="6"/>
-      <c r="B1752" s="13"/>
+      <c r="B1752" s="14"/>
       <c r="C1752" s="6"/>
       <c r="D1752" s="6"/>
       <c r="E1752" s="6"/>
     </row>
     <row r="1753">
       <c r="A1753" s="6"/>
-      <c r="B1753" s="13"/>
+      <c r="B1753" s="14"/>
       <c r="C1753" s="6"/>
       <c r="D1753" s="6"/>
       <c r="E1753" s="6"/>
     </row>
     <row r="1754">
       <c r="A1754" s="6"/>
-      <c r="B1754" s="13"/>
+      <c r="B1754" s="14"/>
       <c r="C1754" s="6"/>
       <c r="D1754" s="6"/>
       <c r="E1754" s="6"/>
     </row>
     <row r="1755">
       <c r="A1755" s="6"/>
-      <c r="B1755" s="13"/>
+      <c r="B1755" s="14"/>
       <c r="C1755" s="6"/>
       <c r="D1755" s="6"/>
       <c r="E1755" s="6"/>
     </row>
     <row r="1756">
       <c r="A1756" s="6"/>
-      <c r="B1756" s="13"/>
+      <c r="B1756" s="14"/>
       <c r="C1756" s="6"/>
       <c r="D1756" s="6"/>
       <c r="E1756" s="6"/>
     </row>
     <row r="1757">
       <c r="A1757" s="6"/>
-      <c r="B1757" s="13"/>
+      <c r="B1757" s="14"/>
       <c r="C1757" s="6"/>
       <c r="D1757" s="6"/>
       <c r="E1757" s="6"/>
     </row>
     <row r="1758">
       <c r="A1758" s="6"/>
-      <c r="B1758" s="13"/>
+      <c r="B1758" s="14"/>
       <c r="C1758" s="6"/>
       <c r="D1758" s="6"/>
       <c r="E1758" s="6"/>
     </row>
     <row r="1759">
       <c r="A1759" s="6"/>
-      <c r="B1759" s="13"/>
+      <c r="B1759" s="14"/>
       <c r="C1759" s="6"/>
       <c r="D1759" s="6"/>
       <c r="E1759" s="6"/>
     </row>
     <row r="1760">
       <c r="A1760" s="6"/>
-      <c r="B1760" s="13"/>
+      <c r="B1760" s="14"/>
       <c r="C1760" s="6"/>
       <c r="D1760" s="6"/>
       <c r="E1760" s="6"/>
     </row>
     <row r="1761">
       <c r="A1761" s="6"/>
-      <c r="B1761" s="13"/>
+      <c r="B1761" s="14"/>
       <c r="C1761" s="6"/>
       <c r="D1761" s="6"/>
       <c r="E1761" s="6"/>
     </row>
     <row r="1762">
       <c r="A1762" s="6"/>
-      <c r="B1762" s="13"/>
+      <c r="B1762" s="14"/>
       <c r="C1762" s="6"/>
       <c r="D1762" s="6"/>
       <c r="E1762" s="6"/>
     </row>
     <row r="1763">
       <c r="A1763" s="6"/>
-      <c r="B1763" s="13"/>
+      <c r="B1763" s="14"/>
       <c r="C1763" s="6"/>
       <c r="D1763" s="6"/>
       <c r="E1763" s="6"/>
     </row>
     <row r="1764">
       <c r="A1764" s="6"/>
-      <c r="B1764" s="13"/>
+      <c r="B1764" s="14"/>
       <c r="C1764" s="6"/>
       <c r="D1764" s="6"/>
       <c r="E1764" s="6"/>
     </row>
     <row r="1765">
       <c r="A1765" s="6"/>
-      <c r="B1765" s="13"/>
+      <c r="B1765" s="14"/>
       <c r="C1765" s="6"/>
       <c r="D1765" s="6"/>
       <c r="E1765" s="6"/>
     </row>
     <row r="1766">
       <c r="A1766" s="6"/>
-      <c r="B1766" s="13"/>
+      <c r="B1766" s="14"/>
       <c r="C1766" s="6"/>
       <c r="D1766" s="6"/>
       <c r="E1766" s="6"/>
     </row>
     <row r="1767">
       <c r="A1767" s="6"/>
-      <c r="B1767" s="13"/>
+      <c r="B1767" s="14"/>
       <c r="C1767" s="6"/>
       <c r="D1767" s="6"/>
       <c r="E1767" s="6"/>
     </row>
     <row r="1768">
       <c r="A1768" s="6"/>
-      <c r="B1768" s="13"/>
+      <c r="B1768" s="14"/>
       <c r="C1768" s="6"/>
       <c r="D1768" s="6"/>
       <c r="E1768" s="6"/>
     </row>
     <row r="1769">
       <c r="A1769" s="6"/>
-      <c r="B1769" s="13"/>
+      <c r="B1769" s="14"/>
       <c r="C1769" s="6"/>
       <c r="D1769" s="6"/>
       <c r="E1769" s="6"/>
     </row>
     <row r="1770">
       <c r="A1770" s="6"/>
-      <c r="B1770" s="13"/>
+      <c r="B1770" s="14"/>
       <c r="C1770" s="6"/>
       <c r="D1770" s="6"/>
       <c r="E1770" s="6"/>
     </row>
     <row r="1771">
       <c r="A1771" s="6"/>
-      <c r="B1771" s="13"/>
+      <c r="B1771" s="14"/>
       <c r="C1771" s="6"/>
       <c r="D1771" s="6"/>
       <c r="E1771" s="6"/>
     </row>
     <row r="1772">
       <c r="A1772" s="6"/>
-      <c r="B1772" s="13"/>
+      <c r="B1772" s="14"/>
       <c r="C1772" s="6"/>
       <c r="D1772" s="6"/>
       <c r="E1772" s="6"/>
     </row>
     <row r="1773">
       <c r="A1773" s="6"/>
-      <c r="B1773" s="13"/>
+      <c r="B1773" s="14"/>
       <c r="C1773" s="6"/>
       <c r="D1773" s="6"/>
       <c r="E1773" s="6"/>
     </row>
     <row r="1774">
       <c r="A1774" s="6"/>
-      <c r="B1774" s="13"/>
+      <c r="B1774" s="14"/>
       <c r="C1774" s="6"/>
       <c r="D1774" s="6"/>
       <c r="E1774" s="6"/>
     </row>
     <row r="1775">
       <c r="A1775" s="6"/>
-      <c r="B1775" s="13"/>
+      <c r="B1775" s="14"/>
       <c r="C1775" s="6"/>
       <c r="D1775" s="6"/>
       <c r="E1775" s="6"/>
     </row>
     <row r="1776">
       <c r="A1776" s="6"/>
-      <c r="B1776" s="13"/>
+      <c r="B1776" s="14"/>
       <c r="C1776" s="6"/>
       <c r="D1776" s="6"/>
       <c r="E1776" s="6"/>
     </row>
     <row r="1777">
       <c r="A1777" s="6"/>
-      <c r="B1777" s="13"/>
+      <c r="B1777" s="14"/>
       <c r="C1777" s="6"/>
       <c r="D1777" s="6"/>
       <c r="E1777" s="6"/>
     </row>
     <row r="1778">
       <c r="A1778" s="6"/>
-      <c r="B1778" s="13"/>
+      <c r="B1778" s="14"/>
       <c r="C1778" s="6"/>
       <c r="D1778" s="6"/>
       <c r="E1778" s="6"/>
     </row>
     <row r="1779">
       <c r="A1779" s="6"/>
-      <c r="B1779" s="13"/>
+      <c r="B1779" s="14"/>
       <c r="C1779" s="6"/>
       <c r="D1779" s="6"/>
       <c r="E1779" s="6"/>
     </row>
     <row r="1780">
       <c r="A1780" s="6"/>
-      <c r="B1780" s="13"/>
+      <c r="B1780" s="14"/>
       <c r="C1780" s="6"/>
       <c r="D1780" s="6"/>
       <c r="E1780" s="6"/>
     </row>
     <row r="1781">
       <c r="A1781" s="6"/>
-      <c r="B1781" s="13"/>
+      <c r="B1781" s="14"/>
       <c r="C1781" s="6"/>
       <c r="D1781" s="6"/>
       <c r="E1781" s="6"/>
     </row>
     <row r="1782">
       <c r="A1782" s="6"/>
-      <c r="B1782" s="13"/>
+      <c r="B1782" s="14"/>
       <c r="C1782" s="6"/>
       <c r="D1782" s="6"/>
       <c r="E1782" s="6"/>
     </row>
     <row r="1783">
       <c r="A1783" s="6"/>
-      <c r="B1783" s="13"/>
+      <c r="B1783" s="14"/>
       <c r="C1783" s="6"/>
       <c r="D1783" s="6"/>
       <c r="E1783" s="6"/>
     </row>
     <row r="1784">
       <c r="A1784" s="6"/>
-      <c r="B1784" s="13"/>
+      <c r="B1784" s="14"/>
       <c r="C1784" s="6"/>
       <c r="D1784" s="6"/>
       <c r="E1784" s="6"/>
     </row>
     <row r="1785">
       <c r="A1785" s="6"/>
-      <c r="B1785" s="13"/>
+      <c r="B1785" s="14"/>
       <c r="C1785" s="6"/>
       <c r="D1785" s="6"/>
       <c r="E1785" s="6"/>
     </row>
     <row r="1786">
       <c r="A1786" s="6"/>
-      <c r="B1786" s="13"/>
+      <c r="B1786" s="14"/>
       <c r="C1786" s="6"/>
       <c r="D1786" s="6"/>
       <c r="E1786" s="6"/>
     </row>
     <row r="1787">
       <c r="A1787" s="6"/>
-      <c r="B1787" s="13"/>
+      <c r="B1787" s="14"/>
       <c r="C1787" s="6"/>
       <c r="D1787" s="6"/>
       <c r="E1787" s="6"/>
     </row>
     <row r="1788">
       <c r="A1788" s="6"/>
-      <c r="B1788" s="13"/>
+      <c r="B1788" s="14"/>
       <c r="C1788" s="6"/>
       <c r="D1788" s="6"/>
       <c r="E1788" s="6"/>
     </row>
     <row r="1789">
       <c r="A1789" s="6"/>
-      <c r="B1789" s="13"/>
+      <c r="B1789" s="14"/>
       <c r="C1789" s="6"/>
       <c r="D1789" s="6"/>
       <c r="E1789" s="6"/>
     </row>
     <row r="1790">
       <c r="A1790" s="6"/>
-      <c r="B1790" s="13"/>
+      <c r="B1790" s="14"/>
       <c r="C1790" s="6"/>
       <c r="D1790" s="6"/>
       <c r="E1790" s="6"/>
     </row>
     <row r="1791">
       <c r="A1791" s="6"/>
-      <c r="B1791" s="13"/>
+      <c r="B1791" s="14"/>
       <c r="C1791" s="6"/>
       <c r="D1791" s="6"/>
       <c r="E1791" s="6"/>
     </row>
     <row r="1792">
       <c r="A1792" s="6"/>
-      <c r="B1792" s="13"/>
+      <c r="B1792" s="14"/>
       <c r="C1792" s="6"/>
       <c r="D1792" s="6"/>
       <c r="E1792" s="6"/>
     </row>
     <row r="1793">
       <c r="A1793" s="6"/>
-      <c r="B1793" s="13"/>
+      <c r="B1793" s="14"/>
       <c r="C1793" s="6"/>
       <c r="D1793" s="6"/>
       <c r="E1793" s="6"/>
     </row>
     <row r="1794">
       <c r="A1794" s="6"/>
-      <c r="B1794" s="13"/>
+      <c r="B1794" s="14"/>
       <c r="C1794" s="6"/>
       <c r="D1794" s="6"/>
       <c r="E1794" s="6"/>
     </row>
     <row r="1795">
       <c r="A1795" s="6"/>
-      <c r="B1795" s="13"/>
+      <c r="B1795" s="14"/>
       <c r="C1795" s="6"/>
       <c r="D1795" s="6"/>
       <c r="E1795" s="6"/>
     </row>
     <row r="1796">
       <c r="A1796" s="6"/>
-      <c r="B1796" s="13"/>
+      <c r="B1796" s="14"/>
       <c r="C1796" s="6"/>
       <c r="D1796" s="6"/>
       <c r="E1796" s="6"/>
     </row>
     <row r="1797">
       <c r="A1797" s="6"/>
-      <c r="B1797" s="13"/>
+      <c r="B1797" s="14"/>
       <c r="C1797" s="6"/>
       <c r="D1797" s="6"/>
       <c r="E1797" s="6"/>
     </row>
     <row r="1798">
       <c r="A1798" s="6"/>
-      <c r="B1798" s="13"/>
+      <c r="B1798" s="14"/>
       <c r="C1798" s="6"/>
       <c r="D1798" s="6"/>
       <c r="E1798" s="6"/>
     </row>
     <row r="1799">
       <c r="A1799" s="6"/>
-      <c r="B1799" s="13"/>
+      <c r="B1799" s="14"/>
       <c r="C1799" s="6"/>
       <c r="D1799" s="6"/>
       <c r="E1799" s="6"/>
     </row>
     <row r="1800">
       <c r="A1800" s="6"/>
-      <c r="B1800" s="13"/>
+      <c r="B1800" s="14"/>
       <c r="C1800" s="6"/>
       <c r="D1800" s="6"/>
       <c r="E1800" s="6"/>
     </row>
     <row r="1801">
       <c r="A1801" s="6"/>
-      <c r="B1801" s="13"/>
+      <c r="B1801" s="14"/>
       <c r="C1801" s="6"/>
       <c r="D1801" s="6"/>
       <c r="E1801" s="6"/>
     </row>
     <row r="1802">
       <c r="A1802" s="6"/>
-      <c r="B1802" s="13"/>
+      <c r="B1802" s="14"/>
       <c r="C1802" s="6"/>
       <c r="D1802" s="6"/>
       <c r="E1802" s="6"/>
     </row>
     <row r="1803">
       <c r="A1803" s="6"/>
-      <c r="B1803" s="13"/>
+      <c r="B1803" s="14"/>
       <c r="C1803" s="6"/>
       <c r="D1803" s="6"/>
       <c r="E1803" s="6"/>
     </row>
     <row r="1804">
       <c r="A1804" s="6"/>
-      <c r="B1804" s="13"/>
+      <c r="B1804" s="14"/>
       <c r="C1804" s="6"/>
       <c r="D1804" s="6"/>
       <c r="E1804" s="6"/>
     </row>
     <row r="1805">
       <c r="A1805" s="6"/>
-      <c r="B1805" s="13"/>
+      <c r="B1805" s="14"/>
       <c r="C1805" s="6"/>
       <c r="D1805" s="6"/>
       <c r="E1805" s="6"/>
     </row>
     <row r="1806">
       <c r="A1806" s="6"/>
-      <c r="B1806" s="13"/>
+      <c r="B1806" s="14"/>
       <c r="C1806" s="6"/>
       <c r="D1806" s="6"/>
       <c r="E1806" s="6"/>
     </row>
     <row r="1807">
       <c r="A1807" s="6"/>
-      <c r="B1807" s="13"/>
+      <c r="B1807" s="14"/>
       <c r="C1807" s="6"/>
       <c r="D1807" s="6"/>
       <c r="E1807" s="6"/>
     </row>
     <row r="1808">
       <c r="A1808" s="6"/>
-      <c r="B1808" s="13"/>
+      <c r="B1808" s="14"/>
       <c r="C1808" s="6"/>
       <c r="D1808" s="6"/>
       <c r="E1808" s="6"/>
     </row>
     <row r="1809">
       <c r="A1809" s="6"/>
-      <c r="B1809" s="13"/>
+      <c r="B1809" s="14"/>
       <c r="C1809" s="6"/>
       <c r="D1809" s="6"/>
       <c r="E1809" s="6"/>
     </row>
     <row r="1810">
       <c r="A1810" s="6"/>
-      <c r="B1810" s="13"/>
+      <c r="B1810" s="14"/>
       <c r="C1810" s="6"/>
       <c r="D1810" s="6"/>
       <c r="E1810" s="6"/>
     </row>
     <row r="1811">
       <c r="A1811" s="6"/>
-      <c r="B1811" s="13"/>
+      <c r="B1811" s="14"/>
       <c r="C1811" s="6"/>
       <c r="D1811" s="6"/>
       <c r="E1811" s="6"/>
     </row>
     <row r="1812">
       <c r="A1812" s="6"/>
-      <c r="B1812" s="13"/>
+      <c r="B1812" s="14"/>
       <c r="C1812" s="6"/>
       <c r="D1812" s="6"/>
       <c r="E1812" s="6"/>
     </row>
     <row r="1813">
       <c r="A1813" s="6"/>
-      <c r="B1813" s="13"/>
+      <c r="B1813" s="14"/>
       <c r="C1813" s="6"/>
       <c r="D1813" s="6"/>
       <c r="E1813" s="6"/>
     </row>
     <row r="1814">
       <c r="A1814" s="6"/>
-      <c r="B1814" s="13"/>
+      <c r="B1814" s="14"/>
       <c r="C1814" s="6"/>
       <c r="D1814" s="6"/>
       <c r="E1814" s="6"/>
     </row>
     <row r="1815">
       <c r="A1815" s="6"/>
-      <c r="B1815" s="13"/>
+      <c r="B1815" s="14"/>
       <c r="C1815" s="6"/>
       <c r="D1815" s="6"/>
       <c r="E1815" s="6"/>
     </row>
     <row r="1816">
       <c r="A1816" s="6"/>
-      <c r="B1816" s="13"/>
+      <c r="B1816" s="14"/>
       <c r="C1816" s="6"/>
       <c r="D1816" s="6"/>
       <c r="E1816" s="6"/>
     </row>
     <row r="1817">
       <c r="A1817" s="6"/>
-      <c r="B1817" s="13"/>
+      <c r="B1817" s="14"/>
       <c r="C1817" s="6"/>
       <c r="D1817" s="6"/>
       <c r="E1817" s="6"/>
     </row>
     <row r="1818">
       <c r="A1818" s="6"/>
-      <c r="B1818" s="13"/>
+      <c r="B1818" s="14"/>
       <c r="C1818" s="6"/>
       <c r="D1818" s="6"/>
       <c r="E1818" s="6"/>
     </row>
     <row r="1819">
       <c r="A1819" s="6"/>
-      <c r="B1819" s="13"/>
+      <c r="B1819" s="14"/>
       <c r="C1819" s="6"/>
       <c r="D1819" s="6"/>
       <c r="E1819" s="6"/>
     </row>
     <row r="1820">
       <c r="A1820" s="6"/>
-      <c r="B1820" s="13"/>
+      <c r="B1820" s="14"/>
       <c r="C1820" s="6"/>
       <c r="D1820" s="6"/>
       <c r="E1820" s="6"/>
     </row>
     <row r="1821">
       <c r="A1821" s="6"/>
-      <c r="B1821" s="13"/>
+      <c r="B1821" s="14"/>
       <c r="C1821" s="6"/>
       <c r="D1821" s="6"/>
       <c r="E1821" s="6"/>
     </row>
     <row r="1822">
       <c r="A1822" s="6"/>
-      <c r="B1822" s="13"/>
+      <c r="B1822" s="14"/>
       <c r="C1822" s="6"/>
       <c r="D1822" s="6"/>
       <c r="E1822" s="6"/>
     </row>
     <row r="1823">
       <c r="A1823" s="6"/>
-      <c r="B1823" s="13"/>
+      <c r="B1823" s="14"/>
       <c r="C1823" s="6"/>
       <c r="D1823" s="6"/>
       <c r="E1823" s="6"/>
     </row>
     <row r="1824">
       <c r="A1824" s="6"/>
-      <c r="B1824" s="13"/>
+      <c r="B1824" s="14"/>
       <c r="C1824" s="6"/>
       <c r="D1824" s="6"/>
       <c r="E1824" s="6"/>
     </row>
     <row r="1825">
       <c r="A1825" s="6"/>
-      <c r="B1825" s="13"/>
+      <c r="B1825" s="14"/>
       <c r="C1825" s="6"/>
       <c r="D1825" s="6"/>
       <c r="E1825" s="6"/>
     </row>
     <row r="1826">
       <c r="A1826" s="6"/>
-      <c r="B1826" s="13"/>
+      <c r="B1826" s="14"/>
       <c r="C1826" s="6"/>
       <c r="D1826" s="6"/>
       <c r="E1826" s="6"/>
     </row>
     <row r="1827">
       <c r="A1827" s="6"/>
-      <c r="B1827" s="13"/>
+      <c r="B1827" s="14"/>
       <c r="C1827" s="6"/>
       <c r="D1827" s="6"/>
       <c r="E1827" s="6"/>
     </row>
     <row r="1828">
       <c r="A1828" s="6"/>
-      <c r="B1828" s="13"/>
+      <c r="B1828" s="14"/>
       <c r="C1828" s="6"/>
       <c r="D1828" s="6"/>
       <c r="E1828" s="6"/>
     </row>
     <row r="1829">
       <c r="A1829" s="6"/>
-      <c r="B1829" s="13"/>
+      <c r="B1829" s="14"/>
       <c r="C1829" s="6"/>
       <c r="D1829" s="6"/>
       <c r="E1829" s="6"/>
     </row>
     <row r="1830">
       <c r="A1830" s="6"/>
-      <c r="B1830" s="13"/>
+      <c r="B1830" s="14"/>
       <c r="C1830" s="6"/>
       <c r="D1830" s="6"/>
       <c r="E1830" s="6"/>
     </row>
     <row r="1831">
       <c r="A1831" s="6"/>
-      <c r="B1831" s="13"/>
+      <c r="B1831" s="14"/>
       <c r="C1831" s="6"/>
       <c r="D1831" s="6"/>
       <c r="E1831" s="6"/>
     </row>
     <row r="1832">
       <c r="A1832" s="6"/>
-      <c r="B1832" s="13"/>
+      <c r="B1832" s="14"/>
       <c r="C1832" s="6"/>
       <c r="D1832" s="6"/>
       <c r="E1832" s="6"/>
     </row>
     <row r="1833">
       <c r="A1833" s="6"/>
-      <c r="B1833" s="13"/>
+      <c r="B1833" s="14"/>
       <c r="C1833" s="6"/>
       <c r="D1833" s="6"/>
       <c r="E1833" s="6"/>
     </row>
     <row r="1834">
       <c r="A1834" s="6"/>
-      <c r="B1834" s="13"/>
+      <c r="B1834" s="14"/>
       <c r="C1834" s="6"/>
       <c r="D1834" s="6"/>
       <c r="E1834" s="6"/>
     </row>
     <row r="1835">
       <c r="A1835" s="6"/>
-      <c r="B1835" s="13"/>
+      <c r="B1835" s="14"/>
       <c r="C1835" s="6"/>
       <c r="D1835" s="6"/>
       <c r="E1835" s="6"/>
     </row>
     <row r="1836">
       <c r="A1836" s="6"/>
-      <c r="B1836" s="13"/>
+      <c r="B1836" s="14"/>
       <c r="C1836" s="6"/>
       <c r="D1836" s="6"/>
       <c r="E1836" s="6"/>
     </row>
     <row r="1837">
       <c r="A1837" s="6"/>
-      <c r="B1837" s="13"/>
+      <c r="B1837" s="14"/>
       <c r="C1837" s="6"/>
       <c r="D1837" s="6"/>
       <c r="E1837" s="6"/>
     </row>
     <row r="1838">
       <c r="A1838" s="6"/>
-      <c r="B1838" s="13"/>
+      <c r="B1838" s="14"/>
       <c r="C1838" s="6"/>
       <c r="D1838" s="6"/>
       <c r="E1838" s="6"/>
     </row>
     <row r="1839">
       <c r="A1839" s="6"/>
-      <c r="B1839" s="13"/>
+      <c r="B1839" s="14"/>
       <c r="C1839" s="6"/>
       <c r="D1839" s="6"/>
       <c r="E1839" s="6"/>
     </row>
     <row r="1840">
       <c r="A1840" s="6"/>
-      <c r="B1840" s="13"/>
+      <c r="B1840" s="14"/>
       <c r="C1840" s="6"/>
       <c r="D1840" s="6"/>
       <c r="E1840" s="6"/>
     </row>
     <row r="1841">
       <c r="A1841" s="6"/>
-      <c r="B1841" s="13"/>
+      <c r="B1841" s="14"/>
       <c r="C1841" s="6"/>
       <c r="D1841" s="6"/>
       <c r="E1841" s="6"/>
     </row>
     <row r="1842">
       <c r="A1842" s="6"/>
-      <c r="B1842" s="13"/>
+      <c r="B1842" s="14"/>
       <c r="C1842" s="6"/>
       <c r="D1842" s="6"/>
       <c r="E1842" s="6"/>
     </row>
     <row r="1843">
       <c r="A1843" s="6"/>
-      <c r="B1843" s="13"/>
+      <c r="B1843" s="14"/>
       <c r="C1843" s="6"/>
       <c r="D1843" s="6"/>
       <c r="E1843" s="6"/>
     </row>
     <row r="1844">
       <c r="A1844" s="6"/>
-      <c r="B1844" s="13"/>
+      <c r="B1844" s="14"/>
       <c r="C1844" s="6"/>
       <c r="D1844" s="6"/>
       <c r="E1844" s="6"/>
     </row>
     <row r="1845">
       <c r="A1845" s="6"/>
-      <c r="B1845" s="13"/>
+      <c r="B1845" s="14"/>
       <c r="C1845" s="6"/>
       <c r="D1845" s="6"/>
       <c r="E1845" s="6"/>
     </row>
     <row r="1846">
       <c r="A1846" s="6"/>
-      <c r="B1846" s="13"/>
+      <c r="B1846" s="14"/>
       <c r="C1846" s="6"/>
       <c r="D1846" s="6"/>
       <c r="E1846" s="6"/>
     </row>
     <row r="1847">
       <c r="A1847" s="6"/>
-      <c r="B1847" s="13"/>
+      <c r="B1847" s="14"/>
       <c r="C1847" s="6"/>
       <c r="D1847" s="6"/>
       <c r="E1847" s="6"/>
     </row>
     <row r="1848">
       <c r="A1848" s="6"/>
-      <c r="B1848" s="13"/>
+      <c r="B1848" s="14"/>
       <c r="C1848" s="6"/>
       <c r="D1848" s="6"/>
       <c r="E1848" s="6"/>
     </row>
     <row r="1849">
       <c r="A1849" s="6"/>
-      <c r="B1849" s="13"/>
+      <c r="B1849" s="14"/>
       <c r="C1849" s="6"/>
       <c r="D1849" s="6"/>
       <c r="E1849" s="6"/>
     </row>
     <row r="1850">
       <c r="A1850" s="6"/>
-      <c r="B1850" s="13"/>
+      <c r="B1850" s="14"/>
       <c r="C1850" s="6"/>
       <c r="D1850" s="6"/>
       <c r="E1850" s="6"/>
     </row>
     <row r="1851">
       <c r="A1851" s="6"/>
-      <c r="B1851" s="13"/>
+      <c r="B1851" s="14"/>
       <c r="C1851" s="6"/>
       <c r="D1851" s="6"/>
       <c r="E1851" s="6"/>
     </row>
     <row r="1852">
       <c r="A1852" s="6"/>
-      <c r="B1852" s="13"/>
+      <c r="B1852" s="14"/>
       <c r="C1852" s="6"/>
       <c r="D1852" s="6"/>
       <c r="E1852" s="6"/>
     </row>
     <row r="1853">
       <c r="A1853" s="6"/>
-      <c r="B1853" s="13"/>
+      <c r="B1853" s="14"/>
       <c r="C1853" s="6"/>
       <c r="D1853" s="6"/>
       <c r="E1853" s="6"/>
     </row>
     <row r="1854">
       <c r="A1854" s="6"/>
-      <c r="B1854" s="13"/>
+      <c r="B1854" s="14"/>
       <c r="C1854" s="6"/>
       <c r="D1854" s="6"/>
       <c r="E1854" s="6"/>
     </row>
     <row r="1855">
       <c r="A1855" s="6"/>
-      <c r="B1855" s="13"/>
+      <c r="B1855" s="14"/>
       <c r="C1855" s="6"/>
       <c r="D1855" s="6"/>
       <c r="E1855" s="6"/>
     </row>
     <row r="1856">
       <c r="A1856" s="6"/>
-      <c r="B1856" s="13"/>
+      <c r="B1856" s="14"/>
       <c r="C1856" s="6"/>
       <c r="D1856" s="6"/>
       <c r="E1856" s="6"/>
     </row>
     <row r="1857">
       <c r="A1857" s="6"/>
-      <c r="B1857" s="13"/>
+      <c r="B1857" s="14"/>
       <c r="C1857" s="6"/>
       <c r="D1857" s="6"/>
       <c r="E1857" s="6"/>
     </row>
     <row r="1858">
       <c r="A1858" s="6"/>
-      <c r="B1858" s="13"/>
+      <c r="B1858" s="14"/>
       <c r="C1858" s="6"/>
       <c r="D1858" s="6"/>
       <c r="E1858" s="6"/>
     </row>
     <row r="1859">
       <c r="A1859" s="6"/>
-      <c r="B1859" s="13"/>
+      <c r="B1859" s="14"/>
       <c r="C1859" s="6"/>
       <c r="D1859" s="6"/>
       <c r="E1859" s="6"/>
     </row>
     <row r="1860">
       <c r="A1860" s="6"/>
-      <c r="B1860" s="13"/>
+      <c r="B1860" s="14"/>
       <c r="C1860" s="6"/>
       <c r="D1860" s="6"/>
       <c r="E1860" s="6"/>
     </row>
     <row r="1861">
       <c r="A1861" s="6"/>
-      <c r="B1861" s="13"/>
+      <c r="B1861" s="14"/>
       <c r="C1861" s="6"/>
       <c r="D1861" s="6"/>
       <c r="E1861" s="6"/>
     </row>
     <row r="1862">
       <c r="A1862" s="6"/>
-      <c r="B1862" s="13"/>
+      <c r="B1862" s="14"/>
       <c r="C1862" s="6"/>
       <c r="D1862" s="6"/>
       <c r="E1862" s="6"/>
     </row>
     <row r="1863">
       <c r="A1863" s="6"/>
-      <c r="B1863" s="13"/>
+      <c r="B1863" s="14"/>
       <c r="C1863" s="6"/>
       <c r="D1863" s="6"/>
       <c r="E1863" s="6"/>
     </row>
     <row r="1864">
       <c r="A1864" s="6"/>
-      <c r="B1864" s="13"/>
+      <c r="B1864" s="14"/>
       <c r="C1864" s="6"/>
       <c r="D1864" s="6"/>
       <c r="E1864" s="6"/>
     </row>
     <row r="1865">
       <c r="A1865" s="6"/>
-      <c r="B1865" s="13"/>
+      <c r="B1865" s="14"/>
       <c r="C1865" s="6"/>
       <c r="D1865" s="6"/>
       <c r="E1865" s="6"/>
     </row>
     <row r="1866">
       <c r="A1866" s="6"/>
-      <c r="B1866" s="13"/>
+      <c r="B1866" s="14"/>
       <c r="C1866" s="6"/>
       <c r="D1866" s="6"/>
       <c r="E1866" s="6"/>
     </row>
     <row r="1867">
       <c r="A1867" s="6"/>
-      <c r="B1867" s="13"/>
+      <c r="B1867" s="14"/>
       <c r="C1867" s="6"/>
       <c r="D1867" s="6"/>
       <c r="E1867" s="6"/>
     </row>
     <row r="1868">
       <c r="A1868" s="6"/>
-      <c r="B1868" s="13"/>
+      <c r="B1868" s="14"/>
       <c r="C1868" s="6"/>
       <c r="D1868" s="6"/>
       <c r="E1868" s="6"/>
     </row>
     <row r="1869">
       <c r="A1869" s="6"/>
-      <c r="B1869" s="13"/>
+      <c r="B1869" s="14"/>
       <c r="C1869" s="6"/>
       <c r="D1869" s="6"/>
       <c r="E1869" s="6"/>
     </row>
     <row r="1870">
       <c r="A1870" s="6"/>
-      <c r="B1870" s="13"/>
+      <c r="B1870" s="14"/>
       <c r="C1870" s="6"/>
       <c r="D1870" s="6"/>
       <c r="E1870" s="6"/>
     </row>
     <row r="1871">
       <c r="A1871" s="6"/>
-      <c r="B1871" s="13"/>
+      <c r="B1871" s="14"/>
       <c r="C1871" s="6"/>
       <c r="D1871" s="6"/>
       <c r="E1871" s="6"/>
     </row>
     <row r="1872">
       <c r="A1872" s="6"/>
-      <c r="B1872" s="13"/>
+      <c r="B1872" s="14"/>
       <c r="C1872" s="6"/>
       <c r="D1872" s="6"/>
       <c r="E1872" s="6"/>
     </row>
     <row r="1873">
       <c r="A1873" s="6"/>
-      <c r="B1873" s="13"/>
+      <c r="B1873" s="14"/>
       <c r="C1873" s="6"/>
       <c r="D1873" s="6"/>
       <c r="E1873" s="6"/>
     </row>
     <row r="1874">
       <c r="A1874" s="6"/>
-      <c r="B1874" s="13"/>
+      <c r="B1874" s="14"/>
       <c r="C1874" s="6"/>
       <c r="D1874" s="6"/>
       <c r="E1874" s="6"/>
     </row>
     <row r="1875">
       <c r="A1875" s="6"/>
-      <c r="B1875" s="13"/>
+      <c r="B1875" s="14"/>
       <c r="C1875" s="6"/>
       <c r="D1875" s="6"/>
       <c r="E1875" s="6"/>
     </row>
     <row r="1876">
       <c r="A1876" s="6"/>
-      <c r="B1876" s="13"/>
+      <c r="B1876" s="14"/>
       <c r="C1876" s="6"/>
       <c r="D1876" s="6"/>
       <c r="E1876" s="6"/>
     </row>
     <row r="1877">
       <c r="A1877" s="6"/>
-      <c r="B1877" s="13"/>
+      <c r="B1877" s="14"/>
       <c r="C1877" s="6"/>
       <c r="D1877" s="6"/>
       <c r="E1877" s="6"/>
     </row>
     <row r="1878">
       <c r="A1878" s="6"/>
-      <c r="B1878" s="13"/>
+      <c r="B1878" s="14"/>
       <c r="C1878" s="6"/>
       <c r="D1878" s="6"/>
       <c r="E1878" s="6"/>
     </row>
     <row r="1879">
       <c r="A1879" s="6"/>
-      <c r="B1879" s="13"/>
+      <c r="B1879" s="14"/>
       <c r="C1879" s="6"/>
       <c r="D1879" s="6"/>
       <c r="E1879" s="6"/>
     </row>
     <row r="1880">
       <c r="A1880" s="6"/>
-      <c r="B1880" s="13"/>
+      <c r="B1880" s="14"/>
       <c r="C1880" s="6"/>
       <c r="D1880" s="6"/>
       <c r="E1880" s="6"/>
     </row>
     <row r="1881">
       <c r="A1881" s="6"/>
-      <c r="B1881" s="13"/>
+      <c r="B1881" s="14"/>
       <c r="C1881" s="6"/>
       <c r="D1881" s="6"/>
       <c r="E1881" s="6"/>
     </row>
     <row r="1882">
       <c r="A1882" s="6"/>
-      <c r="B1882" s="13"/>
+      <c r="B1882" s="14"/>
       <c r="C1882" s="6"/>
       <c r="D1882" s="6"/>
       <c r="E1882" s="6"/>
     </row>
     <row r="1883">
       <c r="A1883" s="6"/>
-      <c r="B1883" s="13"/>
+      <c r="B1883" s="14"/>
       <c r="C1883" s="6"/>
       <c r="D1883" s="6"/>
       <c r="E1883" s="6"/>
     </row>
     <row r="1884">
       <c r="A1884" s="6"/>
-      <c r="B1884" s="13"/>
+      <c r="B1884" s="14"/>
       <c r="C1884" s="6"/>
       <c r="D1884" s="6"/>
       <c r="E1884" s="6"/>
     </row>
     <row r="1885">
       <c r="A1885" s="6"/>
-      <c r="B1885" s="13"/>
+      <c r="B1885" s="14"/>
       <c r="C1885" s="6"/>
       <c r="D1885" s="6"/>
       <c r="E1885" s="6"/>
     </row>
     <row r="1886">
       <c r="A1886" s="6"/>
-      <c r="B1886" s="13"/>
+      <c r="B1886" s="14"/>
       <c r="C1886" s="6"/>
       <c r="D1886" s="6"/>
       <c r="E1886" s="6"/>
     </row>
     <row r="1887">
       <c r="A1887" s="6"/>
-      <c r="B1887" s="13"/>
+      <c r="B1887" s="14"/>
       <c r="C1887" s="6"/>
       <c r="D1887" s="6"/>
       <c r="E1887" s="6"/>
     </row>
     <row r="1888">
       <c r="A1888" s="6"/>
-      <c r="B1888" s="13"/>
+      <c r="B1888" s="14"/>
       <c r="C1888" s="6"/>
       <c r="D1888" s="6"/>
       <c r="E1888" s="6"/>
     </row>
     <row r="1889">
       <c r="A1889" s="6"/>
-      <c r="B1889" s="13"/>
+      <c r="B1889" s="14"/>
       <c r="C1889" s="6"/>
       <c r="D1889" s="6"/>
       <c r="E1889" s="6"/>
     </row>
     <row r="1890">
       <c r="A1890" s="6"/>
-      <c r="B1890" s="13"/>
+      <c r="B1890" s="14"/>
       <c r="C1890" s="6"/>
       <c r="D1890" s="6"/>
       <c r="E1890" s="6"/>
     </row>
     <row r="1891">
       <c r="A1891" s="6"/>
-      <c r="B1891" s="13"/>
+      <c r="B1891" s="14"/>
       <c r="C1891" s="6"/>
       <c r="D1891" s="6"/>
       <c r="E1891" s="6"/>
     </row>
     <row r="1892">
       <c r="A1892" s="6"/>
-      <c r="B1892" s="13"/>
+      <c r="B1892" s="14"/>
       <c r="C1892" s="6"/>
       <c r="D1892" s="6"/>
       <c r="E1892" s="6"/>
     </row>
     <row r="1893">
       <c r="A1893" s="6"/>
-      <c r="B1893" s="13"/>
+      <c r="B1893" s="14"/>
       <c r="C1893" s="6"/>
       <c r="D1893" s="6"/>
       <c r="E1893" s="6"/>
     </row>
     <row r="1894">
       <c r="A1894" s="6"/>
-      <c r="B1894" s="13"/>
+      <c r="B1894" s="14"/>
       <c r="C1894" s="6"/>
       <c r="D1894" s="6"/>
       <c r="E1894" s="6"/>
     </row>
     <row r="1895">
       <c r="A1895" s="6"/>
-      <c r="B1895" s="13"/>
+      <c r="B1895" s="14"/>
       <c r="C1895" s="6"/>
       <c r="D1895" s="6"/>
       <c r="E1895" s="6"/>
     </row>
     <row r="1896">
       <c r="A1896" s="6"/>
-      <c r="B1896" s="13"/>
+      <c r="B1896" s="14"/>
       <c r="C1896" s="6"/>
       <c r="D1896" s="6"/>
       <c r="E1896" s="6"/>
     </row>
     <row r="1897">
       <c r="A1897" s="6"/>
-      <c r="B1897" s="13"/>
+      <c r="B1897" s="14"/>
       <c r="C1897" s="6"/>
       <c r="D1897" s="6"/>
       <c r="E1897" s="6"/>
     </row>
     <row r="1898">
       <c r="A1898" s="6"/>
-      <c r="B1898" s="13"/>
+      <c r="B1898" s="14"/>
       <c r="C1898" s="6"/>
       <c r="D1898" s="6"/>
       <c r="E1898" s="6"/>
     </row>
     <row r="1899">
       <c r="A1899" s="6"/>
-      <c r="B1899" s="13"/>
+      <c r="B1899" s="14"/>
       <c r="C1899" s="6"/>
       <c r="D1899" s="6"/>
       <c r="E1899" s="6"/>
     </row>
     <row r="1900">
       <c r="A1900" s="6"/>
-      <c r="B1900" s="13"/>
+      <c r="B1900" s="14"/>
       <c r="C1900" s="6"/>
       <c r="D1900" s="6"/>
       <c r="E1900" s="6"/>
     </row>
     <row r="1901">
       <c r="A1901" s="6"/>
-      <c r="B1901" s="13"/>
+      <c r="B1901" s="14"/>
       <c r="C1901" s="6"/>
       <c r="D1901" s="6"/>
       <c r="E1901" s="6"/>
     </row>
     <row r="1902">
       <c r="A1902" s="6"/>
-      <c r="B1902" s="13"/>
+      <c r="B1902" s="14"/>
       <c r="C1902" s="6"/>
       <c r="D1902" s="6"/>
       <c r="E1902" s="6"/>
     </row>
     <row r="1903">
       <c r="A1903" s="6"/>
-      <c r="B1903" s="13"/>
+      <c r="B1903" s="14"/>
       <c r="C1903" s="6"/>
       <c r="D1903" s="6"/>
       <c r="E1903" s="6"/>
     </row>
     <row r="1904">
       <c r="A1904" s="6"/>
-      <c r="B1904" s="13"/>
+      <c r="B1904" s="14"/>
       <c r="C1904" s="6"/>
       <c r="D1904" s="6"/>
       <c r="E1904" s="6"/>
     </row>
     <row r="1905">
       <c r="A1905" s="6"/>
-      <c r="B1905" s="13"/>
+      <c r="B1905" s="14"/>
       <c r="C1905" s="6"/>
       <c r="D1905" s="6"/>
       <c r="E1905" s="6"/>
     </row>
     <row r="1906">
       <c r="A1906" s="6"/>
-      <c r="B1906" s="13"/>
+      <c r="B1906" s="14"/>
       <c r="C1906" s="6"/>
       <c r="D1906" s="6"/>
       <c r="E1906" s="6"/>
     </row>
     <row r="1907">
       <c r="A1907" s="6"/>
-      <c r="B1907" s="13"/>
+      <c r="B1907" s="14"/>
       <c r="C1907" s="6"/>
       <c r="D1907" s="6"/>
       <c r="E1907" s="6"/>
     </row>
     <row r="1908">
       <c r="A1908" s="6"/>
-      <c r="B1908" s="13"/>
+      <c r="B1908" s="14"/>
       <c r="C1908" s="6"/>
       <c r="D1908" s="6"/>
       <c r="E1908" s="6"/>
     </row>
     <row r="1909">
       <c r="A1909" s="6"/>
-      <c r="B1909" s="13"/>
+      <c r="B1909" s="14"/>
       <c r="C1909" s="6"/>
       <c r="D1909" s="6"/>
       <c r="E1909" s="6"/>
     </row>
     <row r="1910">
       <c r="A1910" s="6"/>
-      <c r="B1910" s="13"/>
+      <c r="B1910" s="14"/>
       <c r="C1910" s="6"/>
       <c r="D1910" s="6"/>
       <c r="E1910" s="6"/>
     </row>
     <row r="1911">
       <c r="A1911" s="6"/>
-      <c r="B1911" s="13"/>
+      <c r="B1911" s="14"/>
       <c r="C1911" s="6"/>
       <c r="D1911" s="6"/>
       <c r="E1911" s="6"/>
     </row>
     <row r="1912">
       <c r="A1912" s="6"/>
-      <c r="B1912" s="13"/>
+      <c r="B1912" s="14"/>
       <c r="C1912" s="6"/>
       <c r="D1912" s="6"/>
       <c r="E1912" s="6"/>
     </row>
     <row r="1913">
       <c r="A1913" s="6"/>
-      <c r="B1913" s="13"/>
+      <c r="B1913" s="14"/>
       <c r="C1913" s="6"/>
       <c r="D1913" s="6"/>
       <c r="E1913" s="6"/>
     </row>
     <row r="1914">
       <c r="A1914" s="6"/>
-      <c r="B1914" s="13"/>
+      <c r="B1914" s="14"/>
       <c r="C1914" s="6"/>
       <c r="D1914" s="6"/>
       <c r="E1914" s="6"/>
     </row>
     <row r="1915">
       <c r="A1915" s="6"/>
-      <c r="B1915" s="13"/>
+      <c r="B1915" s="14"/>
       <c r="C1915" s="6"/>
       <c r="D1915" s="6"/>
       <c r="E1915" s="6"/>
     </row>
     <row r="1916">
       <c r="A1916" s="6"/>
-      <c r="B1916" s="13"/>
+      <c r="B1916" s="14"/>
       <c r="C1916" s="6"/>
       <c r="D1916" s="6"/>
       <c r="E1916" s="6"/>
     </row>
     <row r="1917">
       <c r="A1917" s="6"/>
-      <c r="B1917" s="13"/>
+      <c r="B1917" s="14"/>
       <c r="C1917" s="6"/>
       <c r="D1917" s="6"/>
       <c r="E1917" s="6"/>
     </row>
     <row r="1918">
       <c r="A1918" s="6"/>
-      <c r="B1918" s="13"/>
+      <c r="B1918" s="14"/>
       <c r="C1918" s="6"/>
       <c r="D1918" s="6"/>
       <c r="E1918" s="6"/>
     </row>
     <row r="1919">
       <c r="A1919" s="6"/>
-      <c r="B1919" s="13"/>
+      <c r="B1919" s="14"/>
       <c r="C1919" s="6"/>
       <c r="D1919" s="6"/>
       <c r="E1919" s="6"/>
     </row>
     <row r="1920">
       <c r="A1920" s="6"/>
-      <c r="B1920" s="13"/>
+      <c r="B1920" s="14"/>
       <c r="C1920" s="6"/>
       <c r="D1920" s="6"/>
       <c r="E1920" s="6"/>
     </row>
     <row r="1921">
       <c r="A1921" s="6"/>
-      <c r="B1921" s="13"/>
+      <c r="B1921" s="14"/>
       <c r="C1921" s="6"/>
       <c r="D1921" s="6"/>
       <c r="E1921" s="6"/>
     </row>
     <row r="1922">
       <c r="A1922" s="6"/>
-      <c r="B1922" s="13"/>
+      <c r="B1922" s="14"/>
       <c r="C1922" s="6"/>
       <c r="D1922" s="6"/>
       <c r="E1922" s="6"/>
     </row>
     <row r="1923">
       <c r="A1923" s="6"/>
-      <c r="B1923" s="13"/>
+      <c r="B1923" s="14"/>
       <c r="C1923" s="6"/>
       <c r="D1923" s="6"/>
       <c r="E1923" s="6"/>
     </row>
     <row r="1924">
       <c r="A1924" s="6"/>
-      <c r="B1924" s="13"/>
+      <c r="B1924" s="14"/>
       <c r="C1924" s="6"/>
       <c r="D1924" s="6"/>
       <c r="E1924" s="6"/>
     </row>
     <row r="1925">
       <c r="A1925" s="6"/>
-      <c r="B1925" s="13"/>
+      <c r="B1925" s="14"/>
       <c r="C1925" s="6"/>
       <c r="D1925" s="6"/>
       <c r="E1925" s="6"/>
     </row>
     <row r="1926">
       <c r="A1926" s="6"/>
-      <c r="B1926" s="13"/>
+      <c r="B1926" s="14"/>
       <c r="C1926" s="6"/>
       <c r="D1926" s="6"/>
       <c r="E1926" s="6"/>
     </row>
     <row r="1927">
       <c r="A1927" s="6"/>
-      <c r="B1927" s="13"/>
+      <c r="B1927" s="14"/>
       <c r="C1927" s="6"/>
       <c r="D1927" s="6"/>
       <c r="E1927" s="6"/>
     </row>
     <row r="1928">
       <c r="A1928" s="6"/>
-      <c r="B1928" s="13"/>
+      <c r="B1928" s="14"/>
       <c r="C1928" s="6"/>
       <c r="D1928" s="6"/>
       <c r="E1928" s="6"/>
     </row>
     <row r="1929">
       <c r="A1929" s="6"/>
-      <c r="B1929" s="13"/>
+      <c r="B1929" s="14"/>
       <c r="C1929" s="6"/>
       <c r="D1929" s="6"/>
       <c r="E1929" s="6"/>
     </row>
     <row r="1930">
       <c r="A1930" s="6"/>
-      <c r="B1930" s="13"/>
+      <c r="B1930" s="14"/>
       <c r="C1930" s="6"/>
       <c r="D1930" s="6"/>
       <c r="E1930" s="6"/>
     </row>
     <row r="1931">
       <c r="A1931" s="6"/>
-      <c r="B1931" s="13"/>
+      <c r="B1931" s="14"/>
       <c r="C1931" s="6"/>
       <c r="D1931" s="6"/>
       <c r="E1931" s="6"/>
     </row>
     <row r="1932">
       <c r="A1932" s="6"/>
-      <c r="B1932" s="13"/>
+      <c r="B1932" s="14"/>
       <c r="C1932" s="6"/>
       <c r="D1932" s="6"/>
       <c r="E1932" s="6"/>
     </row>
     <row r="1933">
       <c r="A1933" s="6"/>
-      <c r="B1933" s="13"/>
+      <c r="B1933" s="14"/>
       <c r="C1933" s="6"/>
       <c r="D1933" s="6"/>
       <c r="E1933" s="6"/>
     </row>
     <row r="1934">
       <c r="A1934" s="6"/>
-      <c r="B1934" s="13"/>
+      <c r="B1934" s="14"/>
       <c r="C1934" s="6"/>
       <c r="D1934" s="6"/>
       <c r="E1934" s="6"/>
     </row>
     <row r="1935">
       <c r="A1935" s="6"/>
-      <c r="B1935" s="13"/>
+      <c r="B1935" s="14"/>
       <c r="C1935" s="6"/>
       <c r="D1935" s="6"/>
       <c r="E1935" s="6"/>
     </row>
     <row r="1936">
       <c r="A1936" s="6"/>
-      <c r="B1936" s="13"/>
+      <c r="B1936" s="14"/>
       <c r="C1936" s="6"/>
       <c r="D1936" s="6"/>
       <c r="E1936" s="6"/>
     </row>
     <row r="1937">
       <c r="A1937" s="6"/>
-      <c r="B1937" s="13"/>
+      <c r="B1937" s="14"/>
       <c r="C1937" s="6"/>
       <c r="D1937" s="6"/>
       <c r="E1937" s="6"/>
     </row>
     <row r="1938">
       <c r="A1938" s="6"/>
-      <c r="B1938" s="13"/>
+      <c r="B1938" s="14"/>
       <c r="C1938" s="6"/>
       <c r="D1938" s="6"/>
       <c r="E1938" s="6"/>
     </row>
     <row r="1939">
       <c r="A1939" s="6"/>
-      <c r="B1939" s="13"/>
+      <c r="B1939" s="14"/>
       <c r="C1939" s="6"/>
       <c r="D1939" s="6"/>
       <c r="E1939" s="6"/>
     </row>
     <row r="1940">
       <c r="A1940" s="6"/>
-      <c r="B1940" s="13"/>
+      <c r="B1940" s="14"/>
       <c r="C1940" s="6"/>
       <c r="D1940" s="6"/>
       <c r="E1940" s="6"/>
     </row>
     <row r="1941">
       <c r="A1941" s="6"/>
-      <c r="B1941" s="13"/>
+      <c r="B1941" s="14"/>
       <c r="C1941" s="6"/>
       <c r="D1941" s="6"/>
       <c r="E1941" s="6"/>
     </row>
     <row r="1942">
       <c r="A1942" s="6"/>
-      <c r="B1942" s="13"/>
+      <c r="B1942" s="14"/>
       <c r="C1942" s="6"/>
       <c r="D1942" s="6"/>
       <c r="E1942" s="6"/>
     </row>
     <row r="1943">
       <c r="A1943" s="6"/>
-      <c r="B1943" s="13"/>
+      <c r="B1943" s="14"/>
       <c r="C1943" s="6"/>
       <c r="D1943" s="6"/>
       <c r="E1943" s="6"/>
     </row>
     <row r="1944">
       <c r="A1944" s="6"/>
-      <c r="B1944" s="13"/>
+      <c r="B1944" s="14"/>
       <c r="C1944" s="6"/>
       <c r="D1944" s="6"/>
       <c r="E1944" s="6"/>
     </row>
     <row r="1945">
       <c r="A1945" s="6"/>
-      <c r="B1945" s="13"/>
+      <c r="B1945" s="14"/>
       <c r="C1945" s="6"/>
       <c r="D1945" s="6"/>
       <c r="E1945" s="6"/>
     </row>
     <row r="1946">
       <c r="A1946" s="6"/>
-      <c r="B1946" s="13"/>
+      <c r="B1946" s="14"/>
       <c r="C1946" s="6"/>
       <c r="D1946" s="6"/>
       <c r="E1946" s="6"/>
     </row>
     <row r="1947">
       <c r="A1947" s="6"/>
-      <c r="B1947" s="13"/>
+      <c r="B1947" s="14"/>
       <c r="C1947" s="6"/>
       <c r="D1947" s="6"/>
       <c r="E1947" s="6"/>
     </row>
     <row r="1948">
       <c r="A1948" s="6"/>
-      <c r="B1948" s="13"/>
+      <c r="B1948" s="14"/>
       <c r="C1948" s="6"/>
       <c r="D1948" s="6"/>
       <c r="E1948" s="6"/>
     </row>
     <row r="1949">
       <c r="A1949" s="6"/>
-      <c r="B1949" s="13"/>
+      <c r="B1949" s="14"/>
       <c r="C1949" s="6"/>
       <c r="D1949" s="6"/>
       <c r="E1949" s="6"/>
     </row>
     <row r="1950">
       <c r="A1950" s="6"/>
-      <c r="B1950" s="13"/>
+      <c r="B1950" s="14"/>
       <c r="C1950" s="6"/>
       <c r="D1950" s="6"/>
       <c r="E1950" s="6"/>
     </row>
     <row r="1951">
       <c r="A1951" s="6"/>
-      <c r="B1951" s="13"/>
+      <c r="B1951" s="14"/>
       <c r="C1951" s="6"/>
       <c r="D1951" s="6"/>
       <c r="E1951" s="6"/>
     </row>
     <row r="1952">
       <c r="A1952" s="6"/>
-      <c r="B1952" s="13"/>
+      <c r="B1952" s="14"/>
       <c r="C1952" s="6"/>
       <c r="D1952" s="6"/>
       <c r="E1952" s="6"/>
     </row>
     <row r="1953">
       <c r="A1953" s="6"/>
-      <c r="B1953" s="13"/>
+      <c r="B1953" s="14"/>
       <c r="C1953" s="6"/>
       <c r="D1953" s="6"/>
       <c r="E1953" s="6"/>
     </row>
     <row r="1954">
       <c r="A1954" s="6"/>
-      <c r="B1954" s="13"/>
+      <c r="B1954" s="14"/>
       <c r="C1954" s="6"/>
       <c r="D1954" s="6"/>
       <c r="E1954" s="6"/>
     </row>
     <row r="1955">
       <c r="A1955" s="6"/>
-      <c r="B1955" s="13"/>
+      <c r="B1955" s="14"/>
       <c r="C1955" s="6"/>
       <c r="D1955" s="6"/>
       <c r="E1955" s="6"/>
     </row>
     <row r="1956">
       <c r="A1956" s="6"/>
-      <c r="B1956" s="13"/>
+      <c r="B1956" s="14"/>
       <c r="C1956" s="6"/>
       <c r="D1956" s="6"/>
       <c r="E1956" s="6"/>
     </row>
     <row r="1957">
       <c r="A1957" s="6"/>
-      <c r="B1957" s="13"/>
+      <c r="B1957" s="14"/>
       <c r="C1957" s="6"/>
       <c r="D1957" s="6"/>
       <c r="E1957" s="6"/>
     </row>
     <row r="1958">
       <c r="A1958" s="6"/>
-      <c r="B1958" s="13"/>
+      <c r="B1958" s="14"/>
       <c r="C1958" s="6"/>
       <c r="D1958" s="6"/>
       <c r="E1958" s="6"/>
     </row>
     <row r="1959">
       <c r="A1959" s="6"/>
-      <c r="B1959" s="13"/>
+      <c r="B1959" s="14"/>
       <c r="C1959" s="6"/>
       <c r="D1959" s="6"/>
       <c r="E1959" s="6"/>
     </row>
     <row r="1960">
       <c r="A1960" s="6"/>
-      <c r="B1960" s="13"/>
+      <c r="B1960" s="14"/>
       <c r="C1960" s="6"/>
       <c r="D1960" s="6"/>
       <c r="E1960" s="6"/>
     </row>
     <row r="1961">
       <c r="A1961" s="6"/>
-      <c r="B1961" s="13"/>
+      <c r="B1961" s="14"/>
       <c r="C1961" s="6"/>
       <c r="D1961" s="6"/>
       <c r="E1961" s="6"/>
     </row>
     <row r="1962">
       <c r="A1962" s="6"/>
-      <c r="B1962" s="13"/>
+      <c r="B1962" s="14"/>
       <c r="C1962" s="6"/>
       <c r="D1962" s="6"/>
       <c r="E1962" s="6"/>
     </row>
     <row r="1963">
       <c r="A1963" s="6"/>
-      <c r="B1963" s="13"/>
+      <c r="B1963" s="14"/>
       <c r="C1963" s="6"/>
       <c r="D1963" s="6"/>
       <c r="E1963" s="6"/>
     </row>
     <row r="1964">
       <c r="A1964" s="6"/>
-      <c r="B1964" s="13"/>
+      <c r="B1964" s="14"/>
       <c r="C1964" s="6"/>
       <c r="D1964" s="6"/>
       <c r="E1964" s="6"/>
     </row>
     <row r="1965">
       <c r="A1965" s="6"/>
-      <c r="B1965" s="13"/>
+      <c r="B1965" s="14"/>
       <c r="C1965" s="6"/>
       <c r="D1965" s="6"/>
       <c r="E1965" s="6"/>
     </row>
     <row r="1966">
       <c r="A1966" s="6"/>
-      <c r="B1966" s="13"/>
+      <c r="B1966" s="14"/>
       <c r="C1966" s="6"/>
       <c r="D1966" s="6"/>
       <c r="E1966" s="6"/>
     </row>
     <row r="1967">
       <c r="A1967" s="6"/>
-      <c r="B1967" s="13"/>
+      <c r="B1967" s="14"/>
       <c r="C1967" s="6"/>
       <c r="D1967" s="6"/>
       <c r="E1967" s="6"/>
     </row>
     <row r="1968">
       <c r="A1968" s="6"/>
-      <c r="B1968" s="13"/>
+      <c r="B1968" s="14"/>
       <c r="C1968" s="6"/>
       <c r="D1968" s="6"/>
       <c r="E1968" s="6"/>
     </row>
     <row r="1969">
       <c r="A1969" s="6"/>
-      <c r="B1969" s="13"/>
+      <c r="B1969" s="14"/>
       <c r="C1969" s="6"/>
       <c r="D1969" s="6"/>
       <c r="E1969" s="6"/>
     </row>
     <row r="1970">
       <c r="A1970" s="6"/>
-      <c r="B1970" s="13"/>
+      <c r="B1970" s="14"/>
       <c r="C1970" s="6"/>
       <c r="D1970" s="6"/>
       <c r="E1970" s="6"/>
     </row>
     <row r="1971">
       <c r="A1971" s="6"/>
-      <c r="B1971" s="13"/>
+      <c r="B1971" s="14"/>
       <c r="C1971" s="6"/>
       <c r="D1971" s="6"/>
       <c r="E1971" s="6"/>
     </row>
     <row r="1972">
       <c r="A1972" s="6"/>
-      <c r="B1972" s="13"/>
+      <c r="B1972" s="14"/>
       <c r="C1972" s="6"/>
       <c r="D1972" s="6"/>
       <c r="E1972" s="6"/>
     </row>
     <row r="1973">
       <c r="A1973" s="6"/>
-      <c r="B1973" s="13"/>
+      <c r="B1973" s="14"/>
       <c r="C1973" s="6"/>
       <c r="D1973" s="6"/>
       <c r="E1973" s="6"/>
     </row>
     <row r="1974">
       <c r="A1974" s="6"/>
-      <c r="B1974" s="13"/>
+      <c r="B1974" s="14"/>
       <c r="C1974" s="6"/>
       <c r="D1974" s="6"/>
       <c r="E1974" s="6"/>
     </row>
     <row r="1975">
       <c r="A1975" s="6"/>
-      <c r="B1975" s="13"/>
+      <c r="B1975" s="14"/>
       <c r="C1975" s="6"/>
       <c r="D1975" s="6"/>
       <c r="E1975" s="6"/>
     </row>
     <row r="1976">
       <c r="A1976" s="6"/>
-      <c r="B1976" s="13"/>
+      <c r="B1976" s="14"/>
       <c r="C1976" s="6"/>
       <c r="D1976" s="6"/>
       <c r="E1976" s="6"/>
     </row>
     <row r="1977">
       <c r="A1977" s="6"/>
-      <c r="B1977" s="13"/>
+      <c r="B1977" s="14"/>
       <c r="C1977" s="6"/>
       <c r="D1977" s="6"/>
       <c r="E1977" s="6"/>
     </row>
     <row r="1978">
       <c r="A1978" s="6"/>
-      <c r="B1978" s="13"/>
+      <c r="B1978" s="14"/>
       <c r="C1978" s="6"/>
       <c r="D1978" s="6"/>
       <c r="E1978" s="6"/>
     </row>
     <row r="1979">
       <c r="A1979" s="6"/>
-      <c r="B1979" s="13"/>
+      <c r="B1979" s="14"/>
       <c r="C1979" s="6"/>
       <c r="D1979" s="6"/>
       <c r="E1979" s="6"/>
     </row>
     <row r="1980">
       <c r="A1980" s="6"/>
-      <c r="B1980" s="13"/>
+      <c r="B1980" s="14"/>
       <c r="C1980" s="6"/>
       <c r="D1980" s="6"/>
       <c r="E1980" s="6"/>
     </row>
     <row r="1981">
       <c r="A1981" s="6"/>
-      <c r="B1981" s="13"/>
+      <c r="B1981" s="14"/>
       <c r="C1981" s="6"/>
       <c r="D1981" s="6"/>
       <c r="E1981" s="6"/>
     </row>
     <row r="1982">
       <c r="A1982" s="6"/>
-      <c r="B1982" s="13"/>
+      <c r="B1982" s="14"/>
       <c r="C1982" s="6"/>
       <c r="D1982" s="6"/>
       <c r="E1982" s="6"/>
     </row>
     <row r="1983">
       <c r="A1983" s="6"/>
-      <c r="B1983" s="13"/>
+      <c r="B1983" s="14"/>
       <c r="C1983" s="6"/>
       <c r="D1983" s="6"/>
       <c r="E1983" s="6"/>
     </row>
     <row r="1984">
       <c r="A1984" s="6"/>
-      <c r="B1984" s="13"/>
+      <c r="B1984" s="14"/>
       <c r="C1984" s="6"/>
       <c r="D1984" s="6"/>
       <c r="E1984" s="6"/>
     </row>
     <row r="1985">
       <c r="A1985" s="6"/>
-      <c r="B1985" s="13"/>
+      <c r="B1985" s="14"/>
       <c r="C1985" s="6"/>
       <c r="D1985" s="6"/>
       <c r="E1985" s="6"/>
     </row>
     <row r="1986">
       <c r="A1986" s="6"/>
-      <c r="B1986" s="13"/>
+      <c r="B1986" s="14"/>
       <c r="C1986" s="6"/>
       <c r="D1986" s="6"/>
       <c r="E1986" s="6"/>
     </row>
     <row r="1987">
       <c r="A1987" s="6"/>
-      <c r="B1987" s="13"/>
+      <c r="B1987" s="14"/>
       <c r="C1987" s="6"/>
       <c r="D1987" s="6"/>
       <c r="E1987" s="6"/>
     </row>
     <row r="1988">
       <c r="A1988" s="6"/>
-      <c r="B1988" s="13"/>
+      <c r="B1988" s="14"/>
       <c r="C1988" s="6"/>
       <c r="D1988" s="6"/>
       <c r="E1988" s="6"/>
     </row>
     <row r="1989">
       <c r="A1989" s="6"/>
-      <c r="B1989" s="13"/>
+      <c r="B1989" s="14"/>
       <c r="C1989" s="6"/>
       <c r="D1989" s="6"/>
       <c r="E1989" s="6"/>
     </row>
     <row r="1990">
       <c r="A1990" s="6"/>
-      <c r="B1990" s="13"/>
+      <c r="B1990" s="14"/>
       <c r="C1990" s="6"/>
       <c r="D1990" s="6"/>
       <c r="E1990" s="6"/>
     </row>
     <row r="1991">
       <c r="A1991" s="6"/>
-      <c r="B1991" s="13"/>
+      <c r="B1991" s="14"/>
       <c r="C1991" s="6"/>
       <c r="D1991" s="6"/>
       <c r="E1991" s="6"/>
     </row>
     <row r="1992">
       <c r="A1992" s="6"/>
-      <c r="B1992" s="13"/>
+      <c r="B1992" s="14"/>
       <c r="C1992" s="6"/>
       <c r="D1992" s="6"/>
       <c r="E1992" s="6"/>
     </row>
     <row r="1993">
       <c r="A1993" s="6"/>
-      <c r="B1993" s="13"/>
+      <c r="B1993" s="14"/>
       <c r="C1993" s="6"/>
       <c r="D1993" s="6"/>
       <c r="E1993" s="6"/>
     </row>
     <row r="1994">
       <c r="A1994" s="6"/>
-      <c r="B1994" s="13"/>
+      <c r="B1994" s="14"/>
       <c r="C1994" s="6"/>
       <c r="D1994" s="6"/>
       <c r="E1994" s="6"/>
     </row>
     <row r="1995">
       <c r="A1995" s="6"/>
-      <c r="B1995" s="13"/>
+      <c r="B1995" s="14"/>
       <c r="C1995" s="6"/>
       <c r="D1995" s="6"/>
       <c r="E1995" s="6"/>
     </row>
     <row r="1996">
       <c r="A1996" s="6"/>
-      <c r="B1996" s="13"/>
+      <c r="B1996" s="14"/>
       <c r="C1996" s="6"/>
       <c r="D1996" s="6"/>
       <c r="E1996" s="6"/>
     </row>
     <row r="1997">
       <c r="A1997" s="6"/>
-      <c r="B1997" s="13"/>
+      <c r="B1997" s="14"/>
       <c r="C1997" s="6"/>
       <c r="D1997" s="6"/>
       <c r="E1997" s="6"/>
     </row>
     <row r="1998">
       <c r="A1998" s="6"/>
-      <c r="B1998" s="13"/>
+      <c r="B1998" s="14"/>
       <c r="C1998" s="6"/>
       <c r="D1998" s="6"/>
       <c r="E1998" s="6"/>
     </row>
     <row r="1999">
       <c r="A1999" s="6"/>
-      <c r="B1999" s="13"/>
+      <c r="B1999" s="14"/>
       <c r="C1999" s="6"/>
       <c r="D1999" s="6"/>
       <c r="E1999" s="6"/>
     </row>
     <row r="2000">
       <c r="A2000" s="6"/>
-      <c r="B2000" s="13"/>
+      <c r="B2000" s="14"/>
       <c r="C2000" s="6"/>
       <c r="D2000" s="6"/>
       <c r="E2000" s="6"/>
     </row>
     <row r="2001">
       <c r="A2001" s="6"/>
-      <c r="B2001" s="13"/>
+      <c r="B2001" s="14"/>
       <c r="C2001" s="6"/>
       <c r="D2001" s="6"/>
       <c r="E2001" s="6"/>
     </row>
     <row r="2002">
       <c r="A2002" s="6"/>
-      <c r="B2002" s="13"/>
+      <c r="B2002" s="14"/>
       <c r="C2002" s="6"/>
       <c r="D2002" s="6"/>
       <c r="E2002" s="6"/>
     </row>
     <row r="2003">
       <c r="A2003" s="6"/>
-      <c r="B2003" s="13"/>
+      <c r="B2003" s="14"/>
       <c r="C2003" s="6"/>
       <c r="D2003" s="6"/>
       <c r="E2003" s="6"/>
     </row>
     <row r="2004">
       <c r="A2004" s="6"/>
-      <c r="B2004" s="13"/>
+      <c r="B2004" s="14"/>
       <c r="C2004" s="6"/>
       <c r="D2004" s="6"/>
       <c r="E2004" s="6"/>
     </row>
     <row r="2005">
       <c r="A2005" s="6"/>
-      <c r="B2005" s="13"/>
+      <c r="B2005" s="14"/>
       <c r="C2005" s="6"/>
       <c r="D2005" s="6"/>
       <c r="E2005" s="6"/>
     </row>
     <row r="2006">
       <c r="A2006" s="6"/>
-      <c r="B2006" s="13"/>
+      <c r="B2006" s="14"/>
       <c r="C2006" s="6"/>
       <c r="D2006" s="6"/>
       <c r="E2006" s="6"/>
     </row>
     <row r="2007">
       <c r="A2007" s="6"/>
-      <c r="B2007" s="13"/>
+      <c r="B2007" s="14"/>
       <c r="C2007" s="6"/>
       <c r="D2007" s="6"/>
       <c r="E2007" s="6"/>
     </row>
     <row r="2008">
       <c r="A2008" s="6"/>
-      <c r="B2008" s="13"/>
+      <c r="B2008" s="14"/>
       <c r="C2008" s="6"/>
       <c r="D2008" s="6"/>
       <c r="E2008" s="6"/>
     </row>
     <row r="2009">
       <c r="A2009" s="6"/>
-      <c r="B2009" s="13"/>
+      <c r="B2009" s="14"/>
       <c r="C2009" s="6"/>
       <c r="D2009" s="6"/>
       <c r="E2009" s="6"/>
     </row>
     <row r="2010">
       <c r="A2010" s="6"/>
-      <c r="B2010" s="13"/>
+      <c r="B2010" s="14"/>
       <c r="C2010" s="6"/>
       <c r="D2010" s="6"/>
       <c r="E2010" s="6"/>
     </row>
     <row r="2011">
       <c r="A2011" s="6"/>
-      <c r="B2011" s="13"/>
+      <c r="B2011" s="14"/>
       <c r="C2011" s="6"/>
       <c r="D2011" s="6"/>
       <c r="E2011" s="6"/>
     </row>
     <row r="2012">
       <c r="A2012" s="6"/>
-      <c r="B2012" s="13"/>
+      <c r="B2012" s="14"/>
       <c r="C2012" s="6"/>
       <c r="D2012" s="6"/>
       <c r="E2012" s="6"/>
     </row>
     <row r="2013">
       <c r="A2013" s="6"/>
-      <c r="B2013" s="13"/>
+      <c r="B2013" s="14"/>
       <c r="C2013" s="6"/>
       <c r="D2013" s="6"/>
       <c r="E2013" s="6"/>
     </row>
     <row r="2014">
       <c r="A2014" s="6"/>
-      <c r="B2014" s="13"/>
+      <c r="B2014" s="14"/>
       <c r="C2014" s="6"/>
       <c r="D2014" s="6"/>
       <c r="E2014" s="6"/>
     </row>
     <row r="2015">
       <c r="A2015" s="6"/>
-      <c r="B2015" s="13"/>
+      <c r="B2015" s="14"/>
       <c r="C2015" s="6"/>
       <c r="D2015" s="6"/>
       <c r="E2015" s="6"/>
     </row>
     <row r="2016">
       <c r="A2016" s="6"/>
-      <c r="B2016" s="13"/>
+      <c r="B2016" s="14"/>
       <c r="C2016" s="6"/>
       <c r="D2016" s="6"/>
       <c r="E2016" s="6"/>
     </row>
     <row r="2017">
       <c r="A2017" s="6"/>
-      <c r="B2017" s="13"/>
+      <c r="B2017" s="14"/>
       <c r="C2017" s="6"/>
       <c r="D2017" s="6"/>
       <c r="E2017" s="6"/>
     </row>
     <row r="2018">
       <c r="A2018" s="6"/>
-      <c r="B2018" s="13"/>
+      <c r="B2018" s="14"/>
       <c r="C2018" s="6"/>
       <c r="D2018" s="6"/>
       <c r="E2018" s="6"/>
     </row>
     <row r="2019">
       <c r="A2019" s="6"/>
-      <c r="B2019" s="13"/>
+      <c r="B2019" s="14"/>
       <c r="C2019" s="6"/>
       <c r="D2019" s="6"/>
       <c r="E2019" s="6"/>
     </row>
     <row r="2020">
       <c r="A2020" s="6"/>
-      <c r="B2020" s="13"/>
+      <c r="B2020" s="14"/>
       <c r="C2020" s="6"/>
       <c r="D2020" s="6"/>
       <c r="E2020" s="6"/>
     </row>
     <row r="2021">
       <c r="A2021" s="6"/>
-      <c r="B2021" s="13"/>
+      <c r="B2021" s="14"/>
       <c r="C2021" s="6"/>
       <c r="D2021" s="6"/>
       <c r="E2021" s="6"/>
     </row>
     <row r="2022">
       <c r="A2022" s="6"/>
-      <c r="B2022" s="13"/>
+      <c r="B2022" s="14"/>
       <c r="C2022" s="6"/>
       <c r="D2022" s="6"/>
       <c r="E2022" s="6"/>
     </row>
     <row r="2023">
       <c r="A2023" s="6"/>
-      <c r="B2023" s="13"/>
+      <c r="B2023" s="14"/>
       <c r="C2023" s="6"/>
       <c r="D2023" s="6"/>
       <c r="E2023" s="6"/>
     </row>
     <row r="2024">
       <c r="A2024" s="6"/>
-      <c r="B2024" s="13"/>
+      <c r="B2024" s="14"/>
       <c r="C2024" s="6"/>
       <c r="D2024" s="6"/>
       <c r="E2024" s="6"/>
     </row>
     <row r="2025">
       <c r="A2025" s="6"/>
-      <c r="B2025" s="13"/>
+      <c r="B2025" s="14"/>
       <c r="C2025" s="6"/>
       <c r="D2025" s="6"/>
       <c r="E2025" s="6"/>
     </row>
     <row r="2026">
       <c r="A2026" s="6"/>
-      <c r="B2026" s="13"/>
+      <c r="B2026" s="14"/>
       <c r="C2026" s="6"/>
       <c r="D2026" s="6"/>
       <c r="E2026" s="6"/>
     </row>
     <row r="2027">
       <c r="A2027" s="6"/>
-      <c r="B2027" s="13"/>
+      <c r="B2027" s="14"/>
       <c r="C2027" s="6"/>
       <c r="D2027" s="6"/>
       <c r="E2027" s="6"/>
     </row>
     <row r="2028">
       <c r="A2028" s="6"/>
-      <c r="B2028" s="13"/>
+      <c r="B2028" s="14"/>
       <c r="C2028" s="6"/>
       <c r="D2028" s="6"/>
       <c r="E2028" s="6"/>
     </row>
     <row r="2029">
       <c r="A2029" s="6"/>
-      <c r="B2029" s="13"/>
+      <c r="B2029" s="14"/>
       <c r="C2029" s="6"/>
       <c r="D2029" s="6"/>
       <c r="E2029" s="6"/>
     </row>
     <row r="2030">
       <c r="A2030" s="6"/>
-      <c r="B2030" s="13"/>
+      <c r="B2030" s="14"/>
       <c r="C2030" s="6"/>
       <c r="D2030" s="6"/>
       <c r="E2030" s="6"/>
     </row>
     <row r="2031">
       <c r="A2031" s="6"/>
-      <c r="B2031" s="13"/>
+      <c r="B2031" s="14"/>
       <c r="C2031" s="6"/>
       <c r="D2031" s="6"/>
       <c r="E2031" s="6"/>
     </row>
     <row r="2032">
       <c r="A2032" s="6"/>
-      <c r="B2032" s="13"/>
+      <c r="B2032" s="14"/>
       <c r="C2032" s="6"/>
       <c r="D2032" s="6"/>
       <c r="E2032" s="6"/>
     </row>
     <row r="2033">
       <c r="A2033" s="6"/>
-      <c r="B2033" s="13"/>
+      <c r="B2033" s="14"/>
       <c r="C2033" s="6"/>
       <c r="D2033" s="6"/>
       <c r="E2033" s="6"/>
     </row>
     <row r="2034">
       <c r="A2034" s="6"/>
-      <c r="B2034" s="13"/>
+      <c r="B2034" s="14"/>
       <c r="C2034" s="6"/>
       <c r="D2034" s="6"/>
       <c r="E2034" s="6"/>
     </row>
     <row r="2035">
       <c r="A2035" s="6"/>
-      <c r="B2035" s="13"/>
+      <c r="B2035" s="14"/>
       <c r="C2035" s="6"/>
       <c r="D2035" s="6"/>
       <c r="E2035" s="6"/>
     </row>
     <row r="2036">
       <c r="A2036" s="6"/>
-      <c r="B2036" s="13"/>
+      <c r="B2036" s="14"/>
       <c r="C2036" s="6"/>
       <c r="D2036" s="6"/>
       <c r="E2036" s="6"/>
     </row>
     <row r="2037">
       <c r="A2037" s="6"/>
-      <c r="B2037" s="13"/>
+      <c r="B2037" s="14"/>
       <c r="C2037" s="6"/>
       <c r="D2037" s="6"/>
       <c r="E2037" s="6"/>
     </row>
     <row r="2038">
       <c r="A2038" s="6"/>
-      <c r="B2038" s="13"/>
+      <c r="B2038" s="14"/>
       <c r="C2038" s="6"/>
       <c r="D2038" s="6"/>
       <c r="E2038" s="6"/>
     </row>
     <row r="2039">
       <c r="A2039" s="6"/>
-      <c r="B2039" s="13"/>
+      <c r="B2039" s="14"/>
       <c r="C2039" s="6"/>
       <c r="D2039" s="6"/>
       <c r="E2039" s="6"/>
     </row>
     <row r="2040">
       <c r="A2040" s="6"/>
-      <c r="B2040" s="13"/>
+      <c r="B2040" s="14"/>
       <c r="C2040" s="6"/>
       <c r="D2040" s="6"/>
       <c r="E2040" s="6"/>
     </row>
     <row r="2041">
       <c r="A2041" s="6"/>
-      <c r="B2041" s="13"/>
+      <c r="B2041" s="14"/>
       <c r="C2041" s="6"/>
       <c r="D2041" s="6"/>
       <c r="E2041" s="6"/>
     </row>
     <row r="2042">
       <c r="A2042" s="6"/>
-      <c r="B2042" s="13"/>
+      <c r="B2042" s="14"/>
       <c r="C2042" s="6"/>
       <c r="D2042" s="6"/>
       <c r="E2042" s="6"/>
     </row>
     <row r="2043">
       <c r="A2043" s="6"/>
-      <c r="B2043" s="13"/>
+      <c r="B2043" s="14"/>
       <c r="C2043" s="6"/>
       <c r="D2043" s="6"/>
       <c r="E2043" s="6"/>
     </row>
     <row r="2044">
       <c r="A2044" s="6"/>
-      <c r="B2044" s="13"/>
+      <c r="B2044" s="14"/>
       <c r="C2044" s="6"/>
       <c r="D2044" s="6"/>
       <c r="E2044" s="6"/>
     </row>
     <row r="2045">
       <c r="A2045" s="6"/>
-      <c r="B2045" s="13"/>
+      <c r="B2045" s="14"/>
       <c r="C2045" s="6"/>
       <c r="D2045" s="6"/>
       <c r="E2045" s="6"/>
     </row>
     <row r="2046">
       <c r="A2046" s="6"/>
-      <c r="B2046" s="13"/>
+      <c r="B2046" s="14"/>
       <c r="C2046" s="6"/>
       <c r="D2046" s="6"/>
       <c r="E2046" s="6"/>
     </row>
     <row r="2047">
       <c r="A2047" s="6"/>
-      <c r="B2047" s="13"/>
+      <c r="B2047" s="14"/>
       <c r="C2047" s="6"/>
       <c r="D2047" s="6"/>
       <c r="E2047" s="6"/>
     </row>
     <row r="2048">
       <c r="A2048" s="6"/>
-      <c r="B2048" s="13"/>
+      <c r="B2048" s="14"/>
       <c r="C2048" s="6"/>
       <c r="D2048" s="6"/>
       <c r="E2048" s="6"/>
     </row>
     <row r="2049">
       <c r="A2049" s="6"/>
-      <c r="B2049" s="13"/>
+      <c r="B2049" s="14"/>
       <c r="C2049" s="6"/>
       <c r="D2049" s="6"/>
       <c r="E2049" s="6"/>
     </row>
     <row r="2050">
       <c r="A2050" s="6"/>
-      <c r="B2050" s="13"/>
+      <c r="B2050" s="14"/>
       <c r="C2050" s="6"/>
       <c r="D2050" s="6"/>
       <c r="E2050" s="6"/>
     </row>
     <row r="2051">
       <c r="A2051" s="6"/>
-      <c r="B2051" s="13"/>
+      <c r="B2051" s="14"/>
       <c r="C2051" s="6"/>
       <c r="D2051" s="6"/>
       <c r="E2051" s="6"/>
     </row>
     <row r="2052">
       <c r="A2052" s="6"/>
-      <c r="B2052" s="13"/>
+      <c r="B2052" s="14"/>
       <c r="C2052" s="6"/>
       <c r="D2052" s="6"/>
       <c r="E2052" s="6"/>
     </row>
     <row r="2053">
       <c r="A2053" s="6"/>
-      <c r="B2053" s="13"/>
+      <c r="B2053" s="14"/>
       <c r="C2053" s="6"/>
       <c r="D2053" s="6"/>
       <c r="E2053" s="6"/>

--- a/PublicCustomerApp/src/python/translation.xlsx
+++ b/PublicCustomerApp/src/python/translation.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2718" uniqueCount="2605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2770" uniqueCount="2655">
   <si>
     <t>key</t>
   </si>
@@ -7840,6 +7840,156 @@
   </si>
   <si>
     <t>உங்கள் சவாரிகள்</t>
+  </si>
+  <si>
+    <t>driver_details</t>
+  </si>
+  <si>
+    <t>Driver Details</t>
+  </si>
+  <si>
+    <t>vehicle_details</t>
+  </si>
+  <si>
+    <t>Vehicle Details</t>
+  </si>
+  <si>
+    <t>bank_details</t>
+  </si>
+  <si>
+    <t>Bank Details</t>
+  </si>
+  <si>
+    <t>document_center</t>
+  </si>
+  <si>
+    <t>Document Center</t>
+  </si>
+  <si>
+    <t>document_center_subtitle</t>
+  </si>
+  <si>
+    <t>Finish these steps so you can start accepting rides</t>
+  </si>
+  <si>
+    <t>valid_phone</t>
+  </si>
+  <si>
+    <t>Please Enter Valid Phone</t>
+  </si>
+  <si>
+    <t>license_number_detected</t>
+  </si>
+  <si>
+    <t>License number detected and filled automatically.</t>
+  </si>
+  <si>
+    <t>dob_detected_auto_filled</t>
+  </si>
+  <si>
+    <t>Date of birth detected and filled automatically.</t>
+  </si>
+  <si>
+    <t>license_details_not_detected</t>
+  </si>
+  <si>
+    <t>Couldn’t detect licence details. Update the fields manually.</t>
+  </si>
+  <si>
+    <t>please_enter_dob</t>
+  </si>
+  <si>
+    <t>Please enter date of birth</t>
+  </si>
+  <si>
+    <t>please_upload_driver_photo</t>
+  </si>
+  <si>
+    <t>Upload the driver photo before proceeding.</t>
+  </si>
+  <si>
+    <t>please_upload_license_document</t>
+  </si>
+  <si>
+    <t>Upload the driving license before proceeding.</t>
+  </si>
+  <si>
+    <t>driver_photo_helper</t>
+  </si>
+  <si>
+    <t>Upload or capture a clear recent photo of the driver.</t>
+  </si>
+  <si>
+    <t>editing_disabled</t>
+  </si>
+  <si>
+    <t>Editing is disabled in this mode.</t>
+  </si>
+  <si>
+    <t>prefer_not_to_say</t>
+  </si>
+  <si>
+    <t>Prefer not to say</t>
+  </si>
+  <si>
+    <t>vehicle_registration_certificate</t>
+  </si>
+  <si>
+    <t>Vehicle RC</t>
+  </si>
+  <si>
+    <t>vehicle_rc_scan_helper</t>
+  </si>
+  <si>
+    <t>Upload or capture the vehicle RC to detect the registration number automatically</t>
+  </si>
+  <si>
+    <t>upload_vehicle_rc</t>
+  </si>
+  <si>
+    <t>Upload or capture vehicle RC</t>
+  </si>
+  <si>
+    <t>aadhaar_card</t>
+  </si>
+  <si>
+    <t>Aadhaar Card</t>
+  </si>
+  <si>
+    <t>details_detected_review</t>
+  </si>
+  <si>
+    <t>Details detected automatically. Review before submitting.</t>
+  </si>
+  <si>
+    <t>details_not_detected_update_manual</t>
+  </si>
+  <si>
+    <t>Could not extract Aadhaar number. Update the field manually.</t>
+  </si>
+  <si>
+    <t>document_upload_in_progress</t>
+  </si>
+  <si>
+    <t>Uploading document. Please wait…</t>
+  </si>
+  <si>
+    <t>document_ready_to_upload</t>
+  </si>
+  <si>
+    <t>Document ready. Tap Upload to send.</t>
+  </si>
+  <si>
+    <t>proof_documents_info</t>
+  </si>
+  <si>
+    <t>Update either Aadhaar or PAN. Provide at least one valid document.</t>
+  </si>
+  <si>
+    <t>please_select_gender</t>
+  </si>
+  <si>
+    <t>Please Select Gender</t>
   </si>
 </sst>
 </file>
@@ -7904,7 +8054,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -7957,7 +8107,21 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -8299,8 +8463,8 @@
         <v>உங்கள் கட்டணத்தை பேசி, நம்ம ஊரு டாக்ஸி® செயலியுடன் பிக்-அப் இடத்தைப் பகிர்ந்து கொள்ளச் சொல்லுங்கள். அறிவிப்பு மூலம் பிக்-அப் இடத்தைப் பெற்று, பயணத்தைத் தொடங்க அதை ஏற்றுக்கொள்ளுங்கள்.</v>
       </c>
       <c r="D5" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B5, ""en"", ""hi"")"),"किराया तय कर लें और उनसे Namma Ooru Taxi ® ऐप के ज़रिए पिकअप लोकेशन शेयर करने के लिए कहें। नोटिफिकेशन के ज़रिए पिकअप लोकेशन मिलने पर उसे स्वीकार करके यात्रा शुरू करें।")</f>
-        <v>किराया तय कर लें और उनसे Namma Ooru Taxi ® ऐप के ज़रिए पिकअप लोकेशन शेयर करने के लिए कहें। नोटिफिकेशन के ज़रिए पिकअप लोकेशन मिलने पर उसे स्वीकार करके यात्रा शुरू करें।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B5, ""en"", ""hi"")"),"किराया तय करें और उनसे Namma Ooru Taxi ® ऐप के ज़रिए पिकअप लोकेशन शेयर करने के लिए कहें। नोटिफिकेशन के ज़रिए पिकअप लोकेशन मिलने पर उसे स्वीकार करके यात्रा शुरू करें।")</f>
+        <v>किराया तय करें और उनसे Namma Ooru Taxi ® ऐप के ज़रिए पिकअप लोकेशन शेयर करने के लिए कहें। नोटिफिकेशन के ज़रिए पिकअप लोकेशन मिलने पर उसे स्वीकार करके यात्रा शुरू करें।</v>
       </c>
       <c r="E5" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B5, ""en"", ""kn"")"),"ನಿಮ್ಮ ದರವನ್ನು ಮಾತುಕತೆ ಮಾಡಿ ಮತ್ತು ನಮ್ಮ ಊರು ಟ್ಯಾಕ್ಸಿ® ಅಪ್ಲಿಕೇಶನ್‌ನೊಂದಿಗೆ ಪಿಕಪ್ ಸ್ಥಳವನ್ನು ಹಂಚಿಕೊಳ್ಳಲು ಅವರನ್ನು ಕೇಳಿ. ಅಧಿಸೂಚನೆಯ ಮೂಲಕ ಪಿಕಪ್ ಸ್ಥಳವನ್ನು ಸ್ವೀಕರಿಸಿ ಮತ್ತು ಪ್ರಯಾಣವನ್ನು ಪ್ರಾರಂಭಿಸಲು ಅದನ್ನು ಸ್ವೀಕರಿಸಿ.")</f>
@@ -8563,8 +8727,8 @@
         <v>കൂടുതൽ പ്രതിബദ്ധതയ്ക്കുള്ള താക്കോലാണ് റേറ്റിംഗുകൾ. നിങ്ങൾക്ക് നല്ല റേറ്റിംഗ് ലഭിക്കുന്നുണ്ടെന്ന് ഉറപ്പാക്കുക.</v>
       </c>
       <c r="G14" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B14, ""en"", ""te"")"),"మరింత నిబద్ధతకు రేటింగ్‌లు కీలకం. మీరు మంచి రేటింగ్ పొందారని నిర్ధారించుకోండి.")</f>
-        <v>మరింత నిబద్ధతకు రేటింగ్‌లు కీలకం. మీరు మంచి రేటింగ్ పొందారని నిర్ధారించుకోండి.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B14, ""en"", ""te"")"),"మరింత నిబద్ధతకు రేటింగ్‌లు కీలకం. మీరు మంచి రేటింగ్ పొందేలా చూసుకోండి.")</f>
+        <v>మరింత నిబద్ధతకు రేటింగ్‌లు కీలకం. మీరు మంచి రేటింగ్ పొందేలా చూసుకోండి.</v>
       </c>
     </row>
     <row r="15">
@@ -8911,8 +9075,8 @@
         <v>58</v>
       </c>
       <c r="C27" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B27, ""en"", ""ta"")"),"தயவுசெய்து செல்லுபடியாகும் உரிம எண்ணை உள்ளிடவும் (TN01 20110012345)")</f>
-        <v>தயவுசெய்து செல்லுபடியாகும் உரிம எண்ணை உள்ளிடவும் (TN01 20110012345)</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B27, ""en"", ""ta"")"),"செல்லுபடியாகும் உரிம எண்ணை (TN01 20110012345) உள்ளிடவும்.")</f>
+        <v>செல்லுபடியாகும் உரிம எண்ணை (TN01 20110012345) உள்ளிடவும்.</v>
       </c>
       <c r="D27" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B27, ""en"", ""hi"")"),"कृपया वैध लाइसेंस नंबर दर्ज करें (TN01 20110012345)")</f>
@@ -8971,8 +9135,8 @@
         <v>இருப்பிட அனுமதி மறுக்கப்பட்டது</v>
       </c>
       <c r="D29" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B29, ""en"", ""hi"")"),"स्थान की अनुमति अस्वीकृत")</f>
-        <v>स्थान की अनुमति अस्वीकृत</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B29, ""en"", ""hi"")"),"स्थान अनुमति अस्वीकृत")</f>
+        <v>स्थान अनुमति अस्वीकृत</v>
       </c>
       <c r="E29" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B29, ""en"", ""kn"")"),"ಸ್ಥಳ ಅನುಮತಿ ನಿರಾಕರಿಸಲಾಗಿದೆ")</f>
@@ -9129,8 +9293,8 @@
         <v>ಆದ್ಯತೆಯ ಕೆಲಸದ ಸ್ಥಳ</v>
       </c>
       <c r="F34" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B34, ""en"", ""ml"")"),"ഇഷ്ടപ്പെട്ട ജോലി സ്ഥലം")</f>
-        <v>ഇഷ്ടപ്പെട്ട ജോലി സ്ഥലം</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B34, ""en"", ""ml"")"),"ഇഷ്ടപ്പെട്ട ജോലിസ്ഥലം")</f>
+        <v>ഇഷ്ടപ്പെട്ട ജോലിസ്ഥലം</v>
       </c>
       <c r="G34" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B34, ""en"", ""te"")"),"ఇష్టపడే పని స్థానం")</f>
@@ -9461,12 +9625,12 @@
         <v>कृपया निर्माण वर्ष दर्ज करें</v>
       </c>
       <c r="E46" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B46, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ತಯಾರಿಕಾ ವರ್ಷವನ್ನು ನಮೂದಿಸಿ.")</f>
-        <v>ದಯವಿಟ್ಟು ತಯಾರಿಕಾ ವರ್ಷವನ್ನು ನಮೂದಿಸಿ.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B46, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ತಯಾರಿಕಾ ವರ್ಷವನ್ನು ನಮೂದಿಸಿ")</f>
+        <v>ದಯವಿಟ್ಟು ತಯಾರಿಕಾ ವರ್ಷವನ್ನು ನಮೂದಿಸಿ</v>
       </c>
       <c r="F46" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B46, ""en"", ""ml"")"),"നിർമ്മാണ വർഷം നൽകുക")</f>
-        <v>നിർമ്മാണ വർഷം നൽകുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B46, ""en"", ""ml"")"),"നിർമ്മാണ വർഷം നൽകുക.")</f>
+        <v>നിർമ്മാണ വർഷം നൽകുക.</v>
       </c>
       <c r="G46" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B46, ""en"", ""te"")"),"దయచేసి తయారీ సంవత్సరాన్ని నమోదు చేయండి")</f>
@@ -10125,8 +10289,8 @@
         <v>144</v>
       </c>
       <c r="C70" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B70, ""en"", ""ta"")"),"வண்ணத்தைத் தேர்ந்தெடுக்கவும்")</f>
-        <v>வண்ணத்தைத் தேர்ந்தெடுக்கவும்</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B70, ""en"", ""ta"")"),"நிறத்தைத் தேர்ந்தெடுக்கவும்")</f>
+        <v>நிறத்தைத் தேர்ந்தெடுக்கவும்</v>
       </c>
       <c r="D70" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B70, ""en"", ""hi"")"),"रंग चुनो")</f>
@@ -11261,8 +11425,8 @@
         <v>ദയവായി സാധുവായ ഒരു UPI ഐഡി നൽകുക - 9999999999@upi</v>
       </c>
       <c r="G110" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B110, ""en"", ""te"")"),"దయచేసి చెల్లుబాటు అయ్యే UPI IDని నమోదు చేయండి - 99999999999@upi")</f>
-        <v>దయచేసి చెల్లుబాటు అయ్యే UPI IDని నమోదు చేయండి - 99999999999@upi</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B110, ""en"", ""te"")"),"దయచేసి చెల్లుబాటు అయ్యే UPI IDని నమోదు చేయండి - 9999999999@upi")</f>
+        <v>దయచేసి చెల్లుబాటు అయ్యే UPI IDని నమోదు చేయండి - 9999999999@upi</v>
       </c>
     </row>
     <row r="111">
@@ -12679,8 +12843,8 @@
         <v>ನೋಂದಾಯಿತ ಫೋನ್ ಸಂಖ್ಯೆಗೆ OTP ಯಶಸ್ವಿಯಾಗಿ ಮರು ಕಳುಹಿಸಲಾಗಿದೆ.</v>
       </c>
       <c r="F160" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B160, ""en"", ""ml"")"),"രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വിജയകരമായി വീണ്ടും അയച്ചു.")</f>
-        <v>രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വിജയകരമായി വീണ്ടും അയച്ചു.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B160, ""en"", ""ml"")"),"രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വീണ്ടും അയച്ചു.")</f>
+        <v>രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വീണ്ടും അയച്ചു.</v>
       </c>
       <c r="G160" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B160, ""en"", ""te"")"),"రిజిస్టర్డ్ ఫోన్ నంబర్‌కు OTP విజయవంతంగా తిరిగి పంపబడింది.")</f>
@@ -12996,9 +13160,9 @@
       </c>
       <c r="F171" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B171, ""en"", ""ml"")"),"ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
-ക്ഷമയ്ക്ക് നന്ദി.")</f>
+നിങ്ങളുടെ ക്ഷമയ്ക്ക് നന്ദി.")</f>
         <v>ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
-ക്ഷമയ്ക്ക് നന്ദി.</v>
+നിങ്ങളുടെ ക്ഷമയ്ക്ക് നന്ദി.</v>
       </c>
       <c r="G171" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B171, ""en"", ""te"")"),"టాక్సీని ధృవీకరించడానికి మరియు వాటిని ఆమోదించడానికి మేము తీవ్రంగా కృషి చేస్తున్నాము. కాబట్టి దయచేసి ఆమోద ప్రక్రియకు కొంత సమయం పడుతుందని అర్థం చేసుకోండి.
@@ -14303,8 +14467,8 @@
         <v>426</v>
       </c>
       <c r="C218" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B218, ""en"", ""ta"")"),"இருப்பிடம் முடிவு")</f>
-        <v>இருப்பிடம் முடிவு</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B218, ""en"", ""ta"")"),"முடிவு இடம்")</f>
+        <v>முடிவு இடம்</v>
       </c>
       <c r="D218" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B218, ""en"", ""hi"")"),"अंतिम स्थान")</f>
@@ -14367,8 +14531,8 @@
         <v>स्थिति का चयन करें</v>
       </c>
       <c r="E220" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B220, ""en"", ""kn"")"),"ಸ್ಥಿತಿಯನ್ನು ಆಯ್ಕೆಮಾಡಿ")</f>
-        <v>ಸ್ಥಿತಿಯನ್ನು ಆಯ್ಕೆಮಾಡಿ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B220, ""en"", ""kn"")"),"ಸ್ಥಿತಿ ಆಯ್ಕೆಮಾಡಿ")</f>
+        <v>ಸ್ಥಿತಿ ಆಯ್ಕೆಮಾಡಿ</v>
       </c>
       <c r="F220" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B220, ""en"", ""ml"")"),"സ്റ്റാറ്റസ് തിരഞ്ഞെടുക്കുക")</f>
@@ -16163,8 +16327,8 @@
         <v>ನಿಮ್ಮಲ್ಲಿ ಬಾಕಿ ಮೊತ್ತವಿದ್ದರೆ, ದಯವಿಟ್ಟು ಮುಂಚಿತವಾಗಿ ಎಲ್ಲಾ ಬಾಕಿ ಮೊತ್ತವನ್ನು ಪಾವತಿಸಿ.</v>
       </c>
       <c r="F284" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B284, ""en"", ""ml"")"),"നിങ്ങളുടെ കുടിശ്ശിക തുക ബാക്കിയുണ്ടെങ്കിൽ, ദയവായി എല്ലാ കുടിശ്ശികകളും മുൻകൂട്ടി തീർക്കുക.")</f>
-        <v>നിങ്ങളുടെ കുടിശ്ശിക തുക ബാക്കിയുണ്ടെങ്കിൽ, ദയവായി എല്ലാ കുടിശ്ശികകളും മുൻകൂട്ടി തീർക്കുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B284, ""en"", ""ml"")"),"കുടിശ്ശിക തുക ബാക്കിയുണ്ടെങ്കിൽ ദയവായി എല്ലാ കുടിശ്ശികയും മുൻകൂട്ടി തീർക്കുക.")</f>
+        <v>കുടിശ്ശിക തുക ബാക്കിയുണ്ടെങ്കിൽ ദയവായി എല്ലാ കുടിശ്ശികയും മുൻകൂട്ടി തീർക്കുക.</v>
       </c>
       <c r="G284" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B284, ""en"", ""te"")"),"మీకు ఇంకా బకాయిలు ఉంటే, దయచేసి ముందుగా అన్ని బకాయిలను చెల్లించండి.")</f>
@@ -16435,8 +16599,8 @@
         <v>டைமரை நிறுத்து</v>
       </c>
       <c r="D294" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B294, ""en"", ""hi"")"),"टाइमर रोकें")</f>
-        <v>टाइमर रोकें</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B294, ""en"", ""hi"")"),"टाइमर बंद करें")</f>
+        <v>टाइमर बंद करें</v>
       </c>
       <c r="E294" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B294, ""en"", ""kn"")"),"ಟೈಮರ್ ನಿಲ್ಲಿಸಿ")</f>
@@ -17787,8 +17951,8 @@
         <v>ಅಪ್ಲಿಕೇಶನ್ ಸಂಬಂಧಿತ</v>
       </c>
       <c r="F342" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B342, ""en"", ""ml"")"),"ആപ്പ് അനുബന്ധം")</f>
-        <v>ആപ്പ് അനുബന്ധം</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B342, ""en"", ""ml"")"),"അനുബന്ധ ആപ്പ്")</f>
+        <v>അനുബന്ധ ആപ്പ്</v>
       </c>
       <c r="G342" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B342, ""en"", ""te"")"),"సంబంధిత యాప్")</f>
@@ -18491,8 +18655,8 @@
         <v>ഈ പ്രവർത്തനം പഴയപടിയാക്കാൻ കഴിയില്ല - ഇല്ലാതാക്കിയ ഡാറ്റ വീണ്ടെടുക്കാൻ കഴിയില്ല.</v>
       </c>
       <c r="G367" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B367, ""en"", ""te"")"),"ఈ చర్యను రద్దు చేయడం సాధ్యం కాదు - తొలగించబడిన డేటాను తిరిగి పొందడం సాధ్యం కాదు.")</f>
-        <v>ఈ చర్యను రద్దు చేయడం సాధ్యం కాదు - తొలగించబడిన డేటాను తిరిగి పొందడం సాధ్యం కాదు.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B367, ""en"", ""te"")"),"ఈ చర్యను రద్దు చేయలేము - తొలగించబడిన డేటాను తిరిగి పొందడం సాధ్యం కాదు.")</f>
+        <v>ఈ చర్యను రద్దు చేయలేము - తొలగించబడిన డేటాను తిరిగి పొందడం సాధ్యం కాదు.</v>
       </c>
     </row>
     <row r="368">
@@ -18755,8 +18919,8 @@
         <v>729</v>
       </c>
       <c r="C377" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B377, ""en"", ""ta"")"),"வாகன ஆர்.சி. ஆவணத்தின் பின்புறம்")</f>
-        <v>வாகன ஆர்.சி. ஆவணத்தின் பின்புறம்</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B377, ""en"", ""ta"")"),"வாகன ஆர்சி ஆவண பின்புறம்")</f>
+        <v>வாகன ஆர்சி ஆவண பின்புறம்</v>
       </c>
       <c r="D377" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B377, ""en"", ""hi"")"),"वाहन आरसी दस्तावेज़ का पिछला भाग")</f>
@@ -19219,8 +19383,8 @@
         <v>ലക്ഷ്യസ്ഥാനത്ത് എത്തി</v>
       </c>
       <c r="G393" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B393, ""en"", ""te"")"),"గమ్యస్థానానికి చేరుకున్నారు")</f>
-        <v>గమ్యస్థానానికి చేరుకున్నారు</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B393, ""en"", ""te"")"),"గమ్యస్థానాన్ని చేరుకున్నారు")</f>
+        <v>గమ్యస్థానాన్ని చేరుకున్నారు</v>
       </c>
     </row>
     <row r="394">
@@ -20888,8 +21052,8 @@
         <v>अलग हुए</v>
       </c>
       <c r="E453" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B453, ""en"", ""kn"")"),"ಬೇರೆಡೆಗೆ ತಿರುಗಿತು")</f>
-        <v>ಬೇರೆಡೆಗೆ ತಿರುಗಿತು</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B453, ""en"", ""kn"")"),"ವಿಭಾಗಿಸಲಾಗಿದೆ")</f>
+        <v>ವಿಭಾಗಿಸಲಾಗಿದೆ</v>
       </c>
       <c r="F453" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B453, ""en"", ""ml"")"),"വിഘടിച്ചു")</f>
@@ -22326,8 +22490,8 @@
         <v>"ಯಾವಾಗಲೂ" ಅಥವಾ "ಆ್ಯಪ್ ಬಳಸುವಾಗ" ಆಯ್ಕೆಮಾಡಿ.</v>
       </c>
       <c r="F506" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B506, ""en"", ""ml"")"),"""എല്ലായ്‌പ്പോഴും"" അല്ലെങ്കിൽ ""ആപ്പ് ഉപയോഗിക്കുമ്പോൾ"" തിരഞ്ഞെടുക്കുക.")</f>
-        <v>"എല്ലായ്‌പ്പോഴും" അല്ലെങ്കിൽ "ആപ്പ് ഉപയോഗിക്കുമ്പോൾ" തിരഞ്ഞെടുക്കുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B506, ""en"", ""ml"")"),"""എല്ലായ്പ്പോഴും"" അല്ലെങ്കിൽ ""ആപ്പ് ഉപയോഗിക്കുമ്പോൾ"" തിരഞ്ഞെടുക്കുക.")</f>
+        <v>"എല്ലായ്പ്പോഴും" അല്ലെങ്കിൽ "ആപ്പ് ഉപയോഗിക്കുമ്പോൾ" തിരഞ്ഞെടുക്കുക.</v>
       </c>
       <c r="G506" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B506, ""en"", ""te"")"),"""ఎల్లప్పుడూ"" లేదా ""యాప్‌ను ఉపయోగిస్తున్నప్పుడు"" ఎంచుకోండి")</f>
@@ -23915,8 +24079,8 @@
         <v>हमसे संपर्क करें पर जाएं</v>
       </c>
       <c r="E565" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B565, ""en"", ""kn"")"),"ನಮ್ಮನ್ನು ಸಂಪರ್ಕಿಸಿ ಗೆ ಹೋಗಿ")</f>
-        <v>ನಮ್ಮನ್ನು ಸಂಪರ್ಕಿಸಿ ಗೆ ಹೋಗಿ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B565, ""en"", ""kn"")"),"ನಮ್ಮನ್ನು ಸಂಪರ್ಕಿಸಿ ವಿಭಾಗಕ್ಕೆ ಹೋಗಿ")</f>
+        <v>ನಮ್ಮನ್ನು ಸಂಪರ್ಕಿಸಿ ವಿಭಾಗಕ್ಕೆ ಹೋಗಿ</v>
       </c>
       <c r="F565" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B565, ""en"", ""ml"")"),"ഞങ്ങളെ ബന്ധപ്പെടുക എന്നതിലേക്ക് പോകുക")</f>
@@ -26572,8 +26736,8 @@
         <v>യാത്രാക്കൂലി വളരെ കൂടുതലാണ് (സർജ്)</v>
       </c>
       <c r="G663" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B663, ""en"", ""te"")"),"ఛార్జీ చాలా ఎక్కువగా ఉంది (పెరుగుదల)")</f>
-        <v>ఛార్జీ చాలా ఎక్కువగా ఉంది (పెరుగుదల)</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B663, ""en"", ""te"")"),"ఛార్జీ చాలా ఎక్కువగా ఉంది (సర్జ్)")</f>
+        <v>ఛార్జీ చాలా ఎక్కువగా ఉంది (సర్జ్)</v>
       </c>
     </row>
     <row r="664">
@@ -28945,8 +29109,8 @@
         <v>ನೀವು {ತ್ರಿಜ್ಯ} ಕಿಮೀ ವ್ಯಾಪ್ತಿಯೊಳಗಿನ ಸ್ಥಳವನ್ನು ಆಯ್ಕೆ ಮಾಡಬೇಕು.</v>
       </c>
       <c r="F751" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B751, ""en"", ""ml"")"),"{radius} കിലോമീറ്റർ ചുറ്റളവിലുള്ള ഒരു സ്ഥലം നിങ്ങൾ തിരഞ്ഞെടുക്കണം.")</f>
-        <v>{radius} കിലോമീറ്റർ ചുറ്റളവിലുള്ള ഒരു സ്ഥലം നിങ്ങൾ തിരഞ്ഞെടുക്കണം.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B751, ""en"", ""ml"")"),"നിങ്ങൾ {radius} കിലോമീറ്റർ ചുറ്റളവിൽ ഒരു സ്ഥലം തിരഞ്ഞെടുക്കണം.")</f>
+        <v>നിങ്ങൾ {radius} കിലോമീറ്റർ ചുറ്റളവിൽ ഒരു സ്ഥലം തിരഞ്ഞെടുക്കണം.</v>
       </c>
       <c r="G751" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B751, ""en"", ""te"")"),"మీరు {radius} కిమీ వ్యాసార్థంలోపు స్థానాన్ని ఎంచుకోవాలి.")</f>
@@ -29618,8 +29782,8 @@
         <v>ನೀವು ಆಯ್ಕೆ ಮಾಡಿದ {ವಾಹನ} ಹತ್ತಿರದಲ್ಲಿ ಯಾವುದೇ ಚಾಲಕರಿಲ್ಲ. ಲಭ್ಯವಿರುವ ಚಾಲಕರಿರುವ ಮತ್ತೊಂದು ವಾಹನವನ್ನು ನಾವು ಆರಿಸಿಕೊಂಡಿದ್ದೇವೆ.</v>
       </c>
       <c r="F776" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B776, ""en"", ""ml"")"),"നിങ്ങൾ തിരഞ്ഞെടുത്ത {വാഹനത്തിന്} സമീപത്ത് ഡ്രൈവറുകളില്ല. ലഭ്യമായ ഡ്രൈവറുകളുള്ള മറ്റൊരു വാഹനം ഞങ്ങൾ തിരഞ്ഞെടുത്തു.")</f>
-        <v>നിങ്ങൾ തിരഞ്ഞെടുത്ത {വാഹനത്തിന്} സമീപത്ത് ഡ്രൈവറുകളില്ല. ലഭ്യമായ ഡ്രൈവറുകളുള്ള മറ്റൊരു വാഹനം ഞങ്ങൾ തിരഞ്ഞെടുത്തു.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B776, ""en"", ""ml"")"),"നിങ്ങൾ തിരഞ്ഞെടുത്ത {വാഹനത്തിന്} സമീപത്ത് ഡ്രൈവറില്ല. ലഭ്യമായ ഡ്രൈവറുകളുള്ള മറ്റൊരു വാഹനം ഞങ്ങൾ തിരഞ്ഞെടുത്തു.")</f>
+        <v>നിങ്ങൾ തിരഞ്ഞെടുത്ത {വാഹനത്തിന്} സമീപത്ത് ഡ്രൈവറില്ല. ലഭ്യമായ ഡ്രൈവറുകളുള്ള മറ്റൊരു വാഹനം ഞങ്ങൾ തിരഞ്ഞെടുത്തു.</v>
       </c>
       <c r="G776" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B776, ""en"", ""te"")"),"మీరు ఎంచుకున్న {vehicle} కి సమీపంలో డ్రైవర్లు లేరు. అందుబాటులో ఉన్న డ్రైవర్లతో మేము మరొక వాహనాన్ని ఎంచుకున్నాము.")</f>
@@ -31010,7 +31174,7 @@
       <c r="A828" s="8" t="s">
         <v>1952</v>
       </c>
-      <c r="B828" s="18" t="s">
+      <c r="B828" s="17" t="s">
         <v>1553</v>
       </c>
       <c r="C828" s="6" t="s">
@@ -31241,8 +31405,8 @@
         <v>ದಯವಿಟ್ಟು ಬೆಂಬಲವನ್ನು ಸಂಪರ್ಕಿಸಿ</v>
       </c>
       <c r="F836" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B836, ""en"", ""ml"")"),"പിന്തുണയുമായി ബന്ധപ്പെടുക.")</f>
-        <v>പിന്തുണയുമായി ബന്ധപ്പെടുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B836, ""en"", ""ml"")"),"പിന്തുണയുമായി ബന്ധപ്പെടുക")</f>
+        <v>പിന്തുണയുമായി ബന്ധപ്പെടുക</v>
       </c>
       <c r="G836" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B836, ""en"", ""te"")"),"దయచేసి మద్దతును సంప్రదించండి")</f>
@@ -31400,8 +31564,8 @@
         <v>कृपया आपातकालीन संपर्क चुनें</v>
       </c>
       <c r="E842" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B842, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ತುರ್ತು ಸಂಪರ್ಕಗಳನ್ನು ಆಯ್ಕೆಮಾಡಿ")</f>
-        <v>ದಯವಿಟ್ಟು ತುರ್ತು ಸಂಪರ್ಕಗಳನ್ನು ಆಯ್ಕೆಮಾಡಿ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B842, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ತುರ್ತು ಸಂಪರ್ಕಗಳನ್ನು ಆಯ್ಕೆಮಾಡಿ.")</f>
+        <v>ದಯವಿಟ್ಟು ತುರ್ತು ಸಂಪರ್ಕಗಳನ್ನು ಆಯ್ಕೆಮಾಡಿ.</v>
       </c>
       <c r="F842" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B842, ""en"", ""ml"")"),"ദയവായി അടിയന്തര കോൺടാക്റ്റുകൾ തിരഞ്ഞെടുക്കുക.")</f>
@@ -33052,8 +33216,8 @@
         <v>ವೇಳಾಪಟ್ಟಿ</v>
       </c>
       <c r="F903" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B903, ""en"", ""ml"")"),"ഷെഡ്യൂൾ")</f>
-        <v>ഷെഡ്യൂൾ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B903, ""en"", ""ml"")"),"പട്ടിക")</f>
+        <v>പട്ടിക</v>
       </c>
       <c r="G903" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B903, ""en"", ""te"")"),"షెడ్యూల్")</f>
@@ -34486,8 +34650,8 @@
         <v>ಅಪ್ಲಿಕೇಶನ್ ಸಂಬಂಧಿತ</v>
       </c>
       <c r="F956" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B956, ""en"", ""ml"")"),"ആപ്പ് അനുബന്ധം")</f>
-        <v>ആപ്പ് അനുബന്ധം</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B956, ""en"", ""ml"")"),"അനുബന്ധ ആപ്പ്")</f>
+        <v>അനുബന്ധ ആപ്പ്</v>
       </c>
       <c r="G956" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B956, ""en"", ""te"")"),"సంబంధిత యాప్")</f>
@@ -37337,8 +37501,8 @@
         <v>आपकी यात्रा बीच में ही रद्द हो गई है।</v>
       </c>
       <c r="E1061" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1061, ""en"", ""kn"")"),"ನಿಮ್ಮ ಸವಾರಿಯನ್ನು ಸವಾರಿಯ ನಡುವೆ ರದ್ದುಗೊಳಿಸಲಾಗಿದೆ.")</f>
-        <v>ನಿಮ್ಮ ಸವಾರಿಯನ್ನು ಸವಾರಿಯ ನಡುವೆ ರದ್ದುಗೊಳಿಸಲಾಗಿದೆ.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1061, ""en"", ""kn"")"),"ನಿಮ್ಮ ಸವಾರಿಯನ್ನು ಮಧ್ಯದಲ್ಲಿ ರದ್ದುಗೊಳಿಸಲಾಗಿದೆ.")</f>
+        <v>ನಿಮ್ಮ ಸವಾರಿಯನ್ನು ಮಧ್ಯದಲ್ಲಿ ರದ್ದುಗೊಳಿಸಲಾಗಿದೆ.</v>
       </c>
       <c r="F1061" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1061, ""en"", ""ml"")"),"ഇടയിലുള്ള യാത്രയിൽ നിങ്ങളുടെ യാത്ര റദ്ദാക്കി.")</f>
@@ -37404,186 +37568,732 @@
       </c>
     </row>
     <row r="1064">
-      <c r="A1064" s="4"/>
-      <c r="B1064" s="5"/>
-      <c r="C1064" s="6"/>
-      <c r="D1064" s="6"/>
-      <c r="E1064" s="6"/>
+      <c r="A1064" s="14" t="s">
+        <v>2605</v>
+      </c>
+      <c r="B1064" s="12" t="s">
+        <v>2606</v>
+      </c>
+      <c r="C1064" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1064, ""en"", ""ta"")"),"ஓட்டுநர் விவரங்கள்")</f>
+        <v>ஓட்டுநர் விவரங்கள்</v>
+      </c>
+      <c r="D1064" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1064, ""en"", ""hi"")"),"चालक विवरण")</f>
+        <v>चालक विवरण</v>
+      </c>
+      <c r="E1064" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1064, ""en"", ""kn"")"),"ಚಾಲಕ ವಿವರಗಳು")</f>
+        <v>ಚಾಲಕ ವಿವರಗಳು</v>
+      </c>
+      <c r="F1064" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1064, ""en"", ""ml"")"),"ഡ്രൈവർ വിശദാംശങ്ങൾ")</f>
+        <v>ഡ്രൈവർ വിശദാംശങ്ങൾ</v>
+      </c>
+      <c r="G1064" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1064, ""en"", ""te"")"),"డ్రైవర్ వివరాలు")</f>
+        <v>డ్రైవర్ వివరాలు</v>
+      </c>
     </row>
     <row r="1065">
-      <c r="A1065" s="4"/>
-      <c r="B1065" s="5"/>
-      <c r="C1065" s="6"/>
-      <c r="D1065" s="6"/>
-      <c r="E1065" s="6"/>
+      <c r="A1065" s="14" t="s">
+        <v>2607</v>
+      </c>
+      <c r="B1065" s="12" t="s">
+        <v>2608</v>
+      </c>
+      <c r="C1065" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1065, ""en"", ""ta"")"),"வாகன விவரங்கள்")</f>
+        <v>வாகன விவரங்கள்</v>
+      </c>
+      <c r="D1065" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1065, ""en"", ""hi"")"),"वाहन की सूचना")</f>
+        <v>वाहन की सूचना</v>
+      </c>
+      <c r="E1065" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1065, ""en"", ""kn"")"),"ವಾಹನ ವಿವರಗಳು")</f>
+        <v>ವಾಹನ ವಿವರಗಳು</v>
+      </c>
+      <c r="F1065" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1065, ""en"", ""ml"")"),"വാഹന വിശദാംശങ്ങൾ")</f>
+        <v>വാഹന വിശദാംശങ്ങൾ</v>
+      </c>
+      <c r="G1065" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1065, ""en"", ""te"")"),"వాహన వివరాలు")</f>
+        <v>వాహన వివరాలు</v>
+      </c>
     </row>
     <row r="1066">
-      <c r="A1066" s="4"/>
-      <c r="B1066" s="5"/>
-      <c r="C1066" s="6"/>
-      <c r="D1066" s="6"/>
-      <c r="E1066" s="6"/>
+      <c r="A1066" s="14" t="s">
+        <v>2609</v>
+      </c>
+      <c r="B1066" s="12" t="s">
+        <v>2610</v>
+      </c>
+      <c r="C1066" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1066, ""en"", ""ta"")"),"வங்கி விவரங்கள்")</f>
+        <v>வங்கி விவரங்கள்</v>
+      </c>
+      <c r="D1066" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1066, ""en"", ""hi"")"),"बैंक विवरण")</f>
+        <v>बैंक विवरण</v>
+      </c>
+      <c r="E1066" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1066, ""en"", ""kn"")"),"ಬ್ಯಾಂಕ್ ವಿವರಗಳು")</f>
+        <v>ಬ್ಯಾಂಕ್ ವಿವರಗಳು</v>
+      </c>
+      <c r="F1066" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1066, ""en"", ""ml"")"),"ബാങ്ക് വിശദാംശങ്ങൾ")</f>
+        <v>ബാങ്ക് വിശദാംശങ്ങൾ</v>
+      </c>
+      <c r="G1066" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1066, ""en"", ""te"")"),"బ్యాంక్ వివరాలు")</f>
+        <v>బ్యాంక్ వివరాలు</v>
+      </c>
     </row>
     <row r="1067">
-      <c r="A1067" s="4"/>
-      <c r="B1067" s="5"/>
-      <c r="C1067" s="6"/>
-      <c r="D1067" s="6"/>
-      <c r="E1067" s="6"/>
+      <c r="A1067" s="14" t="s">
+        <v>554</v>
+      </c>
+      <c r="B1067" s="12" t="s">
+        <v>555</v>
+      </c>
+      <c r="C1067" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1067, ""en"", ""ta"")"),"சான்று ஆவணங்கள்")</f>
+        <v>சான்று ஆவணங்கள்</v>
+      </c>
+      <c r="D1067" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1067, ""en"", ""hi"")"),"प्रमाण दस्तावेज़")</f>
+        <v>प्रमाण दस्तावेज़</v>
+      </c>
+      <c r="E1067" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1067, ""en"", ""kn"")"),"ಪುರಾವೆ ದಾಖಲೆಗಳು")</f>
+        <v>ಪುರಾವೆ ದಾಖಲೆಗಳು</v>
+      </c>
+      <c r="F1067" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1067, ""en"", ""ml"")"),"തെളിവ് രേഖകൾ")</f>
+        <v>തെളിവ് രേഖകൾ</v>
+      </c>
+      <c r="G1067" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1067, ""en"", ""te"")"),"రుజువు పత్రాలు")</f>
+        <v>రుజువు పత్రాలు</v>
+      </c>
     </row>
     <row r="1068">
-      <c r="A1068" s="4"/>
-      <c r="B1068" s="5"/>
-      <c r="C1068" s="6"/>
-      <c r="D1068" s="6"/>
-      <c r="E1068" s="6"/>
+      <c r="A1068" s="14" t="s">
+        <v>2611</v>
+      </c>
+      <c r="B1068" s="18" t="s">
+        <v>2612</v>
+      </c>
+      <c r="C1068" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1068, ""en"", ""ta"")"),"ஆவண மையம்")</f>
+        <v>ஆவண மையம்</v>
+      </c>
+      <c r="D1068" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1068, ""en"", ""hi"")"),"दस्तावेज़ केंद्र")</f>
+        <v>दस्तावेज़ केंद्र</v>
+      </c>
+      <c r="E1068" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1068, ""en"", ""kn"")"),"ಡಾಕ್ಯುಮೆಂಟ್ ಸೆಂಟರ್")</f>
+        <v>ಡಾಕ್ಯುಮೆಂಟ್ ಸೆಂಟರ್</v>
+      </c>
+      <c r="F1068" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1068, ""en"", ""ml"")"),"ഡോക്യുമെന്റ് സെന്റർ")</f>
+        <v>ഡോക്യുമെന്റ് സെന്റർ</v>
+      </c>
+      <c r="G1068" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1068, ""en"", ""te"")"),"డాక్యుమెంట్ సెంటర్")</f>
+        <v>డాక్యుమెంట్ సెంటర్</v>
+      </c>
     </row>
     <row r="1069">
-      <c r="A1069" s="4"/>
-      <c r="B1069" s="5"/>
-      <c r="C1069" s="6"/>
-      <c r="D1069" s="6"/>
-      <c r="E1069" s="6"/>
+      <c r="A1069" s="11" t="s">
+        <v>2613</v>
+      </c>
+      <c r="B1069" s="19" t="s">
+        <v>2614</v>
+      </c>
+      <c r="C1069" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1069, ""en"", ""ta"")"),"இந்தப் படிகளை முடிக்கவும், இதன் மூலம் நீங்கள் சவாரிகளை ஏற்றுக்கொள்ளத் தொடங்கலாம்.")</f>
+        <v>இந்தப் படிகளை முடிக்கவும், இதன் மூலம் நீங்கள் சவாரிகளை ஏற்றுக்கொள்ளத் தொடங்கலாம்.</v>
+      </c>
+      <c r="D1069" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1069, ""en"", ""hi"")"),"इन चरणों को पूरा करें ताकि आप सवारी स्वीकार करना शुरू कर सकें।")</f>
+        <v>इन चरणों को पूरा करें ताकि आप सवारी स्वीकार करना शुरू कर सकें।</v>
+      </c>
+      <c r="E1069" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1069, ""en"", ""kn"")"),"ಈ ಹಂತಗಳನ್ನು ಪೂರ್ಣಗೊಳಿಸಿ ಇದರಿಂದ ನೀವು ಸವಾರಿಗಳನ್ನು ಸ್ವೀಕರಿಸಲು ಪ್ರಾರಂಭಿಸಬಹುದು.")</f>
+        <v>ಈ ಹಂತಗಳನ್ನು ಪೂರ್ಣಗೊಳಿಸಿ ಇದರಿಂದ ನೀವು ಸವಾರಿಗಳನ್ನು ಸ್ವೀಕರಿಸಲು ಪ್ರಾರಂಭಿಸಬಹುದು.</v>
+      </c>
+      <c r="F1069" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1069, ""en"", ""ml"")"),"റൈഡുകൾ സ്വീകരിക്കാൻ തുടങ്ങുന്നതിന് ഈ ഘട്ടങ്ങൾ പൂർത്തിയാക്കുക.")</f>
+        <v>റൈഡുകൾ സ്വീകരിക്കാൻ തുടങ്ങുന്നതിന് ഈ ഘട്ടങ്ങൾ പൂർത്തിയാക്കുക.</v>
+      </c>
+      <c r="G1069" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1069, ""en"", ""te"")"),"ఈ దశలను పూర్తి చేయండి, తద్వారా మీరు రైడ్‌లను అంగీకరించడం ప్రారంభించవచ్చు.")</f>
+        <v>ఈ దశలను పూర్తి చేయండి, తద్వారా మీరు రైడ్‌లను అంగీకరించడం ప్రారంభించవచ్చు.</v>
+      </c>
     </row>
     <row r="1070">
-      <c r="A1070" s="4"/>
-      <c r="B1070" s="5"/>
-      <c r="C1070" s="6"/>
-      <c r="D1070" s="6"/>
-      <c r="E1070" s="6"/>
+      <c r="A1070" s="11" t="s">
+        <v>2615</v>
+      </c>
+      <c r="B1070" s="19" t="s">
+        <v>2616</v>
+      </c>
+      <c r="C1070" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1070, ""en"", ""ta"")"),"தயவுசெய்து செல்லுபடியாகும் தொலைபேசி எண்ணை உள்ளிடவும்.")</f>
+        <v>தயவுசெய்து செல்லுபடியாகும் தொலைபேசி எண்ணை உள்ளிடவும்.</v>
+      </c>
+      <c r="D1070" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1070, ""en"", ""hi"")"),"कृपया मान्य फ़ोन नंबर दर्ज करें")</f>
+        <v>कृपया मान्य फ़ोन नंबर दर्ज करें</v>
+      </c>
+      <c r="E1070" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1070, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ಮಾನ್ಯವಾದ ಫೋನ್ ಸಂಖ್ಯೆಯನ್ನು ನಮೂದಿಸಿ.")</f>
+        <v>ದಯವಿಟ್ಟು ಮಾನ್ಯವಾದ ಫೋನ್ ಸಂಖ್ಯೆಯನ್ನು ನಮೂದಿಸಿ.</v>
+      </c>
+      <c r="F1070" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1070, ""en"", ""ml"")"),"ദയവായി സാധുവായ ഫോൺ നമ്പർ നൽകുക.")</f>
+        <v>ദയവായി സാധുവായ ഫോൺ നമ്പർ നൽകുക.</v>
+      </c>
+      <c r="G1070" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1070, ""en"", ""te"")"),"దయచేసి చెల్లుబాటు అయ్యే ఫోన్ నంబర్‌ను నమోదు చేయండి.")</f>
+        <v>దయచేసి చెల్లుబాటు అయ్యే ఫోన్ నంబర్‌ను నమోదు చేయండి.</v>
+      </c>
     </row>
     <row r="1071">
-      <c r="A1071" s="4"/>
-      <c r="B1071" s="5"/>
-      <c r="C1071" s="6"/>
-      <c r="D1071" s="6"/>
-      <c r="E1071" s="6"/>
+      <c r="A1071" s="11" t="s">
+        <v>2617</v>
+      </c>
+      <c r="B1071" s="19" t="s">
+        <v>2618</v>
+      </c>
+      <c r="C1071" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1071, ""en"", ""ta"")"),"உரிம எண் கண்டறியப்பட்டு தானாகவே நிரப்பப்பட்டது.")</f>
+        <v>உரிம எண் கண்டறியப்பட்டு தானாகவே நிரப்பப்பட்டது.</v>
+      </c>
+      <c r="D1071" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1071, ""en"", ""hi"")"),"लाइसेंस नंबर का पता लगाकर उसे स्वचालित रूप से भर दिया गया।")</f>
+        <v>लाइसेंस नंबर का पता लगाकर उसे स्वचालित रूप से भर दिया गया।</v>
+      </c>
+      <c r="E1071" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1071, ""en"", ""kn"")"),"ಪರವಾನಗಿ ಸಂಖ್ಯೆಯನ್ನು ಪತ್ತೆಹಚ್ಚಲಾಗಿದೆ ಮತ್ತು ಸ್ವಯಂಚಾಲಿತವಾಗಿ ಭರ್ತಿ ಮಾಡಲಾಗಿದೆ.")</f>
+        <v>ಪರವಾನಗಿ ಸಂಖ್ಯೆಯನ್ನು ಪತ್ತೆಹಚ್ಚಲಾಗಿದೆ ಮತ್ತು ಸ್ವಯಂಚಾಲಿತವಾಗಿ ಭರ್ತಿ ಮಾಡಲಾಗಿದೆ.</v>
+      </c>
+      <c r="F1071" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1071, ""en"", ""ml"")"),"ലൈസൻസ് നമ്പർ കണ്ടെത്തി സ്വയമേവ പൂരിപ്പിക്കുന്നു.")</f>
+        <v>ലൈസൻസ് നമ്പർ കണ്ടെത്തി സ്വയമേവ പൂരിപ്പിക്കുന്നു.</v>
+      </c>
+      <c r="G1071" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1071, ""en"", ""te"")"),"లైసెన్స్ నంబర్ గుర్తించబడింది మరియు స్వయంచాలకంగా నింపబడుతుంది.")</f>
+        <v>లైసెన్స్ నంబర్ గుర్తించబడింది మరియు స్వయంచాలకంగా నింపబడుతుంది.</v>
+      </c>
     </row>
     <row r="1072">
-      <c r="A1072" s="4"/>
-      <c r="B1072" s="5"/>
-      <c r="C1072" s="6"/>
-      <c r="D1072" s="6"/>
-      <c r="E1072" s="6"/>
+      <c r="A1072" s="11" t="s">
+        <v>2619</v>
+      </c>
+      <c r="B1072" s="19" t="s">
+        <v>2620</v>
+      </c>
+      <c r="C1072" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1072, ""en"", ""ta"")"),"பிறந்த தேதி கண்டறியப்பட்டு தானாகவே நிரப்பப்படும்.")</f>
+        <v>பிறந்த தேதி கண்டறியப்பட்டு தானாகவே நிரப்பப்படும்.</v>
+      </c>
+      <c r="D1072" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1072, ""en"", ""hi"")"),"जन्म तिथि का पता लगाकर उसे स्वचालित रूप से भर दिया जाता है।")</f>
+        <v>जन्म तिथि का पता लगाकर उसे स्वचालित रूप से भर दिया जाता है।</v>
+      </c>
+      <c r="E1072" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1072, ""en"", ""kn"")"),"ಜನ್ಮ ದಿನಾಂಕವನ್ನು ಪತ್ತೆಹಚ್ಚಲಾಗುತ್ತದೆ ಮತ್ತು ಸ್ವಯಂಚಾಲಿತವಾಗಿ ಭರ್ತಿ ಮಾಡಲಾಗುತ್ತದೆ.")</f>
+        <v>ಜನ್ಮ ದಿನಾಂಕವನ್ನು ಪತ್ತೆಹಚ್ಚಲಾಗುತ್ತದೆ ಮತ್ತು ಸ್ವಯಂಚಾಲಿತವಾಗಿ ಭರ್ತಿ ಮಾಡಲಾಗುತ್ತದೆ.</v>
+      </c>
+      <c r="F1072" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1072, ""en"", ""ml"")"),"ജനനത്തീയതി കണ്ടെത്തി സ്വയമേവ പൂരിപ്പിക്കുന്നു.")</f>
+        <v>ജനനത്തീയതി കണ്ടെത്തി സ്വയമേവ പൂരിപ്പിക്കുന്നു.</v>
+      </c>
+      <c r="G1072" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1072, ""en"", ""te"")"),"పుట్టిన తేదీ గుర్తించబడింది మరియు స్వయంచాలకంగా నింపబడుతుంది.")</f>
+        <v>పుట్టిన తేదీ గుర్తించబడింది మరియు స్వయంచాలకంగా నింపబడుతుంది.</v>
+      </c>
     </row>
     <row r="1073">
-      <c r="A1073" s="4"/>
-      <c r="B1073" s="5"/>
-      <c r="C1073" s="6"/>
-      <c r="D1073" s="6"/>
-      <c r="E1073" s="6"/>
+      <c r="A1073" s="11" t="s">
+        <v>2621</v>
+      </c>
+      <c r="B1073" s="12" t="s">
+        <v>2622</v>
+      </c>
+      <c r="C1073" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1073, ""en"", ""ta"")"),"உரிம விவரங்களைக் கண்டறிய முடியவில்லை. புலங்களை கைமுறையாகப் புதுப்பிக்கவும்.")</f>
+        <v>உரிம விவரங்களைக் கண்டறிய முடியவில்லை. புலங்களை கைமுறையாகப் புதுப்பிக்கவும்.</v>
+      </c>
+      <c r="D1073" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1073, ""en"", ""hi"")"),"लाइसेंस संबंधी जानकारी नहीं मिल पाई। कृपया फ़ील्ड को मैन्युअल रूप से अपडेट करें।")</f>
+        <v>लाइसेंस संबंधी जानकारी नहीं मिल पाई। कृपया फ़ील्ड को मैन्युअल रूप से अपडेट करें।</v>
+      </c>
+      <c r="E1073" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1073, ""en"", ""kn"")"),"ಪರವಾನಗಿ ವಿವರಗಳನ್ನು ಪತ್ತೆಹಚ್ಚಲು ಸಾಧ್ಯವಾಗಲಿಲ್ಲ. ಕ್ಷೇತ್ರಗಳನ್ನು ಹಸ್ತಚಾಲಿತವಾಗಿ ನವೀಕರಿಸಿ.")</f>
+        <v>ಪರವಾನಗಿ ವಿವರಗಳನ್ನು ಪತ್ತೆಹಚ್ಚಲು ಸಾಧ್ಯವಾಗಲಿಲ್ಲ. ಕ್ಷೇತ್ರಗಳನ್ನು ಹಸ್ತಚಾಲಿತವಾಗಿ ನವೀಕರಿಸಿ.</v>
+      </c>
+      <c r="F1073" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1073, ""en"", ""ml"")"),"ലൈസൻസ് വിശദാംശങ്ങൾ കണ്ടെത്താനായില്ല. ഫീൽഡുകൾ നേരിട്ട് അപ്‌ഡേറ്റ് ചെയ്യുക.")</f>
+        <v>ലൈസൻസ് വിശദാംശങ്ങൾ കണ്ടെത്താനായില്ല. ഫീൽഡുകൾ നേരിട്ട് അപ്‌ഡേറ്റ് ചെയ്യുക.</v>
+      </c>
+      <c r="G1073" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1073, ""en"", ""te"")"),"లైసెన్స్ వివరాలను గుర్తించలేకపోయాము. ఫీల్డ్‌లను మాన్యువల్‌గా అప్‌డేట్ చేయండి.")</f>
+        <v>లైసెన్స్ వివరాలను గుర్తించలేకపోయాము. ఫీల్డ్‌లను మాన్యువల్‌గా అప్‌డేట్ చేయండి.</v>
+      </c>
     </row>
     <row r="1074">
-      <c r="A1074" s="4"/>
-      <c r="B1074" s="5"/>
-      <c r="C1074" s="6"/>
-      <c r="D1074" s="6"/>
-      <c r="E1074" s="6"/>
+      <c r="A1074" s="11" t="s">
+        <v>2623</v>
+      </c>
+      <c r="B1074" s="12" t="s">
+        <v>2624</v>
+      </c>
+      <c r="C1074" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1074, ""en"", ""ta"")"),"பிறந்த தேதியை உள்ளிடவும்.")</f>
+        <v>பிறந்த தேதியை உள்ளிடவும்.</v>
+      </c>
+      <c r="D1074" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1074, ""en"", ""hi"")"),"कृपया जन्मतिथि दर्ज करें")</f>
+        <v>कृपया जन्मतिथि दर्ज करें</v>
+      </c>
+      <c r="E1074" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1074, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ಜನ್ಮ ದಿನಾಂಕವನ್ನು ನಮೂದಿಸಿ.")</f>
+        <v>ದಯವಿಟ್ಟು ಜನ್ಮ ದಿನಾಂಕವನ್ನು ನಮೂದಿಸಿ.</v>
+      </c>
+      <c r="F1074" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1074, ""en"", ""ml"")"),"ദയവായി ജനനത്തീയതി നൽകുക.")</f>
+        <v>ദയവായി ജനനത്തീയതി നൽകുക.</v>
+      </c>
+      <c r="G1074" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1074, ""en"", ""te"")"),"దయచేసి పుట్టిన తేదీని నమోదు చేయండి.")</f>
+        <v>దయచేసి పుట్టిన తేదీని నమోదు చేయండి.</v>
+      </c>
     </row>
     <row r="1075">
-      <c r="A1075" s="4"/>
-      <c r="B1075" s="5"/>
-      <c r="C1075" s="6"/>
-      <c r="D1075" s="6"/>
-      <c r="E1075" s="6"/>
+      <c r="A1075" s="11" t="s">
+        <v>2625</v>
+      </c>
+      <c r="B1075" s="12" t="s">
+        <v>2626</v>
+      </c>
+      <c r="C1075" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1075, ""en"", ""ta"")"),"தொடர்வதற்கு முன் ஓட்டுநர் புகைப்படத்தைப் பதிவேற்றவும்.")</f>
+        <v>தொடர்வதற்கு முன் ஓட்டுநர் புகைப்படத்தைப் பதிவேற்றவும்.</v>
+      </c>
+      <c r="D1075" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1075, ""en"", ""hi"")"),"आगे बढ़ने से पहले ड्राइवर की फोटो अपलोड करें।")</f>
+        <v>आगे बढ़ने से पहले ड्राइवर की फोटो अपलोड करें।</v>
+      </c>
+      <c r="E1075" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1075, ""en"", ""kn"")"),"ಮುಂದುವರಿಯುವ ಮೊದಲು ಚಾಲಕ ಫೋಟೋವನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ.")</f>
+        <v>ಮುಂದುವರಿಯುವ ಮೊದಲು ಚಾಲಕ ಫೋಟೋವನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ.</v>
+      </c>
+      <c r="F1075" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1075, ""en"", ""ml"")"),"തുടരുന്നതിന് മുമ്പ് ഡ്രൈവർ ഫോട്ടോ അപ്‌ലോഡ് ചെയ്യുക.")</f>
+        <v>തുടരുന്നതിന് മുമ്പ് ഡ്രൈവർ ഫോട്ടോ അപ്‌ലോഡ് ചെയ്യുക.</v>
+      </c>
+      <c r="G1075" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1075, ""en"", ""te"")"),"కొనసాగే ముందు డ్రైవర్ ఫోటోను అప్‌లోడ్ చేయండి.")</f>
+        <v>కొనసాగే ముందు డ్రైవర్ ఫోటోను అప్‌లోడ్ చేయండి.</v>
+      </c>
     </row>
     <row r="1076">
-      <c r="A1076" s="4"/>
-      <c r="B1076" s="5"/>
-      <c r="C1076" s="6"/>
-      <c r="D1076" s="6"/>
-      <c r="E1076" s="6"/>
+      <c r="A1076" s="11" t="s">
+        <v>2627</v>
+      </c>
+      <c r="B1076" s="12" t="s">
+        <v>2628</v>
+      </c>
+      <c r="C1076" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1076, ""en"", ""ta"")"),"தொடர்வதற்கு முன் ஓட்டுநர் உரிமத்தைப் பதிவேற்றவும்.")</f>
+        <v>தொடர்வதற்கு முன் ஓட்டுநர் உரிமத்தைப் பதிவேற்றவும்.</v>
+      </c>
+      <c r="D1076" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1076, ""en"", ""hi"")"),"आगे बढ़ने से पहले ड्राइविंग लाइसेंस अपलोड करें।")</f>
+        <v>आगे बढ़ने से पहले ड्राइविंग लाइसेंस अपलोड करें।</v>
+      </c>
+      <c r="E1076" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1076, ""en"", ""kn"")"),"ಮುಂದುವರಿಯುವ ಮೊದಲು ಚಾಲನಾ ಪರವಾನಗಿಯನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ.")</f>
+        <v>ಮುಂದುವರಿಯುವ ಮೊದಲು ಚಾಲನಾ ಪರವಾನಗಿಯನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ.</v>
+      </c>
+      <c r="F1076" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1076, ""en"", ""ml"")"),"തുടരുന്നതിന് മുമ്പ് ഡ്രൈവിംഗ് ലൈസൻസ് അപ്‌ലോഡ് ചെയ്യുക.")</f>
+        <v>തുടരുന്നതിന് മുമ്പ് ഡ്രൈവിംഗ് ലൈസൻസ് അപ്‌ലോഡ് ചെയ്യുക.</v>
+      </c>
+      <c r="G1076" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1076, ""en"", ""te"")"),"కొనసాగే ముందు డ్రైవింగ్ లైసెన్స్‌ను అప్‌లోడ్ చేయండి.")</f>
+        <v>కొనసాగే ముందు డ్రైవింగ్ లైసెన్స్‌ను అప్‌లోడ్ చేయండి.</v>
+      </c>
     </row>
     <row r="1077">
-      <c r="A1077" s="4"/>
-      <c r="B1077" s="5"/>
-      <c r="C1077" s="6"/>
-      <c r="D1077" s="6"/>
-      <c r="E1077" s="6"/>
+      <c r="A1077" s="11" t="s">
+        <v>2629</v>
+      </c>
+      <c r="B1077" s="12" t="s">
+        <v>2630</v>
+      </c>
+      <c r="C1077" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1077, ""en"", ""ta"")"),"ஓட்டுநரின் தெளிவான சமீபத்திய புகைப்படத்தைப் பதிவேற்றவும் அல்லது பிடிக்கவும்.")</f>
+        <v>ஓட்டுநரின் தெளிவான சமீபத்திய புகைப்படத்தைப் பதிவேற்றவும் அல்லது பிடிக்கவும்.</v>
+      </c>
+      <c r="D1077" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1077, ""en"", ""hi"")"),"ड्राइवर की हाल ही की स्पष्ट तस्वीर अपलोड करें या खींचकर भेजें।")</f>
+        <v>ड्राइवर की हाल ही की स्पष्ट तस्वीर अपलोड करें या खींचकर भेजें।</v>
+      </c>
+      <c r="E1077" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1077, ""en"", ""kn"")"),"ಚಾಲಕನ ಇತ್ತೀಚಿನ ಸ್ಪಷ್ಟ ಫೋಟೋವನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ.")</f>
+        <v>ಚಾಲಕನ ಇತ್ತೀಚಿನ ಸ್ಪಷ್ಟ ಫೋಟೋವನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ.</v>
+      </c>
+      <c r="F1077" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1077, ""en"", ""ml"")"),"ഡ്രൈവറുടെ വ്യക്തമായ ഒരു സമീപകാല ഫോട്ടോ അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ പകർത്തുക.")</f>
+        <v>ഡ്രൈവറുടെ വ്യക്തമായ ഒരു സമീപകാല ഫോട്ടോ അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ പകർത്തുക.</v>
+      </c>
+      <c r="G1077" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1077, ""en"", ""te"")"),"డ్రైవర్ యొక్క స్పష్టమైన ఇటీవలి ఫోటోను అప్‌లోడ్ చేయండి లేదా క్యాప్చర్ చేయండి.")</f>
+        <v>డ్రైవర్ యొక్క స్పష్టమైన ఇటీవలి ఫోటోను అప్‌లోడ్ చేయండి లేదా క్యాప్చర్ చేయండి.</v>
+      </c>
     </row>
     <row r="1078">
-      <c r="A1078" s="4"/>
-      <c r="B1078" s="5"/>
-      <c r="C1078" s="6"/>
-      <c r="D1078" s="6"/>
-      <c r="E1078" s="6"/>
+      <c r="A1078" s="11" t="s">
+        <v>2631</v>
+      </c>
+      <c r="B1078" s="12" t="s">
+        <v>2632</v>
+      </c>
+      <c r="C1078" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1078, ""en"", ""ta"")"),"இந்த பயன்முறையில் திருத்துதல் முடக்கப்பட்டுள்ளது.")</f>
+        <v>இந்த பயன்முறையில் திருத்துதல் முடக்கப்பட்டுள்ளது.</v>
+      </c>
+      <c r="D1078" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1078, ""en"", ""hi"")"),"इस मोड में संपादन की सुविधा अक्षम है।")</f>
+        <v>इस मोड में संपादन की सुविधा अक्षम है।</v>
+      </c>
+      <c r="E1078" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1078, ""en"", ""kn"")"),"ಈ ಕ್ರಮದಲ್ಲಿ ಸಂಪಾದನೆಯನ್ನು ನಿಷ್ಕ್ರಿಯಗೊಳಿಸಲಾಗಿದೆ.")</f>
+        <v>ಈ ಕ್ರಮದಲ್ಲಿ ಸಂಪಾದನೆಯನ್ನು ನಿಷ್ಕ್ರಿಯಗೊಳಿಸಲಾಗಿದೆ.</v>
+      </c>
+      <c r="F1078" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1078, ""en"", ""ml"")"),"ഈ മോഡിൽ എഡിറ്റിംഗ് അപ്രാപ്തമാക്കിയിരിക്കുന്നു.")</f>
+        <v>ഈ മോഡിൽ എഡിറ്റിംഗ് അപ്രാപ്തമാക്കിയിരിക്കുന്നു.</v>
+      </c>
+      <c r="G1078" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1078, ""en"", ""te"")"),"ఈ మోడ్‌లో సవరణ నిలిపివేయబడింది.")</f>
+        <v>ఈ మోడ్‌లో సవరణ నిలిపివేయబడింది.</v>
+      </c>
     </row>
     <row r="1079">
-      <c r="A1079" s="4"/>
-      <c r="B1079" s="5"/>
-      <c r="C1079" s="6"/>
-      <c r="D1079" s="6"/>
-      <c r="E1079" s="6"/>
+      <c r="A1079" s="11" t="s">
+        <v>2633</v>
+      </c>
+      <c r="B1079" s="12" t="s">
+        <v>2634</v>
+      </c>
+      <c r="C1079" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1079, ""en"", ""ta"")"),"சொல்ல வேண்டாம்னு ஆசைப்படுறேன்.")</f>
+        <v>சொல்ல வேண்டாம்னு ஆசைப்படுறேன்.</v>
+      </c>
+      <c r="D1079" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1079, ""en"", ""hi"")"),"नहीं कहना पसंद करते हैं")</f>
+        <v>नहीं कहना पसंद करते हैं</v>
+      </c>
+      <c r="E1079" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1079, ""en"", ""kn"")"),"ಹೇಳಲು ಇಷ್ಟಪಡುವುದಿಲ್ಲ")</f>
+        <v>ಹೇಳಲು ಇಷ್ಟಪಡುವುದಿಲ್ಲ</v>
+      </c>
+      <c r="F1079" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1079, ""en"", ""ml"")"),"പറയാതിരിക്കാൻ ഇഷ്ടപ്പെടുന്നു")</f>
+        <v>പറയാതിരിക്കാൻ ഇഷ്ടപ്പെടുന്നു</v>
+      </c>
+      <c r="G1079" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1079, ""en"", ""te"")"),"చెప్పకూడదని కోరుకుంటున్నాను")</f>
+        <v>చెప్పకూడదని కోరుకుంటున్నాను</v>
+      </c>
     </row>
     <row r="1080">
-      <c r="A1080" s="8"/>
-      <c r="B1080" s="9"/>
-      <c r="C1080" s="6"/>
-      <c r="D1080" s="6"/>
-      <c r="E1080" s="6"/>
+      <c r="A1080" s="20" t="s">
+        <v>2635</v>
+      </c>
+      <c r="B1080" s="21" t="s">
+        <v>2636</v>
+      </c>
+      <c r="C1080" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1080, ""en"", ""ta"")"),"வாகன ஆர்.சி.")</f>
+        <v>வாகன ஆர்.சி.</v>
+      </c>
+      <c r="D1080" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1080, ""en"", ""hi"")"),"वाहन आरसी")</f>
+        <v>वाहन आरसी</v>
+      </c>
+      <c r="E1080" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1080, ""en"", ""kn"")"),"ವಾಹನ ಆರ್‌ಸಿ")</f>
+        <v>ವಾಹನ ಆರ್‌ಸಿ</v>
+      </c>
+      <c r="F1080" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1080, ""en"", ""ml"")"),"വാഹന ആർസി")</f>
+        <v>വാഹന ആർസി</v>
+      </c>
+      <c r="G1080" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1080, ""en"", ""te"")"),"వాహన RC")</f>
+        <v>వాహన RC</v>
+      </c>
     </row>
     <row r="1081">
-      <c r="A1081" s="8"/>
-      <c r="B1081" s="6"/>
-      <c r="C1081" s="6"/>
-      <c r="D1081" s="6"/>
-      <c r="E1081" s="6"/>
+      <c r="A1081" s="20" t="s">
+        <v>2637</v>
+      </c>
+      <c r="B1081" s="15" t="s">
+        <v>2638</v>
+      </c>
+      <c r="C1081" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1081, ""en"", ""ta"")"),"பதிவு எண்ணை தானாகவே கண்டறிய வாகன RC-ஐ பதிவேற்றவும் அல்லது பிடிக்கவும்.")</f>
+        <v>பதிவு எண்ணை தானாகவே கண்டறிய வாகன RC-ஐ பதிவேற்றவும் அல்லது பிடிக்கவும்.</v>
+      </c>
+      <c r="D1081" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1081, ""en"", ""hi"")"),"वाहन की आरसी अपलोड करें या कैप्चर करें ताकि पंजीकरण संख्या स्वचालित रूप से पता चल सके।")</f>
+        <v>वाहन की आरसी अपलोड करें या कैप्चर करें ताकि पंजीकरण संख्या स्वचालित रूप से पता चल सके।</v>
+      </c>
+      <c r="E1081" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1081, ""en"", ""kn"")"),"ನೋಂದಣಿ ಸಂಖ್ಯೆಯನ್ನು ಸ್ವಯಂಚಾಲಿತವಾಗಿ ಪತ್ತೆಹಚ್ಚಲು ವಾಹನದ ಆರ್‌ಸಿಯನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ.")</f>
+        <v>ನೋಂದಣಿ ಸಂಖ್ಯೆಯನ್ನು ಸ್ವಯಂಚಾಲಿತವಾಗಿ ಪತ್ತೆಹಚ್ಚಲು ವಾಹನದ ಆರ್‌ಸಿಯನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ.</v>
+      </c>
+      <c r="F1081" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1081, ""en"", ""ml"")"),"രജിസ്ട്രേഷൻ നമ്പർ സ്വയമേവ കണ്ടെത്തുന്നതിന് വാഹന ആർസി അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ ക്യാപ്‌ചർ ചെയ്യുക.")</f>
+        <v>രജിസ്ട്രേഷൻ നമ്പർ സ്വയമേവ കണ്ടെത്തുന്നതിന് വാഹന ആർസി അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ ക്യാപ്‌ചർ ചെയ്യുക.</v>
+      </c>
+      <c r="G1081" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1081, ""en"", ""te"")"),"రిజిస్ట్రేషన్ నంబర్‌ను స్వయంచాలకంగా గుర్తించడానికి వాహన RCని అప్‌లోడ్ చేయండి లేదా సంగ్రహించండి.")</f>
+        <v>రిజిస్ట్రేషన్ నంబర్‌ను స్వయంచాలకంగా గుర్తించడానికి వాహన RCని అప్‌లోడ్ చేయండి లేదా సంగ్రహించండి.</v>
+      </c>
     </row>
     <row r="1082">
-      <c r="A1082" s="8"/>
-      <c r="B1082" s="6"/>
-      <c r="C1082" s="6"/>
-      <c r="D1082" s="6"/>
-      <c r="E1082" s="6"/>
+      <c r="A1082" s="20" t="s">
+        <v>2639</v>
+      </c>
+      <c r="B1082" s="15" t="s">
+        <v>2640</v>
+      </c>
+      <c r="C1082" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1082, ""en"", ""ta"")"),"வாகன RC-ஐ பதிவேற்றவும் அல்லது பிடிக்கவும்")</f>
+        <v>வாகன RC-ஐ பதிவேற்றவும் அல்லது பிடிக்கவும்</v>
+      </c>
+      <c r="D1082" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1082, ""en"", ""hi"")"),"वाहन आरसी अपलोड करें या कैप्चर करें")</f>
+        <v>वाहन आरसी अपलोड करें या कैप्चर करें</v>
+      </c>
+      <c r="E1082" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1082, ""en"", ""kn"")"),"ವಾಹನ ಆರ್‌ಸಿಯನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ")</f>
+        <v>ವಾಹನ ಆರ್‌ಸಿಯನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ</v>
+      </c>
+      <c r="F1082" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1082, ""en"", ""ml"")"),"വാഹന RC അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ പിടിച്ചെടുക്കുക")</f>
+        <v>വാഹന RC അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ പിടിച്ചെടുക്കുക</v>
+      </c>
+      <c r="G1082" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1082, ""en"", ""te"")"),"వాహన RCని అప్‌లోడ్ చేయండి లేదా సంగ్రహించండి")</f>
+        <v>వాహన RCని అప్‌లోడ్ చేయండి లేదా సంగ్రహించండి</v>
+      </c>
     </row>
     <row r="1083">
-      <c r="A1083" s="8"/>
-      <c r="B1083" s="6"/>
-      <c r="C1083" s="6"/>
-      <c r="D1083" s="6"/>
-      <c r="E1083" s="6"/>
+      <c r="A1083" s="20" t="s">
+        <v>2641</v>
+      </c>
+      <c r="B1083" s="15" t="s">
+        <v>2642</v>
+      </c>
+      <c r="C1083" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1083, ""en"", ""ta"")"),"ஆதார் அட்டை")</f>
+        <v>ஆதார் அட்டை</v>
+      </c>
+      <c r="D1083" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1083, ""en"", ""hi"")"),"आधार कार्ड")</f>
+        <v>आधार कार्ड</v>
+      </c>
+      <c r="E1083" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1083, ""en"", ""kn"")"),"ಆಧಾರ್ ಕಾರ್ಡ್")</f>
+        <v>ಆಧಾರ್ ಕಾರ್ಡ್</v>
+      </c>
+      <c r="F1083" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1083, ""en"", ""ml"")"),"ആധാർ കാർഡ്")</f>
+        <v>ആധാർ കാർഡ്</v>
+      </c>
+      <c r="G1083" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1083, ""en"", ""te"")"),"ఆధార్ కార్డు")</f>
+        <v>ఆధార్ కార్డు</v>
+      </c>
     </row>
     <row r="1084">
-      <c r="A1084" s="8"/>
-      <c r="B1084" s="6"/>
-      <c r="C1084" s="6"/>
-      <c r="D1084" s="6"/>
-      <c r="E1084" s="6"/>
+      <c r="A1084" s="20" t="s">
+        <v>2643</v>
+      </c>
+      <c r="B1084" s="15" t="s">
+        <v>2644</v>
+      </c>
+      <c r="C1084" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1084, ""en"", ""ta"")"),"விவரங்கள் தானாகவே கண்டறியப்பட்டன. சமர்ப்பிக்கும் முன் மதிப்பாய்வு செய்யவும்.")</f>
+        <v>விவரங்கள் தானாகவே கண்டறியப்பட்டன. சமர்ப்பிக்கும் முன் மதிப்பாய்வு செய்யவும்.</v>
+      </c>
+      <c r="D1084" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1084, ""en"", ""hi"")"),"विवरण स्वचालित रूप से पता लगा लिया गया है। सबमिट करने से पहले समीक्षा करें।")</f>
+        <v>विवरण स्वचालित रूप से पता लगा लिया गया है। सबमिट करने से पहले समीक्षा करें।</v>
+      </c>
+      <c r="E1084" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1084, ""en"", ""kn"")"),"ವಿವರಗಳನ್ನು ಸ್ವಯಂಚಾಲಿತವಾಗಿ ಪತ್ತೆಹಚ್ಚಲಾಗಿದೆ. ಸಲ್ಲಿಸುವ ಮೊದಲು ಪರಿಶೀಲಿಸಿ.")</f>
+        <v>ವಿವರಗಳನ್ನು ಸ್ವಯಂಚಾಲಿತವಾಗಿ ಪತ್ತೆಹಚ್ಚಲಾಗಿದೆ. ಸಲ್ಲಿಸುವ ಮೊದಲು ಪರಿಶೀಲಿಸಿ.</v>
+      </c>
+      <c r="F1084" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1084, ""en"", ""ml"")"),"വിശദാംശങ്ങൾ സ്വയമേവ കണ്ടെത്തി. സമർപ്പിക്കുന്നതിന് മുമ്പ് അവലോകനം ചെയ്യുക.")</f>
+        <v>വിശദാംശങ്ങൾ സ്വയമേവ കണ്ടെത്തി. സമർപ്പിക്കുന്നതിന് മുമ്പ് അവലോകനം ചെയ്യുക.</v>
+      </c>
+      <c r="G1084" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1084, ""en"", ""te"")"),"వివరాలు స్వయంచాలకంగా గుర్తించబడ్డాయి. సమర్పించే ముందు సమీక్షించండి.")</f>
+        <v>వివరాలు స్వయంచాలకంగా గుర్తించబడ్డాయి. సమర్పించే ముందు సమీక్షించండి.</v>
+      </c>
     </row>
     <row r="1085">
-      <c r="A1085" s="10"/>
-      <c r="B1085" s="6"/>
-      <c r="C1085" s="6"/>
-      <c r="D1085" s="6"/>
-      <c r="E1085" s="6"/>
+      <c r="A1085" s="22" t="s">
+        <v>2645</v>
+      </c>
+      <c r="B1085" s="15" t="s">
+        <v>2646</v>
+      </c>
+      <c r="C1085" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1085, ""en"", ""ta"")"),"ஆதார் எண்ணைப் பிரித்தெடுக்க முடியவில்லை. புலத்தை கைமுறையாகப் புதுப்பிக்கவும்.")</f>
+        <v>ஆதார் எண்ணைப் பிரித்தெடுக்க முடியவில்லை. புலத்தை கைமுறையாகப் புதுப்பிக்கவும்.</v>
+      </c>
+      <c r="D1085" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1085, ""en"", ""hi"")"),"आधार नंबर नहीं निकाला जा सका। कृपया फ़ील्ड को मैन्युअल रूप से अपडेट करें।")</f>
+        <v>आधार नंबर नहीं निकाला जा सका। कृपया फ़ील्ड को मैन्युअल रूप से अपडेट करें।</v>
+      </c>
+      <c r="E1085" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1085, ""en"", ""kn"")"),"ಆಧಾರ್ ಸಂಖ್ಯೆಯನ್ನು ಹೊರತೆಗೆಯಲು ಸಾಧ್ಯವಾಗಲಿಲ್ಲ. ಕ್ಷೇತ್ರವನ್ನು ಹಸ್ತಚಾಲಿತವಾಗಿ ನವೀಕರಿಸಿ.")</f>
+        <v>ಆಧಾರ್ ಸಂಖ್ಯೆಯನ್ನು ಹೊರತೆಗೆಯಲು ಸಾಧ್ಯವಾಗಲಿಲ್ಲ. ಕ್ಷೇತ್ರವನ್ನು ಹಸ್ತಚಾಲಿತವಾಗಿ ನವೀಕರಿಸಿ.</v>
+      </c>
+      <c r="F1085" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1085, ""en"", ""ml"")"),"ആധാർ നമ്പർ വേർതിരിച്ചെടുക്കാൻ കഴിഞ്ഞില്ല. ഫീൽഡ് നേരിട്ട് അപ്ഡേറ്റ് ചെയ്യുക.")</f>
+        <v>ആധാർ നമ്പർ വേർതിരിച്ചെടുക്കാൻ കഴിഞ്ഞില്ല. ഫീൽഡ് നേരിട്ട് അപ്ഡേറ്റ് ചെയ്യുക.</v>
+      </c>
+      <c r="G1085" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1085, ""en"", ""te"")"),"ఆధార్ నంబర్‌ను సంగ్రహించడం సాధ్యం కాలేదు. ఫీల్డ్‌ను మాన్యువల్‌గా అప్‌డేట్ చేయండి.")</f>
+        <v>ఆధార్ నంబర్‌ను సంగ్రహించడం సాధ్యం కాలేదు. ఫీల్డ్‌ను మాన్యువల్‌గా అప్‌డేట్ చేయండి.</v>
+      </c>
     </row>
     <row r="1086">
-      <c r="A1086" s="8"/>
-      <c r="B1086" s="6"/>
-      <c r="C1086" s="6"/>
-      <c r="D1086" s="6"/>
-      <c r="E1086" s="6"/>
+      <c r="A1086" s="20" t="s">
+        <v>2647</v>
+      </c>
+      <c r="B1086" s="15" t="s">
+        <v>2648</v>
+      </c>
+      <c r="C1086" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1086, ""en"", ""ta"")"),"ஆவணத்தைப் பதிவேற்றுகிறது. காத்திருக்கவும்…")</f>
+        <v>ஆவணத்தைப் பதிவேற்றுகிறது. காத்திருக்கவும்…</v>
+      </c>
+      <c r="D1086" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1086, ""en"", ""hi"")"),"दस्तावेज़ अपलोड हो रहा है। कृपया प्रतीक्षा करें…")</f>
+        <v>दस्तावेज़ अपलोड हो रहा है। कृपया प्रतीक्षा करें…</v>
+      </c>
+      <c r="E1086" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1086, ""en"", ""kn"")"),"ಡಾಕ್ಯುಮೆಂಟ್ ಅಪ್‌ಲೋಡ್ ಮಾಡಲಾಗುತ್ತಿದೆ. ದಯವಿಟ್ಟು ನಿರೀಕ್ಷಿಸಿ…")</f>
+        <v>ಡಾಕ್ಯುಮೆಂಟ್ ಅಪ್‌ಲೋಡ್ ಮಾಡಲಾಗುತ್ತಿದೆ. ದಯವಿಟ್ಟು ನಿರೀಕ್ಷಿಸಿ…</v>
+      </c>
+      <c r="F1086" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1086, ""en"", ""ml"")"),"ഡോക്യുമെന്റ് അപ്‌ലോഡ് ചെയ്യുന്നു. ദയവായി കാത്തിരിക്കുക…")</f>
+        <v>ഡോക്യുമെന്റ് അപ്‌ലോഡ് ചെയ്യുന്നു. ദയവായി കാത്തിരിക്കുക…</v>
+      </c>
+      <c r="G1086" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1086, ""en"", ""te"")"),"పత్రాన్ని అప్‌లోడ్ చేస్తోంది. దయచేసి వేచి ఉండండి…")</f>
+        <v>పత్రాన్ని అప్‌లోడ్ చేస్తోంది. దయచేసి వేచి ఉండండి…</v>
+      </c>
     </row>
     <row r="1087">
-      <c r="A1087" s="8"/>
-      <c r="B1087" s="6"/>
-      <c r="C1087" s="6"/>
-      <c r="D1087" s="6"/>
-      <c r="E1087" s="6"/>
+      <c r="A1087" s="20" t="s">
+        <v>2649</v>
+      </c>
+      <c r="B1087" s="15" t="s">
+        <v>2650</v>
+      </c>
+      <c r="C1087" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1087, ""en"", ""ta"")"),"ஆவணம் தயாராக உள்ளது. அனுப்ப பதிவேற்று என்பதைத் தட்டவும்.")</f>
+        <v>ஆவணம் தயாராக உள்ளது. அனுப்ப பதிவேற்று என்பதைத் தட்டவும்.</v>
+      </c>
+      <c r="D1087" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1087, ""en"", ""hi"")"),"दस्तावेज़ तैयार है। भेजने के लिए अपलोड पर टैप करें।")</f>
+        <v>दस्तावेज़ तैयार है। भेजने के लिए अपलोड पर टैप करें।</v>
+      </c>
+      <c r="E1087" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1087, ""en"", ""kn"")"),"ಡಾಕ್ಯುಮೆಂಟ್ ಸಿದ್ಧವಾಗಿದೆ. ಕಳುಹಿಸಲು ಅಪ್‌ಲೋಡ್ ಟ್ಯಾಪ್ ಮಾಡಿ.")</f>
+        <v>ಡಾಕ್ಯುಮೆಂಟ್ ಸಿದ್ಧವಾಗಿದೆ. ಕಳುಹಿಸಲು ಅಪ್‌ಲೋಡ್ ಟ್ಯಾಪ್ ಮಾಡಿ.</v>
+      </c>
+      <c r="F1087" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1087, ""en"", ""ml"")"),"ഡോക്യുമെന്റ് തയ്യാറാണ്. അയയ്ക്കാൻ അപ്‌ലോഡ് ടാപ്പ് ചെയ്യുക.")</f>
+        <v>ഡോക്യുമെന്റ് തയ്യാറാണ്. അയയ്ക്കാൻ അപ്‌ലോഡ് ടാപ്പ് ചെയ്യുക.</v>
+      </c>
+      <c r="G1087" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1087, ""en"", ""te"")"),"పత్రం సిద్ధంగా ఉంది. పంపడానికి అప్‌లోడ్‌ను నొక్కండి.")</f>
+        <v>పత్రం సిద్ధంగా ఉంది. పంపడానికి అప్‌లోడ్‌ను నొక్కండి.</v>
+      </c>
     </row>
     <row r="1088">
-      <c r="A1088" s="8"/>
-      <c r="B1088" s="6"/>
-      <c r="C1088" s="6"/>
-      <c r="D1088" s="6"/>
-      <c r="E1088" s="6"/>
+      <c r="A1088" s="20" t="s">
+        <v>2651</v>
+      </c>
+      <c r="B1088" s="15" t="s">
+        <v>2652</v>
+      </c>
+      <c r="C1088" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1088, ""en"", ""ta"")"),"ஆதார் அல்லது பான் எண்ணைப் புதுப்பிக்கவும். குறைந்தது ஒரு செல்லுபடியாகும் ஆவணத்தையாவது வழங்கவும்.")</f>
+        <v>ஆதார் அல்லது பான் எண்ணைப் புதுப்பிக்கவும். குறைந்தது ஒரு செல்லுபடியாகும் ஆவணத்தையாவது வழங்கவும்.</v>
+      </c>
+      <c r="D1088" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1088, ""en"", ""hi"")"),"आधार या पैन कार्ड अपडेट करें। कम से कम एक वैध दस्तावेज प्रदान करें।")</f>
+        <v>आधार या पैन कार्ड अपडेट करें। कम से कम एक वैध दस्तावेज प्रदान करें।</v>
+      </c>
+      <c r="E1088" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1088, ""en"", ""kn"")"),"ಆಧಾರ್ ಅಥವಾ ಪ್ಯಾನ್ ಅನ್ನು ನವೀಕರಿಸಿ. ಕನಿಷ್ಠ ಒಂದು ಮಾನ್ಯ ದಾಖಲೆಯನ್ನು ಒದಗಿಸಿ.")</f>
+        <v>ಆಧಾರ್ ಅಥವಾ ಪ್ಯಾನ್ ಅನ್ನು ನವೀಕರಿಸಿ. ಕನಿಷ್ಠ ಒಂದು ಮಾನ್ಯ ದಾಖಲೆಯನ್ನು ಒದಗಿಸಿ.</v>
+      </c>
+      <c r="F1088" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1088, ""en"", ""ml"")"),"ആധാർ അല്ലെങ്കിൽ പാൻ അപ്ഡേറ്റ് ചെയ്യുക. കുറഞ്ഞത് ഒരു സാധുവായ രേഖയെങ്കിലും നൽകുക.")</f>
+        <v>ആധാർ അല്ലെങ്കിൽ പാൻ അപ്ഡേറ്റ് ചെയ്യുക. കുറഞ്ഞത് ഒരു സാധുവായ രേഖയെങ്കിലും നൽകുക.</v>
+      </c>
+      <c r="G1088" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1088, ""en"", ""te"")"),"ఆధార్ లేదా పాన్‌ను అప్‌డేట్ చేయండి. కనీసం ఒక చెల్లుబాటు అయ్యే పత్రాన్ని అందించండి.")</f>
+        <v>ఆధార్ లేదా పాన్‌ను అప్‌డేట్ చేయండి. కనీసం ఒక చెల్లుబాటు అయ్యే పత్రాన్ని అందించండి.</v>
+      </c>
     </row>
     <row r="1089">
-      <c r="A1089" s="8"/>
-      <c r="B1089" s="6"/>
-      <c r="C1089" s="6"/>
-      <c r="D1089" s="6"/>
-      <c r="E1089" s="6"/>
+      <c r="A1089" s="20" t="s">
+        <v>2653</v>
+      </c>
+      <c r="B1089" s="15" t="s">
+        <v>2654</v>
+      </c>
+      <c r="C1089" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1089, ""en"", ""ta"")"),"பாலினத்தைத் தேர்ந்தெடுக்கவும்.")</f>
+        <v>பாலினத்தைத் தேர்ந்தெடுக்கவும்.</v>
+      </c>
+      <c r="D1089" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1089, ""en"", ""hi"")"),"कृपया लिंग चुनें")</f>
+        <v>कृपया लिंग चुनें</v>
+      </c>
+      <c r="E1089" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1089, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ಲಿಂಗವನ್ನು ಆಯ್ಕೆಮಾಡಿ")</f>
+        <v>ದಯವಿಟ್ಟು ಲಿಂಗವನ್ನು ಆಯ್ಕೆಮಾಡಿ</v>
+      </c>
+      <c r="F1089" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1089, ""en"", ""ml"")"),"ദയവായി ലിംഗഭേദം തിരഞ്ഞെടുക്കുക.")</f>
+        <v>ദയവായി ലിംഗഭേദം തിരഞ്ഞെടുക്കുക.</v>
+      </c>
+      <c r="G1089" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1089, ""en"", ""te"")"),"దయచేసి లింగాన్ని ఎంచుకోండి.")</f>
+        <v>దయచేసి లింగాన్ని ఎంచుకోండి.</v>
+      </c>
     </row>
     <row r="1090">
       <c r="A1090" s="8"/>
@@ -39505,4830 +40215,4830 @@
     </row>
     <row r="1364">
       <c r="A1364" s="10"/>
-      <c r="B1364" s="18"/>
+      <c r="B1364" s="17"/>
       <c r="C1364" s="10"/>
       <c r="D1364" s="10"/>
       <c r="E1364" s="10"/>
     </row>
     <row r="1365">
       <c r="A1365" s="10"/>
-      <c r="B1365" s="18"/>
+      <c r="B1365" s="17"/>
       <c r="C1365" s="10"/>
       <c r="D1365" s="10"/>
       <c r="E1365" s="10"/>
     </row>
     <row r="1366">
       <c r="A1366" s="10"/>
-      <c r="B1366" s="18"/>
+      <c r="B1366" s="17"/>
       <c r="C1366" s="10"/>
       <c r="D1366" s="10"/>
       <c r="E1366" s="10"/>
     </row>
     <row r="1367">
       <c r="A1367" s="10"/>
-      <c r="B1367" s="18"/>
+      <c r="B1367" s="17"/>
       <c r="C1367" s="10"/>
       <c r="D1367" s="10"/>
       <c r="E1367" s="10"/>
     </row>
     <row r="1368">
       <c r="A1368" s="10"/>
-      <c r="B1368" s="18"/>
+      <c r="B1368" s="17"/>
       <c r="C1368" s="10"/>
       <c r="D1368" s="10"/>
       <c r="E1368" s="10"/>
     </row>
     <row r="1369">
       <c r="A1369" s="10"/>
-      <c r="B1369" s="18"/>
+      <c r="B1369" s="17"/>
       <c r="C1369" s="10"/>
       <c r="D1369" s="10"/>
       <c r="E1369" s="10"/>
     </row>
     <row r="1370">
       <c r="A1370" s="10"/>
-      <c r="B1370" s="18"/>
+      <c r="B1370" s="17"/>
       <c r="C1370" s="10"/>
       <c r="D1370" s="10"/>
       <c r="E1370" s="10"/>
     </row>
     <row r="1371">
       <c r="A1371" s="10"/>
-      <c r="B1371" s="18"/>
+      <c r="B1371" s="17"/>
       <c r="C1371" s="10"/>
       <c r="D1371" s="10"/>
       <c r="E1371" s="10"/>
     </row>
     <row r="1372">
       <c r="A1372" s="10"/>
-      <c r="B1372" s="18"/>
+      <c r="B1372" s="17"/>
       <c r="C1372" s="10"/>
       <c r="D1372" s="10"/>
       <c r="E1372" s="10"/>
     </row>
     <row r="1373">
       <c r="A1373" s="10"/>
-      <c r="B1373" s="18"/>
+      <c r="B1373" s="17"/>
       <c r="C1373" s="10"/>
       <c r="D1373" s="10"/>
       <c r="E1373" s="10"/>
     </row>
     <row r="1374">
       <c r="A1374" s="10"/>
-      <c r="B1374" s="18"/>
+      <c r="B1374" s="17"/>
       <c r="C1374" s="10"/>
       <c r="D1374" s="10"/>
       <c r="E1374" s="10"/>
     </row>
     <row r="1375">
       <c r="A1375" s="10"/>
-      <c r="B1375" s="18"/>
+      <c r="B1375" s="17"/>
       <c r="C1375" s="10"/>
       <c r="D1375" s="10"/>
       <c r="E1375" s="10"/>
     </row>
     <row r="1376">
       <c r="A1376" s="10"/>
-      <c r="B1376" s="18"/>
+      <c r="B1376" s="17"/>
       <c r="C1376" s="10"/>
       <c r="D1376" s="10"/>
       <c r="E1376" s="10"/>
     </row>
     <row r="1377">
       <c r="A1377" s="10"/>
-      <c r="B1377" s="18"/>
+      <c r="B1377" s="17"/>
       <c r="C1377" s="10"/>
       <c r="D1377" s="10"/>
       <c r="E1377" s="10"/>
     </row>
     <row r="1378">
       <c r="A1378" s="10"/>
-      <c r="B1378" s="18"/>
+      <c r="B1378" s="17"/>
       <c r="C1378" s="10"/>
       <c r="D1378" s="10"/>
       <c r="E1378" s="10"/>
     </row>
     <row r="1379">
       <c r="A1379" s="10"/>
-      <c r="B1379" s="18"/>
+      <c r="B1379" s="17"/>
       <c r="C1379" s="10"/>
       <c r="D1379" s="10"/>
       <c r="E1379" s="10"/>
     </row>
     <row r="1380">
       <c r="A1380" s="10"/>
-      <c r="B1380" s="18"/>
+      <c r="B1380" s="17"/>
       <c r="C1380" s="10"/>
       <c r="D1380" s="10"/>
       <c r="E1380" s="10"/>
     </row>
     <row r="1381">
       <c r="A1381" s="10"/>
-      <c r="B1381" s="18"/>
+      <c r="B1381" s="17"/>
       <c r="C1381" s="10"/>
       <c r="D1381" s="10"/>
       <c r="E1381" s="10"/>
     </row>
     <row r="1382">
       <c r="A1382" s="10"/>
-      <c r="B1382" s="18"/>
+      <c r="B1382" s="17"/>
       <c r="C1382" s="10"/>
       <c r="D1382" s="10"/>
       <c r="E1382" s="10"/>
     </row>
     <row r="1383">
       <c r="A1383" s="10"/>
-      <c r="B1383" s="18"/>
+      <c r="B1383" s="17"/>
       <c r="C1383" s="10"/>
       <c r="D1383" s="10"/>
       <c r="E1383" s="10"/>
     </row>
     <row r="1384">
       <c r="A1384" s="10"/>
-      <c r="B1384" s="18"/>
+      <c r="B1384" s="17"/>
       <c r="C1384" s="10"/>
       <c r="D1384" s="10"/>
       <c r="E1384" s="10"/>
     </row>
     <row r="1385">
       <c r="A1385" s="10"/>
-      <c r="B1385" s="18"/>
+      <c r="B1385" s="17"/>
       <c r="C1385" s="10"/>
       <c r="D1385" s="10"/>
       <c r="E1385" s="10"/>
     </row>
     <row r="1386">
       <c r="A1386" s="10"/>
-      <c r="B1386" s="18"/>
+      <c r="B1386" s="17"/>
       <c r="C1386" s="10"/>
       <c r="D1386" s="10"/>
       <c r="E1386" s="10"/>
     </row>
     <row r="1387">
       <c r="A1387" s="10"/>
-      <c r="B1387" s="18"/>
+      <c r="B1387" s="17"/>
       <c r="C1387" s="10"/>
       <c r="D1387" s="10"/>
       <c r="E1387" s="10"/>
     </row>
     <row r="1388">
       <c r="A1388" s="10"/>
-      <c r="B1388" s="18"/>
+      <c r="B1388" s="17"/>
       <c r="C1388" s="10"/>
       <c r="D1388" s="10"/>
       <c r="E1388" s="10"/>
     </row>
     <row r="1389">
       <c r="A1389" s="10"/>
-      <c r="B1389" s="18"/>
+      <c r="B1389" s="17"/>
       <c r="C1389" s="10"/>
       <c r="D1389" s="10"/>
       <c r="E1389" s="10"/>
     </row>
     <row r="1390">
       <c r="A1390" s="10"/>
-      <c r="B1390" s="18"/>
+      <c r="B1390" s="17"/>
       <c r="C1390" s="10"/>
       <c r="D1390" s="10"/>
       <c r="E1390" s="10"/>
     </row>
     <row r="1391">
       <c r="A1391" s="10"/>
-      <c r="B1391" s="18"/>
+      <c r="B1391" s="17"/>
       <c r="C1391" s="10"/>
       <c r="D1391" s="10"/>
       <c r="E1391" s="10"/>
     </row>
     <row r="1392">
       <c r="A1392" s="10"/>
-      <c r="B1392" s="18"/>
+      <c r="B1392" s="17"/>
       <c r="C1392" s="10"/>
       <c r="D1392" s="10"/>
       <c r="E1392" s="10"/>
     </row>
     <row r="1393">
       <c r="A1393" s="10"/>
-      <c r="B1393" s="18"/>
+      <c r="B1393" s="17"/>
       <c r="C1393" s="10"/>
       <c r="D1393" s="10"/>
       <c r="E1393" s="10"/>
     </row>
     <row r="1394">
       <c r="A1394" s="10"/>
-      <c r="B1394" s="18"/>
+      <c r="B1394" s="17"/>
       <c r="C1394" s="10"/>
       <c r="D1394" s="10"/>
       <c r="E1394" s="10"/>
     </row>
     <row r="1395">
       <c r="A1395" s="10"/>
-      <c r="B1395" s="18"/>
+      <c r="B1395" s="17"/>
       <c r="C1395" s="10"/>
       <c r="D1395" s="10"/>
       <c r="E1395" s="10"/>
     </row>
     <row r="1396">
       <c r="A1396" s="10"/>
-      <c r="B1396" s="18"/>
+      <c r="B1396" s="17"/>
       <c r="C1396" s="10"/>
       <c r="D1396" s="10"/>
       <c r="E1396" s="10"/>
     </row>
     <row r="1397">
       <c r="A1397" s="10"/>
-      <c r="B1397" s="18"/>
+      <c r="B1397" s="17"/>
       <c r="C1397" s="10"/>
       <c r="D1397" s="10"/>
       <c r="E1397" s="10"/>
     </row>
     <row r="1398">
       <c r="A1398" s="10"/>
-      <c r="B1398" s="18"/>
+      <c r="B1398" s="17"/>
       <c r="C1398" s="10"/>
       <c r="D1398" s="10"/>
       <c r="E1398" s="10"/>
     </row>
     <row r="1399">
       <c r="A1399" s="10"/>
-      <c r="B1399" s="18"/>
+      <c r="B1399" s="17"/>
       <c r="C1399" s="10"/>
       <c r="D1399" s="10"/>
       <c r="E1399" s="10"/>
     </row>
     <row r="1400">
       <c r="A1400" s="10"/>
-      <c r="B1400" s="18"/>
+      <c r="B1400" s="17"/>
       <c r="C1400" s="10"/>
       <c r="D1400" s="10"/>
       <c r="E1400" s="10"/>
     </row>
     <row r="1401">
       <c r="A1401" s="10"/>
-      <c r="B1401" s="18"/>
+      <c r="B1401" s="17"/>
       <c r="C1401" s="10"/>
       <c r="D1401" s="10"/>
       <c r="E1401" s="10"/>
     </row>
     <row r="1402">
       <c r="A1402" s="10"/>
-      <c r="B1402" s="18"/>
+      <c r="B1402" s="17"/>
       <c r="C1402" s="10"/>
       <c r="D1402" s="10"/>
       <c r="E1402" s="10"/>
     </row>
     <row r="1403">
       <c r="A1403" s="10"/>
-      <c r="B1403" s="18"/>
+      <c r="B1403" s="17"/>
       <c r="C1403" s="10"/>
       <c r="D1403" s="10"/>
       <c r="E1403" s="10"/>
     </row>
     <row r="1404">
       <c r="A1404" s="10"/>
-      <c r="B1404" s="18"/>
+      <c r="B1404" s="17"/>
       <c r="C1404" s="10"/>
       <c r="D1404" s="10"/>
       <c r="E1404" s="10"/>
     </row>
     <row r="1405">
       <c r="A1405" s="10"/>
-      <c r="B1405" s="18"/>
+      <c r="B1405" s="17"/>
       <c r="C1405" s="10"/>
       <c r="D1405" s="10"/>
       <c r="E1405" s="10"/>
     </row>
     <row r="1406">
       <c r="A1406" s="10"/>
-      <c r="B1406" s="18"/>
+      <c r="B1406" s="17"/>
       <c r="C1406" s="10"/>
       <c r="D1406" s="10"/>
       <c r="E1406" s="10"/>
     </row>
     <row r="1407">
       <c r="A1407" s="10"/>
-      <c r="B1407" s="18"/>
+      <c r="B1407" s="17"/>
       <c r="C1407" s="10"/>
       <c r="D1407" s="10"/>
       <c r="E1407" s="10"/>
     </row>
     <row r="1408">
       <c r="A1408" s="10"/>
-      <c r="B1408" s="18"/>
+      <c r="B1408" s="17"/>
       <c r="C1408" s="10"/>
       <c r="D1408" s="10"/>
       <c r="E1408" s="10"/>
     </row>
     <row r="1409">
       <c r="A1409" s="10"/>
-      <c r="B1409" s="18"/>
+      <c r="B1409" s="17"/>
       <c r="C1409" s="10"/>
       <c r="D1409" s="10"/>
       <c r="E1409" s="10"/>
     </row>
     <row r="1410">
       <c r="A1410" s="10"/>
-      <c r="B1410" s="18"/>
+      <c r="B1410" s="17"/>
       <c r="C1410" s="10"/>
       <c r="D1410" s="10"/>
       <c r="E1410" s="10"/>
     </row>
     <row r="1411">
       <c r="A1411" s="10"/>
-      <c r="B1411" s="18"/>
+      <c r="B1411" s="17"/>
       <c r="C1411" s="10"/>
       <c r="D1411" s="10"/>
       <c r="E1411" s="10"/>
     </row>
     <row r="1412">
       <c r="A1412" s="10"/>
-      <c r="B1412" s="18"/>
+      <c r="B1412" s="17"/>
       <c r="C1412" s="10"/>
       <c r="D1412" s="10"/>
       <c r="E1412" s="10"/>
     </row>
     <row r="1413">
       <c r="A1413" s="10"/>
-      <c r="B1413" s="18"/>
+      <c r="B1413" s="17"/>
       <c r="C1413" s="10"/>
       <c r="D1413" s="10"/>
       <c r="E1413" s="10"/>
     </row>
     <row r="1414">
       <c r="A1414" s="10"/>
-      <c r="B1414" s="18"/>
+      <c r="B1414" s="17"/>
       <c r="C1414" s="10"/>
       <c r="D1414" s="10"/>
       <c r="E1414" s="10"/>
     </row>
     <row r="1415">
       <c r="A1415" s="10"/>
-      <c r="B1415" s="18"/>
+      <c r="B1415" s="17"/>
       <c r="C1415" s="10"/>
       <c r="D1415" s="10"/>
       <c r="E1415" s="10"/>
     </row>
     <row r="1416">
       <c r="A1416" s="10"/>
-      <c r="B1416" s="18"/>
+      <c r="B1416" s="17"/>
       <c r="C1416" s="10"/>
       <c r="D1416" s="10"/>
       <c r="E1416" s="10"/>
     </row>
     <row r="1417">
       <c r="A1417" s="10"/>
-      <c r="B1417" s="18"/>
+      <c r="B1417" s="17"/>
       <c r="C1417" s="10"/>
       <c r="D1417" s="10"/>
       <c r="E1417" s="10"/>
     </row>
     <row r="1418">
       <c r="A1418" s="10"/>
-      <c r="B1418" s="18"/>
+      <c r="B1418" s="17"/>
       <c r="C1418" s="10"/>
       <c r="D1418" s="10"/>
       <c r="E1418" s="10"/>
     </row>
     <row r="1419">
       <c r="A1419" s="10"/>
-      <c r="B1419" s="18"/>
+      <c r="B1419" s="17"/>
       <c r="C1419" s="10"/>
       <c r="D1419" s="10"/>
       <c r="E1419" s="10"/>
     </row>
     <row r="1420">
       <c r="A1420" s="10"/>
-      <c r="B1420" s="18"/>
+      <c r="B1420" s="17"/>
       <c r="C1420" s="10"/>
       <c r="D1420" s="10"/>
       <c r="E1420" s="10"/>
     </row>
     <row r="1421">
       <c r="A1421" s="10"/>
-      <c r="B1421" s="18"/>
+      <c r="B1421" s="17"/>
       <c r="C1421" s="10"/>
       <c r="D1421" s="10"/>
       <c r="E1421" s="10"/>
     </row>
     <row r="1422">
       <c r="A1422" s="10"/>
-      <c r="B1422" s="18"/>
+      <c r="B1422" s="17"/>
       <c r="C1422" s="10"/>
       <c r="D1422" s="10"/>
       <c r="E1422" s="10"/>
     </row>
     <row r="1423">
       <c r="A1423" s="10"/>
-      <c r="B1423" s="18"/>
+      <c r="B1423" s="17"/>
       <c r="C1423" s="10"/>
       <c r="D1423" s="10"/>
       <c r="E1423" s="10"/>
     </row>
     <row r="1424">
       <c r="A1424" s="10"/>
-      <c r="B1424" s="18"/>
+      <c r="B1424" s="17"/>
       <c r="C1424" s="10"/>
       <c r="D1424" s="10"/>
       <c r="E1424" s="10"/>
     </row>
     <row r="1425">
       <c r="A1425" s="10"/>
-      <c r="B1425" s="18"/>
+      <c r="B1425" s="17"/>
       <c r="C1425" s="10"/>
       <c r="D1425" s="10"/>
       <c r="E1425" s="10"/>
     </row>
     <row r="1426">
       <c r="A1426" s="10"/>
-      <c r="B1426" s="18"/>
+      <c r="B1426" s="17"/>
       <c r="C1426" s="10"/>
       <c r="D1426" s="10"/>
       <c r="E1426" s="10"/>
     </row>
     <row r="1427">
       <c r="A1427" s="10"/>
-      <c r="B1427" s="18"/>
+      <c r="B1427" s="17"/>
       <c r="C1427" s="10"/>
       <c r="D1427" s="10"/>
       <c r="E1427" s="10"/>
     </row>
     <row r="1428">
       <c r="A1428" s="10"/>
-      <c r="B1428" s="18"/>
+      <c r="B1428" s="17"/>
       <c r="C1428" s="10"/>
       <c r="D1428" s="10"/>
       <c r="E1428" s="10"/>
     </row>
     <row r="1429">
       <c r="A1429" s="10"/>
-      <c r="B1429" s="18"/>
+      <c r="B1429" s="17"/>
       <c r="C1429" s="10"/>
       <c r="D1429" s="10"/>
       <c r="E1429" s="10"/>
     </row>
     <row r="1430">
       <c r="A1430" s="10"/>
-      <c r="B1430" s="18"/>
+      <c r="B1430" s="17"/>
       <c r="C1430" s="10"/>
       <c r="D1430" s="10"/>
       <c r="E1430" s="10"/>
     </row>
     <row r="1431">
       <c r="A1431" s="10"/>
-      <c r="B1431" s="18"/>
+      <c r="B1431" s="17"/>
       <c r="C1431" s="10"/>
       <c r="D1431" s="10"/>
       <c r="E1431" s="10"/>
     </row>
     <row r="1432">
       <c r="A1432" s="10"/>
-      <c r="B1432" s="18"/>
+      <c r="B1432" s="17"/>
       <c r="C1432" s="10"/>
       <c r="D1432" s="10"/>
       <c r="E1432" s="10"/>
     </row>
     <row r="1433">
       <c r="A1433" s="10"/>
-      <c r="B1433" s="18"/>
+      <c r="B1433" s="17"/>
       <c r="C1433" s="10"/>
       <c r="D1433" s="10"/>
       <c r="E1433" s="10"/>
     </row>
     <row r="1434">
       <c r="A1434" s="10"/>
-      <c r="B1434" s="18"/>
+      <c r="B1434" s="17"/>
       <c r="C1434" s="10"/>
       <c r="D1434" s="10"/>
       <c r="E1434" s="10"/>
     </row>
     <row r="1435">
       <c r="A1435" s="10"/>
-      <c r="B1435" s="18"/>
+      <c r="B1435" s="17"/>
       <c r="C1435" s="10"/>
       <c r="D1435" s="10"/>
       <c r="E1435" s="10"/>
     </row>
     <row r="1436">
       <c r="A1436" s="10"/>
-      <c r="B1436" s="18"/>
+      <c r="B1436" s="17"/>
       <c r="C1436" s="10"/>
       <c r="D1436" s="10"/>
       <c r="E1436" s="10"/>
     </row>
     <row r="1437">
       <c r="A1437" s="10"/>
-      <c r="B1437" s="18"/>
+      <c r="B1437" s="17"/>
       <c r="C1437" s="10"/>
       <c r="D1437" s="10"/>
       <c r="E1437" s="10"/>
     </row>
     <row r="1438">
       <c r="A1438" s="10"/>
-      <c r="B1438" s="18"/>
+      <c r="B1438" s="17"/>
       <c r="C1438" s="10"/>
       <c r="D1438" s="10"/>
       <c r="E1438" s="10"/>
     </row>
     <row r="1439">
       <c r="A1439" s="10"/>
-      <c r="B1439" s="18"/>
+      <c r="B1439" s="17"/>
       <c r="C1439" s="10"/>
       <c r="D1439" s="10"/>
       <c r="E1439" s="10"/>
     </row>
     <row r="1440">
       <c r="A1440" s="10"/>
-      <c r="B1440" s="18"/>
+      <c r="B1440" s="17"/>
       <c r="C1440" s="10"/>
       <c r="D1440" s="10"/>
       <c r="E1440" s="10"/>
     </row>
     <row r="1441">
       <c r="A1441" s="10"/>
-      <c r="B1441" s="18"/>
+      <c r="B1441" s="17"/>
       <c r="C1441" s="10"/>
       <c r="D1441" s="10"/>
       <c r="E1441" s="10"/>
     </row>
     <row r="1442">
       <c r="A1442" s="10"/>
-      <c r="B1442" s="18"/>
+      <c r="B1442" s="17"/>
       <c r="C1442" s="10"/>
       <c r="D1442" s="10"/>
       <c r="E1442" s="10"/>
     </row>
     <row r="1443">
       <c r="A1443" s="10"/>
-      <c r="B1443" s="18"/>
+      <c r="B1443" s="17"/>
       <c r="C1443" s="10"/>
       <c r="D1443" s="10"/>
       <c r="E1443" s="10"/>
     </row>
     <row r="1444">
       <c r="A1444" s="10"/>
-      <c r="B1444" s="18"/>
+      <c r="B1444" s="17"/>
       <c r="C1444" s="10"/>
       <c r="D1444" s="10"/>
       <c r="E1444" s="10"/>
     </row>
     <row r="1445">
       <c r="A1445" s="10"/>
-      <c r="B1445" s="18"/>
+      <c r="B1445" s="17"/>
       <c r="C1445" s="10"/>
       <c r="D1445" s="10"/>
       <c r="E1445" s="10"/>
     </row>
     <row r="1446">
       <c r="A1446" s="10"/>
-      <c r="B1446" s="18"/>
+      <c r="B1446" s="17"/>
       <c r="C1446" s="10"/>
       <c r="D1446" s="10"/>
       <c r="E1446" s="10"/>
     </row>
     <row r="1447">
       <c r="A1447" s="10"/>
-      <c r="B1447" s="18"/>
+      <c r="B1447" s="17"/>
       <c r="C1447" s="10"/>
       <c r="D1447" s="10"/>
       <c r="E1447" s="10"/>
     </row>
     <row r="1448">
       <c r="A1448" s="10"/>
-      <c r="B1448" s="18"/>
+      <c r="B1448" s="17"/>
       <c r="C1448" s="10"/>
       <c r="D1448" s="10"/>
       <c r="E1448" s="10"/>
     </row>
     <row r="1449">
       <c r="A1449" s="10"/>
-      <c r="B1449" s="18"/>
+      <c r="B1449" s="17"/>
       <c r="C1449" s="10"/>
       <c r="D1449" s="10"/>
       <c r="E1449" s="10"/>
     </row>
     <row r="1450">
       <c r="A1450" s="10"/>
-      <c r="B1450" s="18"/>
+      <c r="B1450" s="17"/>
       <c r="C1450" s="10"/>
       <c r="D1450" s="10"/>
       <c r="E1450" s="10"/>
     </row>
     <row r="1451">
       <c r="A1451" s="10"/>
-      <c r="B1451" s="18"/>
+      <c r="B1451" s="17"/>
       <c r="C1451" s="10"/>
       <c r="D1451" s="10"/>
       <c r="E1451" s="10"/>
     </row>
     <row r="1452">
       <c r="A1452" s="10"/>
-      <c r="B1452" s="18"/>
+      <c r="B1452" s="17"/>
       <c r="C1452" s="10"/>
       <c r="D1452" s="10"/>
       <c r="E1452" s="10"/>
     </row>
     <row r="1453">
       <c r="A1453" s="10"/>
-      <c r="B1453" s="18"/>
+      <c r="B1453" s="17"/>
       <c r="C1453" s="10"/>
       <c r="D1453" s="10"/>
       <c r="E1453" s="10"/>
     </row>
     <row r="1454">
       <c r="A1454" s="10"/>
-      <c r="B1454" s="18"/>
+      <c r="B1454" s="17"/>
       <c r="C1454" s="10"/>
       <c r="D1454" s="10"/>
       <c r="E1454" s="10"/>
     </row>
     <row r="1455">
       <c r="A1455" s="10"/>
-      <c r="B1455" s="18"/>
+      <c r="B1455" s="17"/>
       <c r="C1455" s="10"/>
       <c r="D1455" s="10"/>
       <c r="E1455" s="10"/>
     </row>
     <row r="1456">
       <c r="A1456" s="10"/>
-      <c r="B1456" s="18"/>
+      <c r="B1456" s="17"/>
       <c r="C1456" s="10"/>
       <c r="D1456" s="10"/>
       <c r="E1456" s="10"/>
     </row>
     <row r="1457">
       <c r="A1457" s="10"/>
-      <c r="B1457" s="18"/>
+      <c r="B1457" s="17"/>
       <c r="C1457" s="10"/>
       <c r="D1457" s="10"/>
       <c r="E1457" s="10"/>
     </row>
     <row r="1458">
       <c r="A1458" s="10"/>
-      <c r="B1458" s="18"/>
+      <c r="B1458" s="17"/>
       <c r="C1458" s="10"/>
       <c r="D1458" s="10"/>
       <c r="E1458" s="10"/>
     </row>
     <row r="1459">
       <c r="A1459" s="10"/>
-      <c r="B1459" s="18"/>
+      <c r="B1459" s="17"/>
       <c r="C1459" s="10"/>
       <c r="D1459" s="10"/>
       <c r="E1459" s="10"/>
     </row>
     <row r="1460">
       <c r="A1460" s="10"/>
-      <c r="B1460" s="18"/>
+      <c r="B1460" s="17"/>
       <c r="C1460" s="10"/>
       <c r="D1460" s="10"/>
       <c r="E1460" s="10"/>
     </row>
     <row r="1461">
       <c r="A1461" s="10"/>
-      <c r="B1461" s="18"/>
+      <c r="B1461" s="17"/>
       <c r="C1461" s="10"/>
       <c r="D1461" s="10"/>
       <c r="E1461" s="10"/>
     </row>
     <row r="1462">
       <c r="A1462" s="10"/>
-      <c r="B1462" s="18"/>
+      <c r="B1462" s="17"/>
       <c r="C1462" s="10"/>
       <c r="D1462" s="10"/>
       <c r="E1462" s="10"/>
     </row>
     <row r="1463">
       <c r="A1463" s="10"/>
-      <c r="B1463" s="18"/>
+      <c r="B1463" s="17"/>
       <c r="C1463" s="10"/>
       <c r="D1463" s="10"/>
       <c r="E1463" s="10"/>
     </row>
     <row r="1464">
       <c r="A1464" s="10"/>
-      <c r="B1464" s="18"/>
+      <c r="B1464" s="17"/>
       <c r="C1464" s="10"/>
       <c r="D1464" s="10"/>
       <c r="E1464" s="10"/>
     </row>
     <row r="1465">
       <c r="A1465" s="10"/>
-      <c r="B1465" s="18"/>
+      <c r="B1465" s="17"/>
       <c r="C1465" s="10"/>
       <c r="D1465" s="10"/>
       <c r="E1465" s="10"/>
     </row>
     <row r="1466">
       <c r="A1466" s="10"/>
-      <c r="B1466" s="18"/>
+      <c r="B1466" s="17"/>
       <c r="C1466" s="10"/>
       <c r="D1466" s="10"/>
       <c r="E1466" s="10"/>
     </row>
     <row r="1467">
       <c r="A1467" s="10"/>
-      <c r="B1467" s="18"/>
+      <c r="B1467" s="17"/>
       <c r="C1467" s="10"/>
       <c r="D1467" s="10"/>
       <c r="E1467" s="10"/>
     </row>
     <row r="1468">
       <c r="A1468" s="10"/>
-      <c r="B1468" s="18"/>
+      <c r="B1468" s="17"/>
       <c r="C1468" s="10"/>
       <c r="D1468" s="10"/>
       <c r="E1468" s="10"/>
     </row>
     <row r="1469">
       <c r="A1469" s="10"/>
-      <c r="B1469" s="18"/>
+      <c r="B1469" s="17"/>
       <c r="C1469" s="10"/>
       <c r="D1469" s="10"/>
       <c r="E1469" s="10"/>
     </row>
     <row r="1470">
       <c r="A1470" s="10"/>
-      <c r="B1470" s="18"/>
+      <c r="B1470" s="17"/>
       <c r="C1470" s="10"/>
       <c r="D1470" s="10"/>
       <c r="E1470" s="10"/>
     </row>
     <row r="1471">
       <c r="A1471" s="10"/>
-      <c r="B1471" s="18"/>
+      <c r="B1471" s="17"/>
       <c r="C1471" s="10"/>
       <c r="D1471" s="10"/>
       <c r="E1471" s="10"/>
     </row>
     <row r="1472">
       <c r="A1472" s="10"/>
-      <c r="B1472" s="18"/>
+      <c r="B1472" s="17"/>
       <c r="C1472" s="10"/>
       <c r="D1472" s="10"/>
       <c r="E1472" s="10"/>
     </row>
     <row r="1473">
       <c r="A1473" s="10"/>
-      <c r="B1473" s="18"/>
+      <c r="B1473" s="17"/>
       <c r="C1473" s="10"/>
       <c r="D1473" s="10"/>
       <c r="E1473" s="10"/>
     </row>
     <row r="1474">
       <c r="A1474" s="10"/>
-      <c r="B1474" s="18"/>
+      <c r="B1474" s="17"/>
       <c r="C1474" s="10"/>
       <c r="D1474" s="10"/>
       <c r="E1474" s="10"/>
     </row>
     <row r="1475">
       <c r="A1475" s="10"/>
-      <c r="B1475" s="18"/>
+      <c r="B1475" s="17"/>
       <c r="C1475" s="10"/>
       <c r="D1475" s="10"/>
       <c r="E1475" s="10"/>
     </row>
     <row r="1476">
       <c r="A1476" s="10"/>
-      <c r="B1476" s="18"/>
+      <c r="B1476" s="17"/>
       <c r="C1476" s="10"/>
       <c r="D1476" s="10"/>
       <c r="E1476" s="10"/>
     </row>
     <row r="1477">
       <c r="A1477" s="10"/>
-      <c r="B1477" s="18"/>
+      <c r="B1477" s="17"/>
       <c r="C1477" s="10"/>
       <c r="D1477" s="10"/>
       <c r="E1477" s="10"/>
     </row>
     <row r="1478">
       <c r="A1478" s="10"/>
-      <c r="B1478" s="18"/>
+      <c r="B1478" s="17"/>
       <c r="C1478" s="10"/>
       <c r="D1478" s="10"/>
       <c r="E1478" s="10"/>
     </row>
     <row r="1479">
       <c r="A1479" s="10"/>
-      <c r="B1479" s="18"/>
+      <c r="B1479" s="17"/>
       <c r="C1479" s="10"/>
       <c r="D1479" s="10"/>
       <c r="E1479" s="10"/>
     </row>
     <row r="1480">
       <c r="A1480" s="10"/>
-      <c r="B1480" s="18"/>
+      <c r="B1480" s="17"/>
       <c r="C1480" s="10"/>
       <c r="D1480" s="10"/>
       <c r="E1480" s="10"/>
     </row>
     <row r="1481">
       <c r="A1481" s="10"/>
-      <c r="B1481" s="18"/>
+      <c r="B1481" s="17"/>
       <c r="C1481" s="10"/>
       <c r="D1481" s="10"/>
       <c r="E1481" s="10"/>
     </row>
     <row r="1482">
       <c r="A1482" s="10"/>
-      <c r="B1482" s="18"/>
+      <c r="B1482" s="17"/>
       <c r="C1482" s="10"/>
       <c r="D1482" s="10"/>
       <c r="E1482" s="10"/>
     </row>
     <row r="1483">
       <c r="A1483" s="10"/>
-      <c r="B1483" s="18"/>
+      <c r="B1483" s="17"/>
       <c r="C1483" s="10"/>
       <c r="D1483" s="10"/>
       <c r="E1483" s="10"/>
     </row>
     <row r="1484">
       <c r="A1484" s="10"/>
-      <c r="B1484" s="18"/>
+      <c r="B1484" s="17"/>
       <c r="C1484" s="10"/>
       <c r="D1484" s="10"/>
       <c r="E1484" s="10"/>
     </row>
     <row r="1485">
       <c r="A1485" s="10"/>
-      <c r="B1485" s="18"/>
+      <c r="B1485" s="17"/>
       <c r="C1485" s="10"/>
       <c r="D1485" s="10"/>
       <c r="E1485" s="10"/>
     </row>
     <row r="1486">
       <c r="A1486" s="10"/>
-      <c r="B1486" s="18"/>
+      <c r="B1486" s="17"/>
       <c r="C1486" s="10"/>
       <c r="D1486" s="10"/>
       <c r="E1486" s="10"/>
     </row>
     <row r="1487">
       <c r="A1487" s="10"/>
-      <c r="B1487" s="18"/>
+      <c r="B1487" s="17"/>
       <c r="C1487" s="10"/>
       <c r="D1487" s="10"/>
       <c r="E1487" s="10"/>
     </row>
     <row r="1488">
       <c r="A1488" s="10"/>
-      <c r="B1488" s="18"/>
+      <c r="B1488" s="17"/>
       <c r="C1488" s="10"/>
       <c r="D1488" s="10"/>
       <c r="E1488" s="10"/>
     </row>
     <row r="1489">
       <c r="A1489" s="10"/>
-      <c r="B1489" s="18"/>
+      <c r="B1489" s="17"/>
       <c r="C1489" s="10"/>
       <c r="D1489" s="10"/>
       <c r="E1489" s="10"/>
     </row>
     <row r="1490">
       <c r="A1490" s="10"/>
-      <c r="B1490" s="18"/>
+      <c r="B1490" s="17"/>
       <c r="C1490" s="10"/>
       <c r="D1490" s="10"/>
       <c r="E1490" s="10"/>
     </row>
     <row r="1491">
       <c r="A1491" s="10"/>
-      <c r="B1491" s="18"/>
+      <c r="B1491" s="17"/>
       <c r="C1491" s="10"/>
       <c r="D1491" s="10"/>
       <c r="E1491" s="10"/>
     </row>
     <row r="1492">
       <c r="A1492" s="10"/>
-      <c r="B1492" s="18"/>
+      <c r="B1492" s="17"/>
       <c r="C1492" s="10"/>
       <c r="D1492" s="10"/>
       <c r="E1492" s="10"/>
     </row>
     <row r="1493">
       <c r="A1493" s="10"/>
-      <c r="B1493" s="18"/>
+      <c r="B1493" s="17"/>
       <c r="C1493" s="10"/>
       <c r="D1493" s="10"/>
       <c r="E1493" s="10"/>
     </row>
     <row r="1494">
       <c r="A1494" s="10"/>
-      <c r="B1494" s="18"/>
+      <c r="B1494" s="17"/>
       <c r="C1494" s="10"/>
       <c r="D1494" s="10"/>
       <c r="E1494" s="10"/>
     </row>
     <row r="1495">
       <c r="A1495" s="10"/>
-      <c r="B1495" s="18"/>
+      <c r="B1495" s="17"/>
       <c r="C1495" s="10"/>
       <c r="D1495" s="10"/>
       <c r="E1495" s="10"/>
     </row>
     <row r="1496">
       <c r="A1496" s="10"/>
-      <c r="B1496" s="18"/>
+      <c r="B1496" s="17"/>
       <c r="C1496" s="10"/>
       <c r="D1496" s="10"/>
       <c r="E1496" s="10"/>
     </row>
     <row r="1497">
       <c r="A1497" s="10"/>
-      <c r="B1497" s="18"/>
+      <c r="B1497" s="17"/>
       <c r="C1497" s="10"/>
       <c r="D1497" s="10"/>
       <c r="E1497" s="10"/>
     </row>
     <row r="1498">
       <c r="A1498" s="10"/>
-      <c r="B1498" s="18"/>
+      <c r="B1498" s="17"/>
       <c r="C1498" s="10"/>
       <c r="D1498" s="10"/>
       <c r="E1498" s="10"/>
     </row>
     <row r="1499">
       <c r="A1499" s="10"/>
-      <c r="B1499" s="18"/>
+      <c r="B1499" s="17"/>
       <c r="C1499" s="10"/>
       <c r="D1499" s="10"/>
       <c r="E1499" s="10"/>
     </row>
     <row r="1500">
       <c r="A1500" s="10"/>
-      <c r="B1500" s="18"/>
+      <c r="B1500" s="17"/>
       <c r="C1500" s="10"/>
       <c r="D1500" s="10"/>
       <c r="E1500" s="10"/>
     </row>
     <row r="1501">
       <c r="A1501" s="10"/>
-      <c r="B1501" s="18"/>
+      <c r="B1501" s="17"/>
       <c r="C1501" s="10"/>
       <c r="D1501" s="10"/>
       <c r="E1501" s="10"/>
     </row>
     <row r="1502">
       <c r="A1502" s="10"/>
-      <c r="B1502" s="18"/>
+      <c r="B1502" s="17"/>
       <c r="C1502" s="10"/>
       <c r="D1502" s="10"/>
       <c r="E1502" s="10"/>
     </row>
     <row r="1503">
       <c r="A1503" s="10"/>
-      <c r="B1503" s="18"/>
+      <c r="B1503" s="17"/>
       <c r="C1503" s="10"/>
       <c r="D1503" s="10"/>
       <c r="E1503" s="10"/>
     </row>
     <row r="1504">
       <c r="A1504" s="10"/>
-      <c r="B1504" s="18"/>
+      <c r="B1504" s="17"/>
       <c r="C1504" s="10"/>
       <c r="D1504" s="10"/>
       <c r="E1504" s="10"/>
     </row>
     <row r="1505">
       <c r="A1505" s="10"/>
-      <c r="B1505" s="18"/>
+      <c r="B1505" s="17"/>
       <c r="C1505" s="10"/>
       <c r="D1505" s="10"/>
       <c r="E1505" s="10"/>
     </row>
     <row r="1506">
       <c r="A1506" s="10"/>
-      <c r="B1506" s="18"/>
+      <c r="B1506" s="17"/>
       <c r="C1506" s="10"/>
       <c r="D1506" s="10"/>
       <c r="E1506" s="10"/>
     </row>
     <row r="1507">
       <c r="A1507" s="10"/>
-      <c r="B1507" s="18"/>
+      <c r="B1507" s="17"/>
       <c r="C1507" s="10"/>
       <c r="D1507" s="10"/>
       <c r="E1507" s="10"/>
     </row>
     <row r="1508">
       <c r="A1508" s="10"/>
-      <c r="B1508" s="18"/>
+      <c r="B1508" s="17"/>
       <c r="C1508" s="10"/>
       <c r="D1508" s="10"/>
       <c r="E1508" s="10"/>
     </row>
     <row r="1509">
       <c r="A1509" s="10"/>
-      <c r="B1509" s="18"/>
+      <c r="B1509" s="17"/>
       <c r="C1509" s="10"/>
       <c r="D1509" s="10"/>
       <c r="E1509" s="10"/>
     </row>
     <row r="1510">
       <c r="A1510" s="10"/>
-      <c r="B1510" s="18"/>
+      <c r="B1510" s="17"/>
       <c r="C1510" s="10"/>
       <c r="D1510" s="10"/>
       <c r="E1510" s="10"/>
     </row>
     <row r="1511">
       <c r="A1511" s="10"/>
-      <c r="B1511" s="18"/>
+      <c r="B1511" s="17"/>
       <c r="C1511" s="10"/>
       <c r="D1511" s="10"/>
       <c r="E1511" s="10"/>
     </row>
     <row r="1512">
       <c r="A1512" s="10"/>
-      <c r="B1512" s="18"/>
+      <c r="B1512" s="17"/>
       <c r="C1512" s="10"/>
       <c r="D1512" s="10"/>
       <c r="E1512" s="10"/>
     </row>
     <row r="1513">
       <c r="A1513" s="10"/>
-      <c r="B1513" s="18"/>
+      <c r="B1513" s="17"/>
       <c r="C1513" s="10"/>
       <c r="D1513" s="10"/>
       <c r="E1513" s="10"/>
     </row>
     <row r="1514">
       <c r="A1514" s="10"/>
-      <c r="B1514" s="18"/>
+      <c r="B1514" s="17"/>
       <c r="C1514" s="10"/>
       <c r="D1514" s="10"/>
       <c r="E1514" s="10"/>
     </row>
     <row r="1515">
       <c r="A1515" s="10"/>
-      <c r="B1515" s="18"/>
+      <c r="B1515" s="17"/>
       <c r="C1515" s="10"/>
       <c r="D1515" s="10"/>
       <c r="E1515" s="10"/>
     </row>
     <row r="1516">
       <c r="A1516" s="10"/>
-      <c r="B1516" s="18"/>
+      <c r="B1516" s="17"/>
       <c r="C1516" s="10"/>
       <c r="D1516" s="10"/>
       <c r="E1516" s="10"/>
     </row>
     <row r="1517">
       <c r="A1517" s="10"/>
-      <c r="B1517" s="18"/>
+      <c r="B1517" s="17"/>
       <c r="C1517" s="10"/>
       <c r="D1517" s="10"/>
       <c r="E1517" s="10"/>
     </row>
     <row r="1518">
       <c r="A1518" s="10"/>
-      <c r="B1518" s="18"/>
+      <c r="B1518" s="17"/>
       <c r="C1518" s="10"/>
       <c r="D1518" s="10"/>
       <c r="E1518" s="10"/>
     </row>
     <row r="1519">
       <c r="A1519" s="10"/>
-      <c r="B1519" s="18"/>
+      <c r="B1519" s="17"/>
       <c r="C1519" s="10"/>
       <c r="D1519" s="10"/>
       <c r="E1519" s="10"/>
     </row>
     <row r="1520">
       <c r="A1520" s="10"/>
-      <c r="B1520" s="18"/>
+      <c r="B1520" s="17"/>
       <c r="C1520" s="10"/>
       <c r="D1520" s="10"/>
       <c r="E1520" s="10"/>
     </row>
     <row r="1521">
       <c r="A1521" s="10"/>
-      <c r="B1521" s="18"/>
+      <c r="B1521" s="17"/>
       <c r="C1521" s="10"/>
       <c r="D1521" s="10"/>
       <c r="E1521" s="10"/>
     </row>
     <row r="1522">
       <c r="A1522" s="10"/>
-      <c r="B1522" s="18"/>
+      <c r="B1522" s="17"/>
       <c r="C1522" s="10"/>
       <c r="D1522" s="10"/>
       <c r="E1522" s="10"/>
     </row>
     <row r="1523">
       <c r="A1523" s="10"/>
-      <c r="B1523" s="18"/>
+      <c r="B1523" s="17"/>
       <c r="C1523" s="10"/>
       <c r="D1523" s="10"/>
       <c r="E1523" s="10"/>
     </row>
     <row r="1524">
       <c r="A1524" s="10"/>
-      <c r="B1524" s="18"/>
+      <c r="B1524" s="17"/>
       <c r="C1524" s="10"/>
       <c r="D1524" s="10"/>
       <c r="E1524" s="10"/>
     </row>
     <row r="1525">
       <c r="A1525" s="10"/>
-      <c r="B1525" s="18"/>
+      <c r="B1525" s="17"/>
       <c r="C1525" s="10"/>
       <c r="D1525" s="10"/>
       <c r="E1525" s="10"/>
     </row>
     <row r="1526">
       <c r="A1526" s="10"/>
-      <c r="B1526" s="18"/>
+      <c r="B1526" s="17"/>
       <c r="C1526" s="10"/>
       <c r="D1526" s="10"/>
       <c r="E1526" s="10"/>
     </row>
     <row r="1527">
       <c r="A1527" s="10"/>
-      <c r="B1527" s="18"/>
+      <c r="B1527" s="17"/>
       <c r="C1527" s="10"/>
       <c r="D1527" s="10"/>
       <c r="E1527" s="10"/>
     </row>
     <row r="1528">
       <c r="A1528" s="10"/>
-      <c r="B1528" s="18"/>
+      <c r="B1528" s="17"/>
       <c r="C1528" s="10"/>
       <c r="D1528" s="10"/>
       <c r="E1528" s="10"/>
     </row>
     <row r="1529">
       <c r="A1529" s="10"/>
-      <c r="B1529" s="18"/>
+      <c r="B1529" s="17"/>
       <c r="C1529" s="10"/>
       <c r="D1529" s="10"/>
       <c r="E1529" s="10"/>
     </row>
     <row r="1530">
       <c r="A1530" s="10"/>
-      <c r="B1530" s="18"/>
+      <c r="B1530" s="17"/>
       <c r="C1530" s="10"/>
       <c r="D1530" s="10"/>
       <c r="E1530" s="10"/>
     </row>
     <row r="1531">
       <c r="A1531" s="10"/>
-      <c r="B1531" s="18"/>
+      <c r="B1531" s="17"/>
       <c r="C1531" s="10"/>
       <c r="D1531" s="10"/>
       <c r="E1531" s="10"/>
     </row>
     <row r="1532">
       <c r="A1532" s="10"/>
-      <c r="B1532" s="18"/>
+      <c r="B1532" s="17"/>
       <c r="C1532" s="10"/>
       <c r="D1532" s="10"/>
       <c r="E1532" s="10"/>
     </row>
     <row r="1533">
       <c r="A1533" s="10"/>
-      <c r="B1533" s="18"/>
+      <c r="B1533" s="17"/>
       <c r="C1533" s="10"/>
       <c r="D1533" s="10"/>
       <c r="E1533" s="10"/>
     </row>
     <row r="1534">
       <c r="A1534" s="10"/>
-      <c r="B1534" s="18"/>
+      <c r="B1534" s="17"/>
       <c r="C1534" s="10"/>
       <c r="D1534" s="10"/>
       <c r="E1534" s="10"/>
     </row>
     <row r="1535">
       <c r="A1535" s="10"/>
-      <c r="B1535" s="18"/>
+      <c r="B1535" s="17"/>
       <c r="C1535" s="10"/>
       <c r="D1535" s="10"/>
       <c r="E1535" s="10"/>
     </row>
     <row r="1536">
       <c r="A1536" s="10"/>
-      <c r="B1536" s="18"/>
+      <c r="B1536" s="17"/>
       <c r="C1536" s="10"/>
       <c r="D1536" s="10"/>
       <c r="E1536" s="10"/>
     </row>
     <row r="1537">
       <c r="A1537" s="10"/>
-      <c r="B1537" s="18"/>
+      <c r="B1537" s="17"/>
       <c r="C1537" s="10"/>
       <c r="D1537" s="10"/>
       <c r="E1537" s="10"/>
     </row>
     <row r="1538">
       <c r="A1538" s="10"/>
-      <c r="B1538" s="18"/>
+      <c r="B1538" s="17"/>
       <c r="C1538" s="10"/>
       <c r="D1538" s="10"/>
       <c r="E1538" s="10"/>
     </row>
     <row r="1539">
       <c r="A1539" s="10"/>
-      <c r="B1539" s="18"/>
+      <c r="B1539" s="17"/>
       <c r="C1539" s="10"/>
       <c r="D1539" s="10"/>
       <c r="E1539" s="10"/>
     </row>
     <row r="1540">
       <c r="A1540" s="10"/>
-      <c r="B1540" s="18"/>
+      <c r="B1540" s="17"/>
       <c r="C1540" s="10"/>
       <c r="D1540" s="10"/>
       <c r="E1540" s="10"/>
     </row>
     <row r="1541">
       <c r="A1541" s="10"/>
-      <c r="B1541" s="18"/>
+      <c r="B1541" s="17"/>
       <c r="C1541" s="10"/>
       <c r="D1541" s="10"/>
       <c r="E1541" s="10"/>
     </row>
     <row r="1542">
       <c r="A1542" s="10"/>
-      <c r="B1542" s="18"/>
+      <c r="B1542" s="17"/>
       <c r="C1542" s="10"/>
       <c r="D1542" s="10"/>
       <c r="E1542" s="10"/>
     </row>
     <row r="1543">
       <c r="A1543" s="10"/>
-      <c r="B1543" s="18"/>
+      <c r="B1543" s="17"/>
       <c r="C1543" s="10"/>
       <c r="D1543" s="10"/>
       <c r="E1543" s="10"/>
     </row>
     <row r="1544">
       <c r="A1544" s="10"/>
-      <c r="B1544" s="18"/>
+      <c r="B1544" s="17"/>
       <c r="C1544" s="10"/>
       <c r="D1544" s="10"/>
       <c r="E1544" s="10"/>
     </row>
     <row r="1545">
       <c r="A1545" s="10"/>
-      <c r="B1545" s="18"/>
+      <c r="B1545" s="17"/>
       <c r="C1545" s="10"/>
       <c r="D1545" s="10"/>
       <c r="E1545" s="10"/>
     </row>
     <row r="1546">
       <c r="A1546" s="10"/>
-      <c r="B1546" s="18"/>
+      <c r="B1546" s="17"/>
       <c r="C1546" s="10"/>
       <c r="D1546" s="10"/>
       <c r="E1546" s="10"/>
     </row>
     <row r="1547">
       <c r="A1547" s="10"/>
-      <c r="B1547" s="18"/>
+      <c r="B1547" s="17"/>
       <c r="C1547" s="10"/>
       <c r="D1547" s="10"/>
       <c r="E1547" s="10"/>
     </row>
     <row r="1548">
       <c r="A1548" s="10"/>
-      <c r="B1548" s="18"/>
+      <c r="B1548" s="17"/>
       <c r="C1548" s="10"/>
       <c r="D1548" s="10"/>
       <c r="E1548" s="10"/>
     </row>
     <row r="1549">
       <c r="A1549" s="10"/>
-      <c r="B1549" s="18"/>
+      <c r="B1549" s="17"/>
       <c r="C1549" s="10"/>
       <c r="D1549" s="10"/>
       <c r="E1549" s="10"/>
     </row>
     <row r="1550">
       <c r="A1550" s="10"/>
-      <c r="B1550" s="18"/>
+      <c r="B1550" s="17"/>
       <c r="C1550" s="10"/>
       <c r="D1550" s="10"/>
       <c r="E1550" s="10"/>
     </row>
     <row r="1551">
       <c r="A1551" s="10"/>
-      <c r="B1551" s="18"/>
+      <c r="B1551" s="17"/>
       <c r="C1551" s="10"/>
       <c r="D1551" s="10"/>
       <c r="E1551" s="10"/>
     </row>
     <row r="1552">
       <c r="A1552" s="10"/>
-      <c r="B1552" s="18"/>
+      <c r="B1552" s="17"/>
       <c r="C1552" s="10"/>
       <c r="D1552" s="10"/>
       <c r="E1552" s="10"/>
     </row>
     <row r="1553">
       <c r="A1553" s="10"/>
-      <c r="B1553" s="18"/>
+      <c r="B1553" s="17"/>
       <c r="C1553" s="10"/>
       <c r="D1553" s="10"/>
       <c r="E1553" s="10"/>
     </row>
     <row r="1554">
       <c r="A1554" s="10"/>
-      <c r="B1554" s="18"/>
+      <c r="B1554" s="17"/>
       <c r="C1554" s="10"/>
       <c r="D1554" s="10"/>
       <c r="E1554" s="10"/>
     </row>
     <row r="1555">
       <c r="A1555" s="10"/>
-      <c r="B1555" s="18"/>
+      <c r="B1555" s="17"/>
       <c r="C1555" s="10"/>
       <c r="D1555" s="10"/>
       <c r="E1555" s="10"/>
     </row>
     <row r="1556">
       <c r="A1556" s="10"/>
-      <c r="B1556" s="18"/>
+      <c r="B1556" s="17"/>
       <c r="C1556" s="10"/>
       <c r="D1556" s="10"/>
       <c r="E1556" s="10"/>
     </row>
     <row r="1557">
       <c r="A1557" s="10"/>
-      <c r="B1557" s="18"/>
+      <c r="B1557" s="17"/>
       <c r="C1557" s="10"/>
       <c r="D1557" s="10"/>
       <c r="E1557" s="10"/>
     </row>
     <row r="1558">
       <c r="A1558" s="10"/>
-      <c r="B1558" s="18"/>
+      <c r="B1558" s="17"/>
       <c r="C1558" s="10"/>
       <c r="D1558" s="10"/>
       <c r="E1558" s="10"/>
     </row>
     <row r="1559">
       <c r="A1559" s="10"/>
-      <c r="B1559" s="18"/>
+      <c r="B1559" s="17"/>
       <c r="C1559" s="10"/>
       <c r="D1559" s="10"/>
       <c r="E1559" s="10"/>
     </row>
     <row r="1560">
       <c r="A1560" s="10"/>
-      <c r="B1560" s="18"/>
+      <c r="B1560" s="17"/>
       <c r="C1560" s="10"/>
       <c r="D1560" s="10"/>
       <c r="E1560" s="10"/>
     </row>
     <row r="1561">
       <c r="A1561" s="10"/>
-      <c r="B1561" s="18"/>
+      <c r="B1561" s="17"/>
       <c r="C1561" s="10"/>
       <c r="D1561" s="10"/>
       <c r="E1561" s="10"/>
     </row>
     <row r="1562">
       <c r="A1562" s="10"/>
-      <c r="B1562" s="18"/>
+      <c r="B1562" s="17"/>
       <c r="C1562" s="10"/>
       <c r="D1562" s="10"/>
       <c r="E1562" s="10"/>
     </row>
     <row r="1563">
       <c r="A1563" s="10"/>
-      <c r="B1563" s="18"/>
+      <c r="B1563" s="17"/>
       <c r="C1563" s="10"/>
       <c r="D1563" s="10"/>
       <c r="E1563" s="10"/>
     </row>
     <row r="1564">
       <c r="A1564" s="10"/>
-      <c r="B1564" s="18"/>
+      <c r="B1564" s="17"/>
       <c r="C1564" s="10"/>
       <c r="D1564" s="10"/>
       <c r="E1564" s="10"/>
     </row>
     <row r="1565">
       <c r="A1565" s="10"/>
-      <c r="B1565" s="18"/>
+      <c r="B1565" s="17"/>
       <c r="C1565" s="10"/>
       <c r="D1565" s="10"/>
       <c r="E1565" s="10"/>
     </row>
     <row r="1566">
       <c r="A1566" s="10"/>
-      <c r="B1566" s="18"/>
+      <c r="B1566" s="17"/>
       <c r="C1566" s="10"/>
       <c r="D1566" s="10"/>
       <c r="E1566" s="10"/>
     </row>
     <row r="1567">
       <c r="A1567" s="10"/>
-      <c r="B1567" s="18"/>
+      <c r="B1567" s="17"/>
       <c r="C1567" s="10"/>
       <c r="D1567" s="10"/>
       <c r="E1567" s="10"/>
     </row>
     <row r="1568">
       <c r="A1568" s="10"/>
-      <c r="B1568" s="18"/>
+      <c r="B1568" s="17"/>
       <c r="C1568" s="10"/>
       <c r="D1568" s="10"/>
       <c r="E1568" s="10"/>
     </row>
     <row r="1569">
       <c r="A1569" s="10"/>
-      <c r="B1569" s="18"/>
+      <c r="B1569" s="17"/>
       <c r="C1569" s="10"/>
       <c r="D1569" s="10"/>
       <c r="E1569" s="10"/>
     </row>
     <row r="1570">
       <c r="A1570" s="10"/>
-      <c r="B1570" s="18"/>
+      <c r="B1570" s="17"/>
       <c r="C1570" s="10"/>
       <c r="D1570" s="10"/>
       <c r="E1570" s="10"/>
     </row>
     <row r="1571">
       <c r="A1571" s="10"/>
-      <c r="B1571" s="18"/>
+      <c r="B1571" s="17"/>
       <c r="C1571" s="10"/>
       <c r="D1571" s="10"/>
       <c r="E1571" s="10"/>
     </row>
     <row r="1572">
       <c r="A1572" s="10"/>
-      <c r="B1572" s="18"/>
+      <c r="B1572" s="17"/>
       <c r="C1572" s="10"/>
       <c r="D1572" s="10"/>
       <c r="E1572" s="10"/>
     </row>
     <row r="1573">
       <c r="A1573" s="10"/>
-      <c r="B1573" s="18"/>
+      <c r="B1573" s="17"/>
       <c r="C1573" s="10"/>
       <c r="D1573" s="10"/>
       <c r="E1573" s="10"/>
     </row>
     <row r="1574">
       <c r="A1574" s="10"/>
-      <c r="B1574" s="18"/>
+      <c r="B1574" s="17"/>
       <c r="C1574" s="10"/>
       <c r="D1574" s="10"/>
       <c r="E1574" s="10"/>
     </row>
     <row r="1575">
       <c r="A1575" s="10"/>
-      <c r="B1575" s="18"/>
+      <c r="B1575" s="17"/>
       <c r="C1575" s="10"/>
       <c r="D1575" s="10"/>
       <c r="E1575" s="10"/>
     </row>
     <row r="1576">
       <c r="A1576" s="10"/>
-      <c r="B1576" s="18"/>
+      <c r="B1576" s="17"/>
       <c r="C1576" s="10"/>
       <c r="D1576" s="10"/>
       <c r="E1576" s="10"/>
     </row>
     <row r="1577">
       <c r="A1577" s="10"/>
-      <c r="B1577" s="18"/>
+      <c r="B1577" s="17"/>
       <c r="C1577" s="10"/>
       <c r="D1577" s="10"/>
       <c r="E1577" s="10"/>
     </row>
     <row r="1578">
       <c r="A1578" s="10"/>
-      <c r="B1578" s="18"/>
+      <c r="B1578" s="17"/>
       <c r="C1578" s="10"/>
       <c r="D1578" s="10"/>
       <c r="E1578" s="10"/>
     </row>
     <row r="1579">
       <c r="A1579" s="10"/>
-      <c r="B1579" s="18"/>
+      <c r="B1579" s="17"/>
       <c r="C1579" s="10"/>
       <c r="D1579" s="10"/>
       <c r="E1579" s="10"/>
     </row>
     <row r="1580">
       <c r="A1580" s="10"/>
-      <c r="B1580" s="18"/>
+      <c r="B1580" s="17"/>
       <c r="C1580" s="10"/>
       <c r="D1580" s="10"/>
       <c r="E1580" s="10"/>
     </row>
     <row r="1581">
       <c r="A1581" s="10"/>
-      <c r="B1581" s="18"/>
+      <c r="B1581" s="17"/>
       <c r="C1581" s="10"/>
       <c r="D1581" s="10"/>
       <c r="E1581" s="10"/>
     </row>
     <row r="1582">
       <c r="A1582" s="10"/>
-      <c r="B1582" s="18"/>
+      <c r="B1582" s="17"/>
       <c r="C1582" s="10"/>
       <c r="D1582" s="10"/>
       <c r="E1582" s="10"/>
     </row>
     <row r="1583">
       <c r="A1583" s="10"/>
-      <c r="B1583" s="18"/>
+      <c r="B1583" s="17"/>
       <c r="C1583" s="10"/>
       <c r="D1583" s="10"/>
       <c r="E1583" s="10"/>
     </row>
     <row r="1584">
       <c r="A1584" s="10"/>
-      <c r="B1584" s="18"/>
+      <c r="B1584" s="17"/>
       <c r="C1584" s="10"/>
       <c r="D1584" s="10"/>
       <c r="E1584" s="10"/>
     </row>
     <row r="1585">
       <c r="A1585" s="10"/>
-      <c r="B1585" s="18"/>
+      <c r="B1585" s="17"/>
       <c r="C1585" s="10"/>
       <c r="D1585" s="10"/>
       <c r="E1585" s="10"/>
     </row>
     <row r="1586">
       <c r="A1586" s="10"/>
-      <c r="B1586" s="18"/>
+      <c r="B1586" s="17"/>
       <c r="C1586" s="10"/>
       <c r="D1586" s="10"/>
       <c r="E1586" s="10"/>
     </row>
     <row r="1587">
       <c r="A1587" s="10"/>
-      <c r="B1587" s="18"/>
+      <c r="B1587" s="17"/>
       <c r="C1587" s="10"/>
       <c r="D1587" s="10"/>
       <c r="E1587" s="10"/>
     </row>
     <row r="1588">
       <c r="A1588" s="10"/>
-      <c r="B1588" s="18"/>
+      <c r="B1588" s="17"/>
       <c r="C1588" s="10"/>
       <c r="D1588" s="10"/>
       <c r="E1588" s="10"/>
     </row>
     <row r="1589">
       <c r="A1589" s="10"/>
-      <c r="B1589" s="18"/>
+      <c r="B1589" s="17"/>
       <c r="C1589" s="10"/>
       <c r="D1589" s="10"/>
       <c r="E1589" s="10"/>
     </row>
     <row r="1590">
       <c r="A1590" s="10"/>
-      <c r="B1590" s="18"/>
+      <c r="B1590" s="17"/>
       <c r="C1590" s="10"/>
       <c r="D1590" s="10"/>
       <c r="E1590" s="10"/>
     </row>
     <row r="1591">
       <c r="A1591" s="10"/>
-      <c r="B1591" s="18"/>
+      <c r="B1591" s="17"/>
       <c r="C1591" s="10"/>
       <c r="D1591" s="10"/>
       <c r="E1591" s="10"/>
     </row>
     <row r="1592">
       <c r="A1592" s="10"/>
-      <c r="B1592" s="18"/>
+      <c r="B1592" s="17"/>
       <c r="C1592" s="10"/>
       <c r="D1592" s="10"/>
       <c r="E1592" s="10"/>
     </row>
     <row r="1593">
       <c r="A1593" s="10"/>
-      <c r="B1593" s="18"/>
+      <c r="B1593" s="17"/>
       <c r="C1593" s="10"/>
       <c r="D1593" s="10"/>
       <c r="E1593" s="10"/>
     </row>
     <row r="1594">
       <c r="A1594" s="10"/>
-      <c r="B1594" s="18"/>
+      <c r="B1594" s="17"/>
       <c r="C1594" s="10"/>
       <c r="D1594" s="10"/>
       <c r="E1594" s="10"/>
     </row>
     <row r="1595">
       <c r="A1595" s="10"/>
-      <c r="B1595" s="18"/>
+      <c r="B1595" s="17"/>
       <c r="C1595" s="10"/>
       <c r="D1595" s="10"/>
       <c r="E1595" s="10"/>
     </row>
     <row r="1596">
       <c r="A1596" s="10"/>
-      <c r="B1596" s="18"/>
+      <c r="B1596" s="17"/>
       <c r="C1596" s="10"/>
       <c r="D1596" s="10"/>
       <c r="E1596" s="10"/>
     </row>
     <row r="1597">
       <c r="A1597" s="10"/>
-      <c r="B1597" s="18"/>
+      <c r="B1597" s="17"/>
       <c r="C1597" s="10"/>
       <c r="D1597" s="10"/>
       <c r="E1597" s="10"/>
     </row>
     <row r="1598">
       <c r="A1598" s="10"/>
-      <c r="B1598" s="18"/>
+      <c r="B1598" s="17"/>
       <c r="C1598" s="10"/>
       <c r="D1598" s="10"/>
       <c r="E1598" s="10"/>
     </row>
     <row r="1599">
       <c r="A1599" s="10"/>
-      <c r="B1599" s="18"/>
+      <c r="B1599" s="17"/>
       <c r="C1599" s="10"/>
       <c r="D1599" s="10"/>
       <c r="E1599" s="10"/>
     </row>
     <row r="1600">
       <c r="A1600" s="10"/>
-      <c r="B1600" s="18"/>
+      <c r="B1600" s="17"/>
       <c r="C1600" s="10"/>
       <c r="D1600" s="10"/>
       <c r="E1600" s="10"/>
     </row>
     <row r="1601">
       <c r="A1601" s="10"/>
-      <c r="B1601" s="18"/>
+      <c r="B1601" s="17"/>
       <c r="C1601" s="10"/>
       <c r="D1601" s="10"/>
       <c r="E1601" s="10"/>
     </row>
     <row r="1602">
       <c r="A1602" s="10"/>
-      <c r="B1602" s="18"/>
+      <c r="B1602" s="17"/>
       <c r="C1602" s="10"/>
       <c r="D1602" s="10"/>
       <c r="E1602" s="10"/>
     </row>
     <row r="1603">
       <c r="A1603" s="10"/>
-      <c r="B1603" s="18"/>
+      <c r="B1603" s="17"/>
       <c r="C1603" s="10"/>
       <c r="D1603" s="10"/>
       <c r="E1603" s="10"/>
     </row>
     <row r="1604">
       <c r="A1604" s="10"/>
-      <c r="B1604" s="18"/>
+      <c r="B1604" s="17"/>
       <c r="C1604" s="10"/>
       <c r="D1604" s="10"/>
       <c r="E1604" s="10"/>
     </row>
     <row r="1605">
       <c r="A1605" s="10"/>
-      <c r="B1605" s="18"/>
+      <c r="B1605" s="17"/>
       <c r="C1605" s="10"/>
       <c r="D1605" s="10"/>
       <c r="E1605" s="10"/>
     </row>
     <row r="1606">
       <c r="A1606" s="10"/>
-      <c r="B1606" s="18"/>
+      <c r="B1606" s="17"/>
       <c r="C1606" s="10"/>
       <c r="D1606" s="10"/>
       <c r="E1606" s="10"/>
     </row>
     <row r="1607">
       <c r="A1607" s="10"/>
-      <c r="B1607" s="18"/>
+      <c r="B1607" s="17"/>
       <c r="C1607" s="10"/>
       <c r="D1607" s="10"/>
       <c r="E1607" s="10"/>
     </row>
     <row r="1608">
       <c r="A1608" s="10"/>
-      <c r="B1608" s="18"/>
+      <c r="B1608" s="17"/>
       <c r="C1608" s="10"/>
       <c r="D1608" s="10"/>
       <c r="E1608" s="10"/>
     </row>
     <row r="1609">
       <c r="A1609" s="10"/>
-      <c r="B1609" s="18"/>
+      <c r="B1609" s="17"/>
       <c r="C1609" s="10"/>
       <c r="D1609" s="10"/>
       <c r="E1609" s="10"/>
     </row>
     <row r="1610">
       <c r="A1610" s="10"/>
-      <c r="B1610" s="18"/>
+      <c r="B1610" s="17"/>
       <c r="C1610" s="10"/>
       <c r="D1610" s="10"/>
       <c r="E1610" s="10"/>
     </row>
     <row r="1611">
       <c r="A1611" s="10"/>
-      <c r="B1611" s="18"/>
+      <c r="B1611" s="17"/>
       <c r="C1611" s="10"/>
       <c r="D1611" s="10"/>
       <c r="E1611" s="10"/>
     </row>
     <row r="1612">
       <c r="A1612" s="10"/>
-      <c r="B1612" s="18"/>
+      <c r="B1612" s="17"/>
       <c r="C1612" s="10"/>
       <c r="D1612" s="10"/>
       <c r="E1612" s="10"/>
     </row>
     <row r="1613">
       <c r="A1613" s="10"/>
-      <c r="B1613" s="18"/>
+      <c r="B1613" s="17"/>
       <c r="C1613" s="10"/>
       <c r="D1613" s="10"/>
       <c r="E1613" s="10"/>
     </row>
     <row r="1614">
       <c r="A1614" s="10"/>
-      <c r="B1614" s="18"/>
+      <c r="B1614" s="17"/>
       <c r="C1614" s="10"/>
       <c r="D1614" s="10"/>
       <c r="E1614" s="10"/>
     </row>
     <row r="1615">
       <c r="A1615" s="10"/>
-      <c r="B1615" s="18"/>
+      <c r="B1615" s="17"/>
       <c r="C1615" s="10"/>
       <c r="D1615" s="10"/>
       <c r="E1615" s="10"/>
     </row>
     <row r="1616">
       <c r="A1616" s="10"/>
-      <c r="B1616" s="18"/>
+      <c r="B1616" s="17"/>
       <c r="C1616" s="10"/>
       <c r="D1616" s="10"/>
       <c r="E1616" s="10"/>
     </row>
     <row r="1617">
       <c r="A1617" s="10"/>
-      <c r="B1617" s="18"/>
+      <c r="B1617" s="17"/>
       <c r="C1617" s="10"/>
       <c r="D1617" s="10"/>
       <c r="E1617" s="10"/>
     </row>
     <row r="1618">
       <c r="A1618" s="10"/>
-      <c r="B1618" s="18"/>
+      <c r="B1618" s="17"/>
       <c r="C1618" s="10"/>
       <c r="D1618" s="10"/>
       <c r="E1618" s="10"/>
     </row>
     <row r="1619">
       <c r="A1619" s="10"/>
-      <c r="B1619" s="18"/>
+      <c r="B1619" s="17"/>
       <c r="C1619" s="10"/>
       <c r="D1619" s="10"/>
       <c r="E1619" s="10"/>
     </row>
     <row r="1620">
       <c r="A1620" s="10"/>
-      <c r="B1620" s="18"/>
+      <c r="B1620" s="17"/>
       <c r="C1620" s="10"/>
       <c r="D1620" s="10"/>
       <c r="E1620" s="10"/>
     </row>
     <row r="1621">
       <c r="A1621" s="10"/>
-      <c r="B1621" s="18"/>
+      <c r="B1621" s="17"/>
       <c r="C1621" s="10"/>
       <c r="D1621" s="10"/>
       <c r="E1621" s="10"/>
     </row>
     <row r="1622">
       <c r="A1622" s="10"/>
-      <c r="B1622" s="18"/>
+      <c r="B1622" s="17"/>
       <c r="C1622" s="10"/>
       <c r="D1622" s="10"/>
       <c r="E1622" s="10"/>
     </row>
     <row r="1623">
       <c r="A1623" s="10"/>
-      <c r="B1623" s="18"/>
+      <c r="B1623" s="17"/>
       <c r="C1623" s="10"/>
       <c r="D1623" s="10"/>
       <c r="E1623" s="10"/>
     </row>
     <row r="1624">
       <c r="A1624" s="10"/>
-      <c r="B1624" s="18"/>
+      <c r="B1624" s="17"/>
       <c r="C1624" s="10"/>
       <c r="D1624" s="10"/>
       <c r="E1624" s="10"/>
     </row>
     <row r="1625">
       <c r="A1625" s="10"/>
-      <c r="B1625" s="18"/>
+      <c r="B1625" s="17"/>
       <c r="C1625" s="10"/>
       <c r="D1625" s="10"/>
       <c r="E1625" s="10"/>
     </row>
     <row r="1626">
       <c r="A1626" s="10"/>
-      <c r="B1626" s="18"/>
+      <c r="B1626" s="17"/>
       <c r="C1626" s="10"/>
       <c r="D1626" s="10"/>
       <c r="E1626" s="10"/>
     </row>
     <row r="1627">
       <c r="A1627" s="10"/>
-      <c r="B1627" s="18"/>
+      <c r="B1627" s="17"/>
       <c r="C1627" s="10"/>
       <c r="D1627" s="10"/>
       <c r="E1627" s="10"/>
     </row>
     <row r="1628">
       <c r="A1628" s="10"/>
-      <c r="B1628" s="18"/>
+      <c r="B1628" s="17"/>
       <c r="C1628" s="10"/>
       <c r="D1628" s="10"/>
       <c r="E1628" s="10"/>
     </row>
     <row r="1629">
       <c r="A1629" s="10"/>
-      <c r="B1629" s="18"/>
+      <c r="B1629" s="17"/>
       <c r="C1629" s="10"/>
       <c r="D1629" s="10"/>
       <c r="E1629" s="10"/>
     </row>
     <row r="1630">
       <c r="A1630" s="10"/>
-      <c r="B1630" s="18"/>
+      <c r="B1630" s="17"/>
       <c r="C1630" s="10"/>
       <c r="D1630" s="10"/>
       <c r="E1630" s="10"/>
     </row>
     <row r="1631">
       <c r="A1631" s="10"/>
-      <c r="B1631" s="18"/>
+      <c r="B1631" s="17"/>
       <c r="C1631" s="10"/>
       <c r="D1631" s="10"/>
       <c r="E1631" s="10"/>
     </row>
     <row r="1632">
       <c r="A1632" s="10"/>
-      <c r="B1632" s="18"/>
+      <c r="B1632" s="17"/>
       <c r="C1632" s="10"/>
       <c r="D1632" s="10"/>
       <c r="E1632" s="10"/>
     </row>
     <row r="1633">
       <c r="A1633" s="10"/>
-      <c r="B1633" s="18"/>
+      <c r="B1633" s="17"/>
       <c r="C1633" s="10"/>
       <c r="D1633" s="10"/>
       <c r="E1633" s="10"/>
     </row>
     <row r="1634">
       <c r="A1634" s="10"/>
-      <c r="B1634" s="18"/>
+      <c r="B1634" s="17"/>
       <c r="C1634" s="10"/>
       <c r="D1634" s="10"/>
       <c r="E1634" s="10"/>
     </row>
     <row r="1635">
       <c r="A1635" s="10"/>
-      <c r="B1635" s="18"/>
+      <c r="B1635" s="17"/>
       <c r="C1635" s="10"/>
       <c r="D1635" s="10"/>
       <c r="E1635" s="10"/>
     </row>
     <row r="1636">
       <c r="A1636" s="10"/>
-      <c r="B1636" s="18"/>
+      <c r="B1636" s="17"/>
       <c r="C1636" s="10"/>
       <c r="D1636" s="10"/>
       <c r="E1636" s="10"/>
     </row>
     <row r="1637">
       <c r="A1637" s="10"/>
-      <c r="B1637" s="18"/>
+      <c r="B1637" s="17"/>
       <c r="C1637" s="10"/>
       <c r="D1637" s="10"/>
       <c r="E1637" s="10"/>
     </row>
     <row r="1638">
       <c r="A1638" s="10"/>
-      <c r="B1638" s="18"/>
+      <c r="B1638" s="17"/>
       <c r="C1638" s="10"/>
       <c r="D1638" s="10"/>
       <c r="E1638" s="10"/>
     </row>
     <row r="1639">
       <c r="A1639" s="10"/>
-      <c r="B1639" s="18"/>
+      <c r="B1639" s="17"/>
       <c r="C1639" s="10"/>
       <c r="D1639" s="10"/>
       <c r="E1639" s="10"/>
     </row>
     <row r="1640">
       <c r="A1640" s="10"/>
-      <c r="B1640" s="18"/>
+      <c r="B1640" s="17"/>
       <c r="C1640" s="10"/>
       <c r="D1640" s="10"/>
       <c r="E1640" s="10"/>
     </row>
     <row r="1641">
       <c r="A1641" s="10"/>
-      <c r="B1641" s="18"/>
+      <c r="B1641" s="17"/>
       <c r="C1641" s="10"/>
       <c r="D1641" s="10"/>
       <c r="E1641" s="10"/>
     </row>
     <row r="1642">
       <c r="A1642" s="10"/>
-      <c r="B1642" s="18"/>
+      <c r="B1642" s="17"/>
       <c r="C1642" s="10"/>
       <c r="D1642" s="10"/>
       <c r="E1642" s="10"/>
     </row>
     <row r="1643">
       <c r="A1643" s="10"/>
-      <c r="B1643" s="18"/>
+      <c r="B1643" s="17"/>
       <c r="C1643" s="10"/>
       <c r="D1643" s="10"/>
       <c r="E1643" s="10"/>
     </row>
     <row r="1644">
       <c r="A1644" s="10"/>
-      <c r="B1644" s="18"/>
+      <c r="B1644" s="17"/>
       <c r="C1644" s="10"/>
       <c r="D1644" s="10"/>
       <c r="E1644" s="10"/>
     </row>
     <row r="1645">
       <c r="A1645" s="10"/>
-      <c r="B1645" s="18"/>
+      <c r="B1645" s="17"/>
       <c r="C1645" s="10"/>
       <c r="D1645" s="10"/>
       <c r="E1645" s="10"/>
     </row>
     <row r="1646">
       <c r="A1646" s="10"/>
-      <c r="B1646" s="18"/>
+      <c r="B1646" s="17"/>
       <c r="C1646" s="10"/>
       <c r="D1646" s="10"/>
       <c r="E1646" s="10"/>
     </row>
     <row r="1647">
       <c r="A1647" s="10"/>
-      <c r="B1647" s="18"/>
+      <c r="B1647" s="17"/>
       <c r="C1647" s="10"/>
       <c r="D1647" s="10"/>
       <c r="E1647" s="10"/>
     </row>
     <row r="1648">
       <c r="A1648" s="10"/>
-      <c r="B1648" s="18"/>
+      <c r="B1648" s="17"/>
       <c r="C1648" s="10"/>
       <c r="D1648" s="10"/>
       <c r="E1648" s="10"/>
     </row>
     <row r="1649">
       <c r="A1649" s="10"/>
-      <c r="B1649" s="18"/>
+      <c r="B1649" s="17"/>
       <c r="C1649" s="10"/>
       <c r="D1649" s="10"/>
       <c r="E1649" s="10"/>
     </row>
     <row r="1650">
       <c r="A1650" s="10"/>
-      <c r="B1650" s="18"/>
+      <c r="B1650" s="17"/>
       <c r="C1650" s="10"/>
       <c r="D1650" s="10"/>
       <c r="E1650" s="10"/>
     </row>
     <row r="1651">
       <c r="A1651" s="10"/>
-      <c r="B1651" s="18"/>
+      <c r="B1651" s="17"/>
       <c r="C1651" s="10"/>
       <c r="D1651" s="10"/>
       <c r="E1651" s="10"/>
     </row>
     <row r="1652">
       <c r="A1652" s="10"/>
-      <c r="B1652" s="18"/>
+      <c r="B1652" s="17"/>
       <c r="C1652" s="10"/>
       <c r="D1652" s="10"/>
       <c r="E1652" s="10"/>
     </row>
     <row r="1653">
       <c r="A1653" s="10"/>
-      <c r="B1653" s="18"/>
+      <c r="B1653" s="17"/>
       <c r="C1653" s="10"/>
       <c r="D1653" s="10"/>
       <c r="E1653" s="10"/>
     </row>
     <row r="1654">
       <c r="A1654" s="10"/>
-      <c r="B1654" s="18"/>
+      <c r="B1654" s="17"/>
       <c r="C1654" s="10"/>
       <c r="D1654" s="10"/>
       <c r="E1654" s="10"/>
     </row>
     <row r="1655">
       <c r="A1655" s="10"/>
-      <c r="B1655" s="18"/>
+      <c r="B1655" s="17"/>
       <c r="C1655" s="10"/>
       <c r="D1655" s="10"/>
       <c r="E1655" s="10"/>
     </row>
     <row r="1656">
       <c r="A1656" s="10"/>
-      <c r="B1656" s="18"/>
+      <c r="B1656" s="17"/>
       <c r="C1656" s="10"/>
       <c r="D1656" s="10"/>
       <c r="E1656" s="10"/>
     </row>
     <row r="1657">
       <c r="A1657" s="10"/>
-      <c r="B1657" s="18"/>
+      <c r="B1657" s="17"/>
       <c r="C1657" s="10"/>
       <c r="D1657" s="10"/>
       <c r="E1657" s="10"/>
     </row>
     <row r="1658">
       <c r="A1658" s="10"/>
-      <c r="B1658" s="18"/>
+      <c r="B1658" s="17"/>
       <c r="C1658" s="10"/>
       <c r="D1658" s="10"/>
       <c r="E1658" s="10"/>
     </row>
     <row r="1659">
       <c r="A1659" s="10"/>
-      <c r="B1659" s="18"/>
+      <c r="B1659" s="17"/>
       <c r="C1659" s="10"/>
       <c r="D1659" s="10"/>
       <c r="E1659" s="10"/>
     </row>
     <row r="1660">
       <c r="A1660" s="10"/>
-      <c r="B1660" s="18"/>
+      <c r="B1660" s="17"/>
       <c r="C1660" s="10"/>
       <c r="D1660" s="10"/>
       <c r="E1660" s="10"/>
     </row>
     <row r="1661">
       <c r="A1661" s="10"/>
-      <c r="B1661" s="18"/>
+      <c r="B1661" s="17"/>
       <c r="C1661" s="10"/>
       <c r="D1661" s="10"/>
       <c r="E1661" s="10"/>
     </row>
     <row r="1662">
       <c r="A1662" s="10"/>
-      <c r="B1662" s="18"/>
+      <c r="B1662" s="17"/>
       <c r="C1662" s="10"/>
       <c r="D1662" s="10"/>
       <c r="E1662" s="10"/>
     </row>
     <row r="1663">
       <c r="A1663" s="10"/>
-      <c r="B1663" s="18"/>
+      <c r="B1663" s="17"/>
       <c r="C1663" s="10"/>
       <c r="D1663" s="10"/>
       <c r="E1663" s="10"/>
     </row>
     <row r="1664">
       <c r="A1664" s="10"/>
-      <c r="B1664" s="18"/>
+      <c r="B1664" s="17"/>
       <c r="C1664" s="10"/>
       <c r="D1664" s="10"/>
       <c r="E1664" s="10"/>
     </row>
     <row r="1665">
       <c r="A1665" s="10"/>
-      <c r="B1665" s="18"/>
+      <c r="B1665" s="17"/>
       <c r="C1665" s="10"/>
       <c r="D1665" s="10"/>
       <c r="E1665" s="10"/>
     </row>
     <row r="1666">
       <c r="A1666" s="10"/>
-      <c r="B1666" s="18"/>
+      <c r="B1666" s="17"/>
       <c r="C1666" s="10"/>
       <c r="D1666" s="10"/>
       <c r="E1666" s="10"/>
     </row>
     <row r="1667">
       <c r="A1667" s="10"/>
-      <c r="B1667" s="18"/>
+      <c r="B1667" s="17"/>
       <c r="C1667" s="10"/>
       <c r="D1667" s="10"/>
       <c r="E1667" s="10"/>
     </row>
     <row r="1668">
       <c r="A1668" s="10"/>
-      <c r="B1668" s="18"/>
+      <c r="B1668" s="17"/>
       <c r="C1668" s="10"/>
       <c r="D1668" s="10"/>
       <c r="E1668" s="10"/>
     </row>
     <row r="1669">
       <c r="A1669" s="10"/>
-      <c r="B1669" s="18"/>
+      <c r="B1669" s="17"/>
       <c r="C1669" s="10"/>
       <c r="D1669" s="10"/>
       <c r="E1669" s="10"/>
     </row>
     <row r="1670">
       <c r="A1670" s="10"/>
-      <c r="B1670" s="18"/>
+      <c r="B1670" s="17"/>
       <c r="C1670" s="10"/>
       <c r="D1670" s="10"/>
       <c r="E1670" s="10"/>
     </row>
     <row r="1671">
       <c r="A1671" s="10"/>
-      <c r="B1671" s="18"/>
+      <c r="B1671" s="17"/>
       <c r="C1671" s="10"/>
       <c r="D1671" s="10"/>
       <c r="E1671" s="10"/>
     </row>
     <row r="1672">
       <c r="A1672" s="10"/>
-      <c r="B1672" s="18"/>
+      <c r="B1672" s="17"/>
       <c r="C1672" s="10"/>
       <c r="D1672" s="10"/>
       <c r="E1672" s="10"/>
     </row>
     <row r="1673">
       <c r="A1673" s="10"/>
-      <c r="B1673" s="18"/>
+      <c r="B1673" s="17"/>
       <c r="C1673" s="10"/>
       <c r="D1673" s="10"/>
       <c r="E1673" s="10"/>
     </row>
     <row r="1674">
       <c r="A1674" s="10"/>
-      <c r="B1674" s="18"/>
+      <c r="B1674" s="17"/>
       <c r="C1674" s="10"/>
       <c r="D1674" s="10"/>
       <c r="E1674" s="10"/>
     </row>
     <row r="1675">
       <c r="A1675" s="10"/>
-      <c r="B1675" s="18"/>
+      <c r="B1675" s="17"/>
       <c r="C1675" s="10"/>
       <c r="D1675" s="10"/>
       <c r="E1675" s="10"/>
     </row>
     <row r="1676">
       <c r="A1676" s="10"/>
-      <c r="B1676" s="18"/>
+      <c r="B1676" s="17"/>
       <c r="C1676" s="10"/>
       <c r="D1676" s="10"/>
       <c r="E1676" s="10"/>
     </row>
     <row r="1677">
       <c r="A1677" s="10"/>
-      <c r="B1677" s="18"/>
+      <c r="B1677" s="17"/>
       <c r="C1677" s="10"/>
       <c r="D1677" s="10"/>
       <c r="E1677" s="10"/>
     </row>
     <row r="1678">
       <c r="A1678" s="10"/>
-      <c r="B1678" s="18"/>
+      <c r="B1678" s="17"/>
       <c r="C1678" s="10"/>
       <c r="D1678" s="10"/>
       <c r="E1678" s="10"/>
     </row>
     <row r="1679">
       <c r="A1679" s="10"/>
-      <c r="B1679" s="18"/>
+      <c r="B1679" s="17"/>
       <c r="C1679" s="10"/>
       <c r="D1679" s="10"/>
       <c r="E1679" s="10"/>
     </row>
     <row r="1680">
       <c r="A1680" s="10"/>
-      <c r="B1680" s="18"/>
+      <c r="B1680" s="17"/>
       <c r="C1680" s="10"/>
       <c r="D1680" s="10"/>
       <c r="E1680" s="10"/>
     </row>
     <row r="1681">
       <c r="A1681" s="10"/>
-      <c r="B1681" s="18"/>
+      <c r="B1681" s="17"/>
       <c r="C1681" s="10"/>
       <c r="D1681" s="10"/>
       <c r="E1681" s="10"/>
     </row>
     <row r="1682">
       <c r="A1682" s="10"/>
-      <c r="B1682" s="18"/>
+      <c r="B1682" s="17"/>
       <c r="C1682" s="10"/>
       <c r="D1682" s="10"/>
       <c r="E1682" s="10"/>
     </row>
     <row r="1683">
       <c r="A1683" s="10"/>
-      <c r="B1683" s="18"/>
+      <c r="B1683" s="17"/>
       <c r="C1683" s="10"/>
       <c r="D1683" s="10"/>
       <c r="E1683" s="10"/>
     </row>
     <row r="1684">
       <c r="A1684" s="10"/>
-      <c r="B1684" s="18"/>
+      <c r="B1684" s="17"/>
       <c r="C1684" s="10"/>
       <c r="D1684" s="10"/>
       <c r="E1684" s="10"/>
     </row>
     <row r="1685">
       <c r="A1685" s="10"/>
-      <c r="B1685" s="18"/>
+      <c r="B1685" s="17"/>
       <c r="C1685" s="10"/>
       <c r="D1685" s="10"/>
       <c r="E1685" s="10"/>
     </row>
     <row r="1686">
       <c r="A1686" s="10"/>
-      <c r="B1686" s="18"/>
+      <c r="B1686" s="17"/>
       <c r="C1686" s="10"/>
       <c r="D1686" s="10"/>
       <c r="E1686" s="10"/>
     </row>
     <row r="1687">
       <c r="A1687" s="10"/>
-      <c r="B1687" s="18"/>
+      <c r="B1687" s="17"/>
       <c r="C1687" s="10"/>
       <c r="D1687" s="10"/>
       <c r="E1687" s="10"/>
     </row>
     <row r="1688">
       <c r="A1688" s="10"/>
-      <c r="B1688" s="18"/>
+      <c r="B1688" s="17"/>
       <c r="C1688" s="10"/>
       <c r="D1688" s="10"/>
       <c r="E1688" s="10"/>
     </row>
     <row r="1689">
       <c r="A1689" s="10"/>
-      <c r="B1689" s="18"/>
+      <c r="B1689" s="17"/>
       <c r="C1689" s="10"/>
       <c r="D1689" s="10"/>
       <c r="E1689" s="10"/>
     </row>
     <row r="1690">
       <c r="A1690" s="10"/>
-      <c r="B1690" s="18"/>
+      <c r="B1690" s="17"/>
       <c r="C1690" s="10"/>
       <c r="D1690" s="10"/>
       <c r="E1690" s="10"/>
     </row>
     <row r="1691">
       <c r="A1691" s="10"/>
-      <c r="B1691" s="18"/>
+      <c r="B1691" s="17"/>
       <c r="C1691" s="10"/>
       <c r="D1691" s="10"/>
       <c r="E1691" s="10"/>
     </row>
     <row r="1692">
       <c r="A1692" s="10"/>
-      <c r="B1692" s="18"/>
+      <c r="B1692" s="17"/>
       <c r="C1692" s="10"/>
       <c r="D1692" s="10"/>
       <c r="E1692" s="10"/>
     </row>
     <row r="1693">
       <c r="A1693" s="10"/>
-      <c r="B1693" s="18"/>
+      <c r="B1693" s="17"/>
       <c r="C1693" s="10"/>
       <c r="D1693" s="10"/>
       <c r="E1693" s="10"/>
     </row>
     <row r="1694">
       <c r="A1694" s="10"/>
-      <c r="B1694" s="18"/>
+      <c r="B1694" s="17"/>
       <c r="C1694" s="10"/>
       <c r="D1694" s="10"/>
       <c r="E1694" s="10"/>
     </row>
     <row r="1695">
       <c r="A1695" s="10"/>
-      <c r="B1695" s="18"/>
+      <c r="B1695" s="17"/>
       <c r="C1695" s="10"/>
       <c r="D1695" s="10"/>
       <c r="E1695" s="10"/>
     </row>
     <row r="1696">
       <c r="A1696" s="10"/>
-      <c r="B1696" s="18"/>
+      <c r="B1696" s="17"/>
       <c r="C1696" s="10"/>
       <c r="D1696" s="10"/>
       <c r="E1696" s="10"/>
     </row>
     <row r="1697">
       <c r="A1697" s="10"/>
-      <c r="B1697" s="18"/>
+      <c r="B1697" s="17"/>
       <c r="C1697" s="10"/>
       <c r="D1697" s="10"/>
       <c r="E1697" s="10"/>
     </row>
     <row r="1698">
       <c r="A1698" s="10"/>
-      <c r="B1698" s="18"/>
+      <c r="B1698" s="17"/>
       <c r="C1698" s="10"/>
       <c r="D1698" s="10"/>
       <c r="E1698" s="10"/>
     </row>
     <row r="1699">
       <c r="A1699" s="10"/>
-      <c r="B1699" s="18"/>
+      <c r="B1699" s="17"/>
       <c r="C1699" s="10"/>
       <c r="D1699" s="10"/>
       <c r="E1699" s="10"/>
     </row>
     <row r="1700">
       <c r="A1700" s="10"/>
-      <c r="B1700" s="18"/>
+      <c r="B1700" s="17"/>
       <c r="C1700" s="10"/>
       <c r="D1700" s="10"/>
       <c r="E1700" s="10"/>
     </row>
     <row r="1701">
       <c r="A1701" s="10"/>
-      <c r="B1701" s="18"/>
+      <c r="B1701" s="17"/>
       <c r="C1701" s="10"/>
       <c r="D1701" s="10"/>
       <c r="E1701" s="10"/>
     </row>
     <row r="1702">
       <c r="A1702" s="10"/>
-      <c r="B1702" s="18"/>
+      <c r="B1702" s="17"/>
       <c r="C1702" s="10"/>
       <c r="D1702" s="10"/>
       <c r="E1702" s="10"/>
     </row>
     <row r="1703">
       <c r="A1703" s="10"/>
-      <c r="B1703" s="18"/>
+      <c r="B1703" s="17"/>
       <c r="C1703" s="10"/>
       <c r="D1703" s="10"/>
       <c r="E1703" s="10"/>
     </row>
     <row r="1704">
       <c r="A1704" s="10"/>
-      <c r="B1704" s="18"/>
+      <c r="B1704" s="17"/>
       <c r="C1704" s="10"/>
       <c r="D1704" s="10"/>
       <c r="E1704" s="10"/>
     </row>
     <row r="1705">
       <c r="A1705" s="10"/>
-      <c r="B1705" s="18"/>
+      <c r="B1705" s="17"/>
       <c r="C1705" s="10"/>
       <c r="D1705" s="10"/>
       <c r="E1705" s="10"/>
     </row>
     <row r="1706">
       <c r="A1706" s="10"/>
-      <c r="B1706" s="18"/>
+      <c r="B1706" s="17"/>
       <c r="C1706" s="10"/>
       <c r="D1706" s="10"/>
       <c r="E1706" s="10"/>
     </row>
     <row r="1707">
       <c r="A1707" s="10"/>
-      <c r="B1707" s="18"/>
+      <c r="B1707" s="17"/>
       <c r="C1707" s="10"/>
       <c r="D1707" s="10"/>
       <c r="E1707" s="10"/>
     </row>
     <row r="1708">
       <c r="A1708" s="10"/>
-      <c r="B1708" s="18"/>
+      <c r="B1708" s="17"/>
       <c r="C1708" s="10"/>
       <c r="D1708" s="10"/>
       <c r="E1708" s="10"/>
     </row>
     <row r="1709">
       <c r="A1709" s="10"/>
-      <c r="B1709" s="18"/>
+      <c r="B1709" s="17"/>
       <c r="C1709" s="10"/>
       <c r="D1709" s="10"/>
       <c r="E1709" s="10"/>
     </row>
     <row r="1710">
       <c r="A1710" s="10"/>
-      <c r="B1710" s="18"/>
+      <c r="B1710" s="17"/>
       <c r="C1710" s="10"/>
       <c r="D1710" s="10"/>
       <c r="E1710" s="10"/>
     </row>
     <row r="1711">
       <c r="A1711" s="10"/>
-      <c r="B1711" s="18"/>
+      <c r="B1711" s="17"/>
       <c r="C1711" s="10"/>
       <c r="D1711" s="10"/>
       <c r="E1711" s="10"/>
     </row>
     <row r="1712">
       <c r="A1712" s="10"/>
-      <c r="B1712" s="18"/>
+      <c r="B1712" s="17"/>
       <c r="C1712" s="10"/>
       <c r="D1712" s="10"/>
       <c r="E1712" s="10"/>
     </row>
     <row r="1713">
       <c r="A1713" s="10"/>
-      <c r="B1713" s="18"/>
+      <c r="B1713" s="17"/>
       <c r="C1713" s="10"/>
       <c r="D1713" s="10"/>
       <c r="E1713" s="10"/>
     </row>
     <row r="1714">
       <c r="A1714" s="10"/>
-      <c r="B1714" s="18"/>
+      <c r="B1714" s="17"/>
       <c r="C1714" s="10"/>
       <c r="D1714" s="10"/>
       <c r="E1714" s="10"/>
     </row>
     <row r="1715">
       <c r="A1715" s="10"/>
-      <c r="B1715" s="18"/>
+      <c r="B1715" s="17"/>
       <c r="C1715" s="10"/>
       <c r="D1715" s="10"/>
       <c r="E1715" s="10"/>
     </row>
     <row r="1716">
       <c r="A1716" s="10"/>
-      <c r="B1716" s="18"/>
+      <c r="B1716" s="17"/>
       <c r="C1716" s="10"/>
       <c r="D1716" s="10"/>
       <c r="E1716" s="10"/>
     </row>
     <row r="1717">
       <c r="A1717" s="10"/>
-      <c r="B1717" s="18"/>
+      <c r="B1717" s="17"/>
       <c r="C1717" s="10"/>
       <c r="D1717" s="10"/>
       <c r="E1717" s="10"/>
     </row>
     <row r="1718">
       <c r="A1718" s="10"/>
-      <c r="B1718" s="18"/>
+      <c r="B1718" s="17"/>
       <c r="C1718" s="10"/>
       <c r="D1718" s="10"/>
       <c r="E1718" s="10"/>
     </row>
     <row r="1719">
       <c r="A1719" s="10"/>
-      <c r="B1719" s="18"/>
+      <c r="B1719" s="17"/>
       <c r="C1719" s="10"/>
       <c r="D1719" s="10"/>
       <c r="E1719" s="10"/>
     </row>
     <row r="1720">
       <c r="A1720" s="10"/>
-      <c r="B1720" s="18"/>
+      <c r="B1720" s="17"/>
       <c r="C1720" s="10"/>
       <c r="D1720" s="10"/>
       <c r="E1720" s="10"/>
     </row>
     <row r="1721">
       <c r="A1721" s="10"/>
-      <c r="B1721" s="18"/>
+      <c r="B1721" s="17"/>
       <c r="C1721" s="10"/>
       <c r="D1721" s="10"/>
       <c r="E1721" s="10"/>
     </row>
     <row r="1722">
       <c r="A1722" s="10"/>
-      <c r="B1722" s="18"/>
+      <c r="B1722" s="17"/>
       <c r="C1722" s="10"/>
       <c r="D1722" s="10"/>
       <c r="E1722" s="10"/>
     </row>
     <row r="1723">
       <c r="A1723" s="10"/>
-      <c r="B1723" s="18"/>
+      <c r="B1723" s="17"/>
       <c r="C1723" s="10"/>
       <c r="D1723" s="10"/>
       <c r="E1723" s="10"/>
     </row>
     <row r="1724">
       <c r="A1724" s="10"/>
-      <c r="B1724" s="18"/>
+      <c r="B1724" s="17"/>
       <c r="C1724" s="10"/>
       <c r="D1724" s="10"/>
       <c r="E1724" s="10"/>
     </row>
     <row r="1725">
       <c r="A1725" s="10"/>
-      <c r="B1725" s="18"/>
+      <c r="B1725" s="17"/>
       <c r="C1725" s="10"/>
       <c r="D1725" s="10"/>
       <c r="E1725" s="10"/>
     </row>
     <row r="1726">
       <c r="A1726" s="10"/>
-      <c r="B1726" s="18"/>
+      <c r="B1726" s="17"/>
       <c r="C1726" s="10"/>
       <c r="D1726" s="10"/>
       <c r="E1726" s="10"/>
     </row>
     <row r="1727">
       <c r="A1727" s="10"/>
-      <c r="B1727" s="18"/>
+      <c r="B1727" s="17"/>
       <c r="C1727" s="10"/>
       <c r="D1727" s="10"/>
       <c r="E1727" s="10"/>
     </row>
     <row r="1728">
       <c r="A1728" s="10"/>
-      <c r="B1728" s="18"/>
+      <c r="B1728" s="17"/>
       <c r="C1728" s="10"/>
       <c r="D1728" s="10"/>
       <c r="E1728" s="10"/>
     </row>
     <row r="1729">
       <c r="A1729" s="10"/>
-      <c r="B1729" s="18"/>
+      <c r="B1729" s="17"/>
       <c r="C1729" s="10"/>
       <c r="D1729" s="10"/>
       <c r="E1729" s="10"/>
     </row>
     <row r="1730">
       <c r="A1730" s="10"/>
-      <c r="B1730" s="18"/>
+      <c r="B1730" s="17"/>
       <c r="C1730" s="10"/>
       <c r="D1730" s="10"/>
       <c r="E1730" s="10"/>
     </row>
     <row r="1731">
       <c r="A1731" s="10"/>
-      <c r="B1731" s="18"/>
+      <c r="B1731" s="17"/>
       <c r="C1731" s="10"/>
       <c r="D1731" s="10"/>
       <c r="E1731" s="10"/>
     </row>
     <row r="1732">
       <c r="A1732" s="10"/>
-      <c r="B1732" s="18"/>
+      <c r="B1732" s="17"/>
       <c r="C1732" s="10"/>
       <c r="D1732" s="10"/>
       <c r="E1732" s="10"/>
     </row>
     <row r="1733">
       <c r="A1733" s="10"/>
-      <c r="B1733" s="18"/>
+      <c r="B1733" s="17"/>
       <c r="C1733" s="10"/>
       <c r="D1733" s="10"/>
       <c r="E1733" s="10"/>
     </row>
     <row r="1734">
       <c r="A1734" s="10"/>
-      <c r="B1734" s="18"/>
+      <c r="B1734" s="17"/>
       <c r="C1734" s="10"/>
       <c r="D1734" s="10"/>
       <c r="E1734" s="10"/>
     </row>
     <row r="1735">
       <c r="A1735" s="10"/>
-      <c r="B1735" s="18"/>
+      <c r="B1735" s="17"/>
       <c r="C1735" s="10"/>
       <c r="D1735" s="10"/>
       <c r="E1735" s="10"/>
     </row>
     <row r="1736">
       <c r="A1736" s="10"/>
-      <c r="B1736" s="18"/>
+      <c r="B1736" s="17"/>
       <c r="C1736" s="10"/>
       <c r="D1736" s="10"/>
       <c r="E1736" s="10"/>
     </row>
     <row r="1737">
       <c r="A1737" s="10"/>
-      <c r="B1737" s="18"/>
+      <c r="B1737" s="17"/>
       <c r="C1737" s="10"/>
       <c r="D1737" s="10"/>
       <c r="E1737" s="10"/>
     </row>
     <row r="1738">
       <c r="A1738" s="10"/>
-      <c r="B1738" s="18"/>
+      <c r="B1738" s="17"/>
       <c r="C1738" s="10"/>
       <c r="D1738" s="10"/>
       <c r="E1738" s="10"/>
     </row>
     <row r="1739">
       <c r="A1739" s="10"/>
-      <c r="B1739" s="18"/>
+      <c r="B1739" s="17"/>
       <c r="C1739" s="10"/>
       <c r="D1739" s="10"/>
       <c r="E1739" s="10"/>
     </row>
     <row r="1740">
       <c r="A1740" s="10"/>
-      <c r="B1740" s="18"/>
+      <c r="B1740" s="17"/>
       <c r="C1740" s="10"/>
       <c r="D1740" s="10"/>
       <c r="E1740" s="10"/>
     </row>
     <row r="1741">
       <c r="A1741" s="10"/>
-      <c r="B1741" s="18"/>
+      <c r="B1741" s="17"/>
       <c r="C1741" s="10"/>
       <c r="D1741" s="10"/>
       <c r="E1741" s="10"/>
     </row>
     <row r="1742">
       <c r="A1742" s="10"/>
-      <c r="B1742" s="18"/>
+      <c r="B1742" s="17"/>
       <c r="C1742" s="10"/>
       <c r="D1742" s="10"/>
       <c r="E1742" s="10"/>
     </row>
     <row r="1743">
       <c r="A1743" s="10"/>
-      <c r="B1743" s="18"/>
+      <c r="B1743" s="17"/>
       <c r="C1743" s="10"/>
       <c r="D1743" s="10"/>
       <c r="E1743" s="10"/>
     </row>
     <row r="1744">
       <c r="A1744" s="10"/>
-      <c r="B1744" s="18"/>
+      <c r="B1744" s="17"/>
       <c r="C1744" s="10"/>
       <c r="D1744" s="10"/>
       <c r="E1744" s="10"/>
     </row>
     <row r="1745">
       <c r="A1745" s="10"/>
-      <c r="B1745" s="18"/>
+      <c r="B1745" s="17"/>
       <c r="C1745" s="10"/>
       <c r="D1745" s="10"/>
       <c r="E1745" s="10"/>
     </row>
     <row r="1746">
       <c r="A1746" s="10"/>
-      <c r="B1746" s="18"/>
+      <c r="B1746" s="17"/>
       <c r="C1746" s="10"/>
       <c r="D1746" s="10"/>
       <c r="E1746" s="10"/>
     </row>
     <row r="1747">
       <c r="A1747" s="10"/>
-      <c r="B1747" s="18"/>
+      <c r="B1747" s="17"/>
       <c r="C1747" s="10"/>
       <c r="D1747" s="10"/>
       <c r="E1747" s="10"/>
     </row>
     <row r="1748">
       <c r="A1748" s="10"/>
-      <c r="B1748" s="18"/>
+      <c r="B1748" s="17"/>
       <c r="C1748" s="10"/>
       <c r="D1748" s="10"/>
       <c r="E1748" s="10"/>
     </row>
     <row r="1749">
       <c r="A1749" s="10"/>
-      <c r="B1749" s="18"/>
+      <c r="B1749" s="17"/>
       <c r="C1749" s="10"/>
       <c r="D1749" s="10"/>
       <c r="E1749" s="10"/>
     </row>
     <row r="1750">
       <c r="A1750" s="10"/>
-      <c r="B1750" s="18"/>
+      <c r="B1750" s="17"/>
       <c r="C1750" s="10"/>
       <c r="D1750" s="10"/>
       <c r="E1750" s="10"/>
     </row>
     <row r="1751">
       <c r="A1751" s="10"/>
-      <c r="B1751" s="18"/>
+      <c r="B1751" s="17"/>
       <c r="C1751" s="10"/>
       <c r="D1751" s="10"/>
       <c r="E1751" s="10"/>
     </row>
     <row r="1752">
       <c r="A1752" s="10"/>
-      <c r="B1752" s="18"/>
+      <c r="B1752" s="17"/>
       <c r="C1752" s="10"/>
       <c r="D1752" s="10"/>
       <c r="E1752" s="10"/>
     </row>
     <row r="1753">
       <c r="A1753" s="10"/>
-      <c r="B1753" s="18"/>
+      <c r="B1753" s="17"/>
       <c r="C1753" s="10"/>
       <c r="D1753" s="10"/>
       <c r="E1753" s="10"/>
     </row>
     <row r="1754">
       <c r="A1754" s="10"/>
-      <c r="B1754" s="18"/>
+      <c r="B1754" s="17"/>
       <c r="C1754" s="10"/>
       <c r="D1754" s="10"/>
       <c r="E1754" s="10"/>
     </row>
     <row r="1755">
       <c r="A1755" s="10"/>
-      <c r="B1755" s="18"/>
+      <c r="B1755" s="17"/>
       <c r="C1755" s="10"/>
       <c r="D1755" s="10"/>
       <c r="E1755" s="10"/>
     </row>
     <row r="1756">
       <c r="A1756" s="10"/>
-      <c r="B1756" s="18"/>
+      <c r="B1756" s="17"/>
       <c r="C1756" s="10"/>
       <c r="D1756" s="10"/>
       <c r="E1756" s="10"/>
     </row>
     <row r="1757">
       <c r="A1757" s="10"/>
-      <c r="B1757" s="18"/>
+      <c r="B1757" s="17"/>
       <c r="C1757" s="10"/>
       <c r="D1757" s="10"/>
       <c r="E1757" s="10"/>
     </row>
     <row r="1758">
       <c r="A1758" s="10"/>
-      <c r="B1758" s="18"/>
+      <c r="B1758" s="17"/>
       <c r="C1758" s="10"/>
       <c r="D1758" s="10"/>
       <c r="E1758" s="10"/>
     </row>
     <row r="1759">
       <c r="A1759" s="10"/>
-      <c r="B1759" s="18"/>
+      <c r="B1759" s="17"/>
       <c r="C1759" s="10"/>
       <c r="D1759" s="10"/>
       <c r="E1759" s="10"/>
     </row>
     <row r="1760">
       <c r="A1760" s="10"/>
-      <c r="B1760" s="18"/>
+      <c r="B1760" s="17"/>
       <c r="C1760" s="10"/>
       <c r="D1760" s="10"/>
       <c r="E1760" s="10"/>
     </row>
     <row r="1761">
       <c r="A1761" s="10"/>
-      <c r="B1761" s="18"/>
+      <c r="B1761" s="17"/>
       <c r="C1761" s="10"/>
       <c r="D1761" s="10"/>
       <c r="E1761" s="10"/>
     </row>
     <row r="1762">
       <c r="A1762" s="10"/>
-      <c r="B1762" s="18"/>
+      <c r="B1762" s="17"/>
       <c r="C1762" s="10"/>
       <c r="D1762" s="10"/>
       <c r="E1762" s="10"/>
     </row>
     <row r="1763">
       <c r="A1763" s="10"/>
-      <c r="B1763" s="18"/>
+      <c r="B1763" s="17"/>
       <c r="C1763" s="10"/>
       <c r="D1763" s="10"/>
       <c r="E1763" s="10"/>
     </row>
     <row r="1764">
       <c r="A1764" s="10"/>
-      <c r="B1764" s="18"/>
+      <c r="B1764" s="17"/>
       <c r="C1764" s="10"/>
       <c r="D1764" s="10"/>
       <c r="E1764" s="10"/>
     </row>
     <row r="1765">
       <c r="A1765" s="10"/>
-      <c r="B1765" s="18"/>
+      <c r="B1765" s="17"/>
       <c r="C1765" s="10"/>
       <c r="D1765" s="10"/>
       <c r="E1765" s="10"/>
     </row>
     <row r="1766">
       <c r="A1766" s="10"/>
-      <c r="B1766" s="18"/>
+      <c r="B1766" s="17"/>
       <c r="C1766" s="10"/>
       <c r="D1766" s="10"/>
       <c r="E1766" s="10"/>
     </row>
     <row r="1767">
       <c r="A1767" s="10"/>
-      <c r="B1767" s="18"/>
+      <c r="B1767" s="17"/>
       <c r="C1767" s="10"/>
       <c r="D1767" s="10"/>
       <c r="E1767" s="10"/>
     </row>
     <row r="1768">
       <c r="A1768" s="10"/>
-      <c r="B1768" s="18"/>
+      <c r="B1768" s="17"/>
       <c r="C1768" s="10"/>
       <c r="D1768" s="10"/>
       <c r="E1768" s="10"/>
     </row>
     <row r="1769">
       <c r="A1769" s="10"/>
-      <c r="B1769" s="18"/>
+      <c r="B1769" s="17"/>
       <c r="C1769" s="10"/>
       <c r="D1769" s="10"/>
       <c r="E1769" s="10"/>
     </row>
     <row r="1770">
       <c r="A1770" s="10"/>
-      <c r="B1770" s="18"/>
+      <c r="B1770" s="17"/>
       <c r="C1770" s="10"/>
       <c r="D1770" s="10"/>
       <c r="E1770" s="10"/>
     </row>
     <row r="1771">
       <c r="A1771" s="10"/>
-      <c r="B1771" s="18"/>
+      <c r="B1771" s="17"/>
       <c r="C1771" s="10"/>
       <c r="D1771" s="10"/>
       <c r="E1771" s="10"/>
     </row>
     <row r="1772">
       <c r="A1772" s="10"/>
-      <c r="B1772" s="18"/>
+      <c r="B1772" s="17"/>
       <c r="C1772" s="10"/>
       <c r="D1772" s="10"/>
       <c r="E1772" s="10"/>
     </row>
     <row r="1773">
       <c r="A1773" s="10"/>
-      <c r="B1773" s="18"/>
+      <c r="B1773" s="17"/>
       <c r="C1773" s="10"/>
       <c r="D1773" s="10"/>
       <c r="E1773" s="10"/>
     </row>
     <row r="1774">
       <c r="A1774" s="10"/>
-      <c r="B1774" s="18"/>
+      <c r="B1774" s="17"/>
       <c r="C1774" s="10"/>
       <c r="D1774" s="10"/>
       <c r="E1774" s="10"/>
     </row>
     <row r="1775">
       <c r="A1775" s="10"/>
-      <c r="B1775" s="18"/>
+      <c r="B1775" s="17"/>
       <c r="C1775" s="10"/>
       <c r="D1775" s="10"/>
       <c r="E1775" s="10"/>
     </row>
     <row r="1776">
       <c r="A1776" s="10"/>
-      <c r="B1776" s="18"/>
+      <c r="B1776" s="17"/>
       <c r="C1776" s="10"/>
       <c r="D1776" s="10"/>
       <c r="E1776" s="10"/>
     </row>
     <row r="1777">
       <c r="A1777" s="10"/>
-      <c r="B1777" s="18"/>
+      <c r="B1777" s="17"/>
       <c r="C1777" s="10"/>
       <c r="D1777" s="10"/>
       <c r="E1777" s="10"/>
     </row>
     <row r="1778">
       <c r="A1778" s="10"/>
-      <c r="B1778" s="18"/>
+      <c r="B1778" s="17"/>
       <c r="C1778" s="10"/>
       <c r="D1778" s="10"/>
       <c r="E1778" s="10"/>
     </row>
     <row r="1779">
       <c r="A1779" s="10"/>
-      <c r="B1779" s="18"/>
+      <c r="B1779" s="17"/>
       <c r="C1779" s="10"/>
       <c r="D1779" s="10"/>
       <c r="E1779" s="10"/>
     </row>
     <row r="1780">
       <c r="A1780" s="10"/>
-      <c r="B1780" s="18"/>
+      <c r="B1780" s="17"/>
       <c r="C1780" s="10"/>
       <c r="D1780" s="10"/>
       <c r="E1780" s="10"/>
     </row>
     <row r="1781">
       <c r="A1781" s="10"/>
-      <c r="B1781" s="18"/>
+      <c r="B1781" s="17"/>
       <c r="C1781" s="10"/>
       <c r="D1781" s="10"/>
       <c r="E1781" s="10"/>
     </row>
     <row r="1782">
       <c r="A1782" s="10"/>
-      <c r="B1782" s="18"/>
+      <c r="B1782" s="17"/>
       <c r="C1782" s="10"/>
       <c r="D1782" s="10"/>
       <c r="E1782" s="10"/>
     </row>
     <row r="1783">
       <c r="A1783" s="10"/>
-      <c r="B1783" s="18"/>
+      <c r="B1783" s="17"/>
       <c r="C1783" s="10"/>
       <c r="D1783" s="10"/>
       <c r="E1783" s="10"/>
     </row>
     <row r="1784">
       <c r="A1784" s="10"/>
-      <c r="B1784" s="18"/>
+      <c r="B1784" s="17"/>
       <c r="C1784" s="10"/>
       <c r="D1784" s="10"/>
       <c r="E1784" s="10"/>
     </row>
     <row r="1785">
       <c r="A1785" s="10"/>
-      <c r="B1785" s="18"/>
+      <c r="B1785" s="17"/>
       <c r="C1785" s="10"/>
       <c r="D1785" s="10"/>
       <c r="E1785" s="10"/>
     </row>
     <row r="1786">
       <c r="A1786" s="10"/>
-      <c r="B1786" s="18"/>
+      <c r="B1786" s="17"/>
       <c r="C1786" s="10"/>
       <c r="D1786" s="10"/>
       <c r="E1786" s="10"/>
     </row>
     <row r="1787">
       <c r="A1787" s="10"/>
-      <c r="B1787" s="18"/>
+      <c r="B1787" s="17"/>
       <c r="C1787" s="10"/>
       <c r="D1787" s="10"/>
       <c r="E1787" s="10"/>
     </row>
     <row r="1788">
       <c r="A1788" s="10"/>
-      <c r="B1788" s="18"/>
+      <c r="B1788" s="17"/>
       <c r="C1788" s="10"/>
       <c r="D1788" s="10"/>
       <c r="E1788" s="10"/>
     </row>
     <row r="1789">
       <c r="A1789" s="10"/>
-      <c r="B1789" s="18"/>
+      <c r="B1789" s="17"/>
       <c r="C1789" s="10"/>
       <c r="D1789" s="10"/>
       <c r="E1789" s="10"/>
     </row>
     <row r="1790">
       <c r="A1790" s="10"/>
-      <c r="B1790" s="18"/>
+      <c r="B1790" s="17"/>
       <c r="C1790" s="10"/>
       <c r="D1790" s="10"/>
       <c r="E1790" s="10"/>
     </row>
     <row r="1791">
       <c r="A1791" s="10"/>
-      <c r="B1791" s="18"/>
+      <c r="B1791" s="17"/>
       <c r="C1791" s="10"/>
       <c r="D1791" s="10"/>
       <c r="E1791" s="10"/>
     </row>
     <row r="1792">
       <c r="A1792" s="10"/>
-      <c r="B1792" s="18"/>
+      <c r="B1792" s="17"/>
       <c r="C1792" s="10"/>
       <c r="D1792" s="10"/>
       <c r="E1792" s="10"/>
     </row>
     <row r="1793">
       <c r="A1793" s="10"/>
-      <c r="B1793" s="18"/>
+      <c r="B1793" s="17"/>
       <c r="C1793" s="10"/>
       <c r="D1793" s="10"/>
       <c r="E1793" s="10"/>
     </row>
     <row r="1794">
       <c r="A1794" s="10"/>
-      <c r="B1794" s="18"/>
+      <c r="B1794" s="17"/>
       <c r="C1794" s="10"/>
       <c r="D1794" s="10"/>
       <c r="E1794" s="10"/>
     </row>
     <row r="1795">
       <c r="A1795" s="10"/>
-      <c r="B1795" s="18"/>
+      <c r="B1795" s="17"/>
       <c r="C1795" s="10"/>
       <c r="D1795" s="10"/>
       <c r="E1795" s="10"/>
     </row>
     <row r="1796">
       <c r="A1796" s="10"/>
-      <c r="B1796" s="18"/>
+      <c r="B1796" s="17"/>
       <c r="C1796" s="10"/>
       <c r="D1796" s="10"/>
       <c r="E1796" s="10"/>
     </row>
     <row r="1797">
       <c r="A1797" s="10"/>
-      <c r="B1797" s="18"/>
+      <c r="B1797" s="17"/>
       <c r="C1797" s="10"/>
       <c r="D1797" s="10"/>
       <c r="E1797" s="10"/>
     </row>
     <row r="1798">
       <c r="A1798" s="10"/>
-      <c r="B1798" s="18"/>
+      <c r="B1798" s="17"/>
       <c r="C1798" s="10"/>
       <c r="D1798" s="10"/>
       <c r="E1798" s="10"/>
     </row>
     <row r="1799">
       <c r="A1799" s="10"/>
-      <c r="B1799" s="18"/>
+      <c r="B1799" s="17"/>
       <c r="C1799" s="10"/>
       <c r="D1799" s="10"/>
       <c r="E1799" s="10"/>
     </row>
     <row r="1800">
       <c r="A1800" s="10"/>
-      <c r="B1800" s="18"/>
+      <c r="B1800" s="17"/>
       <c r="C1800" s="10"/>
       <c r="D1800" s="10"/>
       <c r="E1800" s="10"/>
     </row>
     <row r="1801">
       <c r="A1801" s="10"/>
-      <c r="B1801" s="18"/>
+      <c r="B1801" s="17"/>
       <c r="C1801" s="10"/>
       <c r="D1801" s="10"/>
       <c r="E1801" s="10"/>
     </row>
     <row r="1802">
       <c r="A1802" s="10"/>
-      <c r="B1802" s="18"/>
+      <c r="B1802" s="17"/>
       <c r="C1802" s="10"/>
       <c r="D1802" s="10"/>
       <c r="E1802" s="10"/>
     </row>
     <row r="1803">
       <c r="A1803" s="10"/>
-      <c r="B1803" s="18"/>
+      <c r="B1803" s="17"/>
       <c r="C1803" s="10"/>
       <c r="D1803" s="10"/>
       <c r="E1803" s="10"/>
     </row>
     <row r="1804">
       <c r="A1804" s="10"/>
-      <c r="B1804" s="18"/>
+      <c r="B1804" s="17"/>
       <c r="C1804" s="10"/>
       <c r="D1804" s="10"/>
       <c r="E1804" s="10"/>
     </row>
     <row r="1805">
       <c r="A1805" s="10"/>
-      <c r="B1805" s="18"/>
+      <c r="B1805" s="17"/>
       <c r="C1805" s="10"/>
       <c r="D1805" s="10"/>
       <c r="E1805" s="10"/>
     </row>
     <row r="1806">
       <c r="A1806" s="10"/>
-      <c r="B1806" s="18"/>
+      <c r="B1806" s="17"/>
       <c r="C1806" s="10"/>
       <c r="D1806" s="10"/>
       <c r="E1806" s="10"/>
     </row>
     <row r="1807">
       <c r="A1807" s="10"/>
-      <c r="B1807" s="18"/>
+      <c r="B1807" s="17"/>
       <c r="C1807" s="10"/>
       <c r="D1807" s="10"/>
       <c r="E1807" s="10"/>
     </row>
     <row r="1808">
       <c r="A1808" s="10"/>
-      <c r="B1808" s="18"/>
+      <c r="B1808" s="17"/>
       <c r="C1808" s="10"/>
       <c r="D1808" s="10"/>
       <c r="E1808" s="10"/>
     </row>
     <row r="1809">
       <c r="A1809" s="10"/>
-      <c r="B1809" s="18"/>
+      <c r="B1809" s="17"/>
       <c r="C1809" s="10"/>
       <c r="D1809" s="10"/>
       <c r="E1809" s="10"/>
     </row>
     <row r="1810">
       <c r="A1810" s="10"/>
-      <c r="B1810" s="18"/>
+      <c r="B1810" s="17"/>
       <c r="C1810" s="10"/>
       <c r="D1810" s="10"/>
       <c r="E1810" s="10"/>
     </row>
     <row r="1811">
       <c r="A1811" s="10"/>
-      <c r="B1811" s="18"/>
+      <c r="B1811" s="17"/>
       <c r="C1811" s="10"/>
       <c r="D1811" s="10"/>
       <c r="E1811" s="10"/>
     </row>
     <row r="1812">
       <c r="A1812" s="10"/>
-      <c r="B1812" s="18"/>
+      <c r="B1812" s="17"/>
       <c r="C1812" s="10"/>
       <c r="D1812" s="10"/>
       <c r="E1812" s="10"/>
     </row>
     <row r="1813">
       <c r="A1813" s="10"/>
-      <c r="B1813" s="18"/>
+      <c r="B1813" s="17"/>
       <c r="C1813" s="10"/>
       <c r="D1813" s="10"/>
       <c r="E1813" s="10"/>
     </row>
     <row r="1814">
       <c r="A1814" s="10"/>
-      <c r="B1814" s="18"/>
+      <c r="B1814" s="17"/>
       <c r="C1814" s="10"/>
       <c r="D1814" s="10"/>
       <c r="E1814" s="10"/>
     </row>
     <row r="1815">
       <c r="A1815" s="10"/>
-      <c r="B1815" s="18"/>
+      <c r="B1815" s="17"/>
       <c r="C1815" s="10"/>
       <c r="D1815" s="10"/>
       <c r="E1815" s="10"/>
     </row>
     <row r="1816">
       <c r="A1816" s="10"/>
-      <c r="B1816" s="18"/>
+      <c r="B1816" s="17"/>
       <c r="C1816" s="10"/>
       <c r="D1816" s="10"/>
       <c r="E1816" s="10"/>
     </row>
     <row r="1817">
       <c r="A1817" s="10"/>
-      <c r="B1817" s="18"/>
+      <c r="B1817" s="17"/>
       <c r="C1817" s="10"/>
       <c r="D1817" s="10"/>
       <c r="E1817" s="10"/>
     </row>
     <row r="1818">
       <c r="A1818" s="10"/>
-      <c r="B1818" s="18"/>
+      <c r="B1818" s="17"/>
       <c r="C1818" s="10"/>
       <c r="D1818" s="10"/>
       <c r="E1818" s="10"/>
     </row>
     <row r="1819">
       <c r="A1819" s="10"/>
-      <c r="B1819" s="18"/>
+      <c r="B1819" s="17"/>
       <c r="C1819" s="10"/>
       <c r="D1819" s="10"/>
       <c r="E1819" s="10"/>
     </row>
     <row r="1820">
       <c r="A1820" s="10"/>
-      <c r="B1820" s="18"/>
+      <c r="B1820" s="17"/>
       <c r="C1820" s="10"/>
       <c r="D1820" s="10"/>
       <c r="E1820" s="10"/>
     </row>
     <row r="1821">
       <c r="A1821" s="10"/>
-      <c r="B1821" s="18"/>
+      <c r="B1821" s="17"/>
       <c r="C1821" s="10"/>
       <c r="D1821" s="10"/>
       <c r="E1821" s="10"/>
     </row>
     <row r="1822">
       <c r="A1822" s="10"/>
-      <c r="B1822" s="18"/>
+      <c r="B1822" s="17"/>
       <c r="C1822" s="10"/>
       <c r="D1822" s="10"/>
       <c r="E1822" s="10"/>
     </row>
     <row r="1823">
       <c r="A1823" s="10"/>
-      <c r="B1823" s="18"/>
+      <c r="B1823" s="17"/>
       <c r="C1823" s="10"/>
       <c r="D1823" s="10"/>
       <c r="E1823" s="10"/>
     </row>
     <row r="1824">
       <c r="A1824" s="10"/>
-      <c r="B1824" s="18"/>
+      <c r="B1824" s="17"/>
       <c r="C1824" s="10"/>
       <c r="D1824" s="10"/>
       <c r="E1824" s="10"/>
     </row>
     <row r="1825">
       <c r="A1825" s="10"/>
-      <c r="B1825" s="18"/>
+      <c r="B1825" s="17"/>
       <c r="C1825" s="10"/>
       <c r="D1825" s="10"/>
       <c r="E1825" s="10"/>
     </row>
     <row r="1826">
       <c r="A1826" s="10"/>
-      <c r="B1826" s="18"/>
+      <c r="B1826" s="17"/>
       <c r="C1826" s="10"/>
       <c r="D1826" s="10"/>
       <c r="E1826" s="10"/>
     </row>
     <row r="1827">
       <c r="A1827" s="10"/>
-      <c r="B1827" s="18"/>
+      <c r="B1827" s="17"/>
       <c r="C1827" s="10"/>
       <c r="D1827" s="10"/>
       <c r="E1827" s="10"/>
     </row>
     <row r="1828">
       <c r="A1828" s="10"/>
-      <c r="B1828" s="18"/>
+      <c r="B1828" s="17"/>
       <c r="C1828" s="10"/>
       <c r="D1828" s="10"/>
       <c r="E1828" s="10"/>
     </row>
     <row r="1829">
       <c r="A1829" s="10"/>
-      <c r="B1829" s="18"/>
+      <c r="B1829" s="17"/>
       <c r="C1829" s="10"/>
       <c r="D1829" s="10"/>
       <c r="E1829" s="10"/>
     </row>
     <row r="1830">
       <c r="A1830" s="10"/>
-      <c r="B1830" s="18"/>
+      <c r="B1830" s="17"/>
       <c r="C1830" s="10"/>
       <c r="D1830" s="10"/>
       <c r="E1830" s="10"/>
     </row>
     <row r="1831">
       <c r="A1831" s="10"/>
-      <c r="B1831" s="18"/>
+      <c r="B1831" s="17"/>
       <c r="C1831" s="10"/>
       <c r="D1831" s="10"/>
       <c r="E1831" s="10"/>
     </row>
     <row r="1832">
       <c r="A1832" s="10"/>
-      <c r="B1832" s="18"/>
+      <c r="B1832" s="17"/>
       <c r="C1832" s="10"/>
       <c r="D1832" s="10"/>
       <c r="E1832" s="10"/>
     </row>
     <row r="1833">
       <c r="A1833" s="10"/>
-      <c r="B1833" s="18"/>
+      <c r="B1833" s="17"/>
       <c r="C1833" s="10"/>
       <c r="D1833" s="10"/>
       <c r="E1833" s="10"/>
     </row>
     <row r="1834">
       <c r="A1834" s="10"/>
-      <c r="B1834" s="18"/>
+      <c r="B1834" s="17"/>
       <c r="C1834" s="10"/>
       <c r="D1834" s="10"/>
       <c r="E1834" s="10"/>
     </row>
     <row r="1835">
       <c r="A1835" s="10"/>
-      <c r="B1835" s="18"/>
+      <c r="B1835" s="17"/>
       <c r="C1835" s="10"/>
       <c r="D1835" s="10"/>
       <c r="E1835" s="10"/>
     </row>
     <row r="1836">
       <c r="A1836" s="10"/>
-      <c r="B1836" s="18"/>
+      <c r="B1836" s="17"/>
       <c r="C1836" s="10"/>
       <c r="D1836" s="10"/>
       <c r="E1836" s="10"/>
     </row>
     <row r="1837">
       <c r="A1837" s="10"/>
-      <c r="B1837" s="18"/>
+      <c r="B1837" s="17"/>
       <c r="C1837" s="10"/>
       <c r="D1837" s="10"/>
       <c r="E1837" s="10"/>
     </row>
     <row r="1838">
       <c r="A1838" s="10"/>
-      <c r="B1838" s="18"/>
+      <c r="B1838" s="17"/>
       <c r="C1838" s="10"/>
       <c r="D1838" s="10"/>
       <c r="E1838" s="10"/>
     </row>
     <row r="1839">
       <c r="A1839" s="10"/>
-      <c r="B1839" s="18"/>
+      <c r="B1839" s="17"/>
       <c r="C1839" s="10"/>
       <c r="D1839" s="10"/>
       <c r="E1839" s="10"/>
     </row>
     <row r="1840">
       <c r="A1840" s="10"/>
-      <c r="B1840" s="18"/>
+      <c r="B1840" s="17"/>
       <c r="C1840" s="10"/>
       <c r="D1840" s="10"/>
       <c r="E1840" s="10"/>
     </row>
     <row r="1841">
       <c r="A1841" s="10"/>
-      <c r="B1841" s="18"/>
+      <c r="B1841" s="17"/>
       <c r="C1841" s="10"/>
       <c r="D1841" s="10"/>
       <c r="E1841" s="10"/>
     </row>
     <row r="1842">
       <c r="A1842" s="10"/>
-      <c r="B1842" s="18"/>
+      <c r="B1842" s="17"/>
       <c r="C1842" s="10"/>
       <c r="D1842" s="10"/>
       <c r="E1842" s="10"/>
     </row>
     <row r="1843">
       <c r="A1843" s="10"/>
-      <c r="B1843" s="18"/>
+      <c r="B1843" s="17"/>
       <c r="C1843" s="10"/>
       <c r="D1843" s="10"/>
       <c r="E1843" s="10"/>
     </row>
     <row r="1844">
       <c r="A1844" s="10"/>
-      <c r="B1844" s="18"/>
+      <c r="B1844" s="17"/>
       <c r="C1844" s="10"/>
       <c r="D1844" s="10"/>
       <c r="E1844" s="10"/>
     </row>
     <row r="1845">
       <c r="A1845" s="10"/>
-      <c r="B1845" s="18"/>
+      <c r="B1845" s="17"/>
       <c r="C1845" s="10"/>
       <c r="D1845" s="10"/>
       <c r="E1845" s="10"/>
     </row>
     <row r="1846">
       <c r="A1846" s="10"/>
-      <c r="B1846" s="18"/>
+      <c r="B1846" s="17"/>
       <c r="C1846" s="10"/>
       <c r="D1846" s="10"/>
       <c r="E1846" s="10"/>
     </row>
     <row r="1847">
       <c r="A1847" s="10"/>
-      <c r="B1847" s="18"/>
+      <c r="B1847" s="17"/>
       <c r="C1847" s="10"/>
       <c r="D1847" s="10"/>
       <c r="E1847" s="10"/>
     </row>
     <row r="1848">
       <c r="A1848" s="10"/>
-      <c r="B1848" s="18"/>
+      <c r="B1848" s="17"/>
       <c r="C1848" s="10"/>
       <c r="D1848" s="10"/>
       <c r="E1848" s="10"/>
     </row>
     <row r="1849">
       <c r="A1849" s="10"/>
-      <c r="B1849" s="18"/>
+      <c r="B1849" s="17"/>
       <c r="C1849" s="10"/>
       <c r="D1849" s="10"/>
       <c r="E1849" s="10"/>
     </row>
     <row r="1850">
       <c r="A1850" s="10"/>
-      <c r="B1850" s="18"/>
+      <c r="B1850" s="17"/>
       <c r="C1850" s="10"/>
       <c r="D1850" s="10"/>
       <c r="E1850" s="10"/>
     </row>
     <row r="1851">
       <c r="A1851" s="10"/>
-      <c r="B1851" s="18"/>
+      <c r="B1851" s="17"/>
       <c r="C1851" s="10"/>
       <c r="D1851" s="10"/>
       <c r="E1851" s="10"/>
     </row>
     <row r="1852">
       <c r="A1852" s="10"/>
-      <c r="B1852" s="18"/>
+      <c r="B1852" s="17"/>
       <c r="C1852" s="10"/>
       <c r="D1852" s="10"/>
       <c r="E1852" s="10"/>
     </row>
     <row r="1853">
       <c r="A1853" s="10"/>
-      <c r="B1853" s="18"/>
+      <c r="B1853" s="17"/>
       <c r="C1853" s="10"/>
       <c r="D1853" s="10"/>
       <c r="E1853" s="10"/>
     </row>
     <row r="1854">
       <c r="A1854" s="10"/>
-      <c r="B1854" s="18"/>
+      <c r="B1854" s="17"/>
       <c r="C1854" s="10"/>
       <c r="D1854" s="10"/>
       <c r="E1854" s="10"/>
     </row>
     <row r="1855">
       <c r="A1855" s="10"/>
-      <c r="B1855" s="18"/>
+      <c r="B1855" s="17"/>
       <c r="C1855" s="10"/>
       <c r="D1855" s="10"/>
       <c r="E1855" s="10"/>
     </row>
     <row r="1856">
       <c r="A1856" s="10"/>
-      <c r="B1856" s="18"/>
+      <c r="B1856" s="17"/>
       <c r="C1856" s="10"/>
       <c r="D1856" s="10"/>
       <c r="E1856" s="10"/>
     </row>
     <row r="1857">
       <c r="A1857" s="10"/>
-      <c r="B1857" s="18"/>
+      <c r="B1857" s="17"/>
       <c r="C1857" s="10"/>
       <c r="D1857" s="10"/>
       <c r="E1857" s="10"/>
     </row>
     <row r="1858">
       <c r="A1858" s="10"/>
-      <c r="B1858" s="18"/>
+      <c r="B1858" s="17"/>
       <c r="C1858" s="10"/>
       <c r="D1858" s="10"/>
       <c r="E1858" s="10"/>
     </row>
     <row r="1859">
       <c r="A1859" s="10"/>
-      <c r="B1859" s="18"/>
+      <c r="B1859" s="17"/>
       <c r="C1859" s="10"/>
       <c r="D1859" s="10"/>
       <c r="E1859" s="10"/>
     </row>
     <row r="1860">
       <c r="A1860" s="10"/>
-      <c r="B1860" s="18"/>
+      <c r="B1860" s="17"/>
       <c r="C1860" s="10"/>
       <c r="D1860" s="10"/>
       <c r="E1860" s="10"/>
     </row>
     <row r="1861">
       <c r="A1861" s="10"/>
-      <c r="B1861" s="18"/>
+      <c r="B1861" s="17"/>
       <c r="C1861" s="10"/>
       <c r="D1861" s="10"/>
       <c r="E1861" s="10"/>
     </row>
     <row r="1862">
       <c r="A1862" s="10"/>
-      <c r="B1862" s="18"/>
+      <c r="B1862" s="17"/>
       <c r="C1862" s="10"/>
       <c r="D1862" s="10"/>
       <c r="E1862" s="10"/>
     </row>
     <row r="1863">
       <c r="A1863" s="10"/>
-      <c r="B1863" s="18"/>
+      <c r="B1863" s="17"/>
       <c r="C1863" s="10"/>
       <c r="D1863" s="10"/>
       <c r="E1863" s="10"/>
     </row>
     <row r="1864">
       <c r="A1864" s="10"/>
-      <c r="B1864" s="18"/>
+      <c r="B1864" s="17"/>
       <c r="C1864" s="10"/>
       <c r="D1864" s="10"/>
       <c r="E1864" s="10"/>
     </row>
     <row r="1865">
       <c r="A1865" s="10"/>
-      <c r="B1865" s="18"/>
+      <c r="B1865" s="17"/>
       <c r="C1865" s="10"/>
       <c r="D1865" s="10"/>
       <c r="E1865" s="10"/>
     </row>
     <row r="1866">
       <c r="A1866" s="10"/>
-      <c r="B1866" s="18"/>
+      <c r="B1866" s="17"/>
       <c r="C1866" s="10"/>
       <c r="D1866" s="10"/>
       <c r="E1866" s="10"/>
     </row>
     <row r="1867">
       <c r="A1867" s="10"/>
-      <c r="B1867" s="18"/>
+      <c r="B1867" s="17"/>
       <c r="C1867" s="10"/>
       <c r="D1867" s="10"/>
       <c r="E1867" s="10"/>
     </row>
     <row r="1868">
       <c r="A1868" s="10"/>
-      <c r="B1868" s="18"/>
+      <c r="B1868" s="17"/>
       <c r="C1868" s="10"/>
       <c r="D1868" s="10"/>
       <c r="E1868" s="10"/>
     </row>
     <row r="1869">
       <c r="A1869" s="10"/>
-      <c r="B1869" s="18"/>
+      <c r="B1869" s="17"/>
       <c r="C1869" s="10"/>
       <c r="D1869" s="10"/>
       <c r="E1869" s="10"/>
     </row>
     <row r="1870">
       <c r="A1870" s="10"/>
-      <c r="B1870" s="18"/>
+      <c r="B1870" s="17"/>
       <c r="C1870" s="10"/>
       <c r="D1870" s="10"/>
       <c r="E1870" s="10"/>
     </row>
     <row r="1871">
       <c r="A1871" s="10"/>
-      <c r="B1871" s="18"/>
+      <c r="B1871" s="17"/>
       <c r="C1871" s="10"/>
       <c r="D1871" s="10"/>
       <c r="E1871" s="10"/>
     </row>
     <row r="1872">
       <c r="A1872" s="10"/>
-      <c r="B1872" s="18"/>
+      <c r="B1872" s="17"/>
       <c r="C1872" s="10"/>
       <c r="D1872" s="10"/>
       <c r="E1872" s="10"/>
     </row>
     <row r="1873">
       <c r="A1873" s="10"/>
-      <c r="B1873" s="18"/>
+      <c r="B1873" s="17"/>
       <c r="C1873" s="10"/>
       <c r="D1873" s="10"/>
       <c r="E1873" s="10"/>
     </row>
     <row r="1874">
       <c r="A1874" s="10"/>
-      <c r="B1874" s="18"/>
+      <c r="B1874" s="17"/>
       <c r="C1874" s="10"/>
       <c r="D1874" s="10"/>
       <c r="E1874" s="10"/>
     </row>
     <row r="1875">
       <c r="A1875" s="10"/>
-      <c r="B1875" s="18"/>
+      <c r="B1875" s="17"/>
       <c r="C1875" s="10"/>
       <c r="D1875" s="10"/>
       <c r="E1875" s="10"/>
     </row>
     <row r="1876">
       <c r="A1876" s="10"/>
-      <c r="B1876" s="18"/>
+      <c r="B1876" s="17"/>
       <c r="C1876" s="10"/>
       <c r="D1876" s="10"/>
       <c r="E1876" s="10"/>
     </row>
     <row r="1877">
       <c r="A1877" s="10"/>
-      <c r="B1877" s="18"/>
+      <c r="B1877" s="17"/>
       <c r="C1877" s="10"/>
       <c r="D1877" s="10"/>
       <c r="E1877" s="10"/>
     </row>
     <row r="1878">
       <c r="A1878" s="10"/>
-      <c r="B1878" s="18"/>
+      <c r="B1878" s="17"/>
       <c r="C1878" s="10"/>
       <c r="D1878" s="10"/>
       <c r="E1878" s="10"/>
     </row>
     <row r="1879">
       <c r="A1879" s="10"/>
-      <c r="B1879" s="18"/>
+      <c r="B1879" s="17"/>
       <c r="C1879" s="10"/>
       <c r="D1879" s="10"/>
       <c r="E1879" s="10"/>
     </row>
     <row r="1880">
       <c r="A1880" s="10"/>
-      <c r="B1880" s="18"/>
+      <c r="B1880" s="17"/>
       <c r="C1880" s="10"/>
       <c r="D1880" s="10"/>
       <c r="E1880" s="10"/>
     </row>
     <row r="1881">
       <c r="A1881" s="10"/>
-      <c r="B1881" s="18"/>
+      <c r="B1881" s="17"/>
       <c r="C1881" s="10"/>
       <c r="D1881" s="10"/>
       <c r="E1881" s="10"/>
     </row>
     <row r="1882">
       <c r="A1882" s="10"/>
-      <c r="B1882" s="18"/>
+      <c r="B1882" s="17"/>
       <c r="C1882" s="10"/>
       <c r="D1882" s="10"/>
       <c r="E1882" s="10"/>
     </row>
     <row r="1883">
       <c r="A1883" s="10"/>
-      <c r="B1883" s="18"/>
+      <c r="B1883" s="17"/>
       <c r="C1883" s="10"/>
       <c r="D1883" s="10"/>
       <c r="E1883" s="10"/>
     </row>
     <row r="1884">
       <c r="A1884" s="10"/>
-      <c r="B1884" s="18"/>
+      <c r="B1884" s="17"/>
       <c r="C1884" s="10"/>
       <c r="D1884" s="10"/>
       <c r="E1884" s="10"/>
     </row>
     <row r="1885">
       <c r="A1885" s="10"/>
-      <c r="B1885" s="18"/>
+      <c r="B1885" s="17"/>
       <c r="C1885" s="10"/>
       <c r="D1885" s="10"/>
       <c r="E1885" s="10"/>
     </row>
     <row r="1886">
       <c r="A1886" s="10"/>
-      <c r="B1886" s="18"/>
+      <c r="B1886" s="17"/>
       <c r="C1886" s="10"/>
       <c r="D1886" s="10"/>
       <c r="E1886" s="10"/>
     </row>
     <row r="1887">
       <c r="A1887" s="10"/>
-      <c r="B1887" s="18"/>
+      <c r="B1887" s="17"/>
       <c r="C1887" s="10"/>
       <c r="D1887" s="10"/>
       <c r="E1887" s="10"/>
     </row>
     <row r="1888">
       <c r="A1888" s="10"/>
-      <c r="B1888" s="18"/>
+      <c r="B1888" s="17"/>
       <c r="C1888" s="10"/>
       <c r="D1888" s="10"/>
       <c r="E1888" s="10"/>
     </row>
     <row r="1889">
       <c r="A1889" s="10"/>
-      <c r="B1889" s="18"/>
+      <c r="B1889" s="17"/>
       <c r="C1889" s="10"/>
       <c r="D1889" s="10"/>
       <c r="E1889" s="10"/>
     </row>
     <row r="1890">
       <c r="A1890" s="10"/>
-      <c r="B1890" s="18"/>
+      <c r="B1890" s="17"/>
       <c r="C1890" s="10"/>
       <c r="D1890" s="10"/>
       <c r="E1890" s="10"/>
     </row>
     <row r="1891">
       <c r="A1891" s="10"/>
-      <c r="B1891" s="18"/>
+      <c r="B1891" s="17"/>
       <c r="C1891" s="10"/>
       <c r="D1891" s="10"/>
       <c r="E1891" s="10"/>
     </row>
     <row r="1892">
       <c r="A1892" s="10"/>
-      <c r="B1892" s="18"/>
+      <c r="B1892" s="17"/>
       <c r="C1892" s="10"/>
       <c r="D1892" s="10"/>
       <c r="E1892" s="10"/>
     </row>
     <row r="1893">
       <c r="A1893" s="10"/>
-      <c r="B1893" s="18"/>
+      <c r="B1893" s="17"/>
       <c r="C1893" s="10"/>
       <c r="D1893" s="10"/>
       <c r="E1893" s="10"/>
     </row>
     <row r="1894">
       <c r="A1894" s="10"/>
-      <c r="B1894" s="18"/>
+      <c r="B1894" s="17"/>
       <c r="C1894" s="10"/>
       <c r="D1894" s="10"/>
       <c r="E1894" s="10"/>
     </row>
     <row r="1895">
       <c r="A1895" s="10"/>
-      <c r="B1895" s="18"/>
+      <c r="B1895" s="17"/>
       <c r="C1895" s="10"/>
       <c r="D1895" s="10"/>
       <c r="E1895" s="10"/>
     </row>
     <row r="1896">
       <c r="A1896" s="10"/>
-      <c r="B1896" s="18"/>
+      <c r="B1896" s="17"/>
       <c r="C1896" s="10"/>
       <c r="D1896" s="10"/>
       <c r="E1896" s="10"/>
     </row>
     <row r="1897">
       <c r="A1897" s="10"/>
-      <c r="B1897" s="18"/>
+      <c r="B1897" s="17"/>
       <c r="C1897" s="10"/>
       <c r="D1897" s="10"/>
       <c r="E1897" s="10"/>
     </row>
     <row r="1898">
       <c r="A1898" s="10"/>
-      <c r="B1898" s="18"/>
+      <c r="B1898" s="17"/>
       <c r="C1898" s="10"/>
       <c r="D1898" s="10"/>
       <c r="E1898" s="10"/>
     </row>
     <row r="1899">
       <c r="A1899" s="10"/>
-      <c r="B1899" s="18"/>
+      <c r="B1899" s="17"/>
       <c r="C1899" s="10"/>
       <c r="D1899" s="10"/>
       <c r="E1899" s="10"/>
     </row>
     <row r="1900">
       <c r="A1900" s="10"/>
-      <c r="B1900" s="18"/>
+      <c r="B1900" s="17"/>
       <c r="C1900" s="10"/>
       <c r="D1900" s="10"/>
       <c r="E1900" s="10"/>
     </row>
     <row r="1901">
       <c r="A1901" s="10"/>
-      <c r="B1901" s="18"/>
+      <c r="B1901" s="17"/>
       <c r="C1901" s="10"/>
       <c r="D1901" s="10"/>
       <c r="E1901" s="10"/>
     </row>
     <row r="1902">
       <c r="A1902" s="10"/>
-      <c r="B1902" s="18"/>
+      <c r="B1902" s="17"/>
       <c r="C1902" s="10"/>
       <c r="D1902" s="10"/>
       <c r="E1902" s="10"/>
     </row>
     <row r="1903">
       <c r="A1903" s="10"/>
-      <c r="B1903" s="18"/>
+      <c r="B1903" s="17"/>
       <c r="C1903" s="10"/>
       <c r="D1903" s="10"/>
       <c r="E1903" s="10"/>
     </row>
     <row r="1904">
       <c r="A1904" s="10"/>
-      <c r="B1904" s="18"/>
+      <c r="B1904" s="17"/>
       <c r="C1904" s="10"/>
       <c r="D1904" s="10"/>
       <c r="E1904" s="10"/>
     </row>
     <row r="1905">
       <c r="A1905" s="10"/>
-      <c r="B1905" s="18"/>
+      <c r="B1905" s="17"/>
       <c r="C1905" s="10"/>
       <c r="D1905" s="10"/>
       <c r="E1905" s="10"/>
     </row>
     <row r="1906">
       <c r="A1906" s="10"/>
-      <c r="B1906" s="18"/>
+      <c r="B1906" s="17"/>
       <c r="C1906" s="10"/>
       <c r="D1906" s="10"/>
       <c r="E1906" s="10"/>
     </row>
     <row r="1907">
       <c r="A1907" s="10"/>
-      <c r="B1907" s="18"/>
+      <c r="B1907" s="17"/>
       <c r="C1907" s="10"/>
       <c r="D1907" s="10"/>
       <c r="E1907" s="10"/>
     </row>
     <row r="1908">
       <c r="A1908" s="10"/>
-      <c r="B1908" s="18"/>
+      <c r="B1908" s="17"/>
       <c r="C1908" s="10"/>
       <c r="D1908" s="10"/>
       <c r="E1908" s="10"/>
     </row>
     <row r="1909">
       <c r="A1909" s="10"/>
-      <c r="B1909" s="18"/>
+      <c r="B1909" s="17"/>
       <c r="C1909" s="10"/>
       <c r="D1909" s="10"/>
       <c r="E1909" s="10"/>
     </row>
     <row r="1910">
       <c r="A1910" s="10"/>
-      <c r="B1910" s="18"/>
+      <c r="B1910" s="17"/>
       <c r="C1910" s="10"/>
       <c r="D1910" s="10"/>
       <c r="E1910" s="10"/>
     </row>
     <row r="1911">
       <c r="A1911" s="10"/>
-      <c r="B1911" s="18"/>
+      <c r="B1911" s="17"/>
       <c r="C1911" s="10"/>
       <c r="D1911" s="10"/>
       <c r="E1911" s="10"/>
     </row>
     <row r="1912">
       <c r="A1912" s="10"/>
-      <c r="B1912" s="18"/>
+      <c r="B1912" s="17"/>
       <c r="C1912" s="10"/>
       <c r="D1912" s="10"/>
       <c r="E1912" s="10"/>
     </row>
     <row r="1913">
       <c r="A1913" s="10"/>
-      <c r="B1913" s="18"/>
+      <c r="B1913" s="17"/>
       <c r="C1913" s="10"/>
       <c r="D1913" s="10"/>
       <c r="E1913" s="10"/>
     </row>
     <row r="1914">
       <c r="A1914" s="10"/>
-      <c r="B1914" s="18"/>
+      <c r="B1914" s="17"/>
       <c r="C1914" s="10"/>
       <c r="D1914" s="10"/>
       <c r="E1914" s="10"/>
     </row>
     <row r="1915">
       <c r="A1915" s="10"/>
-      <c r="B1915" s="18"/>
+      <c r="B1915" s="17"/>
       <c r="C1915" s="10"/>
       <c r="D1915" s="10"/>
       <c r="E1915" s="10"/>
     </row>
     <row r="1916">
       <c r="A1916" s="10"/>
-      <c r="B1916" s="18"/>
+      <c r="B1916" s="17"/>
       <c r="C1916" s="10"/>
       <c r="D1916" s="10"/>
       <c r="E1916" s="10"/>
     </row>
     <row r="1917">
       <c r="A1917" s="10"/>
-      <c r="B1917" s="18"/>
+      <c r="B1917" s="17"/>
       <c r="C1917" s="10"/>
       <c r="D1917" s="10"/>
       <c r="E1917" s="10"/>
     </row>
     <row r="1918">
       <c r="A1918" s="10"/>
-      <c r="B1918" s="18"/>
+      <c r="B1918" s="17"/>
       <c r="C1918" s="10"/>
       <c r="D1918" s="10"/>
       <c r="E1918" s="10"/>
     </row>
     <row r="1919">
       <c r="A1919" s="10"/>
-      <c r="B1919" s="18"/>
+      <c r="B1919" s="17"/>
       <c r="C1919" s="10"/>
       <c r="D1919" s="10"/>
       <c r="E1919" s="10"/>
     </row>
     <row r="1920">
       <c r="A1920" s="10"/>
-      <c r="B1920" s="18"/>
+      <c r="B1920" s="17"/>
       <c r="C1920" s="10"/>
       <c r="D1920" s="10"/>
       <c r="E1920" s="10"/>
     </row>
     <row r="1921">
       <c r="A1921" s="10"/>
-      <c r="B1921" s="18"/>
+      <c r="B1921" s="17"/>
       <c r="C1921" s="10"/>
       <c r="D1921" s="10"/>
       <c r="E1921" s="10"/>
     </row>
     <row r="1922">
       <c r="A1922" s="10"/>
-      <c r="B1922" s="18"/>
+      <c r="B1922" s="17"/>
       <c r="C1922" s="10"/>
       <c r="D1922" s="10"/>
       <c r="E1922" s="10"/>
     </row>
     <row r="1923">
       <c r="A1923" s="10"/>
-      <c r="B1923" s="18"/>
+      <c r="B1923" s="17"/>
       <c r="C1923" s="10"/>
       <c r="D1923" s="10"/>
       <c r="E1923" s="10"/>
     </row>
     <row r="1924">
       <c r="A1924" s="10"/>
-      <c r="B1924" s="18"/>
+      <c r="B1924" s="17"/>
       <c r="C1924" s="10"/>
       <c r="D1924" s="10"/>
       <c r="E1924" s="10"/>
     </row>
     <row r="1925">
       <c r="A1925" s="10"/>
-      <c r="B1925" s="18"/>
+      <c r="B1925" s="17"/>
       <c r="C1925" s="10"/>
       <c r="D1925" s="10"/>
       <c r="E1925" s="10"/>
     </row>
     <row r="1926">
       <c r="A1926" s="10"/>
-      <c r="B1926" s="18"/>
+      <c r="B1926" s="17"/>
       <c r="C1926" s="10"/>
       <c r="D1926" s="10"/>
       <c r="E1926" s="10"/>
     </row>
     <row r="1927">
       <c r="A1927" s="10"/>
-      <c r="B1927" s="18"/>
+      <c r="B1927" s="17"/>
       <c r="C1927" s="10"/>
       <c r="D1927" s="10"/>
       <c r="E1927" s="10"/>
     </row>
     <row r="1928">
       <c r="A1928" s="10"/>
-      <c r="B1928" s="18"/>
+      <c r="B1928" s="17"/>
       <c r="C1928" s="10"/>
       <c r="D1928" s="10"/>
       <c r="E1928" s="10"/>
     </row>
     <row r="1929">
       <c r="A1929" s="10"/>
-      <c r="B1929" s="18"/>
+      <c r="B1929" s="17"/>
       <c r="C1929" s="10"/>
       <c r="D1929" s="10"/>
       <c r="E1929" s="10"/>
     </row>
     <row r="1930">
       <c r="A1930" s="10"/>
-      <c r="B1930" s="18"/>
+      <c r="B1930" s="17"/>
       <c r="C1930" s="10"/>
       <c r="D1930" s="10"/>
       <c r="E1930" s="10"/>
     </row>
     <row r="1931">
       <c r="A1931" s="10"/>
-      <c r="B1931" s="18"/>
+      <c r="B1931" s="17"/>
       <c r="C1931" s="10"/>
       <c r="D1931" s="10"/>
       <c r="E1931" s="10"/>
     </row>
     <row r="1932">
       <c r="A1932" s="10"/>
-      <c r="B1932" s="18"/>
+      <c r="B1932" s="17"/>
       <c r="C1932" s="10"/>
       <c r="D1932" s="10"/>
       <c r="E1932" s="10"/>
     </row>
     <row r="1933">
       <c r="A1933" s="10"/>
-      <c r="B1933" s="18"/>
+      <c r="B1933" s="17"/>
       <c r="C1933" s="10"/>
       <c r="D1933" s="10"/>
       <c r="E1933" s="10"/>
     </row>
     <row r="1934">
       <c r="A1934" s="10"/>
-      <c r="B1934" s="18"/>
+      <c r="B1934" s="17"/>
       <c r="C1934" s="10"/>
       <c r="D1934" s="10"/>
       <c r="E1934" s="10"/>
     </row>
     <row r="1935">
       <c r="A1935" s="10"/>
-      <c r="B1935" s="18"/>
+      <c r="B1935" s="17"/>
       <c r="C1935" s="10"/>
       <c r="D1935" s="10"/>
       <c r="E1935" s="10"/>
     </row>
     <row r="1936">
       <c r="A1936" s="10"/>
-      <c r="B1936" s="18"/>
+      <c r="B1936" s="17"/>
       <c r="C1936" s="10"/>
       <c r="D1936" s="10"/>
       <c r="E1936" s="10"/>
     </row>
     <row r="1937">
       <c r="A1937" s="10"/>
-      <c r="B1937" s="18"/>
+      <c r="B1937" s="17"/>
       <c r="C1937" s="10"/>
       <c r="D1937" s="10"/>
       <c r="E1937" s="10"/>
     </row>
     <row r="1938">
       <c r="A1938" s="10"/>
-      <c r="B1938" s="18"/>
+      <c r="B1938" s="17"/>
       <c r="C1938" s="10"/>
       <c r="D1938" s="10"/>
       <c r="E1938" s="10"/>
     </row>
     <row r="1939">
       <c r="A1939" s="10"/>
-      <c r="B1939" s="18"/>
+      <c r="B1939" s="17"/>
       <c r="C1939" s="10"/>
       <c r="D1939" s="10"/>
       <c r="E1939" s="10"/>
     </row>
     <row r="1940">
       <c r="A1940" s="10"/>
-      <c r="B1940" s="18"/>
+      <c r="B1940" s="17"/>
       <c r="C1940" s="10"/>
       <c r="D1940" s="10"/>
       <c r="E1940" s="10"/>
     </row>
     <row r="1941">
       <c r="A1941" s="10"/>
-      <c r="B1941" s="18"/>
+      <c r="B1941" s="17"/>
       <c r="C1941" s="10"/>
       <c r="D1941" s="10"/>
       <c r="E1941" s="10"/>
     </row>
     <row r="1942">
       <c r="A1942" s="10"/>
-      <c r="B1942" s="18"/>
+      <c r="B1942" s="17"/>
       <c r="C1942" s="10"/>
       <c r="D1942" s="10"/>
       <c r="E1942" s="10"/>
     </row>
     <row r="1943">
       <c r="A1943" s="10"/>
-      <c r="B1943" s="18"/>
+      <c r="B1943" s="17"/>
       <c r="C1943" s="10"/>
       <c r="D1943" s="10"/>
       <c r="E1943" s="10"/>
     </row>
     <row r="1944">
       <c r="A1944" s="10"/>
-      <c r="B1944" s="18"/>
+      <c r="B1944" s="17"/>
       <c r="C1944" s="10"/>
       <c r="D1944" s="10"/>
       <c r="E1944" s="10"/>
     </row>
     <row r="1945">
       <c r="A1945" s="10"/>
-      <c r="B1945" s="18"/>
+      <c r="B1945" s="17"/>
       <c r="C1945" s="10"/>
       <c r="D1945" s="10"/>
       <c r="E1945" s="10"/>
     </row>
     <row r="1946">
       <c r="A1946" s="10"/>
-      <c r="B1946" s="18"/>
+      <c r="B1946" s="17"/>
       <c r="C1946" s="10"/>
       <c r="D1946" s="10"/>
       <c r="E1946" s="10"/>
     </row>
     <row r="1947">
       <c r="A1947" s="10"/>
-      <c r="B1947" s="18"/>
+      <c r="B1947" s="17"/>
       <c r="C1947" s="10"/>
       <c r="D1947" s="10"/>
       <c r="E1947" s="10"/>
     </row>
     <row r="1948">
       <c r="A1948" s="10"/>
-      <c r="B1948" s="18"/>
+      <c r="B1948" s="17"/>
       <c r="C1948" s="10"/>
       <c r="D1948" s="10"/>
       <c r="E1948" s="10"/>
     </row>
     <row r="1949">
       <c r="A1949" s="10"/>
-      <c r="B1949" s="18"/>
+      <c r="B1949" s="17"/>
       <c r="C1949" s="10"/>
       <c r="D1949" s="10"/>
       <c r="E1949" s="10"/>
     </row>
     <row r="1950">
       <c r="A1950" s="10"/>
-      <c r="B1950" s="18"/>
+      <c r="B1950" s="17"/>
       <c r="C1950" s="10"/>
       <c r="D1950" s="10"/>
       <c r="E1950" s="10"/>
     </row>
     <row r="1951">
       <c r="A1951" s="10"/>
-      <c r="B1951" s="18"/>
+      <c r="B1951" s="17"/>
       <c r="C1951" s="10"/>
       <c r="D1951" s="10"/>
       <c r="E1951" s="10"/>
     </row>
     <row r="1952">
       <c r="A1952" s="10"/>
-      <c r="B1952" s="18"/>
+      <c r="B1952" s="17"/>
       <c r="C1952" s="10"/>
       <c r="D1952" s="10"/>
       <c r="E1952" s="10"/>
     </row>
     <row r="1953">
       <c r="A1953" s="10"/>
-      <c r="B1953" s="18"/>
+      <c r="B1953" s="17"/>
       <c r="C1953" s="10"/>
       <c r="D1953" s="10"/>
       <c r="E1953" s="10"/>
     </row>
     <row r="1954">
       <c r="A1954" s="10"/>
-      <c r="B1954" s="18"/>
+      <c r="B1954" s="17"/>
       <c r="C1954" s="10"/>
       <c r="D1954" s="10"/>
       <c r="E1954" s="10"/>
     </row>
     <row r="1955">
       <c r="A1955" s="10"/>
-      <c r="B1955" s="18"/>
+      <c r="B1955" s="17"/>
       <c r="C1955" s="10"/>
       <c r="D1955" s="10"/>
       <c r="E1955" s="10"/>
     </row>
     <row r="1956">
       <c r="A1956" s="10"/>
-      <c r="B1956" s="18"/>
+      <c r="B1956" s="17"/>
       <c r="C1956" s="10"/>
       <c r="D1956" s="10"/>
       <c r="E1956" s="10"/>
     </row>
     <row r="1957">
       <c r="A1957" s="10"/>
-      <c r="B1957" s="18"/>
+      <c r="B1957" s="17"/>
       <c r="C1957" s="10"/>
       <c r="D1957" s="10"/>
       <c r="E1957" s="10"/>
     </row>
     <row r="1958">
       <c r="A1958" s="10"/>
-      <c r="B1958" s="18"/>
+      <c r="B1958" s="17"/>
       <c r="C1958" s="10"/>
       <c r="D1958" s="10"/>
       <c r="E1958" s="10"/>
     </row>
     <row r="1959">
       <c r="A1959" s="10"/>
-      <c r="B1959" s="18"/>
+      <c r="B1959" s="17"/>
       <c r="C1959" s="10"/>
       <c r="D1959" s="10"/>
       <c r="E1959" s="10"/>
     </row>
     <row r="1960">
       <c r="A1960" s="10"/>
-      <c r="B1960" s="18"/>
+      <c r="B1960" s="17"/>
       <c r="C1960" s="10"/>
       <c r="D1960" s="10"/>
       <c r="E1960" s="10"/>
     </row>
     <row r="1961">
       <c r="A1961" s="10"/>
-      <c r="B1961" s="18"/>
+      <c r="B1961" s="17"/>
       <c r="C1961" s="10"/>
       <c r="D1961" s="10"/>
       <c r="E1961" s="10"/>
     </row>
     <row r="1962">
       <c r="A1962" s="10"/>
-      <c r="B1962" s="18"/>
+      <c r="B1962" s="17"/>
       <c r="C1962" s="10"/>
       <c r="D1962" s="10"/>
       <c r="E1962" s="10"/>
     </row>
     <row r="1963">
       <c r="A1963" s="10"/>
-      <c r="B1963" s="18"/>
+      <c r="B1963" s="17"/>
       <c r="C1963" s="10"/>
       <c r="D1963" s="10"/>
       <c r="E1963" s="10"/>
     </row>
     <row r="1964">
       <c r="A1964" s="10"/>
-      <c r="B1964" s="18"/>
+      <c r="B1964" s="17"/>
       <c r="C1964" s="10"/>
       <c r="D1964" s="10"/>
       <c r="E1964" s="10"/>
     </row>
     <row r="1965">
       <c r="A1965" s="10"/>
-      <c r="B1965" s="18"/>
+      <c r="B1965" s="17"/>
       <c r="C1965" s="10"/>
       <c r="D1965" s="10"/>
       <c r="E1965" s="10"/>
     </row>
     <row r="1966">
       <c r="A1966" s="10"/>
-      <c r="B1966" s="18"/>
+      <c r="B1966" s="17"/>
       <c r="C1966" s="10"/>
       <c r="D1966" s="10"/>
       <c r="E1966" s="10"/>
     </row>
     <row r="1967">
       <c r="A1967" s="10"/>
-      <c r="B1967" s="18"/>
+      <c r="B1967" s="17"/>
       <c r="C1967" s="10"/>
       <c r="D1967" s="10"/>
       <c r="E1967" s="10"/>
     </row>
     <row r="1968">
       <c r="A1968" s="10"/>
-      <c r="B1968" s="18"/>
+      <c r="B1968" s="17"/>
       <c r="C1968" s="10"/>
       <c r="D1968" s="10"/>
       <c r="E1968" s="10"/>
     </row>
     <row r="1969">
       <c r="A1969" s="10"/>
-      <c r="B1969" s="18"/>
+      <c r="B1969" s="17"/>
       <c r="C1969" s="10"/>
       <c r="D1969" s="10"/>
       <c r="E1969" s="10"/>
     </row>
     <row r="1970">
       <c r="A1970" s="10"/>
-      <c r="B1970" s="18"/>
+      <c r="B1970" s="17"/>
       <c r="C1970" s="10"/>
       <c r="D1970" s="10"/>
       <c r="E1970" s="10"/>
     </row>
     <row r="1971">
       <c r="A1971" s="10"/>
-      <c r="B1971" s="18"/>
+      <c r="B1971" s="17"/>
       <c r="C1971" s="10"/>
       <c r="D1971" s="10"/>
       <c r="E1971" s="10"/>
     </row>
     <row r="1972">
       <c r="A1972" s="10"/>
-      <c r="B1972" s="18"/>
+      <c r="B1972" s="17"/>
       <c r="C1972" s="10"/>
       <c r="D1972" s="10"/>
       <c r="E1972" s="10"/>
     </row>
     <row r="1973">
       <c r="A1973" s="10"/>
-      <c r="B1973" s="18"/>
+      <c r="B1973" s="17"/>
       <c r="C1973" s="10"/>
       <c r="D1973" s="10"/>
       <c r="E1973" s="10"/>
     </row>
     <row r="1974">
       <c r="A1974" s="10"/>
-      <c r="B1974" s="18"/>
+      <c r="B1974" s="17"/>
       <c r="C1974" s="10"/>
       <c r="D1974" s="10"/>
       <c r="E1974" s="10"/>
     </row>
     <row r="1975">
       <c r="A1975" s="10"/>
-      <c r="B1975" s="18"/>
+      <c r="B1975" s="17"/>
       <c r="C1975" s="10"/>
       <c r="D1975" s="10"/>
       <c r="E1975" s="10"/>
     </row>
     <row r="1976">
       <c r="A1976" s="10"/>
-      <c r="B1976" s="18"/>
+      <c r="B1976" s="17"/>
       <c r="C1976" s="10"/>
       <c r="D1976" s="10"/>
       <c r="E1976" s="10"/>
     </row>
     <row r="1977">
       <c r="A1977" s="10"/>
-      <c r="B1977" s="18"/>
+      <c r="B1977" s="17"/>
       <c r="C1977" s="10"/>
       <c r="D1977" s="10"/>
       <c r="E1977" s="10"/>
     </row>
     <row r="1978">
       <c r="A1978" s="10"/>
-      <c r="B1978" s="18"/>
+      <c r="B1978" s="17"/>
       <c r="C1978" s="10"/>
       <c r="D1978" s="10"/>
       <c r="E1978" s="10"/>
     </row>
     <row r="1979">
       <c r="A1979" s="10"/>
-      <c r="B1979" s="18"/>
+      <c r="B1979" s="17"/>
       <c r="C1979" s="10"/>
       <c r="D1979" s="10"/>
       <c r="E1979" s="10"/>
     </row>
     <row r="1980">
       <c r="A1980" s="10"/>
-      <c r="B1980" s="18"/>
+      <c r="B1980" s="17"/>
       <c r="C1980" s="10"/>
       <c r="D1980" s="10"/>
       <c r="E1980" s="10"/>
     </row>
     <row r="1981">
       <c r="A1981" s="10"/>
-      <c r="B1981" s="18"/>
+      <c r="B1981" s="17"/>
       <c r="C1981" s="10"/>
       <c r="D1981" s="10"/>
       <c r="E1981" s="10"/>
     </row>
     <row r="1982">
       <c r="A1982" s="10"/>
-      <c r="B1982" s="18"/>
+      <c r="B1982" s="17"/>
       <c r="C1982" s="10"/>
       <c r="D1982" s="10"/>
       <c r="E1982" s="10"/>
     </row>
     <row r="1983">
       <c r="A1983" s="10"/>
-      <c r="B1983" s="18"/>
+      <c r="B1983" s="17"/>
       <c r="C1983" s="10"/>
       <c r="D1983" s="10"/>
       <c r="E1983" s="10"/>
     </row>
     <row r="1984">
       <c r="A1984" s="10"/>
-      <c r="B1984" s="18"/>
+      <c r="B1984" s="17"/>
       <c r="C1984" s="10"/>
       <c r="D1984" s="10"/>
       <c r="E1984" s="10"/>
     </row>
     <row r="1985">
       <c r="A1985" s="10"/>
-      <c r="B1985" s="18"/>
+      <c r="B1985" s="17"/>
       <c r="C1985" s="10"/>
       <c r="D1985" s="10"/>
       <c r="E1985" s="10"/>
     </row>
     <row r="1986">
       <c r="A1986" s="10"/>
-      <c r="B1986" s="18"/>
+      <c r="B1986" s="17"/>
       <c r="C1986" s="10"/>
       <c r="D1986" s="10"/>
       <c r="E1986" s="10"/>
     </row>
     <row r="1987">
       <c r="A1987" s="10"/>
-      <c r="B1987" s="18"/>
+      <c r="B1987" s="17"/>
       <c r="C1987" s="10"/>
       <c r="D1987" s="10"/>
       <c r="E1987" s="10"/>
     </row>
     <row r="1988">
       <c r="A1988" s="10"/>
-      <c r="B1988" s="18"/>
+      <c r="B1988" s="17"/>
       <c r="C1988" s="10"/>
       <c r="D1988" s="10"/>
       <c r="E1988" s="10"/>
     </row>
     <row r="1989">
       <c r="A1989" s="10"/>
-      <c r="B1989" s="18"/>
+      <c r="B1989" s="17"/>
       <c r="C1989" s="10"/>
       <c r="D1989" s="10"/>
       <c r="E1989" s="10"/>
     </row>
     <row r="1990">
       <c r="A1990" s="10"/>
-      <c r="B1990" s="18"/>
+      <c r="B1990" s="17"/>
       <c r="C1990" s="10"/>
       <c r="D1990" s="10"/>
       <c r="E1990" s="10"/>
     </row>
     <row r="1991">
       <c r="A1991" s="10"/>
-      <c r="B1991" s="18"/>
+      <c r="B1991" s="17"/>
       <c r="C1991" s="10"/>
       <c r="D1991" s="10"/>
       <c r="E1991" s="10"/>
     </row>
     <row r="1992">
       <c r="A1992" s="10"/>
-      <c r="B1992" s="18"/>
+      <c r="B1992" s="17"/>
       <c r="C1992" s="10"/>
       <c r="D1992" s="10"/>
       <c r="E1992" s="10"/>
     </row>
     <row r="1993">
       <c r="A1993" s="10"/>
-      <c r="B1993" s="18"/>
+      <c r="B1993" s="17"/>
       <c r="C1993" s="10"/>
       <c r="D1993" s="10"/>
       <c r="E1993" s="10"/>
     </row>
     <row r="1994">
       <c r="A1994" s="10"/>
-      <c r="B1994" s="18"/>
+      <c r="B1994" s="17"/>
       <c r="C1994" s="10"/>
       <c r="D1994" s="10"/>
       <c r="E1994" s="10"/>
     </row>
     <row r="1995">
       <c r="A1995" s="10"/>
-      <c r="B1995" s="18"/>
+      <c r="B1995" s="17"/>
       <c r="C1995" s="10"/>
       <c r="D1995" s="10"/>
       <c r="E1995" s="10"/>
     </row>
     <row r="1996">
       <c r="A1996" s="10"/>
-      <c r="B1996" s="18"/>
+      <c r="B1996" s="17"/>
       <c r="C1996" s="10"/>
       <c r="D1996" s="10"/>
       <c r="E1996" s="10"/>
     </row>
     <row r="1997">
       <c r="A1997" s="10"/>
-      <c r="B1997" s="18"/>
+      <c r="B1997" s="17"/>
       <c r="C1997" s="10"/>
       <c r="D1997" s="10"/>
       <c r="E1997" s="10"/>
     </row>
     <row r="1998">
       <c r="A1998" s="10"/>
-      <c r="B1998" s="18"/>
+      <c r="B1998" s="17"/>
       <c r="C1998" s="10"/>
       <c r="D1998" s="10"/>
       <c r="E1998" s="10"/>
     </row>
     <row r="1999">
       <c r="A1999" s="10"/>
-      <c r="B1999" s="18"/>
+      <c r="B1999" s="17"/>
       <c r="C1999" s="10"/>
       <c r="D1999" s="10"/>
       <c r="E1999" s="10"/>
     </row>
     <row r="2000">
       <c r="A2000" s="10"/>
-      <c r="B2000" s="18"/>
+      <c r="B2000" s="17"/>
       <c r="C2000" s="10"/>
       <c r="D2000" s="10"/>
       <c r="E2000" s="10"/>
     </row>
     <row r="2001">
       <c r="A2001" s="10"/>
-      <c r="B2001" s="18"/>
+      <c r="B2001" s="17"/>
       <c r="C2001" s="10"/>
       <c r="D2001" s="10"/>
       <c r="E2001" s="10"/>
     </row>
     <row r="2002">
       <c r="A2002" s="10"/>
-      <c r="B2002" s="18"/>
+      <c r="B2002" s="17"/>
       <c r="C2002" s="10"/>
       <c r="D2002" s="10"/>
       <c r="E2002" s="10"/>
     </row>
     <row r="2003">
       <c r="A2003" s="10"/>
-      <c r="B2003" s="18"/>
+      <c r="B2003" s="17"/>
       <c r="C2003" s="10"/>
       <c r="D2003" s="10"/>
       <c r="E2003" s="10"/>
     </row>
     <row r="2004">
       <c r="A2004" s="10"/>
-      <c r="B2004" s="18"/>
+      <c r="B2004" s="17"/>
       <c r="C2004" s="10"/>
       <c r="D2004" s="10"/>
       <c r="E2004" s="10"/>
     </row>
     <row r="2005">
       <c r="A2005" s="10"/>
-      <c r="B2005" s="18"/>
+      <c r="B2005" s="17"/>
       <c r="C2005" s="10"/>
       <c r="D2005" s="10"/>
       <c r="E2005" s="10"/>
     </row>
     <row r="2006">
       <c r="A2006" s="10"/>
-      <c r="B2006" s="18"/>
+      <c r="B2006" s="17"/>
       <c r="C2006" s="10"/>
       <c r="D2006" s="10"/>
       <c r="E2006" s="10"/>
     </row>
     <row r="2007">
       <c r="A2007" s="10"/>
-      <c r="B2007" s="18"/>
+      <c r="B2007" s="17"/>
       <c r="C2007" s="10"/>
       <c r="D2007" s="10"/>
       <c r="E2007" s="10"/>
     </row>
     <row r="2008">
       <c r="A2008" s="10"/>
-      <c r="B2008" s="18"/>
+      <c r="B2008" s="17"/>
       <c r="C2008" s="10"/>
       <c r="D2008" s="10"/>
       <c r="E2008" s="10"/>
     </row>
     <row r="2009">
       <c r="A2009" s="10"/>
-      <c r="B2009" s="18"/>
+      <c r="B2009" s="17"/>
       <c r="C2009" s="10"/>
       <c r="D2009" s="10"/>
       <c r="E2009" s="10"/>
     </row>
     <row r="2010">
       <c r="A2010" s="10"/>
-      <c r="B2010" s="18"/>
+      <c r="B2010" s="17"/>
       <c r="C2010" s="10"/>
       <c r="D2010" s="10"/>
       <c r="E2010" s="10"/>
     </row>
     <row r="2011">
       <c r="A2011" s="10"/>
-      <c r="B2011" s="18"/>
+      <c r="B2011" s="17"/>
       <c r="C2011" s="10"/>
       <c r="D2011" s="10"/>
       <c r="E2011" s="10"/>
     </row>
     <row r="2012">
       <c r="A2012" s="10"/>
-      <c r="B2012" s="18"/>
+      <c r="B2012" s="17"/>
       <c r="C2012" s="10"/>
       <c r="D2012" s="10"/>
       <c r="E2012" s="10"/>
     </row>
     <row r="2013">
       <c r="A2013" s="10"/>
-      <c r="B2013" s="18"/>
+      <c r="B2013" s="17"/>
       <c r="C2013" s="10"/>
       <c r="D2013" s="10"/>
       <c r="E2013" s="10"/>
     </row>
     <row r="2014">
       <c r="A2014" s="10"/>
-      <c r="B2014" s="18"/>
+      <c r="B2014" s="17"/>
       <c r="C2014" s="10"/>
       <c r="D2014" s="10"/>
       <c r="E2014" s="10"/>
     </row>
     <row r="2015">
       <c r="A2015" s="10"/>
-      <c r="B2015" s="18"/>
+      <c r="B2015" s="17"/>
       <c r="C2015" s="10"/>
       <c r="D2015" s="10"/>
       <c r="E2015" s="10"/>
     </row>
     <row r="2016">
       <c r="A2016" s="10"/>
-      <c r="B2016" s="18"/>
+      <c r="B2016" s="17"/>
       <c r="C2016" s="10"/>
       <c r="D2016" s="10"/>
       <c r="E2016" s="10"/>
     </row>
     <row r="2017">
       <c r="A2017" s="10"/>
-      <c r="B2017" s="18"/>
+      <c r="B2017" s="17"/>
       <c r="C2017" s="10"/>
       <c r="D2017" s="10"/>
       <c r="E2017" s="10"/>
     </row>
     <row r="2018">
       <c r="A2018" s="10"/>
-      <c r="B2018" s="18"/>
+      <c r="B2018" s="17"/>
       <c r="C2018" s="10"/>
       <c r="D2018" s="10"/>
       <c r="E2018" s="10"/>
     </row>
     <row r="2019">
       <c r="A2019" s="10"/>
-      <c r="B2019" s="18"/>
+      <c r="B2019" s="17"/>
       <c r="C2019" s="10"/>
       <c r="D2019" s="10"/>
       <c r="E2019" s="10"/>
     </row>
     <row r="2020">
       <c r="A2020" s="10"/>
-      <c r="B2020" s="18"/>
+      <c r="B2020" s="17"/>
       <c r="C2020" s="10"/>
       <c r="D2020" s="10"/>
       <c r="E2020" s="10"/>
     </row>
     <row r="2021">
       <c r="A2021" s="10"/>
-      <c r="B2021" s="18"/>
+      <c r="B2021" s="17"/>
       <c r="C2021" s="10"/>
       <c r="D2021" s="10"/>
       <c r="E2021" s="10"/>
     </row>
     <row r="2022">
       <c r="A2022" s="10"/>
-      <c r="B2022" s="18"/>
+      <c r="B2022" s="17"/>
       <c r="C2022" s="10"/>
       <c r="D2022" s="10"/>
       <c r="E2022" s="10"/>
     </row>
     <row r="2023">
       <c r="A2023" s="10"/>
-      <c r="B2023" s="18"/>
+      <c r="B2023" s="17"/>
       <c r="C2023" s="10"/>
       <c r="D2023" s="10"/>
       <c r="E2023" s="10"/>
     </row>
     <row r="2024">
       <c r="A2024" s="10"/>
-      <c r="B2024" s="18"/>
+      <c r="B2024" s="17"/>
       <c r="C2024" s="10"/>
       <c r="D2024" s="10"/>
       <c r="E2024" s="10"/>
     </row>
     <row r="2025">
       <c r="A2025" s="10"/>
-      <c r="B2025" s="18"/>
+      <c r="B2025" s="17"/>
       <c r="C2025" s="10"/>
       <c r="D2025" s="10"/>
       <c r="E2025" s="10"/>
     </row>
     <row r="2026">
       <c r="A2026" s="10"/>
-      <c r="B2026" s="18"/>
+      <c r="B2026" s="17"/>
       <c r="C2026" s="10"/>
       <c r="D2026" s="10"/>
       <c r="E2026" s="10"/>
     </row>
     <row r="2027">
       <c r="A2027" s="10"/>
-      <c r="B2027" s="18"/>
+      <c r="B2027" s="17"/>
       <c r="C2027" s="10"/>
       <c r="D2027" s="10"/>
       <c r="E2027" s="10"/>
     </row>
     <row r="2028">
       <c r="A2028" s="10"/>
-      <c r="B2028" s="18"/>
+      <c r="B2028" s="17"/>
       <c r="C2028" s="10"/>
       <c r="D2028" s="10"/>
       <c r="E2028" s="10"/>
     </row>
     <row r="2029">
       <c r="A2029" s="10"/>
-      <c r="B2029" s="18"/>
+      <c r="B2029" s="17"/>
       <c r="C2029" s="10"/>
       <c r="D2029" s="10"/>
       <c r="E2029" s="10"/>
     </row>
     <row r="2030">
       <c r="A2030" s="10"/>
-      <c r="B2030" s="18"/>
+      <c r="B2030" s="17"/>
       <c r="C2030" s="10"/>
       <c r="D2030" s="10"/>
       <c r="E2030" s="10"/>
     </row>
     <row r="2031">
       <c r="A2031" s="10"/>
-      <c r="B2031" s="18"/>
+      <c r="B2031" s="17"/>
       <c r="C2031" s="10"/>
       <c r="D2031" s="10"/>
       <c r="E2031" s="10"/>
     </row>
     <row r="2032">
       <c r="A2032" s="10"/>
-      <c r="B2032" s="18"/>
+      <c r="B2032" s="17"/>
       <c r="C2032" s="10"/>
       <c r="D2032" s="10"/>
       <c r="E2032" s="10"/>
     </row>
     <row r="2033">
       <c r="A2033" s="10"/>
-      <c r="B2033" s="18"/>
+      <c r="B2033" s="17"/>
       <c r="C2033" s="10"/>
       <c r="D2033" s="10"/>
       <c r="E2033" s="10"/>
     </row>
     <row r="2034">
       <c r="A2034" s="10"/>
-      <c r="B2034" s="18"/>
+      <c r="B2034" s="17"/>
       <c r="C2034" s="10"/>
       <c r="D2034" s="10"/>
       <c r="E2034" s="10"/>
     </row>
     <row r="2035">
       <c r="A2035" s="10"/>
-      <c r="B2035" s="18"/>
+      <c r="B2035" s="17"/>
       <c r="C2035" s="10"/>
       <c r="D2035" s="10"/>
       <c r="E2035" s="10"/>
     </row>
     <row r="2036">
       <c r="A2036" s="10"/>
-      <c r="B2036" s="18"/>
+      <c r="B2036" s="17"/>
       <c r="C2036" s="10"/>
       <c r="D2036" s="10"/>
       <c r="E2036" s="10"/>
     </row>
     <row r="2037">
       <c r="A2037" s="10"/>
-      <c r="B2037" s="18"/>
+      <c r="B2037" s="17"/>
       <c r="C2037" s="10"/>
       <c r="D2037" s="10"/>
       <c r="E2037" s="10"/>
     </row>
     <row r="2038">
       <c r="A2038" s="10"/>
-      <c r="B2038" s="18"/>
+      <c r="B2038" s="17"/>
       <c r="C2038" s="10"/>
       <c r="D2038" s="10"/>
       <c r="E2038" s="10"/>
     </row>
     <row r="2039">
       <c r="A2039" s="10"/>
-      <c r="B2039" s="18"/>
+      <c r="B2039" s="17"/>
       <c r="C2039" s="10"/>
       <c r="D2039" s="10"/>
       <c r="E2039" s="10"/>
     </row>
     <row r="2040">
       <c r="A2040" s="10"/>
-      <c r="B2040" s="18"/>
+      <c r="B2040" s="17"/>
       <c r="C2040" s="10"/>
       <c r="D2040" s="10"/>
       <c r="E2040" s="10"/>
     </row>
     <row r="2041">
       <c r="A2041" s="10"/>
-      <c r="B2041" s="18"/>
+      <c r="B2041" s="17"/>
       <c r="C2041" s="10"/>
       <c r="D2041" s="10"/>
       <c r="E2041" s="10"/>
     </row>
     <row r="2042">
       <c r="A2042" s="10"/>
-      <c r="B2042" s="18"/>
+      <c r="B2042" s="17"/>
       <c r="C2042" s="10"/>
       <c r="D2042" s="10"/>
       <c r="E2042" s="10"/>
     </row>
     <row r="2043">
       <c r="A2043" s="10"/>
-      <c r="B2043" s="18"/>
+      <c r="B2043" s="17"/>
       <c r="C2043" s="10"/>
       <c r="D2043" s="10"/>
       <c r="E2043" s="10"/>
     </row>
     <row r="2044">
       <c r="A2044" s="10"/>
-      <c r="B2044" s="18"/>
+      <c r="B2044" s="17"/>
       <c r="C2044" s="10"/>
       <c r="D2044" s="10"/>
       <c r="E2044" s="10"/>
     </row>
     <row r="2045">
       <c r="A2045" s="10"/>
-      <c r="B2045" s="18"/>
+      <c r="B2045" s="17"/>
       <c r="C2045" s="10"/>
       <c r="D2045" s="10"/>
       <c r="E2045" s="10"/>
     </row>
     <row r="2046">
       <c r="A2046" s="10"/>
-      <c r="B2046" s="18"/>
+      <c r="B2046" s="17"/>
       <c r="C2046" s="10"/>
       <c r="D2046" s="10"/>
       <c r="E2046" s="10"/>
     </row>
     <row r="2047">
       <c r="A2047" s="10"/>
-      <c r="B2047" s="18"/>
+      <c r="B2047" s="17"/>
       <c r="C2047" s="10"/>
       <c r="D2047" s="10"/>
       <c r="E2047" s="10"/>
     </row>
     <row r="2048">
       <c r="A2048" s="10"/>
-      <c r="B2048" s="18"/>
+      <c r="B2048" s="17"/>
       <c r="C2048" s="10"/>
       <c r="D2048" s="10"/>
       <c r="E2048" s="10"/>
     </row>
     <row r="2049">
       <c r="A2049" s="10"/>
-      <c r="B2049" s="18"/>
+      <c r="B2049" s="17"/>
       <c r="C2049" s="10"/>
       <c r="D2049" s="10"/>
       <c r="E2049" s="10"/>
     </row>
     <row r="2050">
       <c r="A2050" s="10"/>
-      <c r="B2050" s="18"/>
+      <c r="B2050" s="17"/>
       <c r="C2050" s="10"/>
       <c r="D2050" s="10"/>
       <c r="E2050" s="10"/>
     </row>
     <row r="2051">
       <c r="A2051" s="10"/>
-      <c r="B2051" s="18"/>
+      <c r="B2051" s="17"/>
       <c r="C2051" s="10"/>
       <c r="D2051" s="10"/>
       <c r="E2051" s="10"/>
     </row>
     <row r="2052">
       <c r="A2052" s="10"/>
-      <c r="B2052" s="18"/>
+      <c r="B2052" s="17"/>
       <c r="C2052" s="10"/>
       <c r="D2052" s="10"/>
       <c r="E2052" s="10"/>
     </row>
     <row r="2053">
       <c r="A2053" s="10"/>
-      <c r="B2053" s="18"/>
+      <c r="B2053" s="17"/>
       <c r="C2053" s="10"/>
       <c r="D2053" s="10"/>
       <c r="E2053" s="10"/>

--- a/PublicCustomerApp/src/python/translation.xlsx
+++ b/PublicCustomerApp/src/python/translation.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2770" uniqueCount="2655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2794" uniqueCount="2678">
   <si>
     <t>key</t>
   </si>
@@ -7662,6 +7662,9 @@
     <t>welcome_became_a_driver</t>
   </si>
   <si>
+    <t>Became a Driver</t>
+  </si>
+  <si>
     <t>ஆகிவிட்டார்</t>
   </si>
   <si>
@@ -7990,6 +7993,72 @@
   </si>
   <si>
     <t>Please Select Gender</t>
+  </si>
+  <si>
+    <t>upload_driver_photo</t>
+  </si>
+  <si>
+    <t>Upload or capture driver photo</t>
+  </si>
+  <si>
+    <t>upload_driving_license</t>
+  </si>
+  <si>
+    <t>Upload or capture driving license</t>
+  </si>
+  <si>
+    <t>upload_aadhaar_card</t>
+  </si>
+  <si>
+    <t>Upload or capture Aadhaar card</t>
+  </si>
+  <si>
+    <t>upload_pan_card</t>
+  </si>
+  <si>
+    <t>Upload or capture PAN card</t>
+  </si>
+  <si>
+    <t>upload_aadhaar_document</t>
+  </si>
+  <si>
+    <t>Upload Aadhaar Document</t>
+  </si>
+  <si>
+    <t>upload_pan_document</t>
+  </si>
+  <si>
+    <t>Upload PAN Document</t>
+  </si>
+  <si>
+    <t>document_center_bank_modal_title</t>
+  </si>
+  <si>
+    <t>Verify payouts with</t>
+  </si>
+  <si>
+    <t>document_center_select_upi</t>
+  </si>
+  <si>
+    <t>Verify UPI ID</t>
+  </si>
+  <si>
+    <t>document_center_select_bank</t>
+  </si>
+  <si>
+    <t>Verify Bank Account</t>
+  </si>
+  <si>
+    <t>enter_your_residential_address</t>
+  </si>
+  <si>
+    <t>Enter Your Residential_ Address</t>
+  </si>
+  <si>
+    <t>passbook_scan_helper</t>
+  </si>
+  <si>
+    <t>Upload or capture the front page to auto-detect account details.</t>
   </si>
 </sst>
 </file>
@@ -8491,8 +8560,8 @@
         <v>பயணத்தை உறுதிசெய்து தொடங்க வாடிக்கையாளரைத் தொடர்பு கொண்டதை உறுதிப்படுத்திக் கொள்ளுங்கள்.</v>
       </c>
       <c r="D6" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B6, ""en"", ""hi"")"),"ग्राहक से संपर्क करके यात्रा की पुष्टि अवश्य कर लें और यात्रा शुरू करें।")</f>
-        <v>ग्राहक से संपर्क करके यात्रा की पुष्टि अवश्य कर लें और यात्रा शुरू करें।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B6, ""en"", ""hi"")"),"ग्राहक से संपर्क करके यात्रा की पुष्टि कर लें और यात्रा शुरू करें।")</f>
+        <v>ग्राहक से संपर्क करके यात्रा की पुष्टि कर लें और यात्रा शुरू करें।</v>
       </c>
       <c r="E6" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B6, ""en"", ""kn"")"),"ಖಚಿತಪಡಿಸಲು ಮತ್ತು ಪ್ರಯಾಣವನ್ನು ಪ್ರಾರಂಭಿಸಲು ನೀವು ಗ್ರಾಹಕರನ್ನು ಸಂಪರ್ಕಿಸಿದ್ದೀರಿ ಎಂದು ಖಚಿತಪಡಿಸಿಕೊಳ್ಳಿ.")</f>
@@ -9135,8 +9204,8 @@
         <v>இருப்பிட அனுமதி மறுக்கப்பட்டது</v>
       </c>
       <c r="D29" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B29, ""en"", ""hi"")"),"स्थान अनुमति अस्वीकृत")</f>
-        <v>स्थान अनुमति अस्वीकृत</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B29, ""en"", ""hi"")"),"स्थान की अनुमति अस्वीकृत")</f>
+        <v>स्थान की अनुमति अस्वीकृत</v>
       </c>
       <c r="E29" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B29, ""en"", ""kn"")"),"ಸ್ಥಳ ಅನುಮತಿ ನಿರಾಕರಿಸಲಾಗಿದೆ")</f>
@@ -12843,8 +12912,8 @@
         <v>ನೋಂದಾಯಿತ ಫೋನ್ ಸಂಖ್ಯೆಗೆ OTP ಯಶಸ್ವಿಯಾಗಿ ಮರು ಕಳುಹಿಸಲಾಗಿದೆ.</v>
       </c>
       <c r="F160" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B160, ""en"", ""ml"")"),"രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വീണ്ടും അയച്ചു.")</f>
-        <v>രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വീണ്ടും അയച്ചു.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B160, ""en"", ""ml"")"),"രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വിജയകരമായി വീണ്ടും അയച്ചു.")</f>
+        <v>രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വിജയകരമായി വീണ്ടും അയച്ചു.</v>
       </c>
       <c r="G160" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B160, ""en"", ""te"")"),"రిజిస్టర్డ్ ఫోన్ నంబర్‌కు OTP విజయవంతంగా తిరిగి పంపబడింది.")</f>
@@ -13275,8 +13344,8 @@
         <v>ಇಲ್ಲ, ಆನ್‌ಲೈನ್‌ನಲ್ಲಿರಿ</v>
       </c>
       <c r="F175" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B175, ""en"", ""ml"")"),"വേണ്ട, ഓൺലൈനാകൂ")</f>
-        <v>വേണ്ട, ഓൺലൈനാകൂ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B175, ""en"", ""ml"")"),"വേണ്ട, ഓൺലൈനിൽ ആയിരിക്കൂ")</f>
+        <v>വേണ്ട, ഓൺലൈനിൽ ആയിരിക്കൂ</v>
       </c>
       <c r="G175" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B175, ""en"", ""te"")"),"వద్దు, ఆన్‌లైన్‌లో ఉండు")</f>
@@ -13859,8 +13928,8 @@
         <v>यदि सत्यापन में अधिक समय लगता है तो सहायता टीम से संपर्क करें।</v>
       </c>
       <c r="E196" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B196, ""en"", ""kn"")"),"ಪರಿಶೀಲನೆಗೆ ಹೆಚ್ಚಿನ ಸಮಯ ತೆಗೆದುಕೊಂಡರೆ ಬೆಂಬಲವನ್ನು ಸಂಪರ್ಕಿಸಿ")</f>
-        <v>ಪರಿಶೀಲನೆಗೆ ಹೆಚ್ಚಿನ ಸಮಯ ತೆಗೆದುಕೊಂಡರೆ ಬೆಂಬಲವನ್ನು ಸಂಪರ್ಕಿಸಿ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B196, ""en"", ""kn"")"),"ಪರಿಶೀಲನೆಗೆ ಹೆಚ್ಚು ಸಮಯ ತೆಗೆದುಕೊಂಡರೆ ಬೆಂಬಲವನ್ನು ಸಂಪರ್ಕಿಸಿ")</f>
+        <v>ಪರಿಶೀಲನೆಗೆ ಹೆಚ್ಚು ಸಮಯ ತೆಗೆದುಕೊಂಡರೆ ಬೆಂಬಲವನ್ನು ಸಂಪರ್ಕಿಸಿ</v>
       </c>
       <c r="F196" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B196, ""en"", ""ml"")"),"പരിശോധിച്ചുറപ്പിക്കലിന് കൂടുതൽ സമയമെടുക്കുന്നുവെങ്കിൽ പിന്തുണയുമായി ബന്ധപ്പെടുക.")</f>
@@ -13947,8 +14016,8 @@
         <v>ಆನ್‌ಲೈನ್‌ಗೆ ಹೋಗಿ</v>
       </c>
       <c r="F199" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B199, ""en"", ""ml"")"),"ഓൺലൈനിൽ പോകുക")</f>
-        <v>ഓൺലൈനിൽ പോകുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B199, ""en"", ""ml"")"),"ഓൺലൈനാകുക")</f>
+        <v>ഓൺലൈനാകുക</v>
       </c>
       <c r="G199" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B199, ""en"", ""te"")"),"ఆన్‌లైన్‌లోకి వెళ్లండి")</f>
@@ -17211,8 +17280,8 @@
         <v>611</v>
       </c>
       <c r="C316" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B316, ""en"", ""ta"")"),"பயணியை அடைய முடியவில்லை அல்லது பிக்அப் இடத்தில் இல்லை.")</f>
-        <v>பயணியை அடைய முடியவில்லை அல்லது பிக்அப் இடத்தில் இல்லை.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B316, ""en"", ""ta"")"),"பயணியை அணுக முடியவில்லை அல்லது பிக்அப் இடத்தில் இல்லை.")</f>
+        <v>பயணியை அணுக முடியவில்லை அல்லது பிக்அப் இடத்தில் இல்லை.</v>
       </c>
       <c r="D316" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B316, ""en"", ""hi"")"),"राइडर से संपर्क नहीं हो पा रहा है या वह पिकअप स्थान पर मौजूद नहीं है")</f>
@@ -17411,8 +17480,8 @@
         <v>மோசமான போக்குவரத்து அல்லது வானிலை</v>
       </c>
       <c r="D323" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B323, ""en"", ""hi"")"),"यातायात की खराब स्थिति या मौसम की स्थिति")</f>
-        <v>यातायात की खराब स्थिति या मौसम की स्थिति</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B323, ""en"", ""hi"")"),"खराब यातायात या खराब मौसम की स्थिति")</f>
+        <v>खराब यातायात या खराब मौसम की स्थिति</v>
       </c>
       <c r="E323" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B323, ""en"", ""kn"")"),"ಕಳಪೆ ಸಂಚಾರ ಅಥವಾ ಹವಾಮಾನ ಪರಿಸ್ಥಿತಿಗಳು")</f>
@@ -17783,8 +17852,8 @@
         <v>ಯಾವುದೇ ಟಿಕೆಟ್‌ಗಳು ಕಂಡುಬಂದಿಲ್ಲ.</v>
       </c>
       <c r="F336" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B336, ""en"", ""ml"")"),"ടിക്കറ്റുകളൊന്നും കണ്ടെത്തിയില്ല")</f>
-        <v>ടിക്കറ്റുകളൊന്നും കണ്ടെത്തിയില്ല</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B336, ""en"", ""ml"")"),"ടിക്കറ്റുകളൊന്നും കണ്ടെത്തിയില്ല.")</f>
+        <v>ടിക്കറ്റുകളൊന്നും കണ്ടെത്തിയില്ല.</v>
       </c>
       <c r="G336" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B336, ""en"", ""te"")"),"టిక్కెట్లు దొరకలేదు.")</f>
@@ -18655,8 +18724,8 @@
         <v>ഈ പ്രവർത്തനം പഴയപടിയാക്കാൻ കഴിയില്ല - ഇല്ലാതാക്കിയ ഡാറ്റ വീണ്ടെടുക്കാൻ കഴിയില്ല.</v>
       </c>
       <c r="G367" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B367, ""en"", ""te"")"),"ఈ చర్యను రద్దు చేయలేము - తొలగించబడిన డేటాను తిరిగి పొందడం సాధ్యం కాదు.")</f>
-        <v>ఈ చర్యను రద్దు చేయలేము - తొలగించబడిన డేటాను తిరిగి పొందడం సాధ్యం కాదు.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B367, ""en"", ""te"")"),"ఈ చర్యను రద్దు చేయడం సాధ్యం కాదు - తొలగించబడిన డేటాను తిరిగి పొందడం సాధ్యం కాదు.")</f>
+        <v>ఈ చర్యను రద్దు చేయడం సాధ్యం కాదు - తొలగించబడిన డేటాను తిరిగి పొందడం సాధ్యం కాదు.</v>
       </c>
     </row>
     <row r="368">
@@ -18919,8 +18988,8 @@
         <v>729</v>
       </c>
       <c r="C377" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B377, ""en"", ""ta"")"),"வாகன ஆர்சி ஆவண பின்புறம்")</f>
-        <v>வாகன ஆர்சி ஆவண பின்புறம்</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B377, ""en"", ""ta"")"),"வாகன ஆர்.சி. ஆவணத்தின் பின்புறம்")</f>
+        <v>வாகன ஆர்.சி. ஆவணத்தின் பின்புறம்</v>
       </c>
       <c r="D377" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B377, ""en"", ""hi"")"),"वाहन आरसी दस्तावेज़ का पिछला भाग")</f>
@@ -20207,8 +20276,8 @@
         <v>821</v>
       </c>
       <c r="C423" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B423, ""en"", ""ta"")"),"வாட்ஸ்அப்")</f>
-        <v>வாட்ஸ்அப்</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B423, ""en"", ""ta"")"),"பயன்கள்")</f>
+        <v>பயன்கள்</v>
       </c>
       <c r="D423" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B423, ""en"", ""hi"")"),"WhatsApp")</f>
@@ -20835,8 +20904,8 @@
         <v>ಸಂಪರ್ಕಿಸಿ</v>
       </c>
       <c r="F445" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B445, ""en"", ""ml"")"),"ബന്ധപ്പെടുക")</f>
-        <v>ബന്ധപ്പെടുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B445, ""en"", ""ml"")"),"വാര്ത്താവിനിമയം")</f>
+        <v>വാര്ത്താവിനിമയം</v>
       </c>
       <c r="G445" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B445, ""en"", ""te"")"),"సంప్రదించండి")</f>
@@ -22031,8 +22100,8 @@
         <v>ഡ്രോപ്പ് ലൊക്കേഷൻ സ്ഥിരീകരിക്കുക</v>
       </c>
       <c r="G489" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B489, ""en"", ""te"")"),"డ్రాప్ స్థానాన్ని నిర్ధారించండి")</f>
-        <v>డ్రాప్ స్థానాన్ని నిర్ధారించండి</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B489, ""en"", ""te"")"),"డ్రాప్ లొకేషన్‌ను నిర్ధారించండి")</f>
+        <v>డ్రాప్ లొకేషన్‌ను నిర్ధారించండి</v>
       </c>
     </row>
     <row r="490">
@@ -29782,8 +29851,8 @@
         <v>ನೀವು ಆಯ್ಕೆ ಮಾಡಿದ {ವಾಹನ} ಹತ್ತಿರದಲ್ಲಿ ಯಾವುದೇ ಚಾಲಕರಿಲ್ಲ. ಲಭ್ಯವಿರುವ ಚಾಲಕರಿರುವ ಮತ್ತೊಂದು ವಾಹನವನ್ನು ನಾವು ಆರಿಸಿಕೊಂಡಿದ್ದೇವೆ.</v>
       </c>
       <c r="F776" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B776, ""en"", ""ml"")"),"നിങ്ങൾ തിരഞ്ഞെടുത്ത {വാഹനത്തിന്} സമീപത്ത് ഡ്രൈവറില്ല. ലഭ്യമായ ഡ്രൈവറുകളുള്ള മറ്റൊരു വാഹനം ഞങ്ങൾ തിരഞ്ഞെടുത്തു.")</f>
-        <v>നിങ്ങൾ തിരഞ്ഞെടുത്ത {വാഹനത്തിന്} സമീപത്ത് ഡ്രൈവറില്ല. ലഭ്യമായ ഡ്രൈവറുകളുള്ള മറ്റൊരു വാഹനം ഞങ്ങൾ തിരഞ്ഞെടുത്തു.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B776, ""en"", ""ml"")"),"നിങ്ങൾ തിരഞ്ഞെടുത്ത {വാഹനത്തിന്} സമീപത്ത് ഡ്രൈവറുകളില്ല. ലഭ്യമായ ഡ്രൈവറുകളുള്ള മറ്റൊരു വാഹനം ഞങ്ങൾ തിരഞ്ഞെടുത്തു.")</f>
+        <v>നിങ്ങൾ തിരഞ്ഞെടുത്ത {വാഹനത്തിന്} സമീപത്ത് ഡ്രൈവറുകളില്ല. ലഭ്യമായ ഡ്രൈവറുകളുള്ള മറ്റൊരു വാഹനം ഞങ്ങൾ തിരഞ്ഞെടുത്തു.</v>
       </c>
       <c r="G776" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B776, ""en"", ""te"")"),"మీరు ఎంచుకున్న {vehicle} కి సమీపంలో డ్రైవర్లు లేరు. అందుబాటులో ఉన్న డ్రైవర్లతో మేము మరొక వాహనాన్ని ఎంచుకున్నాము.")</f>
@@ -29940,8 +30009,8 @@
         <v>कोई सुरक्षित स्थान नहीं</v>
       </c>
       <c r="E782" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B782, ""en"", ""kn"")"),"ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ")</f>
-        <v>ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B782, ""en"", ""kn"")"),"ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ.")</f>
+        <v>ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ.</v>
       </c>
       <c r="F782" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B782, ""en"", ""ml"")"),"സംരക്ഷിച്ച സ്ഥലങ്ങളൊന്നുമില്ല.")</f>
@@ -34588,8 +34657,8 @@
         <v>2311</v>
       </c>
       <c r="D954" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B954, ""en"", ""hi"")"),"ड्राइवर बुक किए गए वाहन के बजाय किसी दूसरे प्रकार का वाहन लेकर आया (उदाहरण के लिए, एसयूवी के बजाय सेडान)।")</f>
-        <v>ड्राइवर बुक किए गए वाहन के बजाय किसी दूसरे प्रकार का वाहन लेकर आया (उदाहरण के लिए, एसयूवी के बजाय सेडान)।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B954, ""en"", ""hi"")"),"ड्राइवर बुक किए गए वाहन के प्रकार से भिन्न वाहन लेकर आया (उदाहरण के लिए, एसयूवी के बजाय सेडान)।")</f>
+        <v>ड्राइवर बुक किए गए वाहन के प्रकार से भिन्न वाहन लेकर आया (उदाहरण के लिए, एसयूवी के बजाय सेडान)।</v>
       </c>
       <c r="E954" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B954, ""en"", ""kn"")"),"ಚಾಲಕ ಬುಕ್ ಮಾಡಿದ ವಾಹನಕ್ಕಿಂತ ಬೇರೆ ವಾಹನ ಪ್ರಕಾರದೊಂದಿಗೆ ಬಂದಿದ್ದಾನೆ (ಉದಾ. SUV ಬದಲಿಗೆ ಸೆಡಾನ್)")</f>
@@ -36950,37 +37019,37 @@
         <v>2544</v>
       </c>
       <c r="B1041" s="12" t="s">
-        <v>943</v>
+        <v>2545</v>
       </c>
       <c r="C1041" s="6" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
       <c r="D1041" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1041, ""en"", ""hi"")"),"ड्राइवर बन गया")</f>
         <v>ड्राइवर बन गया</v>
       </c>
       <c r="E1041" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1041, ""en"", ""kn"")"),"ಚಾಲಕನಾದನು")</f>
-        <v>ಚಾಲಕನಾದನು</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1041, ""en"", ""kn"")"),"ಚಾಲಕನಾದ.")</f>
+        <v>ಚಾಲಕನಾದ.</v>
       </c>
       <c r="F1041" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1041, ""en"", ""ml"")"),"ഒരു_ഡ്രൈവർ ആയി")</f>
-        <v>ഒരു_ഡ്രൈവർ ആയി</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1041, ""en"", ""ml"")"),"ഡ്രൈവർ ആയി.")</f>
+        <v>ഡ്രൈവർ ആയി.</v>
       </c>
       <c r="G1041" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1041, ""en"", ""te"")"),"డ్రైవర్_అయ్యాడు")</f>
-        <v>డ్రైవర్_అయ్యాడు</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1041, ""en"", ""te"")"),"డ్రైవర్ అయ్యాడు.")</f>
+        <v>డ్రైవర్ అయ్యాడు.</v>
       </c>
     </row>
     <row r="1042">
       <c r="A1042" s="4" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
       <c r="B1042" s="12" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="C1042" s="6" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="D1042" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1042, ""en"", ""hi"")"),"स्वागत")</f>
@@ -37001,13 +37070,13 @@
     </row>
     <row r="1043">
       <c r="A1043" s="4" t="s">
-        <v>2549</v>
+        <v>2550</v>
       </c>
       <c r="B1043" s="12" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="C1043" s="6" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
       <c r="D1043" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1043, ""en"", ""hi"")"),"स्वागत")</f>
@@ -37028,13 +37097,13 @@
     </row>
     <row r="1044">
       <c r="A1044" s="4" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
       <c r="B1044" s="12" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="C1044" s="6" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="D1044" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1044, ""en"", ""hi"")"),"स्वागत")</f>
@@ -37055,13 +37124,13 @@
     </row>
     <row r="1045">
       <c r="A1045" s="4" t="s">
-        <v>2553</v>
+        <v>2554</v>
       </c>
       <c r="B1045" s="12" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="C1045" s="6" t="s">
-        <v>2554</v>
+        <v>2555</v>
       </c>
       <c r="D1045" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1045, ""en"", ""hi"")"),"स्वागत")</f>
@@ -37082,40 +37151,40 @@
     </row>
     <row r="1046">
       <c r="A1046" s="4" t="s">
-        <v>2555</v>
+        <v>2556</v>
       </c>
       <c r="B1046" s="12" t="s">
-        <v>2547</v>
+        <v>2545</v>
       </c>
       <c r="C1046" s="6" t="s">
-        <v>2556</v>
+        <v>2557</v>
       </c>
       <c r="D1046" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1046, ""en"", ""hi"")"),"स्वागत")</f>
-        <v>स्वागत</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1046, ""en"", ""hi"")"),"ड्राइवर बन गया")</f>
+        <v>ड्राइवर बन गया</v>
       </c>
       <c r="E1046" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1046, ""en"", ""kn"")"),"ಸ್ವಾಗತ")</f>
-        <v>ಸ್ವಾಗತ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1046, ""en"", ""kn"")"),"ಚಾಲಕನಾದ.")</f>
+        <v>ಚಾಲಕನಾದ.</v>
       </c>
       <c r="F1046" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1046, ""en"", ""ml"")"),"സ്വാഗതം")</f>
-        <v>സ്വാഗതം</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1046, ""en"", ""ml"")"),"ഡ്രൈവർ ആയി.")</f>
+        <v>ഡ്രൈവർ ആയി.</v>
       </c>
       <c r="G1046" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1046, ""en"", ""te"")"),"స్వాగతం")</f>
-        <v>స్వాగతం</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1046, ""en"", ""te"")"),"డ్రైవర్ అయ్యాడు.")</f>
+        <v>డ్రైవర్ అయ్యాడు.</v>
       </c>
     </row>
     <row r="1047">
       <c r="A1047" s="4" t="s">
-        <v>2557</v>
+        <v>2558</v>
       </c>
       <c r="B1047" s="12" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="C1047" s="6" t="s">
-        <v>2558</v>
+        <v>2559</v>
       </c>
       <c r="D1047" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1047, ""en"", ""hi"")"),"स्वागत")</f>
@@ -37136,13 +37205,13 @@
     </row>
     <row r="1048">
       <c r="A1048" s="4" t="s">
-        <v>2559</v>
+        <v>2560</v>
       </c>
       <c r="B1048" s="12" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="C1048" s="6" t="s">
-        <v>2560</v>
+        <v>2561</v>
       </c>
       <c r="D1048" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1048, ""en"", ""hi"")"),"स्वागत")</f>
@@ -37163,13 +37232,13 @@
     </row>
     <row r="1049">
       <c r="A1049" s="4" t="s">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="B1049" s="5" t="s">
-        <v>2562</v>
+        <v>2563</v>
       </c>
       <c r="C1049" s="6" t="s">
-        <v>2563</v>
+        <v>2564</v>
       </c>
       <c r="D1049" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1049, ""en"", ""hi"")"),"आपका ई मेल पता क्या है")</f>
@@ -37190,13 +37259,13 @@
     </row>
     <row r="1050">
       <c r="A1050" s="4" t="s">
-        <v>2564</v>
+        <v>2565</v>
       </c>
       <c r="B1050" s="5" t="s">
-        <v>2565</v>
+        <v>2566</v>
       </c>
       <c r="C1050" s="6" t="s">
-        <v>2566</v>
+        <v>2567</v>
       </c>
       <c r="D1050" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1050, ""en"", ""hi"")"),"तुम लड़का हो या लड़की")</f>
@@ -37217,13 +37286,13 @@
     </row>
     <row r="1051">
       <c r="A1051" s="4" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="B1051" s="5" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="C1051" s="6" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="D1051" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1051, ""en"", ""hi"")"),"आप कहाँ जाना चाहते हैं?")</f>
@@ -37244,13 +37313,13 @@
     </row>
     <row r="1052">
       <c r="A1052" s="4" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="B1052" s="5" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="C1052" s="6" t="s">
-        <v>2572</v>
+        <v>2573</v>
       </c>
       <c r="D1052" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1052, ""en"", ""hi"")"),"आप यात्रा क्यों रद्द कर रहे हैं?")</f>
@@ -37271,13 +37340,13 @@
     </row>
     <row r="1053">
       <c r="A1053" s="4" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="B1053" s="5" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="C1053" s="6" t="s">
-        <v>2575</v>
+        <v>2576</v>
       </c>
       <c r="D1053" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1053, ""en"", ""hi"")"),"काम")</f>
@@ -37298,10 +37367,10 @@
     </row>
     <row r="1054">
       <c r="A1054" s="4" t="s">
-        <v>2576</v>
+        <v>2577</v>
       </c>
       <c r="B1054" s="5" t="s">
-        <v>2577</v>
+        <v>2578</v>
       </c>
       <c r="C1054" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1054, ""en"", ""ta"")"),"நீங்கள் Razorpay வழியாக பணம் செலுத்துகிறீர்கள்.")</f>
@@ -37326,13 +37395,13 @@
     </row>
     <row r="1055">
       <c r="A1055" s="4" t="s">
-        <v>2578</v>
+        <v>2579</v>
       </c>
       <c r="B1055" s="5" t="s">
-        <v>2579</v>
+        <v>2580</v>
       </c>
       <c r="C1055" s="6" t="s">
-        <v>2580</v>
+        <v>2581</v>
       </c>
       <c r="D1055" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1055, ""en"", ""hi"")"),"आपका ड्राइवर आ जाएगा")</f>
@@ -37353,13 +37422,13 @@
     </row>
     <row r="1056">
       <c r="A1056" s="4" t="s">
-        <v>2581</v>
+        <v>2582</v>
       </c>
       <c r="B1056" s="5" t="s">
-        <v>2582</v>
+        <v>2583</v>
       </c>
       <c r="C1056" s="6" t="s">
-        <v>2583</v>
+        <v>2584</v>
       </c>
       <c r="D1056" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1056, ""en"", ""hi"")"),"आपकी प्रतिक्रिया से हमें ड्राइविंग अनुभव को बेहतर बनाने में मदद मिलेगी।")</f>
@@ -37380,13 +37449,13 @@
     </row>
     <row r="1057">
       <c r="A1057" s="4" t="s">
-        <v>2584</v>
+        <v>2585</v>
       </c>
       <c r="B1057" s="5" t="s">
-        <v>2585</v>
+        <v>2586</v>
       </c>
       <c r="C1057" s="6" t="s">
-        <v>2586</v>
+        <v>2587</v>
       </c>
       <c r="D1057" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1057, ""en"", ""hi"")"),"आपका स्थान")</f>
@@ -37407,13 +37476,13 @@
     </row>
     <row r="1058">
       <c r="A1058" s="4" t="s">
-        <v>2587</v>
+        <v>2588</v>
       </c>
       <c r="B1058" s="5" t="s">
-        <v>2588</v>
+        <v>2589</v>
       </c>
       <c r="C1058" s="6" t="s">
-        <v>2589</v>
+        <v>2590</v>
       </c>
       <c r="D1058" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1058, ""en"", ""hi"")"),"आपका नाम")</f>
@@ -37434,13 +37503,13 @@
     </row>
     <row r="1059">
       <c r="A1059" s="4" t="s">
-        <v>2590</v>
+        <v>2591</v>
       </c>
       <c r="B1059" s="5" t="s">
-        <v>2591</v>
+        <v>2592</v>
       </c>
       <c r="C1059" s="6" t="s">
-        <v>2592</v>
+        <v>2593</v>
       </c>
       <c r="D1059" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1059, ""en"", ""hi"")"),"आपकी हाल की खोजें यहां दिखाई देंगी।")</f>
@@ -37461,13 +37530,13 @@
     </row>
     <row r="1060">
       <c r="A1060" s="4" t="s">
-        <v>2593</v>
+        <v>2594</v>
       </c>
       <c r="B1060" s="5" t="s">
-        <v>2594</v>
+        <v>2595</v>
       </c>
       <c r="C1060" s="6" t="s">
-        <v>2595</v>
+        <v>2596</v>
       </c>
       <c r="D1060" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1060, ""en"", ""hi"")"),"आपकी सवारी सफलतापूर्वक बुक हो गई है!")</f>
@@ -37488,21 +37557,21 @@
     </row>
     <row r="1061">
       <c r="A1061" s="4" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="B1061" s="5" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="C1061" s="6" t="s">
-        <v>2598</v>
+        <v>2599</v>
       </c>
       <c r="D1061" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1061, ""en"", ""hi"")"),"आपकी यात्रा बीच में ही रद्द हो गई है।")</f>
         <v>आपकी यात्रा बीच में ही रद्द हो गई है।</v>
       </c>
       <c r="E1061" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1061, ""en"", ""kn"")"),"ನಿಮ್ಮ ಸವಾರಿಯನ್ನು ಮಧ್ಯದಲ್ಲಿ ರದ್ದುಗೊಳಿಸಲಾಗಿದೆ.")</f>
-        <v>ನಿಮ್ಮ ಸವಾರಿಯನ್ನು ಮಧ್ಯದಲ್ಲಿ ರದ್ದುಗೊಳಿಸಲಾಗಿದೆ.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1061, ""en"", ""kn"")"),"ನಿಮ್ಮ ಸವಾರಿಯನ್ನು ಸವಾರಿಯ ನಡುವೆ ರದ್ದುಗೊಳಿಸಲಾಗಿದೆ.")</f>
+        <v>ನಿಮ್ಮ ಸವಾರಿಯನ್ನು ಸವಾರಿಯ ನಡುವೆ ರದ್ದುಗೊಳಿಸಲಾಗಿದೆ.</v>
       </c>
       <c r="F1061" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1061, ""en"", ""ml"")"),"ഇടയിലുള്ള യാത്രയിൽ നിങ്ങളുടെ യാത്ര റദ്ദാക്കി.")</f>
@@ -37515,13 +37584,13 @@
     </row>
     <row r="1062">
       <c r="A1062" s="4" t="s">
-        <v>2599</v>
+        <v>2600</v>
       </c>
       <c r="B1062" s="5" t="s">
-        <v>2600</v>
+        <v>2601</v>
       </c>
       <c r="C1062" s="6" t="s">
-        <v>2601</v>
+        <v>2602</v>
       </c>
       <c r="D1062" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1062, ""en"", ""hi"")"),"आपकी यात्रा पूरी हो गई है।")</f>
@@ -37542,13 +37611,13 @@
     </row>
     <row r="1063">
       <c r="A1063" s="4" t="s">
-        <v>2602</v>
+        <v>2603</v>
       </c>
       <c r="B1063" s="5" t="s">
-        <v>2603</v>
+        <v>2604</v>
       </c>
       <c r="C1063" s="6" t="s">
-        <v>2604</v>
+        <v>2605</v>
       </c>
       <c r="D1063" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1063, ""en"", ""hi"")"),"आपकी सवारी")</f>
@@ -37569,10 +37638,10 @@
     </row>
     <row r="1064">
       <c r="A1064" s="14" t="s">
-        <v>2605</v>
+        <v>2606</v>
       </c>
       <c r="B1064" s="12" t="s">
-        <v>2606</v>
+        <v>2607</v>
       </c>
       <c r="C1064" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1064, ""en"", ""ta"")"),"ஓட்டுநர் விவரங்கள்")</f>
@@ -37597,10 +37666,10 @@
     </row>
     <row r="1065">
       <c r="A1065" s="14" t="s">
-        <v>2607</v>
+        <v>2608</v>
       </c>
       <c r="B1065" s="12" t="s">
-        <v>2608</v>
+        <v>2609</v>
       </c>
       <c r="C1065" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1065, ""en"", ""ta"")"),"வாகன விவரங்கள்")</f>
@@ -37625,10 +37694,10 @@
     </row>
     <row r="1066">
       <c r="A1066" s="14" t="s">
-        <v>2609</v>
+        <v>2610</v>
       </c>
       <c r="B1066" s="12" t="s">
-        <v>2610</v>
+        <v>2611</v>
       </c>
       <c r="C1066" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1066, ""en"", ""ta"")"),"வங்கி விவரங்கள்")</f>
@@ -37681,10 +37750,10 @@
     </row>
     <row r="1068">
       <c r="A1068" s="14" t="s">
-        <v>2611</v>
+        <v>2612</v>
       </c>
       <c r="B1068" s="18" t="s">
-        <v>2612</v>
+        <v>2613</v>
       </c>
       <c r="C1068" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1068, ""en"", ""ta"")"),"ஆவண மையம்")</f>
@@ -37709,10 +37778,10 @@
     </row>
     <row r="1069">
       <c r="A1069" s="11" t="s">
-        <v>2613</v>
+        <v>2614</v>
       </c>
       <c r="B1069" s="19" t="s">
-        <v>2614</v>
+        <v>2615</v>
       </c>
       <c r="C1069" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1069, ""en"", ""ta"")"),"இந்தப் படிகளை முடிக்கவும், இதன் மூலம் நீங்கள் சவாரிகளை ஏற்றுக்கொள்ளத் தொடங்கலாம்.")</f>
@@ -37737,10 +37806,10 @@
     </row>
     <row r="1070">
       <c r="A1070" s="11" t="s">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="B1070" s="19" t="s">
-        <v>2616</v>
+        <v>2617</v>
       </c>
       <c r="C1070" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1070, ""en"", ""ta"")"),"தயவுசெய்து செல்லுபடியாகும் தொலைபேசி எண்ணை உள்ளிடவும்.")</f>
@@ -37765,10 +37834,10 @@
     </row>
     <row r="1071">
       <c r="A1071" s="11" t="s">
-        <v>2617</v>
+        <v>2618</v>
       </c>
       <c r="B1071" s="19" t="s">
-        <v>2618</v>
+        <v>2619</v>
       </c>
       <c r="C1071" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1071, ""en"", ""ta"")"),"உரிம எண் கண்டறியப்பட்டு தானாகவே நிரப்பப்பட்டது.")</f>
@@ -37793,10 +37862,10 @@
     </row>
     <row r="1072">
       <c r="A1072" s="11" t="s">
-        <v>2619</v>
+        <v>2620</v>
       </c>
       <c r="B1072" s="19" t="s">
-        <v>2620</v>
+        <v>2621</v>
       </c>
       <c r="C1072" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1072, ""en"", ""ta"")"),"பிறந்த தேதி கண்டறியப்பட்டு தானாகவே நிரப்பப்படும்.")</f>
@@ -37821,10 +37890,10 @@
     </row>
     <row r="1073">
       <c r="A1073" s="11" t="s">
-        <v>2621</v>
+        <v>2622</v>
       </c>
       <c r="B1073" s="12" t="s">
-        <v>2622</v>
+        <v>2623</v>
       </c>
       <c r="C1073" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1073, ""en"", ""ta"")"),"உரிம விவரங்களைக் கண்டறிய முடியவில்லை. புலங்களை கைமுறையாகப் புதுப்பிக்கவும்.")</f>
@@ -37849,10 +37918,10 @@
     </row>
     <row r="1074">
       <c r="A1074" s="11" t="s">
-        <v>2623</v>
+        <v>2624</v>
       </c>
       <c r="B1074" s="12" t="s">
-        <v>2624</v>
+        <v>2625</v>
       </c>
       <c r="C1074" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1074, ""en"", ""ta"")"),"பிறந்த தேதியை உள்ளிடவும்.")</f>
@@ -37877,10 +37946,10 @@
     </row>
     <row r="1075">
       <c r="A1075" s="11" t="s">
-        <v>2625</v>
+        <v>2626</v>
       </c>
       <c r="B1075" s="12" t="s">
-        <v>2626</v>
+        <v>2627</v>
       </c>
       <c r="C1075" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1075, ""en"", ""ta"")"),"தொடர்வதற்கு முன் ஓட்டுநர் புகைப்படத்தைப் பதிவேற்றவும்.")</f>
@@ -37905,10 +37974,10 @@
     </row>
     <row r="1076">
       <c r="A1076" s="11" t="s">
-        <v>2627</v>
+        <v>2628</v>
       </c>
       <c r="B1076" s="12" t="s">
-        <v>2628</v>
+        <v>2629</v>
       </c>
       <c r="C1076" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1076, ""en"", ""ta"")"),"தொடர்வதற்கு முன் ஓட்டுநர் உரிமத்தைப் பதிவேற்றவும்.")</f>
@@ -37933,10 +38002,10 @@
     </row>
     <row r="1077">
       <c r="A1077" s="11" t="s">
-        <v>2629</v>
+        <v>2630</v>
       </c>
       <c r="B1077" s="12" t="s">
-        <v>2630</v>
+        <v>2631</v>
       </c>
       <c r="C1077" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1077, ""en"", ""ta"")"),"ஓட்டுநரின் தெளிவான சமீபத்திய புகைப்படத்தைப் பதிவேற்றவும் அல்லது பிடிக்கவும்.")</f>
@@ -37961,10 +38030,10 @@
     </row>
     <row r="1078">
       <c r="A1078" s="11" t="s">
-        <v>2631</v>
+        <v>2632</v>
       </c>
       <c r="B1078" s="12" t="s">
-        <v>2632</v>
+        <v>2633</v>
       </c>
       <c r="C1078" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1078, ""en"", ""ta"")"),"இந்த பயன்முறையில் திருத்துதல் முடக்கப்பட்டுள்ளது.")</f>
@@ -37989,10 +38058,10 @@
     </row>
     <row r="1079">
       <c r="A1079" s="11" t="s">
-        <v>2633</v>
+        <v>2634</v>
       </c>
       <c r="B1079" s="12" t="s">
-        <v>2634</v>
+        <v>2635</v>
       </c>
       <c r="C1079" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1079, ""en"", ""ta"")"),"சொல்ல வேண்டாம்னு ஆசைப்படுறேன்.")</f>
@@ -38017,10 +38086,10 @@
     </row>
     <row r="1080">
       <c r="A1080" s="20" t="s">
-        <v>2635</v>
+        <v>2636</v>
       </c>
       <c r="B1080" s="21" t="s">
-        <v>2636</v>
+        <v>2637</v>
       </c>
       <c r="C1080" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1080, ""en"", ""ta"")"),"வாகன ஆர்.சி.")</f>
@@ -38045,10 +38114,10 @@
     </row>
     <row r="1081">
       <c r="A1081" s="20" t="s">
-        <v>2637</v>
+        <v>2638</v>
       </c>
       <c r="B1081" s="15" t="s">
-        <v>2638</v>
+        <v>2639</v>
       </c>
       <c r="C1081" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1081, ""en"", ""ta"")"),"பதிவு எண்ணை தானாகவே கண்டறிய வாகன RC-ஐ பதிவேற்றவும் அல்லது பிடிக்கவும்.")</f>
@@ -38073,10 +38142,10 @@
     </row>
     <row r="1082">
       <c r="A1082" s="20" t="s">
-        <v>2639</v>
+        <v>2640</v>
       </c>
       <c r="B1082" s="15" t="s">
-        <v>2640</v>
+        <v>2641</v>
       </c>
       <c r="C1082" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1082, ""en"", ""ta"")"),"வாகன RC-ஐ பதிவேற்றவும் அல்லது பிடிக்கவும்")</f>
@@ -38101,10 +38170,10 @@
     </row>
     <row r="1083">
       <c r="A1083" s="20" t="s">
-        <v>2641</v>
+        <v>2642</v>
       </c>
       <c r="B1083" s="15" t="s">
-        <v>2642</v>
+        <v>2643</v>
       </c>
       <c r="C1083" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1083, ""en"", ""ta"")"),"ஆதார் அட்டை")</f>
@@ -38129,10 +38198,10 @@
     </row>
     <row r="1084">
       <c r="A1084" s="20" t="s">
-        <v>2643</v>
+        <v>2644</v>
       </c>
       <c r="B1084" s="15" t="s">
-        <v>2644</v>
+        <v>2645</v>
       </c>
       <c r="C1084" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1084, ""en"", ""ta"")"),"விவரங்கள் தானாகவே கண்டறியப்பட்டன. சமர்ப்பிக்கும் முன் மதிப்பாய்வு செய்யவும்.")</f>
@@ -38157,10 +38226,10 @@
     </row>
     <row r="1085">
       <c r="A1085" s="22" t="s">
-        <v>2645</v>
+        <v>2646</v>
       </c>
       <c r="B1085" s="15" t="s">
-        <v>2646</v>
+        <v>2647</v>
       </c>
       <c r="C1085" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1085, ""en"", ""ta"")"),"ஆதார் எண்ணைப் பிரித்தெடுக்க முடியவில்லை. புலத்தை கைமுறையாகப் புதுப்பிக்கவும்.")</f>
@@ -38185,10 +38254,10 @@
     </row>
     <row r="1086">
       <c r="A1086" s="20" t="s">
-        <v>2647</v>
+        <v>2648</v>
       </c>
       <c r="B1086" s="15" t="s">
-        <v>2648</v>
+        <v>2649</v>
       </c>
       <c r="C1086" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1086, ""en"", ""ta"")"),"ஆவணத்தைப் பதிவேற்றுகிறது. காத்திருக்கவும்…")</f>
@@ -38213,10 +38282,10 @@
     </row>
     <row r="1087">
       <c r="A1087" s="20" t="s">
-        <v>2649</v>
+        <v>2650</v>
       </c>
       <c r="B1087" s="15" t="s">
-        <v>2650</v>
+        <v>2651</v>
       </c>
       <c r="C1087" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1087, ""en"", ""ta"")"),"ஆவணம் தயாராக உள்ளது. அனுப்ப பதிவேற்று என்பதைத் தட்டவும்.")</f>
@@ -38241,10 +38310,10 @@
     </row>
     <row r="1088">
       <c r="A1088" s="20" t="s">
-        <v>2651</v>
+        <v>2652</v>
       </c>
       <c r="B1088" s="15" t="s">
-        <v>2652</v>
+        <v>2653</v>
       </c>
       <c r="C1088" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1088, ""en"", ""ta"")"),"ஆதார் அல்லது பான் எண்ணைப் புதுப்பிக்கவும். குறைந்தது ஒரு செல்லுபடியாகும் ஆவணத்தையாவது வழங்கவும்.")</f>
@@ -38269,10 +38338,10 @@
     </row>
     <row r="1089">
       <c r="A1089" s="20" t="s">
-        <v>2653</v>
+        <v>2654</v>
       </c>
       <c r="B1089" s="15" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="C1089" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1089, ""en"", ""ta"")"),"பாலினத்தைத் தேர்ந்தெடுக்கவும்.")</f>
@@ -38296,88 +38365,340 @@
       </c>
     </row>
     <row r="1090">
-      <c r="A1090" s="8"/>
-      <c r="B1090" s="6"/>
-      <c r="C1090" s="6"/>
-      <c r="D1090" s="6"/>
-      <c r="E1090" s="6"/>
+      <c r="A1090" s="20" t="s">
+        <v>2656</v>
+      </c>
+      <c r="B1090" s="15" t="s">
+        <v>2657</v>
+      </c>
+      <c r="C1090" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1090, ""en"", ""ta"")"),"இயக்கி புகைப்படத்தைப் பதிவேற்றவும் அல்லது பிடிக்கவும்")</f>
+        <v>இயக்கி புகைப்படத்தைப் பதிவேற்றவும் அல்லது பிடிக்கவும்</v>
+      </c>
+      <c r="D1090" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1090, ""en"", ""hi"")"),"ड्राइवर की फोटो अपलोड करें या कैप्चर करें")</f>
+        <v>ड्राइवर की फोटो अपलोड करें या कैप्चर करें</v>
+      </c>
+      <c r="E1090" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1090, ""en"", ""kn"")"),"ಚಾಲಕ ಫೋಟೋ ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ")</f>
+        <v>ಚಾಲಕ ಫೋಟೋ ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ</v>
+      </c>
+      <c r="F1090" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1090, ""en"", ""ml"")"),"ഡ്രൈവർ ഫോട്ടോ അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ പകർത്തുക")</f>
+        <v>ഡ്രൈവർ ഫോട്ടോ അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ പകർത്തുക</v>
+      </c>
+      <c r="G1090" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1090, ""en"", ""te"")"),"డ్రైవర్ ఫోటోను అప్‌లోడ్ చేయండి లేదా క్యాప్చర్ చేయండి")</f>
+        <v>డ్రైవర్ ఫోటోను అప్‌లోడ్ చేయండి లేదా క్యాప్చర్ చేయండి</v>
+      </c>
     </row>
     <row r="1091">
-      <c r="A1091" s="8"/>
-      <c r="B1091" s="6"/>
-      <c r="C1091" s="6"/>
-      <c r="D1091" s="6"/>
-      <c r="E1091" s="6"/>
+      <c r="A1091" s="20" t="s">
+        <v>2658</v>
+      </c>
+      <c r="B1091" s="15" t="s">
+        <v>2659</v>
+      </c>
+      <c r="C1091" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1091, ""en"", ""ta"")"),"ஓட்டுநர் உரிமத்தைப் பதிவேற்றவும் அல்லது பிடிக்கவும்")</f>
+        <v>ஓட்டுநர் உரிமத்தைப் பதிவேற்றவும் அல்லது பிடிக்கவும்</v>
+      </c>
+      <c r="D1091" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1091, ""en"", ""hi"")"),"ड्राइविंग लाइसेंस अपलोड करें या उसका स्क्रीनशॉट लें")</f>
+        <v>ड्राइविंग लाइसेंस अपलोड करें या उसका स्क्रीनशॉट लें</v>
+      </c>
+      <c r="E1091" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1091, ""en"", ""kn"")"),"ಚಾಲನಾ ಪರವಾನಗಿಯನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ")</f>
+        <v>ಚಾಲನಾ ಪರವಾನಗಿಯನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ</v>
+      </c>
+      <c r="F1091" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1091, ""en"", ""ml"")"),"ഡ്രൈവിംഗ് ലൈസൻസ് അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ പിടിച്ചെടുക്കുക")</f>
+        <v>ഡ്രൈവിംഗ് ലൈസൻസ് അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ പിടിച്ചെടുക്കുക</v>
+      </c>
+      <c r="G1091" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1091, ""en"", ""te"")"),"డ్రైవింగ్ లైసెన్స్‌ను అప్‌లోడ్ చేయండి లేదా సంగ్రహించండి")</f>
+        <v>డ్రైవింగ్ లైసెన్స్‌ను అప్‌లోడ్ చేయండి లేదా సంగ్రహించండి</v>
+      </c>
     </row>
     <row r="1092">
-      <c r="A1092" s="4"/>
-      <c r="B1092" s="5"/>
-      <c r="C1092" s="6"/>
-      <c r="D1092" s="6"/>
-      <c r="E1092" s="6"/>
+      <c r="A1092" s="11" t="s">
+        <v>2660</v>
+      </c>
+      <c r="B1092" s="12" t="s">
+        <v>2661</v>
+      </c>
+      <c r="C1092" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1092, ""en"", ""ta"")"),"ஆதார் அட்டையைப் பதிவேற்றவும் அல்லது பிடிக்கவும்")</f>
+        <v>ஆதார் அட்டையைப் பதிவேற்றவும் அல்லது பிடிக்கவும்</v>
+      </c>
+      <c r="D1092" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1092, ""en"", ""hi"")"),"आधार कार्ड अपलोड करें या कैप्चर करें")</f>
+        <v>आधार कार्ड अपलोड करें या कैप्चर करें</v>
+      </c>
+      <c r="E1092" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1092, ""en"", ""kn"")"),"ಆಧಾರ್ ಕಾರ್ಡ್ ಅನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ")</f>
+        <v>ಆಧಾರ್ ಕಾರ್ಡ್ ಅನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ</v>
+      </c>
+      <c r="F1092" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1092, ""en"", ""ml"")"),"ആധാർ കാർഡ് അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ എടുക്കുക")</f>
+        <v>ആധാർ കാർഡ് അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ എടുക്കുക</v>
+      </c>
+      <c r="G1092" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1092, ""en"", ""te"")"),"ఆధార్ కార్డును అప్‌లోడ్ చేయండి లేదా సంగ్రహించండి")</f>
+        <v>ఆధార్ కార్డును అప్‌లోడ్ చేయండి లేదా సంగ్రహించండి</v>
+      </c>
     </row>
     <row r="1093">
-      <c r="A1093" s="10"/>
-      <c r="B1093" s="5"/>
-      <c r="C1093" s="6"/>
-      <c r="D1093" s="6"/>
-      <c r="E1093" s="6"/>
+      <c r="A1093" s="22" t="s">
+        <v>2662</v>
+      </c>
+      <c r="B1093" s="12" t="s">
+        <v>2663</v>
+      </c>
+      <c r="C1093" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1093, ""en"", ""ta"")"),"PAN கார்டைப் பதிவேற்றவும் அல்லது எடுக்கவும்")</f>
+        <v>PAN கார்டைப் பதிவேற்றவும் அல்லது எடுக்கவும்</v>
+      </c>
+      <c r="D1093" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1093, ""en"", ""hi"")"),"पैन कार्ड अपलोड करें या कैप्चर करें")</f>
+        <v>पैन कार्ड अपलोड करें या कैप्चर करें</v>
+      </c>
+      <c r="E1093" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1093, ""en"", ""kn"")"),"PAN ಕಾರ್ಡ್ ಅನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ")</f>
+        <v>PAN ಕಾರ್ಡ್ ಅನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ</v>
+      </c>
+      <c r="F1093" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1093, ""en"", ""ml"")"),"പാൻ കാർഡ് അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ ക്യാപ്‌ചർ ചെയ്യുക")</f>
+        <v>പാൻ കാർഡ് അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ ക്യാപ്‌ചർ ചെയ്യുക</v>
+      </c>
+      <c r="G1093" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1093, ""en"", ""te"")"),"PAN కార్డ్‌ను అప్‌లోడ్ చేయండి లేదా క్యాప్చర్ చేయండి")</f>
+        <v>PAN కార్డ్‌ను అప్‌లోడ్ చేయండి లేదా క్యాప్చర్ చేయండి</v>
+      </c>
     </row>
     <row r="1094">
-      <c r="A1094" s="10"/>
-      <c r="B1094" s="5"/>
-      <c r="C1094" s="6"/>
-      <c r="D1094" s="6"/>
-      <c r="E1094" s="6"/>
+      <c r="A1094" s="22" t="s">
+        <v>2664</v>
+      </c>
+      <c r="B1094" s="12" t="s">
+        <v>2665</v>
+      </c>
+      <c r="C1094" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1094, ""en"", ""ta"")"),"ஆதார் ஆவணத்தைப் பதிவேற்றவும்")</f>
+        <v>ஆதார் ஆவணத்தைப் பதிவேற்றவும்</v>
+      </c>
+      <c r="D1094" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1094, ""en"", ""hi"")"),"आधार दस्तावेज़ अपलोड करें")</f>
+        <v>आधार दस्तावेज़ अपलोड करें</v>
+      </c>
+      <c r="E1094" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1094, ""en"", ""kn"")"),"ಆಧಾರ್ ದಾಖಲೆಯನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ")</f>
+        <v>ಆಧಾರ್ ದಾಖಲೆಯನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ</v>
+      </c>
+      <c r="F1094" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1094, ""en"", ""ml"")"),"ആധാർ രേഖ അപ്‌ലോഡ് ചെയ്യുക")</f>
+        <v>ആധാർ രേഖ അപ്‌ലോഡ് ചെയ്യുക</v>
+      </c>
+      <c r="G1094" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1094, ""en"", ""te"")"),"ఆధార్ పత్రాన్ని అప్‌లోడ్ చేయండి")</f>
+        <v>ఆధార్ పత్రాన్ని అప్‌లోడ్ చేయండి</v>
+      </c>
     </row>
     <row r="1095">
-      <c r="A1095" s="10"/>
-      <c r="B1095" s="5"/>
-      <c r="C1095" s="6"/>
-      <c r="D1095" s="6"/>
-      <c r="E1095" s="6"/>
+      <c r="A1095" s="22" t="s">
+        <v>2666</v>
+      </c>
+      <c r="B1095" s="12" t="s">
+        <v>2667</v>
+      </c>
+      <c r="C1095" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1095, ""en"", ""ta"")"),"PAN ஆவணத்தைப் பதிவேற்றவும்")</f>
+        <v>PAN ஆவணத்தைப் பதிவேற்றவும்</v>
+      </c>
+      <c r="D1095" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1095, ""en"", ""hi"")"),"पैन दस्तावेज़ अपलोड करें")</f>
+        <v>पैन दस्तावेज़ अपलोड करें</v>
+      </c>
+      <c r="E1095" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1095, ""en"", ""kn"")"),"ಪ್ಯಾನ್ ದಾಖಲೆಯನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ")</f>
+        <v>ಪ್ಯಾನ್ ದಾಖಲೆಯನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ</v>
+      </c>
+      <c r="F1095" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1095, ""en"", ""ml"")"),"പാൻ രേഖ അപ്‌ലോഡ് ചെയ്യുക")</f>
+        <v>പാൻ രേഖ അപ്‌ലോഡ് ചെയ്യുക</v>
+      </c>
+      <c r="G1095" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1095, ""en"", ""te"")"),"పాన్ పత్రాన్ని అప్‌లోడ్ చేయండి")</f>
+        <v>పాన్ పత్రాన్ని అప్‌లోడ్ చేయండి</v>
+      </c>
     </row>
     <row r="1096">
-      <c r="A1096" s="10"/>
-      <c r="B1096" s="5"/>
-      <c r="C1096" s="6"/>
-      <c r="D1096" s="6"/>
-      <c r="E1096" s="6"/>
+      <c r="A1096" s="22" t="s">
+        <v>2668</v>
+      </c>
+      <c r="B1096" s="12" t="s">
+        <v>2669</v>
+      </c>
+      <c r="C1096" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1096, ""en"", ""ta"")"),"இதன் மூலம் பணம் செலுத்துதல்களைச் சரிபார்க்கவும்")</f>
+        <v>இதன் மூலம் பணம் செலுத்துதல்களைச் சரிபார்க்கவும்</v>
+      </c>
+      <c r="D1096" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1096, ""en"", ""hi"")"),"भुगतान की पुष्टि करें")</f>
+        <v>भुगतान की पुष्टि करें</v>
+      </c>
+      <c r="E1096" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1096, ""en"", ""kn"")"),"ಇದರೊಂದಿಗೆ ಪಾವತಿಗಳನ್ನು ಪರಿಶೀಲಿಸಿ")</f>
+        <v>ಇದರೊಂದಿಗೆ ಪಾವತಿಗಳನ್ನು ಪರಿಶೀಲಿಸಿ</v>
+      </c>
+      <c r="F1096" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1096, ""en"", ""ml"")"),"ഇതുപയോഗിച്ച് പേഔട്ടുകൾ പരിശോധിക്കുക")</f>
+        <v>ഇതുപയോഗിച്ച് പേഔട്ടുകൾ പരിശോധിക്കുക</v>
+      </c>
+      <c r="G1096" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1096, ""en"", ""te"")"),"చెల్లింపులను ధృవీకరించండి")</f>
+        <v>చెల్లింపులను ధృవీకరించండి</v>
+      </c>
     </row>
     <row r="1097">
-      <c r="A1097" s="10"/>
-      <c r="B1097" s="5"/>
-      <c r="C1097" s="6"/>
-      <c r="D1097" s="6"/>
-      <c r="E1097" s="6"/>
+      <c r="A1097" s="22" t="s">
+        <v>2670</v>
+      </c>
+      <c r="B1097" s="12" t="s">
+        <v>2671</v>
+      </c>
+      <c r="C1097" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1097, ""en"", ""ta"")"),"UPI ஐடியைச் சரிபார்க்கவும்")</f>
+        <v>UPI ஐடியைச் சரிபார்க்கவும்</v>
+      </c>
+      <c r="D1097" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1097, ""en"", ""hi"")"),"यूपीआई आईडी सत्यापित करें")</f>
+        <v>यूपीआई आईडी सत्यापित करें</v>
+      </c>
+      <c r="E1097" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1097, ""en"", ""kn"")"),"UPI ಐಡಿ ಪರಿಶೀಲಿಸಿ")</f>
+        <v>UPI ಐಡಿ ಪರಿಶೀಲಿಸಿ</v>
+      </c>
+      <c r="F1097" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1097, ""en"", ""ml"")"),"UPI ഐഡി പരിശോധിച്ചുറപ്പിക്കുക")</f>
+        <v>UPI ഐഡി പരിശോധിച്ചുറപ്പിക്കുക</v>
+      </c>
+      <c r="G1097" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1097, ""en"", ""te"")"),"UPI IDని ధృవీకరించండి")</f>
+        <v>UPI IDని ధృవీకరించండి</v>
+      </c>
     </row>
     <row r="1098">
-      <c r="A1098" s="10"/>
-      <c r="B1098" s="5"/>
-      <c r="C1098" s="6"/>
-      <c r="D1098" s="6"/>
-      <c r="E1098" s="6"/>
+      <c r="A1098" s="22" t="s">
+        <v>2672</v>
+      </c>
+      <c r="B1098" s="12" t="s">
+        <v>2673</v>
+      </c>
+      <c r="C1098" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1098, ""en"", ""ta"")"),"வங்கிக் கணக்கைச் சரிபார்க்கவும்")</f>
+        <v>வங்கிக் கணக்கைச் சரிபார்க்கவும்</v>
+      </c>
+      <c r="D1098" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1098, ""en"", ""hi"")"),"बैंक खाते का सत्यापन करें")</f>
+        <v>बैंक खाते का सत्यापन करें</v>
+      </c>
+      <c r="E1098" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1098, ""en"", ""kn"")"),"ಬ್ಯಾಂಕ್ ಖಾತೆಯನ್ನು ಪರಿಶೀಲಿಸಿ")</f>
+        <v>ಬ್ಯಾಂಕ್ ಖಾತೆಯನ್ನು ಪರಿಶೀಲಿಸಿ</v>
+      </c>
+      <c r="F1098" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1098, ""en"", ""ml"")"),"ബാങ്ക് അക്കൗണ്ട് പരിശോധിക്കുക")</f>
+        <v>ബാങ്ക് അക്കൗണ്ട് പരിശോധിക്കുക</v>
+      </c>
+      <c r="G1098" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1098, ""en"", ""te"")"),"బ్యాంక్ ఖాతాను ధృవీకరించండి")</f>
+        <v>బ్యాంక్ ఖాతాను ధృవీకరించండి</v>
+      </c>
     </row>
     <row r="1099">
-      <c r="A1099" s="10"/>
-      <c r="B1099" s="5"/>
-      <c r="C1099" s="6"/>
-      <c r="D1099" s="6"/>
-      <c r="E1099" s="6"/>
+      <c r="A1099" s="22" t="s">
+        <v>2674</v>
+      </c>
+      <c r="B1099" s="12" t="s">
+        <v>2675</v>
+      </c>
+      <c r="C1099" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1099, ""en"", ""ta"")"),"உங்கள் வீட்டு முகவரியை உள்ளிடவும்")</f>
+        <v>உங்கள் வீட்டு முகவரியை உள்ளிடவும்</v>
+      </c>
+      <c r="D1099" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1099, ""en"", ""hi"")"),"अपना आवासीय पता दर्ज करें")</f>
+        <v>अपना आवासीय पता दर्ज करें</v>
+      </c>
+      <c r="E1099" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1099, ""en"", ""kn"")"),"ನಿಮ್ಮ ವಸತಿ_ ವಿಳಾಸವನ್ನು ನಮೂದಿಸಿ")</f>
+        <v>ನಿಮ್ಮ ವಸತಿ_ ವಿಳಾಸವನ್ನು ನಮೂದಿಸಿ</v>
+      </c>
+      <c r="F1099" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1099, ""en"", ""ml"")"),"നിങ്ങളുടെ താമസ വിലാസം നൽകുക")</f>
+        <v>നിങ്ങളുടെ താമസ വിലാസം നൽകുക</v>
+      </c>
+      <c r="G1099" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1099, ""en"", ""te"")"),"మీ నివాస_ చిరునామాను నమోదు చేయండి")</f>
+        <v>మీ నివాస_ చిరునామాను నమోదు చేయండి</v>
+      </c>
     </row>
     <row r="1100">
-      <c r="A1100" s="10"/>
-      <c r="B1100" s="5"/>
-      <c r="C1100" s="6"/>
-      <c r="D1100" s="6"/>
-      <c r="E1100" s="6"/>
+      <c r="A1100" s="22" t="s">
+        <v>2676</v>
+      </c>
+      <c r="B1100" s="12" t="s">
+        <v>2677</v>
+      </c>
+      <c r="C1100" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1100, ""en"", ""ta"")"),"கணக்கு விவரங்களைத் தானாகக் கண்டறிய முதல் பக்கத்தைப் பதிவேற்றவும் அல்லது பிடிக்கவும்.")</f>
+        <v>கணக்கு விவரங்களைத் தானாகக் கண்டறிய முதல் பக்கத்தைப் பதிவேற்றவும் அல்லது பிடிக்கவும்.</v>
+      </c>
+      <c r="D1100" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1100, ""en"", ""hi"")"),"खाता विवरण स्वतः पता लगाने के लिए मुख्य पृष्ठ को अपलोड करें या उसका स्क्रीनशॉट लें।")</f>
+        <v>खाता विवरण स्वतः पता लगाने के लिए मुख्य पृष्ठ को अपलोड करें या उसका स्क्रीनशॉट लें।</v>
+      </c>
+      <c r="E1100" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1100, ""en"", ""kn"")"),"ಖಾತೆ ವಿವರಗಳನ್ನು ಸ್ವಯಂ ಪತ್ತೆ ಮಾಡಲು ಮುಖಪುಟವನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ.")</f>
+        <v>ಖಾತೆ ವಿವರಗಳನ್ನು ಸ್ವಯಂ ಪತ್ತೆ ಮಾಡಲು ಮುಖಪುಟವನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ.</v>
+      </c>
+      <c r="F1100" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1100, ""en"", ""ml"")"),"അക്കൗണ്ട് വിശദാംശങ്ങൾ സ്വയമേവ കണ്ടെത്തുന്നതിന് മുൻ പേജ് അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ ക്യാപ്‌ചർ ചെയ്യുക.")</f>
+        <v>അക്കൗണ്ട് വിശദാംശങ്ങൾ സ്വയമേവ കണ്ടെത്തുന്നതിന് മുൻ പേജ് അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ ക്യാപ്‌ചർ ചെയ്യുക.</v>
+      </c>
+      <c r="G1100" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1100, ""en"", ""te"")"),"ఖాతా వివరాలను స్వయంచాలకంగా గుర్తించడానికి మొదటి పేజీని అప్‌లోడ్ చేయండి లేదా సంగ్రహించండి.")</f>
+        <v>ఖాతా వివరాలను స్వయంచాలకంగా గుర్తించడానికి మొదటి పేజీని అప్‌లోడ్ చేయండి లేదా సంగ్రహించండి.</v>
+      </c>
     </row>
     <row r="1101">
-      <c r="A1101" s="10"/>
-      <c r="B1101" s="5"/>
-      <c r="C1101" s="6"/>
-      <c r="D1101" s="6"/>
-      <c r="E1101" s="6"/>
+      <c r="A1101" s="22" t="s">
+        <v>2632</v>
+      </c>
+      <c r="B1101" s="12" t="s">
+        <v>2633</v>
+      </c>
+      <c r="C1101" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1101, ""en"", ""ta"")"),"இந்த பயன்முறையில் திருத்துதல் முடக்கப்பட்டுள்ளது.")</f>
+        <v>இந்த பயன்முறையில் திருத்துதல் முடக்கப்பட்டுள்ளது.</v>
+      </c>
+      <c r="D1101" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1101, ""en"", ""hi"")"),"इस मोड में संपादन की सुविधा अक्षम है।")</f>
+        <v>इस मोड में संपादन की सुविधा अक्षम है।</v>
+      </c>
+      <c r="E1101" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1101, ""en"", ""kn"")"),"ಈ ಕ್ರಮದಲ್ಲಿ ಸಂಪಾದನೆಯನ್ನು ನಿಷ್ಕ್ರಿಯಗೊಳಿಸಲಾಗಿದೆ.")</f>
+        <v>ಈ ಕ್ರಮದಲ್ಲಿ ಸಂಪಾದನೆಯನ್ನು ನಿಷ್ಕ್ರಿಯಗೊಳಿಸಲಾಗಿದೆ.</v>
+      </c>
+      <c r="F1101" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1101, ""en"", ""ml"")"),"ഈ മോഡിൽ എഡിറ്റിംഗ് അപ്രാപ്തമാക്കിയിരിക്കുന്നു.")</f>
+        <v>ഈ മോഡിൽ എഡിറ്റിംഗ് അപ്രാപ്തമാക്കിയിരിക്കുന്നു.</v>
+      </c>
+      <c r="G1101" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1101, ""en"", ""te"")"),"ఈ మోడ్‌లో సవరణ నిలిపివేయబడింది.")</f>
+        <v>ఈ మోడ్‌లో సవరణ నిలిపివేయబడింది.</v>
+      </c>
     </row>
     <row r="1102">
       <c r="A1102" s="10"/>

--- a/PublicCustomerApp/src/python/translation.xlsx
+++ b/PublicCustomerApp/src/python/translation.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2794" uniqueCount="2678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2800" uniqueCount="2684">
   <si>
     <t>key</t>
   </si>
@@ -8052,13 +8052,31 @@
     <t>enter_your_residential_address</t>
   </si>
   <si>
-    <t>Enter Your Residential_ Address</t>
+    <t>Enter Your Residential Address</t>
   </si>
   <si>
     <t>passbook_scan_helper</t>
   </si>
   <si>
     <t>Upload or capture the front page to auto-detect account details.</t>
+  </si>
+  <si>
+    <t>upi_verification</t>
+  </si>
+  <si>
+    <t>UPI  Verification</t>
+  </si>
+  <si>
+    <t>upi_updated_successfully</t>
+  </si>
+  <si>
+    <t>UPI Updated Successfully</t>
+  </si>
+  <si>
+    <t>still_under_review</t>
+  </si>
+  <si>
+    <t>Still under review</t>
   </si>
 </sst>
 </file>
@@ -8201,6 +8219,10 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8532,8 +8554,8 @@
         <v>உங்கள் கட்டணத்தை பேசி, நம்ம ஊரு டாக்ஸி® செயலியுடன் பிக்-அப் இடத்தைப் பகிர்ந்து கொள்ளச் சொல்லுங்கள். அறிவிப்பு மூலம் பிக்-அப் இடத்தைப் பெற்று, பயணத்தைத் தொடங்க அதை ஏற்றுக்கொள்ளுங்கள்.</v>
       </c>
       <c r="D5" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B5, ""en"", ""hi"")"),"किराया तय करें और उनसे Namma Ooru Taxi ® ऐप के ज़रिए पिकअप लोकेशन शेयर करने के लिए कहें। नोटिफिकेशन के ज़रिए पिकअप लोकेशन मिलने पर उसे स्वीकार करके यात्रा शुरू करें।")</f>
-        <v>किराया तय करें और उनसे Namma Ooru Taxi ® ऐप के ज़रिए पिकअप लोकेशन शेयर करने के लिए कहें। नोटिफिकेशन के ज़रिए पिकअप लोकेशन मिलने पर उसे स्वीकार करके यात्रा शुरू करें।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B5, ""en"", ""hi"")"),"किराया तय कर लें और उनसे Namma Ooru Taxi ® ऐप के ज़रिए पिकअप लोकेशन शेयर करने के लिए कहें। नोटिफिकेशन के ज़रिए पिकअप लोकेशन मिलने पर उसे स्वीकार करके यात्रा शुरू करें।")</f>
+        <v>किराया तय कर लें और उनसे Namma Ooru Taxi ® ऐप के ज़रिए पिकअप लोकेशन शेयर करने के लिए कहें। नोटिफिकेशन के ज़रिए पिकअप लोकेशन मिलने पर उसे स्वीकार करके यात्रा शुरू करें।</v>
       </c>
       <c r="E5" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B5, ""en"", ""kn"")"),"ನಿಮ್ಮ ದರವನ್ನು ಮಾತುಕತೆ ಮಾಡಿ ಮತ್ತು ನಮ್ಮ ಊರು ಟ್ಯಾಕ್ಸಿ® ಅಪ್ಲಿಕೇಶನ್‌ನೊಂದಿಗೆ ಪಿಕಪ್ ಸ್ಥಳವನ್ನು ಹಂಚಿಕೊಳ್ಳಲು ಅವರನ್ನು ಕೇಳಿ. ಅಧಿಸೂಚನೆಯ ಮೂಲಕ ಪಿಕಪ್ ಸ್ಥಳವನ್ನು ಸ್ವೀಕರಿಸಿ ಮತ್ತು ಪ್ರಯಾಣವನ್ನು ಪ್ರಾರಂಭಿಸಲು ಅದನ್ನು ಸ್ವೀಕರಿಸಿ.")</f>
@@ -8544,8 +8566,8 @@
         <v>നിങ്ങളുടെ നിരക്ക് ചർച്ച ചെയ്ത് നമ്മ ഊരു ടാക്സി® ആപ്പുമായി പിക്കപ്പ് ലൊക്കേഷൻ പങ്കിടാൻ ആവശ്യപ്പെടുക. അറിയിപ്പ് വഴി പിക്ക്-അപ്പ് ലൊക്കേഷൻ സ്വീകരിച്ച് യാത്ര ആരംഭിക്കുക.</v>
       </c>
       <c r="G5" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B5, ""en"", ""te"")"),"మీ రేటును బేరసారాలు చేసి, నమ్మ ఊరు టాక్సీ® యాప్‌తో పికప్ లొకేషన్‌ను షేర్ చేయమని వారిని అడగండి. నోటిఫికేషన్ ద్వారా పికప్ లొకేషన్‌ను స్వీకరించి, ట్రిప్ ప్రారంభించడానికి దానిని అంగీకరించండి.")</f>
-        <v>మీ రేటును బేరసారాలు చేసి, నమ్మ ఊరు టాక్సీ® యాప్‌తో పికప్ లొకేషన్‌ను షేర్ చేయమని వారిని అడగండి. నోటిఫికేషన్ ద్వారా పికప్ లొకేషన్‌ను స్వీకరించి, ట్రిప్ ప్రారంభించడానికి దానిని అంగీకరించండి.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B5, ""en"", ""te"")"),"మీ రేటును బేరం చేసి, నమ్మ ఊరు టాక్సీ® యాప్‌తో పికప్ లొకేషన్‌ను షేర్ చేయమని వారిని అడగండి. నోటిఫికేషన్ ద్వారా పికప్ లొకేషన్‌ను స్వీకరించి, ట్రిప్ ప్రారంభించడానికి దానిని అంగీకరించండి.")</f>
+        <v>మీ రేటును బేరం చేసి, నమ్మ ఊరు టాక్సీ® యాప్‌తో పికప్ లొకేషన్‌ను షేర్ చేయమని వారిని అడగండి. నోటిఫికేషన్ ద్వారా పికప్ లొకేషన్‌ను స్వీకరించి, ట్రిప్ ప్రారంభించడానికి దానిని అంగీకరించండి.</v>
       </c>
     </row>
     <row r="6">
@@ -8560,8 +8582,8 @@
         <v>பயணத்தை உறுதிசெய்து தொடங்க வாடிக்கையாளரைத் தொடர்பு கொண்டதை உறுதிப்படுத்திக் கொள்ளுங்கள்.</v>
       </c>
       <c r="D6" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B6, ""en"", ""hi"")"),"ग्राहक से संपर्क करके यात्रा की पुष्टि कर लें और यात्रा शुरू करें।")</f>
-        <v>ग्राहक से संपर्क करके यात्रा की पुष्टि कर लें और यात्रा शुरू करें।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B6, ""en"", ""hi"")"),"ग्राहक से संपर्क करके यात्रा की पुष्टि अवश्य कर लें और यात्रा शुरू करें।")</f>
+        <v>ग्राहक से संपर्क करके यात्रा की पुष्टि अवश्य कर लें और यात्रा शुरू करें।</v>
       </c>
       <c r="E6" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B6, ""en"", ""kn"")"),"ಖಚಿತಪಡಿಸಲು ಮತ್ತು ಪ್ರಯಾಣವನ್ನು ಪ್ರಾರಂಭಿಸಲು ನೀವು ಗ್ರಾಹಕರನ್ನು ಸಂಪರ್ಕಿಸಿದ್ದೀರಿ ಎಂದು ಖಚಿತಪಡಿಸಿಕೊಳ್ಳಿ.")</f>
@@ -9144,8 +9166,8 @@
         <v>58</v>
       </c>
       <c r="C27" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B27, ""en"", ""ta"")"),"செல்லுபடியாகும் உரிம எண்ணை (TN01 20110012345) உள்ளிடவும்.")</f>
-        <v>செல்லுபடியாகும் உரிம எண்ணை (TN01 20110012345) உள்ளிடவும்.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B27, ""en"", ""ta"")"),"தயவுசெய்து செல்லுபடியாகும் உரிம எண்ணை உள்ளிடவும் (TN01 20110012345)")</f>
+        <v>தயவுசெய்து செல்லுபடியாகும் உரிம எண்ணை உள்ளிடவும் (TN01 20110012345)</v>
       </c>
       <c r="D27" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B27, ""en"", ""hi"")"),"कृपया वैध लाइसेंस नंबर दर्ज करें (TN01 20110012345)")</f>
@@ -9204,8 +9226,8 @@
         <v>இருப்பிட அனுமதி மறுக்கப்பட்டது</v>
       </c>
       <c r="D29" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B29, ""en"", ""hi"")"),"स्थान की अनुमति अस्वीकृत")</f>
-        <v>स्थान की अनुमति अस्वीकृत</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B29, ""en"", ""hi"")"),"स्थान अनुमति अस्वीकृत")</f>
+        <v>स्थान अनुमति अस्वीकृत</v>
       </c>
       <c r="E29" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B29, ""en"", ""kn"")"),"ಸ್ಥಳ ಅನುಮತಿ ನಿರಾಕರಿಸಲಾಗಿದೆ")</f>
@@ -9362,8 +9384,8 @@
         <v>ಆದ್ಯತೆಯ ಕೆಲಸದ ಸ್ಥಳ</v>
       </c>
       <c r="F34" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B34, ""en"", ""ml"")"),"ഇഷ്ടപ്പെട്ട ജോലിസ്ഥലം")</f>
-        <v>ഇഷ്ടപ്പെട്ട ജോലിസ്ഥലം</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B34, ""en"", ""ml"")"),"ഇഷ്ടപ്പെട്ട ജോലി സ്ഥലം")</f>
+        <v>ഇഷ്ടപ്പെട്ട ജോലി സ്ഥലം</v>
       </c>
       <c r="G34" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B34, ""en"", ""te"")"),"ఇష్టపడే పని స్థానం")</f>
@@ -9670,8 +9692,8 @@
         <v>ದಯವಿಟ್ಟು ವಾಹನ ಮಾದರಿಯನ್ನು ನಮೂದಿಸಿ.</v>
       </c>
       <c r="F45" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B45, ""en"", ""ml"")"),"ദയവായി വാഹന മോഡൽ നൽകുക.")</f>
-        <v>ദയവായി വാഹന മോഡൽ നൽകുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B45, ""en"", ""ml"")"),"വാഹന മോഡൽ നൽകുക.")</f>
+        <v>വാഹന മോഡൽ നൽകുക.</v>
       </c>
       <c r="G45" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B45, ""en"", ""te"")"),"దయచేసి వాహన నమూనాను నమోదు చేయండి.")</f>
@@ -9694,8 +9716,8 @@
         <v>कृपया निर्माण वर्ष दर्ज करें</v>
       </c>
       <c r="E46" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B46, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ತಯಾರಿಕಾ ವರ್ಷವನ್ನು ನಮೂದಿಸಿ")</f>
-        <v>ದಯವಿಟ್ಟು ತಯಾರಿಕಾ ವರ್ಷವನ್ನು ನಮೂದಿಸಿ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B46, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ತಯಾರಿಕಾ ವರ್ಷವನ್ನು ನಮೂದಿಸಿ.")</f>
+        <v>ದಯವಿಟ್ಟು ತಯಾರಿಕಾ ವರ್ಷವನ್ನು ನಮೂದಿಸಿ.</v>
       </c>
       <c r="F46" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B46, ""en"", ""ml"")"),"നിർമ്മാണ വർഷം നൽകുക.")</f>
@@ -13229,9 +13251,9 @@
       </c>
       <c r="F171" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B171, ""en"", ""ml"")"),"ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
-നിങ്ങളുടെ ക്ഷമയ്ക്ക് നന്ദി.")</f>
+ക്ഷമയ്ക്ക് നന്ദി.")</f>
         <v>ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
-നിങ്ങളുടെ ക്ഷമയ്ക്ക് നന്ദി.</v>
+ക്ഷമയ്ക്ക് നന്ദി.</v>
       </c>
       <c r="G171" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B171, ""en"", ""te"")"),"టాక్సీని ధృవీకరించడానికి మరియు వాటిని ఆమోదించడానికి మేము తీవ్రంగా కృషి చేస్తున్నాము. కాబట్టి దయచేసి ఆమోద ప్రక్రియకు కొంత సమయం పడుతుందని అర్థం చేసుకోండి.
@@ -14016,8 +14038,8 @@
         <v>ಆನ್‌ಲೈನ್‌ಗೆ ಹೋಗಿ</v>
       </c>
       <c r="F199" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B199, ""en"", ""ml"")"),"ഓൺലൈനാകുക")</f>
-        <v>ഓൺലൈനാകുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B199, ""en"", ""ml"")"),"ഓൺലൈനിൽ പോകുക")</f>
+        <v>ഓൺലൈനിൽ പോകുക</v>
       </c>
       <c r="G199" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B199, ""en"", ""te"")"),"ఆన్‌లైన్‌లోకి వెళ్లండి")</f>
@@ -14520,8 +14542,8 @@
         <v>ವಿವರಗಳು ವೀಕ್ಷಿಸಿ</v>
       </c>
       <c r="F217" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B217, ""en"", ""ml"")"),"വിശദാംശങ്ങൾ കാണുക")</f>
-        <v>വിശദാംശങ്ങൾ കാണുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B217, ""en"", ""ml"")"),"കാണുക വിശദാംശങ്ങൾ")</f>
+        <v>കാണുക വിശദാംശങ്ങൾ</v>
       </c>
       <c r="G217" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B217, ""en"", ""te"")"),"వివరాలు చూడండి")</f>
@@ -16668,8 +16690,8 @@
         <v>டைமரை நிறுத்து</v>
       </c>
       <c r="D294" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B294, ""en"", ""hi"")"),"टाइमर बंद करें")</f>
-        <v>टाइमर बंद करें</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B294, ""en"", ""hi"")"),"टाइमर रोकें")</f>
+        <v>टाइमर रोकें</v>
       </c>
       <c r="E294" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B294, ""en"", ""kn"")"),"ಟೈಮರ್ ನಿಲ್ಲಿಸಿ")</f>
@@ -17480,8 +17502,8 @@
         <v>மோசமான போக்குவரத்து அல்லது வானிலை</v>
       </c>
       <c r="D323" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B323, ""en"", ""hi"")"),"खराब यातायात या खराब मौसम की स्थिति")</f>
-        <v>खराब यातायात या खराब मौसम की स्थिति</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B323, ""en"", ""hi"")"),"यातायात की खराब स्थिति या मौसम की स्थिति")</f>
+        <v>यातायात की खराब स्थिति या मौसम की स्थिति</v>
       </c>
       <c r="E323" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B323, ""en"", ""kn"")"),"ಕಳಪೆ ಸಂಚಾರ ಅಥವಾ ಹವಾಮಾನ ಪರಿಸ್ಥಿತಿಗಳು")</f>
@@ -17852,8 +17874,8 @@
         <v>ಯಾವುದೇ ಟಿಕೆಟ್‌ಗಳು ಕಂಡುಬಂದಿಲ್ಲ.</v>
       </c>
       <c r="F336" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B336, ""en"", ""ml"")"),"ടിക്കറ്റുകളൊന്നും കണ്ടെത്തിയില്ല.")</f>
-        <v>ടിക്കറ്റുകളൊന്നും കണ്ടെത്തിയില്ല.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B336, ""en"", ""ml"")"),"ടിക്കറ്റുകളൊന്നും കണ്ടെത്തിയില്ല")</f>
+        <v>ടിക്കറ്റുകളൊന്നും കണ്ടെത്തിയില്ല</v>
       </c>
       <c r="G336" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B336, ""en"", ""te"")"),"టిక్కెట్లు దొరకలేదు.")</f>
@@ -17956,8 +17978,8 @@
         <v>உங்கள் சிக்கலை விவரிக்கவும், அதைத் தீர்க்க நாங்கள் உங்களுக்கு உதவுவோம்.</v>
       </c>
       <c r="D340" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B340, ""en"", ""hi"")"),"अपनी समस्या का वर्णन करें, हम उसे हल करने में आपकी सहायता करेंगे।")</f>
-        <v>अपनी समस्या का वर्णन करें, हम उसे हल करने में आपकी सहायता करेंगे।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B340, ""en"", ""hi"")"),"अपनी समस्या का वर्णन करें और हम इसे हल करने में आपकी सहायता करेंगे।")</f>
+        <v>अपनी समस्या का वर्णन करें और हम इसे हल करने में आपकी सहायता करेंगे।</v>
       </c>
       <c r="E340" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B340, ""en"", ""kn"")"),"ನಿಮ್ಮ ಸಮಸ್ಯೆಯನ್ನು ವಿವರಿಸಿ, ಅದನ್ನು ಪರಿಹರಿಸಲು ನಾವು ನಿಮಗೆ ಸಹಾಯ ಮಾಡುತ್ತೇವೆ.")</f>
@@ -18724,8 +18746,8 @@
         <v>ഈ പ്രവർത്തനം പഴയപടിയാക്കാൻ കഴിയില്ല - ഇല്ലാതാക്കിയ ഡാറ്റ വീണ്ടെടുക്കാൻ കഴിയില്ല.</v>
       </c>
       <c r="G367" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B367, ""en"", ""te"")"),"ఈ చర్యను రద్దు చేయడం సాధ్యం కాదు - తొలగించబడిన డేటాను తిరిగి పొందడం సాధ్యం కాదు.")</f>
-        <v>ఈ చర్యను రద్దు చేయడం సాధ్యం కాదు - తొలగించబడిన డేటాను తిరిగి పొందడం సాధ్యం కాదు.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B367, ""en"", ""te"")"),"ఈ చర్యను రద్దు చేయలేము - తొలగించబడిన డేటాను తిరిగి పొందడం సాధ్యం కాదు.")</f>
+        <v>ఈ చర్యను రద్దు చేయలేము - తొలగించబడిన డేటాను తిరిగి పొందడం సాధ్యం కాదు.</v>
       </c>
     </row>
     <row r="368">
@@ -20904,8 +20926,8 @@
         <v>ಸಂಪರ್ಕಿಸಿ</v>
       </c>
       <c r="F445" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B445, ""en"", ""ml"")"),"വാര്ത്താവിനിമയം")</f>
-        <v>വാര്ത്താവിനിമയം</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B445, ""en"", ""ml"")"),"ബന്ധപ്പെടുക")</f>
+        <v>ബന്ധപ്പെടുക</v>
       </c>
       <c r="G445" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B445, ""en"", ""te"")"),"సంప్రదించండి")</f>
@@ -21121,8 +21143,8 @@
         <v>अलग हुए</v>
       </c>
       <c r="E453" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B453, ""en"", ""kn"")"),"ವಿಭಾಗಿಸಲಾಗಿದೆ")</f>
-        <v>ವಿಭಾಗಿಸಲಾಗಿದೆ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B453, ""en"", ""kn"")"),"ಬೇರೆಡೆಗೆ ತಿರುಗಿತು")</f>
+        <v>ಬೇರೆಡೆಗೆ ತಿರುಗಿತು</v>
       </c>
       <c r="F453" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B453, ""en"", ""ml"")"),"വിഘടിച്ചു")</f>
@@ -22100,8 +22122,8 @@
         <v>ഡ്രോപ്പ് ലൊക്കേഷൻ സ്ഥിരീകരിക്കുക</v>
       </c>
       <c r="G489" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B489, ""en"", ""te"")"),"డ్రాప్ లొకేషన్‌ను నిర్ధారించండి")</f>
-        <v>డ్రాప్ లొకేషన్‌ను నిర్ధారించండి</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B489, ""en"", ""te"")"),"డ్రాప్ స్థానాన్ని నిర్ధారించండి")</f>
+        <v>డ్రాప్ స్థానాన్ని నిర్ధారించండి</v>
       </c>
     </row>
     <row r="490">
@@ -22229,8 +22251,8 @@
         <v>ड्राइवर से जल्द ही संपर्क किया जाएगा।</v>
       </c>
       <c r="E494" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B494, ""en"", ""kn"")"),"ಸ್ವಲ್ಪ ಹೊತ್ತಿನಲ್ಲೇ ಚಾಲಕನೊಂದಿಗೆ ಕರೆ ಆರಂಭವಾಯಿತು.")</f>
-        <v>ಸ್ವಲ್ಪ ಹೊತ್ತಿನಲ್ಲೇ ಚಾಲಕನೊಂದಿಗೆ ಕರೆ ಆರಂಭವಾಯಿತು.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B494, ""en"", ""kn"")"),"ಸ್ವಲ್ಪ ಹೊತ್ತಿನಲ್ಲೇ ಚಾಲಕನೊಂದಿಗೆ ಕರೆ ಪ್ರಾರಂಭವಾಯಿತು.")</f>
+        <v>ಸ್ವಲ್ಪ ಹೊತ್ತಿನಲ್ಲೇ ಚಾಲಕನೊಂದಿಗೆ ಕರೆ ಪ್ರಾರಂಭವಾಯಿತು.</v>
       </c>
       <c r="F494" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B494, ""en"", ""ml"")"),"ഡ്രൈവറുമായി ഉടൻ തന്നെ കോൾ ആരംഭിച്ചു.")</f>
@@ -26423,8 +26445,8 @@
         <v>ಸ್ಥಳವನ್ನು ಅಳಿಸಲು ವಿಫಲವಾಗಿದೆ. ದಯವಿಟ್ಟು ಮತ್ತೆ ಪ್ರಯತ್ನಿಸಿ.</v>
       </c>
       <c r="F649" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B649, ""en"", ""ml"")"),"സ്ഥലം ഇല്ലാതാക്കാനായില്ല. വീണ്ടും ശ്രമിക്കുക.")</f>
-        <v>സ്ഥലം ഇല്ലാതാക്കാനായില്ല. വീണ്ടും ശ്രമിക്കുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B649, ""en"", ""ml"")"),"സ്ഥലം ഇല്ലാതാക്കുന്നതിൽ പരാജയപ്പെട്ടു. വീണ്ടും ശ്രമിക്കുക.")</f>
+        <v>സ്ഥലം ഇല്ലാതാക്കുന്നതിൽ പരാജയപ്പെട്ടു. വീണ്ടും ശ്രമിക്കുക.</v>
       </c>
       <c r="G649" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B649, ""en"", ""te"")"),"స్థలాన్ని తొలగించడంలో విఫలమైంది. దయచేసి మళ్ళీ ప్రయత్నించండి.")</f>
@@ -26805,8 +26827,8 @@
         <v>യാത്രാക്കൂലി വളരെ കൂടുതലാണ് (സർജ്)</v>
       </c>
       <c r="G663" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B663, ""en"", ""te"")"),"ఛార్జీ చాలా ఎక్కువగా ఉంది (సర్జ్)")</f>
-        <v>ఛార్జీ చాలా ఎక్కువగా ఉంది (సర్జ్)</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B663, ""en"", ""te"")"),"ఛార్జీ చాలా ఎక్కువగా ఉంది (పెరుగుదల)")</f>
+        <v>ఛార్జీ చాలా ఎక్కువగా ఉంది (పెరుగుదల)</v>
       </c>
     </row>
     <row r="664">
@@ -28715,8 +28737,8 @@
         <v>अमान्य स्टॉप</v>
       </c>
       <c r="E734" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B734, ""en"", ""kn"")"),"ಅಮಾನ್ಯವಾದ ನಿಲ್ದಾಣಗಳು")</f>
-        <v>ಅಮಾನ್ಯವಾದ ನಿಲ್ದಾಣಗಳು</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B734, ""en"", ""kn"")"),"ಅಮಾನ್ಯ ನಿಲ್ದಾಣಗಳು")</f>
+        <v>ಅಮಾನ್ಯ ನಿಲ್ದಾಣಗಳು</v>
       </c>
       <c r="F734" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B734, ""en"", ""ml"")"),"അസാധുവായ സ്റ്റോപ്പുകൾ")</f>
@@ -29178,8 +29200,8 @@
         <v>ನೀವು {ತ್ರಿಜ್ಯ} ಕಿಮೀ ವ್ಯಾಪ್ತಿಯೊಳಗಿನ ಸ್ಥಳವನ್ನು ಆಯ್ಕೆ ಮಾಡಬೇಕು.</v>
       </c>
       <c r="F751" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B751, ""en"", ""ml"")"),"നിങ്ങൾ {radius} കിലോമീറ്റർ ചുറ്റളവിൽ ഒരു സ്ഥലം തിരഞ്ഞെടുക്കണം.")</f>
-        <v>നിങ്ങൾ {radius} കിലോമീറ്റർ ചുറ്റളവിൽ ഒരു സ്ഥലം തിരഞ്ഞെടുക്കണം.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B751, ""en"", ""ml"")"),"{radius} കിലോമീറ്റർ ചുറ്റളവിലുള്ള ഒരു സ്ഥലം നിങ്ങൾ തിരഞ്ഞെടുക്കണം.")</f>
+        <v>{radius} കിലോമീറ്റർ ചുറ്റളവിലുള്ള ഒരു സ്ഥലം നിങ്ങൾ തിരഞ്ഞെടുക്കണം.</v>
       </c>
       <c r="G751" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B751, ""en"", ""te"")"),"మీరు {radius} కిమీ వ్యాసార్థంలోపు స్థానాన్ని ఎంచుకోవాలి.")</f>
@@ -29851,8 +29873,8 @@
         <v>ನೀವು ಆಯ್ಕೆ ಮಾಡಿದ {ವಾಹನ} ಹತ್ತಿರದಲ್ಲಿ ಯಾವುದೇ ಚಾಲಕರಿಲ್ಲ. ಲಭ್ಯವಿರುವ ಚಾಲಕರಿರುವ ಮತ್ತೊಂದು ವಾಹನವನ್ನು ನಾವು ಆರಿಸಿಕೊಂಡಿದ್ದೇವೆ.</v>
       </c>
       <c r="F776" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B776, ""en"", ""ml"")"),"നിങ്ങൾ തിരഞ്ഞെടുത്ത {വാഹനത്തിന്} സമീപത്ത് ഡ്രൈവറുകളില്ല. ലഭ്യമായ ഡ്രൈവറുകളുള്ള മറ്റൊരു വാഹനം ഞങ്ങൾ തിരഞ്ഞെടുത്തു.")</f>
-        <v>നിങ്ങൾ തിരഞ്ഞെടുത്ത {വാഹനത്തിന്} സമീപത്ത് ഡ്രൈവറുകളില്ല. ലഭ്യമായ ഡ്രൈവറുകളുള്ള മറ്റൊരു വാഹനം ഞങ്ങൾ തിരഞ്ഞെടുത്തു.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B776, ""en"", ""ml"")"),"നിങ്ങൾ തിരഞ്ഞെടുത്ത {വാഹനത്തിന്} സമീപത്ത് ഡ്രൈവറില്ല. ലഭ്യമായ ഡ്രൈവറുകളുള്ള മറ്റൊരു വാഹനം ഞങ്ങൾ തിരഞ്ഞെടുത്തു.")</f>
+        <v>നിങ്ങൾ തിരഞ്ഞെടുത്ത {വാഹനത്തിന്} സമീപത്ത് ഡ്രൈവറില്ല. ലഭ്യമായ ഡ്രൈവറുകളുള്ള മറ്റൊരു വാഹനം ഞങ്ങൾ തിരഞ്ഞെടുത്തു.</v>
       </c>
       <c r="G776" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B776, ""en"", ""te"")"),"మీరు ఎంచుకున్న {vehicle} కి సమీపంలో డ్రైవర్లు లేరు. అందుబాటులో ఉన్న డ్రైవర్లతో మేము మరొక వాహనాన్ని ఎంచుకున్నాము.")</f>
@@ -30009,8 +30031,8 @@
         <v>कोई सुरक्षित स्थान नहीं</v>
       </c>
       <c r="E782" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B782, ""en"", ""kn"")"),"ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ.")</f>
-        <v>ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B782, ""en"", ""kn"")"),"ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ")</f>
+        <v>ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ</v>
       </c>
       <c r="F782" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B782, ""en"", ""ml"")"),"സംരക്ഷിച്ച സ്ഥലങ്ങളൊന്നുമില്ല.")</f>
@@ -30059,8 +30081,8 @@
         <v>1829</v>
       </c>
       <c r="D784" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B784, ""en"", ""hi"")"),"इस समय आस-पास कोई नाइट ड्राइवर उपलब्ध नहीं है। आप चाहें तो सभी ड्राइवरों को खोज सकते हैं।")</f>
-        <v>इस समय आस-पास कोई नाइट ड्राइवर उपलब्ध नहीं है। आप चाहें तो सभी ड्राइवरों को खोज सकते हैं।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B784, ""en"", ""hi"")"),"फिलहाल आस-पास कोई नाइट ड्राइवर उपलब्ध नहीं है। आप चाहें तो सभी ड्राइवरों को खोज सकते हैं।")</f>
+        <v>फिलहाल आस-पास कोई नाइट ड्राइवर उपलब्ध नहीं है। आप चाहें तो सभी ड्राइवरों को खोज सकते हैं।</v>
       </c>
       <c r="E784" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B784, ""en"", ""kn"")"),"ಈಗ ಹತ್ತಿರದಲ್ಲಿ ಯಾವುದೇ ರಾತ್ರಿ ಚಾಲಕರು ಇಲ್ಲ. ಬದಲಿಗೆ ನೀವು ಎಲ್ಲಾ ಚಾಲಕರನ್ನು ಹುಡುಕಬಹುದು.")</f>
@@ -31474,8 +31496,8 @@
         <v>ದಯವಿಟ್ಟು ಬೆಂಬಲವನ್ನು ಸಂಪರ್ಕಿಸಿ</v>
       </c>
       <c r="F836" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B836, ""en"", ""ml"")"),"പിന്തുണയുമായി ബന്ധപ്പെടുക")</f>
-        <v>പിന്തുണയുമായി ബന്ധപ്പെടുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B836, ""en"", ""ml"")"),"പിന്തുണയുമായി ബന്ധപ്പെടുക.")</f>
+        <v>പിന്തുണയുമായി ബന്ധപ്പെടുക.</v>
       </c>
       <c r="G836" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B836, ""en"", ""te"")"),"దయచేసి మద్దతును సంప్రదించండి")</f>
@@ -32826,8 +32848,8 @@
         <v>ಸವಾರಿಯನ್ನು ಮಧ್ಯದಲ್ಲಿ ರದ್ದುಗೊಳಿಸಲಾಗಿದೆ.</v>
       </c>
       <c r="F886" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B886, ""en"", ""ml"")"),"യാത്ര പകുതി വഴിയിൽ വെച്ച് റദ്ദാക്കി.")</f>
-        <v>യാത്ര പകുതി വഴിയിൽ വെച്ച് റദ്ദാക്കി.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B886, ""en"", ""ml"")"),"യാത്ര പകുതി വഴിയിൽ റദ്ദാക്കി.")</f>
+        <v>യാത്ര പകുതി വഴിയിൽ റദ്ദാക്കി.</v>
       </c>
       <c r="G886" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B886, ""en"", ""te"")"),"రైడ్ మధ్యలో రద్దు చేయబడింది")</f>
@@ -33227,8 +33249,8 @@
         <v>आपके सहेजे गए स्थान यहां दिखाई देंगे।</v>
       </c>
       <c r="E901" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B901, ""en"", ""kn"")"),"ನಿಮ್ಮ ಉಳಿಸಿದ ಸ್ಥಳಗಳು ಇಲ್ಲಿ ಗೋಚರಿಸುತ್ತವೆ.")</f>
-        <v>ನಿಮ್ಮ ಉಳಿಸಿದ ಸ್ಥಳಗಳು ಇಲ್ಲಿ ಗೋಚರಿಸುತ್ತವೆ.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B901, ""en"", ""kn"")"),"ನಿಮ್ಮ ಉಳಿಸಿದ ಸ್ಥಳಗಳು ಇಲ್ಲಿ ಕಾಣಿಸಿಕೊಳ್ಳುತ್ತವೆ.")</f>
+        <v>ನಿಮ್ಮ ಉಳಿಸಿದ ಸ್ಥಳಗಳು ಇಲ್ಲಿ ಕಾಣಿಸಿಕೊಳ್ಳುತ್ತವೆ.</v>
       </c>
       <c r="F901" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B901, ""en"", ""ml"")"),"നിങ്ങളുടെ സംരക്ഷിച്ച സ്ഥലങ്ങൾ ഇവിടെ ദൃശ്യമാകും.")</f>
@@ -33285,8 +33307,8 @@
         <v>ವೇಳಾಪಟ್ಟಿ</v>
       </c>
       <c r="F903" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B903, ""en"", ""ml"")"),"പട്ടിക")</f>
-        <v>പട്ടിക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B903, ""en"", ""ml"")"),"ഷെഡ്യൂൾ")</f>
+        <v>ഷെഡ്യൂൾ</v>
       </c>
       <c r="G903" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B903, ""en"", ""te"")"),"షెడ్యూల్")</f>
@@ -34476,8 +34498,8 @@
         <v>ಚಾಲಕ ತಡವಾಗಿ ಬಂದಿರುವುದು</v>
       </c>
       <c r="F947" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B947, ""en"", ""ml"")"),"ഡ്രൈവർ വൈകിയുള്ള വരവ്")</f>
-        <v>ഡ്രൈവർ വൈകിയുള്ള വരവ്</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B947, ""en"", ""ml"")"),"ഡ്രൈവർ വൈകി എത്തൽ")</f>
+        <v>ഡ്രൈവർ വൈകി എത്തൽ</v>
       </c>
       <c r="G947" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B947, ""en"", ""te"")"),"డ్రైవర్ ఆలస్యంగా రావడం")</f>
@@ -34657,8 +34679,8 @@
         <v>2311</v>
       </c>
       <c r="D954" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B954, ""en"", ""hi"")"),"ड्राइवर बुक किए गए वाहन के प्रकार से भिन्न वाहन लेकर आया (उदाहरण के लिए, एसयूवी के बजाय सेडान)।")</f>
-        <v>ड्राइवर बुक किए गए वाहन के प्रकार से भिन्न वाहन लेकर आया (उदाहरण के लिए, एसयूवी के बजाय सेडान)।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B954, ""en"", ""hi"")"),"ड्राइवर बुक किए गए वाहन के बजाय किसी दूसरे प्रकार का वाहन लेकर आया (उदाहरण के लिए, एसयूवी के बजाय सेडान)।")</f>
+        <v>ड्राइवर बुक किए गए वाहन के बजाय किसी दूसरे प्रकार का वाहन लेकर आया (उदाहरण के लिए, एसयूवी के बजाय सेडान)।</v>
       </c>
       <c r="E954" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B954, ""en"", ""kn"")"),"ಚಾಲಕ ಬುಕ್ ಮಾಡಿದ ವಾಹನಕ್ಕಿಂತ ಬೇರೆ ವಾಹನ ಪ್ರಕಾರದೊಂದಿಗೆ ಬಂದಿದ್ದಾನೆ (ಉದಾ. SUV ಬದಲಿಗೆ ಸೆಡಾನ್)")</f>
@@ -35197,8 +35219,8 @@
         <v>2356</v>
       </c>
       <c r="D974" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B974, ""en"", ""hi"")"),"अपनी समस्या का वर्णन करें, हम उसे हल करने में आपकी सहायता करेंगे।")</f>
-        <v>अपनी समस्या का वर्णन करें, हम उसे हल करने में आपकी सहायता करेंगे।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B974, ""en"", ""hi"")"),"अपनी समस्या का वर्णन करें और हम इसे हल करने में आपकी सहायता करेंगे।")</f>
+        <v>अपनी समस्या का वर्णन करें और हम इसे हल करने में आपकी सहायता करेंगे।</v>
       </c>
       <c r="E974" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B974, ""en"", ""kn"")"),"ನಿಮ್ಮ ಸಮಸ್ಯೆಯನ್ನು ವಿವರಿಸಿ, ಅದನ್ನು ಪರಿಹರಿಸಲು ನಾವು ನಿಮಗೆ ಸಹಾಯ ಮಾಡುತ್ತೇವೆ.")</f>
@@ -35962,8 +35984,8 @@
         <v>{vehicleName} ಗರಿಷ್ಠ ದೂರ {maxKm} ಕಿ.ಮೀ. ದಯವಿಟ್ಟು ಬೇರೆ ವಾಹನವನ್ನು ಆಯ್ಕೆಮಾಡಿ ಅಥವಾ {maxKm} ಕಿ.ಮೀ.ಗಿಂತ ಕಡಿಮೆ ಪ್ರಯಾಣವನ್ನು ಯೋಜಿಸಿ.</v>
       </c>
       <c r="F1002" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1002, ""en"", ""ml"")"),"{vehicleName} പരമാവധി ദൂരം {maxKm} കിലോമീറ്ററാണ്. മറ്റൊരു വാഹനം തിരഞ്ഞെടുക്കുകയോ {maxKm} കിലോമീറ്ററിൽ താഴെയുള്ള യാത്ര പ്ലാൻ ചെയ്യുകയോ ചെയ്യുക.")</f>
-        <v>{vehicleName} പരമാവധി ദൂരം {maxKm} കിലോമീറ്ററാണ്. മറ്റൊരു വാഹനം തിരഞ്ഞെടുക്കുകയോ {maxKm} കിലോമീറ്ററിൽ താഴെയുള്ള യാത്ര പ്ലാൻ ചെയ്യുകയോ ചെയ്യുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1002, ""en"", ""ml"")"),"{vehicleName} പരമാവധി ദൂരം {maxKm} കിലോമീറ്ററാണ്. ദയവായി മറ്റൊരു വാഹനം തിരഞ്ഞെടുക്കുകയോ {maxKm} കിലോമീറ്ററിൽ താഴെയുള്ള യാത്ര പ്ലാൻ ചെയ്യുകയോ ചെയ്യുക.")</f>
+        <v>{vehicleName} പരമാവധി ദൂരം {maxKm} കിലോമീറ്ററാണ്. ദയവായി മറ്റൊരു വാഹനം തിരഞ്ഞെടുക്കുകയോ {maxKm} കിലോമീറ്ററിൽ താഴെയുള്ള യാത്ര പ്ലാൻ ചെയ്യുകയോ ചെയ്യുക.</v>
       </c>
       <c r="G1002" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1002, ""en"", ""te"")"),"{vehicleName} గరిష్ట దూరం {maxKm} కి.మీ. దయచేసి వేరే వాహనాన్ని ఎంచుకోండి లేదా {maxKm} కి.మీ కంటే తక్కువ దూరం ప్రయాణించడానికి ప్లాన్ చేయండి.")</f>
@@ -36259,8 +36281,8 @@
         <v>ಬೇರೆ ಹೆಸರು ಅಥವಾ ಸಂಖ್ಯೆಯನ್ನು ಪ್ರಯತ್ನಿಸಿ</v>
       </c>
       <c r="F1013" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1013, ""en"", ""ml"")"),"മറ്റൊരു പേരോ നമ്പറോ പരീക്ഷിക്കൂ")</f>
-        <v>മറ്റൊരു പേരോ നമ്പറോ പരീക്ഷിക്കൂ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1013, ""en"", ""ml"")"),"മറ്റൊരു പേരോ നമ്പറോ പരീക്ഷിച്ചുനോക്കൂ")</f>
+        <v>മറ്റൊരു പേരോ നമ്പറോ പരീക്ഷിച്ചുനോക്കൂ</v>
       </c>
       <c r="G1013" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1013, ""en"", ""te"")"),"వేరే పేరు లేదా నంబర్‌ను ప్రయత్నించండి")</f>
@@ -37796,8 +37818,8 @@
         <v>ಈ ಹಂತಗಳನ್ನು ಪೂರ್ಣಗೊಳಿಸಿ ಇದರಿಂದ ನೀವು ಸವಾರಿಗಳನ್ನು ಸ್ವೀಕರಿಸಲು ಪ್ರಾರಂಭಿಸಬಹುದು.</v>
       </c>
       <c r="F1069" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1069, ""en"", ""ml"")"),"റൈഡുകൾ സ്വീകരിക്കാൻ തുടങ്ങുന്നതിന് ഈ ഘട്ടങ്ങൾ പൂർത്തിയാക്കുക.")</f>
-        <v>റൈഡുകൾ സ്വീകരിക്കാൻ തുടങ്ങുന്നതിന് ഈ ഘട്ടങ്ങൾ പൂർത്തിയാക്കുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1069, ""en"", ""ml"")"),"റൈഡുകൾ സ്വീകരിച്ചു തുടങ്ങാൻ ഈ ഘട്ടങ്ങൾ പൂർത്തിയാക്കുക.")</f>
+        <v>റൈഡുകൾ സ്വീകരിച്ചു തുടങ്ങാൻ ഈ ഘട്ടങ്ങൾ പൂർത്തിയാക്കുക.</v>
       </c>
       <c r="G1069" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1069, ""en"", ""te"")"),"ఈ దశలను పూర్తి చేయండి, తద్వారా మీరు రైడ్‌లను అంగీకరించడం ప్రారంభించవచ్చు.")</f>
@@ -37952,8 +37974,8 @@
         <v>2627</v>
       </c>
       <c r="C1075" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1075, ""en"", ""ta"")"),"தொடர்வதற்கு முன் ஓட்டுநர் புகைப்படத்தைப் பதிவேற்றவும்.")</f>
-        <v>தொடர்வதற்கு முன் ஓட்டுநர் புகைப்படத்தைப் பதிவேற்றவும்.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1075, ""en"", ""ta"")"),"தொடர்வதற்கு முன் இயக்கி புகைப்படத்தைப் பதிவேற்றவும்.")</f>
+        <v>தொடர்வதற்கு முன் இயக்கி புகைப்படத்தைப் பதிவேற்றவும்.</v>
       </c>
       <c r="D1075" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1075, ""en"", ""hi"")"),"आगे बढ़ने से पहले ड्राइवर की फोटो अपलोड करें।")</f>
@@ -38272,8 +38294,8 @@
         <v>ಡಾಕ್ಯುಮೆಂಟ್ ಅಪ್‌ಲೋಡ್ ಮಾಡಲಾಗುತ್ತಿದೆ. ದಯವಿಟ್ಟು ನಿರೀಕ್ಷಿಸಿ…</v>
       </c>
       <c r="F1086" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1086, ""en"", ""ml"")"),"ഡോക്യുമെന്റ് അപ്‌ലോഡ് ചെയ്യുന്നു. ദയവായി കാത്തിരിക്കുക…")</f>
-        <v>ഡോക്യുമെന്റ് അപ്‌ലോഡ് ചെയ്യുന്നു. ദയവായി കാത്തിരിക്കുക…</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1086, ""en"", ""ml"")"),"ഡോക്യുമെന്റ് അപ്‌ലോഡ് ചെയ്യുന്നു. കാത്തിരിക്കൂ...")</f>
+        <v>ഡോക്യുമെന്റ് അപ്‌ലോഡ് ചെയ്യുന്നു. കാത്തിരിക്കൂ...</v>
       </c>
       <c r="G1086" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1086, ""en"", ""te"")"),"పత్రాన్ని అప్‌లోడ్ చేస్తోంది. దయచేసి వేచి ఉండండి…")</f>
@@ -38440,8 +38462,8 @@
         <v>ಆಧಾರ್ ಕಾರ್ಡ್ ಅನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ</v>
       </c>
       <c r="F1092" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1092, ""en"", ""ml"")"),"ആധാർ കാർഡ് അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ എടുക്കുക")</f>
-        <v>ആധാർ കാർഡ് അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ എടുക്കുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1092, ""en"", ""ml"")"),"ആധാർ കാർഡ് അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ പിടിച്ചെടുക്കുക")</f>
+        <v>ആധാർ കാർഡ് അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ പിടിച്ചെടുക്കുക</v>
       </c>
       <c r="G1092" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1092, ""en"", ""te"")"),"ఆధార్ కార్డును అప్‌లోడ్ చేయండి లేదా సంగ్రహించండి")</f>
@@ -38632,16 +38654,16 @@
         <v>अपना आवासीय पता दर्ज करें</v>
       </c>
       <c r="E1099" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1099, ""en"", ""kn"")"),"ನಿಮ್ಮ ವಸತಿ_ ವಿಳಾಸವನ್ನು ನಮೂದಿಸಿ")</f>
-        <v>ನಿಮ್ಮ ವಸತಿ_ ವಿಳಾಸವನ್ನು ನಮೂದಿಸಿ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1099, ""en"", ""kn"")"),"ನಿಮ್ಮ ವಸತಿ ವಿಳಾಸವನ್ನು ನಮೂದಿಸಿ")</f>
+        <v>ನಿಮ್ಮ ವಸತಿ ವಿಳಾಸವನ್ನು ನಮೂದಿಸಿ</v>
       </c>
       <c r="F1099" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1099, ""en"", ""ml"")"),"നിങ്ങളുടെ താമസ വിലാസം നൽകുക")</f>
-        <v>നിങ്ങളുടെ താമസ വിലാസം നൽകുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1099, ""en"", ""ml"")"),"നിങ്ങളുടെ വീട്ടുവിലാസം നൽകുക")</f>
+        <v>നിങ്ങളുടെ വീട്ടുവിലാസം നൽകുക</v>
       </c>
       <c r="G1099" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1099, ""en"", ""te"")"),"మీ నివాస_ చిరునామాను నమోదు చేయండి")</f>
-        <v>మీ నివాస_ చిరునామాను నమోదు చేయండి</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1099, ""en"", ""te"")"),"మీ నివాస చిరునామాను నమోదు చేయండి")</f>
+        <v>మీ నివాస చిరునామాను నమోదు చేయండి</v>
       </c>
     </row>
     <row r="1100">
@@ -38701,25 +38723,88 @@
       </c>
     </row>
     <row r="1102">
-      <c r="A1102" s="10"/>
-      <c r="B1102" s="5"/>
-      <c r="C1102" s="6"/>
-      <c r="D1102" s="6"/>
-      <c r="E1102" s="6"/>
+      <c r="A1102" s="22" t="s">
+        <v>2678</v>
+      </c>
+      <c r="B1102" s="12" t="s">
+        <v>2679</v>
+      </c>
+      <c r="C1102" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1102, ""en"", ""ta"")"),"UPI சரிபார்ப்பு")</f>
+        <v>UPI சரிபார்ப்பு</v>
+      </c>
+      <c r="D1102" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1102, ""en"", ""hi"")"),"यूपीआई सत्यापन")</f>
+        <v>यूपीआई सत्यापन</v>
+      </c>
+      <c r="E1102" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1102, ""en"", ""kn"")"),"UPI ಪರಿಶೀಲನೆ")</f>
+        <v>UPI ಪರಿಶೀಲನೆ</v>
+      </c>
+      <c r="F1102" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1102, ""en"", ""ml"")"),"യുപിഐ പരിശോധന")</f>
+        <v>യുപിഐ പരിശോധന</v>
+      </c>
+      <c r="G1102" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1102, ""en"", ""te"")"),"UPI ధృవీకరణ")</f>
+        <v>UPI ధృవీకరణ</v>
+      </c>
     </row>
     <row r="1103">
-      <c r="A1103" s="10"/>
-      <c r="B1103" s="5"/>
-      <c r="C1103" s="6"/>
-      <c r="D1103" s="6"/>
-      <c r="E1103" s="6"/>
+      <c r="A1103" s="22" t="s">
+        <v>2680</v>
+      </c>
+      <c r="B1103" s="12" t="s">
+        <v>2681</v>
+      </c>
+      <c r="C1103" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1103, ""en"", ""ta"")"),"UPI வெற்றிகரமாகப் புதுப்பிக்கப்பட்டது.")</f>
+        <v>UPI வெற்றிகரமாகப் புதுப்பிக்கப்பட்டது.</v>
+      </c>
+      <c r="D1103" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1103, ""en"", ""hi"")"),"यूपीआई सफलतापूर्वक अपडेट हो गया")</f>
+        <v>यूपीआई सफलतापूर्वक अपडेट हो गया</v>
+      </c>
+      <c r="E1103" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1103, ""en"", ""kn"")"),"UPI ಅನ್ನು ಯಶಸ್ವಿಯಾಗಿ ನವೀಕರಿಸಲಾಗಿದೆ")</f>
+        <v>UPI ಅನ್ನು ಯಶಸ್ವಿಯಾಗಿ ನವೀಕರಿಸಲಾಗಿದೆ</v>
+      </c>
+      <c r="F1103" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1103, ""en"", ""ml"")"),"UPI വിജയകരമായി അപ്‌ഡേറ്റ് ചെയ്തു")</f>
+        <v>UPI വിജയകരമായി അപ്‌ഡേറ്റ് ചെയ്തു</v>
+      </c>
+      <c r="G1103" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1103, ""en"", ""te"")"),"UPI విజయవంతంగా నవీకరించబడింది")</f>
+        <v>UPI విజయవంతంగా నవీకరించబడింది</v>
+      </c>
     </row>
     <row r="1104">
-      <c r="A1104" s="10"/>
-      <c r="B1104" s="5"/>
-      <c r="C1104" s="6"/>
-      <c r="D1104" s="6"/>
-      <c r="E1104" s="6"/>
+      <c r="A1104" s="22" t="s">
+        <v>2682</v>
+      </c>
+      <c r="B1104" s="12" t="s">
+        <v>2683</v>
+      </c>
+      <c r="C1104" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1104, ""en"", ""ta"")"),"இன்னும் மதிப்பாய்வில் உள்ளது")</f>
+        <v>இன்னும் மதிப்பாய்வில் உள்ளது</v>
+      </c>
+      <c r="D1104" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1104, ""en"", ""hi"")"),"अभी भी समीक्षाधीन है")</f>
+        <v>अभी भी समीक्षाधीन है</v>
+      </c>
+      <c r="E1104" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1104, ""en"", ""kn"")"),"ಇನ್ನೂ ಪರಿಶೀಲನೆಯಲ್ಲಿದೆ")</f>
+        <v>ಇನ್ನೂ ಪರಿಶೀಲನೆಯಲ್ಲಿದೆ</v>
+      </c>
+      <c r="F1104" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1104, ""en"", ""ml"")"),"ഇപ്പോഴും അവലോകനത്തിലാണ്")</f>
+        <v>ഇപ്പോഴും അവലോകനത്തിലാണ്</v>
+      </c>
+      <c r="G1104" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1104, ""en"", ""te"")"),"ఇంకా సమీక్షలో ఉంది")</f>
+        <v>ఇంకా సమీక్షలో ఉంది</v>
+      </c>
     </row>
     <row r="1105">
       <c r="A1105" s="4"/>

--- a/PublicCustomerApp/src/python/translation.xlsx
+++ b/PublicCustomerApp/src/python/translation.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2819" uniqueCount="2703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2849" uniqueCount="2730">
   <si>
     <t>key</t>
   </si>
@@ -3593,7 +3593,7 @@
     <t>driver_access_banner_title</t>
   </si>
   <si>
-    <t>Drive With VMtracker</t>
+    <t>Drive With Namma Ooru Taxi</t>
   </si>
   <si>
     <t>VMtracker உடன் ஓட்டுங்கள்</t>
@@ -3602,7 +3602,7 @@
     <t>driver_access_download_driver_app</t>
   </si>
   <si>
-    <t>Download VMtracker Driver App</t>
+    <t>SignUp Namma Ooru Taxi Driver App</t>
   </si>
   <si>
     <t>VMtracker Driver ஆப்பை பதிவிறக்கம் செய்க</t>
@@ -3674,7 +3674,7 @@
     <t>driver_access_steps_signup_desc</t>
   </si>
   <si>
-    <t>Download VM Tracker App and Create your driver profile with basic information.</t>
+    <t>Signup as a Driver App and Create your driver profile with basic information.</t>
   </si>
   <si>
     <t>VM Tracker ஆப்பை பதிவிறக்கம் செய்து அடிப்படை தகவல்களுடன் ஓட்டுநர் சுயவிவரத்தை உருவாக்கவும்.</t>
@@ -8134,13 +8134,94 @@
   </si>
   <si>
     <t>Next due in</t>
+  </si>
+  <si>
+    <t>maximum_wait_time</t>
+  </si>
+  <si>
+    <t>Maximum wait time is {maxwaitingTime} minutes</t>
+  </si>
+  <si>
+    <t>cancel_trip_warning_title</t>
+  </si>
+  <si>
+    <t>cancel_trip_warning_message</t>
+  </si>
+  <si>
+    <t>Are you sure you want to cancel this trip? A cancellation penalty may apply.</t>
+  </si>
+  <si>
+    <t>cancel_anyway</t>
+  </si>
+  <si>
+    <t>Cancel anyway</t>
+  </si>
+  <si>
+    <t>driver_access_ios_alert_title</t>
+  </si>
+  <si>
+    <t>Driver App on iOS</t>
+  </si>
+  <si>
+    <t>driver_access_ios_alert_message</t>
+  </si>
+  <si>
+    <t>The Namma Ooru Taxi Driver App is not available on iOS at the moment. Please use an Android device to access the Driver App</t>
+  </si>
+  <si>
+    <t>Sign_Up_to_Become_a_Driver</t>
+  </si>
+  <si>
+    <t>Sign Up to Become a Driver</t>
+  </si>
+  <si>
+    <t>refer_your_friends</t>
+  </si>
+  <si>
+    <t>Refer Your Friends</t>
+  </si>
+  <si>
+    <t>verify_customer_to_start_trip</t>
+  </si>
+  <si>
+    <t>Verify customer to start trip</t>
+  </si>
+  <si>
+    <t>vehicle_approval</t>
+  </si>
+  <si>
+    <t>Vehicle Approval</t>
+  </si>
+  <si>
+    <t>vehicle_approval_desc</t>
+  </si>
+  <si>
+    <t>vehicle_approval_desc_info</t>
+  </si>
+  <si>
+    <t>vehicle_blocked</t>
+  </si>
+  <si>
+    <t>Your vehicle has been blocked due to some reasons.</t>
+  </si>
+  <si>
+    <t>vehicle_deleted</t>
+  </si>
+  <si>
+    <t>Your vehicle has been deleted.</t>
+  </si>
+  <si>
+    <t>vehicle_approval_info</t>
+  </si>
+  <si>
+    <t>Your vehicle is still under approval.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -8171,6 +8252,11 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="9.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -8198,7 +8284,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -8265,6 +8351,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8639,8 +8728,8 @@
         <v>பயணத்தை உறுதிசெய்து தொடங்க வாடிக்கையாளரைத் தொடர்பு கொண்டதை உறுதிப்படுத்திக் கொள்ளுங்கள்.</v>
       </c>
       <c r="D6" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B6, ""en"", ""hi"")"),"ग्राहक से संपर्क करके यात्रा की पुष्टि अवश्य कर लें और यात्रा शुरू करें।")</f>
-        <v>ग्राहक से संपर्क करके यात्रा की पुष्टि अवश्य कर लें और यात्रा शुरू करें।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B6, ""en"", ""hi"")"),"ग्राहक से संपर्क करके यात्रा की पुष्टि कर लें और यात्रा शुरू करें।")</f>
+        <v>ग्राहक से संपर्क करके यात्रा की पुष्टि कर लें और यात्रा शुरू करें।</v>
       </c>
       <c r="E6" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B6, ""en"", ""kn"")"),"ಖಚಿತಪಡಿಸಲು ಮತ್ತು ಪ್ರಯಾಣವನ್ನು ಪ್ರಾರಂಭಿಸಲು ನೀವು ಗ್ರಾಹಕರನ್ನು ಸಂಪರ್ಕಿಸಿದ್ದೀರಿ ಎಂದು ಖಚಿತಪಡಿಸಿಕೊಳ್ಳಿ.")</f>
@@ -8875,8 +8964,8 @@
         <v>കൂടുതൽ പ്രതിബദ്ധതയ്ക്കുള്ള താക്കോലാണ് റേറ്റിംഗുകൾ. നിങ്ങൾക്ക് നല്ല റേറ്റിംഗ് ലഭിക്കുന്നുണ്ടെന്ന് ഉറപ്പാക്കുക.</v>
       </c>
       <c r="G14" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B14, ""en"", ""te"")"),"మరింత నిబద్ధతకు రేటింగ్‌లు కీలకం. మీరు మంచి రేటింగ్ పొందేలా చూసుకోండి.")</f>
-        <v>మరింత నిబద్ధతకు రేటింగ్‌లు కీలకం. మీరు మంచి రేటింగ్ పొందేలా చూసుకోండి.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B14, ""en"", ""te"")"),"మరింత నిబద్ధతకు రేటింగ్‌లు కీలకం. మీరు మంచి రేటింగ్ పొందారని నిర్ధారించుకోండి.")</f>
+        <v>మరింత నిబద్ధతకు రేటింగ్‌లు కీలకం. మీరు మంచి రేటింగ్ పొందారని నిర్ధారించుకోండి.</v>
       </c>
     </row>
     <row r="15">
@@ -9221,8 +9310,8 @@
         <v>60</v>
       </c>
       <c r="C27" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B27, ""en"", ""ta"")"),"செல்லுபடியாகும் உரிம எண்ணை (TN01 20110012345) உள்ளிடவும்.")</f>
-        <v>செல்லுபடியாகும் உரிம எண்ணை (TN01 20110012345) உள்ளிடவும்.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B27, ""en"", ""ta"")"),"தயவுசெய்து செல்லுபடியாகும் உரிம எண்ணை உள்ளிடவும் (TN01 20110012345)")</f>
+        <v>தயவுசெய்து செல்லுபடியாகும் உரிம எண்ணை உள்ளிடவும் (TN01 20110012345)</v>
       </c>
       <c r="D27" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B27, ""en"", ""hi"")"),"कृपया वैध लाइसेंस नंबर दर्ज करें (TN01 20110012345)")</f>
@@ -10435,8 +10524,8 @@
         <v>146</v>
       </c>
       <c r="C70" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B70, ""en"", ""ta"")"),"நிறத்தைத் தேர்ந்தெடுக்கவும்")</f>
-        <v>நிறத்தைத் தேர்ந்தெடுக்கவும்</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B70, ""en"", ""ta"")"),"வண்ணத்தைத் தேர்ந்தெடுக்கவும்")</f>
+        <v>வண்ணத்தைத் தேர்ந்தெடுக்கவும்</v>
       </c>
       <c r="D70" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B70, ""en"", ""hi"")"),"रंग चुनो")</f>
@@ -13041,8 +13130,8 @@
         <v>रीयल टाइम अपडेट प्राप्त करने के लिए कृपया नोटिफिकेशन की अनुमति चालू करें।</v>
       </c>
       <c r="E162" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B162, ""en"", ""kn"")"),"ನೈಜ ಸಮಯದ ನವೀಕರಣಗಳನ್ನು ಪಡೆಯಲು ಅಧಿಸೂಚನೆ ಅನುಮತಿಯನ್ನು ಸಕ್ರಿಯಗೊಳಿಸಿ.")</f>
-        <v>ನೈಜ ಸಮಯದ ನವೀಕರಣಗಳನ್ನು ಪಡೆಯಲು ಅಧಿಸೂಚನೆ ಅನುಮತಿಯನ್ನು ಸಕ್ರಿಯಗೊಳಿಸಿ.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B162, ""en"", ""kn"")"),"ನೈಜ ಸಮಯದ ನವೀಕರಣಗಳನ್ನು ಪಡೆಯಲು ದಯವಿಟ್ಟು ಅಧಿಸೂಚನೆ ಅನುಮತಿಯನ್ನು ಸಕ್ರಿಯಗೊಳಿಸಿ.")</f>
+        <v>ನೈಜ ಸಮಯದ ನವೀಕರಣಗಳನ್ನು ಪಡೆಯಲು ದಯವಿಟ್ಟು ಅಧಿಸೂಚನೆ ಅನುಮತಿಯನ್ನು ಸಕ್ರಿಯಗೊಳಿಸಿ.</v>
       </c>
       <c r="F162" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B162, ""en"", ""ml"")"),"തത്സമയ അപ്‌ഡേറ്റുകൾ ലഭിക്കാൻ അറിയിപ്പ് അനുമതി പ്രവർത്തനക്ഷമമാക്കുക.")</f>
@@ -14677,8 +14766,8 @@
         <v>स्थिति का चयन करें</v>
       </c>
       <c r="E220" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B220, ""en"", ""kn"")"),"ಸ್ಥಿತಿ ಆಯ್ಕೆಮಾಡಿ")</f>
-        <v>ಸ್ಥಿತಿ ಆಯ್ಕೆಮಾಡಿ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B220, ""en"", ""kn"")"),"ಸ್ಥಿತಿಯನ್ನು ಆಯ್ಕೆಮಾಡಿ")</f>
+        <v>ಸ್ಥಿತಿಯನ್ನು ಆಯ್ಕೆಮಾಡಿ</v>
       </c>
       <c r="F220" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B220, ""en"", ""ml"")"),"സ്റ്റാറ്റസ് തിരഞ്ഞെടുക്കുക")</f>
@@ -16473,8 +16562,8 @@
         <v>ನಿಮ್ಮಲ್ಲಿ ಬಾಕಿ ಮೊತ್ತವಿದ್ದರೆ, ದಯವಿಟ್ಟು ಮುಂಚಿತವಾಗಿ ಎಲ್ಲಾ ಬಾಕಿ ಮೊತ್ತವನ್ನು ಪಾವತಿಸಿ.</v>
       </c>
       <c r="F284" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B284, ""en"", ""ml"")"),"നിങ്ങളുടെ കുടിശ്ശിക തുക ബാക്കിയുണ്ടെങ്കിൽ, ദയവായി എല്ലാ കുടിശ്ശികകളും മുൻകൂട്ടി തീർക്കുക.")</f>
-        <v>നിങ്ങളുടെ കുടിശ്ശിക തുക ബാക്കിയുണ്ടെങ്കിൽ, ദയവായി എല്ലാ കുടിശ്ശികകളും മുൻകൂട്ടി തീർക്കുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B284, ""en"", ""ml"")"),"കുടിശ്ശിക തുക ബാക്കിയുണ്ടെങ്കിൽ ദയവായി എല്ലാ കുടിശ്ശികയും മുൻകൂട്ടി തീർക്കുക.")</f>
+        <v>കുടിശ്ശിക തുക ബാക്കിയുണ്ടെങ്കിൽ ദയവായി എല്ലാ കുടിശ്ശികയും മുൻകൂട്ടി തീർക്കുക.</v>
       </c>
       <c r="G284" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B284, ""en"", ""te"")"),"మీకు ఇంకా బకాయిలు ఉంటే, దయచేసి ముందుగా అన్ని బకాయిలను చెల్లించండి.")</f>
@@ -17928,8 +18017,8 @@
         <v>ಯಾವುದೇ ಟಿಕೆಟ್‌ಗಳು ಕಂಡುಬಂದಿಲ್ಲ.</v>
       </c>
       <c r="F336" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B336, ""en"", ""ml"")"),"ടിക്കറ്റുകളൊന്നും കണ്ടെത്തിയില്ല")</f>
-        <v>ടിക്കറ്റുകളൊന്നും കണ്ടെത്തിയില്ല</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B336, ""en"", ""ml"")"),"ടിക്കറ്റുകളൊന്നും കണ്ടെത്തിയില്ല.")</f>
+        <v>ടിക്കറ്റുകളൊന്നും കണ്ടെത്തിയില്ല.</v>
       </c>
       <c r="G336" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B336, ""en"", ""te"")"),"టిక్కెట్లు దొరకలేదు.")</f>
@@ -18032,8 +18121,8 @@
         <v>உங்கள் சிக்கலை விவரிக்கவும், அதைத் தீர்க்க நாங்கள் உங்களுக்கு உதவுவோம்.</v>
       </c>
       <c r="D340" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B340, ""en"", ""hi"")"),"अपनी समस्या का वर्णन करें, हम उसे हल करने में आपकी सहायता करेंगे।")</f>
-        <v>अपनी समस्या का वर्णन करें, हम उसे हल करने में आपकी सहायता करेंगे।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B340, ""en"", ""hi"")"),"अपनी समस्या का वर्णन करें और हम इसे हल करने में आपकी सहायता करेंगे।")</f>
+        <v>अपनी समस्या का वर्णन करें और हम इसे हल करने में आपकी सहायता करेंगे।</v>
       </c>
       <c r="E340" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B340, ""en"", ""kn"")"),"ನಿಮ್ಮ ಸಮಸ್ಯೆಯನ್ನು ವಿವರಿಸಿ, ಅದನ್ನು ಪರಿಹರಿಸಲು ನಾವು ನಿಮಗೆ ಸಹಾಯ ಮಾಡುತ್ತೇವೆ.")</f>
@@ -18096,8 +18185,8 @@
         <v>ಅಪ್ಲಿಕೇಶನ್ ಸಂಬಂಧಿತ</v>
       </c>
       <c r="F342" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B342, ""en"", ""ml"")"),"ആപ്പ് അനുബന്ധം")</f>
-        <v>ആപ്പ് അനുബന്ധം</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B342, ""en"", ""ml"")"),"അനുബന്ധ ആപ്പ്")</f>
+        <v>അനുബന്ധ ആപ്പ്</v>
       </c>
       <c r="G342" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B342, ""en"", ""te"")"),"సంబంధిత యాప్")</f>
@@ -19064,8 +19153,8 @@
         <v>732</v>
       </c>
       <c r="C377" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B377, ""en"", ""ta"")"),"வாகன ஆர்.சி. ஆவணத்தின் பின்புறம்")</f>
-        <v>வாகன ஆர்.சி. ஆவணத்தின் பின்புறம்</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B377, ""en"", ""ta"")"),"வாகன ஆர்சி ஆவண பின்புறம்")</f>
+        <v>வாகன ஆர்சி ஆவண பின்புறம்</v>
       </c>
       <c r="D377" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B377, ""en"", ""hi"")"),"वाहन आरसी दस्तावेज़ का पिछला भाग")</f>
@@ -19908,8 +19997,8 @@
         <v>பயன்பாடு திறக்கப்படாதபோதும் கூட உங்கள் இருப்பிடத்தைக் கண்காணிக்க NOT க்கு பின்னணி இருப்பிட அனுமதி தேவையில்லை. இது தொடர்ச்சியான கண்காணிப்பை அனுமதிக்கிறது மற்றும் எல்லா நேரங்களிலும் துல்லியமான இருப்பிடத் தரவு சேகரிக்கப்படுவதை உறுதி செய்கிறது.</v>
       </c>
       <c r="D407" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B407, ""en"", ""hi"")"),"NOT ऐप को आपके स्थान को ट्रैक करने के लिए बैकग्राउंड लोकेशन अनुमति की आवश्यकता होती है, भले ही ऐप खुला न हो। इससे निरंतर ट्रैकिंग संभव होती है और यह सुनिश्चित होता है कि हर समय सटीक स्थान डेटा एकत्र किया जाए।")</f>
-        <v>NOT ऐप को आपके स्थान को ट्रैक करने के लिए बैकग्राउंड लोकेशन अनुमति की आवश्यकता होती है, भले ही ऐप खुला न हो। इससे निरंतर ट्रैकिंग संभव होती है और यह सुनिश्चित होता है कि हर समय सटीक स्थान डेटा एकत्र किया जाए।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B407, ""en"", ""hi"")"),"NOT ऐप के बंद होने पर भी आपकी लोकेशन ट्रैक करने के लिए बैकग्राउंड लोकेशन परमिशन की आवश्यकता होती है। इससे लगातार ट्रैकिंग संभव होती है और यह सुनिश्चित होता है कि हर समय सटीक लोकेशन डेटा एकत्र किया जाए।")</f>
+        <v>NOT ऐप के बंद होने पर भी आपकी लोकेशन ट्रैक करने के लिए बैकग्राउंड लोकेशन परमिशन की आवश्यकता होती है। इससे लगातार ट्रैकिंग संभव होती है और यह सुनिश्चित होता है कि हर समय सटीक लोकेशन डेटा एकत्र किया जाए।</v>
       </c>
       <c r="E407" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B407, ""en"", ""kn"")"),"ಅಪ್ಲಿಕೇಶನ್ ತೆರೆದಿಲ್ಲದಿದ್ದರೂ ಸಹ ನಿಮ್ಮ ಸ್ಥಳವನ್ನು ಟ್ರ್ಯಾಕ್ ಮಾಡಲು NOT ಗೆ ಹಿನ್ನೆಲೆ ಸ್ಥಳ ಅನುಮತಿ ಅಗತ್ಯವಿಲ್ಲ. ಇದು ನಿರಂತರ ಟ್ರ್ಯಾಕಿಂಗ್‌ಗೆ ಅವಕಾಶ ನೀಡುತ್ತದೆ ಮತ್ತು ಎಲ್ಲಾ ಸಮಯದಲ್ಲೂ ನಿಖರವಾದ ಸ್ಥಳ ಡೇಟಾವನ್ನು ಸಂಗ್ರಹಿಸಲಾಗಿದೆ ಎಂದು ಖಚಿತಪಡಿಸುತ್ತದೆ.")</f>
@@ -20352,8 +20441,8 @@
         <v>824</v>
       </c>
       <c r="C423" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B423, ""en"", ""ta"")"),"பயன்கள்")</f>
-        <v>பயன்கள்</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B423, ""en"", ""ta"")"),"வாட்ஸ்அப்")</f>
+        <v>வாட்ஸ்அப்</v>
       </c>
       <c r="D423" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B423, ""en"", ""hi"")"),"WhatsApp")</f>
@@ -24159,54 +24248,54 @@
       <c r="A563" s="4" t="s">
         <v>1189</v>
       </c>
-      <c r="B563" s="5" t="s">
+      <c r="B563" s="13" t="s">
         <v>1190</v>
       </c>
       <c r="C563" s="6" t="s">
         <v>1191</v>
       </c>
       <c r="D563" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B563, ""en"", ""hi"")"),"VMtracker के साथ ड्राइव करें")</f>
-        <v>VMtracker के साथ ड्राइव करें</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B563, ""en"", ""hi"")"),"नम्मा ऊरु टैक्सी के साथ ड्राइव करें")</f>
+        <v>नम्मा ऊरु टैक्सी के साथ ड्राइव करें</v>
       </c>
       <c r="E563" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B563, ""en"", ""kn"")"),"VMtracker ನೊಂದಿಗೆ ಡ್ರೈವ್ ಮಾಡಿ")</f>
-        <v>VMtracker ನೊಂದಿಗೆ ಡ್ರೈವ್ ಮಾಡಿ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B563, ""en"", ""kn"")"),"ನಮ್ಮ ಊರು ಟ್ಯಾಕ್ಸಿಯೊಂದಿಗೆ ಚಾಲನೆ ಮಾಡಿ")</f>
+        <v>ನಮ್ಮ ಊರು ಟ್ಯಾಕ್ಸಿಯೊಂದಿಗೆ ಚಾಲನೆ ಮಾಡಿ</v>
       </c>
       <c r="F563" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B563, ""en"", ""ml"")"),"VMtracker ഉപയോഗിച്ച് ഡ്രൈവ് ചെയ്യുക")</f>
-        <v>VMtracker ഉപയോഗിച്ച് ഡ്രൈവ് ചെയ്യുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B563, ""en"", ""ml"")"),"നമ്മ ഊരു ടാക്സിയിൽ യാത്ര ചെയ്യൂ")</f>
+        <v>നമ്മ ഊരു ടാക്സിയിൽ യാത്ര ചെയ്യൂ</v>
       </c>
       <c r="G563" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B563, ""en"", ""te"")"),"VMtracker తో డ్రైవ్ చేయండి")</f>
-        <v>VMtracker తో డ్రైవ్ చేయండి</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B563, ""en"", ""te"")"),"నమ్మ ఊరు టాక్సీతో డ్రైవ్ చేయండి")</f>
+        <v>నమ్మ ఊరు టాక్సీతో డ్రైవ్ చేయండి</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" s="4" t="s">
         <v>1192</v>
       </c>
-      <c r="B564" s="5" t="s">
+      <c r="B564" s="13" t="s">
         <v>1193</v>
       </c>
       <c r="C564" s="6" t="s">
         <v>1194</v>
       </c>
       <c r="D564" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B564, ""en"", ""hi"")"),"VMtracker ड्राइवर ऐप डाउनलोड करें")</f>
-        <v>VMtracker ड्राइवर ऐप डाउनलोड करें</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B564, ""en"", ""hi"")"),"साइनअप नम्मा ऊरु टैक्सी ड्राइवर ऐप")</f>
+        <v>साइनअप नम्मा ऊरु टैक्सी ड्राइवर ऐप</v>
       </c>
       <c r="E564" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B564, ""en"", ""kn"")"),"VMtracker ಡ್ರೈವರ್ ಅಪ್ಲಿಕೇಶನ್ ಡೌನ್‌ಲೋಡ್ ಮಾಡಿ")</f>
-        <v>VMtracker ಡ್ರೈವರ್ ಅಪ್ಲಿಕೇಶನ್ ಡೌನ್‌ಲೋಡ್ ಮಾಡಿ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B564, ""en"", ""kn"")"),"ಸೈನ್ ಅಪ್ ನಮ್ಮ ಊರು ಟ್ಯಾಕ್ಸಿ ಡ್ರೈವರ್ ಅಪ್ಲಿಕೇಶನ್")</f>
+        <v>ಸೈನ್ ಅಪ್ ನಮ್ಮ ಊರು ಟ್ಯಾಕ್ಸಿ ಡ್ರೈವರ್ ಅಪ್ಲಿಕೇಶನ್</v>
       </c>
       <c r="F564" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B564, ""en"", ""ml"")"),"VMtracker ഡ്രൈവർ ആപ്പ് ഡൗൺലോഡ് ചെയ്യുക")</f>
-        <v>VMtracker ഡ്രൈവർ ആപ്പ് ഡൗൺലോഡ് ചെയ്യുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B564, ""en"", ""ml"")"),"നമ്മ ഊരു ടാക്സി ഡ്രൈവർ ആപ്പ് സൈൻ അപ്പ് ചെയ്യുക")</f>
+        <v>നമ്മ ഊരു ടാക്സി ഡ്രൈവർ ആപ്പ് സൈൻ അപ്പ് ചെയ്യുക</v>
       </c>
       <c r="G564" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B564, ""en"", ""te"")"),"VMtracker డ్రైవర్ యాప్‌ను డౌన్‌లోడ్ చేసుకోండి")</f>
-        <v>VMtracker డ్రైవర్ యాప్‌ను డౌన్‌లోడ్ చేసుకోండి</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B564, ""en"", ""te"")"),"సైన్అప్ నమ్మ ఊరు టాక్సీ డ్రైవర్ యాప్")</f>
+        <v>సైన్అప్ నమ్మ ఊరు టాక్సీ డ్రైవర్ యాప్</v>
       </c>
     </row>
     <row r="565">
@@ -24402,27 +24491,27 @@
       <c r="A572" s="4" t="s">
         <v>1216</v>
       </c>
-      <c r="B572" s="5" t="s">
+      <c r="B572" s="13" t="s">
         <v>1217</v>
       </c>
       <c r="C572" s="6" t="s">
         <v>1218</v>
       </c>
       <c r="D572" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B572, ""en"", ""hi"")"),"वीएम ट्रैकर ऐप डाउनलोड करें और बुनियादी जानकारी के साथ अपना ड्राइवर प्रोफाइल बनाएं।")</f>
-        <v>वीएम ट्रैकर ऐप डाउनलोड करें और बुनियादी जानकारी के साथ अपना ड्राइवर प्रोफाइल बनाएं।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B572, ""en"", ""hi"")"),"ड्राइवर ऐप के रूप में साइन अप करें और बुनियादी जानकारी के साथ अपना ड्राइवर प्रोफाइल बनाएं।")</f>
+        <v>ड्राइवर ऐप के रूप में साइन अप करें और बुनियादी जानकारी के साथ अपना ड्राइवर प्रोफाइल बनाएं।</v>
       </c>
       <c r="E572" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B572, ""en"", ""kn"")"),"VM ಟ್ರ್ಯಾಕರ್ ಅಪ್ಲಿಕೇಶನ್ ಡೌನ್‌ಲೋಡ್ ಮಾಡಿ ಮತ್ತು ಮೂಲ ಮಾಹಿತಿಯೊಂದಿಗೆ ನಿಮ್ಮ ಚಾಲಕ ಪ್ರೊಫೈಲ್ ಅನ್ನು ರಚಿಸಿ.")</f>
-        <v>VM ಟ್ರ್ಯಾಕರ್ ಅಪ್ಲಿಕೇಶನ್ ಡೌನ್‌ಲೋಡ್ ಮಾಡಿ ಮತ್ತು ಮೂಲ ಮಾಹಿತಿಯೊಂದಿಗೆ ನಿಮ್ಮ ಚಾಲಕ ಪ್ರೊಫೈಲ್ ಅನ್ನು ರಚಿಸಿ.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B572, ""en"", ""kn"")"),"ಚಾಲಕ ಅಪ್ಲಿಕೇಶನ್ ಆಗಿ ಸೈನ್ ಅಪ್ ಮಾಡಿ ಮತ್ತು ಮೂಲಭೂತ ಮಾಹಿತಿಯೊಂದಿಗೆ ನಿಮ್ಮ ಚಾಲಕ ಪ್ರೊಫೈಲ್ ಅನ್ನು ರಚಿಸಿ.")</f>
+        <v>ಚಾಲಕ ಅಪ್ಲಿಕೇಶನ್ ಆಗಿ ಸೈನ್ ಅಪ್ ಮಾಡಿ ಮತ್ತು ಮೂಲಭೂತ ಮಾಹಿತಿಯೊಂದಿಗೆ ನಿಮ್ಮ ಚಾಲಕ ಪ್ರೊಫೈಲ್ ಅನ್ನು ರಚಿಸಿ.</v>
       </c>
       <c r="F572" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B572, ""en"", ""ml"")"),"VM ട്രാക്കർ ആപ്പ് ഡൗൺലോഡ് ചെയ്ത് അടിസ്ഥാന വിവരങ്ങൾ ഉപയോഗിച്ച് നിങ്ങളുടെ ഡ്രൈവർ പ്രൊഫൈൽ സൃഷ്ടിക്കുക.")</f>
-        <v>VM ട്രാക്കർ ആപ്പ് ഡൗൺലോഡ് ചെയ്ത് അടിസ്ഥാന വിവരങ്ങൾ ഉപയോഗിച്ച് നിങ്ങളുടെ ഡ്രൈവർ പ്രൊഫൈൽ സൃഷ്ടിക്കുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B572, ""en"", ""ml"")"),"ഒരു ഡ്രൈവർ ആപ്പായി സൈൻ അപ്പ് ചെയ്ത് അടിസ്ഥാന വിവരങ്ങൾ ഉപയോഗിച്ച് നിങ്ങളുടെ ഡ്രൈവർ പ്രൊഫൈൽ സൃഷ്ടിക്കുക.")</f>
+        <v>ഒരു ഡ്രൈവർ ആപ്പായി സൈൻ അപ്പ് ചെയ്ത് അടിസ്ഥാന വിവരങ്ങൾ ഉപയോഗിച്ച് നിങ്ങളുടെ ഡ്രൈവർ പ്രൊഫൈൽ സൃഷ്ടിക്കുക.</v>
       </c>
       <c r="G572" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B572, ""en"", ""te"")"),"VM ట్రాకర్ యాప్‌ను డౌన్‌లోడ్ చేసుకోండి మరియు ప్రాథమిక సమాచారంతో మీ డ్రైవర్ ప్రొఫైల్‌ను సృష్టించండి.")</f>
-        <v>VM ట్రాకర్ యాప్‌ను డౌన్‌లోడ్ చేసుకోండి మరియు ప్రాథమిక సమాచారంతో మీ డ్రైవర్ ప్రొఫైల్‌ను సృష్టించండి.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B572, ""en"", ""te"")"),"డ్రైవర్ యాప్‌గా సైన్ అప్ చేయండి మరియు ప్రాథమిక సమాచారంతో మీ డ్రైవర్ ప్రొఫైల్‌ను సృష్టించండి.")</f>
+        <v>డ్రైవర్ యాప్‌గా సైన్ అప్ చేయండి మరియు ప్రాథమిక సమాచారంతో మీ డ్రైవర్ ప్రొఫైల్‌ను సృష్టించండి.</v>
       </c>
     </row>
     <row r="573">
@@ -24660,8 +24749,8 @@
         <v>ಚಾಲಕ ಆಗಮಿಸುತ್ತಿದ್ದಾರೆ</v>
       </c>
       <c r="F581" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B581, ""en"", ""ml"")"),"ഡ്രൈവർ എത്തുന്നു")</f>
-        <v>ഡ്രൈവർ എത്തുന്നു</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B581, ""en"", ""ml"")"),"ഡ്രൈവർ എത്തിച്ചേരുന്നു")</f>
+        <v>ഡ്രൈവർ എത്തിച്ചേരുന്നു</v>
       </c>
       <c r="G581" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B581, ""en"", ""te"")"),"డ్రైవర్ వస్తున్నాడు")</f>
@@ -25691,8 +25780,8 @@
         <v>കോൺടാക്റ്റ് നീക്കം ചെയ്യുക</v>
       </c>
       <c r="G619" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B619, ""en"", ""te"")"),"పరిచయాన్ని తీసివేయి")</f>
-        <v>పరిచయాన్ని తీసివేయి</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B619, ""en"", ""te"")"),"పరిచయాన్ని తీసివేయండి")</f>
+        <v>పరిచయాన్ని తీసివేయండి</v>
       </c>
     </row>
     <row r="620">
@@ -26499,8 +26588,8 @@
         <v>ಸ್ಥಳವನ್ನು ಅಳಿಸಲು ವಿಫಲವಾಗಿದೆ. ದಯವಿಟ್ಟು ಮತ್ತೆ ಪ್ರಯತ್ನಿಸಿ.</v>
       </c>
       <c r="F649" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B649, ""en"", ""ml"")"),"സ്ഥലം ഇല്ലാതാക്കാനായില്ല. വീണ്ടും ശ്രമിക്കുക.")</f>
-        <v>സ്ഥലം ഇല്ലാതാക്കാനായില്ല. വീണ്ടും ശ്രമിക്കുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B649, ""en"", ""ml"")"),"സ്ഥലം ഇല്ലാതാക്കുന്നതിൽ പരാജയപ്പെട്ടു. വീണ്ടും ശ്രമിക്കുക.")</f>
+        <v>സ്ഥലം ഇല്ലാതാക്കുന്നതിൽ പരാജയപ്പെട്ടു. വീണ്ടും ശ്രമിക്കുക.</v>
       </c>
       <c r="G649" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B649, ""en"", ""te"")"),"స్థలాన్ని తొలగించడంలో విఫలమైంది. దయచేసి మళ్ళీ ప్రయత్నించండి.")</f>
@@ -28791,8 +28880,8 @@
         <v>अमान्य स्टॉप</v>
       </c>
       <c r="E734" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B734, ""en"", ""kn"")"),"ಅಮಾನ್ಯವಾದ ನಿಲ್ದಾಣಗಳು")</f>
-        <v>ಅಮಾನ್ಯವಾದ ನಿಲ್ದಾಣಗಳು</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B734, ""en"", ""kn"")"),"ಅಮಾನ್ಯ ನಿಲ್ದಾಣಗಳು")</f>
+        <v>ಅಮಾನ್ಯ ನಿಲ್ದಾಣಗಳು</v>
       </c>
       <c r="F734" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B734, ""en"", ""ml"")"),"അസാധുവായ സ്റ്റോപ്പുകൾ")</f>
@@ -29254,8 +29343,8 @@
         <v>ನೀವು {ತ್ರಿಜ್ಯ} ಕಿಮೀ ವ್ಯಾಪ್ತಿಯೊಳಗಿನ ಸ್ಥಳವನ್ನು ಆಯ್ಕೆ ಮಾಡಬೇಕು.</v>
       </c>
       <c r="F751" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B751, ""en"", ""ml"")"),"നിങ്ങൾ {radius} കിലോമീറ്റർ ചുറ്റളവിൽ ഒരു സ്ഥലം തിരഞ്ഞെടുക്കണം.")</f>
-        <v>നിങ്ങൾ {radius} കിലോമീറ്റർ ചുറ്റളവിൽ ഒരു സ്ഥലം തിരഞ്ഞെടുക്കണം.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B751, ""en"", ""ml"")"),"{radius} കിലോമീറ്റർ ചുറ്റളവിലുള്ള ഒരു സ്ഥലം നിങ്ങൾ തിരഞ്ഞെടുക്കണം.")</f>
+        <v>{radius} കിലോമീറ്റർ ചുറ്റളവിലുള്ള ഒരു സ്ഥലം നിങ്ങൾ തിരഞ്ഞെടുക്കണം.</v>
       </c>
       <c r="G751" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B751, ""en"", ""te"")"),"మీరు {radius} కిమీ వ్యాసార్థంలోపు స్థానాన్ని ఎంచుకోవాలి.")</f>
@@ -30085,8 +30174,8 @@
         <v>कोई सुरक्षित स्थान नहीं</v>
       </c>
       <c r="E782" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B782, ""en"", ""kn"")"),"ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ.")</f>
-        <v>ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B782, ""en"", ""kn"")"),"ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ")</f>
+        <v>ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ</v>
       </c>
       <c r="F782" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B782, ""en"", ""ml"")"),"സംരക്ഷിച്ച സ്ഥലങ്ങളൊന്നുമില്ല.")</f>
@@ -30783,8 +30872,8 @@
         <v>1902</v>
       </c>
       <c r="D808" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B808, ""en"", ""hi"")"),"यात्रा में देरी का चित्रण")</f>
-        <v>यात्रा में देरी का चित्रण</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B808, ""en"", ""hi"")"),"यात्रा में देरी का उदाहरण")</f>
+        <v>यात्रा में देरी का उदाहरण</v>
       </c>
       <c r="E808" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B808, ""en"", ""kn"")"),"ಪ್ರಯಾಣದ ಬಾಕಿ ಇರುವ ವಿವರಣೆ")</f>
@@ -31709,8 +31798,8 @@
         <v>कृपया आपातकालीन संपर्क चुनें</v>
       </c>
       <c r="E842" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B842, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ತುರ್ತು ಸಂಪರ್ಕಗಳನ್ನು ಆಯ್ಕೆಮಾಡಿ.")</f>
-        <v>ದಯವಿಟ್ಟು ತುರ್ತು ಸಂಪರ್ಕಗಳನ್ನು ಆಯ್ಕೆಮಾಡಿ.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B842, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ತುರ್ತು ಸಂಪರ್ಕಗಳನ್ನು ಆಯ್ಕೆಮಾಡಿ")</f>
+        <v>ದಯವಿಟ್ಟು ತುರ್ತು ಸಂಪರ್ಕಗಳನ್ನು ಆಯ್ಕೆಮಾಡಿ</v>
       </c>
       <c r="F842" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B842, ""en"", ""ml"")"),"ദയവായി അടിയന്തര കോൺടാക്റ്റുകൾ തിരഞ്ഞെടുക്കുക.")</f>
@@ -31871,8 +31960,8 @@
         <v>कृपया पुन: प्रयास करें</v>
       </c>
       <c r="E848" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B848, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ಮತ್ತೆ ಪ್ರಯತ್ನಿಸಿ.")</f>
-        <v>ದಯವಿಟ್ಟು ಮತ್ತೆ ಪ್ರಯತ್ನಿಸಿ.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B848, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ಮತ್ತೆ ಪ್ರಯತ್ನಿಸಿ")</f>
+        <v>ದಯವಿಟ್ಟು ಮತ್ತೆ ಪ್ರಯತ್ನಿಸಿ</v>
       </c>
       <c r="F848" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B848, ""en"", ""ml"")"),"ദയവായി വീണ്ടും ശ്രമിക്കുക.")</f>
@@ -33303,8 +33392,8 @@
         <v>आपके सहेजे गए स्थान यहां दिखाई देंगे।</v>
       </c>
       <c r="E901" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B901, ""en"", ""kn"")"),"ನಿಮ್ಮ ಉಳಿಸಿದ ಸ್ಥಳಗಳು ಇಲ್ಲಿ ಕಾಣಿಸಿಕೊಳ್ಳುತ್ತವೆ.")</f>
-        <v>ನಿಮ್ಮ ಉಳಿಸಿದ ಸ್ಥಳಗಳು ಇಲ್ಲಿ ಕಾಣಿಸಿಕೊಳ್ಳುತ್ತವೆ.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B901, ""en"", ""kn"")"),"ನಿಮ್ಮ ಉಳಿಸಿದ ಸ್ಥಳಗಳು ಇಲ್ಲಿ ಗೋಚರಿಸುತ್ತವೆ.")</f>
+        <v>ನಿಮ್ಮ ಉಳಿಸಿದ ಸ್ಥಳಗಳು ಇಲ್ಲಿ ಗೋಚರಿಸುತ್ತವೆ.</v>
       </c>
       <c r="F901" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B901, ""en"", ""ml"")"),"നിങ്ങളുടെ സംരക്ഷിച്ച സ്ഥലങ്ങൾ ഇവിടെ ദൃശ്യമാകും.")</f>
@@ -34552,8 +34641,8 @@
         <v>ಚಾಲಕ ತಡವಾಗಿ ಬಂದಿರುವುದು</v>
       </c>
       <c r="F947" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B947, ""en"", ""ml"")"),"ഡ്രൈവർ വൈകിയുള്ള വരവ്")</f>
-        <v>ഡ്രൈവർ വൈകിയുള്ള വരവ്</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B947, ""en"", ""ml"")"),"ഡ്രൈവർ വൈകി എത്തൽ")</f>
+        <v>ഡ്രൈവർ വൈകി എത്തൽ</v>
       </c>
       <c r="G947" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B947, ""en"", ""te"")"),"డ్రైవర్ ఆలస్యంగా రావడం")</f>
@@ -34733,8 +34822,8 @@
         <v>2314</v>
       </c>
       <c r="D954" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B954, ""en"", ""hi"")"),"ड्राइवर बुक किए गए वाहन के बजाय किसी दूसरे प्रकार का वाहन लेकर आया (उदाहरण के लिए, एसयूवी के बजाय सेडान)।")</f>
-        <v>ड्राइवर बुक किए गए वाहन के बजाय किसी दूसरे प्रकार का वाहन लेकर आया (उदाहरण के लिए, एसयूवी के बजाय सेडान)।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B954, ""en"", ""hi"")"),"ड्राइवर बुक किए गए वाहन के प्रकार से भिन्न वाहन लेकर आया (उदाहरण के लिए, एसयूवी के बजाय सेडान)।")</f>
+        <v>ड्राइवर बुक किए गए वाहन के प्रकार से भिन्न वाहन लेकर आया (उदाहरण के लिए, एसयूवी के बजाय सेडान)।</v>
       </c>
       <c r="E954" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B954, ""en"", ""kn"")"),"ಚಾಲಕ ಬುಕ್ ಮಾಡಿದ ವಾಹನಕ್ಕಿಂತ ಬೇರೆ ವಾಹನ ಪ್ರಕಾರದೊಂದಿಗೆ ಬಂದಿದ್ದಾನೆ (ಉದಾ. SUV ಬದಲಿಗೆ ಸೆಡಾನ್)")</f>
@@ -34795,8 +34884,8 @@
         <v>ಅಪ್ಲಿಕೇಶನ್ ಸಂಬಂಧಿತ</v>
       </c>
       <c r="F956" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B956, ""en"", ""ml"")"),"ആപ്പ് അനുബന്ധം")</f>
-        <v>ആപ്പ് അനുബന്ധം</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B956, ""en"", ""ml"")"),"അനുബന്ധ ആപ്പ്")</f>
+        <v>അനുബന്ധ ആപ്പ്</v>
       </c>
       <c r="G956" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B956, ""en"", ""te"")"),"సంబంధిత యాప్")</f>
@@ -35273,8 +35362,8 @@
         <v>2359</v>
       </c>
       <c r="D974" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B974, ""en"", ""hi"")"),"अपनी समस्या का वर्णन करें, हम उसे हल करने में आपकी सहायता करेंगे।")</f>
-        <v>अपनी समस्या का वर्णन करें, हम उसे हल करने में आपकी सहायता करेंगे।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B974, ""en"", ""hi"")"),"अपनी समस्या का वर्णन करें और हम इसे हल करने में आपकी सहायता करेंगे।")</f>
+        <v>अपनी समस्या का वर्णन करें और हम इसे हल करने में आपकी सहायता करेंगे।</v>
       </c>
       <c r="E974" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B974, ""en"", ""kn"")"),"ನಿಮ್ಮ ಸಮಸ್ಯೆಯನ್ನು ವಿವರಿಸಿ, ಅದನ್ನು ಪರಿಹರಿಸಲು ನಾವು ನಿಮಗೆ ಸಹಾಯ ಮಾಡುತ್ತೇವೆ.")</f>
@@ -35903,8 +35992,8 @@
         <v>ನಿಮ್ಮ ಚಾಲಕನ ಆಗಮನವನ್ನು ನೈಜ ಸಮಯದಲ್ಲಿ ವೀಕ್ಷಿಸಿ ಮತ್ತು ಅವರ ಸ್ಥಳದ ಬಗ್ಗೆ ನವೀಕೃತವಾಗಿರಿ. ನಿಮ್ಮ ಸವಾರಿ ಯಾವಾಗ ಬರುತ್ತದೆ ಎಂದು ಇನ್ನು ಮುಂದೆ ಊಹಿಸುವ ಅಗತ್ಯವಿಲ್ಲ.</v>
       </c>
       <c r="F997" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B997, ""en"", ""ml"")"),"നിങ്ങളുടെ ഡ്രൈവറുടെ വരവ് തത്സമയം കാണുകയും അവരുടെ ലൊക്കേഷനുമായി അപ്‌ഡേറ്റ് ആയിരിക്കുകയും ചെയ്യുക. നിങ്ങളുടെ റൈഡ് എപ്പോൾ എത്തുമെന്ന് ഇനി ഊഹിക്കേണ്ടതില്ല.")</f>
-        <v>നിങ്ങളുടെ ഡ്രൈവറുടെ വരവ് തത്സമയം കാണുകയും അവരുടെ ലൊക്കേഷനുമായി അപ്‌ഡേറ്റ് ആയിരിക്കുകയും ചെയ്യുക. നിങ്ങളുടെ റൈഡ് എപ്പോൾ എത്തുമെന്ന് ഇനി ഊഹിക്കേണ്ടതില്ല.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B997, ""en"", ""ml"")"),"നിങ്ങളുടെ ഡ്രൈവറുടെ വരവ് തത്സമയം നിരീക്ഷിക്കുകയും അവരുടെ ലൊക്കേഷനുമായി അപ്‌ഡേറ്റ് ചെയ്യുകയും ചെയ്യുക. നിങ്ങളുടെ റൈഡ് എപ്പോൾ എത്തുമെന്ന് ഇനി ഊഹിക്കേണ്ടതില്ല.")</f>
+        <v>നിങ്ങളുടെ ഡ്രൈവറുടെ വരവ് തത്സമയം നിരീക്ഷിക്കുകയും അവരുടെ ലൊക്കേഷനുമായി അപ്‌ഡേറ്റ് ചെയ്യുകയും ചെയ്യുക. നിങ്ങളുടെ റൈഡ് എപ്പോൾ എത്തുമെന്ന് ഇനി ഊഹിക്കേണ്ടതില്ല.</v>
       </c>
       <c r="G997" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B997, ""en"", ""te"")"),"మీ డ్రైవర్ రాకను నిజ సమయంలో చూడండి మరియు వారి స్థానంతో తాజాగా ఉండండి. మీ రైడ్ ఎప్పుడు వస్తుందో ఊహించాల్సిన అవసరం లేదు.")</f>
@@ -36038,8 +36127,8 @@
         <v>{vehicleName} ಗರಿಷ್ಠ ದೂರ {maxKm} ಕಿ.ಮೀ. ದಯವಿಟ್ಟು ಬೇರೆ ವಾಹನವನ್ನು ಆಯ್ಕೆಮಾಡಿ ಅಥವಾ {maxKm} ಕಿ.ಮೀ.ಗಿಂತ ಕಡಿಮೆ ಪ್ರಯಾಣವನ್ನು ಯೋಜಿಸಿ.</v>
       </c>
       <c r="F1002" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1002, ""en"", ""ml"")"),"{vehicleName} പരമാവധി ദൂരം {maxKm} കിലോമീറ്ററാണ്. ദയവായി മറ്റൊരു വാഹനം തിരഞ്ഞെടുക്കുകയോ {maxKm} കിലോമീറ്ററിൽ താഴെയുള്ള യാത്ര പ്ലാൻ ചെയ്യുകയോ ചെയ്യുക.")</f>
-        <v>{vehicleName} പരമാവധി ദൂരം {maxKm} കിലോമീറ്ററാണ്. ദയവായി മറ്റൊരു വാഹനം തിരഞ്ഞെടുക്കുകയോ {maxKm} കിലോമീറ്ററിൽ താഴെയുള്ള യാത്ര പ്ലാൻ ചെയ്യുകയോ ചെയ്യുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1002, ""en"", ""ml"")"),"{vehicleName} പരമാവധി ദൂരം {maxKm} കിലോമീറ്ററാണ്. മറ്റൊരു വാഹനം തിരഞ്ഞെടുക്കുകയോ {maxKm} കിലോമീറ്ററിൽ താഴെയുള്ള യാത്ര പ്ലാൻ ചെയ്യുകയോ ചെയ്യുക.")</f>
+        <v>{vehicleName} പരമാവധി ദൂരം {maxKm} കിലോമീറ്ററാണ്. മറ്റൊരു വാഹനം തിരഞ്ഞെടുക്കുകയോ {maxKm} കിലോമീറ്ററിൽ താഴെയുള്ള യാത്ര പ്ലാൻ ചെയ്യുകയോ ചെയ്യുക.</v>
       </c>
       <c r="G1002" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1002, ""en"", ""te"")"),"{vehicleName} గరిష్ట దూరం {maxKm} కి.మీ. దయచేసి వేరే వాహనాన్ని ఎంచుకోండి లేదా {maxKm} కి.మీ కంటే తక్కువ దూరం ప్రయాణించడానికి ప్లాన్ చేయండి.")</f>
@@ -38922,8 +39011,8 @@
         <v>2694</v>
       </c>
       <c r="C1107" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1107, ""en"", ""ta"")"),"நிலுவையில் உள்ள தொகை")</f>
-        <v>நிலுவையில் உள்ள தொகை</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1107, ""en"", ""ta"")"),"நிலுவையில் உள்ள நிலுவைத் தொகை")</f>
+        <v>நிலுவையில் உள்ள நிலுவைத் தொகை</v>
       </c>
       <c r="D1107" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1107, ""en"", ""hi"")"),"बकाया राशि")</f>
@@ -39034,8 +39123,8 @@
         <v>2702</v>
       </c>
       <c r="C1111" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1111, ""en"", ""ta"")"),"அடுத்த தேதி")</f>
-        <v>அடுத்த தேதி</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1111, ""en"", ""ta"")"),"அடுத்தது செலுத்த வேண்டிய தேதி")</f>
+        <v>அடுத்தது செலுத்த வேண்டிய தேதி</v>
       </c>
       <c r="D1111" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1111, ""en"", ""hi"")"),"अगली देय तिथि में")</f>
@@ -39055,109 +39144,434 @@
       </c>
     </row>
     <row r="1112">
-      <c r="A1112" s="4"/>
-      <c r="B1112" s="5"/>
-      <c r="C1112" s="6"/>
-      <c r="D1112" s="6"/>
-      <c r="E1112" s="6"/>
+      <c r="A1112" s="12" t="s">
+        <v>2703</v>
+      </c>
+      <c r="B1112" s="13" t="s">
+        <v>2704</v>
+      </c>
+      <c r="C1112" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1112, ""en"", ""ta"")"),"அதிகபட்ச காத்திருப்பு நேரம் {maxwaitingTime} நிமிடங்கள்.")</f>
+        <v>அதிகபட்ச காத்திருப்பு நேரம் {maxwaitingTime} நிமிடங்கள்.</v>
+      </c>
+      <c r="D1112" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1112, ""en"", ""hi"")"),"अधिकतम प्रतीक्षा समय {maxwaitingTime} मिनट है")</f>
+        <v>अधिकतम प्रतीक्षा समय {maxwaitingTime} मिनट है</v>
+      </c>
+      <c r="E1112" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1112, ""en"", ""kn"")"),"ಗರಿಷ್ಠ ಕಾಯುವ ಸಮಯ {maxwaitingTime} ನಿಮಿಷಗಳು")</f>
+        <v>ಗರಿಷ್ಠ ಕಾಯುವ ಸಮಯ {maxwaitingTime} ನಿಮಿಷಗಳು</v>
+      </c>
+      <c r="F1112" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1112, ""en"", ""ml"")"),"പരമാവധി കാത്തിരിപ്പ് സമയം {maxwaitingTime} മിനിറ്റാണ്")</f>
+        <v>പരമാവധി കാത്തിരിപ്പ് സമയം {maxwaitingTime} മിനിറ്റാണ്</v>
+      </c>
+      <c r="G1112" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1112, ""en"", ""te"")"),"గరిష్ట నిరీక్షణ సమయం {maxwaitingTime} నిమిషాలు")</f>
+        <v>గరిష్ట నిరీక్షణ సమయం {maxwaitingTime} నిమిషాలు</v>
+      </c>
     </row>
     <row r="1113">
-      <c r="A1113" s="4"/>
-      <c r="B1113" s="5"/>
-      <c r="C1113" s="6"/>
-      <c r="D1113" s="6"/>
-      <c r="E1113" s="6"/>
+      <c r="A1113" s="12" t="s">
+        <v>2705</v>
+      </c>
+      <c r="B1113" s="13" t="s">
+        <v>539</v>
+      </c>
+      <c r="C1113" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1113, ""en"", ""ta"")"),"பயணத்தை ரத்துசெய்")</f>
+        <v>பயணத்தை ரத்துசெய்</v>
+      </c>
+      <c r="D1113" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1113, ""en"", ""hi"")"),"यात्रा रद्द करें")</f>
+        <v>यात्रा रद्द करें</v>
+      </c>
+      <c r="E1113" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1113, ""en"", ""kn"")"),"ಪ್ರವಾಸ ರದ್ದುಗೊಳಿಸಿ")</f>
+        <v>ಪ್ರವಾಸ ರದ್ದುಗೊಳಿಸಿ</v>
+      </c>
+      <c r="F1113" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1113, ""en"", ""ml"")"),"യാത്ര റദ്ദാക്കുക")</f>
+        <v>യാത്ര റദ്ദാക്കുക</v>
+      </c>
+      <c r="G1113" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1113, ""en"", ""te"")"),"ట్రిప్ రద్దు చేయి")</f>
+        <v>ట్రిప్ రద్దు చేయి</v>
+      </c>
     </row>
     <row r="1114">
-      <c r="A1114" s="4"/>
-      <c r="B1114" s="5"/>
-      <c r="C1114" s="6"/>
-      <c r="D1114" s="6"/>
-      <c r="E1114" s="6"/>
+      <c r="A1114" s="12" t="s">
+        <v>2706</v>
+      </c>
+      <c r="B1114" s="13" t="s">
+        <v>2707</v>
+      </c>
+      <c r="C1114" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1114, ""en"", ""ta"")"),"இந்தப் பயணத்தை ரத்து செய்ய விரும்புகிறீர்களா? ரத்துசெய்தல் அபராதம் விதிக்கப்படலாம்.")</f>
+        <v>இந்தப் பயணத்தை ரத்து செய்ய விரும்புகிறீர்களா? ரத்துசெய்தல் அபராதம் விதிக்கப்படலாம்.</v>
+      </c>
+      <c r="D1114" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1114, ""en"", ""hi"")"),"क्या आप वाकई इस यात्रा को रद्द करना चाहते हैं? रद्द करने पर जुर्माना लग सकता है।")</f>
+        <v>क्या आप वाकई इस यात्रा को रद्द करना चाहते हैं? रद्द करने पर जुर्माना लग सकता है।</v>
+      </c>
+      <c r="E1114" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1114, ""en"", ""kn"")"),"ಈ ಪ್ರವಾಸವನ್ನು ರದ್ದುಗೊಳಿಸಲು ನೀವು ಖಚಿತವಾಗಿ ಬಯಸುವಿರಾ? ರದ್ದತಿ ದಂಡ ಅನ್ವಯಿಸಬಹುದು.")</f>
+        <v>ಈ ಪ್ರವಾಸವನ್ನು ರದ್ದುಗೊಳಿಸಲು ನೀವು ಖಚಿತವಾಗಿ ಬಯಸುವಿರಾ? ರದ್ದತಿ ದಂಡ ಅನ್ವಯಿಸಬಹುದು.</v>
+      </c>
+      <c r="F1114" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1114, ""en"", ""ml"")"),"ഈ യാത്ര റദ്ദാക്കണമെന്ന് നിങ്ങൾക്ക് ഉറപ്പാണോ? റദ്ദാക്കൽ പിഴ ബാധകമായേക്കാം.")</f>
+        <v>ഈ യാത്ര റദ്ദാക്കണമെന്ന് നിങ്ങൾക്ക് ഉറപ്പാണോ? റദ്ദാക്കൽ പിഴ ബാധകമായേക്കാം.</v>
+      </c>
+      <c r="G1114" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1114, ""en"", ""te"")"),"మీరు ఈ ట్రిప్‌ను ఖచ్చితంగా రద్దు చేయాలనుకుంటున్నారా? రద్దు జరిమానా వర్తించవచ్చు.")</f>
+        <v>మీరు ఈ ట్రిప్‌ను ఖచ్చితంగా రద్దు చేయాలనుకుంటున్నారా? రద్దు జరిమానా వర్తించవచ్చు.</v>
+      </c>
     </row>
     <row r="1115">
-      <c r="A1115" s="4"/>
-      <c r="B1115" s="5"/>
-      <c r="C1115" s="6"/>
-      <c r="D1115" s="6"/>
-      <c r="E1115" s="6"/>
+      <c r="A1115" s="12" t="s">
+        <v>2708</v>
+      </c>
+      <c r="B1115" s="13" t="s">
+        <v>2709</v>
+      </c>
+      <c r="C1115" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1115, ""en"", ""ta"")"),"எப்படியும் ரத்துசெய்")</f>
+        <v>எப்படியும் ரத்துசெய்</v>
+      </c>
+      <c r="D1115" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1115, ""en"", ""hi"")"),"फिर भी रद्द करें")</f>
+        <v>फिर भी रद्द करें</v>
+      </c>
+      <c r="E1115" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1115, ""en"", ""kn"")"),"ಹೇಗಾದರೂ ರದ್ದುಮಾಡಿ")</f>
+        <v>ಹೇಗಾದರೂ ರದ್ದುಮಾಡಿ</v>
+      </c>
+      <c r="F1115" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1115, ""en"", ""ml"")"),"എന്തായാലും റദ്ദാക്കുക")</f>
+        <v>എന്തായാലും റദ്ദാക്കുക</v>
+      </c>
+      <c r="G1115" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1115, ""en"", ""te"")"),"ఏదేమైనా రద్దు చేయి")</f>
+        <v>ఏదేమైనా రద్దు చేయి</v>
+      </c>
     </row>
     <row r="1116">
-      <c r="A1116" s="4"/>
-      <c r="B1116" s="5"/>
-      <c r="C1116" s="6"/>
-      <c r="D1116" s="6"/>
-      <c r="E1116" s="6"/>
+      <c r="A1116" s="12" t="s">
+        <v>2710</v>
+      </c>
+      <c r="B1116" s="13" t="s">
+        <v>2711</v>
+      </c>
+      <c r="C1116" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1116, ""en"", ""ta"")"),"iOS இல் டிரைவர் செயலி")</f>
+        <v>iOS இல் டிரைவர் செயலி</v>
+      </c>
+      <c r="D1116" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1116, ""en"", ""hi"")"),"iOS पर ड्राइवर ऐप")</f>
+        <v>iOS पर ड्राइवर ऐप</v>
+      </c>
+      <c r="E1116" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1116, ""en"", ""kn"")"),"iOS ನಲ್ಲಿ ಚಾಲಕ ಅಪ್ಲಿಕೇಶನ್")</f>
+        <v>iOS ನಲ್ಲಿ ಚಾಲಕ ಅಪ್ಲಿಕೇಶನ್</v>
+      </c>
+      <c r="F1116" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1116, ""en"", ""ml"")"),"iOS-ലെ ഡ്രൈവർ ആപ്പ്")</f>
+        <v>iOS-ലെ ഡ്രൈവർ ആപ്പ്</v>
+      </c>
+      <c r="G1116" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1116, ""en"", ""te"")"),"iOS లో డ్రైవర్ యాప్")</f>
+        <v>iOS లో డ్రైవర్ యాప్</v>
+      </c>
     </row>
     <row r="1117">
-      <c r="A1117" s="4"/>
-      <c r="B1117" s="5"/>
-      <c r="C1117" s="6"/>
-      <c r="D1117" s="6"/>
-      <c r="E1117" s="6"/>
+      <c r="A1117" s="12" t="s">
+        <v>2712</v>
+      </c>
+      <c r="B1117" s="13" t="s">
+        <v>2713</v>
+      </c>
+      <c r="C1117" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1117, ""en"", ""ta"")"),"நம்ம ஊரு டாக்ஸி டிரைவர் ஆப் தற்போது iOS இல் கிடைக்கவில்லை. டிரைவர் செயலியை அணுக Android சாதனத்தைப் பயன்படுத்தவும்.")</f>
+        <v>நம்ம ஊரு டாக்ஸி டிரைவர் ஆப் தற்போது iOS இல் கிடைக்கவில்லை. டிரைவர் செயலியை அணுக Android சாதனத்தைப் பயன்படுத்தவும்.</v>
+      </c>
+      <c r="D1117" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1117, ""en"", ""hi"")"),"Namma Ooru Taxi Driver App फिलहाल iOS पर उपलब्ध नहीं है। कृपया ड्राइवर ऐप का उपयोग करने के लिए Android डिवाइस का इस्तेमाल करें।")</f>
+        <v>Namma Ooru Taxi Driver App फिलहाल iOS पर उपलब्ध नहीं है। कृपया ड्राइवर ऐप का उपयोग करने के लिए Android डिवाइस का इस्तेमाल करें।</v>
+      </c>
+      <c r="E1117" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1117, ""en"", ""kn"")"),"ನಮ್ಮ ಊರು ಟ್ಯಾಕ್ಸಿ ಡ್ರೈವರ್ ಆಪ್ ಸದ್ಯಕ್ಕೆ iOS ನಲ್ಲಿ ಲಭ್ಯವಿಲ್ಲ. ಡ್ರೈವರ್ ಆಪ್ ಪ್ರವೇಶಿಸಲು ದಯವಿಟ್ಟು Android ಸಾಧನವನ್ನು ಬಳಸಿ.")</f>
+        <v>ನಮ್ಮ ಊರು ಟ್ಯಾಕ್ಸಿ ಡ್ರೈವರ್ ಆಪ್ ಸದ್ಯಕ್ಕೆ iOS ನಲ್ಲಿ ಲಭ್ಯವಿಲ್ಲ. ಡ್ರೈವರ್ ಆಪ್ ಪ್ರವೇಶಿಸಲು ದಯವಿಟ್ಟು Android ಸಾಧನವನ್ನು ಬಳಸಿ.</v>
+      </c>
+      <c r="F1117" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1117, ""en"", ""ml"")"),"നമ്മ ഊരു ടാക്സി ഡ്രൈവർ ആപ്പ് ഇപ്പോൾ iOS-ൽ ലഭ്യമല്ല. ഡ്രൈവർ ആപ്പ് ആക്‌സസ് ചെയ്യാൻ ഒരു Android ഉപകരണം ഉപയോഗിക്കുക.")</f>
+        <v>നമ്മ ഊരു ടാക്സി ഡ്രൈവർ ആപ്പ് ഇപ്പോൾ iOS-ൽ ലഭ്യമല്ല. ഡ്രൈവർ ആപ്പ് ആക്‌സസ് ചെയ്യാൻ ഒരു Android ഉപകരണം ഉപയോഗിക്കുക.</v>
+      </c>
+      <c r="G1117" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1117, ""en"", ""te"")"),"నమ్మ ఊరు టాక్సీ డ్రైవర్ యాప్ ప్రస్తుతం iOS లో అందుబాటులో లేదు. డ్రైవర్ యాప్‌ను యాక్సెస్ చేయడానికి దయచేసి Android పరికరాన్ని ఉపయోగించండి.")</f>
+        <v>నమ్మ ఊరు టాక్సీ డ్రైవర్ యాప్ ప్రస్తుతం iOS లో అందుబాటులో లేదు. డ్రైవర్ యాప్‌ను యాక్సెస్ చేయడానికి దయచేసి Android పరికరాన్ని ఉపయోగించండి.</v>
+      </c>
     </row>
     <row r="1118">
-      <c r="A1118" s="4"/>
-      <c r="B1118" s="5"/>
-      <c r="C1118" s="6"/>
-      <c r="D1118" s="6"/>
-      <c r="E1118" s="6"/>
+      <c r="A1118" s="12" t="s">
+        <v>2714</v>
+      </c>
+      <c r="B1118" s="13" t="s">
+        <v>2715</v>
+      </c>
+      <c r="C1118" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1118, ""en"", ""ta"")"),"ஓட்டுநராக பதிவு செய்யவும்")</f>
+        <v>ஓட்டுநராக பதிவு செய்யவும்</v>
+      </c>
+      <c r="D1118" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1118, ""en"", ""hi"")"),"ड्राइवर बनने के लिए साइन अप करें")</f>
+        <v>ड्राइवर बनने के लिए साइन अप करें</v>
+      </c>
+      <c r="E1118" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1118, ""en"", ""kn"")"),"ಚಾಲಕರಾಗಲು ಸೈನ್ ಅಪ್ ಮಾಡಿ")</f>
+        <v>ಚಾಲಕರಾಗಲು ಸೈನ್ ಅಪ್ ಮಾಡಿ</v>
+      </c>
+      <c r="F1118" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1118, ""en"", ""ml"")"),"ഡ്രൈവർ ആകാൻ സൈൻ അപ്പ് ചെയ്യുക")</f>
+        <v>ഡ്രൈവർ ആകാൻ സൈൻ അപ്പ് ചെയ്യുക</v>
+      </c>
+      <c r="G1118" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1118, ""en"", ""te"")"),"డ్రైవర్ కావడానికి సైన్ అప్ చేయండి")</f>
+        <v>డ్రైవర్ కావడానికి సైన్ అప్ చేయండి</v>
+      </c>
     </row>
     <row r="1119">
-      <c r="A1119" s="4"/>
-      <c r="B1119" s="5"/>
-      <c r="C1119" s="6"/>
-      <c r="D1119" s="6"/>
-      <c r="E1119" s="6"/>
+      <c r="A1119" s="12" t="s">
+        <v>2716</v>
+      </c>
+      <c r="B1119" s="13" t="s">
+        <v>2717</v>
+      </c>
+      <c r="C1119" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1119, ""en"", ""ta"")"),"உங்கள் நண்பர்களைப் பரிந்துரைக்கவும்")</f>
+        <v>உங்கள் நண்பர்களைப் பரிந்துரைக்கவும்</v>
+      </c>
+      <c r="D1119" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1119, ""en"", ""hi"")"),"अपने दोस्तों को बताएं")</f>
+        <v>अपने दोस्तों को बताएं</v>
+      </c>
+      <c r="E1119" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1119, ""en"", ""kn"")"),"ನಿಮ್ಮ ಸ್ನೇಹಿತರನ್ನು ಉಲ್ಲೇಖಿಸಿ")</f>
+        <v>ನಿಮ್ಮ ಸ್ನೇಹಿತರನ್ನು ಉಲ್ಲೇಖಿಸಿ</v>
+      </c>
+      <c r="F1119" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1119, ""en"", ""ml"")"),"നിങ്ങളുടെ സുഹൃത്തുക്കളെ റഫർ ചെയ്യുക")</f>
+        <v>നിങ്ങളുടെ സുഹൃത്തുക്കളെ റഫർ ചെയ്യുക</v>
+      </c>
+      <c r="G1119" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1119, ""en"", ""te"")"),"మీ స్నేహితులను సూచించండి")</f>
+        <v>మీ స్నేహితులను సూచించండి</v>
+      </c>
     </row>
     <row r="1120">
-      <c r="A1120" s="4"/>
-      <c r="B1120" s="5"/>
-      <c r="C1120" s="6"/>
-      <c r="D1120" s="6"/>
-      <c r="E1120" s="6"/>
+      <c r="A1120" s="12" t="s">
+        <v>2718</v>
+      </c>
+      <c r="B1120" s="13" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C1120" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1120, ""en"", ""ta"")"),"பயணத்தைத் தொடங்க வாடிக்கையாளரைச் சரிபார்க்கவும்.")</f>
+        <v>பயணத்தைத் தொடங்க வாடிக்கையாளரைச் சரிபார்க்கவும்.</v>
+      </c>
+      <c r="D1120" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1120, ""en"", ""hi"")"),"यात्रा शुरू करने के लिए ग्राहक की पुष्टि करें")</f>
+        <v>यात्रा शुरू करने के लिए ग्राहक की पुष्टि करें</v>
+      </c>
+      <c r="E1120" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1120, ""en"", ""kn"")"),"ಪ್ರಯಾಣವನ್ನು ಪ್ರಾರಂಭಿಸಲು ಗ್ರಾಹಕರನ್ನು ಪರಿಶೀಲಿಸಿ.")</f>
+        <v>ಪ್ರಯಾಣವನ್ನು ಪ್ರಾರಂಭಿಸಲು ಗ್ರಾಹಕರನ್ನು ಪರಿಶೀಲಿಸಿ.</v>
+      </c>
+      <c r="F1120" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1120, ""en"", ""ml"")"),"യാത്ര ആരംഭിക്കാൻ ഉപഭോക്താവിനെ സ്ഥിരീകരിക്കുക.")</f>
+        <v>യാത്ര ആരംഭിക്കാൻ ഉപഭോക്താവിനെ സ്ഥിരീകരിക്കുക.</v>
+      </c>
+      <c r="G1120" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1120, ""en"", ""te"")"),"ట్రిప్ ప్రారంభించడానికి కస్టమర్‌ను ధృవీకరించండి.")</f>
+        <v>ట్రిప్ ప్రారంభించడానికి కస్టమర్‌ను ధృవీకరించండి.</v>
+      </c>
     </row>
     <row r="1121">
-      <c r="A1121" s="4"/>
-      <c r="B1121" s="5"/>
-      <c r="C1121" s="6"/>
-      <c r="D1121" s="6"/>
-      <c r="E1121" s="6"/>
+      <c r="A1121" s="23" t="s">
+        <v>2720</v>
+      </c>
+      <c r="B1121" s="13" t="s">
+        <v>2721</v>
+      </c>
+      <c r="C1121" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1121, ""en"", ""ta"")"),"வாகன ஒப்புதல்")</f>
+        <v>வாகன ஒப்புதல்</v>
+      </c>
+      <c r="D1121" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1121, ""en"", ""hi"")"),"वाहन अनुमोदन")</f>
+        <v>वाहन अनुमोदन</v>
+      </c>
+      <c r="E1121" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1121, ""en"", ""kn"")"),"ವಾಹನ ಅನುಮೋದನೆ")</f>
+        <v>ವಾಹನ ಅನುಮೋದನೆ</v>
+      </c>
+      <c r="F1121" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1121, ""en"", ""ml"")"),"വാഹന അംഗീകാരം")</f>
+        <v>വാഹന അംഗീകാരം</v>
+      </c>
+      <c r="G1121" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1121, ""en"", ""te"")"),"వాహన ఆమోదం")</f>
+        <v>వాహన ఆమోదం</v>
+      </c>
     </row>
     <row r="1122">
-      <c r="A1122" s="4"/>
-      <c r="B1122" s="5"/>
-      <c r="C1122" s="6"/>
-      <c r="D1122" s="6"/>
-      <c r="E1122" s="6"/>
+      <c r="A1122" s="12" t="s">
+        <v>2722</v>
+      </c>
+      <c r="B1122" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="C1122" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1122, ""en"", ""ta"")"),"டாக்ஸியை சரிபார்த்து அவற்றை அங்கீகரிக்க நாங்கள் கடுமையாக உழைத்து வருகிறோம். எனவே ஒப்புதல் செயல்முறை சிறிது நேரம் எடுக்கும் என்பதை புரிந்து கொள்ளுங்கள்.
+உங்கள் பொறுமைக்கு நன்றி.")</f>
+        <v>டாக்ஸியை சரிபார்த்து அவற்றை அங்கீகரிக்க நாங்கள் கடுமையாக உழைத்து வருகிறோம். எனவே ஒப்புதல் செயல்முறை சிறிது நேரம் எடுக்கும் என்பதை புரிந்து கொள்ளுங்கள்.
+உங்கள் பொறுமைக்கு நன்றி.</v>
+      </c>
+      <c r="D1122" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1122, ""en"", ""hi"")"),"हम टैक्सियों की जांच और अनुमोदन के लिए कड़ी मेहनत कर रहे हैं। कृपया समझें कि अनुमोदन प्रक्रिया में कुछ समय लगेगा।
+आपके धैर्य के लिए धन्यवाद।")</f>
+        <v>हम टैक्सियों की जांच और अनुमोदन के लिए कड़ी मेहनत कर रहे हैं। कृपया समझें कि अनुमोदन प्रक्रिया में कुछ समय लगेगा।
+आपके धैर्य के लिए धन्यवाद।</v>
+      </c>
+      <c r="E1122" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1122, ""en"", ""kn"")"),"ಟ್ಯಾಕ್ಸಿಯನ್ನು ಪರಿಶೀಲಿಸಲು ಮತ್ತು ಅವುಗಳನ್ನು ಅನುಮೋದಿಸಲು ನಾವು ಶ್ರಮಿಸುತ್ತಿದ್ದೇವೆ. ಆದ್ದರಿಂದ ಅನುಮೋದನೆ ಪ್ರಕ್ರಿಯೆಯು ಸ್ವಲ್ಪ ಸಮಯ ತೆಗೆದುಕೊಳ್ಳುತ್ತದೆ ಎಂಬುದನ್ನು ದಯವಿಟ್ಟು ಅರ್ಥಮಾಡಿಕೊಳ್ಳಿ.
+ನಿಮ್ಮ ತಾಳ್ಮೆಗೆ ಧನ್ಯವಾದಗಳು.")</f>
+        <v>ಟ್ಯಾಕ್ಸಿಯನ್ನು ಪರಿಶೀಲಿಸಲು ಮತ್ತು ಅವುಗಳನ್ನು ಅನುಮೋದಿಸಲು ನಾವು ಶ್ರಮಿಸುತ್ತಿದ್ದೇವೆ. ಆದ್ದರಿಂದ ಅನುಮೋದನೆ ಪ್ರಕ್ರಿಯೆಯು ಸ್ವಲ್ಪ ಸಮಯ ತೆಗೆದುಕೊಳ್ಳುತ್ತದೆ ಎಂಬುದನ್ನು ದಯವಿಟ್ಟು ಅರ್ಥಮಾಡಿಕೊಳ್ಳಿ.
+ನಿಮ್ಮ ತಾಳ್ಮೆಗೆ ಧನ್ಯವಾದಗಳು.</v>
+      </c>
+      <c r="F1122" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1122, ""en"", ""ml"")"),"ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
+ക്ഷമയ്ക്ക് നന്ദി.")</f>
+        <v>ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
+ക്ഷമയ്ക്ക് നന്ദി.</v>
+      </c>
+      <c r="G1122" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1122, ""en"", ""te"")"),"టాక్సీని ధృవీకరించడానికి మరియు వాటిని ఆమోదించడానికి మేము తీవ్రంగా కృషి చేస్తున్నాము. కాబట్టి దయచేసి ఆమోద ప్రక్రియకు కొంత సమయం పడుతుందని అర్థం చేసుకోండి.
+మీ ఓర్పుకు ధన్యవాదాలు.")</f>
+        <v>టాక్సీని ధృవీకరించడానికి మరియు వాటిని ఆమోదించడానికి మేము తీవ్రంగా కృషి చేస్తున్నాము. కాబట్టి దయచేసి ఆమోద ప్రక్రియకు కొంత సమయం పడుతుందని అర్థం చేసుకోండి.
+మీ ఓర్పుకు ధన్యవాదాలు.</v>
+      </c>
     </row>
     <row r="1123">
-      <c r="A1123" s="4"/>
-      <c r="B1123" s="5"/>
-      <c r="C1123" s="6"/>
-      <c r="D1123" s="6"/>
-      <c r="E1123" s="6"/>
+      <c r="A1123" s="12" t="s">
+        <v>2723</v>
+      </c>
+      <c r="B1123" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="C1123" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1123, ""en"", ""ta"")"),"பதிவு அல்லது செயலி தொடர்பாக ஏதேனும் கேள்விகள் இருந்தால், தயவுசெய்து")</f>
+        <v>பதிவு அல்லது செயலி தொடர்பாக ஏதேனும் கேள்விகள் இருந்தால், தயவுசெய்து</v>
+      </c>
+      <c r="D1123" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1123, ""en"", ""hi"")"),"यदि पंजीकरण या ऐप से संबंधित आपके कोई प्रश्न हैं, तो कृपया")</f>
+        <v>यदि पंजीकरण या ऐप से संबंधित आपके कोई प्रश्न हैं, तो कृपया</v>
+      </c>
+      <c r="E1123" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1123, ""en"", ""kn"")"),"ನೋಂದಣಿ ಅಥವಾ ಅಪ್ಲಿಕೇಶನ್ ಕುರಿತು ನೀವು ಯಾವುದೇ ಪ್ರಶ್ನೆಗಳನ್ನು ಹೊಂದಿದ್ದರೆ, ದಯವಿಟ್ಟು")</f>
+        <v>ನೋಂದಣಿ ಅಥವಾ ಅಪ್ಲಿಕೇಶನ್ ಕುರಿತು ನೀವು ಯಾವುದೇ ಪ್ರಶ್ನೆಗಳನ್ನು ಹೊಂದಿದ್ದರೆ, ದಯವಿಟ್ಟು</v>
+      </c>
+      <c r="F1123" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1123, ""en"", ""ml"")"),"രജിസ്ട്രേഷനെക്കുറിച്ചോ ആപ്പിനെക്കുറിച്ചോ എന്തെങ്കിലും സംശയങ്ങൾ ഉണ്ടെങ്കിൽ, ദയവായി")</f>
+        <v>രജിസ്ട്രേഷനെക്കുറിച്ചോ ആപ്പിനെക്കുറിച്ചോ എന്തെങ്കിലും സംശയങ്ങൾ ഉണ്ടെങ്കിൽ, ദയവായി</v>
+      </c>
+      <c r="G1123" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1123, ""en"", ""te"")"),"రిజిస్ట్రేషన్ లేదా యాప్ గురించి మీకు ఏవైనా ప్రశ్నలు ఉంటే, దయచేసి")</f>
+        <v>రిజిస్ట్రేషన్ లేదా యాప్ గురించి మీకు ఏవైనా ప్రశ్నలు ఉంటే, దయచేసి</v>
+      </c>
     </row>
     <row r="1124">
-      <c r="A1124" s="4"/>
-      <c r="B1124" s="5"/>
-      <c r="C1124" s="6"/>
-      <c r="D1124" s="6"/>
-      <c r="E1124" s="6"/>
+      <c r="A1124" s="12" t="s">
+        <v>2724</v>
+      </c>
+      <c r="B1124" s="13" t="s">
+        <v>2725</v>
+      </c>
+      <c r="C1124" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1124, ""en"", ""ta"")"),"சில காரணங்களால் உங்கள் வாகனம் தடுக்கப்பட்டுள்ளது.")</f>
+        <v>சில காரணங்களால் உங்கள் வாகனம் தடுக்கப்பட்டுள்ளது.</v>
+      </c>
+      <c r="D1124" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1124, ""en"", ""hi"")"),"कुछ कारणों से आपका वाहन अवरुद्ध हो गया है।")</f>
+        <v>कुछ कारणों से आपका वाहन अवरुद्ध हो गया है।</v>
+      </c>
+      <c r="E1124" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1124, ""en"", ""kn"")"),"ಕೆಲವು ಕಾರಣಗಳಿಂದ ನಿಮ್ಮ ವಾಹನವನ್ನು ನಿರ್ಬಂಧಿಸಲಾಗಿದೆ.")</f>
+        <v>ಕೆಲವು ಕಾರಣಗಳಿಂದ ನಿಮ್ಮ ವಾಹನವನ್ನು ನಿರ್ಬಂಧಿಸಲಾಗಿದೆ.</v>
+      </c>
+      <c r="F1124" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1124, ""en"", ""ml"")"),"ചില കാരണങ്ങളാൽ നിങ്ങളുടെ വാഹനം തടഞ്ഞിരിക്കുന്നു.")</f>
+        <v>ചില കാരണങ്ങളാൽ നിങ്ങളുടെ വാഹനം തടഞ്ഞിരിക്കുന്നു.</v>
+      </c>
+      <c r="G1124" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1124, ""en"", ""te"")"),"కొన్ని కారణాల వల్ల మీ వాహనం బ్లాక్ చేయబడింది.")</f>
+        <v>కొన్ని కారణాల వల్ల మీ వాహనం బ్లాక్ చేయబడింది.</v>
+      </c>
     </row>
     <row r="1125">
-      <c r="A1125" s="4"/>
-      <c r="B1125" s="5"/>
-      <c r="C1125" s="6"/>
-      <c r="D1125" s="6"/>
-      <c r="E1125" s="6"/>
+      <c r="A1125" s="12" t="s">
+        <v>2726</v>
+      </c>
+      <c r="B1125" s="13" t="s">
+        <v>2727</v>
+      </c>
+      <c r="C1125" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1125, ""en"", ""ta"")"),"உங்கள் வாகனம் நீக்கப்பட்டது.")</f>
+        <v>உங்கள் வாகனம் நீக்கப்பட்டது.</v>
+      </c>
+      <c r="D1125" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1125, ""en"", ""hi"")"),"आपका वाहन हटा दिया गया है।")</f>
+        <v>आपका वाहन हटा दिया गया है।</v>
+      </c>
+      <c r="E1125" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1125, ""en"", ""kn"")"),"ನಿಮ್ಮ ವಾಹನವನ್ನು ಅಳಿಸಲಾಗಿದೆ.")</f>
+        <v>ನಿಮ್ಮ ವಾಹನವನ್ನು ಅಳಿಸಲಾಗಿದೆ.</v>
+      </c>
+      <c r="F1125" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1125, ""en"", ""ml"")"),"നിങ്ങളുടെ വാഹനം ഇല്ലാതാക്കി.")</f>
+        <v>നിങ്ങളുടെ വാഹനം ഇല്ലാതാക്കി.</v>
+      </c>
+      <c r="G1125" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1125, ""en"", ""te"")"),"మీ వాహనం తొలగించబడింది.")</f>
+        <v>మీ వాహనం తొలగించబడింది.</v>
+      </c>
     </row>
     <row r="1126">
-      <c r="A1126" s="4"/>
-      <c r="B1126" s="5"/>
-      <c r="C1126" s="6"/>
-      <c r="D1126" s="6"/>
-      <c r="E1126" s="6"/>
+      <c r="A1126" s="12" t="s">
+        <v>2728</v>
+      </c>
+      <c r="B1126" s="13" t="s">
+        <v>2729</v>
+      </c>
+      <c r="C1126" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1126, ""en"", ""ta"")"),"உங்கள் வாகனம் இன்னும் ஒப்புதலில் உள்ளது.")</f>
+        <v>உங்கள் வாகனம் இன்னும் ஒப்புதலில் உள்ளது.</v>
+      </c>
+      <c r="D1126" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1126, ""en"", ""hi"")"),"आपका वाहन अभी भी अनुमोदन प्रक्रिया में है।")</f>
+        <v>आपका वाहन अभी भी अनुमोदन प्रक्रिया में है।</v>
+      </c>
+      <c r="E1126" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1126, ""en"", ""kn"")"),"ನಿಮ್ಮ ವಾಹನ ಇನ್ನೂ ಅನುಮೋದನೆ ಹಂತದಲ್ಲಿದೆ.")</f>
+        <v>ನಿಮ್ಮ ವಾಹನ ಇನ್ನೂ ಅನುಮೋದನೆ ಹಂತದಲ್ಲಿದೆ.</v>
+      </c>
+      <c r="F1126" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1126, ""en"", ""ml"")"),"നിങ്ങളുടെ വാഹനം ഇപ്പോഴും അംഗീകാരത്തിലാണ്.")</f>
+        <v>നിങ്ങളുടെ വാഹനം ഇപ്പോഴും അംഗീകാരത്തിലാണ്.</v>
+      </c>
+      <c r="G1126" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1126, ""en"", ""te"")"),"మీ వాహనం ఇంకా ఆమోదం పొందుతోంది.")</f>
+        <v>మీ వాహనం ఇంకా ఆమోదం పొందుతోంది.</v>
+      </c>
     </row>
     <row r="1127">
       <c r="A1127" s="4"/>
@@ -45649,6 +46063,11 @@
       <c r="E2053" s="11"/>
     </row>
   </sheetData>
+  <dataValidations>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B566">
+      <formula1>"We’re here to help. Contact us anytime."</formula1>
+    </dataValidation>
+  </dataValidations>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/PublicCustomerApp/src/python/translation.xlsx
+++ b/PublicCustomerApp/src/python/translation.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2849" uniqueCount="2730">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2867" uniqueCount="2748">
   <si>
     <t>key</t>
   </si>
@@ -8215,6 +8215,60 @@
   </si>
   <si>
     <t>Your vehicle is still under approval.</t>
+  </si>
+  <si>
+    <t>ride_cancelled_by_driver</t>
+  </si>
+  <si>
+    <t>Ride Cancelled By Driver</t>
+  </si>
+  <si>
+    <t>ride_cancelled_by_passenger</t>
+  </si>
+  <si>
+    <t>Ride Cancelled By Passenger</t>
+  </si>
+  <si>
+    <t>refresh_to_get_driver_details</t>
+  </si>
+  <si>
+    <t>Refresh to get driver details</t>
+  </si>
+  <si>
+    <t>driver_access_logout_confirm_title</t>
+  </si>
+  <si>
+    <t>Confirm Driver Login</t>
+  </si>
+  <si>
+    <t>driver_access_logout_confirm_message</t>
+  </si>
+  <si>
+    <t>We'll log you out of the customer app so you can sign in as a driver. Continue?</t>
+  </si>
+  <si>
+    <t>driver_access_logout_confirm_cancel_button</t>
+  </si>
+  <si>
+    <t>Stay in Customer App</t>
+  </si>
+  <si>
+    <t>driver_access_logout_confirm_confirm_button</t>
+  </si>
+  <si>
+    <t>Yes, Log Out</t>
+  </si>
+  <si>
+    <t>session_expired</t>
+  </si>
+  <si>
+    <t>Session Expired</t>
+  </si>
+  <si>
+    <t>session_expired_message</t>
+  </si>
+  <si>
+    <t>Your session has expired. Please log in again.</t>
   </si>
 </sst>
 </file>
@@ -8700,8 +8754,8 @@
         <v>உங்கள் கட்டணத்தை பேசி, நம்ம ஊரு டாக்ஸி® செயலியுடன் பிக்-அப் இடத்தைப் பகிர்ந்து கொள்ளச் சொல்லுங்கள். அறிவிப்பு மூலம் பிக்-அப் இடத்தைப் பெற்று, பயணத்தைத் தொடங்க அதை ஏற்றுக்கொள்ளுங்கள்.</v>
       </c>
       <c r="D5" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B5, ""en"", ""hi"")"),"किराया तय करें और उनसे Namma Ooru Taxi ® ऐप के ज़रिए पिकअप लोकेशन शेयर करने के लिए कहें। नोटिफिकेशन के ज़रिए पिकअप लोकेशन मिलने पर उसे स्वीकार करके यात्रा शुरू करें।")</f>
-        <v>किराया तय करें और उनसे Namma Ooru Taxi ® ऐप के ज़रिए पिकअप लोकेशन शेयर करने के लिए कहें। नोटिफिकेशन के ज़रिए पिकअप लोकेशन मिलने पर उसे स्वीकार करके यात्रा शुरू करें।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B5, ""en"", ""hi"")"),"किराया तय कर लें और उनसे Namma Ooru Taxi ® ऐप के ज़रिए पिकअप लोकेशन शेयर करने के लिए कहें। नोटिफिकेशन के ज़रिए पिकअप लोकेशन मिलने पर उसे स्वीकार करके यात्रा शुरू करें।")</f>
+        <v>किराया तय कर लें और उनसे Namma Ooru Taxi ® ऐप के ज़रिए पिकअप लोकेशन शेयर करने के लिए कहें। नोटिफिकेशन के ज़रिए पिकअप लोकेशन मिलने पर उसे स्वीकार करके यात्रा शुरू करें।</v>
       </c>
       <c r="E5" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B5, ""en"", ""kn"")"),"ನಿಮ್ಮ ದರವನ್ನು ಮಾತುಕತೆ ಮಾಡಿ ಮತ್ತು ನಮ್ಮ ಊರು ಟ್ಯಾಕ್ಸಿ® ಅಪ್ಲಿಕೇಶನ್‌ನೊಂದಿಗೆ ಪಿಕಪ್ ಸ್ಥಳವನ್ನು ಹಂಚಿಕೊಳ್ಳಲು ಅವರನ್ನು ಕೇಳಿ. ಅಧಿಸೂಚನೆಯ ಮೂಲಕ ಪಿಕಪ್ ಸ್ಥಳವನ್ನು ಸ್ವೀಕರಿಸಿ ಮತ್ತು ಪ್ರಯಾಣವನ್ನು ಪ್ರಾರಂಭಿಸಲು ಅದನ್ನು ಸ್ವೀಕರಿಸಿ.")</f>
@@ -8712,8 +8766,8 @@
         <v>നിങ്ങളുടെ നിരക്ക് ചർച്ച ചെയ്ത് നമ്മ ഊരു ടാക്സി® ആപ്പുമായി പിക്കപ്പ് ലൊക്കേഷൻ പങ്കിടാൻ ആവശ്യപ്പെടുക. അറിയിപ്പ് വഴി പിക്ക്-അപ്പ് ലൊക്കേഷൻ സ്വീകരിച്ച് യാത്ര ആരംഭിക്കുക.</v>
       </c>
       <c r="G5" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B5, ""en"", ""te"")"),"మీ రేటును బేరసారాలు చేసి, నమ్మ ఊరు టాక్సీ® యాప్‌తో పికప్ లొకేషన్‌ను షేర్ చేయమని వారిని అడగండి. నోటిఫికేషన్ ద్వారా పికప్ లొకేషన్‌ను స్వీకరించి, ట్రిప్ ప్రారంభించడానికి దానిని అంగీకరించండి.")</f>
-        <v>మీ రేటును బేరసారాలు చేసి, నమ్మ ఊరు టాక్సీ® యాప్‌తో పికప్ లొకేషన్‌ను షేర్ చేయమని వారిని అడగండి. నోటిఫికేషన్ ద్వారా పికప్ లొకేషన్‌ను స్వీకరించి, ట్రిప్ ప్రారంభించడానికి దానిని అంగీకరించండి.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B5, ""en"", ""te"")"),"మీ రేటును బేరం చేసి, నమ్మ ఊరు టాక్సీ® యాప్‌తో పికప్ లొకేషన్‌ను షేర్ చేయమని వారిని అడగండి. నోటిఫికేషన్ ద్వారా పికప్ లొకేషన్‌ను స్వీకరించి, ట్రిప్ ప్రారంభించడానికి దానిని అంగీకరించండి.")</f>
+        <v>మీ రేటును బేరం చేసి, నమ్మ ఊరు టాక్సీ® యాప్‌తో పికప్ లొకేషన్‌ను షేర్ చేయమని వారిని అడగండి. నోటిఫికేషన్ ద్వారా పికప్ లొకేషన్‌ను స్వీకరించి, ట్రిప్ ప్రారంభించడానికి దానిని అంగీకరించండి.</v>
       </c>
     </row>
     <row r="6">
@@ -8728,8 +8782,8 @@
         <v>பயணத்தை உறுதிசெய்து தொடங்க வாடிக்கையாளரைத் தொடர்பு கொண்டதை உறுதிப்படுத்திக் கொள்ளுங்கள்.</v>
       </c>
       <c r="D6" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B6, ""en"", ""hi"")"),"ग्राहक से संपर्क करके यात्रा की पुष्टि कर लें और यात्रा शुरू करें।")</f>
-        <v>ग्राहक से संपर्क करके यात्रा की पुष्टि कर लें और यात्रा शुरू करें।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B6, ""en"", ""hi"")"),"ग्राहक से संपर्क करके यात्रा की पुष्टि अवश्य कर लें और यात्रा शुरू करें।")</f>
+        <v>ग्राहक से संपर्क करके यात्रा की पुष्टि अवश्य कर लें और यात्रा शुरू करें।</v>
       </c>
       <c r="E6" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B6, ""en"", ""kn"")"),"ಖಚಿತಪಡಿಸಲು ಮತ್ತು ಪ್ರಯಾಣವನ್ನು ಪ್ರಾರಂಭಿಸಲು ನೀವು ಗ್ರಾಹಕರನ್ನು ಸಂಪರ್ಕಿಸಿದ್ದೀರಿ ಎಂದು ಖಚಿತಪಡಿಸಿಕೊಳ್ಳಿ.")</f>
@@ -9310,8 +9364,8 @@
         <v>60</v>
       </c>
       <c r="C27" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B27, ""en"", ""ta"")"),"தயவுசெய்து செல்லுபடியாகும் உரிம எண்ணை உள்ளிடவும் (TN01 20110012345)")</f>
-        <v>தயவுசெய்து செல்லுபடியாகும் உரிம எண்ணை உள்ளிடவும் (TN01 20110012345)</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B27, ""en"", ""ta"")"),"செல்லுபடியாகும் உரிம எண்ணை (TN01 20110012345) உள்ளிடவும்.")</f>
+        <v>செல்லுபடியாகும் உரிம எண்ணை (TN01 20110012345) உள்ளிடவும்.</v>
       </c>
       <c r="D27" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B27, ""en"", ""hi"")"),"कृपया वैध लाइसेंस नंबर दर्ज करें (TN01 20110012345)")</f>
@@ -9836,8 +9890,8 @@
         <v>ದಯವಿಟ್ಟು ವಾಹನ ಮಾದರಿಯನ್ನು ನಮೂದಿಸಿ.</v>
       </c>
       <c r="F45" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B45, ""en"", ""ml"")"),"ദയവായി വാഹന മോഡൽ നൽകുക.")</f>
-        <v>ദയവായി വാഹന മോഡൽ നൽകുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B45, ""en"", ""ml"")"),"വാഹന മോഡൽ നൽകുക.")</f>
+        <v>വാഹന മോഡൽ നൽകുക.</v>
       </c>
       <c r="G45" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B45, ""en"", ""te"")"),"దయచేసి వాహన నమూనాను నమోదు చేయండి.")</f>
@@ -10524,8 +10578,8 @@
         <v>146</v>
       </c>
       <c r="C70" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B70, ""en"", ""ta"")"),"வண்ணத்தைத் தேர்ந்தெடுக்கவும்")</f>
-        <v>வண்ணத்தைத் தேர்ந்தெடுக்கவும்</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B70, ""en"", ""ta"")"),"நிறத்தைத் தேர்ந்தெடுக்கவும்")</f>
+        <v>நிறத்தைத் தேர்ந்தெடுக்கவும்</v>
       </c>
       <c r="D70" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B70, ""en"", ""hi"")"),"रंग चुनो")</f>
@@ -12539,9 +12593,9 @@
       </c>
       <c r="F141" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B141, ""en"", ""ml"")"),"ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
-ക്ഷമയ്ക്ക് നന്ദി.")</f>
+നിങ്ങളുടെ ക്ഷമയ്ക്ക് നന്ദി.")</f>
         <v>ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
-ക്ഷമയ്ക്ക് നന്ദി.</v>
+നിങ്ങളുടെ ക്ഷമയ്ക്ക് നന്ദി.</v>
       </c>
       <c r="G141" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B141, ""en"", ""te"")"),"టాక్సీని ధృవీకరించడానికి మరియు వాటిని ఆమోదించడానికి మేము తీవ్రంగా కృషి చేస్తున్నాము. కాబట్టి దయచేసి ఆమోద ప్రక్రియకు కొంత సమయం పడుతుందని అర్థం చేసుకోండి.
@@ -13078,8 +13132,8 @@
         <v>ನೋಂದಾಯಿತ ಫೋನ್ ಸಂಖ್ಯೆಗೆ OTP ಯಶಸ್ವಿಯಾಗಿ ಮರು ಕಳುಹಿಸಲಾಗಿದೆ.</v>
       </c>
       <c r="F160" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B160, ""en"", ""ml"")"),"രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വീണ്ടും അയച്ചു.")</f>
-        <v>രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വീണ്ടും അയച്ചു.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B160, ""en"", ""ml"")"),"രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വിജയകരമായി വീണ്ടും അയച്ചു.")</f>
+        <v>രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വിജയകരമായി വീണ്ടും അയച്ചു.</v>
       </c>
       <c r="G160" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B160, ""en"", ""te"")"),"రిజిస్టర్డ్ ఫోన్ నంబర్‌కు OTP విజయవంతంగా తిరిగి పంపబడింది.")</f>
@@ -13395,9 +13449,9 @@
       </c>
       <c r="F171" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B171, ""en"", ""ml"")"),"ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
-ക്ഷമയ്ക്ക് നന്ദി.")</f>
+നിങ്ങളുടെ ക്ഷമയ്ക്ക് നന്ദി.")</f>
         <v>ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
-ക്ഷമയ്ക്ക് നന്ദി.</v>
+നിങ്ങളുടെ ക്ഷമയ്ക്ക് നന്ദി.</v>
       </c>
       <c r="G171" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B171, ""en"", ""te"")"),"టాక్సీని ధృవీకరించడానికి మరియు వాటిని ఆమోదించడానికి మేము తీవ్రంగా కృషి చేస్తున్నాము. కాబట్టి దయచేసి ఆమోద ప్రక్రియకు కొంత సమయం పడుతుందని అర్థం చేసుకోండి.
@@ -14094,8 +14148,8 @@
         <v>यदि सत्यापन में अधिक समय लगता है तो सहायता टीम से संपर्क करें।</v>
       </c>
       <c r="E196" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B196, ""en"", ""kn"")"),"ಪರಿಶೀಲನೆಗೆ ಹೆಚ್ಚಿನ ಸಮಯ ತೆಗೆದುಕೊಂಡರೆ ಬೆಂಬಲವನ್ನು ಸಂಪರ್ಕಿಸಿ")</f>
-        <v>ಪರಿಶೀಲನೆಗೆ ಹೆಚ್ಚಿನ ಸಮಯ ತೆಗೆದುಕೊಂಡರೆ ಬೆಂಬಲವನ್ನು ಸಂಪರ್ಕಿಸಿ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B196, ""en"", ""kn"")"),"ಪರಿಶೀಲನೆಗೆ ಹೆಚ್ಚು ಸಮಯ ತೆಗೆದುಕೊಂಡರೆ ಬೆಂಬಲವನ್ನು ಸಂಪರ್ಕಿಸಿ")</f>
+        <v>ಪರಿಶೀಲನೆಗೆ ಹೆಚ್ಚು ಸಮಯ ತೆಗೆದುಕೊಂಡರೆ ಬೆಂಬಲವನ್ನು ಸಂಪರ್ಕಿಸಿ</v>
       </c>
       <c r="F196" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B196, ""en"", ""ml"")"),"പരിശോധിച്ചുറപ്പിക്കലിന് കൂടുതൽ സമയമെടുക്കുന്നുവെങ്കിൽ പിന്തുണയുമായി ബന്ധപ്പെടുക.")</f>
@@ -14766,8 +14820,8 @@
         <v>स्थिति का चयन करें</v>
       </c>
       <c r="E220" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B220, ""en"", ""kn"")"),"ಸ್ಥಿತಿಯನ್ನು ಆಯ್ಕೆಮಾಡಿ")</f>
-        <v>ಸ್ಥಿತಿಯನ್ನು ಆಯ್ಕೆಮಾಡಿ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B220, ""en"", ""kn"")"),"ಸ್ಥಿತಿ ಆಯ್ಕೆಮಾಡಿ")</f>
+        <v>ಸ್ಥಿತಿ ಆಯ್ಕೆಮಾಡಿ</v>
       </c>
       <c r="F220" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B220, ""en"", ""ml"")"),"സ്റ്റാറ്റസ് തിരഞ്ഞെടുക്കുക")</f>
@@ -16562,8 +16616,8 @@
         <v>ನಿಮ್ಮಲ್ಲಿ ಬಾಕಿ ಮೊತ್ತವಿದ್ದರೆ, ದಯವಿಟ್ಟು ಮುಂಚಿತವಾಗಿ ಎಲ್ಲಾ ಬಾಕಿ ಮೊತ್ತವನ್ನು ಪಾವತಿಸಿ.</v>
       </c>
       <c r="F284" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B284, ""en"", ""ml"")"),"കുടിശ്ശിക തുക ബാക്കിയുണ്ടെങ്കിൽ ദയവായി എല്ലാ കുടിശ്ശികയും മുൻകൂട്ടി തീർക്കുക.")</f>
-        <v>കുടിശ്ശിക തുക ബാക്കിയുണ്ടെങ്കിൽ ദയവായി എല്ലാ കുടിശ്ശികയും മുൻകൂട്ടി തീർക്കുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B284, ""en"", ""ml"")"),"നിങ്ങളുടെ കുടിശ്ശിക തുക ബാക്കിയുണ്ടെങ്കിൽ, ദയവായി എല്ലാ കുടിശ്ശികകളും മുൻകൂട്ടി തീർക്കുക.")</f>
+        <v>നിങ്ങളുടെ കുടിശ്ശിക തുക ബാക്കിയുണ്ടെങ്കിൽ, ദയവായി എല്ലാ കുടിശ്ശികകളും മുൻകൂട്ടി തീർക്കുക.</v>
       </c>
       <c r="G284" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B284, ""en"", ""te"")"),"మీకు ఇంకా బకాయిలు ఉంటే, దయచేసి ముందుగా అన్ని బకాయిలను చెల్లించండి.")</f>
@@ -17645,8 +17699,8 @@
         <v>மோசமான போக்குவரத்து அல்லது வானிலை</v>
       </c>
       <c r="D323" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B323, ""en"", ""hi"")"),"यातायात की खराब स्थिति या मौसम की स्थिति")</f>
-        <v>यातायात की खराब स्थिति या मौसम की स्थिति</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B323, ""en"", ""hi"")"),"खराब यातायात या खराब मौसम की स्थिति")</f>
+        <v>खराब यातायात या खराब मौसम की स्थिति</v>
       </c>
       <c r="E323" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B323, ""en"", ""kn"")"),"ಕಳಪೆ ಸಂಚಾರ ಅಥವಾ ಹವಾಮಾನ ಪರಿಸ್ಥಿತಿಗಳು")</f>
@@ -18121,8 +18175,8 @@
         <v>உங்கள் சிக்கலை விவரிக்கவும், அதைத் தீர்க்க நாங்கள் உங்களுக்கு உதவுவோம்.</v>
       </c>
       <c r="D340" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B340, ""en"", ""hi"")"),"अपनी समस्या का वर्णन करें और हम इसे हल करने में आपकी सहायता करेंगे।")</f>
-        <v>अपनी समस्या का वर्णन करें और हम इसे हल करने में आपकी सहायता करेंगे।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B340, ""en"", ""hi"")"),"अपनी समस्या का वर्णन करें, हम उसे हल करने में आपकी सहायता करेंगे।")</f>
+        <v>अपनी समस्या का वर्णन करें, हम उसे हल करने में आपकी सहायता करेंगे।</v>
       </c>
       <c r="E340" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B340, ""en"", ""kn"")"),"ನಿಮ್ಮ ಸಮಸ್ಯೆಯನ್ನು ವಿವರಿಸಿ, ಅದನ್ನು ಪರಿಹರಿಸಲು ನಾವು ನಿಮಗೆ ಸಹಾಯ ಮಾಡುತ್ತೇವೆ.")</f>
@@ -18889,8 +18943,8 @@
         <v>ഈ പ്രവർത്തനം പഴയപടിയാക്കാൻ കഴിയില്ല - ഇല്ലാതാക്കിയ ഡാറ്റ വീണ്ടെടുക്കാൻ കഴിയില്ല.</v>
       </c>
       <c r="G367" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B367, ""en"", ""te"")"),"ఈ చర్యను రద్దు చేయలేము - తొలగించబడిన డేటాను తిరిగి పొందడం సాధ్యం కాదు.")</f>
-        <v>ఈ చర్యను రద్దు చేయలేము - తొలగించబడిన డేటాను తిరిగి పొందడం సాధ్యం కాదు.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B367, ""en"", ""te"")"),"ఈ చర్యను రద్దు చేయడం సాధ్యం కాదు - తొలగించబడిన డేటాను తిరిగి పొందడం సాధ్యం కాదు.")</f>
+        <v>ఈ చర్యను రద్దు చేయడం సాధ్యం కాదు - తొలగించబడిన డేటాను తిరిగి పొందడం సాధ్యం కాదు.</v>
       </c>
     </row>
     <row r="368">
@@ -19153,8 +19207,8 @@
         <v>732</v>
       </c>
       <c r="C377" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B377, ""en"", ""ta"")"),"வாகன ஆர்சி ஆவண பின்புறம்")</f>
-        <v>வாகன ஆர்சி ஆவண பின்புறம்</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B377, ""en"", ""ta"")"),"வாகன ஆர்.சி. ஆவணத்தின் பின்புறம்")</f>
+        <v>வாகன ஆர்.சி. ஆவணத்தின் பின்புறம்</v>
       </c>
       <c r="D377" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B377, ""en"", ""hi"")"),"वाहन आरसी दस्तावेज़ का पिछला भाग")</f>
@@ -19997,8 +20051,8 @@
         <v>பயன்பாடு திறக்கப்படாதபோதும் கூட உங்கள் இருப்பிடத்தைக் கண்காணிக்க NOT க்கு பின்னணி இருப்பிட அனுமதி தேவையில்லை. இது தொடர்ச்சியான கண்காணிப்பை அனுமதிக்கிறது மற்றும் எல்லா நேரங்களிலும் துல்லியமான இருப்பிடத் தரவு சேகரிக்கப்படுவதை உறுதி செய்கிறது.</v>
       </c>
       <c r="D407" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B407, ""en"", ""hi"")"),"NOT ऐप के बंद होने पर भी आपकी लोकेशन ट्रैक करने के लिए बैकग्राउंड लोकेशन परमिशन की आवश्यकता होती है। इससे लगातार ट्रैकिंग संभव होती है और यह सुनिश्चित होता है कि हर समय सटीक लोकेशन डेटा एकत्र किया जाए।")</f>
-        <v>NOT ऐप के बंद होने पर भी आपकी लोकेशन ट्रैक करने के लिए बैकग्राउंड लोकेशन परमिशन की आवश्यकता होती है। इससे लगातार ट्रैकिंग संभव होती है और यह सुनिश्चित होता है कि हर समय सटीक लोकेशन डेटा एकत्र किया जाए।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B407, ""en"", ""hi"")"),"NOT ऐप को आपके स्थान को ट्रैक करने के लिए बैकग्राउंड लोकेशन अनुमति की आवश्यकता होती है, भले ही ऐप खुला न हो। इससे निरंतर ट्रैकिंग संभव होती है और यह सुनिश्चित होता है कि हर समय सटीक स्थान डेटा एकत्र किया जाए।")</f>
+        <v>NOT ऐप को आपके स्थान को ट्रैक करने के लिए बैकग्राउंड लोकेशन अनुमति की आवश्यकता होती है, भले ही ऐप खुला न हो। इससे निरंतर ट्रैकिंग संभव होती है और यह सुनिश्चित होता है कि हर समय सटीक स्थान डेटा एकत्र किया जाए।</v>
       </c>
       <c r="E407" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B407, ""en"", ""kn"")"),"ಅಪ್ಲಿಕೇಶನ್ ತೆರೆದಿಲ್ಲದಿದ್ದರೂ ಸಹ ನಿಮ್ಮ ಸ್ಥಳವನ್ನು ಟ್ರ್ಯಾಕ್ ಮಾಡಲು NOT ಗೆ ಹಿನ್ನೆಲೆ ಸ್ಥಳ ಅನುಮತಿ ಅಗತ್ಯವಿಲ್ಲ. ಇದು ನಿರಂತರ ಟ್ರ್ಯಾಕಿಂಗ್‌ಗೆ ಅವಕಾಶ ನೀಡುತ್ತದೆ ಮತ್ತು ಎಲ್ಲಾ ಸಮಯದಲ್ಲೂ ನಿಖರವಾದ ಸ್ಥಳ ಡೇಟಾವನ್ನು ಸಂಗ್ರಹಿಸಲಾಗಿದೆ ಎಂದು ಖಚಿತಪಡಿಸುತ್ತದೆ.")</f>
@@ -21069,8 +21123,8 @@
         <v>ಸಂಪರ್ಕಿಸಿ</v>
       </c>
       <c r="F445" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B445, ""en"", ""ml"")"),"ബന്ധപ്പെടുക")</f>
-        <v>ബന്ധപ്പെടുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B445, ""en"", ""ml"")"),"വാര്ത്താവിനിമയം")</f>
+        <v>വാര്ത്താവിനിമയം</v>
       </c>
       <c r="G445" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B445, ""en"", ""te"")"),"సంప్రదించండి")</f>
@@ -21286,8 +21340,8 @@
         <v>अलग हुए</v>
       </c>
       <c r="E453" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B453, ""en"", ""kn"")"),"ಬೇರೆಡೆಗೆ ತಿರುಗಿತು")</f>
-        <v>ಬೇರೆಡೆಗೆ ತಿರುಗಿತು</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B453, ""en"", ""kn"")"),"ವಿಭಾಗಿಸಲಾಗಿದೆ")</f>
+        <v>ವಿಭಾಗಿಸಲಾಗಿದೆ</v>
       </c>
       <c r="F453" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B453, ""en"", ""ml"")"),"വിഘടിച്ചു")</f>
@@ -22316,8 +22370,8 @@
         <v>ನಿಲ್ಲಿಸುವುದನ್ನು ದೃಢೀಕರಿಸಿ {ನಿಲುಗಡೆ}</v>
       </c>
       <c r="F491" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B491, ""en"", ""ml"")"),"നിർത്തുക {നിർത്തുക} സ്ഥിരീകരിക്കുക")</f>
-        <v>നിർത്തുക {നിർത്തുക} സ്ഥിരീകരിക്കുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B491, ""en"", ""ml"")"),"നിർത്തുക സ്ഥിരീകരിക്കുക {നിർത്തുക}")</f>
+        <v>നിർത്തുക സ്ഥിരീകരിക്കുക {നിർത്തുക}</v>
       </c>
       <c r="G491" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B491, ""en"", ""te"")"),"ఆపు {stop} ని నిర్ధారించండి")</f>
@@ -24294,8 +24348,8 @@
         <v>നമ്മ ഊരു ടാക്സി ഡ്രൈവർ ആപ്പ് സൈൻ അപ്പ് ചെയ്യുക</v>
       </c>
       <c r="G564" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B564, ""en"", ""te"")"),"సైన్అప్ నమ్మ ఊరు టాక్సీ డ్రైవర్ యాప్")</f>
-        <v>సైన్అప్ నమ్మ ఊరు టాక్సీ డ్రైవర్ యాప్</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B564, ""en"", ""te"")"),"సైన్ అప్ నమ్మ ఊరు టాక్సీ డ్రైవర్ యాప్")</f>
+        <v>సైన్ అప్ నమ్మ ఊరు టాక్సీ డ్రైవర్ యాప్</v>
       </c>
     </row>
     <row r="565">
@@ -26588,8 +26642,8 @@
         <v>ಸ್ಥಳವನ್ನು ಅಳಿಸಲು ವಿಫಲವಾಗಿದೆ. ದಯವಿಟ್ಟು ಮತ್ತೆ ಪ್ರಯತ್ನಿಸಿ.</v>
       </c>
       <c r="F649" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B649, ""en"", ""ml"")"),"സ്ഥലം ഇല്ലാതാക്കുന്നതിൽ പരാജയപ്പെട്ടു. വീണ്ടും ശ്രമിക്കുക.")</f>
-        <v>സ്ഥലം ഇല്ലാതാക്കുന്നതിൽ പരാജയപ്പെട്ടു. വീണ്ടും ശ്രമിക്കുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B649, ""en"", ""ml"")"),"സ്ഥലം ഇല്ലാതാക്കാനായില്ല. വീണ്ടും ശ്രമിക്കുക.")</f>
+        <v>സ്ഥലം ഇല്ലാതാക്കാനായില്ല. വീണ്ടും ശ്രമിക്കുക.</v>
       </c>
       <c r="G649" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B649, ""en"", ""te"")"),"స్థలాన్ని తొలగించడంలో విఫలమైంది. దయచేసి మళ్ళీ ప్రయత్నించండి.")</f>
@@ -26970,8 +27024,8 @@
         <v>യാത്രാക്കൂലി വളരെ കൂടുതലാണ് (സർജ്)</v>
       </c>
       <c r="G663" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B663, ""en"", ""te"")"),"ఛార్జీ చాలా ఎక్కువగా ఉంది (పెరుగుదల)")</f>
-        <v>ఛార్జీ చాలా ఎక్కువగా ఉంది (పెరుగుదల)</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B663, ""en"", ""te"")"),"ఛార్జీ చాలా ఎక్కువగా ఉంది (సర్జ్)")</f>
+        <v>ఛార్జీ చాలా ఎక్కువగా ఉంది (సర్జ్)</v>
       </c>
     </row>
     <row r="664">
@@ -30174,8 +30228,8 @@
         <v>कोई सुरक्षित स्थान नहीं</v>
       </c>
       <c r="E782" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B782, ""en"", ""kn"")"),"ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ")</f>
-        <v>ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B782, ""en"", ""kn"")"),"ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ.")</f>
+        <v>ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ.</v>
       </c>
       <c r="F782" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B782, ""en"", ""ml"")"),"സംരക്ഷിച്ച സ്ഥലങ്ങളൊന്നുമില്ല.")</f>
@@ -30197,8 +30251,8 @@
         <v>1829</v>
       </c>
       <c r="D783" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B783, ""en"", ""hi"")"),"रात में गाड़ी चलाने वाले ड्राइवर उपलब्ध नहीं हैं")</f>
-        <v>रात में गाड़ी चलाने वाले ड्राइवर उपलब्ध नहीं हैं</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B783, ""en"", ""hi"")"),"रात में ड्राइवर उपलब्ध नहीं हैं")</f>
+        <v>रात में ड्राइवर उपलब्ध नहीं हैं</v>
       </c>
       <c r="E783" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B783, ""en"", ""kn"")"),"ರಾತ್ರಿ ಚಾಲಕರು ಲಭ್ಯವಿಲ್ಲ.")</f>
@@ -30872,8 +30926,8 @@
         <v>1902</v>
       </c>
       <c r="D808" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B808, ""en"", ""hi"")"),"यात्रा में देरी का उदाहरण")</f>
-        <v>यात्रा में देरी का उदाहरण</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B808, ""en"", ""hi"")"),"यात्रा में देरी का चित्रण")</f>
+        <v>यात्रा में देरी का चित्रण</v>
       </c>
       <c r="E808" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B808, ""en"", ""kn"")"),"ಪ್ರಯಾಣದ ಬಾಕಿ ಇರುವ ವಿವರಣೆ")</f>
@@ -31798,8 +31852,8 @@
         <v>कृपया आपातकालीन संपर्क चुनें</v>
       </c>
       <c r="E842" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B842, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ತುರ್ತು ಸಂಪರ್ಕಗಳನ್ನು ಆಯ್ಕೆಮಾಡಿ")</f>
-        <v>ದಯವಿಟ್ಟು ತುರ್ತು ಸಂಪರ್ಕಗಳನ್ನು ಆಯ್ಕೆಮಾಡಿ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B842, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ತುರ್ತು ಸಂಪರ್ಕಗಳನ್ನು ಆಯ್ಕೆಮಾಡಿ.")</f>
+        <v>ದಯವಿಟ್ಟು ತುರ್ತು ಸಂಪರ್ಕಗಳನ್ನು ಆಯ್ಕೆಮಾಡಿ.</v>
       </c>
       <c r="F842" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B842, ""en"", ""ml"")"),"ദയവായി അടിയന്തര കോൺടാക്റ്റുകൾ തിരഞ്ഞെടുക്കുക.")</f>
@@ -31960,8 +32014,8 @@
         <v>कृपया पुन: प्रयास करें</v>
       </c>
       <c r="E848" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B848, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ಮತ್ತೆ ಪ್ರಯತ್ನಿಸಿ")</f>
-        <v>ದಯವಿಟ್ಟು ಮತ್ತೆ ಪ್ರಯತ್ನಿಸಿ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B848, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ಮತ್ತೆ ಪ್ರಯತ್ನಿಸಿ.")</f>
+        <v>ದಯವಿಟ್ಟು ಮತ್ತೆ ಪ್ರಯತ್ನಿಸಿ.</v>
       </c>
       <c r="F848" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B848, ""en"", ""ml"")"),"ദയവായി വീണ്ടും ശ്രമിക്കുക.")</f>
@@ -32631,8 +32685,8 @@
         <v>2083</v>
       </c>
       <c r="D873" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B873, ""en"", ""hi"")"),"राइड रद्द कर दी गई")</f>
-        <v>राइड रद्द कर दी गई</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B873, ""en"", ""hi"")"),"राइड रद्द हो गई")</f>
+        <v>राइड रद्द हो गई</v>
       </c>
       <c r="E873" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B873, ""en"", ""kn"")"),"ಸವಾರಿ ರದ್ದುಗೊಳಿಸಲಾಗಿದೆ")</f>
@@ -32875,8 +32929,8 @@
         <v>2108</v>
       </c>
       <c r="D882" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B882, ""en"", ""hi"")"),"सवारी उठा ली गई")</f>
-        <v>सवारी उठा ली गई</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B882, ""en"", ""hi"")"),"सवारी को पिकअप कर लिया गया")</f>
+        <v>सवारी को पिकअप कर लिया गया</v>
       </c>
       <c r="E882" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B882, ""en"", ""kn"")"),"ಸವಾರಿ ಎತ್ತಿಕೊಳ್ಳಲಾಗಿದೆ")</f>
@@ -32991,8 +33045,8 @@
         <v>ಸವಾರಿಯನ್ನು ಮಧ್ಯದಲ್ಲಿ ರದ್ದುಗೊಳಿಸಲಾಗಿದೆ.</v>
       </c>
       <c r="F886" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B886, ""en"", ""ml"")"),"യാത്ര പകുതി വഴിയിൽ വെച്ച് റദ്ദാക്കി.")</f>
-        <v>യാത്ര പകുതി വഴിയിൽ വെച്ച് റദ്ദാക്കി.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B886, ""en"", ""ml"")"),"യാത്ര പകുതി വഴിയിൽ റദ്ദാക്കി.")</f>
+        <v>യാത്ര പകുതി വഴിയിൽ റദ്ദാക്കി.</v>
       </c>
       <c r="G886" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B886, ""en"", ""te"")"),"రైడ్ మధ్యలో రద్దు చేయబడింది")</f>
@@ -33450,8 +33504,8 @@
         <v>ವೇಳಾಪಟ್ಟಿ</v>
       </c>
       <c r="F903" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B903, ""en"", ""ml"")"),"ഷെഡ്യൂൾ")</f>
-        <v>ഷെഡ്യൂൾ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B903, ""en"", ""ml"")"),"പട്ടിക")</f>
+        <v>പട്ടിക</v>
       </c>
       <c r="G903" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B903, ""en"", ""te"")"),"షెడ్యూల్")</f>
@@ -33670,8 +33724,8 @@
         <v>പിക്കപ്പ് ലൊക്കേഷൻ തിരയുക</v>
       </c>
       <c r="G911" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B911, ""en"", ""te"")"),"పికప్ స్థానాన్ని శోధించండి")</f>
-        <v>పికప్ స్థానాన్ని శోధించండి</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B911, ""en"", ""te"")"),"పికప్ లొకేషన్‌ను శోధించండి")</f>
+        <v>పికప్ లొకేషన్‌ను శోధించండి</v>
       </c>
     </row>
     <row r="912">
@@ -34641,8 +34695,8 @@
         <v>ಚಾಲಕ ತಡವಾಗಿ ಬಂದಿರುವುದು</v>
       </c>
       <c r="F947" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B947, ""en"", ""ml"")"),"ഡ്രൈവർ വൈകി എത്തൽ")</f>
-        <v>ഡ്രൈവർ വൈകി എത്തൽ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B947, ""en"", ""ml"")"),"ഡ്രൈവർ വൈകിയുള്ള വരവ്")</f>
+        <v>ഡ്രൈവർ വൈകിയുള്ള വരവ്</v>
       </c>
       <c r="G947" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B947, ""en"", ""te"")"),"డ్రైవర్ ఆలస్యంగా రావడం")</f>
@@ -35362,8 +35416,8 @@
         <v>2359</v>
       </c>
       <c r="D974" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B974, ""en"", ""hi"")"),"अपनी समस्या का वर्णन करें और हम इसे हल करने में आपकी सहायता करेंगे।")</f>
-        <v>अपनी समस्या का वर्णन करें और हम इसे हल करने में आपकी सहायता करेंगे।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B974, ""en"", ""hi"")"),"अपनी समस्या का वर्णन करें, हम उसे हल करने में आपकी सहायता करेंगे।")</f>
+        <v>अपनी समस्या का वर्णन करें, हम उसे हल करने में आपकी सहायता करेंगे।</v>
       </c>
       <c r="E974" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B974, ""en"", ""kn"")"),"ನಿಮ್ಮ ಸಮಸ್ಯೆಯನ್ನು ವಿವರಿಸಿ, ಅದನ್ನು ಪರಿಹರಿಸಲು ನಾವು ನಿಮಗೆ ಸಹಾಯ ಮಾಡುತ್ತೇವೆ.")</f>
@@ -37961,8 +38015,8 @@
         <v>ಈ ಹಂತಗಳನ್ನು ಪೂರ್ಣಗೊಳಿಸಿ ಇದರಿಂದ ನೀವು ಸವಾರಿಗಳನ್ನು ಸ್ವೀಕರಿಸಲು ಪ್ರಾರಂಭಿಸಬಹುದು.</v>
       </c>
       <c r="F1069" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1069, ""en"", ""ml"")"),"റൈഡുകൾ സ്വീകരിക്കാൻ തുടങ്ങുന്നതിന് ഈ ഘട്ടങ്ങൾ പൂർത്തിയാക്കുക.")</f>
-        <v>റൈഡുകൾ സ്വീകരിക്കാൻ തുടങ്ങുന്നതിന് ഈ ഘട്ടങ്ങൾ പൂർത്തിയാക്കുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1069, ""en"", ""ml"")"),"റൈഡുകൾ സ്വീകരിച്ചു തുടങ്ങാൻ ഈ ഘട്ടങ്ങൾ പൂർത്തിയാക്കുക.")</f>
+        <v>റൈഡുകൾ സ്വീകരിച്ചു തുടങ്ങാൻ ഈ ഘട്ടങ്ങൾ പൂർത്തിയാക്കുക.</v>
       </c>
       <c r="G1069" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1069, ""en"", ""te"")"),"ఈ దశలను పూర్తి చేయండి, తద్వారా మీరు రైడ్‌లను అంగీకరించడం ప్రారంభించవచ్చు.")</f>
@@ -38205,8 +38259,8 @@
         <v>இந்த பயன்முறையில் திருத்துதல் முடக்கப்பட்டுள்ளது.</v>
       </c>
       <c r="D1078" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1078, ""en"", ""hi"")"),"इस मोड में संपादन अक्षम है।")</f>
-        <v>इस मोड में संपादन अक्षम है।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1078, ""en"", ""hi"")"),"इस मोड में संपादन की सुविधा अक्षम है।")</f>
+        <v>इस मोड में संपादन की सुविधा अक्षम है।</v>
       </c>
       <c r="E1078" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1078, ""en"", ""kn"")"),"ಈ ಕ್ರಮದಲ್ಲಿ ಸಂಪಾದನೆಯನ್ನು ನಿಷ್ಕ್ರಿಯಗೊಳಿಸಲಾಗಿದೆ.")</f>
@@ -38545,8 +38599,8 @@
         <v>ड्राइवर की फोटो अपलोड करें या कैप्चर करें</v>
       </c>
       <c r="E1090" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1090, ""en"", ""kn"")"),"ಚಾಲಕ ಫೋಟೋ ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ")</f>
-        <v>ಚಾಲಕ ಫೋಟೋ ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1090, ""en"", ""kn"")"),"ಚಾಲಕ ಫೋಟೋವನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ")</f>
+        <v>ಚಾಲಕ ಫೋಟೋವನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ</v>
       </c>
       <c r="F1090" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1090, ""en"", ""ml"")"),"ഡ്രൈവർ ഫോട്ടോ അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ പകർത്തുക")</f>
@@ -38605,8 +38659,8 @@
         <v>ಆಧಾರ್ ಕಾರ್ಡ್ ಅನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ</v>
       </c>
       <c r="F1092" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1092, ""en"", ""ml"")"),"ആധാർ കാർഡ് അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ എടുക്കുക")</f>
-        <v>ആധാർ കാർഡ് അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ എടുക്കുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1092, ""en"", ""ml"")"),"ആധാർ കാർഡ് അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ പിടിച്ചെടുക്കുക")</f>
+        <v>ആധാർ കാർഡ് അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ പിടിച്ചെടുക്കുക</v>
       </c>
       <c r="G1092" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1092, ""en"", ""te"")"),"ఆధార్ కార్డును అప్‌లోడ్ చేయండి లేదా సంగ్రహించండి")</f>
@@ -38847,8 +38901,8 @@
         <v>இந்த பயன்முறையில் திருத்துதல் முடக்கப்பட்டுள்ளது.</v>
       </c>
       <c r="D1101" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1101, ""en"", ""hi"")"),"इस मोड में संपादन अक्षम है।")</f>
-        <v>इस मोड में संपादन अक्षम है।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1101, ""en"", ""hi"")"),"इस मोड में संपादन की सुविधा अक्षम है।")</f>
+        <v>इस मोड में संपादन की सुविधा अक्षम है।</v>
       </c>
       <c r="E1101" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1101, ""en"", ""kn"")"),"ಈ ಕ್ರಮದಲ್ಲಿ ಸಂಪಾದನೆಯನ್ನು ನಿಷ್ಕ್ರಿಯಗೊಳಿಸಲಾಗಿದೆ.")</f>
@@ -39011,8 +39065,8 @@
         <v>2694</v>
       </c>
       <c r="C1107" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1107, ""en"", ""ta"")"),"நிலுவையில் உள்ள நிலுவைத் தொகை")</f>
-        <v>நிலுவையில் உள்ள நிலுவைத் தொகை</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1107, ""en"", ""ta"")"),"நிலுவையில் உள்ள தொகை")</f>
+        <v>நிலுவையில் உள்ள தொகை</v>
       </c>
       <c r="D1107" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1107, ""en"", ""hi"")"),"बकाया राशि")</f>
@@ -39051,8 +39105,8 @@
         <v>ಸವಾರಿಗಳನ್ನು ಸ್ವೀಕರಿಸುವುದನ್ನು ಮುಂದುವರಿಸಲು ನಿಮ್ಮ ಬಾಕಿಗಳನ್ನು ಪಾವತಿಸಿ.</v>
       </c>
       <c r="F1108" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1108, ""en"", ""ml"")"),"റൈഡുകൾ സ്വീകരിക്കുന്നത് തുടരാൻ നിങ്ങളുടെ കുടിശ്ശികകൾ അടയ്ക്കുക.")</f>
-        <v>റൈഡുകൾ സ്വീകരിക്കുന്നത് തുടരാൻ നിങ്ങളുടെ കുടിശ്ശികകൾ അടയ്ക്കുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1108, ""en"", ""ml"")"),"റൈഡുകൾ സ്വീകരിക്കുന്നത് തുടരാൻ നിങ്ങളുടെ കുടിശ്ശിക അടയ്ക്കുക.")</f>
+        <v>റൈഡുകൾ സ്വീകരിക്കുന്നത് തുടരാൻ നിങ്ങളുടെ കുടിശ്ശിക അടയ്ക്കുക.</v>
       </c>
       <c r="G1108" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1108, ""en"", ""te"")"),"రైడ్‌లు అంగీకరించడం కొనసాగించడానికి మీ బకాయిలను క్లియర్ చేయండి.")</f>
@@ -39123,8 +39177,8 @@
         <v>2702</v>
       </c>
       <c r="C1111" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1111, ""en"", ""ta"")"),"அடுத்தது செலுத்த வேண்டிய தேதி")</f>
-        <v>அடுத்தது செலுத்த வேண்டிய தேதி</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1111, ""en"", ""ta"")"),"அடுத்த தேதி")</f>
+        <v>அடுத்த தேதி</v>
       </c>
       <c r="D1111" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1111, ""en"", ""hi"")"),"अगली देय तिथि में")</f>
@@ -39450,9 +39504,9 @@
       </c>
       <c r="F1122" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1122, ""en"", ""ml"")"),"ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
-ക്ഷമയ്ക്ക് നന്ദി.")</f>
+നിങ്ങളുടെ ക്ഷമയ്ക്ക് നന്ദി.")</f>
         <v>ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
-ക്ഷമയ്ക്ക് നന്ദി.</v>
+നിങ്ങളുടെ ക്ഷമയ്ക്ക് നന്ദി.</v>
       </c>
       <c r="G1122" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1122, ""en"", ""te"")"),"టాక్సీని ధృవీకరించడానికి మరియు వాటిని ఆమోదించడానికి మేము తీవ్రంగా కృషి చేస్తున్నాము. కాబట్టి దయచేసి ఆమోద ప్రక్రియకు కొంత సమయం పడుతుందని అర్థం చేసుకోండి.
@@ -39574,67 +39628,256 @@
       </c>
     </row>
     <row r="1127">
-      <c r="A1127" s="4"/>
-      <c r="B1127" s="5"/>
-      <c r="C1127" s="6"/>
-      <c r="D1127" s="6"/>
-      <c r="E1127" s="6"/>
+      <c r="A1127" s="12" t="s">
+        <v>2730</v>
+      </c>
+      <c r="B1127" s="13" t="s">
+        <v>2731</v>
+      </c>
+      <c r="C1127" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1127, ""en"", ""ta"")"),"ஓட்டுநர் சவாரியை ரத்து செய்தார்")</f>
+        <v>ஓட்டுநர் சவாரியை ரத்து செய்தார்</v>
+      </c>
+      <c r="D1127" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1127, ""en"", ""hi"")"),"ड्राइवर द्वारा राइड रद्द कर दी गई")</f>
+        <v>ड्राइवर द्वारा राइड रद्द कर दी गई</v>
+      </c>
+      <c r="E1127" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1127, ""en"", ""kn"")"),"ಚಾಲಕನಿಂದ ಸವಾರಿ ರದ್ದುಗೊಂಡಿದೆ")</f>
+        <v>ಚಾಲಕನಿಂದ ಸವಾರಿ ರದ್ದುಗೊಂಡಿದೆ</v>
+      </c>
+      <c r="F1127" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1127, ""en"", ""ml"")"),"ഡ്രൈവർ റദ്ദാക്കിയ യാത്ര")</f>
+        <v>ഡ്രൈവർ റദ്ദാക്കിയ യാത്ര</v>
+      </c>
+      <c r="G1127" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1127, ""en"", ""te"")"),"డ్రైవర్ ద్వారా రైడ్ రద్దు చేయబడింది")</f>
+        <v>డ్రైవర్ ద్వారా రైడ్ రద్దు చేయబడింది</v>
+      </c>
     </row>
     <row r="1128">
-      <c r="A1128" s="4"/>
-      <c r="B1128" s="5"/>
-      <c r="C1128" s="6"/>
-      <c r="D1128" s="6"/>
-      <c r="E1128" s="6"/>
+      <c r="A1128" s="12" t="s">
+        <v>2732</v>
+      </c>
+      <c r="B1128" s="13" t="s">
+        <v>2733</v>
+      </c>
+      <c r="C1128" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1128, ""en"", ""ta"")"),"பயணியால் ரத்து செய்யப்பட்ட பயணம்")</f>
+        <v>பயணியால் ரத்து செய்யப்பட்ட பயணம்</v>
+      </c>
+      <c r="D1128" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1128, ""en"", ""hi"")"),"यात्री द्वारा यात्रा रद्द कर दी गई")</f>
+        <v>यात्री द्वारा यात्रा रद्द कर दी गई</v>
+      </c>
+      <c r="E1128" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1128, ""en"", ""kn"")"),"ಪ್ರಯಾಣಿಕರಿಂದ ಸವಾರಿ ರದ್ದುಗೊಂಡಿದೆ")</f>
+        <v>ಪ್ರಯಾಣಿಕರಿಂದ ಸವಾರಿ ರದ್ದುಗೊಂಡಿದೆ</v>
+      </c>
+      <c r="F1128" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1128, ""en"", ""ml"")"),"യാത്രക്കാരൻ റദ്ദാക്കിയ യാത്ര")</f>
+        <v>യാത്രക്കാരൻ റദ്ദാക്കിയ യാത്ര</v>
+      </c>
+      <c r="G1128" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1128, ""en"", ""te"")"),"ప్రయాణీకుడు రద్దు చేసిన రైడ్")</f>
+        <v>ప్రయాణీకుడు రద్దు చేసిన రైడ్</v>
+      </c>
     </row>
     <row r="1129">
-      <c r="A1129" s="4"/>
-      <c r="B1129" s="5"/>
-      <c r="C1129" s="6"/>
-      <c r="D1129" s="6"/>
-      <c r="E1129" s="6"/>
+      <c r="A1129" s="12" t="s">
+        <v>2734</v>
+      </c>
+      <c r="B1129" s="13" t="s">
+        <v>2735</v>
+      </c>
+      <c r="C1129" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1129, ""en"", ""ta"")"),"இயக்கி விவரங்களைப் பெற புதுப்பிக்கவும்.")</f>
+        <v>இயக்கி விவரங்களைப் பெற புதுப்பிக்கவும்.</v>
+      </c>
+      <c r="D1129" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1129, ""en"", ""hi"")"),"ड्राइवर की जानकारी प्राप्त करने के लिए पेज को रिफ्रेश करें")</f>
+        <v>ड्राइवर की जानकारी प्राप्त करने के लिए पेज को रिफ्रेश करें</v>
+      </c>
+      <c r="E1129" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1129, ""en"", ""kn"")"),"ಚಾಲಕ ವಿವರಗಳನ್ನು ಪಡೆಯಲು ರಿಫ್ರೆಶ್ ಮಾಡಿ")</f>
+        <v>ಚಾಲಕ ವಿವರಗಳನ್ನು ಪಡೆಯಲು ರಿಫ್ರೆಶ್ ಮಾಡಿ</v>
+      </c>
+      <c r="F1129" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1129, ""en"", ""ml"")"),"ഡ്രൈവർ വിശദാംശങ്ങൾ ലഭിക്കാൻ പുതുക്കുക")</f>
+        <v>ഡ്രൈവർ വിശദാംശങ്ങൾ ലഭിക്കാൻ പുതുക്കുക</v>
+      </c>
+      <c r="G1129" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1129, ""en"", ""te"")"),"డ్రైవర్ వివరాలను పొందడానికి రిఫ్రెష్ చేయండి")</f>
+        <v>డ్రైవర్ వివరాలను పొందడానికి రిఫ్రెష్ చేయండి</v>
+      </c>
     </row>
     <row r="1130">
-      <c r="A1130" s="4"/>
-      <c r="B1130" s="5"/>
-      <c r="C1130" s="6"/>
-      <c r="D1130" s="6"/>
-      <c r="E1130" s="6"/>
+      <c r="A1130" s="12" t="s">
+        <v>2736</v>
+      </c>
+      <c r="B1130" s="13" t="s">
+        <v>2737</v>
+      </c>
+      <c r="C1130" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1130, ""en"", ""ta"")"),"இயக்கி உள்நுழைவை உறுதிப்படுத்தவும்")</f>
+        <v>இயக்கி உள்நுழைவை உறுதிப்படுத்தவும்</v>
+      </c>
+      <c r="D1130" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1130, ""en"", ""hi"")"),"ड्राइवर लॉगिन की पुष्टि करें")</f>
+        <v>ड्राइवर लॉगिन की पुष्टि करें</v>
+      </c>
+      <c r="E1130" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1130, ""en"", ""kn"")"),"ಚಾಲಕ ಲಾಗಿನ್ ಅನ್ನು ದೃಢೀಕರಿಸಿ")</f>
+        <v>ಚಾಲಕ ಲಾಗಿನ್ ಅನ್ನು ದೃಢೀಕರಿಸಿ</v>
+      </c>
+      <c r="F1130" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1130, ""en"", ""ml"")"),"ഡ്രൈവർ ലോഗിൻ സ്ഥിരീകരിക്കുക")</f>
+        <v>ഡ്രൈവർ ലോഗിൻ സ്ഥിരീകരിക്കുക</v>
+      </c>
+      <c r="G1130" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1130, ""en"", ""te"")"),"డ్రైవర్ లాగిన్‌ను నిర్ధారించండి")</f>
+        <v>డ్రైవర్ లాగిన్‌ను నిర్ధారించండి</v>
+      </c>
     </row>
     <row r="1131">
-      <c r="A1131" s="4"/>
-      <c r="B1131" s="5"/>
-      <c r="C1131" s="6"/>
-      <c r="D1131" s="6"/>
-      <c r="E1131" s="6"/>
+      <c r="A1131" s="12" t="s">
+        <v>2738</v>
+      </c>
+      <c r="B1131" s="13" t="s">
+        <v>2739</v>
+      </c>
+      <c r="C1131" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1131, ""en"", ""ta"")"),"நீங்கள் ஒரு ஓட்டுநராக உள்நுழைய, வாடிக்கையாளர் பயன்பாட்டிலிருந்து உங்களை வெளியேற்றுவோம். தொடரவா?")</f>
+        <v>நீங்கள் ஒரு ஓட்டுநராக உள்நுழைய, வாடிக்கையாளர் பயன்பாட்டிலிருந்து உங்களை வெளியேற்றுவோம். தொடரவா?</v>
+      </c>
+      <c r="D1131" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1131, ""en"", ""hi"")"),"हम आपको ग्राहक ऐप से लॉग आउट कर देंगे ताकि आप ड्राइवर के रूप में साइन इन कर सकें। जारी रखें?")</f>
+        <v>हम आपको ग्राहक ऐप से लॉग आउट कर देंगे ताकि आप ड्राइवर के रूप में साइन इन कर सकें। जारी रखें?</v>
+      </c>
+      <c r="E1131" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1131, ""en"", ""kn"")"),"ನೀವು ಡ್ರೈವರ್ ಆಗಿ ಸೈನ್ ಇನ್ ಆಗುವಂತೆ ನಾವು ನಿಮ್ಮನ್ನು ಗ್ರಾಹಕ ಅಪ್ಲಿಕೇಶನ್‌ನಿಂದ ಲಾಗ್ ಔಟ್ ಮಾಡುತ್ತೇವೆ. ಮುಂದುವರಿಸುವುದೇ?")</f>
+        <v>ನೀವು ಡ್ರೈವರ್ ಆಗಿ ಸೈನ್ ಇನ್ ಆಗುವಂತೆ ನಾವು ನಿಮ್ಮನ್ನು ಗ್ರಾಹಕ ಅಪ್ಲಿಕೇಶನ್‌ನಿಂದ ಲಾಗ್ ಔಟ್ ಮಾಡುತ್ತೇವೆ. ಮುಂದುವರಿಸುವುದೇ?</v>
+      </c>
+      <c r="F1131" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1131, ""en"", ""ml"")"),"ഡ്രൈവറായി സൈൻ ഇൻ ചെയ്യാൻ നിങ്ങളെ ഉപഭോക്തൃ ആപ്പിൽ നിന്ന് ഞങ്ങൾ ലോഗ് ഔട്ട് ചെയ്യും. തുടരണോ?")</f>
+        <v>ഡ്രൈവറായി സൈൻ ഇൻ ചെയ്യാൻ നിങ്ങളെ ഉപഭോക്തൃ ആപ്പിൽ നിന്ന് ഞങ്ങൾ ലോഗ് ഔട്ട് ചെയ്യും. തുടരണോ?</v>
+      </c>
+      <c r="G1131" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1131, ""en"", ""te"")"),"మీరు డ్రైవర్‌గా సైన్ ఇన్ అవ్వడానికి వీలుగా మేము మిమ్మల్ని కస్టమర్ యాప్ నుండి లాగ్ అవుట్ చేస్తాము. కొనసాగించాలా?")</f>
+        <v>మీరు డ్రైవర్‌గా సైన్ ఇన్ అవ్వడానికి వీలుగా మేము మిమ్మల్ని కస్టమర్ యాప్ నుండి లాగ్ అవుట్ చేస్తాము. కొనసాగించాలా?</v>
+      </c>
     </row>
     <row r="1132">
-      <c r="A1132" s="4"/>
-      <c r="B1132" s="5"/>
-      <c r="C1132" s="6"/>
-      <c r="D1132" s="6"/>
-      <c r="E1132" s="6"/>
+      <c r="A1132" s="12" t="s">
+        <v>2740</v>
+      </c>
+      <c r="B1132" s="13" t="s">
+        <v>2741</v>
+      </c>
+      <c r="C1132" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1132, ""en"", ""ta"")"),"வாடிக்கையாளர் பயன்பாட்டில் இருங்கள்")</f>
+        <v>வாடிக்கையாளர் பயன்பாட்டில் இருங்கள்</v>
+      </c>
+      <c r="D1132" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1132, ""en"", ""hi"")"),"ग्राहक ऐप में बने रहें")</f>
+        <v>ग्राहक ऐप में बने रहें</v>
+      </c>
+      <c r="E1132" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1132, ""en"", ""kn"")"),"ಗ್ರಾಹಕ ಅಪ್ಲಿಕೇಶನ್‌ನಲ್ಲಿ ಉಳಿಯಿರಿ")</f>
+        <v>ಗ್ರಾಹಕ ಅಪ್ಲಿಕೇಶನ್‌ನಲ್ಲಿ ಉಳಿಯಿರಿ</v>
+      </c>
+      <c r="F1132" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1132, ""en"", ""ml"")"),"ഉപഭോക്തൃ ആപ്പിൽ തുടരുക")</f>
+        <v>ഉപഭോക്തൃ ആപ്പിൽ തുടരുക</v>
+      </c>
+      <c r="G1132" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1132, ""en"", ""te"")"),"కస్టమర్ యాప్‌లో ఉండండి")</f>
+        <v>కస్టమర్ యాప్‌లో ఉండండి</v>
+      </c>
     </row>
     <row r="1133">
-      <c r="A1133" s="4"/>
-      <c r="B1133" s="5"/>
-      <c r="C1133" s="6"/>
-      <c r="D1133" s="6"/>
-      <c r="E1133" s="6"/>
+      <c r="A1133" s="12" t="s">
+        <v>2742</v>
+      </c>
+      <c r="B1133" s="13" t="s">
+        <v>2743</v>
+      </c>
+      <c r="C1133" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1133, ""en"", ""ta"")"),"ஆம், வெளியேறு")</f>
+        <v>ஆம், வெளியேறு</v>
+      </c>
+      <c r="D1133" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1133, ""en"", ""hi"")"),"हां, लॉग आउट करें")</f>
+        <v>हां, लॉग आउट करें</v>
+      </c>
+      <c r="E1133" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1133, ""en"", ""kn"")"),"ಹೌದು, ಲಾಗ್ ಔಟ್ ಮಾಡಿ")</f>
+        <v>ಹೌದು, ಲಾಗ್ ಔಟ್ ಮಾಡಿ</v>
+      </c>
+      <c r="F1133" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1133, ""en"", ""ml"")"),"അതെ, ലോഗ് ഔട്ട് ചെയ്യുക")</f>
+        <v>അതെ, ലോഗ് ഔട്ട് ചെയ്യുക</v>
+      </c>
+      <c r="G1133" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1133, ""en"", ""te"")"),"అవును, లాగ్ అవుట్ చేయి")</f>
+        <v>అవును, లాగ్ అవుట్ చేయి</v>
+      </c>
     </row>
     <row r="1134">
-      <c r="A1134" s="4"/>
-      <c r="B1134" s="5"/>
-      <c r="C1134" s="6"/>
-      <c r="D1134" s="6"/>
-      <c r="E1134" s="6"/>
+      <c r="A1134" s="12" t="s">
+        <v>2744</v>
+      </c>
+      <c r="B1134" s="13" t="s">
+        <v>2745</v>
+      </c>
+      <c r="C1134" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1134, ""en"", ""ta"")"),"அமர்வு காலாவதியானது")</f>
+        <v>அமர்வு காலாவதியானது</v>
+      </c>
+      <c r="D1134" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1134, ""en"", ""hi"")"),"सत्र समाप्त हुआ")</f>
+        <v>सत्र समाप्त हुआ</v>
+      </c>
+      <c r="E1134" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1134, ""en"", ""kn"")"),"ಅವಧಿ ಮುಗಿದಿದೆ")</f>
+        <v>ಅವಧಿ ಮುಗಿದಿದೆ</v>
+      </c>
+      <c r="F1134" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1134, ""en"", ""ml"")"),"സെഷൻ കാലഹരണപ്പെട്ടു")</f>
+        <v>സെഷൻ കാലഹരണപ്പെട്ടു</v>
+      </c>
+      <c r="G1134" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1134, ""en"", ""te"")"),"సెషన్ గడువు ముగిసింది")</f>
+        <v>సెషన్ గడువు ముగిసింది</v>
+      </c>
     </row>
     <row r="1135">
-      <c r="A1135" s="4"/>
-      <c r="B1135" s="5"/>
-      <c r="C1135" s="6"/>
-      <c r="D1135" s="6"/>
-      <c r="E1135" s="6"/>
+      <c r="A1135" s="12" t="s">
+        <v>2746</v>
+      </c>
+      <c r="B1135" s="13" t="s">
+        <v>2747</v>
+      </c>
+      <c r="C1135" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1135, ""en"", ""ta"")"),"உங்கள் அமர்வு காலாவதியாகிவிட்டது. மீண்டும் உள்நுழையவும்.")</f>
+        <v>உங்கள் அமர்வு காலாவதியாகிவிட்டது. மீண்டும் உள்நுழையவும்.</v>
+      </c>
+      <c r="D1135" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1135, ""en"", ""hi"")"),"आपका सत्र समाप्त हो गया है। कृपया पुनः लॉग इन करें।")</f>
+        <v>आपका सत्र समाप्त हो गया है। कृपया पुनः लॉग इन करें।</v>
+      </c>
+      <c r="E1135" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1135, ""en"", ""kn"")"),"ನಿಮ್ಮ ಅವಧಿ ಮುಗಿದಿದೆ. ದಯವಿಟ್ಟು ಮತ್ತೆ ಲಾಗಿನ್ ಮಾಡಿ.")</f>
+        <v>ನಿಮ್ಮ ಅವಧಿ ಮುಗಿದಿದೆ. ದಯವಿಟ್ಟು ಮತ್ತೆ ಲಾಗಿನ್ ಮಾಡಿ.</v>
+      </c>
+      <c r="F1135" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1135, ""en"", ""ml"")"),"നിങ്ങളുടെ സെഷൻ കാലഹരണപ്പെട്ടു. ദയവായി വീണ്ടും ലോഗിൻ ചെയ്യുക.")</f>
+        <v>നിങ്ങളുടെ സെഷൻ കാലഹരണപ്പെട്ടു. ദയവായി വീണ്ടും ലോഗിൻ ചെയ്യുക.</v>
+      </c>
+      <c r="G1135" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1135, ""en"", ""te"")"),"మీ సెషన్ గడువు ముగిసింది. దయచేసి మళ్ళీ లాగిన్ అవ్వండి.")</f>
+        <v>మీ సెషన్ గడువు ముగిసింది. దయచేసి మళ్ళీ లాగిన్ అవ్వండి.</v>
+      </c>
     </row>
     <row r="1136">
       <c r="A1136" s="4"/>

--- a/PublicCustomerApp/src/python/translation.xlsx
+++ b/PublicCustomerApp/src/python/translation.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2867" uniqueCount="2748">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2881" uniqueCount="2762">
   <si>
     <t>key</t>
   </si>
@@ -8269,6 +8269,48 @@
   </si>
   <si>
     <t>Your session has expired. Please log in again.</t>
+  </si>
+  <si>
+    <t>are_you_sure</t>
+  </si>
+  <si>
+    <t>Are You Sure To Logout ?</t>
+  </si>
+  <si>
+    <t>are_you_sure_logout</t>
+  </si>
+  <si>
+    <t>Are you sure you want to logout from this vehicle? You must login to another available vehicle to take trips.</t>
+  </si>
+  <si>
+    <t>payments</t>
+  </si>
+  <si>
+    <t>Payments</t>
+  </si>
+  <si>
+    <t>collected_by_driver</t>
+  </si>
+  <si>
+    <t>Collected By Driver</t>
+  </si>
+  <si>
+    <t>sent_to_vendor</t>
+  </si>
+  <si>
+    <t>Sent To Vendor</t>
+  </si>
+  <si>
+    <t>no_work_history_found</t>
+  </si>
+  <si>
+    <t>No Work History Found</t>
+  </si>
+  <si>
+    <t>active_days</t>
+  </si>
+  <si>
+    <t>Active Days</t>
   </si>
 </sst>
 </file>
@@ -8754,8 +8796,8 @@
         <v>உங்கள் கட்டணத்தை பேசி, நம்ம ஊரு டாக்ஸி® செயலியுடன் பிக்-அப் இடத்தைப் பகிர்ந்து கொள்ளச் சொல்லுங்கள். அறிவிப்பு மூலம் பிக்-அப் இடத்தைப் பெற்று, பயணத்தைத் தொடங்க அதை ஏற்றுக்கொள்ளுங்கள்.</v>
       </c>
       <c r="D5" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B5, ""en"", ""hi"")"),"किराया तय कर लें और उनसे Namma Ooru Taxi ® ऐप के ज़रिए पिकअप लोकेशन शेयर करने के लिए कहें। नोटिफिकेशन के ज़रिए पिकअप लोकेशन मिलने पर उसे स्वीकार करके यात्रा शुरू करें।")</f>
-        <v>किराया तय कर लें और उनसे Namma Ooru Taxi ® ऐप के ज़रिए पिकअप लोकेशन शेयर करने के लिए कहें। नोटिफिकेशन के ज़रिए पिकअप लोकेशन मिलने पर उसे स्वीकार करके यात्रा शुरू करें।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B5, ""en"", ""hi"")"),"किराया तय करें और उनसे Namma Ooru Taxi ® ऐप के ज़रिए पिकअप लोकेशन शेयर करने के लिए कहें। नोटिफिकेशन के ज़रिए पिकअप लोकेशन मिलने पर उसे स्वीकार करके यात्रा शुरू करें।")</f>
+        <v>किराया तय करें और उनसे Namma Ooru Taxi ® ऐप के ज़रिए पिकअप लोकेशन शेयर करने के लिए कहें। नोटिफिकेशन के ज़रिए पिकअप लोकेशन मिलने पर उसे स्वीकार करके यात्रा शुरू करें।</v>
       </c>
       <c r="E5" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B5, ""en"", ""kn"")"),"ನಿಮ್ಮ ದರವನ್ನು ಮಾತುಕತೆ ಮಾಡಿ ಮತ್ತು ನಮ್ಮ ಊರು ಟ್ಯಾಕ್ಸಿ® ಅಪ್ಲಿಕೇಶನ್‌ನೊಂದಿಗೆ ಪಿಕಪ್ ಸ್ಥಳವನ್ನು ಹಂಚಿಕೊಳ್ಳಲು ಅವರನ್ನು ಕೇಳಿ. ಅಧಿಸೂಚನೆಯ ಮೂಲಕ ಪಿಕಪ್ ಸ್ಥಳವನ್ನು ಸ್ವೀಕರಿಸಿ ಮತ್ತು ಪ್ರಯಾಣವನ್ನು ಪ್ರಾರಂಭಿಸಲು ಅದನ್ನು ಸ್ವೀಕರಿಸಿ.")</f>
@@ -8766,8 +8808,8 @@
         <v>നിങ്ങളുടെ നിരക്ക് ചർച്ച ചെയ്ത് നമ്മ ഊരു ടാക്സി® ആപ്പുമായി പിക്കപ്പ് ലൊക്കേഷൻ പങ്കിടാൻ ആവശ്യപ്പെടുക. അറിയിപ്പ് വഴി പിക്ക്-അപ്പ് ലൊക്കേഷൻ സ്വീകരിച്ച് യാത്ര ആരംഭിക്കുക.</v>
       </c>
       <c r="G5" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B5, ""en"", ""te"")"),"మీ రేటును బేరం చేసి, నమ్మ ఊరు టాక్సీ® యాప్‌తో పికప్ లొకేషన్‌ను షేర్ చేయమని వారిని అడగండి. నోటిఫికేషన్ ద్వారా పికప్ లొకేషన్‌ను స్వీకరించి, ట్రిప్ ప్రారంభించడానికి దానిని అంగీకరించండి.")</f>
-        <v>మీ రేటును బేరం చేసి, నమ్మ ఊరు టాక్సీ® యాప్‌తో పికప్ లొకేషన్‌ను షేర్ చేయమని వారిని అడగండి. నోటిఫికేషన్ ద్వారా పికప్ లొకేషన్‌ను స్వీకరించి, ట్రిప్ ప్రారంభించడానికి దానిని అంగీకరించండి.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B5, ""en"", ""te"")"),"మీ రేటును బేరసారాలు చేసి, నమ్మ ఊరు టాక్సీ® యాప్‌తో పికప్ లొకేషన్‌ను షేర్ చేయమని వారిని అడగండి. నోటిఫికేషన్ ద్వారా పికప్ లొకేషన్‌ను స్వీకరించి, ట్రిప్ ప్రారంభించడానికి దానిని అంగీకరించండి.")</f>
+        <v>మీ రేటును బేరసారాలు చేసి, నమ్మ ఊరు టాక్సీ® యాప్‌తో పికప్ లొకేషన్‌ను షేర్ చేయమని వారిని అడగండి. నోటిఫికేషన్ ద్వారా పికప్ లొకేషన్‌ను స్వీకరించి, ట్రిప్ ప్రారంభించడానికి దానిని అంగీకరించండి.</v>
       </c>
     </row>
     <row r="6">
@@ -9018,8 +9060,8 @@
         <v>കൂടുതൽ പ്രതിബദ്ധതയ്ക്കുള്ള താക്കോലാണ് റേറ്റിംഗുകൾ. നിങ്ങൾക്ക് നല്ല റേറ്റിംഗ് ലഭിക്കുന്നുണ്ടെന്ന് ഉറപ്പാക്കുക.</v>
       </c>
       <c r="G14" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B14, ""en"", ""te"")"),"మరింత నిబద్ధతకు రేటింగ్‌లు కీలకం. మీరు మంచి రేటింగ్ పొందారని నిర్ధారించుకోండి.")</f>
-        <v>మరింత నిబద్ధతకు రేటింగ్‌లు కీలకం. మీరు మంచి రేటింగ్ పొందారని నిర్ధారించుకోండి.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B14, ""en"", ""te"")"),"మరింత నిబద్ధతకు రేటింగ్‌లు కీలకం. మీరు మంచి రేటింగ్ పొందేలా చూసుకోండి.")</f>
+        <v>మరింత నిబద్ధతకు రేటింగ్‌లు కీలకం. మీరు మంచి రేటింగ్ పొందేలా చూసుకోండి.</v>
       </c>
     </row>
     <row r="15">
@@ -9364,8 +9406,8 @@
         <v>60</v>
       </c>
       <c r="C27" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B27, ""en"", ""ta"")"),"செல்லுபடியாகும் உரிம எண்ணை (TN01 20110012345) உள்ளிடவும்.")</f>
-        <v>செல்லுபடியாகும் உரிம எண்ணை (TN01 20110012345) உள்ளிடவும்.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B27, ""en"", ""ta"")"),"தயவுசெய்து செல்லுபடியாகும் உரிம எண்ணை உள்ளிடவும் (TN01 20110012345)")</f>
+        <v>தயவுசெய்து செல்லுபடியாகும் உரிம எண்ணை உள்ளிடவும் (TN01 20110012345)</v>
       </c>
       <c r="D27" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B27, ""en"", ""hi"")"),"कृपया वैध लाइसेंस नंबर दर्ज करें (TN01 20110012345)")</f>
@@ -9802,8 +9844,8 @@
         <v>कृपया पंजीकरण संख्या दर्ज करें</v>
       </c>
       <c r="E42" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B42, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ನೋಂದಣಿ ಸಂಖ್ಯೆಯನ್ನು ನಮೂದಿಸಿ")</f>
-        <v>ದಯವಿಟ್ಟು ನೋಂದಣಿ ಸಂಖ್ಯೆಯನ್ನು ನಮೂದಿಸಿ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B42, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ನೋಂದಣಿ ಸಂಖ್ಯೆಯನ್ನು ನಮೂದಿಸಿ.")</f>
+        <v>ದಯವಿಟ್ಟು ನೋಂದಣಿ ಸಂಖ್ಯೆಯನ್ನು ನಮೂದಿಸಿ.</v>
       </c>
       <c r="F42" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B42, ""en"", ""ml"")"),"ദയവായി രജിസ്ട്രേഷൻ നമ്പർ നൽകുക")</f>
@@ -9918,8 +9960,8 @@
         <v>ದಯವಿಟ್ಟು ತಯಾರಿಕಾ ವರ್ಷವನ್ನು ನಮೂದಿಸಿ.</v>
       </c>
       <c r="F46" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B46, ""en"", ""ml"")"),"നിർമ്മാണ വർഷം നൽകുക.")</f>
-        <v>നിർമ്മാണ വർഷം നൽകുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B46, ""en"", ""ml"")"),"നിർമ്മാണ വർഷം നൽകുക")</f>
+        <v>നിർമ്മാണ വർഷം നൽകുക</v>
       </c>
       <c r="G46" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B46, ""en"", ""te"")"),"దయచేసి తయారీ సంవత్సరాన్ని నమోదు చేయండి")</f>
@@ -11714,8 +11756,8 @@
         <v>ദയവായി സാധുവായ ഒരു UPI ഐഡി നൽകുക - 9999999999@upi</v>
       </c>
       <c r="G110" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B110, ""en"", ""te"")"),"దయచేసి చెల్లుబాటు అయ్యే UPI IDని నమోదు చేయండి - 9999999999@upi")</f>
-        <v>దయచేసి చెల్లుబాటు అయ్యే UPI IDని నమోదు చేయండి - 9999999999@upi</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B110, ""en"", ""te"")"),"దయచేసి చెల్లుబాటు అయ్యే UPI IDని నమోదు చేయండి - 99999999999@upi")</f>
+        <v>దయచేసి చెల్లుబాటు అయ్యే UPI IDని నమోదు చేయండి - 99999999999@upi</v>
       </c>
     </row>
     <row r="111">
@@ -12308,8 +12350,8 @@
         <v>ഫിറ്റ്നസ് രേഖ</v>
       </c>
       <c r="G131" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B131, ""en"", ""te"")"),"ఫిట్‌నెస్ డాక్యుమెంట్")</f>
-        <v>ఫిట్‌నెస్ డాక్యుమెంట్</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B131, ""en"", ""te"")"),"ఫిట్‌నెస్ పత్రం")</f>
+        <v>ఫిట్‌నెస్ పత్రం</v>
       </c>
     </row>
     <row r="132">
@@ -12593,9 +12635,9 @@
       </c>
       <c r="F141" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B141, ""en"", ""ml"")"),"ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
-നിങ്ങളുടെ ക്ഷമയ്ക്ക് നന്ദി.")</f>
+ക്ഷമയ്ക്ക് നന്ദി.")</f>
         <v>ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
-നിങ്ങളുടെ ക്ഷമയ്ക്ക് നന്ദി.</v>
+ക്ഷമയ്ക്ക് നന്ദി.</v>
       </c>
       <c r="G141" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B141, ""en"", ""te"")"),"టాక్సీని ధృవీకరించడానికి మరియు వాటిని ఆమోదించడానికి మేము తీవ్రంగా కృషి చేస్తున్నాము. కాబట్టి దయచేసి ఆమోద ప్రక్రియకు కొంత సమయం పడుతుందని అర్థం చేసుకోండి.
@@ -13132,8 +13174,8 @@
         <v>ನೋಂದಾಯಿತ ಫೋನ್ ಸಂಖ್ಯೆಗೆ OTP ಯಶಸ್ವಿಯಾಗಿ ಮರು ಕಳುಹಿಸಲಾಗಿದೆ.</v>
       </c>
       <c r="F160" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B160, ""en"", ""ml"")"),"രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വിജയകരമായി വീണ്ടും അയച്ചു.")</f>
-        <v>രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വിജയകരമായി വീണ്ടും അയച്ചു.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B160, ""en"", ""ml"")"),"രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വീണ്ടും അയച്ചു.")</f>
+        <v>രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വീണ്ടും അയച്ചു.</v>
       </c>
       <c r="G160" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B160, ""en"", ""te"")"),"రిజిస్టర్డ్ ఫోన్ నంబర్‌కు OTP విజయవంతంగా తిరిగి పంపబడింది.")</f>
@@ -13184,8 +13226,8 @@
         <v>रीयल टाइम अपडेट प्राप्त करने के लिए कृपया नोटिफिकेशन की अनुमति चालू करें।</v>
       </c>
       <c r="E162" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B162, ""en"", ""kn"")"),"ನೈಜ ಸಮಯದ ನವೀಕರಣಗಳನ್ನು ಪಡೆಯಲು ದಯವಿಟ್ಟು ಅಧಿಸೂಚನೆ ಅನುಮತಿಯನ್ನು ಸಕ್ರಿಯಗೊಳಿಸಿ.")</f>
-        <v>ನೈಜ ಸಮಯದ ನವೀಕರಣಗಳನ್ನು ಪಡೆಯಲು ದಯವಿಟ್ಟು ಅಧಿಸೂಚನೆ ಅನುಮತಿಯನ್ನು ಸಕ್ರಿಯಗೊಳಿಸಿ.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B162, ""en"", ""kn"")"),"ನೈಜ ಸಮಯದ ನವೀಕರಣಗಳನ್ನು ಪಡೆಯಲು ಅಧಿಸೂಚನೆ ಅನುಮತಿಯನ್ನು ಸಕ್ರಿಯಗೊಳಿಸಿ.")</f>
+        <v>ನೈಜ ಸಮಯದ ನವೀಕರಣಗಳನ್ನು ಪಡೆಯಲು ಅಧಿಸೂಚನೆ ಅನುಮತಿಯನ್ನು ಸಕ್ರಿಯಗೊಳಿಸಿ.</v>
       </c>
       <c r="F162" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B162, ""en"", ""ml"")"),"തത്സമയ അപ്‌ഡേറ്റുകൾ ലഭിക്കാൻ അറിയിപ്പ് അനുമതി പ്രവർത്തനക്ഷമമാക്കുക.")</f>
@@ -13449,9 +13491,9 @@
       </c>
       <c r="F171" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B171, ""en"", ""ml"")"),"ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
-നിങ്ങളുടെ ക്ഷമയ്ക്ക് നന്ദി.")</f>
+ക്ഷമയ്ക്ക് നന്ദി.")</f>
         <v>ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
-നിങ്ങളുടെ ക്ഷമയ്ക്ക് നന്ദി.</v>
+ക്ഷമയ്ക്ക് നന്ദി.</v>
       </c>
       <c r="G171" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B171, ""en"", ""te"")"),"టాక్సీని ధృవీకరించడానికి మరియు వాటిని ఆమోదించడానికి మేము తీవ్రంగా కృషి చేస్తున్నాము. కాబట్టి దయచేసి ఆమోద ప్రక్రియకు కొంత సమయం పడుతుందని అర్థం చేసుకోండి.
@@ -13564,8 +13606,8 @@
         <v>ಇಲ್ಲ, ಆನ್‌ಲೈನ್‌ನಲ್ಲಿರಿ</v>
       </c>
       <c r="F175" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B175, ""en"", ""ml"")"),"വേണ്ട, ഓൺലൈനാകൂ")</f>
-        <v>വേണ്ട, ഓൺലൈനാകൂ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B175, ""en"", ""ml"")"),"വേണ്ട, ഓൺലൈനിൽ ആയിരിക്കൂ")</f>
+        <v>വേണ്ട, ഓൺലൈനിൽ ആയിരിക്കൂ</v>
       </c>
       <c r="G175" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B175, ""en"", ""te"")"),"వద్దు, ఆన్‌లైన్‌లో ఉండు")</f>
@@ -14148,8 +14190,8 @@
         <v>यदि सत्यापन में अधिक समय लगता है तो सहायता टीम से संपर्क करें।</v>
       </c>
       <c r="E196" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B196, ""en"", ""kn"")"),"ಪರಿಶೀಲನೆಗೆ ಹೆಚ್ಚು ಸಮಯ ತೆಗೆದುಕೊಂಡರೆ ಬೆಂಬಲವನ್ನು ಸಂಪರ್ಕಿಸಿ")</f>
-        <v>ಪರಿಶೀಲನೆಗೆ ಹೆಚ್ಚು ಸಮಯ ತೆಗೆದುಕೊಂಡರೆ ಬೆಂಬಲವನ್ನು ಸಂಪರ್ಕಿಸಿ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B196, ""en"", ""kn"")"),"ಪರಿಶೀಲನೆಗೆ ಹೆಚ್ಚಿನ ಸಮಯ ತೆಗೆದುಕೊಂಡರೆ ಬೆಂಬಲವನ್ನು ಸಂಪರ್ಕಿಸಿ")</f>
+        <v>ಪರಿಶೀಲನೆಗೆ ಹೆಚ್ಚಿನ ಸಮಯ ತೆಗೆದುಕೊಂಡರೆ ಬೆಂಬಲವನ್ನು ಸಂಪರ್ಕಿಸಿ</v>
       </c>
       <c r="F196" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B196, ""en"", ""ml"")"),"പരിശോധിച്ചുറപ്പിക്കലിന് കൂടുതൽ സമയമെടുക്കുന്നുവെങ്കിൽ പിന്തുണയുമായി ബന്ധപ്പെടുക.")</f>
@@ -14236,8 +14278,8 @@
         <v>ಆನ್‌ಲೈನ್‌ಗೆ ಹೋಗಿ</v>
       </c>
       <c r="F199" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B199, ""en"", ""ml"")"),"ഓൺലൈനാകുക")</f>
-        <v>ഓൺലൈനാകുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B199, ""en"", ""ml"")"),"ഓൺലൈനിൽ പോകുക")</f>
+        <v>ഓൺലൈനിൽ പോകുക</v>
       </c>
       <c r="G199" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B199, ""en"", ""te"")"),"ఆన్‌లైన్‌లోకి వెళ్లండి")</f>
@@ -14756,8 +14798,8 @@
         <v>428</v>
       </c>
       <c r="C218" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B218, ""en"", ""ta"")"),"இருப்பிடம் முடிவு")</f>
-        <v>இருப்பிடம் முடிவு</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B218, ""en"", ""ta"")"),"முடிவு இடம்")</f>
+        <v>முடிவு இடம்</v>
       </c>
       <c r="D218" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B218, ""en"", ""hi"")"),"अंतिम स्थान")</f>
@@ -16616,8 +16658,8 @@
         <v>ನಿಮ್ಮಲ್ಲಿ ಬಾಕಿ ಮೊತ್ತವಿದ್ದರೆ, ದಯವಿಟ್ಟು ಮುಂಚಿತವಾಗಿ ಎಲ್ಲಾ ಬಾಕಿ ಮೊತ್ತವನ್ನು ಪಾವತಿಸಿ.</v>
       </c>
       <c r="F284" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B284, ""en"", ""ml"")"),"നിങ്ങളുടെ കുടിശ്ശിക തുക ബാക്കിയുണ്ടെങ്കിൽ, ദയവായി എല്ലാ കുടിശ്ശികകളും മുൻകൂട്ടി തീർക്കുക.")</f>
-        <v>നിങ്ങളുടെ കുടിശ്ശിക തുക ബാക്കിയുണ്ടെങ്കിൽ, ദയവായി എല്ലാ കുടിശ്ശികകളും മുൻകൂട്ടി തീർക്കുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B284, ""en"", ""ml"")"),"കുടിശ്ശിക തുക ബാക്കിയുണ്ടെങ്കിൽ ദയവായി എല്ലാ കുടിശ്ശികയും മുൻകൂട്ടി തീർക്കുക.")</f>
+        <v>കുടിശ്ശിക തുക ബാക്കിയുണ്ടെങ്കിൽ ദയവായി എല്ലാ കുടിശ്ശികയും മുൻകൂട്ടി തീർക്കുക.</v>
       </c>
       <c r="G284" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B284, ""en"", ""te"")"),"మీకు ఇంకా బకాయిలు ఉంటే, దయచేసి ముందుగా అన్ని బకాయిలను చెల్లించండి.")</f>
@@ -17499,8 +17541,8 @@
         <v>614</v>
       </c>
       <c r="C316" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B316, ""en"", ""ta"")"),"பயணியை அடைய முடியவில்லை அல்லது பிக்அப் இடத்தில் இல்லை.")</f>
-        <v>பயணியை அடைய முடியவில்லை அல்லது பிக்அப் இடத்தில் இல்லை.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B316, ""en"", ""ta"")"),"பயணியை அணுக முடியவில்லை அல்லது பிக்அப் இடத்தில் இல்லை.")</f>
+        <v>பயணியை அணுக முடியவில்லை அல்லது பிக்அப் இடத்தில் இல்லை.</v>
       </c>
       <c r="D316" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B316, ""en"", ""hi"")"),"राइडर से संपर्क नहीं हो पा रहा है या वह पिकअप स्थान पर मौजूद नहीं है")</f>
@@ -17699,8 +17741,8 @@
         <v>மோசமான போக்குவரத்து அல்லது வானிலை</v>
       </c>
       <c r="D323" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B323, ""en"", ""hi"")"),"खराब यातायात या खराब मौसम की स्थिति")</f>
-        <v>खराब यातायात या खराब मौसम की स्थिति</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B323, ""en"", ""hi"")"),"यातायात की खराब स्थिति या मौसम की स्थिति")</f>
+        <v>यातायात की खराब स्थिति या मौसम की स्थिति</v>
       </c>
       <c r="E323" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B323, ""en"", ""kn"")"),"ಕಳಪೆ ಸಂಚಾರ ಅಥವಾ ಹವಾಮಾನ ಪರಿಸ್ಥಿತಿಗಳು")</f>
@@ -18071,8 +18113,8 @@
         <v>ಯಾವುದೇ ಟಿಕೆಟ್‌ಗಳು ಕಂಡುಬಂದಿಲ್ಲ.</v>
       </c>
       <c r="F336" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B336, ""en"", ""ml"")"),"ടിക്കറ്റുകളൊന്നും കണ്ടെത്തിയില്ല.")</f>
-        <v>ടിക്കറ്റുകളൊന്നും കണ്ടെത്തിയില്ല.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B336, ""en"", ""ml"")"),"ടിക്കറ്റുകളൊന്നും കണ്ടെത്തിയില്ല")</f>
+        <v>ടിക്കറ്റുകളൊന്നും കണ്ടെത്തിയില്ല</v>
       </c>
       <c r="G336" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B336, ""en"", ""te"")"),"టిక్కెట్లు దొరకలేదు.")</f>
@@ -18175,8 +18217,8 @@
         <v>உங்கள் சிக்கலை விவரிக்கவும், அதைத் தீர்க்க நாங்கள் உங்களுக்கு உதவுவோம்.</v>
       </c>
       <c r="D340" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B340, ""en"", ""hi"")"),"अपनी समस्या का वर्णन करें, हम उसे हल करने में आपकी सहायता करेंगे।")</f>
-        <v>अपनी समस्या का वर्णन करें, हम उसे हल करने में आपकी सहायता करेंगे।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B340, ""en"", ""hi"")"),"अपनी समस्या का वर्णन करें और हम इसे हल करने में आपकी सहायता करेंगे।")</f>
+        <v>अपनी समस्या का वर्णन करें और हम इसे हल करने में आपकी सहायता करेंगे।</v>
       </c>
       <c r="E340" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B340, ""en"", ""kn"")"),"ನಿಮ್ಮ ಸಮಸ್ಯೆಯನ್ನು ವಿವರಿಸಿ, ಅದನ್ನು ಪರಿಹರಿಸಲು ನಾವು ನಿಮಗೆ ಸಹಾಯ ಮಾಡುತ್ತೇವೆ.")</f>
@@ -19207,8 +19249,8 @@
         <v>732</v>
       </c>
       <c r="C377" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B377, ""en"", ""ta"")"),"வாகன ஆர்.சி. ஆவணத்தின் பின்புறம்")</f>
-        <v>வாகன ஆர்.சி. ஆவணத்தின் பின்புறம்</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B377, ""en"", ""ta"")"),"வாகன ஆர்.சி. ஆவண பின்புறம்")</f>
+        <v>வாகன ஆர்.சி. ஆவண பின்புறம்</v>
       </c>
       <c r="D377" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B377, ""en"", ""hi"")"),"वाहन आरसी दस्तावेज़ का पिछला भाग")</f>
@@ -19635,8 +19677,8 @@
         <v>कृपया एक मान्य ईमेल दर्ज करें</v>
       </c>
       <c r="E392" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B392, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ಮಾನ್ಯವಾದ ಇಮೇಲ್ ವಿಳಾಸವನ್ನು ನಮೂದಿಸಿ.")</f>
-        <v>ದಯವಿಟ್ಟು ಮಾನ್ಯವಾದ ಇಮೇಲ್ ವಿಳಾಸವನ್ನು ನಮೂದಿಸಿ.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B392, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ಮಾನ್ಯ ಇಮೇಲ್ ವಿಳಾಸವನ್ನು ನಮೂದಿಸಿ.")</f>
+        <v>ದಯವಿಟ್ಟು ಮಾನ್ಯ ಇಮೇಲ್ ವಿಳಾಸವನ್ನು ನಮೂದಿಸಿ.</v>
       </c>
       <c r="F392" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B392, ""en"", ""ml"")"),"ദയവായി സാധുവായ ഒരു ഇമെയിൽ വിലാസം നൽകുക.")</f>
@@ -19671,8 +19713,8 @@
         <v>ലക്ഷ്യസ്ഥാനത്ത് എത്തി</v>
       </c>
       <c r="G393" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B393, ""en"", ""te"")"),"గమ్యస్థానాన్ని చేరుకున్నారు")</f>
-        <v>గమ్యస్థానాన్ని చేరుకున్నారు</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B393, ""en"", ""te"")"),"గమ్యస్థానానికి చేరుకున్నారు")</f>
+        <v>గమ్యస్థానానికి చేరుకున్నారు</v>
       </c>
     </row>
     <row r="394">
@@ -21340,8 +21382,8 @@
         <v>अलग हुए</v>
       </c>
       <c r="E453" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B453, ""en"", ""kn"")"),"ವಿಭಾಗಿಸಲಾಗಿದೆ")</f>
-        <v>ವಿಭಾಗಿಸಲಾಗಿದೆ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B453, ""en"", ""kn"")"),"ಬೇರೆಡೆಗೆ ತಿರುಗಿತು")</f>
+        <v>ಬೇರೆಡೆಗೆ ತಿರುಗಿತು</v>
       </c>
       <c r="F453" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B453, ""en"", ""ml"")"),"വിഘടിച്ചു")</f>
@@ -22370,8 +22412,8 @@
         <v>ನಿಲ್ಲಿಸುವುದನ್ನು ದೃಢೀಕರಿಸಿ {ನಿಲುಗಡೆ}</v>
       </c>
       <c r="F491" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B491, ""en"", ""ml"")"),"നിർത്തുക സ്ഥിരീകരിക്കുക {നിർത്തുക}")</f>
-        <v>നിർത്തുക സ്ഥിരീകരിക്കുക {നിർത്തുക}</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B491, ""en"", ""ml"")"),"നിർത്തുക {നിർത്തുക} സ്ഥിരീകരിക്കുക")</f>
+        <v>നിർത്തുക {നിർത്തുക} സ്ഥിരീകരിക്കുക</v>
       </c>
       <c r="G491" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B491, ""en"", ""te"")"),"ఆపు {stop} ని నిర్ధారించండి")</f>
@@ -24348,8 +24390,8 @@
         <v>നമ്മ ഊരു ടാക്സി ഡ്രൈവർ ആപ്പ് സൈൻ അപ്പ് ചെയ്യുക</v>
       </c>
       <c r="G564" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B564, ""en"", ""te"")"),"సైన్ అప్ నమ్మ ఊరు టాక్సీ డ్రైవర్ యాప్")</f>
-        <v>సైన్ అప్ నమ్మ ఊరు టాక్సీ డ్రైవర్ యాప్</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B564, ""en"", ""te"")"),"సైన్అప్ నమ్మ ఊరు టాక్సీ డ్రైవర్ యాప్")</f>
+        <v>సైన్అప్ నమ్మ ఊరు టాక్సీ డ్రైవర్ యాప్</v>
       </c>
     </row>
     <row r="565">
@@ -24367,8 +24409,8 @@
         <v>हमसे संपर्क करें पर जाएं</v>
       </c>
       <c r="E565" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B565, ""en"", ""kn"")"),"ನಮ್ಮನ್ನು ಸಂಪರ್ಕಿಸಿ ವಿಭಾಗಕ್ಕೆ ಹೋಗಿ")</f>
-        <v>ನಮ್ಮನ್ನು ಸಂಪರ್ಕಿಸಿ ವಿಭಾಗಕ್ಕೆ ಹೋಗಿ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B565, ""en"", ""kn"")"),"ನಮ್ಮನ್ನು ಸಂಪರ್ಕಿಸಿ ಗೆ ಹೋಗಿ")</f>
+        <v>ನಮ್ಮನ್ನು ಸಂಪರ್ಕಿಸಿ ಗೆ ಹೋಗಿ</v>
       </c>
       <c r="F565" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B565, ""en"", ""ml"")"),"ഞങ്ങളെ ബന്ധപ്പെടുക എന്നതിലേക്ക് പോകുക")</f>
@@ -25046,8 +25088,8 @@
         <v>ಡ್ರಾಪ್</v>
       </c>
       <c r="F590" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B590, ""en"", ""ml"")"),"ഡ്രോപ്പ് ചെയ്യുക")</f>
-        <v>ഡ്രോപ്പ് ചെയ്യുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B590, ""en"", ""ml"")"),"ഡ്രോപ്പ്")</f>
+        <v>ഡ്രോപ്പ്</v>
       </c>
       <c r="G590" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B590, ""en"", ""te"")"),"డ్రాప్")</f>
@@ -26642,8 +26684,8 @@
         <v>ಸ್ಥಳವನ್ನು ಅಳಿಸಲು ವಿಫಲವಾಗಿದೆ. ದಯವಿಟ್ಟು ಮತ್ತೆ ಪ್ರಯತ್ನಿಸಿ.</v>
       </c>
       <c r="F649" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B649, ""en"", ""ml"")"),"സ്ഥലം ഇല്ലാതാക്കാനായില്ല. വീണ്ടും ശ്രമിക്കുക.")</f>
-        <v>സ്ഥലം ഇല്ലാതാക്കാനായില്ല. വീണ്ടും ശ്രമിക്കുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B649, ""en"", ""ml"")"),"സ്ഥലം ഇല്ലാതാക്കുന്നതിൽ പരാജയപ്പെട്ടു. വീണ്ടും ശ്രമിക്കുക.")</f>
+        <v>സ്ഥലം ഇല്ലാതാക്കുന്നതിൽ പരാജയപ്പെട്ടു. വീണ്ടും ശ്രമിക്കുക.</v>
       </c>
       <c r="G649" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B649, ""en"", ""te"")"),"స్థలాన్ని తొలగించడంలో విఫలమైంది. దయచేసి మళ్ళీ ప్రయత్నించండి.")</f>
@@ -27024,8 +27066,8 @@
         <v>യാത്രാക്കൂലി വളരെ കൂടുതലാണ് (സർജ്)</v>
       </c>
       <c r="G663" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B663, ""en"", ""te"")"),"ఛార్జీ చాలా ఎక్కువగా ఉంది (సర్జ్)")</f>
-        <v>ఛార్జీ చాలా ఎక్కువగా ఉంది (సర్జ్)</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B663, ""en"", ""te"")"),"ఛార్జీ చాలా ఎక్కువగా ఉంది (పెరుగుదల)")</f>
+        <v>ఛార్జీ చాలా ఎక్కువగా ఉంది (పెరుగుదల)</v>
       </c>
     </row>
     <row r="664">
@@ -27263,8 +27305,8 @@
         <v>ಡ್ರಾಪ್</v>
       </c>
       <c r="F672" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B672, ""en"", ""ml"")"),"ഡ്രോപ്പ് ചെയ്യുക")</f>
-        <v>ഡ്രോപ്പ് ചെയ്യുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B672, ""en"", ""ml"")"),"ഡ്രോപ്പ്")</f>
+        <v>ഡ്രോപ്പ്</v>
       </c>
       <c r="G672" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B672, ""en"", ""te"")"),"డ్రాప్")</f>
@@ -30228,8 +30270,8 @@
         <v>कोई सुरक्षित स्थान नहीं</v>
       </c>
       <c r="E782" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B782, ""en"", ""kn"")"),"ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ.")</f>
-        <v>ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B782, ""en"", ""kn"")"),"ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ")</f>
+        <v>ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ</v>
       </c>
       <c r="F782" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B782, ""en"", ""ml"")"),"സംരക്ഷിച്ച സ്ഥലങ്ങളൊന്നുമില്ല.")</f>
@@ -30251,8 +30293,8 @@
         <v>1829</v>
       </c>
       <c r="D783" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B783, ""en"", ""hi"")"),"रात में ड्राइवर उपलब्ध नहीं हैं")</f>
-        <v>रात में ड्राइवर उपलब्ध नहीं हैं</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B783, ""en"", ""hi"")"),"रात में गाड़ी चलाने वाले ड्राइवर उपलब्ध नहीं हैं")</f>
+        <v>रात में गाड़ी चलाने वाले ड्राइवर उपलब्ध नहीं हैं</v>
       </c>
       <c r="E783" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B783, ""en"", ""kn"")"),"ರಾತ್ರಿ ಚಾಲಕರು ಲಭ್ಯವಿಲ್ಲ.")</f>
@@ -32929,8 +32971,8 @@
         <v>2108</v>
       </c>
       <c r="D882" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B882, ""en"", ""hi"")"),"सवारी को पिकअप कर लिया गया")</f>
-        <v>सवारी को पिकअप कर लिया गया</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B882, ""en"", ""hi"")"),"सवारी उठा ली गई")</f>
+        <v>सवारी उठा ली गई</v>
       </c>
       <c r="E882" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B882, ""en"", ""kn"")"),"ಸವಾರಿ ಎತ್ತಿಕೊಳ್ಳಲಾಗಿದೆ")</f>
@@ -33446,8 +33488,8 @@
         <v>आपके सहेजे गए स्थान यहां दिखाई देंगे।</v>
       </c>
       <c r="E901" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B901, ""en"", ""kn"")"),"ನಿಮ್ಮ ಉಳಿಸಿದ ಸ್ಥಳಗಳು ಇಲ್ಲಿ ಗೋಚರಿಸುತ್ತವೆ.")</f>
-        <v>ನಿಮ್ಮ ಉಳಿಸಿದ ಸ್ಥಳಗಳು ಇಲ್ಲಿ ಗೋಚರಿಸುತ್ತವೆ.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B901, ""en"", ""kn"")"),"ನಿಮ್ಮ ಉಳಿಸಿದ ಸ್ಥಳಗಳು ಇಲ್ಲಿ ಕಾಣಿಸಿಕೊಳ್ಳುತ್ತವೆ.")</f>
+        <v>ನಿಮ್ಮ ಉಳಿಸಿದ ಸ್ಥಳಗಳು ಇಲ್ಲಿ ಕಾಣಿಸಿಕೊಳ್ಳುತ್ತವೆ.</v>
       </c>
       <c r="F901" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B901, ""en"", ""ml"")"),"നിങ്ങളുടെ സംരക്ഷിച്ച സ്ഥലങ്ങൾ ഇവിടെ ദൃശ്യമാകും.")</f>
@@ -34695,8 +34737,8 @@
         <v>ಚಾಲಕ ತಡವಾಗಿ ಬಂದಿರುವುದು</v>
       </c>
       <c r="F947" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B947, ""en"", ""ml"")"),"ഡ്രൈവർ വൈകിയുള്ള വരവ്")</f>
-        <v>ഡ്രൈവർ വൈകിയുള്ള വരവ്</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B947, ""en"", ""ml"")"),"ഡ്രൈവർ വൈകി എത്തൽ")</f>
+        <v>ഡ്രൈവർ വൈകി എത്തൽ</v>
       </c>
       <c r="G947" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B947, ""en"", ""te"")"),"డ్రైవర్ ఆలస్యంగా రావడం")</f>
@@ -34876,8 +34918,8 @@
         <v>2314</v>
       </c>
       <c r="D954" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B954, ""en"", ""hi"")"),"ड्राइवर बुक किए गए वाहन के प्रकार से भिन्न वाहन लेकर आया (उदाहरण के लिए, एसयूवी के बजाय सेडान)।")</f>
-        <v>ड्राइवर बुक किए गए वाहन के प्रकार से भिन्न वाहन लेकर आया (उदाहरण के लिए, एसयूवी के बजाय सेडान)।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B954, ""en"", ""hi"")"),"ड्राइवर बुक किए गए वाहन के बजाय किसी दूसरे प्रकार का वाहन लेकर आया (उदाहरण के लिए, एसयूवी के बजाय सेडान)।")</f>
+        <v>ड्राइवर बुक किए गए वाहन के बजाय किसी दूसरे प्रकार का वाहन लेकर आया (उदाहरण के लिए, एसयूवी के बजाय सेडान)।</v>
       </c>
       <c r="E954" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B954, ""en"", ""kn"")"),"ಚಾಲಕ ಬುಕ್ ಮಾಡಿದ ವಾಹನಕ್ಕಿಂತ ಬೇರೆ ವಾಹನ ಪ್ರಕಾರದೊಂದಿಗೆ ಬಂದಿದ್ದಾನೆ (ಉದಾ. SUV ಬದಲಿಗೆ ಸೆಡಾನ್)")</f>
@@ -35416,8 +35458,8 @@
         <v>2359</v>
       </c>
       <c r="D974" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B974, ""en"", ""hi"")"),"अपनी समस्या का वर्णन करें, हम उसे हल करने में आपकी सहायता करेंगे।")</f>
-        <v>अपनी समस्या का वर्णन करें, हम उसे हल करने में आपकी सहायता करेंगे।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B974, ""en"", ""hi"")"),"अपनी समस्या का वर्णन करें और हम इसे हल करने में आपकी सहायता करेंगे।")</f>
+        <v>अपनी समस्या का वर्णन करें और हम इसे हल करने में आपकी सहायता करेंगे।</v>
       </c>
       <c r="E974" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B974, ""en"", ""kn"")"),"ನಿಮ್ಮ ಸಮಸ್ಯೆಯನ್ನು ವಿವರಿಸಿ, ಅದನ್ನು ಪರಿಹರಿಸಲು ನಾವು ನಿಮಗೆ ಸಹಾಯ ಮಾಡುತ್ತೇವೆ.")</f>
@@ -36181,8 +36223,8 @@
         <v>{vehicleName} ಗರಿಷ್ಠ ದೂರ {maxKm} ಕಿ.ಮೀ. ದಯವಿಟ್ಟು ಬೇರೆ ವಾಹನವನ್ನು ಆಯ್ಕೆಮಾಡಿ ಅಥವಾ {maxKm} ಕಿ.ಮೀ.ಗಿಂತ ಕಡಿಮೆ ಪ್ರಯಾಣವನ್ನು ಯೋಜಿಸಿ.</v>
       </c>
       <c r="F1002" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1002, ""en"", ""ml"")"),"{vehicleName} പരമാവധി ദൂരം {maxKm} കിലോമീറ്ററാണ്. മറ്റൊരു വാഹനം തിരഞ്ഞെടുക്കുകയോ {maxKm} കിലോമീറ്ററിൽ താഴെയുള്ള യാത്ര പ്ലാൻ ചെയ്യുകയോ ചെയ്യുക.")</f>
-        <v>{vehicleName} പരമാവധി ദൂരം {maxKm} കിലോമീറ്ററാണ്. മറ്റൊരു വാഹനം തിരഞ്ഞെടുക്കുകയോ {maxKm} കിലോമീറ്ററിൽ താഴെയുള്ള യാത്ര പ്ലാൻ ചെയ്യുകയോ ചെയ്യുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1002, ""en"", ""ml"")"),"{vehicleName} പരമാവധി ദൂരം {maxKm} കിലോമീറ്ററാണ്. ദയവായി മറ്റൊരു വാഹനം തിരഞ്ഞെടുക്കുകയോ {maxKm} കിലോമീറ്ററിൽ താഴെയുള്ള യാത്ര പ്ലാൻ ചെയ്യുകയോ ചെയ്യുക.")</f>
+        <v>{vehicleName} പരമാവധി ദൂരം {maxKm} കിലോമീറ്ററാണ്. ദയവായി മറ്റൊരു വാഹനം തിരഞ്ഞെടുക്കുകയോ {maxKm} കിലോമീറ്ററിൽ താഴെയുള്ള യാത്ര പ്ലാൻ ചെയ്യുകയോ ചെയ്യുക.</v>
       </c>
       <c r="G1002" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1002, ""en"", ""te"")"),"{vehicleName} గరిష్ట దూరం {maxKm} కి.మీ. దయచేసి వేరే వాహనాన్ని ఎంచుకోండి లేదా {maxKm} కి.మీ కంటే తక్కువ దూరం ప్రయాణించడానికి ప్లాన్ చేయండి.")</f>
@@ -38015,8 +38057,8 @@
         <v>ಈ ಹಂತಗಳನ್ನು ಪೂರ್ಣಗೊಳಿಸಿ ಇದರಿಂದ ನೀವು ಸವಾರಿಗಳನ್ನು ಸ್ವೀಕರಿಸಲು ಪ್ರಾರಂಭಿಸಬಹುದು.</v>
       </c>
       <c r="F1069" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1069, ""en"", ""ml"")"),"റൈഡുകൾ സ്വീകരിച്ചു തുടങ്ങാൻ ഈ ഘട്ടങ്ങൾ പൂർത്തിയാക്കുക.")</f>
-        <v>റൈഡുകൾ സ്വീകരിച്ചു തുടങ്ങാൻ ഈ ഘട്ടങ്ങൾ പൂർത്തിയാക്കുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1069, ""en"", ""ml"")"),"റൈഡുകൾ സ്വീകരിക്കാൻ തുടങ്ങുന്നതിന് ഈ ഘട്ടങ്ങൾ പൂർത്തിയാക്കുക.")</f>
+        <v>റൈഡുകൾ സ്വീകരിക്കാൻ തുടങ്ങുന്നതിന് ഈ ഘട്ടങ്ങൾ പൂർത്തിയാക്കുക.</v>
       </c>
       <c r="G1069" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1069, ""en"", ""te"")"),"ఈ దశలను పూర్తి చేయండి, తద్వారా మీరు రైడ్‌లను అంగీకరించడం ప్రారంభించవచ్చు.")</f>
@@ -38259,8 +38301,8 @@
         <v>இந்த பயன்முறையில் திருத்துதல் முடக்கப்பட்டுள்ளது.</v>
       </c>
       <c r="D1078" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1078, ""en"", ""hi"")"),"इस मोड में संपादन की सुविधा अक्षम है।")</f>
-        <v>इस मोड में संपादन की सुविधा अक्षम है।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1078, ""en"", ""hi"")"),"इस मोड में संपादन अक्षम है।")</f>
+        <v>इस मोड में संपादन अक्षम है।</v>
       </c>
       <c r="E1078" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1078, ""en"", ""kn"")"),"ಈ ಕ್ರಮದಲ್ಲಿ ಸಂಪಾದನೆಯನ್ನು ನಿಷ್ಕ್ರಿಯಗೊಳಿಸಲಾಗಿದೆ.")</f>
@@ -38491,8 +38533,8 @@
         <v>ಡಾಕ್ಯುಮೆಂಟ್ ಅಪ್‌ಲೋಡ್ ಮಾಡಲಾಗುತ್ತಿದೆ. ದಯವಿಟ್ಟು ನಿರೀಕ್ಷಿಸಿ…</v>
       </c>
       <c r="F1086" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1086, ""en"", ""ml"")"),"ഡോക്യുമെന്റ് അപ്‌ലോഡ് ചെയ്യുന്നു. ദയവായി കാത്തിരിക്കുക…")</f>
-        <v>ഡോക്യുമെന്റ് അപ്‌ലോഡ് ചെയ്യുന്നു. ദയവായി കാത്തിരിക്കുക…</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1086, ""en"", ""ml"")"),"ഡോക്യുമെന്റ് അപ്‌ലോഡ് ചെയ്യുന്നു. കാത്തിരിക്കൂ...")</f>
+        <v>ഡോക്യുമെന്റ് അപ്‌ലോഡ് ചെയ്യുന്നു. കാത്തിരിക്കൂ...</v>
       </c>
       <c r="G1086" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1086, ""en"", ""te"")"),"పత్రాన్ని అప్‌లోడ్ చేస్తోంది. దయచేసి వేచి ఉండండి…")</f>
@@ -38901,8 +38943,8 @@
         <v>இந்த பயன்முறையில் திருத்துதல் முடக்கப்பட்டுள்ளது.</v>
       </c>
       <c r="D1101" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1101, ""en"", ""hi"")"),"इस मोड में संपादन की सुविधा अक्षम है।")</f>
-        <v>इस मोड में संपादन की सुविधा अक्षम है।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1101, ""en"", ""hi"")"),"इस मोड में संपादन अक्षम है।")</f>
+        <v>इस मोड में संपादन अक्षम है।</v>
       </c>
       <c r="E1101" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1101, ""en"", ""kn"")"),"ಈ ಕ್ರಮದಲ್ಲಿ ಸಂಪಾದನೆಯನ್ನು ನಿಷ್ಕ್ರಿಯಗೊಳಿಸಲಾಗಿದೆ.")</f>
@@ -39105,8 +39147,8 @@
         <v>ಸವಾರಿಗಳನ್ನು ಸ್ವೀಕರಿಸುವುದನ್ನು ಮುಂದುವರಿಸಲು ನಿಮ್ಮ ಬಾಕಿಗಳನ್ನು ಪಾವತಿಸಿ.</v>
       </c>
       <c r="F1108" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1108, ""en"", ""ml"")"),"റൈഡുകൾ സ്വീകരിക്കുന്നത് തുടരാൻ നിങ്ങളുടെ കുടിശ്ശിക അടയ്ക്കുക.")</f>
-        <v>റൈഡുകൾ സ്വീകരിക്കുന്നത് തുടരാൻ നിങ്ങളുടെ കുടിശ്ശിക അടയ്ക്കുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1108, ""en"", ""ml"")"),"റൈഡുകൾ സ്വീകരിക്കുന്നത് തുടരാൻ നിങ്ങളുടെ കുടിശ്ശികകൾ അടയ്ക്കുക.")</f>
+        <v>റൈഡുകൾ സ്വീകരിക്കുന്നത് തുടരാൻ നിങ്ങളുടെ കുടിശ്ശികകൾ അടയ്ക്കുക.</v>
       </c>
       <c r="G1108" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1108, ""en"", ""te"")"),"రైడ్‌లు అంగీకరించడం కొనసాగించడానికి మీ బకాయిలను క్లియర్ చేయండి.")</f>
@@ -39504,9 +39546,9 @@
       </c>
       <c r="F1122" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1122, ""en"", ""ml"")"),"ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
-നിങ്ങളുടെ ക്ഷമയ്ക്ക് നന്ദി.")</f>
+ക്ഷമയ്ക്ക് നന്ദി.")</f>
         <v>ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
-നിങ്ങളുടെ ക്ഷമയ്ക്ക് നന്ദി.</v>
+ക്ഷമയ്ക്ക് നന്ദി.</v>
       </c>
       <c r="G1122" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1122, ""en"", ""te"")"),"టాక్సీని ధృవీకరించడానికి మరియు వాటిని ఆమోదించడానికి మేము తీవ్రంగా కృషి చేస్తున్నాము. కాబట్టి దయచేసి ఆమోద ప్రక్రియకు కొంత సమయం పడుతుందని అర్థం చేసుకోండి.
@@ -39871,8 +39913,8 @@
         <v>ನಿಮ್ಮ ಅವಧಿ ಮುಗಿದಿದೆ. ದಯವಿಟ್ಟು ಮತ್ತೆ ಲಾಗಿನ್ ಮಾಡಿ.</v>
       </c>
       <c r="F1135" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1135, ""en"", ""ml"")"),"നിങ്ങളുടെ സെഷൻ കാലഹരണപ്പെട്ടു. ദയവായി വീണ്ടും ലോഗിൻ ചെയ്യുക.")</f>
-        <v>നിങ്ങളുടെ സെഷൻ കാലഹരണപ്പെട്ടു. ദയവായി വീണ്ടും ലോഗിൻ ചെയ്യുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1135, ""en"", ""ml"")"),"നിങ്ങളുടെ സെഷൻ കാലഹരണപ്പെട്ടു. വീണ്ടും ലോഗിൻ ചെയ്യുക.")</f>
+        <v>നിങ്ങളുടെ സെഷൻ കാലഹരണപ്പെട്ടു. വീണ്ടും ലോഗിൻ ചെയ്യുക.</v>
       </c>
       <c r="G1135" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1135, ""en"", ""te"")"),"మీ సెషన్ గడువు ముగిసింది. దయచేసి మళ్ళీ లాగిన్ అవ్వండి.")</f>
@@ -39880,53 +39922,200 @@
       </c>
     </row>
     <row r="1136">
-      <c r="A1136" s="4"/>
-      <c r="B1136" s="5"/>
-      <c r="C1136" s="6"/>
-      <c r="D1136" s="6"/>
-      <c r="E1136" s="6"/>
+      <c r="A1136" s="12" t="s">
+        <v>2748</v>
+      </c>
+      <c r="B1136" s="13" t="s">
+        <v>2749</v>
+      </c>
+      <c r="C1136" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1136, ""en"", ""ta"")"),"நீங்கள் வெளியேறுவது உறுதியா?")</f>
+        <v>நீங்கள் வெளியேறுவது உறுதியா?</v>
+      </c>
+      <c r="D1136" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1136, ""en"", ""hi"")"),"क्या आप लॉगआउट करने के लिए निश्चित हैं?")</f>
+        <v>क्या आप लॉगआउट करने के लिए निश्चित हैं?</v>
+      </c>
+      <c r="E1136" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1136, ""en"", ""kn"")"),"ನೀವು ಲಾಗ್ ಔಟ್ ಮಾಡುವುದು ಖಚಿತವೇ?")</f>
+        <v>ನೀವು ಲಾಗ್ ಔಟ್ ಮಾಡುವುದು ಖಚಿತವೇ?</v>
+      </c>
+      <c r="F1136" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1136, ""en"", ""ml"")"),"ലോഗ് ഔട്ട് ചെയ്യണമെന്ന് ഉറപ്പാണോ?")</f>
+        <v>ലോഗ് ഔട്ട് ചെയ്യണമെന്ന് ഉറപ്പാണോ?</v>
+      </c>
+      <c r="G1136" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1136, ""en"", ""te"")"),"మీరు ఖచ్చితంగా లాగ్ అవుట్ అవుతారా?")</f>
+        <v>మీరు ఖచ్చితంగా లాగ్ అవుట్ అవుతారా?</v>
+      </c>
     </row>
     <row r="1137">
-      <c r="A1137" s="4"/>
-      <c r="B1137" s="5"/>
-      <c r="C1137" s="6"/>
-      <c r="D1137" s="6"/>
-      <c r="E1137" s="6"/>
+      <c r="A1137" s="12" t="s">
+        <v>2750</v>
+      </c>
+      <c r="B1137" s="13" t="s">
+        <v>2751</v>
+      </c>
+      <c r="C1137" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1137, ""en"", ""ta"")"),"இந்த வாகனத்திலிருந்து வெளியேற விரும்புகிறீர்களா? பயணங்களை மேற்கொள்ள, கிடைக்கக்கூடிய மற்றொரு வாகனத்தில் உள்நுழைய வேண்டும்.")</f>
+        <v>இந்த வாகனத்திலிருந்து வெளியேற விரும்புகிறீர்களா? பயணங்களை மேற்கொள்ள, கிடைக்கக்கூடிய மற்றொரு வாகனத்தில் உள்நுழைய வேண்டும்.</v>
+      </c>
+      <c r="D1137" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1137, ""en"", ""hi"")"),"क्या आप वाकई इस वाहन से लॉगआउट करना चाहते हैं? यात्रा करने के लिए आपको किसी अन्य उपलब्ध वाहन में लॉग इन करना होगा।")</f>
+        <v>क्या आप वाकई इस वाहन से लॉगआउट करना चाहते हैं? यात्रा करने के लिए आपको किसी अन्य उपलब्ध वाहन में लॉग इन करना होगा।</v>
+      </c>
+      <c r="E1137" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1137, ""en"", ""kn"")"),"ನೀವು ಈ ವಾಹನದಿಂದ ಲಾಗ್ ಔಟ್ ಮಾಡಲು ಖಚಿತವಾಗಿ ಬಯಸುವಿರಾ? ಪ್ರವಾಸಗಳನ್ನು ಕೈಗೊಳ್ಳಲು ನೀವು ಲಭ್ಯವಿರುವ ಇನ್ನೊಂದು ವಾಹನಕ್ಕೆ ಲಾಗಿನ್ ಮಾಡಬೇಕು.")</f>
+        <v>ನೀವು ಈ ವಾಹನದಿಂದ ಲಾಗ್ ಔಟ್ ಮಾಡಲು ಖಚಿತವಾಗಿ ಬಯಸುವಿರಾ? ಪ್ರವಾಸಗಳನ್ನು ಕೈಗೊಳ್ಳಲು ನೀವು ಲಭ್ಯವಿರುವ ಇನ್ನೊಂದು ವಾಹನಕ್ಕೆ ಲಾಗಿನ್ ಮಾಡಬೇಕು.</v>
+      </c>
+      <c r="F1137" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1137, ""en"", ""ml"")"),"ഈ വാഹനത്തിൽ നിന്ന് ലോഗ് ഔട്ട് ചെയ്യണമെന്ന് നിങ്ങൾക്ക് ഉറപ്പാണോ? യാത്രകൾ നടത്താൻ ലഭ്യമായ മറ്റൊരു വാഹനത്തിൽ ലോഗിൻ ചെയ്യണം.")</f>
+        <v>ഈ വാഹനത്തിൽ നിന്ന് ലോഗ് ഔട്ട് ചെയ്യണമെന്ന് നിങ്ങൾക്ക് ഉറപ്പാണോ? യാത്രകൾ നടത്താൻ ലഭ്യമായ മറ്റൊരു വാഹനത്തിൽ ലോഗിൻ ചെയ്യണം.</v>
+      </c>
+      <c r="G1137" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1137, ""en"", ""te"")"),"మీరు ఖచ్చితంగా ఈ వాహనం నుండి లాగ్ అవుట్ చేయాలనుకుంటున్నారా? ప్రయాణాలు చేయడానికి మీరు అందుబాటులో ఉన్న మరొక వాహనంలోకి లాగిన్ అవ్వాలి.")</f>
+        <v>మీరు ఖచ్చితంగా ఈ వాహనం నుండి లాగ్ అవుట్ చేయాలనుకుంటున్నారా? ప్రయాణాలు చేయడానికి మీరు అందుబాటులో ఉన్న మరొక వాహనంలోకి లాగిన్ అవ్వాలి.</v>
+      </c>
     </row>
     <row r="1138">
-      <c r="A1138" s="4"/>
-      <c r="B1138" s="5"/>
-      <c r="C1138" s="6"/>
-      <c r="D1138" s="6"/>
-      <c r="E1138" s="6"/>
+      <c r="A1138" s="12" t="s">
+        <v>2752</v>
+      </c>
+      <c r="B1138" s="13" t="s">
+        <v>2753</v>
+      </c>
+      <c r="C1138" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1138, ""en"", ""ta"")"),"கொடுப்பனவுகள்")</f>
+        <v>கொடுப்பனவுகள்</v>
+      </c>
+      <c r="D1138" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1138, ""en"", ""hi"")"),"भुगतान")</f>
+        <v>भुगतान</v>
+      </c>
+      <c r="E1138" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1138, ""en"", ""kn"")"),"ಪಾವತಿಗಳು")</f>
+        <v>ಪಾವತಿಗಳು</v>
+      </c>
+      <c r="F1138" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1138, ""en"", ""ml"")"),"പേയ്‌മെന്റുകൾ")</f>
+        <v>പേയ്‌മെന്റുകൾ</v>
+      </c>
+      <c r="G1138" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1138, ""en"", ""te"")"),"చెల్లింపులు")</f>
+        <v>చెల్లింపులు</v>
+      </c>
     </row>
     <row r="1139">
-      <c r="A1139" s="4"/>
-      <c r="B1139" s="5"/>
-      <c r="C1139" s="6"/>
-      <c r="D1139" s="6"/>
-      <c r="E1139" s="6"/>
+      <c r="A1139" s="12" t="s">
+        <v>2754</v>
+      </c>
+      <c r="B1139" s="13" t="s">
+        <v>2755</v>
+      </c>
+      <c r="C1139" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1139, ""en"", ""ta"")"),"ஓட்டுநரால் சேகரிக்கப்பட்டது")</f>
+        <v>ஓட்டுநரால் சேகரிக்கப்பட்டது</v>
+      </c>
+      <c r="D1139" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1139, ""en"", ""hi"")"),"चालक द्वारा एकत्रित")</f>
+        <v>चालक द्वारा एकत्रित</v>
+      </c>
+      <c r="E1139" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1139, ""en"", ""kn"")"),"ಚಾಲಕರಿಂದ ಸಂಗ್ರಹಿಸಲಾಗಿದೆ")</f>
+        <v>ಚಾಲಕರಿಂದ ಸಂಗ್ರಹಿಸಲಾಗಿದೆ</v>
+      </c>
+      <c r="F1139" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1139, ""en"", ""ml"")"),"ഡ്രൈവർ ശേഖരിച്ചത്")</f>
+        <v>ഡ്രൈവർ ശേഖരിച്ചത്</v>
+      </c>
+      <c r="G1139" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1139, ""en"", ""te"")"),"డ్రైవర్ సేకరించినది")</f>
+        <v>డ్రైవర్ సేకరించినది</v>
+      </c>
     </row>
     <row r="1140">
-      <c r="A1140" s="4"/>
-      <c r="B1140" s="5"/>
-      <c r="C1140" s="6"/>
-      <c r="D1140" s="6"/>
-      <c r="E1140" s="6"/>
+      <c r="A1140" s="12" t="s">
+        <v>2756</v>
+      </c>
+      <c r="B1140" s="13" t="s">
+        <v>2757</v>
+      </c>
+      <c r="C1140" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1140, ""en"", ""ta"")"),"விற்பனையாளருக்கு அனுப்பப்பட்டது")</f>
+        <v>விற்பனையாளருக்கு அனுப்பப்பட்டது</v>
+      </c>
+      <c r="D1140" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1140, ""en"", ""hi"")"),"विक्रेता को भेजा गया")</f>
+        <v>विक्रेता को भेजा गया</v>
+      </c>
+      <c r="E1140" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1140, ""en"", ""kn"")"),"ಮಾರಾಟಗಾರರಿಗೆ ಕಳುಹಿಸಲಾಗಿದೆ")</f>
+        <v>ಮಾರಾಟಗಾರರಿಗೆ ಕಳುಹಿಸಲಾಗಿದೆ</v>
+      </c>
+      <c r="F1140" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1140, ""en"", ""ml"")"),"വെണ്ടർക്ക് അയച്ചു")</f>
+        <v>വെണ്ടർക്ക് അയച്ചു</v>
+      </c>
+      <c r="G1140" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1140, ""en"", ""te"")"),"విక్రేతకు పంపబడింది")</f>
+        <v>విక్రేతకు పంపబడింది</v>
+      </c>
     </row>
     <row r="1141">
-      <c r="A1141" s="4"/>
-      <c r="B1141" s="5"/>
-      <c r="C1141" s="6"/>
-      <c r="D1141" s="6"/>
-      <c r="E1141" s="6"/>
+      <c r="A1141" s="12" t="s">
+        <v>2758</v>
+      </c>
+      <c r="B1141" s="13" t="s">
+        <v>2759</v>
+      </c>
+      <c r="C1141" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1141, ""en"", ""ta"")"),"பணி வரலாறு எதுவும் கிடைக்கவில்லை.")</f>
+        <v>பணி வரலாறு எதுவும் கிடைக்கவில்லை.</v>
+      </c>
+      <c r="D1141" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1141, ""en"", ""hi"")"),"कोई कार्य अनुभव नहीं मिला")</f>
+        <v>कोई कार्य अनुभव नहीं मिला</v>
+      </c>
+      <c r="E1141" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1141, ""en"", ""kn"")"),"ಯಾವುದೇ ಕೆಲಸದ ಇತಿಹಾಸ ಕಂಡುಬಂದಿಲ್ಲ")</f>
+        <v>ಯಾವುದೇ ಕೆಲಸದ ಇತಿಹಾಸ ಕಂಡುಬಂದಿಲ್ಲ</v>
+      </c>
+      <c r="F1141" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1141, ""en"", ""ml"")"),"ജോലി ചരിത്രമൊന്നും കണ്ടെത്തിയില്ല")</f>
+        <v>ജോലി ചരിത്രമൊന്നും കണ്ടെത്തിയില്ല</v>
+      </c>
+      <c r="G1141" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1141, ""en"", ""te"")"),"ఉద్యోగ చరిత్ర కనుగొనబడలేదు")</f>
+        <v>ఉద్యోగ చరిత్ర కనుగొనబడలేదు</v>
+      </c>
     </row>
     <row r="1142">
-      <c r="A1142" s="4"/>
-      <c r="B1142" s="5"/>
-      <c r="C1142" s="6"/>
-      <c r="D1142" s="6"/>
-      <c r="E1142" s="6"/>
+      <c r="A1142" s="12" t="s">
+        <v>2760</v>
+      </c>
+      <c r="B1142" s="13" t="s">
+        <v>2761</v>
+      </c>
+      <c r="C1142" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1142, ""en"", ""ta"")"),"செயலில் உள்ள நாட்கள்")</f>
+        <v>செயலில் உள்ள நாட்கள்</v>
+      </c>
+      <c r="D1142" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1142, ""en"", ""hi"")"),"सक्रिय दिन")</f>
+        <v>सक्रिय दिन</v>
+      </c>
+      <c r="E1142" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1142, ""en"", ""kn"")"),"ಸಕ್ರಿಯ ದಿನಗಳು")</f>
+        <v>ಸಕ್ರಿಯ ದಿನಗಳು</v>
+      </c>
+      <c r="F1142" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1142, ""en"", ""ml"")"),"സജീവ ദിവസങ്ങൾ")</f>
+        <v>സജീവ ദിവസങ്ങൾ</v>
+      </c>
+      <c r="G1142" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1142, ""en"", ""te"")"),"క్రియాశీల రోజులు")</f>
+        <v>క్రియాశీల రోజులు</v>
+      </c>
     </row>
     <row r="1143">
       <c r="A1143" s="4"/>

--- a/PublicCustomerApp/src/python/translation.xlsx
+++ b/PublicCustomerApp/src/python/translation.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2881" uniqueCount="2762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="2764">
   <si>
     <t>key</t>
   </si>
@@ -8311,6 +8311,12 @@
   </si>
   <si>
     <t>Active Days</t>
+  </si>
+  <si>
+    <t>select_date</t>
+  </si>
+  <si>
+    <t>Select Date</t>
   </si>
 </sst>
 </file>
@@ -40118,11 +40124,32 @@
       </c>
     </row>
     <row r="1143">
-      <c r="A1143" s="4"/>
-      <c r="B1143" s="5"/>
-      <c r="C1143" s="6"/>
-      <c r="D1143" s="6"/>
-      <c r="E1143" s="6"/>
+      <c r="A1143" s="12" t="s">
+        <v>2762</v>
+      </c>
+      <c r="B1143" s="13" t="s">
+        <v>2763</v>
+      </c>
+      <c r="C1143" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1143, ""en"", ""ta"")"),"தேதியைத் தேர்ந்தெடுக்கவும்")</f>
+        <v>தேதியைத் தேர்ந்தெடுக்கவும்</v>
+      </c>
+      <c r="D1143" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1143, ""en"", ""hi"")"),"तारीख़ चुनें")</f>
+        <v>तारीख़ चुनें</v>
+      </c>
+      <c r="E1143" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1143, ""en"", ""kn"")"),"ದಿನಾಂಕ ಆಯ್ಕೆಮಾಡಿ")</f>
+        <v>ದಿನಾಂಕ ಆಯ್ಕೆಮಾಡಿ</v>
+      </c>
+      <c r="F1143" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1143, ""en"", ""ml"")"),"തീയതി തിരഞ്ഞെടുക്കുക")</f>
+        <v>തീയതി തിരഞ്ഞെടുക്കുക</v>
+      </c>
+      <c r="G1143" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1143, ""en"", ""te"")"),"తేదీని ఎంచుకోండి")</f>
+        <v>తేదీని ఎంచుకోండి</v>
+      </c>
     </row>
     <row r="1144">
       <c r="A1144" s="4"/>

--- a/PublicCustomerApp/src/python/translation.xlsx
+++ b/PublicCustomerApp/src/python/translation.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2893" uniqueCount="2774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2930" uniqueCount="2807">
   <si>
     <t>key</t>
   </si>
@@ -8346,14 +8346,113 @@
     <t>Acting Driver Login</t>
   </si>
   <si>
-    <t>ஆக்டிங் டிரைவர் உள்நுழைவு</t>
+    <t>driving_experience</t>
+  </si>
+  <si>
+    <t>Driving Experience</t>
+  </si>
+  <si>
+    <t>total_driving_experience</t>
+  </si>
+  <si>
+    <t>Total Driving Experience</t>
+  </si>
+  <si>
+    <t>commercial_driving_experience</t>
+  </si>
+  <si>
+    <t>Commercial Driving Experience</t>
+  </si>
+  <si>
+    <t>ride_hailing_experience</t>
+  </si>
+  <si>
+    <t>Ride-hailing Platform Experience</t>
+  </si>
+  <si>
+    <t>platforms_worked_with</t>
+  </si>
+  <si>
+    <t>Platforms Worked With</t>
+  </si>
+  <si>
+    <t>approx_completed_trips</t>
+  </si>
+  <si>
+    <t>Approx Completed Trips</t>
+  </si>
+  <si>
+    <t>driver_rating_range</t>
+  </si>
+  <si>
+    <t>Driver Rating</t>
+  </si>
+  <si>
+    <t>select_transmission</t>
+  </si>
+  <si>
+    <t>Please select transmission type</t>
+  </si>
+  <si>
+    <t>select_vehicle_type</t>
+  </si>
+  <si>
+    <t>Please select at least one vehicle type</t>
+  </si>
+  <si>
+    <t>vehicle_handling</t>
+  </si>
+  <si>
+    <t>Vehicle Handling</t>
+  </si>
+  <si>
+    <t>vehicle_types_driven</t>
+  </si>
+  <si>
+    <t>Vehicle Types Driven</t>
+  </si>
+  <si>
+    <t>select_all_that_apply</t>
+  </si>
+  <si>
+    <t>Select all that apply</t>
+  </si>
+  <si>
+    <t>transmission_type</t>
+  </si>
+  <si>
+    <t>Transmission Type</t>
+  </si>
+  <si>
+    <t>fuel_types_handled</t>
+  </si>
+  <si>
+    <t>Fuel Types Handled</t>
+  </si>
+  <si>
+    <t>night_driving_experience</t>
+  </si>
+  <si>
+    <t>Night Driving Experience</t>
+  </si>
+  <si>
+    <t>long_distance_experience</t>
+  </si>
+  <si>
+    <t>Long-distance Trip Experience</t>
+  </si>
+  <si>
+    <t>select_total_experience</t>
+  </si>
+  <si>
+    <t>Please select your total driving experience</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -8389,11 +8488,6 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <sz val="12.0"/>
-      <color rgb="FF001D35"/>
-      <name val="&quot;Google Sans&quot;"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -8421,7 +8515,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -8490,9 +8584,6 @@
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -8868,8 +8959,8 @@
         <v>பயணத்தைத் தொடங்குவதற்கும் உறுதிப்படுத்துவதற்கும் வாடிக்கையாளரைத் தொடர்பு கொண்டீர்கள் என்பதை உறுதிப்படுத்திக் கொள்ளுங்கள்.</v>
       </c>
       <c r="D6" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B6, ""en"", ""hi"")"),"ग्राहक से संपर्क करके यात्रा की पुष्टि अवश्य कर लें और यात्रा शुरू करें।")</f>
-        <v>ग्राहक से संपर्क करके यात्रा की पुष्टि अवश्य कर लें और यात्रा शुरू करें।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B6, ""en"", ""hi"")"),"ग्राहक से संपर्क करके यात्रा की पुष्टि कर लें और यात्रा शुरू करें।")</f>
+        <v>ग्राहक से संपर्क करके यात्रा की पुष्टि कर लें और यात्रा शुरू करें।</v>
       </c>
       <c r="E6" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B6, ""en"", ""kn"")"),"ಖಚಿತಪಡಿಸಲು ಮತ್ತು ಪ್ರಯಾಣವನ್ನು ಪ್ರಾರಂಭಿಸಲು ನೀವು ಗ್ರಾಹಕರನ್ನು ಸಂಪರ್ಕಿಸಿದ್ದೀರಿ ಎಂದು ಖಚಿತಪಡಿಸಿಕೊಳ್ಳಿ.")</f>
@@ -9383,8 +9474,8 @@
         <v>ദയവായി പാൻ നമ്പർ നൽകുക</v>
       </c>
       <c r="G24" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B24, ""en"", ""te"")"),"దయచేసి పాన్ నంబర్‌ను నమోదు చేయండి")</f>
-        <v>దయచేసి పాన్ నంబర్‌ను నమోదు చేయండి</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B24, ""en"", ""te"")"),"దయచేసి పాన్ నంబర్ నమోదు చేయండి")</f>
+        <v>దయచేసి పాన్ నంబర్ నమోదు చేయండి</v>
       </c>
     </row>
     <row r="25">
@@ -9668,8 +9759,8 @@
         <v>ಆದ್ಯತೆಯ ಕೆಲಸದ ಸ್ಥಳ</v>
       </c>
       <c r="F34" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B34, ""en"", ""ml"")"),"ഇഷ്ടപ്പെട്ട ജോലി സ്ഥലം")</f>
-        <v>ഇഷ്ടപ്പെട്ട ജോലി സ്ഥലം</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B34, ""en"", ""ml"")"),"ഇഷ്ടപ്പെട്ട ജോലിസ്ഥലം")</f>
+        <v>ഇഷ്ടപ്പെട്ട ജോലിസ്ഥലം</v>
       </c>
       <c r="G34" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B34, ""en"", ""te"")"),"ఇష్టపడే పని ప్రదేశం")</f>
@@ -9888,8 +9979,8 @@
         <v>कृपया पंजीकरण संख्या दर्ज करें</v>
       </c>
       <c r="E42" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B42, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ನೋಂದಣಿ ಸಂಖ್ಯೆಯನ್ನು ನಮೂದಿಸಿ.")</f>
-        <v>ದಯವಿಟ್ಟು ನೋಂದಣಿ ಸಂಖ್ಯೆಯನ್ನು ನಮೂದಿಸಿ.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B42, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ನೋಂದಣಿ ಸಂಖ್ಯೆಯನ್ನು ನಮೂದಿಸಿ")</f>
+        <v>ದಯವಿಟ್ಟು ನೋಂದಣಿ ಸಂಖ್ಯೆಯನ್ನು ನಮೂದಿಸಿ</v>
       </c>
       <c r="F42" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B42, ""en"", ""ml"")"),"ദയവായി രജിസ്ട്രേഷൻ നമ്പർ നൽകുക")</f>
@@ -9976,8 +10067,8 @@
         <v>ದಯವಿಟ್ಟು ವಾಹನ ಮಾದರಿಯನ್ನು ನಮೂದಿಸಿ.</v>
       </c>
       <c r="F45" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B45, ""en"", ""ml"")"),"വാഹന മോഡൽ നൽകുക.")</f>
-        <v>വാഹന മോഡൽ നൽകുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B45, ""en"", ""ml"")"),"ദയവായി വാഹന മോഡൽ നൽകുക.")</f>
+        <v>ദയവായി വാഹന മോഡൽ നൽകുക.</v>
       </c>
       <c r="G45" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B45, ""en"", ""te"")"),"దయచేసి వాహన మోడల్‌ను నమోదు చేయండి")</f>
@@ -10004,8 +10095,8 @@
         <v>ದಯವಿಟ್ಟು ತಯಾರಿಕಾ ವರ್ಷವನ್ನು ನಮೂದಿಸಿ.</v>
       </c>
       <c r="F46" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B46, ""en"", ""ml"")"),"നിർമ്മാണ വർഷം നൽകുക")</f>
-        <v>നിർമ്മാണ വർഷം നൽകുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B46, ""en"", ""ml"")"),"നിർമ്മാണ വർഷം നൽകുക.")</f>
+        <v>നിർമ്മാണ വർഷം നൽകുക.</v>
       </c>
       <c r="G46" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B46, ""en"", ""te"")"),"దయచేసి తయారీ సంవత్సరాన్ని నమోదు చేయండి")</f>
@@ -10932,8 +11023,8 @@
         <v>ചാരനിറം</v>
       </c>
       <c r="G79" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B79, ""en"", ""te"")"),"బూడిద రంగు")</f>
-        <v>బూడిద రంగు</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B79, ""en"", ""te"")"),"గ్రే")</f>
+        <v>గ్రే</v>
       </c>
     </row>
     <row r="80">
@@ -11252,8 +11343,8 @@
         <v>188</v>
       </c>
       <c r="C91" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B91, ""en"", ""ta"")"),"சி.என்.ஜி.")</f>
-        <v>சி.என்.ஜி.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B91, ""en"", ""ta"")"),"சிஎன்ஜி")</f>
+        <v>சிஎன்ஜி</v>
       </c>
       <c r="D91" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B91, ""en"", ""hi"")"),"सीएनजी")</f>
@@ -11968,8 +12059,8 @@
         <v>ശാഖ</v>
       </c>
       <c r="G116" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B116, ""en"", ""te"")"),"బ్రాంచ్")</f>
-        <v>బ్రాంచ్</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B116, ""en"", ""te"")"),"శాఖ")</f>
+        <v>శాఖ</v>
       </c>
     </row>
     <row r="117">
@@ -12679,9 +12770,9 @@
       </c>
       <c r="F141" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B141, ""en"", ""ml"")"),"ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
-ക്ഷമയ്ക്ക് നന്ദി.")</f>
+നിങ്ങളുടെ ക്ഷമയ്ക്ക് നന്ദി.")</f>
         <v>ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
-ക്ഷമയ്ക്ക് നന്ദി.</v>
+നിങ്ങളുടെ ക്ഷമയ്ക്ക് നന്ദി.</v>
       </c>
       <c r="G141" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B141, ""en"", ""te"")"),"మేము టాక్సీలను సరిచూసి, ఆమోదించడానికి తీవ్రంగా కృషి చేస్తున్నాము. కాబట్టి, ఆమోద ప్రక్రియకు కొంత సమయం పడుతుందని దయచేసి అర్థం చేసుకోండి.
@@ -12754,8 +12845,8 @@
         <v>294</v>
       </c>
       <c r="C144" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B144, ""en"", ""ta"")"),"ஏதோ தவறாகிவிட்டது.")</f>
-        <v>ஏதோ தவறாகிவிட்டது.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B144, ""en"", ""ta"")"),"ஏதோ தவறு நடந்துவிட்டது")</f>
+        <v>ஏதோ தவறு நடந்துவிட்டது</v>
       </c>
       <c r="D144" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B144, ""en"", ""hi"")"),"कुछ गलत हो गया")</f>
@@ -12838,8 +12929,8 @@
         <v>300</v>
       </c>
       <c r="C147" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B147, ""en"", ""ta"")"),"ஸ்ட்ரீட் ஒன்")</f>
-        <v>ஸ்ட்ரீட் ஒன்</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B147, ""en"", ""ta"")"),"தெரு ஒன்று")</f>
+        <v>தெரு ஒன்று</v>
       </c>
       <c r="D147" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B147, ""en"", ""hi"")"),"गली एक")</f>
@@ -13006,8 +13097,8 @@
         <v>312</v>
       </c>
       <c r="C153" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B153, ""en"", ""ta"")"),"OTP பெறுங்கள்")</f>
-        <v>OTP பெறுங்கள்</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B153, ""en"", ""ta"")"),"OTP-ஐப் பெறுங்கள்")</f>
+        <v>OTP-ஐப் பெறுங்கள்</v>
       </c>
       <c r="D153" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B153, ""en"", ""hi"")"),"ओटीपी प्राप्त करें")</f>
@@ -13216,8 +13307,8 @@
         <v>ನೋಂದಾಯಿತ ಫೋನ್ ಸಂಖ್ಯೆಗೆ OTP ಯಶಸ್ವಿಯಾಗಿ ಮರು ಕಳುಹಿಸಲಾಗಿದೆ.</v>
       </c>
       <c r="F160" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B160, ""en"", ""ml"")"),"രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വിജയകരമായി വീണ്ടും അയച്ചു.")</f>
-        <v>രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വിജയകരമായി വീണ്ടും അയച്ചു.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B160, ""en"", ""ml"")"),"രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വീണ്ടും അയച്ചു.")</f>
+        <v>രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വീണ്ടും അയച്ചു.</v>
       </c>
       <c r="G160" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B160, ""en"", ""te"")"),"నమోదిత ఫోన్ నంబర్‌కు OTP విజయవంతంగా పంపబడింది")</f>
@@ -13268,8 +13359,8 @@
         <v>रीयल टाइम अपडेट प्राप्त करने के लिए कृपया नोटिफिकेशन की अनुमति चालू करें।</v>
       </c>
       <c r="E162" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B162, ""en"", ""kn"")"),"ನೈಜ ಸಮಯದ ನವೀಕರಣಗಳನ್ನು ಪಡೆಯಲು ದಯವಿಟ್ಟು ಅಧಿಸೂಚನೆ ಅನುಮತಿಯನ್ನು ಸಕ್ರಿಯಗೊಳಿಸಿ.")</f>
-        <v>ನೈಜ ಸಮಯದ ನವೀಕರಣಗಳನ್ನು ಪಡೆಯಲು ದಯವಿಟ್ಟು ಅಧಿಸೂಚನೆ ಅನುಮತಿಯನ್ನು ಸಕ್ರಿಯಗೊಳಿಸಿ.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B162, ""en"", ""kn"")"),"ನೈಜ ಸಮಯದ ನವೀಕರಣಗಳನ್ನು ಪಡೆಯಲು ಅಧಿಸೂಚನೆ ಅನುಮತಿಯನ್ನು ಸಕ್ರಿಯಗೊಳಿಸಿ.")</f>
+        <v>ನೈಜ ಸಮಯದ ನವೀಕರಣಗಳನ್ನು ಪಡೆಯಲು ಅಧಿಸೂಚನೆ ಅನುಮತಿಯನ್ನು ಸಕ್ರಿಯಗೊಳಿಸಿ.</v>
       </c>
       <c r="F162" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B162, ""en"", ""ml"")"),"തത്സമയ അപ്‌ഡേറ്റുകൾ ലഭിക്കാൻ അറിയിപ്പ് അനുമതി പ്രവർത്തനക്ഷമമാക്കുക.")</f>
@@ -13648,8 +13739,8 @@
         <v>ಇಲ್ಲ, ಆನ್‌ಲೈನ್‌ನಲ್ಲಿರಿ</v>
       </c>
       <c r="F175" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B175, ""en"", ""ml"")"),"വേണ്ട, ഓൺലൈനിൽ ആയിരിക്കൂ")</f>
-        <v>വേണ്ട, ഓൺലൈനിൽ ആയിരിക്കൂ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B175, ""en"", ""ml"")"),"വേണ്ട, ഓൺലൈനാകൂ")</f>
+        <v>വേണ്ട, ഓൺലൈനാകൂ</v>
       </c>
       <c r="G175" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B175, ""en"", ""te"")"),"లేదు, ఆన్‌లైన్‌లో ఉండండి")</f>
@@ -14280,8 +14371,8 @@
         <v>390</v>
       </c>
       <c r="C198" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B198, ""en"", ""ta"")"),"வருவாய்")</f>
-        <v>வருவாய்</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B198, ""en"", ""ta"")"),"வருமானம்")</f>
+        <v>வருமானம்</v>
       </c>
       <c r="D198" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B198, ""en"", ""hi"")"),"आय")</f>
@@ -14320,8 +14411,8 @@
         <v>ಆನ್‌ಲೈನ್‌ಗೆ ಹೋಗಿ</v>
       </c>
       <c r="F199" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B199, ""en"", ""ml"")"),"ഓൺലൈനിൽ പോകുക")</f>
-        <v>ഓൺലൈനിൽ പോകുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B199, ""en"", ""ml"")"),"ഓൺലൈനാകുക")</f>
+        <v>ഓൺലൈനാകുക</v>
       </c>
       <c r="G199" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B199, ""en"", ""te"")"),"ఆన్‌లైన్‌కు వెళ్లండి")</f>
@@ -14824,8 +14915,8 @@
         <v>ವಿವರಗಳು ವೀಕ್ಷಿಸಿ</v>
       </c>
       <c r="F217" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B217, ""en"", ""ml"")"),"കാണുക വിശദാംശങ്ങൾ")</f>
-        <v>കാണുക വിശദാംശങ്ങൾ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B217, ""en"", ""ml"")"),"വിശദാംശങ്ങൾ കാണുക")</f>
+        <v>വിശദാംശങ്ങൾ കാണുക</v>
       </c>
       <c r="G217" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B217, ""en"", ""te"")"),"వివరాలను వీక్షించండి")</f>
@@ -14968,8 +15059,8 @@
         <v>ആകെ യാത്രകൾ</v>
       </c>
       <c r="G222" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B222, ""en"", ""te"")"),"మొత్తం పర్యటనలు")</f>
-        <v>మొత్తం పర్యటనలు</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B222, ""en"", ""te"")"),"మొత్తం ప్రయాణాలు")</f>
+        <v>మొత్తం ప్రయాణాలు</v>
       </c>
     </row>
     <row r="223">
@@ -15176,8 +15267,8 @@
         <v>390</v>
       </c>
       <c r="C230" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B230, ""en"", ""ta"")"),"வருவாய்")</f>
-        <v>வருவாய்</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B230, ""en"", ""ta"")"),"வருமானம்")</f>
+        <v>வருமானம்</v>
       </c>
       <c r="D230" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B230, ""en"", ""hi"")"),"आय")</f>
@@ -16100,8 +16191,8 @@
         <v>514</v>
       </c>
       <c r="C263" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B263, ""en"", ""ta"")"),"கட்டண விவரங்கள்")</f>
-        <v>கட்டண விவரங்கள்</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B263, ""en"", ""ta"")"),"பணம் செலுத்தும் விவரங்கள்")</f>
+        <v>பணம் செலுத்தும் விவரங்கள்</v>
       </c>
       <c r="D263" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B263, ""en"", ""hi"")"),"भुगतान विवरण")</f>
@@ -16184,8 +16275,8 @@
         <v>390</v>
       </c>
       <c r="C266" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B266, ""en"", ""ta"")"),"வருவாய்")</f>
-        <v>வருவாய்</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B266, ""en"", ""ta"")"),"வருமானம்")</f>
+        <v>வருமானம்</v>
       </c>
       <c r="D266" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B266, ""en"", ""hi"")"),"आय")</f>
@@ -16871,8 +16962,8 @@
         <v>സവാരി സ്വീകരിക്കുക</v>
       </c>
       <c r="G290" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B290, ""en"", ""te"")"),"రైడ్‌ను అంగీకరించండి")</f>
-        <v>రైడ్‌ను అంగీకరించండి</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B290, ""en"", ""te"")"),"ప్రయాణాన్ని అంగీకరించండి")</f>
+        <v>ప్రయాణాన్ని అంగీకరించండి</v>
       </c>
     </row>
     <row r="291">
@@ -16899,8 +16990,8 @@
         <v>ബുക്ക് ചെയ്തത്</v>
       </c>
       <c r="G291" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B291, ""en"", ""te"")"),"బుక్ చేయబడింది")</f>
-        <v>బుక్ చేయబడింది</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B291, ""en"", ""te"")"),"ఇక్కడ బుక్ చేయబడింది")</f>
+        <v>ఇక్కడ బుక్ చేయబడింది</v>
       </c>
     </row>
     <row r="292">
@@ -17107,8 +17198,8 @@
         <v>582</v>
       </c>
       <c r="C299" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B299, ""en"", ""ta"")"),"OTP ஐ உள்ளிடவும்")</f>
-        <v>OTP ஐ உள்ளிடவும்</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B299, ""en"", ""ta"")"),"OTP-ஐ உள்ளிடவும்")</f>
+        <v>OTP-ஐ உள்ளிடவும்</v>
       </c>
       <c r="D299" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B299, ""en"", ""hi"")"),"ओटीपी दर्ज करें")</f>
@@ -17555,8 +17646,8 @@
         <v>612</v>
       </c>
       <c r="C315" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B315, ""en"", ""ta"")"),"பயணத்தை ரத்துசெய்")</f>
-        <v>பயணத்தை ரத்துசெய்</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B315, ""en"", ""ta"")"),"பயணத்தை ரத்து செய்")</f>
+        <v>பயணத்தை ரத்து செய்</v>
       </c>
       <c r="D315" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B315, ""en"", ""hi"")"),"राइड रद्द करें")</f>
@@ -17571,8 +17662,8 @@
         <v>റൈഡ് റദ്ദാക്കുക</v>
       </c>
       <c r="G315" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B315, ""en"", ""te"")"),"రైడ్‌ను రద్దు చేయి")</f>
-        <v>రైడ్‌ను రద్దు చేయి</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B315, ""en"", ""te"")"),"రైడ్‌ను రద్దు చేయండి")</f>
+        <v>రైడ్‌ను రద్దు చేయండి</v>
       </c>
     </row>
     <row r="316">
@@ -17783,8 +17874,8 @@
         <v>மோசமான போக்குவரத்து அல்லது வானிலை நிலைமைகள்</v>
       </c>
       <c r="D323" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B323, ""en"", ""hi"")"),"यातायात की खराब स्थिति या मौसम की स्थिति")</f>
-        <v>यातायात की खराब स्थिति या मौसम की स्थिति</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B323, ""en"", ""hi"")"),"खराब यातायात या खराब मौसम की स्थिति")</f>
+        <v>खराब यातायात या खराब मौसम की स्थिति</v>
       </c>
       <c r="E323" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B323, ""en"", ""kn"")"),"ಕಳಪೆ ಸಂಚಾರ ಅಥವಾ ಹವಾಮಾನ ಪರಿಸ್ಥಿತಿಗಳು")</f>
@@ -18259,8 +18350,8 @@
         <v>உங்கள் பிரச்சினையை விவரியுங்கள், அதைத் தீர்க்க நாங்கள் உங்களுக்கு உதவுவோம்.</v>
       </c>
       <c r="D340" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B340, ""en"", ""hi"")"),"अपनी समस्या का वर्णन करें, हम उसे हल करने में आपकी सहायता करेंगे।")</f>
-        <v>अपनी समस्या का वर्णन करें, हम उसे हल करने में आपकी सहायता करेंगे।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B340, ""en"", ""hi"")"),"अपनी समस्या का वर्णन करें और हम इसे हल करने में आपकी सहायता करेंगे।")</f>
+        <v>अपनी समस्या का वर्णन करें और हम इसे हल करने में आपकी सहायता करेंगे।</v>
       </c>
       <c r="E340" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B340, ""en"", ""kn"")"),"ನಿಮ್ಮ ಸಮಸ್ಯೆಯನ್ನು ವಿವರಿಸಿ, ಅದನ್ನು ಪರಿಹರಿಸಲು ನಾವು ನಿಮಗೆ ಸಹಾಯ ಮಾಡುತ್ತೇವೆ.")</f>
@@ -18323,8 +18414,8 @@
         <v>ಅಪ್ಲಿಕೇಶನ್ ಸಂಬಂಧಿತ</v>
       </c>
       <c r="F342" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B342, ""en"", ""ml"")"),"ആപ്പ് അനുബന്ധം")</f>
-        <v>ആപ്പ് അനുബന്ധം</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B342, ""en"", ""ml"")"),"അനുബന്ധ ആപ്പ്")</f>
+        <v>അനുബന്ധ ആപ്പ്</v>
       </c>
       <c r="G342" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B342, ""en"", ""te"")"),"యాప్ సంబంధిత")</f>
@@ -19139,8 +19230,8 @@
         <v>ദയവായി നിങ്ങളുടെ ഫോൺ നമ്പർ നൽകുക.</v>
       </c>
       <c r="G371" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B371, ""en"", ""te"")"),"దయచేసి మీ ఫోన్ నంబర్‌ను నమోదు చేయండి.")</f>
-        <v>దయచేసి మీ ఫోన్ నంబర్‌ను నమోదు చేయండి.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B371, ""en"", ""te"")"),"దయచేసి మీ ఫోన్ నంబర్‌ను నమోదు చేయండి")</f>
+        <v>దయచేసి మీ ఫోన్ నంబర్‌ను నమోదు చేయండి</v>
       </c>
     </row>
     <row r="372">
@@ -19727,8 +19818,8 @@
         <v>ദയവായി സാധുവായ ഒരു ഇമെയിൽ വിലാസം നൽകുക.</v>
       </c>
       <c r="G392" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B392, ""en"", ""te"")"),"దయచేసి చెల్లుబాటు అయ్యే ఇమెయిల్‌ను నమోదు చేయండి.")</f>
-        <v>దయచేసి చెల్లుబాటు అయ్యే ఇమెయిల్‌ను నమోదు చేయండి.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B392, ""en"", ""te"")"),"దయచేసి చెల్లుబాటు అయ్యే ఇమెయిల్‌ను నమోదు చేయండి")</f>
+        <v>దయచేసి చెల్లుబాటు అయ్యే ఇమెయిల్‌ను నమోదు చేయండి</v>
       </c>
     </row>
     <row r="393">
@@ -20135,8 +20226,8 @@
         <v>செயலி திறந்திருக்காத போதும் உங்கள் இருப்பிடத்தைக் கண்காணிக்க, NOT செயலிக்குப் பின்னணி இருப்பிட அனுமதி தேவையில்லை. இது தொடர்ச்சியான கண்காணிப்பை அனுமதிப்பதோடு, எல்லா நேரங்களிலும் துல்லியமான இருப்பிடத் தரவு சேகரிக்கப்படுவதையும் உறுதி செய்கிறது.</v>
       </c>
       <c r="D407" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B407, ""en"", ""hi"")"),"NOT ऐप को आपके स्थान को ट्रैक करने के लिए बैकग्राउंड लोकेशन अनुमति की आवश्यकता होती है, भले ही ऐप खुला न हो। इससे निरंतर ट्रैकिंग संभव होती है और यह सुनिश्चित होता है कि हर समय सटीक स्थान डेटा एकत्र किया जाए।")</f>
-        <v>NOT ऐप को आपके स्थान को ट्रैक करने के लिए बैकग्राउंड लोकेशन अनुमति की आवश्यकता होती है, भले ही ऐप खुला न हो। इससे निरंतर ट्रैकिंग संभव होती है और यह सुनिश्चित होता है कि हर समय सटीक स्थान डेटा एकत्र किया जाए।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B407, ""en"", ""hi"")"),"NOT ऐप के बंद होने पर भी आपकी लोकेशन ट्रैक करने के लिए बैकग्राउंड लोकेशन परमिशन की आवश्यकता होती है। इससे लगातार ट्रैकिंग संभव होती है और यह सुनिश्चित होता है कि हर समय सटीक लोकेशन डेटा एकत्र किया जाए।")</f>
+        <v>NOT ऐप के बंद होने पर भी आपकी लोकेशन ट्रैक करने के लिए बैकग्राउंड लोकेशन परमिशन की आवश्यकता होती है। इससे लगातार ट्रैकिंग संभव होती है और यह सुनिश्चित होता है कि हर समय सटीक लोकेशन डेटा एकत्र किया जाए।</v>
       </c>
       <c r="E407" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B407, ""en"", ""kn"")"),"ಅಪ್ಲಿಕೇಶನ್ ತೆರೆದಿಲ್ಲದಿದ್ದರೂ ಸಹ ನಿಮ್ಮ ಸ್ಥಳವನ್ನು ಟ್ರ್ಯಾಕ್ ಮಾಡಲು NOT ಗೆ ಹಿನ್ನೆಲೆ ಸ್ಥಳ ಅನುಮತಿ ಅಗತ್ಯವಿಲ್ಲ. ಇದು ನಿರಂತರ ಟ್ರ್ಯಾಕಿಂಗ್‌ಗೆ ಅವಕಾಶ ನೀಡುತ್ತದೆ ಮತ್ತು ಎಲ್ಲಾ ಸಮಯದಲ್ಲೂ ನಿಖರವಾದ ಸ್ಥಳ ಡೇಟಾವನ್ನು ಸಂಗ್ರಹಿಸಲಾಗಿದೆ ಎಂದು ಖಚಿತಪಡಿಸುತ್ತದೆ.")</f>
@@ -20623,8 +20714,8 @@
         <v>വിളി</v>
       </c>
       <c r="G424" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B424, ""en"", ""te"")"),"కాల్ చేయండి")</f>
-        <v>కాల్ చేయండి</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B424, ""en"", ""te"")"),"కాల్")</f>
+        <v>కాల్</v>
       </c>
     </row>
     <row r="425">
@@ -20663,8 +20754,8 @@
         <v>830</v>
       </c>
       <c r="C426" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B426, ""en"", ""ta"")"),"முகப்புப் பக்கம்")</f>
-        <v>முகப்புப் பக்கம்</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B426, ""en"", ""ta"")"),"வீடு")</f>
+        <v>வீடு</v>
       </c>
       <c r="D426" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B426, ""en"", ""hi"")"),"घर")</f>
@@ -20887,8 +20978,8 @@
         <v>842</v>
       </c>
       <c r="C434" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B434, ""en"", ""ta"")"),"மொபைல் எண்")</f>
-        <v>மொபைல் எண்</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B434, ""en"", ""ta"")"),"கைபேசி எண்")</f>
+        <v>கைபேசி எண்</v>
       </c>
       <c r="D434" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B434, ""en"", ""hi"")"),"मोबाइल नंबर")</f>
@@ -21207,8 +21298,8 @@
         <v>ಸಂಪರ್ಕಿಸಿ</v>
       </c>
       <c r="F445" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B445, ""en"", ""ml"")"),"വാര്ത്താവിനിമയം")</f>
-        <v>വാര്ത്താവിനിമയം</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B445, ""en"", ""ml"")"),"ബന്ധപ്പെടുക")</f>
+        <v>ബന്ധപ്പെടുക</v>
       </c>
       <c r="G445" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B445, ""en"", ""te"")"),"సంప్రదించండి")</f>
@@ -21307,8 +21398,8 @@
         <v>870</v>
       </c>
       <c r="C449" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B449, ""en"", ""ta"")"),"எங்களை பற்றி")</f>
-        <v>எங்களை பற்றி</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B449, ""en"", ""ta"")"),"எங்களைப் பற்றி")</f>
+        <v>எங்களைப் பற்றி</v>
       </c>
       <c r="D449" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B449, ""en"", ""hi"")"),"हमारे बारे में")</f>
@@ -21424,8 +21515,8 @@
         <v>अलग हुए</v>
       </c>
       <c r="E453" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B453, ""en"", ""kn"")"),"ಬೇರೆಡೆಗೆ ತಿರುಗಿತು")</f>
-        <v>ಬೇರೆಡೆಗೆ ತಿರುಗಿತು</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B453, ""en"", ""kn"")"),"ವಿಭಾಗಿಸಲಾಗಿದೆ")</f>
+        <v>ವಿಭಾಗಿಸಲಾಗಿದೆ</v>
       </c>
       <c r="F453" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B453, ""en"", ""ml"")"),"വിഘടിച്ചു")</f>
@@ -22159,8 +22250,8 @@
         <v>പുസ്തക യാത്ര</v>
       </c>
       <c r="G480" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B480, ""en"", ""te"")"),"బుక్ రైడ్")</f>
-        <v>బుక్ రైడ్</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B480, ""en"", ""te"")"),"రైడ్ బుక్ చేయండి")</f>
+        <v>రైడ్ బుక్ చేయండి</v>
       </c>
     </row>
     <row r="481">
@@ -22454,8 +22545,8 @@
         <v>ನಿಲ್ಲಿಸುವುದನ್ನು ದೃಢೀಕರಿಸಿ {ನಿಲುಗಡೆ}</v>
       </c>
       <c r="F491" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B491, ""en"", ""ml"")"),"നിർത്തുക {നിർത്തുക} സ്ഥിരീകരിക്കുക")</f>
-        <v>നിർത്തുക {നിർത്തുക} സ്ഥിരീകരിക്കുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B491, ""en"", ""ml"")"),"നിർത്തുക സ്ഥിരീകരിക്കുക {നിർത്തുക}")</f>
+        <v>നിർത്തുക സ്ഥിരീകരിക്കുക {നിർത്തുക}</v>
       </c>
       <c r="G491" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B491, ""en"", ""te"")"),"ఆపడాన్ని నిర్ధారించండి {stop}")</f>
@@ -22595,8 +22686,8 @@
         <v>ബുക്കിംഗ് റദ്ദാക്കുക</v>
       </c>
       <c r="G496" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B496, ""en"", ""te"")"),"బుకింగ్ రద్దు చేయి")</f>
-        <v>బుకింగ్ రద్దు చేయి</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B496, ""en"", ""te"")"),"బుకింగ్‌ను రద్దు చేయండి")</f>
+        <v>బుకింగ్‌ను రద్దు చేయండి</v>
       </c>
     </row>
     <row r="497">
@@ -22862,8 +22953,8 @@
         <v>"ಯಾವಾಗಲೂ" ಅಥವಾ "ಆ್ಯಪ್ ಬಳಸುವಾಗ" ಆಯ್ಕೆಮಾಡಿ.</v>
       </c>
       <c r="F506" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B506, ""en"", ""ml"")"),"""എല്ലായ്‌പ്പോഴും"" അല്ലെങ്കിൽ ""ആപ്പ് ഉപയോഗിക്കുമ്പോൾ"" തിരഞ്ഞെടുക്കുക.")</f>
-        <v>"എല്ലായ്‌പ്പോഴും" അല്ലെങ്കിൽ "ആപ്പ് ഉപയോഗിക്കുമ്പോൾ" തിരഞ്ഞെടുക്കുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B506, ""en"", ""ml"")"),"""എല്ലായ്പ്പോഴും"" അല്ലെങ്കിൽ ""ആപ്പ് ഉപയോഗിക്കുമ്പോൾ"" തിരഞ്ഞെടുക്കുക.")</f>
+        <v>"എല്ലായ്പ്പോഴും" അല്ലെങ്കിൽ "ആപ്പ് ഉപയോഗിക്കുമ്പോൾ" തിരഞ്ഞെടുക്കുക.</v>
       </c>
       <c r="G506" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B506, ""en"", ""te"")"),"""ఎల్లప్పుడూ"" లేదా ""యాప్‌ను ఉపయోగిస్తున్నప్పుడు"" ఎంచుకోండి")</f>
@@ -24399,8 +24490,8 @@
         <v>नम्मा ऊरु टैक्सी के साथ ड्राइव करें</v>
       </c>
       <c r="E563" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B563, ""en"", ""kn"")"),"ನಮ್ಮ ಊರು ಟ್ಯಾಕ್ಸಿಯೊಂದಿಗೆ ಚಾಲನೆ ಮಾಡಿ")</f>
-        <v>ನಮ್ಮ ಊರು ಟ್ಯಾಕ್ಸಿಯೊಂದಿಗೆ ಚಾಲನೆ ಮಾಡಿ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B563, ""en"", ""kn"")"),"ನಮ್ಮ ಊರು ಟ್ಯಾಕ್ಸಿ ಜೊತೆ ಡ್ರೈವ್ ಮಾಡಿ")</f>
+        <v>ನಮ್ಮ ಊರು ಟ್ಯಾಕ್ಸಿ ಜೊತೆ ಡ್ರೈವ್ ಮಾಡಿ</v>
       </c>
       <c r="F563" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B563, ""en"", ""ml"")"),"നമ്മ ഊരു ടാക്സിയിൽ യാത്ര ചെയ്യൂ")</f>
@@ -24434,8 +24525,8 @@
         <v>നമ്മ ഊരു ടാക്സി ഡ്രൈവർ ആപ്പ് സൈൻ അപ്പ് ചെയ്യുക</v>
       </c>
       <c r="G564" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B564, ""en"", ""te"")"),"సైన్అప్ నమ్మ ఊరు టాక్సీ డ్రైవర్ యాప్")</f>
-        <v>సైన్అప్ నమ్మ ఊరు టాక్సీ డ్రైవర్ యాప్</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B564, ""en"", ""te"")"),"సైన్ అప్ నమ్మ ఊరు టాక్సీ డ్రైవర్ యాప్")</f>
+        <v>సైన్ అప్ నమ్మ ఊరు టాక్సీ డ్రైవర్ యాప్</v>
       </c>
     </row>
     <row r="565">
@@ -26786,8 +26877,8 @@
         <v>റൈഡുകൾ നേടുന്നതിൽ പരാജയപ്പെട്ടു</v>
       </c>
       <c r="G651" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B651, ""en"", ""te"")"),"ప్రయాణం దొరకలేదు")</f>
-        <v>ప్రయాణం దొరకలేదు</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B651, ""en"", ""te"")"),"రైడ్‌లు దొరకలేదు")</f>
+        <v>రైడ్‌లు దొరకలేదు</v>
       </c>
     </row>
     <row r="652">
@@ -28001,8 +28092,8 @@
         <v>ഫീഡ്‌ബാക്ക് വിജയകരമായി സമർപ്പിച്ചു.</v>
       </c>
       <c r="G696" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B696, ""en"", ""te"")"),"అభిప్రాయం విజయవంతంగా సమర్పించబడింది.")</f>
-        <v>అభిప్రాయం విజయవంతంగా సమర్పించబడింది.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B696, ""en"", ""te"")"),"అభిప్రాయం విజయవంతంగా సమర్పించబడింది")</f>
+        <v>అభిప్రాయం విజయవంతంగా సమర్పించబడింది</v>
       </c>
     </row>
     <row r="697">
@@ -30295,8 +30386,8 @@
         <v>ഫലങ്ങളൊന്നും കണ്ടെത്തിയില്ല</v>
       </c>
       <c r="G781" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B781, ""en"", ""te"")"),"ఫలితాలు కనుగొనబడలేదు")</f>
-        <v>ఫలితాలు కనుగొనబడలేదు</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B781, ""en"", ""te"")"),"ఫలితాలు ఏవీ కనుగొనబడలేదు")</f>
+        <v>ఫలితాలు ఏవీ కనుగొనబడలేదు</v>
       </c>
     </row>
     <row r="782">
@@ -30314,8 +30405,8 @@
         <v>कोई सुरक्षित स्थान नहीं</v>
       </c>
       <c r="E782" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B782, ""en"", ""kn"")"),"ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ")</f>
-        <v>ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B782, ""en"", ""kn"")"),"ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ.")</f>
+        <v>ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ.</v>
       </c>
       <c r="F782" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B782, ""en"", ""ml"")"),"സംരക്ഷിച്ച സ്ഥലങ്ങളൊന്നുമില്ല.")</f>
@@ -30364,8 +30455,8 @@
         <v>1832</v>
       </c>
       <c r="D784" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B784, ""en"", ""hi"")"),"फिलहाल आस-पास कोई नाइट ड्राइवर उपलब्ध नहीं है। आप चाहें तो सभी ड्राइवरों को खोज सकते हैं।")</f>
-        <v>फिलहाल आस-पास कोई नाइट ड्राइवर उपलब्ध नहीं है। आप चाहें तो सभी ड्राइवरों को खोज सकते हैं।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B784, ""en"", ""hi"")"),"इस समय आस-पास कोई नाइट ड्राइवर उपलब्ध नहीं है। आप चाहें तो सभी ड्राइवरों को खोज सकते हैं।")</f>
+        <v>इस समय आस-पास कोई नाइट ड्राइवर उपलब्ध नहीं है। आप चाहें तो सभी ड्राइवरों को खोज सकते हैं।</v>
       </c>
       <c r="E784" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B784, ""en"", ""kn"")"),"ಈಗ ಹತ್ತಿರದಲ್ಲಿ ಯಾವುದೇ ರಾತ್ರಿ ಚಾಲಕರು ಇಲ್ಲ. ಬದಲಿಗೆ ನೀವು ಎಲ್ಲಾ ಚಾಲಕರನ್ನು ಹುಡುಕಬಹುದು.")</f>
@@ -31012,8 +31103,8 @@
         <v>1902</v>
       </c>
       <c r="D808" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B808, ""en"", ""hi"")"),"यात्रा में देरी का चित्रण")</f>
-        <v>यात्रा में देरी का चित्रण</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B808, ""en"", ""hi"")"),"यात्रा में देरी का उदाहरण")</f>
+        <v>यात्रा में देरी का उदाहरण</v>
       </c>
       <c r="E808" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B808, ""en"", ""kn"")"),"ಪ್ರಯಾಣದ ಬಾಕಿ ಇರುವ ವಿವರಣೆ")</f>
@@ -33131,8 +33222,8 @@
         <v>ಸವಾರಿಯನ್ನು ಮಧ್ಯದಲ್ಲಿ ರದ್ದುಗೊಳಿಸಲಾಗಿದೆ.</v>
       </c>
       <c r="F886" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B886, ""en"", ""ml"")"),"യാത്ര പകുതി വഴിയിൽ റദ്ദാക്കി.")</f>
-        <v>യാത്ര പകുതി വഴിയിൽ റദ്ദാക്കി.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B886, ""en"", ""ml"")"),"യാത്ര പകുതി വഴിയിൽ വെച്ച് റദ്ദാക്കി.")</f>
+        <v>യാത്ര പകുതി വഴിയിൽ വെച്ച് റദ്ദാക്കി.</v>
       </c>
       <c r="G886" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B886, ""en"", ""te"")"),"ప్రయాణం మధ్యలోనే రద్దు చేయబడింది")</f>
@@ -33590,8 +33681,8 @@
         <v>ವೇಳಾಪಟ್ಟಿ</v>
       </c>
       <c r="F903" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B903, ""en"", ""ml"")"),"ഷെഡ്യൂൾ")</f>
-        <v>ഷെഡ്യൂൾ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B903, ""en"", ""ml"")"),"പട്ടിക")</f>
+        <v>പട്ടിക</v>
       </c>
       <c r="G903" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B903, ""en"", ""te"")"),"షెడ్యూల్")</f>
@@ -34218,8 +34309,8 @@
         <v>വീട്ടിലേക്കുള്ള യാത്രയായാലും ഓഫീസിലേക്കുള്ള യാത്രയായാലും സാഹസിക യാത്രയായാലും "നമ്മ ഊരു ടാക്സി®" നിങ്ങളെ അവിടെ കൊണ്ടുപോകാൻ തയ്യാറാണ്.</v>
       </c>
       <c r="G926" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B926, ""en"", ""te"")"),"ఇంటికి, ఆఫీసుకు ప్రయాణమైనా, లేదా సాహసయాత్రకైనా, ""నమ్మ ఊరు టాక్సీ ®"" మిమ్మల్ని అక్కడికి చేర్చడానికి సిద్ధంగా ఉంది.")</f>
-        <v>ఇంటికి, ఆఫీసుకు ప్రయాణమైనా, లేదా సాహసయాత్రకైనా, "నమ్మ ఊరు టాక్సీ ®" మిమ్మల్ని అక్కడికి చేర్చడానికి సిద్ధంగా ఉంది.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B926, ""en"", ""te"")"),"అది ఇంటి ప్రయాణమైనా, ఆఫీసుకైనా, లేదా ఒక సాహసయాత్రకైనా, ""నమ్మ ఊరు టాక్సీ ®"" మిమ్మల్ని అక్కడికి చేర్చడానికి సిద్ధంగా ఉంది.")</f>
+        <v>అది ఇంటి ప్రయాణమైనా, ఆఫీసుకైనా, లేదా ఒక సాహసయాత్రకైనా, "నమ్మ ఊరు టాక్సీ ®" మిమ్మల్ని అక్కడికి చేర్చడానికి సిద్ధంగా ఉంది.</v>
       </c>
     </row>
     <row r="927">
@@ -34407,8 +34498,8 @@
         <v>നക്ഷത്രം</v>
       </c>
       <c r="G933" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B933, ""en"", ""te"")"),"నక్షత్రం")</f>
-        <v>నక్షత్రం</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B933, ""en"", ""te"")"),"స్టార్")</f>
+        <v>స్టార్</v>
       </c>
     </row>
     <row r="934">
@@ -34542,8 +34633,8 @@
         <v>നിർത്തുക</v>
       </c>
       <c r="G938" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B938, ""en"", ""te"")"),"ఆపు")</f>
-        <v>ఆపు</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B938, ""en"", ""te"")"),"ఆపండి")</f>
+        <v>ఆపండి</v>
       </c>
     </row>
     <row r="939">
@@ -34781,8 +34872,8 @@
         <v>ಚಾಲಕ ತಡವಾಗಿ ಬಂದಿರುವುದು</v>
       </c>
       <c r="F947" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B947, ""en"", ""ml"")"),"ഡ്രൈവർ വൈകി എത്തൽ")</f>
-        <v>ഡ്രൈവർ വൈകി എത്തൽ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B947, ""en"", ""ml"")"),"ഡ്രൈവർ വൈകിയുള്ള വരവ്")</f>
+        <v>ഡ്രൈവർ വൈകിയുള്ള വരവ്</v>
       </c>
       <c r="G947" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B947, ""en"", ""te"")"),"డ్రైవర్ ఆలస్యంగా రావడం")</f>
@@ -34962,8 +35053,8 @@
         <v>2314</v>
       </c>
       <c r="D954" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B954, ""en"", ""hi"")"),"ड्राइवर बुक किए गए वाहन के बजाय किसी दूसरे प्रकार का वाहन लेकर आया (उदाहरण के लिए, एसयूवी के बजाय सेडान)।")</f>
-        <v>ड्राइवर बुक किए गए वाहन के बजाय किसी दूसरे प्रकार का वाहन लेकर आया (उदाहरण के लिए, एसयूवी के बजाय सेडान)।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B954, ""en"", ""hi"")"),"ड्राइवर बुक किए गए वाहन के प्रकार से भिन्न वाहन लेकर आया (उदाहरण के लिए, एसयूवी के बजाय सेडान)।")</f>
+        <v>ड्राइवर बुक किए गए वाहन के प्रकार से भिन्न वाहन लेकर आया (उदाहरण के लिए, एसयूवी के बजाय सेडान)।</v>
       </c>
       <c r="E954" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B954, ""en"", ""kn"")"),"ಚಾಲಕ ಬುಕ್ ಮಾಡಿದ ವಾಹನಕ್ಕಿಂತ ಬೇರೆ ವಾಹನ ಪ್ರಕಾರದೊಂದಿಗೆ ಬಂದಿದ್ದಾನೆ (ಉದಾ. SUV ಬದಲಿಗೆ ಸೆಡಾನ್)")</f>
@@ -35024,8 +35115,8 @@
         <v>ಅಪ್ಲಿಕೇಶನ್ ಸಂಬಂಧಿತ</v>
       </c>
       <c r="F956" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B956, ""en"", ""ml"")"),"ആപ്പ് അനുബന്ധം")</f>
-        <v>ആപ്പ് അനുബന്ധം</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B956, ""en"", ""ml"")"),"അനുബന്ധ ആപ്പ്")</f>
+        <v>അനുബന്ധ ആപ്പ്</v>
       </c>
       <c r="G956" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B956, ""en"", ""te"")"),"యాప్ సంబంధిత")</f>
@@ -35502,8 +35593,8 @@
         <v>2359</v>
       </c>
       <c r="D974" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B974, ""en"", ""hi"")"),"अपनी समस्या का वर्णन करें, हम उसे हल करने में आपकी सहायता करेंगे।")</f>
-        <v>अपनी समस्या का वर्णन करें, हम उसे हल करने में आपकी सहायता करेंगे।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B974, ""en"", ""hi"")"),"अपनी समस्या का वर्णन करें और हम इसे हल करने में आपकी सहायता करेंगे।")</f>
+        <v>अपनी समस्या का वर्णन करें और हम इसे हल करने में आपकी सहायता करेंगे।</v>
       </c>
       <c r="E974" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B974, ""en"", ""kn"")"),"ನಿಮ್ಮ ಸಮಸ್ಯೆಯನ್ನು ವಿವರಿಸಿ, ಅದನ್ನು ಪರಿಹರಿಸಲು ನಾವು ನಿಮಗೆ ಸಹಾಯ ಮಾಡುತ್ತೇವೆ.")</f>
@@ -36267,8 +36358,8 @@
         <v>{vehicleName} ಗರಿಷ್ಠ ದೂರ {maxKm} ಕಿ.ಮೀ. ದಯವಿಟ್ಟು ಬೇರೆ ವಾಹನವನ್ನು ಆಯ್ಕೆಮಾಡಿ ಅಥವಾ {maxKm} ಕಿ.ಮೀ.ಗಿಂತ ಕಡಿಮೆ ಪ್ರಯಾಣವನ್ನು ಯೋಜಿಸಿ.</v>
       </c>
       <c r="F1002" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1002, ""en"", ""ml"")"),"{vehicleName} പരമാവധി ദൂരം {maxKm} കിലോമീറ്ററാണ്. മറ്റൊരു വാഹനം തിരഞ്ഞെടുക്കുകയോ {maxKm} കിലോമീറ്ററിൽ താഴെയുള്ള യാത്ര പ്ലാൻ ചെയ്യുകയോ ചെയ്യുക.")</f>
-        <v>{vehicleName} പരമാവധി ദൂരം {maxKm} കിലോമീറ്ററാണ്. മറ്റൊരു വാഹനം തിരഞ്ഞെടുക്കുകയോ {maxKm} കിലോമീറ്ററിൽ താഴെയുള്ള യാത്ര പ്ലാൻ ചെയ്യുകയോ ചെയ്യുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1002, ""en"", ""ml"")"),"{vehicleName} പരമാവധി ദൂരം {maxKm} കിലോമീറ്ററാണ്. ദയവായി മറ്റൊരു വാഹനം തിരഞ്ഞെടുക്കുകയോ {maxKm} കിലോമീറ്ററിൽ താഴെയുള്ള യാത്ര പ്ലാൻ ചെയ്യുകയോ ചെയ്യുക.")</f>
+        <v>{vehicleName} പരമാവധി ദൂരം {maxKm} കിലോമീറ്ററാണ്. ദയവായി മറ്റൊരു വാഹനം തിരഞ്ഞെടുക്കുകയോ {maxKm} കിലോമീറ്ററിൽ താഴെയുള്ള യാത്ര പ്ലാൻ ചെയ്യുകയോ ചെയ്യുക.</v>
       </c>
       <c r="G1002" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1002, ""en"", ""te"")"),"{vehicleName} గరిష్ట దూరం {maxKm} కి.మీ. దయచేసి వేరే వాహనాన్ని ఎంచుకోండి లేదా {maxKm} కి.మీ. కంటే తక్కువ ప్రయాణాన్ని ప్లాన్ చేసుకోండి.")</f>
@@ -36564,8 +36655,8 @@
         <v>ಬೇರೆ ಹೆಸರು ಅಥವಾ ಸಂಖ್ಯೆಯನ್ನು ಪ್ರಯತ್ನಿಸಿ</v>
       </c>
       <c r="F1013" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1013, ""en"", ""ml"")"),"മറ്റൊരു പേരോ നമ്പറോ പരീക്ഷിച്ചുനോക്കൂ")</f>
-        <v>മറ്റൊരു പേരോ നമ്പറോ പരീക്ഷിച്ചുനോക്കൂ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1013, ""en"", ""ml"")"),"മറ്റൊരു പേരോ നമ്പറോ പരീക്ഷിക്കൂ")</f>
+        <v>മറ്റൊരു പേരോ നമ്പറോ പരീക്ഷിക്കൂ</v>
       </c>
       <c r="G1013" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1013, ""en"", ""te"")"),"వేరే పేరు లేదా నంబర్‌ను ప్రయత్నించండి")</f>
@@ -38101,8 +38192,8 @@
         <v>ಈ ಹಂತಗಳನ್ನು ಪೂರ್ಣಗೊಳಿಸಿ ಇದರಿಂದ ನೀವು ಸವಾರಿಗಳನ್ನು ಸ್ವೀಕರಿಸಲು ಪ್ರಾರಂಭಿಸಬಹುದು.</v>
       </c>
       <c r="F1069" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1069, ""en"", ""ml"")"),"റൈഡുകൾ സ്വീകരിച്ചു തുടങ്ങാൻ ഈ ഘട്ടങ്ങൾ പൂർത്തിയാക്കുക.")</f>
-        <v>റൈഡുകൾ സ്വീകരിച്ചു തുടങ്ങാൻ ഈ ഘട്ടങ്ങൾ പൂർത്തിയാക്കുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1069, ""en"", ""ml"")"),"റൈഡുകൾ സ്വീകരിക്കാൻ തുടങ്ങുന്നതിന് ഈ ഘട്ടങ്ങൾ പൂർത്തിയാക്കുക.")</f>
+        <v>റൈഡുകൾ സ്വീകരിക്കാൻ തുടങ്ങുന്നതിന് ഈ ഘട്ടങ്ങൾ പൂർത്തിയാക്കുക.</v>
       </c>
       <c r="G1069" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1069, ""en"", ""te"")"),"మీరు రైడ్‌లను స్వీకరించడం ప్రారంభించడానికి ఈ దశలను పూర్తి చేయండి")</f>
@@ -38205,8 +38296,8 @@
         <v>உரிம விவரங்களைக் கண்டறிய முடியவில்லை. புலங்களை கைமுறையாகப் புதுப்பிக்கவும்.</v>
       </c>
       <c r="D1073" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1073, ""en"", ""hi"")"),"लाइसेंस संबंधी जानकारी नहीं मिल पाई। कृपया फ़ील्ड को मैन्युअल रूप से अपडेट करें।")</f>
-        <v>लाइसेंस संबंधी जानकारी नहीं मिल पाई। कृपया फ़ील्ड को मैन्युअल रूप से अपडेट करें।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1073, ""en"", ""hi"")"),"लाइसेंस संबंधी विवरण नहीं मिल पाए। कृपया फ़ील्ड को मैन्युअल रूप से अपडेट करें।")</f>
+        <v>लाइसेंस संबंधी विवरण नहीं मिल पाए। कृपया फ़ील्ड को मैन्युअल रूप से अपडेट करें।</v>
       </c>
       <c r="E1073" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1073, ""en"", ""kn"")"),"ಪರವಾನಗಿ ವಿವರಗಳನ್ನು ಪತ್ತೆಹಚ್ಚಲು ಸಾಧ್ಯವಾಗಲಿಲ್ಲ. ಕ್ಷೇತ್ರಗಳನ್ನು ಹಸ್ತಚಾಲಿತವಾಗಿ ನವೀಕರಿಸಿ.")</f>
@@ -38345,8 +38436,8 @@
         <v>இந்தப் பயன்முறையில் திருத்தம் செய்வது முடக்கப்பட்டுள்ளது.</v>
       </c>
       <c r="D1078" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1078, ""en"", ""hi"")"),"इस मोड में संपादन की सुविधा अक्षम है।")</f>
-        <v>इस मोड में संपादन की सुविधा अक्षम है।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1078, ""en"", ""hi"")"),"इस मोड में संपादन अक्षम है।")</f>
+        <v>इस मोड में संपादन अक्षम है।</v>
       </c>
       <c r="E1078" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1078, ""en"", ""kn"")"),"ಈ ಕ್ರಮದಲ್ಲಿ ಸಂಪಾದನೆಯನ್ನು ನಿಷ್ಕ್ರಿಯಗೊಳಿಸಲಾಗಿದೆ.")</f>
@@ -38685,8 +38776,8 @@
         <v>ड्राइवर की फोटो अपलोड करें या कैप्चर करें</v>
       </c>
       <c r="E1090" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1090, ""en"", ""kn"")"),"ಚಾಲಕ ಫೋಟೋ ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ")</f>
-        <v>ಚಾಲಕ ಫೋಟೋ ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1090, ""en"", ""kn"")"),"ಚಾಲಕ ಫೋಟೋವನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ")</f>
+        <v>ಚಾಲಕ ಫೋಟೋವನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ</v>
       </c>
       <c r="F1090" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1090, ""en"", ""ml"")"),"ഡ്രൈവർ ഫോട്ടോ അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ പകർത്തുക")</f>
@@ -38899,8 +38990,8 @@
         <v>2678</v>
       </c>
       <c r="C1098" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1098, ""en"", ""ta"")"),"வங்கிக் கணக்கைச் சரிபார்க்கவும்")</f>
-        <v>வங்கிக் கணக்கைச் சரிபார்க்கவும்</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1098, ""en"", ""ta"")"),"வங்கி கணக்கை சரிபார்க்கவும்")</f>
+        <v>வங்கி கணக்கை சரிபார்க்கவும்</v>
       </c>
       <c r="D1098" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1098, ""en"", ""hi"")"),"बैंक खाते का सत्यापन करें")</f>
@@ -38987,8 +39078,8 @@
         <v>இந்தப் பயன்முறையில் திருத்தம் செய்வது முடக்கப்பட்டுள்ளது.</v>
       </c>
       <c r="D1101" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1101, ""en"", ""hi"")"),"इस मोड में संपादन की सुविधा अक्षम है।")</f>
-        <v>इस मोड में संपादन की सुविधा अक्षम है।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1101, ""en"", ""hi"")"),"इस मोड में संपादन अक्षम है।")</f>
+        <v>इस मोड में संपादन अक्षम है।</v>
       </c>
       <c r="E1101" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1101, ""en"", ""kn"")"),"ಈ ಕ್ರಮದಲ್ಲಿ ಸಂಪಾದನೆಯನ್ನು ನಿಷ್ಕ್ರಿಯಗೊಳಿಸಲಾಗಿದೆ.")</f>
@@ -39363,8 +39454,8 @@
         <v>ഈ യാത്ര റദ്ദാക്കണമെന്ന് നിങ്ങൾക്ക് ഉറപ്പാണോ? റദ്ദാക്കൽ പിഴ ബാധകമായേക്കാം.</v>
       </c>
       <c r="G1114" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1114, ""en"", ""te"")"),"మీరు ఈ యాత్రను రద్దు చేసుకోవాలని ఖచ్చితంగా అనుకుంటున్నారా? రద్దు చేసినందుకు జరిమానా వర్తించవచ్చు.")</f>
-        <v>మీరు ఈ యాత్రను రద్దు చేసుకోవాలని ఖచ్చితంగా అనుకుంటున్నారా? రద్దు చేసినందుకు జరిమానా వర్తించవచ్చు.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1114, ""en"", ""te"")"),"మీరు ఈ యాత్రను రద్దు చేయాలనుకుంటున్నారా? రద్దు చేసినందుకు జరిమానా వర్తించవచ్చు.")</f>
+        <v>మీరు ఈ యాత్రను రద్దు చేయాలనుకుంటున్నారా? రద్దు చేసినందుకు జరిమానా వర్తించవచ్చు.</v>
       </c>
     </row>
     <row r="1115">
@@ -39590,9 +39681,9 @@
       </c>
       <c r="F1122" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1122, ""en"", ""ml"")"),"ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
-ക്ഷമയ്ക്ക് നന്ദി.")</f>
+നിങ്ങളുടെ ക്ഷമയ്ക്ക് നന്ദി.")</f>
         <v>ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
-ക്ഷമയ്ക്ക് നന്ദി.</v>
+നിങ്ങളുടെ ക്ഷമയ്ക്ക് നന്ദി.</v>
       </c>
       <c r="G1122" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1122, ""en"", ""te"")"),"మేము టాక్సీలను సరిచూసి, ఆమోదించడానికి తీవ్రంగా కృషి చేస్తున్నాము. కాబట్టి, ఆమోద ప్రక్రియకు కొంత సమయం పడుతుందని దయచేసి అర్థం చేసుకోండి.
@@ -39781,8 +39872,8 @@
         <v>ஓட்டுநர் விவரங்களைப் பெற புதுப்பிக்கவும்</v>
       </c>
       <c r="D1129" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1129, ""en"", ""hi"")"),"ड्राइवर की जानकारी प्राप्त करने के लिए पेज को रिफ्रेश करें")</f>
-        <v>ड्राइवर की जानकारी प्राप्त करने के लिए पेज को रिफ्रेश करें</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1129, ""en"", ""hi"")"),"ड्राइवर की जानकारी प्राप्त करने के लिए पेज को रिफ्रेश करें।")</f>
+        <v>ड्राइवर की जानकारी प्राप्त करने के लिए पेज को रिफ्रेश करें।</v>
       </c>
       <c r="E1129" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1129, ""en"", ""kn"")"),"ಚಾಲಕ ವಿವರಗಳನ್ನು ಪಡೆಯಲು ರಿಫ್ರೆಶ್ ಮಾಡಿ")</f>
@@ -39849,8 +39940,8 @@
         <v>ഡ്രൈവറായി സൈൻ ഇൻ ചെയ്യാൻ നിങ്ങളെ ഉപഭോക്തൃ ആപ്പിൽ നിന്ന് ഞങ്ങൾ ലോഗ് ഔട്ട് ചെയ്യും. തുടരണോ?</v>
       </c>
       <c r="G1131" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1131, ""en"", ""te"")"),"మీరు డ్రైవర్‌గా సైన్ ఇన్ చేయడానికి వీలుగా, మేము మిమ్మల్ని కస్టమర్ యాప్ నుండి లాగ్ అవుట్ చేస్తాము. కొనసాగించాలా?")</f>
-        <v>మీరు డ్రైవర్‌గా సైన్ ఇన్ చేయడానికి వీలుగా, మేము మిమ్మల్ని కస్టమర్ యాప్ నుండి లాగ్ అవుట్ చేస్తాము. కొనసాగించాలా?</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1131, ""en"", ""te"")"),"మీరు డ్రైవర్‌గా సైన్ ఇన్ చేయడానికి వీలుగా మేము మిమ్మల్ని కస్టమర్ యాప్ నుండి లాగ్ అవుట్ చేస్తాము. కొనసాగించాలా?")</f>
+        <v>మీరు డ్రైవర్‌గా సైన్ ఇన్ చేయడానికి వీలుగా మేము మిమ్మల్ని కస్టమర్ యాప్ నుండి లాగ్ అవుట్ చేస్తాము. కొనసాగించాలా?</v>
       </c>
     </row>
     <row r="1132">
@@ -39945,8 +40036,8 @@
         <v>2747</v>
       </c>
       <c r="C1135" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1135, ""en"", ""ta"")"),"உங்கள் அமர்வு நேரம் முடிந்துவிட்டது. மீண்டும் உள்நுழையவும்.")</f>
-        <v>உங்கள் அமர்வு நேரம் முடிந்துவிட்டது. மீண்டும் உள்நுழையவும்.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1135, ""en"", ""ta"")"),"உங்கள் அமர்வு நேரம் முடிந்துவிட்டது. தயவுசெய்து மீண்டும் உள்நுழையவும்.")</f>
+        <v>உங்கள் அமர்வு நேரம் முடிந்துவிட்டது. தயவுசெய்து மீண்டும் உள்நுழையவும்.</v>
       </c>
       <c r="D1135" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1135, ""en"", ""hi"")"),"आपका सत्र समाप्त हो गया है। कृपया पुनः लॉग इन करें।")</f>
@@ -39957,8 +40048,8 @@
         <v>ನಿಮ್ಮ ಅವಧಿ ಮುಗಿದಿದೆ. ದಯವಿಟ್ಟು ಮತ್ತೆ ಲಾಗಿನ್ ಮಾಡಿ.</v>
       </c>
       <c r="F1135" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1135, ""en"", ""ml"")"),"നിങ്ങളുടെ സെഷൻ കാലഹരണപ്പെട്ടു. ദയവായി വീണ്ടും ലോഗിൻ ചെയ്യുക.")</f>
-        <v>നിങ്ങളുടെ സെഷൻ കാലഹരണപ്പെട്ടു. ദയവായി വീണ്ടും ലോഗിൻ ചെയ്യുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1135, ""en"", ""ml"")"),"നിങ്ങളുടെ സെഷൻ കാലഹരണപ്പെട്ടു. വീണ്ടും ലോഗിൻ ചെയ്യുക.")</f>
+        <v>നിങ്ങളുടെ സെഷൻ കാലഹരണപ്പെട്ടു. വീണ്ടും ലോഗിൻ ചെയ്യുക.</v>
       </c>
       <c r="G1135" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1135, ""en"", ""te"")"),"మీ సెషన్ గడువు ముగిసింది. దయచేసి మళ్ళీ లాగిన్ అవ్వండి.")</f>
@@ -40279,8 +40370,9 @@
       <c r="B1147" s="13" t="s">
         <v>2772</v>
       </c>
-      <c r="C1147" s="8" t="s">
-        <v>2773</v>
+      <c r="C1147" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1147, ""en"", ""ta"")"),"செயல்படும் ஓட்டுநர் உள்நுழைவு")</f>
+        <v>செயல்படும் ஓட்டுநர் உள்நுழைவு</v>
       </c>
       <c r="D1147" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1147, ""en"", ""hi"")"),"कार्यवाहक ड्राइवर लॉगिन")</f>
@@ -40300,137 +40392,536 @@
       </c>
     </row>
     <row r="1148">
-      <c r="A1148" s="4"/>
-      <c r="B1148" s="5"/>
-      <c r="C1148" s="6"/>
-      <c r="D1148" s="6"/>
-      <c r="E1148" s="6"/>
+      <c r="A1148" s="12" t="s">
+        <v>2773</v>
+      </c>
+      <c r="B1148" s="13" t="s">
+        <v>2774</v>
+      </c>
+      <c r="C1148" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1148, ""en"", ""ta"")"),"ஓட்டுநர் அனுபவம்")</f>
+        <v>ஓட்டுநர் அனுபவம்</v>
+      </c>
+      <c r="D1148" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1148, ""en"", ""hi"")"),"ड्राइविंग अनुभव")</f>
+        <v>ड्राइविंग अनुभव</v>
+      </c>
+      <c r="E1148" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1148, ""en"", ""kn"")"),"ಚಾಲನಾ ಅನುಭವ")</f>
+        <v>ಚಾಲನಾ ಅನುಭವ</v>
+      </c>
+      <c r="F1148" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1148, ""en"", ""ml"")"),"ഡ്രൈവിംഗ് അനുഭവം")</f>
+        <v>ഡ്രൈവിംഗ് അനുഭവം</v>
+      </c>
+      <c r="G1148" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1148, ""en"", ""te"")"),"డ్రైవింగ్ అనుభవం")</f>
+        <v>డ్రైవింగ్ అనుభవం</v>
+      </c>
     </row>
     <row r="1149">
-      <c r="A1149" s="4"/>
-      <c r="B1149" s="5"/>
-      <c r="C1149" s="24"/>
-      <c r="D1149" s="6"/>
-      <c r="E1149" s="6"/>
+      <c r="A1149" s="12" t="s">
+        <v>2775</v>
+      </c>
+      <c r="B1149" s="13" t="s">
+        <v>2776</v>
+      </c>
+      <c r="C1149" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1149, ""en"", ""ta"")"),"மொத்த ஓட்டுநர் அனுபவம்")</f>
+        <v>மொத்த ஓட்டுநர் அனுபவம்</v>
+      </c>
+      <c r="D1149" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1149, ""en"", ""hi"")"),"संपूर्ण ड्राइविंग अनुभव")</f>
+        <v>संपूर्ण ड्राइविंग अनुभव</v>
+      </c>
+      <c r="E1149" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1149, ""en"", ""kn"")"),"ಒಟ್ಟು ಚಾಲನಾ ಅನುಭವ")</f>
+        <v>ಒಟ್ಟು ಚಾಲನಾ ಅನುಭವ</v>
+      </c>
+      <c r="F1149" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1149, ""en"", ""ml"")"),"ആകെ ഡ്രൈവിംഗ് അനുഭവം")</f>
+        <v>ആകെ ഡ്രൈവിംഗ് അനുഭവം</v>
+      </c>
+      <c r="G1149" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1149, ""en"", ""te"")"),"మొత్తం డ్రైవింగ్ అనుభవం")</f>
+        <v>మొత్తం డ్రైవింగ్ అనుభవం</v>
+      </c>
     </row>
     <row r="1150">
-      <c r="A1150" s="4"/>
-      <c r="B1150" s="5"/>
-      <c r="C1150" s="6"/>
-      <c r="D1150" s="6"/>
-      <c r="E1150" s="6"/>
+      <c r="A1150" s="12" t="s">
+        <v>2777</v>
+      </c>
+      <c r="B1150" s="13" t="s">
+        <v>2778</v>
+      </c>
+      <c r="C1150" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1150, ""en"", ""ta"")"),"வணிக ஓட்டுநர் அனுபவம்")</f>
+        <v>வணிக ஓட்டுநர் அனுபவம்</v>
+      </c>
+      <c r="D1150" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1150, ""en"", ""hi"")"),"वाणिज्यिक ड्राइविंग अनुभव")</f>
+        <v>वाणिज्यिक ड्राइविंग अनुभव</v>
+      </c>
+      <c r="E1150" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1150, ""en"", ""kn"")"),"ವಾಣಿಜ್ಯ ಚಾಲನಾ ಅನುಭವ")</f>
+        <v>ವಾಣಿಜ್ಯ ಚಾಲನಾ ಅನುಭವ</v>
+      </c>
+      <c r="F1150" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1150, ""en"", ""ml"")"),"വാണിജ്യ ഡ്രൈവിംഗ് അനുഭവം")</f>
+        <v>വാണിജ്യ ഡ്രൈവിംഗ് അനുഭവം</v>
+      </c>
+      <c r="G1150" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1150, ""en"", ""te"")"),"వాణిజ్య డ్రైవింగ్ అనుభవం")</f>
+        <v>వాణిజ్య డ్రైవింగ్ అనుభవం</v>
+      </c>
     </row>
     <row r="1151">
-      <c r="A1151" s="4"/>
-      <c r="B1151" s="5"/>
-      <c r="C1151" s="6"/>
-      <c r="D1151" s="6"/>
-      <c r="E1151" s="6"/>
+      <c r="A1151" s="12" t="s">
+        <v>2779</v>
+      </c>
+      <c r="B1151" s="13" t="s">
+        <v>2780</v>
+      </c>
+      <c r="C1151" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1151, ""en"", ""ta"")"),"சவாரி முன்பதிவு தள அனுபவம்")</f>
+        <v>சவாரி முன்பதிவு தள அனுபவம்</v>
+      </c>
+      <c r="D1151" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1151, ""en"", ""hi"")"),"राइड-हेलिंग प्लेटफॉर्म का अनुभव")</f>
+        <v>राइड-हेलिंग प्लेटफॉर्म का अनुभव</v>
+      </c>
+      <c r="E1151" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1151, ""en"", ""kn"")"),"ರೈಡ್-ಹೇಲಿಂಗ್ ಪ್ಲಾಟ್‌ಫಾರ್ಮ್ ಅನುಭವ")</f>
+        <v>ರೈಡ್-ಹೇಲಿಂಗ್ ಪ್ಲಾಟ್‌ಫಾರ್ಮ್ ಅನುಭವ</v>
+      </c>
+      <c r="F1151" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1151, ""en"", ""ml"")"),"റൈഡ്-ഹെയ്‌ലിംഗ് പ്ലാറ്റ്‌ഫോം അനുഭവം")</f>
+        <v>റൈഡ്-ഹെയ്‌ലിംഗ് പ്ലാറ്റ്‌ഫോം അനുഭവം</v>
+      </c>
+      <c r="G1151" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1151, ""en"", ""te"")"),"రైడ్-హెయిలింగ్ ప్లాట్‌ఫారమ్ అనుభవం")</f>
+        <v>రైడ్-హెయిలింగ్ ప్లాట్‌ఫారమ్ అనుభవం</v>
+      </c>
     </row>
     <row r="1152">
-      <c r="A1152" s="4"/>
-      <c r="B1152" s="5"/>
-      <c r="C1152" s="6"/>
-      <c r="D1152" s="6"/>
-      <c r="E1152" s="6"/>
+      <c r="A1152" s="12" t="s">
+        <v>2781</v>
+      </c>
+      <c r="B1152" s="13" t="s">
+        <v>2782</v>
+      </c>
+      <c r="C1152" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1152, ""en"", ""ta"")"),"பணிபுரிந்த தளங்கள்")</f>
+        <v>பணிபுரிந்த தளங்கள்</v>
+      </c>
+      <c r="D1152" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1152, ""en"", ""hi"")"),"जिन प्लेटफॉर्मों के साथ काम किया गया")</f>
+        <v>जिन प्लेटफॉर्मों के साथ काम किया गया</v>
+      </c>
+      <c r="E1152" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1152, ""en"", ""kn"")"),"ಕೆಲಸ ಮಾಡಿದ ವೇದಿಕೆಗಳು")</f>
+        <v>ಕೆಲಸ ಮಾಡಿದ ವೇದಿಕೆಗಳು</v>
+      </c>
+      <c r="F1152" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1152, ""en"", ""ml"")"),"ഉപയോഗിച്ച പ്ലാറ്റ്‌ഫോമുകൾ")</f>
+        <v>ഉപയോഗിച്ച പ്ലാറ്റ്‌ഫോമുകൾ</v>
+      </c>
+      <c r="G1152" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1152, ""en"", ""te"")"),"ప్లాట్‌ఫారమ్‌లు కలిసి పనిచేశాయి")</f>
+        <v>ప్లాట్‌ఫారమ్‌లు కలిసి పనిచేశాయి</v>
+      </c>
     </row>
     <row r="1153">
-      <c r="A1153" s="4"/>
-      <c r="B1153" s="5"/>
-      <c r="C1153" s="6"/>
-      <c r="D1153" s="6"/>
-      <c r="E1153" s="6"/>
+      <c r="A1153" s="12" t="s">
+        <v>2783</v>
+      </c>
+      <c r="B1153" s="13" t="s">
+        <v>2784</v>
+      </c>
+      <c r="C1153" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1153, ""en"", ""ta"")"),"தோராயமாக முடிக்கப்பட்ட பயணங்கள்")</f>
+        <v>தோராயமாக முடிக்கப்பட்ட பயணங்கள்</v>
+      </c>
+      <c r="D1153" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1153, ""en"", ""hi"")"),"लगभग पूर्ण यात्राएँ")</f>
+        <v>लगभग पूर्ण यात्राएँ</v>
+      </c>
+      <c r="E1153" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1153, ""en"", ""kn"")"),"ಸರಿಸುಮಾರು ಪೂರ್ಣಗೊಂಡ ಪ್ರವಾಸಗಳು")</f>
+        <v>ಸರಿಸುಮಾರು ಪೂರ್ಣಗೊಂಡ ಪ್ರವಾಸಗಳು</v>
+      </c>
+      <c r="F1153" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1153, ""en"", ""ml"")"),"ഏകദേശം പൂർത്തിയാക്കിയ യാത്രകൾ")</f>
+        <v>ഏകദേശം പൂർത്തിയാക്കിയ യാത്രകൾ</v>
+      </c>
+      <c r="G1153" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1153, ""en"", ""te"")"),"సుమారుగా పూర్తి చేసిన పర్యటనలు")</f>
+        <v>సుమారుగా పూర్తి చేసిన పర్యటనలు</v>
+      </c>
     </row>
     <row r="1154">
-      <c r="A1154" s="4"/>
-      <c r="B1154" s="5"/>
-      <c r="C1154" s="6"/>
-      <c r="D1154" s="6"/>
-      <c r="E1154" s="6"/>
+      <c r="A1154" s="12" t="s">
+        <v>2785</v>
+      </c>
+      <c r="B1154" s="13" t="s">
+        <v>2786</v>
+      </c>
+      <c r="C1154" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1154, ""en"", ""ta"")"),"ஓட்டுநர் மதிப்பீடு")</f>
+        <v>ஓட்டுநர் மதிப்பீடு</v>
+      </c>
+      <c r="D1154" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1154, ""en"", ""hi"")"),"ड्राइवर रेटिंग")</f>
+        <v>ड्राइवर रेटिंग</v>
+      </c>
+      <c r="E1154" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1154, ""en"", ""kn"")"),"ಚಾಲಕ ರೇಟಿಂಗ್")</f>
+        <v>ಚಾಲಕ ರೇಟಿಂಗ್</v>
+      </c>
+      <c r="F1154" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1154, ""en"", ""ml"")"),"ഡ്രൈവർ റേറ്റിംഗ്")</f>
+        <v>ഡ്രൈവർ റേറ്റിംഗ്</v>
+      </c>
+      <c r="G1154" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1154, ""en"", ""te"")"),"డ్రైవర్ రేటింగ్")</f>
+        <v>డ్రైవర్ రేటింగ్</v>
+      </c>
     </row>
     <row r="1155">
-      <c r="A1155" s="4"/>
-      <c r="B1155" s="5"/>
-      <c r="C1155" s="6"/>
-      <c r="D1155" s="6"/>
-      <c r="E1155" s="6"/>
+      <c r="A1155" s="12" t="s">
+        <v>2787</v>
+      </c>
+      <c r="B1155" s="13" t="s">
+        <v>2788</v>
+      </c>
+      <c r="C1155" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1155, ""en"", ""ta"")"),"தயவுசெய்து பரிமாற்ற வகையைத் தேர்ந்தெடுக்கவும்")</f>
+        <v>தயவுசெய்து பரிமாற்ற வகையைத் தேர்ந்தெடுக்கவும்</v>
+      </c>
+      <c r="D1155" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1155, ""en"", ""hi"")"),"कृपया संचरण प्रकार का चयन करें")</f>
+        <v>कृपया संचरण प्रकार का चयन करें</v>
+      </c>
+      <c r="E1155" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1155, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ಪ್ರಸರಣ ಪ್ರಕಾರವನ್ನು ಆಯ್ಕೆಮಾಡಿ")</f>
+        <v>ದಯವಿಟ್ಟು ಪ್ರಸರಣ ಪ್ರಕಾರವನ್ನು ಆಯ್ಕೆಮಾಡಿ</v>
+      </c>
+      <c r="F1155" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1155, ""en"", ""ml"")"),"ദയവായി ട്രാൻസ്മിഷൻ തരം തിരഞ്ഞെടുക്കുക.")</f>
+        <v>ദയവായി ട്രാൻസ്മിഷൻ തരം തിരഞ്ഞെടുക്കുക.</v>
+      </c>
+      <c r="G1155" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1155, ""en"", ""te"")"),"దయచేసి ప్రసార రకాన్ని ఎంచుకోండి")</f>
+        <v>దయచేసి ప్రసార రకాన్ని ఎంచుకోండి</v>
+      </c>
     </row>
     <row r="1156">
-      <c r="A1156" s="4"/>
-      <c r="B1156" s="5"/>
-      <c r="C1156" s="6"/>
-      <c r="D1156" s="6"/>
-      <c r="E1156" s="6"/>
+      <c r="A1156" s="12" t="s">
+        <v>2789</v>
+      </c>
+      <c r="B1156" s="13" t="s">
+        <v>2790</v>
+      </c>
+      <c r="C1156" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1156, ""en"", ""ta"")"),"தயவுசெய்து குறைந்தபட்சம் ஒரு வாகன வகையைத் தேர்ந்தெடுக்கவும்.")</f>
+        <v>தயவுசெய்து குறைந்தபட்சம் ஒரு வாகன வகையைத் தேர்ந்தெடுக்கவும்.</v>
+      </c>
+      <c r="D1156" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1156, ""en"", ""hi"")"),"कृपया कम से कम एक वाहन प्रकार का चयन करें")</f>
+        <v>कृपया कम से कम एक वाहन प्रकार का चयन करें</v>
+      </c>
+      <c r="E1156" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1156, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ಕನಿಷ್ಠ ಒಂದು ವಾಹನ ಪ್ರಕಾರವನ್ನು ಆಯ್ಕೆಮಾಡಿ.")</f>
+        <v>ದಯವಿಟ್ಟು ಕನಿಷ್ಠ ಒಂದು ವಾಹನ ಪ್ರಕಾರವನ್ನು ಆಯ್ಕೆಮಾಡಿ.</v>
+      </c>
+      <c r="F1156" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1156, ""en"", ""ml"")"),"കുറഞ്ഞത് ഒരു വാഹന തരമെങ്കിലും തിരഞ്ഞെടുക്കുക.")</f>
+        <v>കുറഞ്ഞത് ഒരു വാഹന തരമെങ്കിലും തിരഞ്ഞെടുക്കുക.</v>
+      </c>
+      <c r="G1156" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1156, ""en"", ""te"")"),"దయచేసి కనీసం ఒక వాహన రకాన్ని ఎంచుకోండి")</f>
+        <v>దయచేసి కనీసం ఒక వాహన రకాన్ని ఎంచుకోండి</v>
+      </c>
     </row>
     <row r="1157">
-      <c r="A1157" s="4"/>
-      <c r="B1157" s="5"/>
-      <c r="C1157" s="6"/>
-      <c r="D1157" s="6"/>
-      <c r="E1157" s="6"/>
+      <c r="A1157" s="12" t="s">
+        <v>2791</v>
+      </c>
+      <c r="B1157" s="13" t="s">
+        <v>2792</v>
+      </c>
+      <c r="C1157" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1157, ""en"", ""ta"")"),"வாகன கையாளுதல்")</f>
+        <v>வாகன கையாளுதல்</v>
+      </c>
+      <c r="D1157" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1157, ""en"", ""hi"")"),"वाहन संचालन")</f>
+        <v>वाहन संचालन</v>
+      </c>
+      <c r="E1157" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1157, ""en"", ""kn"")"),"ವಾಹನ ನಿರ್ವಹಣೆ")</f>
+        <v>ವಾಹನ ನಿರ್ವಹಣೆ</v>
+      </c>
+      <c r="F1157" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1157, ""en"", ""ml"")"),"വാഹന കൈകാര്യം ചെയ്യൽ")</f>
+        <v>വാഹന കൈകാര്യം ചെയ്യൽ</v>
+      </c>
+      <c r="G1157" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1157, ""en"", ""te"")"),"వాహన నిర్వహణ")</f>
+        <v>వాహన నిర్వహణ</v>
+      </c>
     </row>
     <row r="1158">
-      <c r="A1158" s="4"/>
-      <c r="B1158" s="5"/>
-      <c r="C1158" s="6"/>
-      <c r="D1158" s="6"/>
-      <c r="E1158" s="6"/>
+      <c r="A1158" s="12" t="s">
+        <v>2793</v>
+      </c>
+      <c r="B1158" s="13" t="s">
+        <v>2794</v>
+      </c>
+      <c r="C1158" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1158, ""en"", ""ta"")"),"இயக்கப்படும் வாகன வகைகள்")</f>
+        <v>இயக்கப்படும் வாகன வகைகள்</v>
+      </c>
+      <c r="D1158" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1158, ""en"", ""hi"")"),"वाहन के प्रकार जो चलाए जाते हैं")</f>
+        <v>वाहन के प्रकार जो चलाए जाते हैं</v>
+      </c>
+      <c r="E1158" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1158, ""en"", ""kn"")"),"ಚಾಲನೆ ಮಾಡುವ ವಾಹನಗಳ ವಿಧಗಳು")</f>
+        <v>ಚಾಲನೆ ಮಾಡುವ ವಾಹನಗಳ ವಿಧಗಳು</v>
+      </c>
+      <c r="F1158" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1158, ""en"", ""ml"")"),"ഓടിക്കുന്ന വാഹന തരങ്ങൾ")</f>
+        <v>ഓടിക്കുന്ന വാഹന തരങ്ങൾ</v>
+      </c>
+      <c r="G1158" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1158, ""en"", ""te"")"),"నడపబడే వాహన రకాలు")</f>
+        <v>నడపబడే వాహన రకాలు</v>
+      </c>
     </row>
     <row r="1159">
-      <c r="A1159" s="4"/>
-      <c r="B1159" s="5"/>
-      <c r="C1159" s="6"/>
-      <c r="D1159" s="6"/>
-      <c r="E1159" s="6"/>
+      <c r="A1159" s="12" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B1159" s="13" t="s">
+        <v>2796</v>
+      </c>
+      <c r="C1159" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1159, ""en"", ""ta"")"),"பொருந்தக்கூடிய அனைத்தையும் தேர்ந்தெடுக்கவும்")</f>
+        <v>பொருந்தக்கூடிய அனைத்தையும் தேர்ந்தெடுக்கவும்</v>
+      </c>
+      <c r="D1159" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1159, ""en"", ""hi"")"),"उन सभी विकल्पों का चयन करें जो लागू होते हैं।")</f>
+        <v>उन सभी विकल्पों का चयन करें जो लागू होते हैं।</v>
+      </c>
+      <c r="E1159" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1159, ""en"", ""kn"")"),"ಅನ್ವಯವಾಗುವ ಎಲ್ಲವನ್ನೂ ಆಯ್ಕೆಮಾಡಿ")</f>
+        <v>ಅನ್ವಯವಾಗುವ ಎಲ್ಲವನ್ನೂ ಆಯ್ಕೆಮಾಡಿ</v>
+      </c>
+      <c r="F1159" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1159, ""en"", ""ml"")"),"ബാധകമായതെല്ലാം തിരഞ്ഞെടുക്കുക")</f>
+        <v>ബാധകമായതെല്ലാം തിരഞ്ഞെടുക്കുക</v>
+      </c>
+      <c r="G1159" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1159, ""en"", ""te"")"),"వర్తించేవన్నీ ఎంచుకోండి")</f>
+        <v>వర్తించేవన్నీ ఎంచుకోండి</v>
+      </c>
     </row>
     <row r="1160">
-      <c r="A1160" s="4"/>
-      <c r="B1160" s="5"/>
-      <c r="C1160" s="6"/>
-      <c r="D1160" s="6"/>
-      <c r="E1160" s="6"/>
+      <c r="A1160" s="12" t="s">
+        <v>2797</v>
+      </c>
+      <c r="B1160" s="13" t="s">
+        <v>2798</v>
+      </c>
+      <c r="C1160" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1160, ""en"", ""ta"")"),"பரிமாற்ற வகை")</f>
+        <v>பரிமாற்ற வகை</v>
+      </c>
+      <c r="D1160" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1160, ""en"", ""hi"")"),"संचरण प्रकार")</f>
+        <v>संचरण प्रकार</v>
+      </c>
+      <c r="E1160" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1160, ""en"", ""kn"")"),"ಪ್ರಸರಣ ಪ್ರಕಾರ")</f>
+        <v>ಪ್ರಸರಣ ಪ್ರಕಾರ</v>
+      </c>
+      <c r="F1160" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1160, ""en"", ""ml"")"),"ട്രാൻസ്മിഷൻ തരം")</f>
+        <v>ട്രാൻസ്മിഷൻ തരം</v>
+      </c>
+      <c r="G1160" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1160, ""en"", ""te"")"),"ప్రసార రకం")</f>
+        <v>ప్రసార రకం</v>
+      </c>
     </row>
     <row r="1161">
-      <c r="A1161" s="4"/>
-      <c r="B1161" s="5"/>
-      <c r="C1161" s="6"/>
-      <c r="D1161" s="6"/>
-      <c r="E1161" s="6"/>
+      <c r="A1161" s="12" t="s">
+        <v>2799</v>
+      </c>
+      <c r="B1161" s="13" t="s">
+        <v>2800</v>
+      </c>
+      <c r="C1161" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1161, ""en"", ""ta"")"),"கையாளப்படும் எரிபொருள் வகைகள்")</f>
+        <v>கையாளப்படும் எரிபொருள் வகைகள்</v>
+      </c>
+      <c r="D1161" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1161, ""en"", ""hi"")"),"संभाले जाने वाले ईंधन के प्रकार")</f>
+        <v>संभाले जाने वाले ईंधन के प्रकार</v>
+      </c>
+      <c r="E1161" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1161, ""en"", ""kn"")"),"ನಿರ್ವಹಿಸಲಾದ ಇಂಧನ ವಿಧಗಳು")</f>
+        <v>ನಿರ್ವಹಿಸಲಾದ ಇಂಧನ ವಿಧಗಳು</v>
+      </c>
+      <c r="F1161" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1161, ""en"", ""ml"")"),"കൈകാര്യം ചെയ്യുന്ന ഇന്ധന തരങ്ങൾ")</f>
+        <v>കൈകാര്യം ചെയ്യുന്ന ഇന്ധന തരങ്ങൾ</v>
+      </c>
+      <c r="G1161" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1161, ""en"", ""te"")"),"నిర్వహించబడే ఇంధన రకాలు")</f>
+        <v>నిర్వహించబడే ఇంధన రకాలు</v>
+      </c>
     </row>
     <row r="1162">
-      <c r="A1162" s="4"/>
-      <c r="B1162" s="5"/>
-      <c r="C1162" s="6"/>
-      <c r="D1162" s="6"/>
-      <c r="E1162" s="6"/>
+      <c r="A1162" s="12" t="s">
+        <v>2801</v>
+      </c>
+      <c r="B1162" s="13" t="s">
+        <v>2802</v>
+      </c>
+      <c r="C1162" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1162, ""en"", ""ta"")"),"இரவு நேர ஓட்டுநர் அனுபவம்")</f>
+        <v>இரவு நேர ஓட்டுநர் அனுபவம்</v>
+      </c>
+      <c r="D1162" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1162, ""en"", ""hi"")"),"रात्रि ड्राइविंग अनुभव")</f>
+        <v>रात्रि ड्राइविंग अनुभव</v>
+      </c>
+      <c r="E1162" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1162, ""en"", ""kn"")"),"ರಾತ್ರಿ ಚಾಲನಾ ಅನುಭವ")</f>
+        <v>ರಾತ್ರಿ ಚಾಲನಾ ಅನುಭವ</v>
+      </c>
+      <c r="F1162" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1162, ""en"", ""ml"")"),"രാത്രി ഡ്രൈവിംഗ് അനുഭവം")</f>
+        <v>രാത്രി ഡ്രൈവിംഗ് അനുഭവം</v>
+      </c>
+      <c r="G1162" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1162, ""en"", ""te"")"),"రాత్రి డ్రైవింగ్ అనుభవం")</f>
+        <v>రాత్రి డ్రైవింగ్ అనుభవం</v>
+      </c>
     </row>
     <row r="1163">
-      <c r="A1163" s="4"/>
-      <c r="B1163" s="5"/>
-      <c r="C1163" s="6"/>
-      <c r="D1163" s="6"/>
-      <c r="E1163" s="6"/>
+      <c r="A1163" s="12" t="s">
+        <v>2803</v>
+      </c>
+      <c r="B1163" s="13" t="s">
+        <v>2804</v>
+      </c>
+      <c r="C1163" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1163, ""en"", ""ta"")"),"நீண்ட தூர பயண அனுபவம்")</f>
+        <v>நீண்ட தூர பயண அனுபவம்</v>
+      </c>
+      <c r="D1163" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1163, ""en"", ""hi"")"),"लंबी दूरी की यात्रा का अनुभव")</f>
+        <v>लंबी दूरी की यात्रा का अनुभव</v>
+      </c>
+      <c r="E1163" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1163, ""en"", ""kn"")"),"ದೂರದ ಪ್ರಯಾಣದ ಅನುಭವ")</f>
+        <v>ದೂರದ ಪ್ರಯಾಣದ ಅನುಭವ</v>
+      </c>
+      <c r="F1163" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1163, ""en"", ""ml"")"),"ദീർഘദൂര യാത്രാനുഭവം")</f>
+        <v>ദീർഘദൂര യാത്രാനുഭവം</v>
+      </c>
+      <c r="G1163" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1163, ""en"", ""te"")"),"సుదూర ప్రయాణ అనుభవం")</f>
+        <v>సుదూర ప్రయాణ అనుభవం</v>
+      </c>
     </row>
     <row r="1164">
-      <c r="A1164" s="4"/>
-      <c r="B1164" s="5"/>
-      <c r="C1164" s="6"/>
-      <c r="D1164" s="6"/>
-      <c r="E1164" s="6"/>
+      <c r="A1164" s="12" t="s">
+        <v>2805</v>
+      </c>
+      <c r="B1164" s="13" t="s">
+        <v>2806</v>
+      </c>
+      <c r="C1164" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1164, ""en"", ""ta"")"),"உங்கள் மொத்த ஓட்டுநர் அனுபவத்தைத் தேர்ந்தெடுக்கவும்.")</f>
+        <v>உங்கள் மொத்த ஓட்டுநர் அனுபவத்தைத் தேர்ந்தெடுக்கவும்.</v>
+      </c>
+      <c r="D1164" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1164, ""en"", ""hi"")"),"कृपया अपने संपूर्ण ड्राइविंग अनुभव का चयन करें।")</f>
+        <v>कृपया अपने संपूर्ण ड्राइविंग अनुभव का चयन करें।</v>
+      </c>
+      <c r="E1164" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1164, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ನಿಮ್ಮ ಒಟ್ಟು ಚಾಲನಾ ಅನುಭವವನ್ನು ಆಯ್ಕೆಮಾಡಿ.")</f>
+        <v>ದಯವಿಟ್ಟು ನಿಮ್ಮ ಒಟ್ಟು ಚಾಲನಾ ಅನುಭವವನ್ನು ಆಯ್ಕೆಮಾಡಿ.</v>
+      </c>
+      <c r="F1164" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1164, ""en"", ""ml"")"),"നിങ്ങളുടെ മൊത്തം ഡ്രൈവിംഗ് അനുഭവം തിരഞ്ഞെടുക്കുക.")</f>
+        <v>നിങ്ങളുടെ മൊത്തം ഡ്രൈവിംഗ് അനുഭവം തിരഞ്ഞെടുക്കുക.</v>
+      </c>
+      <c r="G1164" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1164, ""en"", ""te"")"),"దయచేసి మీ మొత్తం డ్రైవింగ్ అనుభవాన్ని ఎంచుకోండి")</f>
+        <v>దయచేసి మీ మొత్తం డ్రైవింగ్ అనుభవాన్ని ఎంచుకోండి</v>
+      </c>
     </row>
     <row r="1165">
-      <c r="A1165" s="4"/>
-      <c r="B1165" s="5"/>
-      <c r="C1165" s="6"/>
-      <c r="D1165" s="6"/>
-      <c r="E1165" s="6"/>
+      <c r="A1165" s="12" t="s">
+        <v>2773</v>
+      </c>
+      <c r="B1165" s="13" t="s">
+        <v>2774</v>
+      </c>
+      <c r="C1165" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1165, ""en"", ""ta"")"),"ஓட்டுநர் அனுபவம்")</f>
+        <v>ஓட்டுநர் அனுபவம்</v>
+      </c>
+      <c r="D1165" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1165, ""en"", ""hi"")"),"ड्राइविंग अनुभव")</f>
+        <v>ड्राइविंग अनुभव</v>
+      </c>
+      <c r="E1165" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1165, ""en"", ""kn"")"),"ಚಾಲನಾ ಅನುಭವ")</f>
+        <v>ಚಾಲನಾ ಅನುಭವ</v>
+      </c>
+      <c r="F1165" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1165, ""en"", ""ml"")"),"ഡ്രൈവിംഗ് അനുഭവം")</f>
+        <v>ഡ്രൈവിംഗ് അനുഭവം</v>
+      </c>
+      <c r="G1165" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1165, ""en"", ""te"")"),"డ్రైవింగ్ అనుభవం")</f>
+        <v>డ్రైవింగ్ అనుభవం</v>
+      </c>
     </row>
     <row r="1166">
-      <c r="A1166" s="4"/>
-      <c r="B1166" s="5"/>
-      <c r="C1166" s="6"/>
-      <c r="D1166" s="6"/>
-      <c r="E1166" s="6"/>
+      <c r="A1166" s="12" t="s">
+        <v>2791</v>
+      </c>
+      <c r="B1166" s="13" t="s">
+        <v>2792</v>
+      </c>
+      <c r="C1166" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1166, ""en"", ""ta"")"),"வாகன கையாளுதல்")</f>
+        <v>வாகன கையாளுதல்</v>
+      </c>
+      <c r="D1166" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1166, ""en"", ""hi"")"),"वाहन संचालन")</f>
+        <v>वाहन संचालन</v>
+      </c>
+      <c r="E1166" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1166, ""en"", ""kn"")"),"ವಾಹನ ನಿರ್ವಹಣೆ")</f>
+        <v>ವಾಹನ ನಿರ್ವಹಣೆ</v>
+      </c>
+      <c r="F1166" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1166, ""en"", ""ml"")"),"വാഹന കൈകാര്യം ചെയ്യൽ")</f>
+        <v>വാഹന കൈകാര്യം ചെയ്യൽ</v>
+      </c>
+      <c r="G1166" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1166, ""en"", ""te"")"),"వాహన నిర్వహణ")</f>
+        <v>వాహన నిర్వహణ</v>
+      </c>
     </row>
     <row r="1167">
       <c r="A1167" s="4"/>

--- a/PublicCustomerApp/src/python/translation.xlsx
+++ b/PublicCustomerApp/src/python/translation.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2930" uniqueCount="2807">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3019" uniqueCount="2891">
   <si>
     <t>key</t>
   </si>
@@ -8446,6 +8446,258 @@
   </si>
   <si>
     <t>Please select your total driving experience</t>
+  </si>
+  <si>
+    <t>mygarage</t>
+  </si>
+  <si>
+    <t>My Garage</t>
+  </si>
+  <si>
+    <t>full_address</t>
+  </si>
+  <si>
+    <t>View Full Address</t>
+  </si>
+  <si>
+    <t>upload_photos_and_bills</t>
+  </si>
+  <si>
+    <t>Upload Photos and Bills</t>
+  </si>
+  <si>
+    <t>upload_photos_now</t>
+  </si>
+  <si>
+    <t>Upload Photos Now</t>
+  </si>
+  <si>
+    <t>vehicle_photos_required</t>
+  </si>
+  <si>
+    <t>Vehicle Photos Required</t>
+  </si>
+  <si>
+    <t>please_upload_pre_trip_photos_before_entering_otp</t>
+  </si>
+  <si>
+    <t>Please upload the 4 vehicle condition photos before starting the ride. This helps record the vehicle's condition at trip start.</t>
+  </si>
+  <si>
+    <t>post_trip_photos_required</t>
+  </si>
+  <si>
+    <t>Post-Trip Photos Required</t>
+  </si>
+  <si>
+    <t>please_upload_post_trip_photos_before_ending_ride</t>
+  </si>
+  <si>
+    <t>Please upload the 4 post-trip vehicle condition photos before ending the ride. This helps record the vehicle's condition at trip end.</t>
+  </si>
+  <si>
+    <t>upload_photos</t>
+  </si>
+  <si>
+    <t>Upload Photos</t>
+  </si>
+  <si>
+    <t>uploading</t>
+  </si>
+  <si>
+    <t>Uploading...</t>
+  </si>
+  <si>
+    <t>retake</t>
+  </si>
+  <si>
+    <t>Retake</t>
+  </si>
+  <si>
+    <t>failed_to_load</t>
+  </si>
+  <si>
+    <t>Failed to load</t>
+  </si>
+  <si>
+    <t>vehicle_photos_before_trip</t>
+  </si>
+  <si>
+    <t>Vehicle Photos — Before Trip</t>
+  </si>
+  <si>
+    <t>capture_all_4_angles_before_you_start</t>
+  </si>
+  <si>
+    <t>Capture all 4 angles before you start</t>
+  </si>
+  <si>
+    <t>photos_required</t>
+  </si>
+  <si>
+    <t>Photos Required</t>
+  </si>
+  <si>
+    <t>please_capture_all_4_post_trip_photos</t>
+  </si>
+  <si>
+    <t>Please capture all 4 vehicle photos before starting.</t>
+  </si>
+  <si>
+    <t>vehicle_photos</t>
+  </si>
+  <si>
+    <t>Vehicle Photos</t>
+  </si>
+  <si>
+    <t>upload_before_after_trip_photos</t>
+  </si>
+  <si>
+    <t>Upload before &amp; after trip photos</t>
+  </si>
+  <si>
+    <t>uploaded</t>
+  </si>
+  <si>
+    <t>pre_trip_photos</t>
+  </si>
+  <si>
+    <t>Pre-Trip Photos</t>
+  </si>
+  <si>
+    <t>front</t>
+  </si>
+  <si>
+    <t>Front</t>
+  </si>
+  <si>
+    <t>rear</t>
+  </si>
+  <si>
+    <t>Rear</t>
+  </si>
+  <si>
+    <t>left_side</t>
+  </si>
+  <si>
+    <t>Left Side</t>
+  </si>
+  <si>
+    <t>right_side</t>
+  </si>
+  <si>
+    <t>Right Side</t>
+  </si>
+  <si>
+    <t>reupload_pre_trip</t>
+  </si>
+  <si>
+    <t>Re-upload Pre-Trip</t>
+  </si>
+  <si>
+    <t>upload_pre_trip_photos</t>
+  </si>
+  <si>
+    <t>Upload Pre-Trip Photos</t>
+  </si>
+  <si>
+    <t>reupload_post_trip</t>
+  </si>
+  <si>
+    <t>Re-upload Post-Trip</t>
+  </si>
+  <si>
+    <t>upload_post_trip_photos</t>
+  </si>
+  <si>
+    <t>Upload Post-Trip Photos</t>
+  </si>
+  <si>
+    <t>bills_expenses</t>
+  </si>
+  <si>
+    <t>Bills &amp; Expenses</t>
+  </si>
+  <si>
+    <t>add_trip_expenses_and_receipts</t>
+  </si>
+  <si>
+    <t>Add trip expenses and receipts</t>
+  </si>
+  <si>
+    <t>no_bills_added_yet</t>
+  </si>
+  <si>
+    <t>No bills added yet</t>
+  </si>
+  <si>
+    <t>tap_add_bill_below_to_record_an_expense</t>
+  </si>
+  <si>
+    <t>Tap "Add Bill" below to record an expense</t>
+  </si>
+  <si>
+    <t>bill</t>
+  </si>
+  <si>
+    <t>Bill</t>
+  </si>
+  <si>
+    <t>added</t>
+  </si>
+  <si>
+    <t>Added</t>
+  </si>
+  <si>
+    <t>add_bill</t>
+  </si>
+  <si>
+    <t>Add Bill</t>
+  </si>
+  <si>
+    <t>add_bill_expense</t>
+  </si>
+  <si>
+    <t>Add Bill / Expense</t>
+  </si>
+  <si>
+    <t>description_placeholder</t>
+  </si>
+  <si>
+    <t>e.g. Fuel, Toll, Parking</t>
+  </si>
+  <si>
+    <t>receipt_photo</t>
+  </si>
+  <si>
+    <t>Receipt Photo</t>
+  </si>
+  <si>
+    <t>optional</t>
+  </si>
+  <si>
+    <t>Adding</t>
+  </si>
+  <si>
+    <t>adding</t>
+  </si>
+  <si>
+    <t>amount_placeholder</t>
+  </si>
+  <si>
+    <t>upload_vehicle_photos</t>
+  </si>
+  <si>
+    <t>Upload Vehicle Photos</t>
+  </si>
+  <si>
+    <t>upload_bills_and_expenses</t>
+  </si>
+  <si>
+    <t>Upload Bills and Expenses</t>
+  </si>
+  <si>
+    <t>view_full_address</t>
   </si>
 </sst>
 </file>
@@ -8515,7 +8767,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -8585,6 +8837,12 @@
     </xf>
     <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8959,8 +9217,8 @@
         <v>பயணத்தைத் தொடங்குவதற்கும் உறுதிப்படுத்துவதற்கும் வாடிக்கையாளரைத் தொடர்பு கொண்டீர்கள் என்பதை உறுதிப்படுத்திக் கொள்ளுங்கள்.</v>
       </c>
       <c r="D6" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B6, ""en"", ""hi"")"),"ग्राहक से संपर्क करके यात्रा की पुष्टि कर लें और यात्रा शुरू करें।")</f>
-        <v>ग्राहक से संपर्क करके यात्रा की पुष्टि कर लें और यात्रा शुरू करें।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B6, ""en"", ""hi"")"),"ग्राहक से संपर्क करके यात्रा की पुष्टि अवश्य कर लें और यात्रा शुरू करें।")</f>
+        <v>ग्राहक से संपर्क करके यात्रा की पुष्टि अवश्य कर लें और यात्रा शुरू करें।</v>
       </c>
       <c r="E6" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B6, ""en"", ""kn"")"),"ಖಚಿತಪಡಿಸಲು ಮತ್ತು ಪ್ರಯಾಣವನ್ನು ಪ್ರಾರಂಭಿಸಲು ನೀವು ಗ್ರಾಹಕರನ್ನು ಸಂಪರ್ಕಿಸಿದ್ದೀರಿ ಎಂದು ಖಚಿತಪಡಿಸಿಕೊಳ್ಳಿ.")</f>
@@ -9183,8 +9441,8 @@
         <v>அதிக ஈடுபாட்டிற்கு மதிப்பீடுகளே திறவுகோல். நீங்கள் ஒரு நல்ல மதிப்பீட்டைப் பெறுவதை உறுதிப்படுத்திக் கொள்ளுங்கள்.</v>
       </c>
       <c r="D14" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B14, ""en"", ""hi"")"),"रेटिंग ही प्रतिबद्धता बढ़ाने की कुंजी है। सुनिश्चित करें कि आपको अच्छी रेटिंग मिले।")</f>
-        <v>रेटिंग ही प्रतिबद्धता बढ़ाने की कुंजी है। सुनिश्चित करें कि आपको अच्छी रेटिंग मिले।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B14, ""en"", ""hi"")"),"रेटिंग से प्रतिबद्धता बढ़ती है। इसलिए अच्छी रेटिंग प्राप्त करना सुनिश्चित करें।")</f>
+        <v>रेटिंग से प्रतिबद्धता बढ़ती है। इसलिए अच्छी रेटिंग प्राप्त करना सुनिश्चित करें।</v>
       </c>
       <c r="E14" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B14, ""en"", ""kn"")"),"ಹೆಚ್ಚಿನ ಬದ್ಧತೆಗೆ ರೇಟಿಂಗ್‌ಗಳು ಪ್ರಮುಖವಾಗಿವೆ. ನೀವು ಉತ್ತಮ ರೇಟಿಂಗ್ ಪಡೆಯುವುದನ್ನು ಖಚಿತಪಡಿಸಿಕೊಳ್ಳಿ.")</f>
@@ -9474,8 +9732,8 @@
         <v>ദയവായി പാൻ നമ്പർ നൽകുക</v>
       </c>
       <c r="G24" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B24, ""en"", ""te"")"),"దయచేసి పాన్ నంబర్ నమోదు చేయండి")</f>
-        <v>దయచేసి పాన్ నంబర్ నమోదు చేయండి</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B24, ""en"", ""te"")"),"దయచేసి పాన్ నంబర్‌ను నమోదు చేయండి")</f>
+        <v>దయచేసి పాన్ నంబర్‌ను నమోదు చేయండి</v>
       </c>
     </row>
     <row r="25">
@@ -9979,8 +10237,8 @@
         <v>कृपया पंजीकरण संख्या दर्ज करें</v>
       </c>
       <c r="E42" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B42, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ನೋಂದಣಿ ಸಂಖ್ಯೆಯನ್ನು ನಮೂದಿಸಿ")</f>
-        <v>ದಯವಿಟ್ಟು ನೋಂದಣಿ ಸಂಖ್ಯೆಯನ್ನು ನಮೂದಿಸಿ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B42, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ನೋಂದಣಿ ಸಂಖ್ಯೆಯನ್ನು ನಮೂದಿಸಿ.")</f>
+        <v>ದಯವಿಟ್ಟು ನೋಂದಣಿ ಸಂಖ್ಯೆಯನ್ನು ನಮೂದಿಸಿ.</v>
       </c>
       <c r="F42" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B42, ""en"", ""ml"")"),"ദയവായി രജിസ്ട്രേഷൻ നമ്പർ നൽകുക")</f>
@@ -10095,8 +10353,8 @@
         <v>ದಯವಿಟ್ಟು ತಯಾರಿಕಾ ವರ್ಷವನ್ನು ನಮೂದಿಸಿ.</v>
       </c>
       <c r="F46" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B46, ""en"", ""ml"")"),"നിർമ്മാണ വർഷം നൽകുക.")</f>
-        <v>നിർമ്മാണ വർഷം നൽകുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B46, ""en"", ""ml"")"),"നിർമ്മാണ വർഷം നൽകുക")</f>
+        <v>നിർമ്മാണ വർഷം നൽകുക</v>
       </c>
       <c r="G46" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B46, ""en"", ""te"")"),"దయచేసి తయారీ సంవత్సరాన్ని నమోదు చేయండి")</f>
@@ -12121,8 +12379,8 @@
         <v>ബാങ്ക് പാസ്ബുക്ക് (മുൻ പേജ്) അപ്‌ലോഡ് ചെയ്യുക.</v>
       </c>
       <c r="G118" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B118, ""en"", ""te"")"),"అప్‌లోడ్ చేయండి బ్యాంక్ పాస్‌బుక్ (మొదటి పేజీ)")</f>
-        <v>అప్‌లోడ్ చేయండి బ్యాంక్ పాస్‌బుక్ (మొదటి పేజీ)</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B118, ""en"", ""te"")"),"బ్యాంకు పాస్‌బుక్‌ను అప్‌లోడ్ చేయండి (మొదటి పేజీ)")</f>
+        <v>బ్యాంకు పాస్‌బుక్‌ను అప్‌లోడ్ చేయండి (మొదటి పేజీ)</v>
       </c>
     </row>
     <row r="119">
@@ -12929,8 +13187,8 @@
         <v>300</v>
       </c>
       <c r="C147" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B147, ""en"", ""ta"")"),"தெரு ஒன்று")</f>
-        <v>தெரு ஒன்று</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B147, ""en"", ""ta"")"),"ஸ்ட்ரீட் ஒன்")</f>
+        <v>ஸ்ட்ரீட் ஒன்</v>
       </c>
       <c r="D147" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B147, ""en"", ""hi"")"),"गली एक")</f>
@@ -13307,8 +13565,8 @@
         <v>ನೋಂದಾಯಿತ ಫೋನ್ ಸಂಖ್ಯೆಗೆ OTP ಯಶಸ್ವಿಯಾಗಿ ಮರು ಕಳುಹಿಸಲಾಗಿದೆ.</v>
       </c>
       <c r="F160" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B160, ""en"", ""ml"")"),"രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വീണ്ടും അയച്ചു.")</f>
-        <v>രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വീണ്ടും അയച്ചു.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B160, ""en"", ""ml"")"),"രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വിജയകരമായി വീണ്ടും അയച്ചു.")</f>
+        <v>രജിസ്റ്റർ ചെയ്ത ഫോൺ നമ്പറിലേക്ക് OTP വിജയകരമായി വീണ്ടും അയച്ചു.</v>
       </c>
       <c r="G160" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B160, ""en"", ""te"")"),"నమోదిత ఫోన్ నంబర్‌కు OTP విజయవంతంగా పంపబడింది")</f>
@@ -13359,8 +13617,8 @@
         <v>रीयल टाइम अपडेट प्राप्त करने के लिए कृपया नोटिफिकेशन की अनुमति चालू करें।</v>
       </c>
       <c r="E162" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B162, ""en"", ""kn"")"),"ನೈಜ ಸಮಯದ ನವೀಕರಣಗಳನ್ನು ಪಡೆಯಲು ಅಧಿಸೂಚನೆ ಅನುಮತಿಯನ್ನು ಸಕ್ರಿಯಗೊಳಿಸಿ.")</f>
-        <v>ನೈಜ ಸಮಯದ ನವೀಕರಣಗಳನ್ನು ಪಡೆಯಲು ಅಧಿಸೂಚನೆ ಅನುಮತಿಯನ್ನು ಸಕ್ರಿಯಗೊಳಿಸಿ.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B162, ""en"", ""kn"")"),"ನೈಜ ಸಮಯದ ನವೀಕರಣಗಳನ್ನು ಪಡೆಯಲು ದಯವಿಟ್ಟು ಅಧಿಸೂಚನೆ ಅನುಮತಿಯನ್ನು ಸಕ್ರಿಯಗೊಳಿಸಿ.")</f>
+        <v>ನೈಜ ಸಮಯದ ನವೀಕರಣಗಳನ್ನು ಪಡೆಯಲು ದಯವಿಟ್ಟು ಅಧಿಸೂಚನೆ ಅನುಮತಿಯನ್ನು ಸಕ್ರಿಯಗೊಳಿಸಿ.</v>
       </c>
       <c r="F162" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B162, ""en"", ""ml"")"),"തത്സമയ അപ്‌ഡേറ്റുകൾ ലഭിക്കാൻ അറിയിപ്പ് അനുമതി പ്രവർത്തനക്ഷമമാക്കുക.")</f>
@@ -13624,9 +13882,9 @@
       </c>
       <c r="F171" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B171, ""en"", ""ml"")"),"ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
-നിങ്ങളുടെ ക്ഷമയ്ക്ക് നന്ദി.")</f>
+ക്ഷമയ്ക്ക് നന്ദി.")</f>
         <v>ടാക്സി പരിശോധിച്ചുറപ്പിക്കുന്നതിനും അവ അംഗീകരിക്കുന്നതിനും ഞങ്ങൾ കഠിനമായി പരിശ്രമിക്കുകയാണ്. അതിനാൽ അംഗീകാര പ്രക്രിയയ്ക്ക് കുറച്ച് സമയമെടുക്കുമെന്ന് ദയവായി മനസ്സിലാക്കുക.
-നിങ്ങളുടെ ക്ഷമയ്ക്ക് നന്ദി.</v>
+ക്ഷമയ്ക്ക് നന്ദി.</v>
       </c>
       <c r="G171" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B171, ""en"", ""te"")"),"మేము టాక్సీలను సరిచూసి, ఆమోదించడానికి తీవ్రంగా కృషి చేస్తున్నాము. కాబట్టి, ఆమోద ప్రక్రియకు కొంత సమయం పడుతుందని దయచేసి అర్థం చేసుకోండి.
@@ -13739,8 +13997,8 @@
         <v>ಇಲ್ಲ, ಆನ್‌ಲೈನ್‌ನಲ್ಲಿರಿ</v>
       </c>
       <c r="F175" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B175, ""en"", ""ml"")"),"വേണ്ട, ഓൺലൈനാകൂ")</f>
-        <v>വേണ്ട, ഓൺലൈനാകൂ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B175, ""en"", ""ml"")"),"വേണ്ട, ഓൺലൈനിൽ ആയിരിക്കൂ")</f>
+        <v>വേണ്ട, ഓൺലൈനിൽ ആയിരിക്കൂ</v>
       </c>
       <c r="G175" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B175, ""en"", ""te"")"),"లేదు, ఆన్‌లైన్‌లో ఉండండి")</f>
@@ -14411,8 +14669,8 @@
         <v>ಆನ್‌ಲೈನ್‌ಗೆ ಹೋಗಿ</v>
       </c>
       <c r="F199" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B199, ""en"", ""ml"")"),"ഓൺലൈനാകുക")</f>
-        <v>ഓൺലൈനാകുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B199, ""en"", ""ml"")"),"ഓൺലൈനിൽ പോകുക")</f>
+        <v>ഓൺലൈനിൽ പോകുക</v>
       </c>
       <c r="G199" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B199, ""en"", ""te"")"),"ఆన్‌లైన్‌కు వెళ్లండి")</f>
@@ -14915,8 +15173,8 @@
         <v>ವಿವರಗಳು ವೀಕ್ಷಿಸಿ</v>
       </c>
       <c r="F217" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B217, ""en"", ""ml"")"),"വിശദാംശങ്ങൾ കാണുക")</f>
-        <v>വിശദാംശങ്ങൾ കാണുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B217, ""en"", ""ml"")"),"കാണുക വിശദാംശങ്ങൾ")</f>
+        <v>കാണുക വിശദാംശങ്ങൾ</v>
       </c>
       <c r="G217" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B217, ""en"", ""te"")"),"వివరాలను వీక్షించండి")</f>
@@ -15059,8 +15317,8 @@
         <v>ആകെ യാത്രകൾ</v>
       </c>
       <c r="G222" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B222, ""en"", ""te"")"),"మొత్తం ప్రయాణాలు")</f>
-        <v>మొత్తం ప్రయాణాలు</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B222, ""en"", ""te"")"),"మొత్తం పర్యటనలు")</f>
+        <v>మొత్తం పర్యటనలు</v>
       </c>
     </row>
     <row r="223">
@@ -16962,8 +17220,8 @@
         <v>സവാരി സ്വീകരിക്കുക</v>
       </c>
       <c r="G290" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B290, ""en"", ""te"")"),"ప్రయాణాన్ని అంగీకరించండి")</f>
-        <v>ప్రయాణాన్ని అంగీకరించండి</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B290, ""en"", ""te"")"),"రైడ్‌ను అంగీకరించండి")</f>
+        <v>రైడ్‌ను అంగీకరించండి</v>
       </c>
     </row>
     <row r="291">
@@ -16990,8 +17248,8 @@
         <v>ബുക്ക് ചെയ്തത്</v>
       </c>
       <c r="G291" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B291, ""en"", ""te"")"),"ఇక్కడ బుక్ చేయబడింది")</f>
-        <v>ఇక్కడ బుక్ చేయబడింది</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B291, ""en"", ""te"")"),"బుక్ చేయబడింది")</f>
+        <v>బుక్ చేయబడింది</v>
       </c>
     </row>
     <row r="292">
@@ -17674,8 +17932,8 @@
         <v>614</v>
       </c>
       <c r="C316" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B316, ""en"", ""ta"")"),"டெலிவரி செய்பவரைத் தொடர்பு கொள்ள முடியவில்லை அல்லது அவர் பிக்கப் இடத்தில் இல்லை.")</f>
-        <v>டெலிவரி செய்பவரைத் தொடர்பு கொள்ள முடியவில்லை அல்லது அவர் பிக்கப் இடத்தில் இல்லை.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B316, ""en"", ""ta"")"),"ரைடரைத் தொடர்பு கொள்ள முடியவில்லை அல்லது அவர் பிக்கப் இடத்தில் இல்லை.")</f>
+        <v>ரைடரைத் தொடர்பு கொள்ள முடியவில்லை அல்லது அவர் பிக்கப் இடத்தில் இல்லை.</v>
       </c>
       <c r="D316" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B316, ""en"", ""hi"")"),"राइडर से संपर्क नहीं हो पा रहा है या वह पिकअप स्थान पर मौजूद नहीं है")</f>
@@ -17874,8 +18132,8 @@
         <v>மோசமான போக்குவரத்து அல்லது வானிலை நிலைமைகள்</v>
       </c>
       <c r="D323" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B323, ""en"", ""hi"")"),"खराब यातायात या खराब मौसम की स्थिति")</f>
-        <v>खराब यातायात या खराब मौसम की स्थिति</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B323, ""en"", ""hi"")"),"यातायात की खराब स्थिति या मौसम की स्थिति")</f>
+        <v>यातायात की खराब स्थिति या मौसम की स्थिति</v>
       </c>
       <c r="E323" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B323, ""en"", ""kn"")"),"ಕಳಪೆ ಸಂಚಾರ ಅಥವಾ ಹವಾಮಾನ ಪರಿಸ್ಥಿತಿಗಳು")</f>
@@ -19058,8 +19316,8 @@
         <v>ನಿಮ್ಮ ಖಾತೆಯನ್ನು ತಕ್ಷಣವೇ ಅಳಿಸಲಾಗಿದೆ ಎಂದು ಗುರುತಿಸಲಾಗುತ್ತದೆ.</v>
       </c>
       <c r="F365" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B365, ""en"", ""ml"")"),"നിങ്ങളുടെ അക്കൗണ്ട് ഉടൻ തന്നെ ഇല്ലാതാക്കിയതായി അടയാളപ്പെടുത്തും.")</f>
-        <v>നിങ്ങളുടെ അക്കൗണ്ട് ഉടൻ തന്നെ ഇല്ലാതാക്കിയതായി അടയാളപ്പെടുത്തും.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B365, ""en"", ""ml"")"),"നിങ്ങളുടെ അക്കൗണ്ട് ഉടനടി ഇല്ലാതാക്കിയതായി അടയാളപ്പെടുത്തും.")</f>
+        <v>നിങ്ങളുടെ അക്കൗണ്ട് ഉടനടി ഇല്ലാതാക്കിയതായി അടയാളപ്പെടുത്തും.</v>
       </c>
       <c r="G365" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B365, ""en"", ""te"")"),"మీ ఖాతా తక్షణమే తొలగించబడినట్లుగా గుర్తించబడుతుంది.")</f>
@@ -20226,8 +20484,8 @@
         <v>செயலி திறந்திருக்காத போதும் உங்கள் இருப்பிடத்தைக் கண்காணிக்க, NOT செயலிக்குப் பின்னணி இருப்பிட அனுமதி தேவையில்லை. இது தொடர்ச்சியான கண்காணிப்பை அனுமதிப்பதோடு, எல்லா நேரங்களிலும் துல்லியமான இருப்பிடத் தரவு சேகரிக்கப்படுவதையும் உறுதி செய்கிறது.</v>
       </c>
       <c r="D407" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B407, ""en"", ""hi"")"),"NOT ऐप के बंद होने पर भी आपकी लोकेशन ट्रैक करने के लिए बैकग्राउंड लोकेशन परमिशन की आवश्यकता होती है। इससे लगातार ट्रैकिंग संभव होती है और यह सुनिश्चित होता है कि हर समय सटीक लोकेशन डेटा एकत्र किया जाए।")</f>
-        <v>NOT ऐप के बंद होने पर भी आपकी लोकेशन ट्रैक करने के लिए बैकग्राउंड लोकेशन परमिशन की आवश्यकता होती है। इससे लगातार ट्रैकिंग संभव होती है और यह सुनिश्चित होता है कि हर समय सटीक लोकेशन डेटा एकत्र किया जाए।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B407, ""en"", ""hi"")"),"NOT ऐप को आपके स्थान को ट्रैक करने के लिए बैकग्राउंड लोकेशन अनुमति की आवश्यकता होती है, भले ही ऐप खुला न हो। इससे निरंतर ट्रैकिंग संभव होती है और यह सुनिश्चित होता है कि हर समय सटीक स्थान डेटा एकत्र किया जाए।")</f>
+        <v>NOT ऐप को आपके स्थान को ट्रैक करने के लिए बैकग्राउंड लोकेशन अनुमति की आवश्यकता होती है, भले ही ऐप खुला न हो। इससे निरंतर ट्रैकिंग संभव होती है और यह सुनिश्चित होता है कि हर समय सटीक स्थान डेटा एकत्र किया जाए।</v>
       </c>
       <c r="E407" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B407, ""en"", ""kn"")"),"ಅಪ್ಲಿಕೇಶನ್ ತೆರೆದಿಲ್ಲದಿದ್ದರೂ ಸಹ ನಿಮ್ಮ ಸ್ಥಳವನ್ನು ಟ್ರ್ಯಾಕ್ ಮಾಡಲು NOT ಗೆ ಹಿನ್ನೆಲೆ ಸ್ಥಳ ಅನುಮತಿ ಅಗತ್ಯವಿಲ್ಲ. ಇದು ನಿರಂತರ ಟ್ರ್ಯಾಕಿಂಗ್‌ಗೆ ಅವಕಾಶ ನೀಡುತ್ತದೆ ಮತ್ತು ಎಲ್ಲಾ ಸಮಯದಲ್ಲೂ ನಿಖರವಾದ ಸ್ಥಳ ಡೇಟಾವನ್ನು ಸಂಗ್ರಹಿಸಲಾಗಿದೆ ಎಂದು ಖಚಿತಪಡಿಸುತ್ತದೆ.")</f>
@@ -21298,8 +21556,8 @@
         <v>ಸಂಪರ್ಕಿಸಿ</v>
       </c>
       <c r="F445" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B445, ""en"", ""ml"")"),"ബന്ധപ്പെടുക")</f>
-        <v>ബന്ധപ്പെടുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B445, ""en"", ""ml"")"),"വാര്ത്താവിനിമയം")</f>
+        <v>വാര്ത്താവിനിമയം</v>
       </c>
       <c r="G445" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B445, ""en"", ""te"")"),"సంప్రదించండి")</f>
@@ -22545,8 +22803,8 @@
         <v>ನಿಲ್ಲಿಸುವುದನ್ನು ದೃಢೀಕರಿಸಿ {ನಿಲುಗಡೆ}</v>
       </c>
       <c r="F491" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B491, ""en"", ""ml"")"),"നിർത്തുക സ്ഥിരീകരിക്കുക {നിർത്തുക}")</f>
-        <v>നിർത്തുക സ്ഥിരീകരിക്കുക {നിർത്തുക}</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B491, ""en"", ""ml"")"),"നിർത്തുക {നിർത്തുക} സ്ഥിരീകരിക്കുക")</f>
+        <v>നിർത്തുക {നിർത്തുക} സ്ഥിരീകരിക്കുക</v>
       </c>
       <c r="G491" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B491, ""en"", ""te"")"),"ఆపడాన్ని నిర్ధారించండి {stop}")</f>
@@ -22953,8 +23211,8 @@
         <v>"ಯಾವಾಗಲೂ" ಅಥವಾ "ಆ್ಯಪ್ ಬಳಸುವಾಗ" ಆಯ್ಕೆಮಾಡಿ.</v>
       </c>
       <c r="F506" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B506, ""en"", ""ml"")"),"""എല്ലായ്പ്പോഴും"" അല്ലെങ്കിൽ ""ആപ്പ് ഉപയോഗിക്കുമ്പോൾ"" തിരഞ്ഞെടുക്കുക.")</f>
-        <v>"എല്ലായ്പ്പോഴും" അല്ലെങ്കിൽ "ആപ്പ് ഉപയോഗിക്കുമ്പോൾ" തിരഞ്ഞെടുക്കുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B506, ""en"", ""ml"")"),"""എല്ലായ്‌പ്പോഴും"" അല്ലെങ്കിൽ ""ആപ്പ് ഉപയോഗിക്കുമ്പോൾ"" തിരഞ്ഞെടുക്കുക.")</f>
+        <v>"എല്ലായ്‌പ്പോഴും" അല്ലെങ്കിൽ "ആപ്പ് ഉപയോഗിക്കുമ്പോൾ" തിരഞ്ഞെടുക്കുക.</v>
       </c>
       <c r="G506" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B506, ""en"", ""te"")"),"""ఎల్లప్పుడూ"" లేదా ""యాప్‌ను ఉపయోగిస్తున్నప్పుడు"" ఎంచుకోండి")</f>
@@ -24066,8 +24324,8 @@
         <v>നിങ്ങളുടെ അക്കൗണ്ട് ഇല്ലാതാക്കണമെന്ന് ഉറപ്പാണോ?</v>
       </c>
       <c r="G547" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B547, ""en"", ""te"")"),"మీరు నిజంగా మీ ఖాతాను తొలగించాలనుకుంటున్నారా?")</f>
-        <v>మీరు నిజంగా మీ ఖాతాను తొలగించాలనుకుంటున్నారా?</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B547, ""en"", ""te"")"),"మీరు మీ ఖాతాను తొలగించాలనుకుంటున్నారని ఖచ్చితంగా అనుకుంటున్నారా?")</f>
+        <v>మీరు మీ ఖాతాను తొలగించాలనుకుంటున్నారని ఖచ్చితంగా అనుకుంటున్నారా?</v>
       </c>
     </row>
     <row r="548">
@@ -24490,8 +24748,8 @@
         <v>नम्मा ऊरु टैक्सी के साथ ड्राइव करें</v>
       </c>
       <c r="E563" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B563, ""en"", ""kn"")"),"ನಮ್ಮ ಊರು ಟ್ಯಾಕ್ಸಿ ಜೊತೆ ಡ್ರೈವ್ ಮಾಡಿ")</f>
-        <v>ನಮ್ಮ ಊರು ಟ್ಯಾಕ್ಸಿ ಜೊತೆ ಡ್ರೈವ್ ಮಾಡಿ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B563, ""en"", ""kn"")"),"ನಮ್ಮ ಊರು ಟ್ಯಾಕ್ಸಿಯೊಂದಿಗೆ ಚಾಲನೆ ಮಾಡಿ")</f>
+        <v>ನಮ್ಮ ಊರು ಟ್ಯಾಕ್ಸಿಯೊಂದಿಗೆ ಚಾಲನೆ ಮಾಡಿ</v>
       </c>
       <c r="F563" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B563, ""en"", ""ml"")"),"നമ്മ ഊരു ടാക്സിയിൽ യാത്ര ചെയ്യൂ")</f>
@@ -25223,8 +25481,8 @@
         <v>ಡ್ರಾಪ್</v>
       </c>
       <c r="F590" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B590, ""en"", ""ml"")"),"ഡ്രോപ്പ് ചെയ്യുക")</f>
-        <v>ഡ്രോപ്പ് ചെയ്യുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B590, ""en"", ""ml"")"),"ഡ്രോപ്പ്")</f>
+        <v>ഡ്രോപ്പ്</v>
       </c>
       <c r="G590" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B590, ""en"", ""te"")"),"డ్రాప్")</f>
@@ -27440,8 +27698,8 @@
         <v>ಡ್ರಾಪ್</v>
       </c>
       <c r="F672" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B672, ""en"", ""ml"")"),"ഡ്രോപ്പ് ചെയ്യുക")</f>
-        <v>ഡ്രോപ്പ് ചെയ്യുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B672, ""en"", ""ml"")"),"ഡ്രോപ്പ്")</f>
+        <v>ഡ്രോപ്പ്</v>
       </c>
       <c r="G672" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B672, ""en"", ""te"")"),"డ్రాప్")</f>
@@ -27594,8 +27852,8 @@
         <v>1523</v>
       </c>
       <c r="D678" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B678, ""en"", ""hi"")"),"ऐप की अच्छी बातें साझा करें")</f>
-        <v>ऐप की अच्छी बातें साझा करें</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B678, ""en"", ""hi"")"),"ऐप के बारे में अच्छी बातें साझा करें")</f>
+        <v>ऐप के बारे में अच्छी बातें साझा करें</v>
       </c>
       <c r="E678" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B678, ""en"", ""kn"")"),"ಅಪ್ಲಿಕೇಶನ್ ಬಗ್ಗೆ ಒಳ್ಳೆಯ ವಿಷಯಗಳನ್ನು ಹಂಚಿಕೊಳ್ಳಿ")</f>
@@ -28246,8 +28504,8 @@
         <v>कृपया कम से कम एक संदेश (अच्छा, बुरा, सुधार या समस्या) जोड़ें।</v>
       </c>
       <c r="E702" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B702, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ಕನಿಷ್ಠ ಒಂದು ಸಂದೇಶವನ್ನಾದರೂ ಸೇರಿಸಿ (ಒಳ್ಳೆಯದು, ಕೆಟ್ಟದು, ಸುಧಾರಣೆ ಅಥವಾ ಸಮಸ್ಯೆ).")</f>
-        <v>ದಯವಿಟ್ಟು ಕನಿಷ್ಠ ಒಂದು ಸಂದೇಶವನ್ನಾದರೂ ಸೇರಿಸಿ (ಒಳ್ಳೆಯದು, ಕೆಟ್ಟದು, ಸುಧಾರಣೆ ಅಥವಾ ಸಮಸ್ಯೆ).</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B702, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ಕನಿಷ್ಠ ಒಂದು ಸಂದೇಶವನ್ನು ಸೇರಿಸಿ (ಒಳ್ಳೆಯದು, ಕೆಟ್ಟದು, ಸುಧಾರಣೆ ಅಥವಾ ಸಮಸ್ಯೆ).")</f>
+        <v>ದಯವಿಟ್ಟು ಕನಿಷ್ಠ ಒಂದು ಸಂದೇಶವನ್ನು ಸೇರಿಸಿ (ಒಳ್ಳೆಯದು, ಕೆಟ್ಟದು, ಸುಧಾರಣೆ ಅಥವಾ ಸಮಸ್ಯೆ).</v>
       </c>
       <c r="F702" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B702, ""en"", ""ml"")"),"ദയവായി കുറഞ്ഞത് ഒരു സന്ദേശമെങ്കിലും ചേർക്കുക (നല്ലത്, മോശം, മെച്ചപ്പെടുത്തൽ അല്ലെങ്കിൽ പ്രശ്നം).")</f>
@@ -30133,8 +30391,8 @@
         <v>1797</v>
       </c>
       <c r="D772" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B772, ""en"", ""hi"")"),"चयनित वाहन प्रकार के लिए फिलहाल कोई चालक उपलब्ध नहीं है। कृपया बाद में पुनः प्रयास करें या कोई अन्य वाहन चुनें।")</f>
-        <v>चयनित वाहन प्रकार के लिए फिलहाल कोई चालक उपलब्ध नहीं है। कृपया बाद में पुनः प्रयास करें या कोई अन्य वाहन चुनें।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B772, ""en"", ""hi"")"),"वर्तमान में चयनित वाहन प्रकार के लिए कोई चालक उपलब्ध नहीं है। कृपया बाद में पुनः प्रयास करें या कोई अन्य वाहन चुनें।")</f>
+        <v>वर्तमान में चयनित वाहन प्रकार के लिए कोई चालक उपलब्ध नहीं है। कृपया बाद में पुनः प्रयास करें या कोई अन्य वाहन चुनें।</v>
       </c>
       <c r="E772" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B772, ""en"", ""kn"")"),"ಆಯ್ಕೆಮಾಡಿದ ವಾಹನ ಪ್ರಕಾರಕ್ಕೆ ಪ್ರಸ್ತುತ ಯಾವುದೇ ಚಾಲಕರು ಲಭ್ಯವಿಲ್ಲ. ದಯವಿಟ್ಟು ನಂತರ ಮತ್ತೆ ಪ್ರಯತ್ನಿಸಿ ಅಥವಾ ಬೇರೆ ವಾಹನವನ್ನು ಆರಿಸಿ.")</f>
@@ -30247,8 +30505,8 @@
         <v>ನೀವು ಆಯ್ಕೆ ಮಾಡಿದ {ವಾಹನ} ಹತ್ತಿರದಲ್ಲಿ ಯಾವುದೇ ಚಾಲಕರಿಲ್ಲ. ಲಭ್ಯವಿರುವ ಚಾಲಕರಿರುವ ಮತ್ತೊಂದು ವಾಹನವನ್ನು ನಾವು ಆರಿಸಿಕೊಂಡಿದ್ದೇವೆ.</v>
       </c>
       <c r="F776" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B776, ""en"", ""ml"")"),"നിങ്ങൾ തിരഞ്ഞെടുത്ത {വാഹനത്തിന്} സമീപത്ത് ഡ്രൈവറില്ല. ലഭ്യമായ ഡ്രൈവറുകളുള്ള മറ്റൊരു വാഹനം ഞങ്ങൾ തിരഞ്ഞെടുത്തു.")</f>
-        <v>നിങ്ങൾ തിരഞ്ഞെടുത്ത {വാഹനത്തിന്} സമീപത്ത് ഡ്രൈവറില്ല. ലഭ്യമായ ഡ്രൈവറുകളുള്ള മറ്റൊരു വാഹനം ഞങ്ങൾ തിരഞ്ഞെടുത്തു.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B776, ""en"", ""ml"")"),"നിങ്ങൾ തിരഞ്ഞെടുത്ത {വാഹനത്തിന്} സമീപത്ത് ഡ്രൈവറുകളില്ല. ലഭ്യമായ ഡ്രൈവറുകളുള്ള മറ്റൊരു വാഹനം ഞങ്ങൾ തിരഞ്ഞെടുത്തു.")</f>
+        <v>നിങ്ങൾ തിരഞ്ഞെടുത്ത {വാഹനത്തിന്} സമീപത്ത് ഡ്രൈവറുകളില്ല. ലഭ്യമായ ഡ്രൈവറുകളുള്ള മറ്റൊരു വാഹനം ഞങ്ങൾ തിരഞ്ഞെടുത്തു.</v>
       </c>
       <c r="G776" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B776, ""en"", ""te"")"),"మీరు ఎంచుకున్న వాహనానికి సమీపంలో డ్రైవర్లు ఎవరూ లేరు. మేము డ్రైవర్లు అందుబాటులో ఉన్న మరో వాహనాన్ని ఎంచుకున్నాము.")</f>
@@ -30405,8 +30663,8 @@
         <v>कोई सुरक्षित स्थान नहीं</v>
       </c>
       <c r="E782" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B782, ""en"", ""kn"")"),"ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ.")</f>
-        <v>ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B782, ""en"", ""kn"")"),"ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ")</f>
+        <v>ಉಳಿಸಿದ ಸ್ಥಳಗಳಿಲ್ಲ</v>
       </c>
       <c r="F782" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B782, ""en"", ""ml"")"),"സംരക്ഷിച്ച സ്ഥലങ്ങളൊന്നുമില്ല.")</f>
@@ -30455,8 +30713,8 @@
         <v>1832</v>
       </c>
       <c r="D784" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B784, ""en"", ""hi"")"),"इस समय आस-पास कोई नाइट ड्राइवर उपलब्ध नहीं है। आप चाहें तो सभी ड्राइवरों को खोज सकते हैं।")</f>
-        <v>इस समय आस-पास कोई नाइट ड्राइवर उपलब्ध नहीं है। आप चाहें तो सभी ड्राइवरों को खोज सकते हैं।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B784, ""en"", ""hi"")"),"फिलहाल आस-पास कोई नाइट ड्राइवर उपलब्ध नहीं है। आप चाहें तो सभी ड्राइवरों को खोज सकते हैं।")</f>
+        <v>फिलहाल आस-पास कोई नाइट ड्राइवर उपलब्ध नहीं है। आप चाहें तो सभी ड्राइवरों को खोज सकते हैं।</v>
       </c>
       <c r="E784" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B784, ""en"", ""kn"")"),"ಈಗ ಹತ್ತಿರದಲ್ಲಿ ಯಾವುದೇ ರಾತ್ರಿ ಚಾಲಕರು ಇಲ್ಲ. ಬದಲಿಗೆ ನೀವು ಎಲ್ಲಾ ಚಾಲಕರನ್ನು ಹುಡುಕಬಹುದು.")</f>
@@ -32029,8 +32287,8 @@
         <v>कृपया आपातकालीन संपर्क चुनें</v>
       </c>
       <c r="E842" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B842, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ತುರ್ತು ಸಂಪರ್ಕಗಳನ್ನು ಆಯ್ಕೆಮಾಡಿ.")</f>
-        <v>ದಯವಿಟ್ಟು ತುರ್ತು ಸಂಪರ್ಕಗಳನ್ನು ಆಯ್ಕೆಮಾಡಿ.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B842, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ತುರ್ತು ಸಂಪರ್ಕಗಳನ್ನು ಆಯ್ಕೆಮಾಡಿ")</f>
+        <v>ದಯವಿಟ್ಟು ತುರ್ತು ಸಂಪರ್ಕಗಳನ್ನು ಆಯ್ಕೆಮಾಡಿ</v>
       </c>
       <c r="F842" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B842, ""en"", ""ml"")"),"ദയവായി അടിയന്തര കോൺടാക്റ്റുകൾ തിരഞ്ഞെടുക്കുക.")</f>
@@ -33106,8 +33364,8 @@
         <v>2108</v>
       </c>
       <c r="D882" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B882, ""en"", ""hi"")"),"सवारी उठा ली गई")</f>
-        <v>सवारी उठा ली गई</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B882, ""en"", ""hi"")"),"सवारी को पिकअप कर लिया गया")</f>
+        <v>सवारी को पिकअप कर लिया गया</v>
       </c>
       <c r="E882" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B882, ""en"", ""kn"")"),"ಸವಾರಿ ಎತ್ತಿಕೊಳ್ಳಲಾಗಿದೆ")</f>
@@ -33222,8 +33480,8 @@
         <v>ಸವಾರಿಯನ್ನು ಮಧ್ಯದಲ್ಲಿ ರದ್ದುಗೊಳಿಸಲಾಗಿದೆ.</v>
       </c>
       <c r="F886" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B886, ""en"", ""ml"")"),"യാത്ര പകുതി വഴിയിൽ വെച്ച് റദ്ദാക്കി.")</f>
-        <v>യാത്ര പകുതി വഴിയിൽ വെച്ച് റദ്ദാക്കി.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B886, ""en"", ""ml"")"),"യാത്ര പകുതി വഴിയിൽ റദ്ദാക്കി.")</f>
+        <v>യാത്ര പകുതി വഴിയിൽ റദ്ദാക്കി.</v>
       </c>
       <c r="G886" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B886, ""en"", ""te"")"),"ప్రయాణం మధ్యలోనే రద్దు చేయబడింది")</f>
@@ -33681,8 +33939,8 @@
         <v>ವೇಳಾಪಟ್ಟಿ</v>
       </c>
       <c r="F903" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B903, ""en"", ""ml"")"),"പട്ടിക")</f>
-        <v>പട്ടിക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B903, ""en"", ""ml"")"),"ഷെഡ്യൂൾ")</f>
+        <v>ഷെഡ്യൂൾ</v>
       </c>
       <c r="G903" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B903, ""en"", ""te"")"),"షెడ్యూల్")</f>
@@ -34309,8 +34567,8 @@
         <v>വീട്ടിലേക്കുള്ള യാത്രയായാലും ഓഫീസിലേക്കുള്ള യാത്രയായാലും സാഹസിക യാത്രയായാലും "നമ്മ ഊരു ടാക്സി®" നിങ്ങളെ അവിടെ കൊണ്ടുപോകാൻ തയ്യാറാണ്.</v>
       </c>
       <c r="G926" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B926, ""en"", ""te"")"),"అది ఇంటి ప్రయాణమైనా, ఆఫీసుకైనా, లేదా ఒక సాహసయాత్రకైనా, ""నమ్మ ఊరు టాక్సీ ®"" మిమ్మల్ని అక్కడికి చేర్చడానికి సిద్ధంగా ఉంది.")</f>
-        <v>అది ఇంటి ప్రయాణమైనా, ఆఫీసుకైనా, లేదా ఒక సాహసయాత్రకైనా, "నమ్మ ఊరు టాక్సీ ®" మిమ్మల్ని అక్కడికి చేర్చడానికి సిద్ధంగా ఉంది.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B926, ""en"", ""te"")"),"అది ఇంటికైనా, ఆఫీసుకైనా, లేదా ఒక సాహసయాత్రకైనా, ""నమ్మ ఊరు టాక్సీ ®"" మిమ్మల్ని అక్కడికి చేర్చడానికి సిద్ధంగా ఉంది.")</f>
+        <v>అది ఇంటికైనా, ఆఫీసుకైనా, లేదా ఒక సాహసయాత్రకైనా, "నమ్మ ఊరు టాక్సీ ®" మిమ్మల్ని అక్కడికి చేర్చడానికి సిద్ధంగా ఉంది.</v>
       </c>
     </row>
     <row r="927">
@@ -34872,8 +35130,8 @@
         <v>ಚಾಲಕ ತಡವಾಗಿ ಬಂದಿರುವುದು</v>
       </c>
       <c r="F947" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B947, ""en"", ""ml"")"),"ഡ്രൈവർ വൈകിയുള്ള വരവ്")</f>
-        <v>ഡ്രൈവർ വൈകിയുള്ള വരവ്</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B947, ""en"", ""ml"")"),"ഡ്രൈവർ വൈകി എത്തൽ")</f>
+        <v>ഡ്രൈവർ വൈകി എത്തൽ</v>
       </c>
       <c r="G947" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B947, ""en"", ""te"")"),"డ్రైవర్ ఆలస్యంగా రావడం")</f>
@@ -36223,8 +36481,8 @@
         <v>ನಿಮ್ಮ ಚಾಲಕನ ಆಗಮನವನ್ನು ನೈಜ ಸಮಯದಲ್ಲಿ ವೀಕ್ಷಿಸಿ ಮತ್ತು ಅವರ ಸ್ಥಳದ ಬಗ್ಗೆ ನವೀಕೃತವಾಗಿರಿ. ನಿಮ್ಮ ಸವಾರಿ ಯಾವಾಗ ಬರುತ್ತದೆ ಎಂದು ಇನ್ನು ಮುಂದೆ ಊಹಿಸುವ ಅಗತ್ಯವಿಲ್ಲ.</v>
       </c>
       <c r="F997" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B997, ""en"", ""ml"")"),"നിങ്ങളുടെ ഡ്രൈവറുടെ വരവ് തത്സമയം നിരീക്ഷിക്കുകയും അവരുടെ ലൊക്കേഷനുമായി അപ്‌ഡേറ്റ് ചെയ്യുകയും ചെയ്യുക. നിങ്ങളുടെ റൈഡ് എപ്പോൾ എത്തുമെന്ന് ഇനി ഊഹിക്കേണ്ടതില്ല.")</f>
-        <v>നിങ്ങളുടെ ഡ്രൈവറുടെ വരവ് തത്സമയം നിരീക്ഷിക്കുകയും അവരുടെ ലൊക്കേഷനുമായി അപ്‌ഡേറ്റ് ചെയ്യുകയും ചെയ്യുക. നിങ്ങളുടെ റൈഡ് എപ്പോൾ എത്തുമെന്ന് ഇനി ഊഹിക്കേണ്ടതില്ല.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B997, ""en"", ""ml"")"),"നിങ്ങളുടെ ഡ്രൈവറുടെ വരവ് തത്സമയം കാണുകയും അവരുടെ ലൊക്കേഷനുമായി അപ്‌ഡേറ്റ് ആയിരിക്കുകയും ചെയ്യുക. നിങ്ങളുടെ റൈഡ് എപ്പോൾ എത്തുമെന്ന് ഇനി ഊഹിക്കേണ്ടതില്ല.")</f>
+        <v>നിങ്ങളുടെ ഡ്രൈവറുടെ വരവ് തത്സമയം കാണുകയും അവരുടെ ലൊക്കേഷനുമായി അപ്‌ഡേറ്റ് ആയിരിക്കുകയും ചെയ്യുക. നിങ്ങളുടെ റൈഡ് എപ്പോൾ എത്തുമെന്ന് ഇനി ഊഹിക്കേണ്ടതില്ല.</v>
       </c>
       <c r="G997" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B997, ""en"", ""te"")"),"మీ డ్రైవర్ రాకను నిజ సమయంలో గమనించండి మరియు వారి లొకేషన్ గురించి ఎప్పటికప్పుడు తెలుసుకోండి. మీ రైడ్ ఎప్పుడు వస్తుందో ఇకపై ఊహించాల్సిన అవసరం లేదు.")</f>
@@ -36358,8 +36616,8 @@
         <v>{vehicleName} ಗರಿಷ್ಠ ದೂರ {maxKm} ಕಿ.ಮೀ. ದಯವಿಟ್ಟು ಬೇರೆ ವಾಹನವನ್ನು ಆಯ್ಕೆಮಾಡಿ ಅಥವಾ {maxKm} ಕಿ.ಮೀ.ಗಿಂತ ಕಡಿಮೆ ಪ್ರಯಾಣವನ್ನು ಯೋಜಿಸಿ.</v>
       </c>
       <c r="F1002" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1002, ""en"", ""ml"")"),"{vehicleName} പരമാവധി ദൂരം {maxKm} കിലോമീറ്ററാണ്. ദയവായി മറ്റൊരു വാഹനം തിരഞ്ഞെടുക്കുകയോ {maxKm} കിലോമീറ്ററിൽ താഴെയുള്ള യാത്ര പ്ലാൻ ചെയ്യുകയോ ചെയ്യുക.")</f>
-        <v>{vehicleName} പരമാവധി ദൂരം {maxKm} കിലോമീറ്ററാണ്. ദയവായി മറ്റൊരു വാഹനം തിരഞ്ഞെടുക്കുകയോ {maxKm} കിലോമീറ്ററിൽ താഴെയുള്ള യാത്ര പ്ലാൻ ചെയ്യുകയോ ചെയ്യുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1002, ""en"", ""ml"")"),"{vehicleName} പരമാവധി ദൂരം {maxKm} കിലോമീറ്ററാണ്. മറ്റൊരു വാഹനം തിരഞ്ഞെടുക്കുകയോ {maxKm} കിലോമീറ്ററിൽ താഴെയുള്ള യാത്ര പ്ലാൻ ചെയ്യുകയോ ചെയ്യുക.")</f>
+        <v>{vehicleName} പരമാവധി ദൂരം {maxKm} കിലോമീറ്ററാണ്. മറ്റൊരു വാഹനം തിരഞ്ഞെടുക്കുകയോ {maxKm} കിലോമീറ്ററിൽ താഴെയുള്ള യാത്ര പ്ലാൻ ചെയ്യുകയോ ചെയ്യുക.</v>
       </c>
       <c r="G1002" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1002, ""en"", ""te"")"),"{vehicleName} గరిష్ట దూరం {maxKm} కి.మీ. దయచేసి వేరే వాహనాన్ని ఎంచుకోండి లేదా {maxKm} కి.మీ. కంటే తక్కువ ప్రయాణాన్ని ప్లాన్ చేసుకోండి.")</f>
@@ -36655,8 +36913,8 @@
         <v>ಬೇರೆ ಹೆಸರು ಅಥವಾ ಸಂಖ್ಯೆಯನ್ನು ಪ್ರಯತ್ನಿಸಿ</v>
       </c>
       <c r="F1013" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1013, ""en"", ""ml"")"),"മറ്റൊരു പേരോ നമ്പറോ പരീക്ഷിക്കൂ")</f>
-        <v>മറ്റൊരു പേരോ നമ്പറോ പരീക്ഷിക്കൂ</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1013, ""en"", ""ml"")"),"മറ്റൊരു പേരോ നമ്പറോ പരീക്ഷിച്ചുനോക്കൂ")</f>
+        <v>മറ്റൊരു പേരോ നമ്പറോ പരീക്ഷിച്ചുനോക്കൂ</v>
       </c>
       <c r="G1013" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1013, ""en"", ""te"")"),"వేరే పేరు లేదా నంబర్‌ను ప్రయత్నించండి")</f>
@@ -38192,8 +38450,8 @@
         <v>ಈ ಹಂತಗಳನ್ನು ಪೂರ್ಣಗೊಳಿಸಿ ಇದರಿಂದ ನೀವು ಸವಾರಿಗಳನ್ನು ಸ್ವೀಕರಿಸಲು ಪ್ರಾರಂಭಿಸಬಹುದು.</v>
       </c>
       <c r="F1069" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1069, ""en"", ""ml"")"),"റൈഡുകൾ സ്വീകരിക്കാൻ തുടങ്ങുന്നതിന് ഈ ഘട്ടങ്ങൾ പൂർത്തിയാക്കുക.")</f>
-        <v>റൈഡുകൾ സ്വീകരിക്കാൻ തുടങ്ങുന്നതിന് ഈ ഘട്ടങ്ങൾ പൂർത്തിയാക്കുക.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1069, ""en"", ""ml"")"),"റൈഡുകൾ സ്വീകരിച്ചു തുടങ്ങാൻ ഈ ഘട്ടങ്ങൾ പൂർത്തിയാക്കുക.")</f>
+        <v>റൈഡുകൾ സ്വീകരിച്ചു തുടങ്ങാൻ ഈ ഘട്ടങ്ങൾ പൂർത്തിയാക്കുക.</v>
       </c>
       <c r="G1069" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1069, ""en"", ""te"")"),"మీరు రైడ్‌లను స్వీకరించడం ప్రారంభించడానికి ఈ దశలను పూర్తి చేయండి")</f>
@@ -38836,8 +39094,8 @@
         <v>ಆಧಾರ್ ಕಾರ್ಡ್ ಅನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ ಅಥವಾ ಸೆರೆಹಿಡಿಯಿರಿ</v>
       </c>
       <c r="F1092" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1092, ""en"", ""ml"")"),"ആധാർ കാർഡ് അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ പിടിച്ചെടുക്കുക")</f>
-        <v>ആധാർ കാർഡ് അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ പിടിച്ചെടുക്കുക</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1092, ""en"", ""ml"")"),"ആധാർ കാർഡ് അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ എടുക്കുക")</f>
+        <v>ആധാർ കാർഡ് അപ്‌ലോഡ് ചെയ്യുക അല്ലെങ്കിൽ എടുക്കുക</v>
       </c>
       <c r="G1092" s="7" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1092, ""en"", ""te"")"),"ఆధార్ కార్డును అప్‌లోడ్ చేయండి లేదా చిత్రీకరించండి")</f>
@@ -39454,8 +39712,8 @@
         <v>ഈ യാത്ര റദ്ദാക്കണമെന്ന് നിങ്ങൾക്ക് ഉറപ്പാണോ? റദ്ദാക്കൽ പിഴ ബാധകമായേക്കാം.</v>
       </c>
       <c r="G1114" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1114, ""en"", ""te"")"),"మీరు ఈ యాత్రను రద్దు చేయాలనుకుంటున్నారా? రద్దు చేసినందుకు జరిమానా వర్తించవచ్చు.")</f>
-        <v>మీరు ఈ యాత్రను రద్దు చేయాలనుకుంటున్నారా? రద్దు చేసినందుకు జరిమానా వర్తించవచ్చు.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1114, ""en"", ""te"")"),"మీరు ఈ యాత్రను రద్దు చేసుకోవాలని ఖచ్చితంగా అనుకుంటున్నారా? రద్దు చేసినందుకు జరిమానా వర్తించవచ్చు.")</f>
+        <v>మీరు ఈ యాత్రను రద్దు చేసుకోవాలని ఖచ్చితంగా అనుకుంటున్నారా? రద్దు చేసినందుకు జరిమానా వర్తించవచ్చు.</v>
       </c>
     </row>
     <row r="1115">
@@ -39872,8 +40130,8 @@
         <v>ஓட்டுநர் விவரங்களைப் பெற புதுப்பிக்கவும்</v>
       </c>
       <c r="D1129" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1129, ""en"", ""hi"")"),"ड्राइवर की जानकारी प्राप्त करने के लिए पेज को रिफ्रेश करें।")</f>
-        <v>ड्राइवर की जानकारी प्राप्त करने के लिए पेज को रिफ्रेश करें।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1129, ""en"", ""hi"")"),"ड्राइवर की जानकारी प्राप्त करने के लिए पेज को रिफ्रेश करें")</f>
+        <v>ड्राइवर की जानकारी प्राप्त करने के लिए पेज को रिफ्रेश करें</v>
       </c>
       <c r="E1129" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1129, ""en"", ""kn"")"),"ಚಾಲಕ ವಿವರಗಳನ್ನು ಪಡೆಯಲು ರಿಫ್ರೆಶ್ ಮಾಡಿ")</f>
@@ -39940,8 +40198,8 @@
         <v>ഡ്രൈവറായി സൈൻ ഇൻ ചെയ്യാൻ നിങ്ങളെ ഉപഭോക്തൃ ആപ്പിൽ നിന്ന് ഞങ്ങൾ ലോഗ് ഔട്ട് ചെയ്യും. തുടരണോ?</v>
       </c>
       <c r="G1131" s="7" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1131, ""en"", ""te"")"),"మీరు డ్రైవర్‌గా సైన్ ఇన్ చేయడానికి వీలుగా మేము మిమ్మల్ని కస్టమర్ యాప్ నుండి లాగ్ అవుట్ చేస్తాము. కొనసాగించాలా?")</f>
-        <v>మీరు డ్రైవర్‌గా సైన్ ఇన్ చేయడానికి వీలుగా మేము మిమ్మల్ని కస్టమర్ యాప్ నుండి లాగ్ అవుట్ చేస్తాము. కొనసాగించాలా?</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1131, ""en"", ""te"")"),"మీరు డ్రైవర్‌గా సైన్ ఇన్ చేయడానికి వీలుగా, మేము మిమ్మల్ని కస్టమర్ యాప్ నుండి లాగ్ అవుట్ చేస్తాము. కొనసాగించాలా?")</f>
+        <v>మీరు డ్రైవర్‌గా సైన్ ఇన్ చేయడానికి వీలుగా, మేము మిమ్మల్ని కస్టమర్ యాప్ నుండి లాగ్ అవుట్ చేస్తాము. కొనసాగించాలా?</v>
       </c>
     </row>
     <row r="1132">
@@ -40036,12 +40294,12 @@
         <v>2747</v>
       </c>
       <c r="C1135" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1135, ""en"", ""ta"")"),"உங்கள் அமர்வு நேரம் முடிந்துவிட்டது. தயவுசெய்து மீண்டும் உள்நுழையவும்.")</f>
-        <v>உங்கள் அமர்வு நேரம் முடிந்துவிட்டது. தயவுசெய்து மீண்டும் உள்நுழையவும்.</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1135, ""en"", ""ta"")"),"உங்கள் அமர்வு நேரம் முடிந்துவிட்டது. மீண்டும் உள்நுழையவும்.")</f>
+        <v>உங்கள் அமர்வு நேரம் முடிந்துவிட்டது. மீண்டும் உள்நுழையவும்.</v>
       </c>
       <c r="D1135" s="6" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1135, ""en"", ""hi"")"),"आपका सत्र समाप्त हो गया है। कृपया पुनः लॉग इन करें।")</f>
-        <v>आपका सत्र समाप्त हो गया है। कृपया पुनः लॉग इन करें।</v>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1135, ""en"", ""hi"")"),"आपका सत्र समाप्त हो गया है। कृपया दोबारा लॉग इन करें।")</f>
+        <v>आपका सत्र समाप्त हो गया है। कृपया दोबारा लॉग इन करें।</v>
       </c>
       <c r="E1135" s="6" t="str">
         <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1135, ""en"", ""kn"")"),"ನಿಮ್ಮ ಅವಧಿ ಮುಗಿದಿದೆ. ದಯವಿಟ್ಟು ಮತ್ತೆ ಲಾಗಿನ್ ಮಾಡಿ.")</f>
@@ -40924,319 +41182,1264 @@
       </c>
     </row>
     <row r="1167">
-      <c r="A1167" s="4"/>
-      <c r="B1167" s="5"/>
-      <c r="C1167" s="6"/>
-      <c r="D1167" s="6"/>
-      <c r="E1167" s="6"/>
+      <c r="A1167" s="12" t="s">
+        <v>2807</v>
+      </c>
+      <c r="B1167" s="13" t="s">
+        <v>2808</v>
+      </c>
+      <c r="C1167" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1167, ""en"", ""ta"")"),"என் கேரேஜ்")</f>
+        <v>என் கேரேஜ்</v>
+      </c>
+      <c r="D1167" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1167, ""en"", ""hi"")"),"मेरा गैराज")</f>
+        <v>मेरा गैराज</v>
+      </c>
+      <c r="E1167" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1167, ""en"", ""kn"")"),"ನನ್ನ ಗ್ಯಾರೇಜ್")</f>
+        <v>ನನ್ನ ಗ್ಯಾರೇಜ್</v>
+      </c>
+      <c r="F1167" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1167, ""en"", ""ml"")"),"എന്റെ ഗാരേജ്")</f>
+        <v>എന്റെ ഗാരേജ്</v>
+      </c>
+      <c r="G1167" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1167, ""en"", ""te"")"),"నా గ్యారేజ్")</f>
+        <v>నా గ్యారేజ్</v>
+      </c>
     </row>
     <row r="1168">
-      <c r="A1168" s="4"/>
-      <c r="B1168" s="5"/>
-      <c r="C1168" s="6"/>
-      <c r="D1168" s="6"/>
-      <c r="E1168" s="6"/>
+      <c r="A1168" s="12" t="s">
+        <v>2809</v>
+      </c>
+      <c r="B1168" s="13" t="s">
+        <v>2810</v>
+      </c>
+      <c r="C1168" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1168, ""en"", ""ta"")"),"முழு முகவரியைக் காண்க")</f>
+        <v>முழு முகவரியைக் காண்க</v>
+      </c>
+      <c r="D1168" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1168, ""en"", ""hi"")"),"पूरा पता देखें")</f>
+        <v>पूरा पता देखें</v>
+      </c>
+      <c r="E1168" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1168, ""en"", ""kn"")"),"ಪೂರ್ಣ ವಿಳಾಸವನ್ನು ವೀಕ್ಷಿಸಿ")</f>
+        <v>ಪೂರ್ಣ ವಿಳಾಸವನ್ನು ವೀಕ್ಷಿಸಿ</v>
+      </c>
+      <c r="F1168" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1168, ""en"", ""ml"")"),"മുഴുവൻ വിലാസവും കാണുക")</f>
+        <v>മുഴുവൻ വിലാസവും കാണുക</v>
+      </c>
+      <c r="G1168" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1168, ""en"", ""te"")"),"పూర్తి చిరునామాను వీక్షించండి")</f>
+        <v>పూర్తి చిరునామాను వీక్షించండి</v>
+      </c>
     </row>
     <row r="1169">
-      <c r="A1169" s="4"/>
-      <c r="B1169" s="5"/>
-      <c r="C1169" s="6"/>
-      <c r="D1169" s="6"/>
-      <c r="E1169" s="6"/>
+      <c r="A1169" s="12" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B1169" s="13" t="s">
+        <v>2812</v>
+      </c>
+      <c r="C1169" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1169, ""en"", ""ta"")"),"புகைப்படங்கள் மற்றும் ரசீதுகளைப் பதிவேற்றவும்")</f>
+        <v>புகைப்படங்கள் மற்றும் ரசீதுகளைப் பதிவேற்றவும்</v>
+      </c>
+      <c r="D1169" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1169, ""en"", ""hi"")"),"फ़ोटो और बिल अपलोड करें")</f>
+        <v>फ़ोटो और बिल अपलोड करें</v>
+      </c>
+      <c r="E1169" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1169, ""en"", ""kn"")"),"ಫೋಟೋಗಳು ಮತ್ತು ಬಿಲ್‌ಗಳನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ")</f>
+        <v>ಫೋಟೋಗಳು ಮತ್ತು ಬಿಲ್‌ಗಳನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ</v>
+      </c>
+      <c r="F1169" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1169, ""en"", ""ml"")"),"ഫോട്ടോകളും ബില്ലുകളും അപ്‌ലോഡ് ചെയ്യുക")</f>
+        <v>ഫോട്ടോകളും ബില്ലുകളും അപ്‌ലോഡ് ചെയ്യുക</v>
+      </c>
+      <c r="G1169" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1169, ""en"", ""te"")"),"ఫోటోలు మరియు బిల్లులను అప్‌లోడ్ చేయండి")</f>
+        <v>ఫోటోలు మరియు బిల్లులను అప్‌లోడ్ చేయండి</v>
+      </c>
     </row>
     <row r="1170">
-      <c r="A1170" s="4"/>
-      <c r="B1170" s="5"/>
-      <c r="C1170" s="6"/>
-      <c r="D1170" s="6"/>
-      <c r="E1170" s="6"/>
+      <c r="A1170" s="12" t="s">
+        <v>2813</v>
+      </c>
+      <c r="B1170" s="13" t="s">
+        <v>2814</v>
+      </c>
+      <c r="C1170" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1170, ""en"", ""ta"")"),"இப்போது புகைப்படங்களைப் பதிவேற்றவும்")</f>
+        <v>இப்போது புகைப்படங்களைப் பதிவேற்றவும்</v>
+      </c>
+      <c r="D1170" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1170, ""en"", ""hi"")"),"अभी फ़ोटो अपलोड करें")</f>
+        <v>अभी फ़ोटो अपलोड करें</v>
+      </c>
+      <c r="E1170" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1170, ""en"", ""kn"")"),"ಫೋಟೋಗಳನ್ನು ಈಗಲೇ ಅಪ್‌ಲೋಡ್ ಮಾಡಿ")</f>
+        <v>ಫೋಟೋಗಳನ್ನು ಈಗಲೇ ಅಪ್‌ಲೋಡ್ ಮಾಡಿ</v>
+      </c>
+      <c r="F1170" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1170, ""en"", ""ml"")"),"ഇപ്പോൾ ഫോട്ടോകൾ അപ്‌ലോഡ് ചെയ്യുക")</f>
+        <v>ഇപ്പോൾ ഫോട്ടോകൾ അപ്‌ലോഡ് ചെയ്യുക</v>
+      </c>
+      <c r="G1170" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1170, ""en"", ""te"")"),"ఇప్పుడే ఫోటోలను అప్‌లోడ్ చేయండి")</f>
+        <v>ఇప్పుడే ఫోటోలను అప్‌లోడ్ చేయండి</v>
+      </c>
     </row>
     <row r="1171">
-      <c r="A1171" s="4"/>
-      <c r="B1171" s="5"/>
-      <c r="C1171" s="6"/>
-      <c r="D1171" s="6"/>
-      <c r="E1171" s="6"/>
+      <c r="A1171" s="12" t="s">
+        <v>2815</v>
+      </c>
+      <c r="B1171" s="13" t="s">
+        <v>2816</v>
+      </c>
+      <c r="C1171" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1171, ""en"", ""ta"")"),"வாகனப் புகைப்படங்கள் தேவை")</f>
+        <v>வாகனப் புகைப்படங்கள் தேவை</v>
+      </c>
+      <c r="D1171" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1171, ""en"", ""hi"")"),"वाहन की तस्वीरें आवश्यक हैं")</f>
+        <v>वाहन की तस्वीरें आवश्यक हैं</v>
+      </c>
+      <c r="E1171" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1171, ""en"", ""kn"")"),"ವಾಹನದ ಫೋಟೋಗಳು ಅಗತ್ಯವಿದೆ")</f>
+        <v>ವಾಹನದ ಫೋಟೋಗಳು ಅಗತ್ಯವಿದೆ</v>
+      </c>
+      <c r="F1171" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1171, ""en"", ""ml"")"),"വാഹന ഫോട്ടോകൾ ആവശ്യമാണ്")</f>
+        <v>വാഹന ഫോട്ടോകൾ ആവശ്യമാണ്</v>
+      </c>
+      <c r="G1171" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1171, ""en"", ""te"")"),"వాహన ఫోటోలు అవసరం")</f>
+        <v>వాహన ఫోటోలు అవసరం</v>
+      </c>
     </row>
     <row r="1172">
-      <c r="A1172" s="4"/>
-      <c r="B1172" s="5"/>
-      <c r="C1172" s="6"/>
-      <c r="D1172" s="6"/>
-      <c r="E1172" s="6"/>
+      <c r="A1172" s="12" t="s">
+        <v>2817</v>
+      </c>
+      <c r="B1172" s="13" t="s">
+        <v>2818</v>
+      </c>
+      <c r="C1172" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1172, ""en"", ""ta"")"),"பயணத்தைத் தொடங்குவதற்கு முன், வாகனத்தின் நிலை குறித்த 4 புகைப்படங்களையும் பதிவேற்றவும். இது, பயணம் தொடங்கும் போது வாகனத்தின் நிலையைப் பதிவு செய்ய உதவும்.")</f>
+        <v>பயணத்தைத் தொடங்குவதற்கு முன், வாகனத்தின் நிலை குறித்த 4 புகைப்படங்களையும் பதிவேற்றவும். இது, பயணம் தொடங்கும் போது வாகனத்தின் நிலையைப் பதிவு செய்ய உதவும்.</v>
+      </c>
+      <c r="D1172" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1172, ""en"", ""hi"")"),"कृपया यात्रा शुरू करने से पहले वाहन की स्थिति की 4 तस्वीरें अपलोड करें। इससे यात्रा शुरू होने के समय वाहन की स्थिति का रिकॉर्ड रखने में मदद मिलेगी।")</f>
+        <v>कृपया यात्रा शुरू करने से पहले वाहन की स्थिति की 4 तस्वीरें अपलोड करें। इससे यात्रा शुरू होने के समय वाहन की स्थिति का रिकॉर्ड रखने में मदद मिलेगी।</v>
+      </c>
+      <c r="E1172" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1172, ""en"", ""kn"")"),"ಸವಾರಿ ಪ್ರಾರಂಭಿಸುವ ಮೊದಲು ದಯವಿಟ್ಟು 4 ವಾಹನ ಸ್ಥಿತಿಯ ಫೋಟೋಗಳನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ. ಇದು ಪ್ರಯಾಣದ ಆರಂಭದಲ್ಲಿ ವಾಹನದ ಸ್ಥಿತಿಯನ್ನು ದಾಖಲಿಸಲು ಸಹಾಯ ಮಾಡುತ್ತದೆ.")</f>
+        <v>ಸವಾರಿ ಪ್ರಾರಂಭಿಸುವ ಮೊದಲು ದಯವಿಟ್ಟು 4 ವಾಹನ ಸ್ಥಿತಿಯ ಫೋಟೋಗಳನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ. ಇದು ಪ್ರಯಾಣದ ಆರಂಭದಲ್ಲಿ ವಾಹನದ ಸ್ಥಿತಿಯನ್ನು ದಾಖಲಿಸಲು ಸಹಾಯ ಮಾಡುತ್ತದೆ.</v>
+      </c>
+      <c r="F1172" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1172, ""en"", ""ml"")"),"യാത്ര ആരംഭിക്കുന്നതിന് മുമ്പ് ദയവായി 4 വാഹന അവസ്ഥ ഫോട്ടോകൾ അപ്‌ലോഡ് ചെയ്യുക. യാത്ര ആരംഭിക്കുമ്പോൾ വാഹനത്തിന്റെ അവസ്ഥ രേഖപ്പെടുത്താൻ ഇത് സഹായിക്കുന്നു.")</f>
+        <v>യാത്ര ആരംഭിക്കുന്നതിന് മുമ്പ് ദയവായി 4 വാഹന അവസ്ഥ ഫോട്ടോകൾ അപ്‌ലോഡ് ചെയ്യുക. യാത്ര ആരംഭിക്കുമ്പോൾ വാഹനത്തിന്റെ അവസ്ഥ രേഖപ്പെടുത്താൻ ഇത് സഹായിക്കുന്നു.</v>
+      </c>
+      <c r="G1172" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1172, ""en"", ""te"")"),"దయచేసి ప్రయాణం ప్రారంభించే ముందు వాహనం యొక్క స్థితికి సంబంధించిన 4 ఫోటోలను అప్‌లోడ్ చేయండి. ఇది ప్రయాణం ప్రారంభంలో వాహనం యొక్క స్థితిని నమోదు చేయడానికి సహాయపడుతుంది.")</f>
+        <v>దయచేసి ప్రయాణం ప్రారంభించే ముందు వాహనం యొక్క స్థితికి సంబంధించిన 4 ఫోటోలను అప్‌లోడ్ చేయండి. ఇది ప్రయాణం ప్రారంభంలో వాహనం యొక్క స్థితిని నమోదు చేయడానికి సహాయపడుతుంది.</v>
+      </c>
     </row>
     <row r="1173">
-      <c r="A1173" s="4"/>
-      <c r="B1173" s="5"/>
-      <c r="C1173" s="6"/>
-      <c r="D1173" s="6"/>
-      <c r="E1173" s="6"/>
+      <c r="A1173" s="12" t="s">
+        <v>2819</v>
+      </c>
+      <c r="B1173" s="13" t="s">
+        <v>2820</v>
+      </c>
+      <c r="C1173" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1173, ""en"", ""ta"")"),"பயணத்திற்குப் பிந்தைய புகைப்படங்கள் தேவை")</f>
+        <v>பயணத்திற்குப் பிந்தைய புகைப்படங்கள் தேவை</v>
+      </c>
+      <c r="D1173" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1173, ""en"", ""hi"")"),"यात्रा के बाद की तस्वीरें आवश्यक हैं")</f>
+        <v>यात्रा के बाद की तस्वीरें आवश्यक हैं</v>
+      </c>
+      <c r="E1173" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1173, ""en"", ""kn"")"),"ಪ್ರವಾಸದ ನಂತರದ ಫೋಟೋಗಳು ಕಡ್ಡಾಯ")</f>
+        <v>ಪ್ರವಾಸದ ನಂತರದ ಫೋಟೋಗಳು ಕಡ್ಡಾಯ</v>
+      </c>
+      <c r="F1173" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1173, ""en"", ""ml"")"),"യാത്രയ്ക്കു ശേഷമുള്ള ഫോട്ടോകൾ നിർബന്ധം")</f>
+        <v>യാത്രയ്ക്കു ശേഷമുള്ള ഫോട്ടോകൾ നിർബന്ധം</v>
+      </c>
+      <c r="G1173" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1173, ""en"", ""te"")"),"ప్రయాణం తర్వాత ఫోటోలు అవసరం")</f>
+        <v>ప్రయాణం తర్వాత ఫోటోలు అవసరం</v>
+      </c>
     </row>
     <row r="1174">
-      <c r="A1174" s="4"/>
-      <c r="B1174" s="5"/>
-      <c r="C1174" s="6"/>
-      <c r="D1174" s="6"/>
-      <c r="E1174" s="6"/>
+      <c r="A1174" s="12" t="s">
+        <v>2821</v>
+      </c>
+      <c r="B1174" s="13" t="s">
+        <v>2822</v>
+      </c>
+      <c r="C1174" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1174, ""en"", ""ta"")"),"பயணத்தை முடிப்பதற்கு முன், பயணத்திற்குப் பிந்தைய வாகனத்தின் நிலை குறித்த 4 புகைப்படங்களைப் பதிவேற்றவும். இது பயணத்தின் முடிவில் வாகனத்தின் நிலையைப் பதிவு செய்ய உதவும்.")</f>
+        <v>பயணத்தை முடிப்பதற்கு முன், பயணத்திற்குப் பிந்தைய வாகனத்தின் நிலை குறித்த 4 புகைப்படங்களைப் பதிவேற்றவும். இது பயணத்தின் முடிவில் வாகனத்தின் நிலையைப் பதிவு செய்ய உதவும்.</v>
+      </c>
+      <c r="D1174" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1174, ""en"", ""hi"")"),"यात्रा समाप्त करने से पहले कृपया वाहन की स्थिति की चार तस्वीरें अपलोड करें। इससे यात्रा समाप्त होने पर वाहन की स्थिति का रिकॉर्ड रखने में मदद मिलेगी।")</f>
+        <v>यात्रा समाप्त करने से पहले कृपया वाहन की स्थिति की चार तस्वीरें अपलोड करें। इससे यात्रा समाप्त होने पर वाहन की स्थिति का रिकॉर्ड रखने में मदद मिलेगी।</v>
+      </c>
+      <c r="E1174" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1174, ""en"", ""kn"")"),"ಸವಾರಿಯನ್ನು ಕೊನೆಗೊಳಿಸುವ ಮೊದಲು ದಯವಿಟ್ಟು 4 ಪ್ರವಾಸದ ನಂತರದ ವಾಹನ ಸ್ಥಿತಿಯ ಫೋಟೋಗಳನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ. ಇದು ಪ್ರಯಾಣದ ಕೊನೆಯಲ್ಲಿ ವಾಹನದ ಸ್ಥಿತಿಯನ್ನು ದಾಖಲಿಸಲು ಸಹಾಯ ಮಾಡುತ್ತದೆ.")</f>
+        <v>ಸವಾರಿಯನ್ನು ಕೊನೆಗೊಳಿಸುವ ಮೊದಲು ದಯವಿಟ್ಟು 4 ಪ್ರವಾಸದ ನಂತರದ ವಾಹನ ಸ್ಥಿತಿಯ ಫೋಟೋಗಳನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ. ಇದು ಪ್ರಯಾಣದ ಕೊನೆಯಲ್ಲಿ ವಾಹನದ ಸ್ಥಿತಿಯನ್ನು ದಾಖಲಿಸಲು ಸಹಾಯ ಮಾಡುತ್ತದೆ.</v>
+      </c>
+      <c r="F1174" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1174, ""en"", ""ml"")"),"യാത്ര അവസാനിപ്പിക്കുന്നതിന് മുമ്പ് യാത്രയ്ക്ക് ശേഷമുള്ള 4 വാഹന കണ്ടീഷൻ ഫോട്ടോകൾ അപ്‌ലോഡ് ചെയ്യുക. യാത്രയുടെ അവസാനം വാഹനത്തിന്റെ കണ്ടീഷൻ രേഖപ്പെടുത്താൻ ഇത് സഹായിക്കുന്നു.")</f>
+        <v>യാത്ര അവസാനിപ്പിക്കുന്നതിന് മുമ്പ് യാത്രയ്ക്ക് ശേഷമുള്ള 4 വാഹന കണ്ടീഷൻ ഫോട്ടോകൾ അപ്‌ലോഡ് ചെയ്യുക. യാത്രയുടെ അവസാനം വാഹനത്തിന്റെ കണ്ടീഷൻ രേഖപ്പെടുത്താൻ ഇത് സഹായിക്കുന്നു.</v>
+      </c>
+      <c r="G1174" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1174, ""en"", ""te"")"),"దయచేసి ప్రయాణం ముగించే ముందు, ప్రయాణం తర్వాత వాహనం యొక్క స్థితికి సంబంధించిన 4 ఫోటోలను అప్‌లోడ్ చేయండి. ఇది ప్రయాణం ముగిసే సమయానికి వాహనం యొక్క స్థితిని నమోదు చేయడానికి సహాయపడుతుంది.")</f>
+        <v>దయచేసి ప్రయాణం ముగించే ముందు, ప్రయాణం తర్వాత వాహనం యొక్క స్థితికి సంబంధించిన 4 ఫోటోలను అప్‌లోడ్ చేయండి. ఇది ప్రయాణం ముగిసే సమయానికి వాహనం యొక్క స్థితిని నమోదు చేయడానికి సహాయపడుతుంది.</v>
+      </c>
     </row>
     <row r="1175">
-      <c r="A1175" s="4"/>
-      <c r="B1175" s="5"/>
-      <c r="C1175" s="6"/>
-      <c r="D1175" s="6"/>
-      <c r="E1175" s="6"/>
+      <c r="A1175" s="12" t="s">
+        <v>2823</v>
+      </c>
+      <c r="B1175" s="13" t="s">
+        <v>2824</v>
+      </c>
+      <c r="C1175" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1175, ""en"", ""ta"")"),"புகைப்படங்களைப் பதிவேற்றவும்")</f>
+        <v>புகைப்படங்களைப் பதிவேற்றவும்</v>
+      </c>
+      <c r="D1175" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1175, ""en"", ""hi"")"),"फ़ोटो अपलोड करें")</f>
+        <v>फ़ोटो अपलोड करें</v>
+      </c>
+      <c r="E1175" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1175, ""en"", ""kn"")"),"ಫೋಟೋಗಳನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ")</f>
+        <v>ಫೋಟೋಗಳನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ</v>
+      </c>
+      <c r="F1175" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1175, ""en"", ""ml"")"),"ഫോട്ടോകൾ അപ്‌ലോഡ് ചെയ്യുക")</f>
+        <v>ഫോട്ടോകൾ അപ്‌ലോഡ് ചെയ്യുക</v>
+      </c>
+      <c r="G1175" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1175, ""en"", ""te"")"),"ఫోటోలను అప్‌లోడ్ చేయండి")</f>
+        <v>ఫోటోలను అప్‌లోడ్ చేయండి</v>
+      </c>
     </row>
     <row r="1176">
-      <c r="A1176" s="4"/>
-      <c r="B1176" s="5"/>
-      <c r="C1176" s="6"/>
-      <c r="D1176" s="6"/>
-      <c r="E1176" s="6"/>
+      <c r="A1176" s="12" t="s">
+        <v>2825</v>
+      </c>
+      <c r="B1176" s="13" t="s">
+        <v>2826</v>
+      </c>
+      <c r="C1176" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1176, ""en"", ""ta"")"),"பதிவேற்றப்படுகிறது...")</f>
+        <v>பதிவேற்றப்படுகிறது...</v>
+      </c>
+      <c r="D1176" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1176, ""en"", ""hi"")"),"अपलोड हो रहा है...")</f>
+        <v>अपलोड हो रहा है...</v>
+      </c>
+      <c r="E1176" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1176, ""en"", ""kn"")"),"ಅಪ್‌ಲೋಡ್ ಮಾಡಲಾಗುತ್ತಿದೆ...")</f>
+        <v>ಅಪ್‌ಲೋಡ್ ಮಾಡಲಾಗುತ್ತಿದೆ...</v>
+      </c>
+      <c r="F1176" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1176, ""en"", ""ml"")"),"അപ്‌ലോഡ് ചെയ്യുന്നു...")</f>
+        <v>അപ്‌ലോഡ് ചെയ്യുന്നു...</v>
+      </c>
+      <c r="G1176" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1176, ""en"", ""te"")"),"అప్‌లోడ్ అవుతోంది...")</f>
+        <v>అప్‌లోడ్ అవుతోంది...</v>
+      </c>
     </row>
     <row r="1177">
-      <c r="A1177" s="4"/>
-      <c r="B1177" s="5"/>
-      <c r="C1177" s="6"/>
-      <c r="D1177" s="6"/>
-      <c r="E1177" s="6"/>
+      <c r="A1177" s="12" t="s">
+        <v>2827</v>
+      </c>
+      <c r="B1177" s="13" t="s">
+        <v>2828</v>
+      </c>
+      <c r="C1177" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1177, ""en"", ""ta"")"),"மறுதேர்வு")</f>
+        <v>மறுதேர்வு</v>
+      </c>
+      <c r="D1177" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1177, ""en"", ""hi"")"),"फिर से लेना")</f>
+        <v>फिर से लेना</v>
+      </c>
+      <c r="E1177" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1177, ""en"", ""kn"")"),"ಪುನಃ ತೆಗೆದುಕೊಳ್ಳಿ")</f>
+        <v>ಪುನಃ ತೆಗೆದುಕೊಳ್ಳಿ</v>
+      </c>
+      <c r="F1177" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1177, ""en"", ""ml"")"),"വീണ്ടും എടുക്കുക")</f>
+        <v>വീണ്ടും എടുക്കുക</v>
+      </c>
+      <c r="G1177" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1177, ""en"", ""te"")"),"తిరిగి తీసుకోండి")</f>
+        <v>తిరిగి తీసుకోండి</v>
+      </c>
     </row>
     <row r="1178">
-      <c r="A1178" s="4"/>
-      <c r="B1178" s="5"/>
-      <c r="C1178" s="6"/>
-      <c r="D1178" s="6"/>
-      <c r="E1178" s="6"/>
+      <c r="A1178" s="12" t="s">
+        <v>2829</v>
+      </c>
+      <c r="B1178" s="13" t="s">
+        <v>2830</v>
+      </c>
+      <c r="C1178" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1178, ""en"", ""ta"")"),"ஏற்றத் தவறிவிட்டது")</f>
+        <v>ஏற்றத் தவறிவிட்டது</v>
+      </c>
+      <c r="D1178" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1178, ""en"", ""hi"")"),"लोड करने में विफल")</f>
+        <v>लोड करने में विफल</v>
+      </c>
+      <c r="E1178" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1178, ""en"", ""kn"")"),"ಲೋಡ್ ಮಾಡಲು ವಿಫಲವಾಗಿದೆ")</f>
+        <v>ಲೋಡ್ ಮಾಡಲು ವಿಫಲವಾಗಿದೆ</v>
+      </c>
+      <c r="F1178" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1178, ""en"", ""ml"")"),"ലോഡ് ചെയ്യാനായില്ല")</f>
+        <v>ലോഡ് ചെയ്യാനായില്ല</v>
+      </c>
+      <c r="G1178" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1178, ""en"", ""te"")"),"లోడ్ చేయడంలో విఫలమైంది")</f>
+        <v>లోడ్ చేయడంలో విఫలమైంది</v>
+      </c>
     </row>
     <row r="1179">
-      <c r="A1179" s="4"/>
-      <c r="B1179" s="5"/>
-      <c r="C1179" s="6"/>
-      <c r="D1179" s="6"/>
-      <c r="E1179" s="6"/>
+      <c r="A1179" s="12" t="s">
+        <v>2831</v>
+      </c>
+      <c r="B1179" s="13" t="s">
+        <v>2832</v>
+      </c>
+      <c r="C1179" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1179, ""en"", ""ta"")"),"வாகனப் புகைப்படங்கள் — பயணத்திற்கு முன்")</f>
+        <v>வாகனப் புகைப்படங்கள் — பயணத்திற்கு முன்</v>
+      </c>
+      <c r="D1179" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1179, ""en"", ""hi"")"),"यात्रा से पहले वाहन की तस्वीरें")</f>
+        <v>यात्रा से पहले वाहन की तस्वीरें</v>
+      </c>
+      <c r="E1179" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1179, ""en"", ""kn"")"),"ವಾಹನದ ಫೋಟೋಗಳು — ಪ್ರಯಾಣಕ್ಕೂ ಮುನ್ನ")</f>
+        <v>ವಾಹನದ ಫೋಟೋಗಳು — ಪ್ರಯಾಣಕ್ಕೂ ಮುನ್ನ</v>
+      </c>
+      <c r="F1179" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1179, ""en"", ""ml"")"),"വാഹന ഫോട്ടോകൾ — യാത്രയ്ക്ക് മുമ്പ്")</f>
+        <v>വാഹന ഫോട്ടോകൾ — യാത്രയ്ക്ക് മുമ്പ്</v>
+      </c>
+      <c r="G1179" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1179, ""en"", ""te"")"),"వాహన ఫోటోలు — ప్రయాణానికి ముందు")</f>
+        <v>వాహన ఫోటోలు — ప్రయాణానికి ముందు</v>
+      </c>
     </row>
     <row r="1180">
-      <c r="A1180" s="4"/>
-      <c r="B1180" s="5"/>
-      <c r="C1180" s="6"/>
-      <c r="D1180" s="6"/>
-      <c r="E1180" s="6"/>
+      <c r="A1180" s="12" t="s">
+        <v>2833</v>
+      </c>
+      <c r="B1180" s="13" t="s">
+        <v>2834</v>
+      </c>
+      <c r="C1180" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1180, ""en"", ""ta"")"),"தொடங்குவதற்கு முன் நான்கு கோணங்களையும் படம்பிடியுங்கள்.")</f>
+        <v>தொடங்குவதற்கு முன் நான்கு கோணங்களையும் படம்பிடியுங்கள்.</v>
+      </c>
+      <c r="D1180" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1180, ""en"", ""hi"")"),"शुरू करने से पहले चारों कोणों से तस्वीर खींच लें।")</f>
+        <v>शुरू करने से पहले चारों कोणों से तस्वीर खींच लें।</v>
+      </c>
+      <c r="E1180" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1180, ""en"", ""kn"")"),"ನೀವು ಪ್ರಾರಂಭಿಸುವ ಮೊದಲು ಎಲ್ಲಾ 4 ಕೋನಗಳನ್ನು ಸೆರೆಹಿಡಿಯಿರಿ")</f>
+        <v>ನೀವು ಪ್ರಾರಂಭಿಸುವ ಮೊದಲು ಎಲ್ಲಾ 4 ಕೋನಗಳನ್ನು ಸೆರೆಹಿಡಿಯಿರಿ</v>
+      </c>
+      <c r="F1180" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1180, ""en"", ""ml"")"),"ആരംഭിക്കുന്നതിന് മുമ്പ് 4 കോണുകളും പകർത്തുക")</f>
+        <v>ആരംഭിക്കുന്നതിന് മുമ്പ് 4 കോണുകളും പകർത്തുക</v>
+      </c>
+      <c r="G1180" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1180, ""en"", ""te"")"),"మీరు ప్రారంభించే ముందు నాలుగు కోణాలనూ చిత్రీకరించండి")</f>
+        <v>మీరు ప్రారంభించే ముందు నాలుగు కోణాలనూ చిత్రీకరించండి</v>
+      </c>
     </row>
     <row r="1181">
-      <c r="A1181" s="4"/>
-      <c r="B1181" s="5"/>
-      <c r="C1181" s="6"/>
-      <c r="D1181" s="6"/>
-      <c r="E1181" s="6"/>
+      <c r="A1181" s="12" t="s">
+        <v>2835</v>
+      </c>
+      <c r="B1181" s="13" t="s">
+        <v>2836</v>
+      </c>
+      <c r="C1181" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1181, ""en"", ""ta"")"),"புகைப்படங்கள் தேவை")</f>
+        <v>புகைப்படங்கள் தேவை</v>
+      </c>
+      <c r="D1181" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1181, ""en"", ""hi"")"),"फ़ोटो आवश्यक हैं")</f>
+        <v>फ़ोटो आवश्यक हैं</v>
+      </c>
+      <c r="E1181" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1181, ""en"", ""kn"")"),"ಫೋಟೋಗಳು ಅಗತ್ಯವಿದೆ")</f>
+        <v>ಫೋಟೋಗಳು ಅಗತ್ಯವಿದೆ</v>
+      </c>
+      <c r="F1181" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1181, ""en"", ""ml"")"),"ഫോട്ടോകൾ ആവശ്യമാണ്")</f>
+        <v>ഫോട്ടോകൾ ആവശ്യമാണ്</v>
+      </c>
+      <c r="G1181" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1181, ""en"", ""te"")"),"ఫోటోలు అవసరం")</f>
+        <v>ఫోటోలు అవసరం</v>
+      </c>
     </row>
     <row r="1182">
-      <c r="A1182" s="4"/>
-      <c r="B1182" s="5"/>
-      <c r="C1182" s="6"/>
-      <c r="D1182" s="6"/>
-      <c r="E1182" s="6"/>
+      <c r="A1182" s="12" t="s">
+        <v>2837</v>
+      </c>
+      <c r="B1182" s="13" t="s">
+        <v>2838</v>
+      </c>
+      <c r="C1182" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1182, ""en"", ""ta"")"),"தொடங்குவதற்கு முன், வாகனத்தின் நான்கு புகைப்படங்களையும் எடுத்துக் கொள்ளவும்.")</f>
+        <v>தொடங்குவதற்கு முன், வாகனத்தின் நான்கு புகைப்படங்களையும் எடுத்துக் கொள்ளவும்.</v>
+      </c>
+      <c r="D1182" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1182, ""en"", ""hi"")"),"कृपया शुरू करने से पहले चारों वाहनों की तस्वीरें खींच लें।")</f>
+        <v>कृपया शुरू करने से पहले चारों वाहनों की तस्वीरें खींच लें।</v>
+      </c>
+      <c r="E1182" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1182, ""en"", ""kn"")"),"ದಯವಿಟ್ಟು ಪ್ರಾರಂಭಿಸುವ ಮೊದಲು ಎಲ್ಲಾ 4 ವಾಹನಗಳ ಫೋಟೋಗಳನ್ನು ಸೆರೆಹಿಡಿಯಿರಿ.")</f>
+        <v>ದಯವಿಟ್ಟು ಪ್ರಾರಂಭಿಸುವ ಮೊದಲು ಎಲ್ಲಾ 4 ವಾಹನಗಳ ಫೋಟೋಗಳನ್ನು ಸೆರೆಹಿಡಿಯಿರಿ.</v>
+      </c>
+      <c r="F1182" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1182, ""en"", ""ml"")"),"യാത്ര ആരംഭിക്കുന്നതിന് മുമ്പ് 4 വാഹനങ്ങളുടെയും ഫോട്ടോകൾ എടുക്കുക.")</f>
+        <v>യാത്ര ആരംഭിക്കുന്നതിന് മുമ്പ് 4 വാഹനങ്ങളുടെയും ഫോട്ടോകൾ എടുക്കുക.</v>
+      </c>
+      <c r="G1182" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1182, ""en"", ""te"")"),"దయచేసి ప్రారంభించే ముందు 4 వాహనాల ఫోటోలను తీయండి.")</f>
+        <v>దయచేసి ప్రారంభించే ముందు 4 వాహనాల ఫోటోలను తీయండి.</v>
+      </c>
     </row>
     <row r="1183">
-      <c r="A1183" s="4"/>
-      <c r="B1183" s="5"/>
-      <c r="C1183" s="6"/>
-      <c r="D1183" s="6"/>
-      <c r="E1183" s="6"/>
+      <c r="A1183" s="12" t="s">
+        <v>2839</v>
+      </c>
+      <c r="B1183" s="13" t="s">
+        <v>2840</v>
+      </c>
+      <c r="C1183" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1183, ""en"", ""ta"")"),"வாகன புகைப்படங்கள்")</f>
+        <v>வாகன புகைப்படங்கள்</v>
+      </c>
+      <c r="D1183" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1183, ""en"", ""hi"")"),"वाहन की तस्वीरें")</f>
+        <v>वाहन की तस्वीरें</v>
+      </c>
+      <c r="E1183" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1183, ""en"", ""kn"")"),"ವಾಹನ ಫೋಟೋಗಳು")</f>
+        <v>ವಾಹನ ಫೋಟೋಗಳು</v>
+      </c>
+      <c r="F1183" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1183, ""en"", ""ml"")"),"വാഹന ഫോട്ടോകൾ")</f>
+        <v>വാഹന ഫോട്ടോകൾ</v>
+      </c>
+      <c r="G1183" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1183, ""en"", ""te"")"),"వాహన ఫోటోలు")</f>
+        <v>వాహన ఫోటోలు</v>
+      </c>
     </row>
     <row r="1184">
-      <c r="A1184" s="4"/>
-      <c r="B1184" s="5"/>
-      <c r="C1184" s="6"/>
-      <c r="D1184" s="6"/>
-      <c r="E1184" s="6"/>
+      <c r="A1184" s="12" t="s">
+        <v>2841</v>
+      </c>
+      <c r="B1184" s="13" t="s">
+        <v>2842</v>
+      </c>
+      <c r="C1184" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1184, ""en"", ""ta"")"),"பயணத்திற்கு முன்னும் பின்னும் எடுத்த புகைப்படங்களைப் பதிவேற்றவும்")</f>
+        <v>பயணத்திற்கு முன்னும் பின்னும் எடுத்த புகைப்படங்களைப் பதிவேற்றவும்</v>
+      </c>
+      <c r="D1184" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1184, ""en"", ""hi"")"),"यात्रा से पहले और बाद की तस्वीरें अपलोड करें")</f>
+        <v>यात्रा से पहले और बाद की तस्वीरें अपलोड करें</v>
+      </c>
+      <c r="E1184" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1184, ""en"", ""kn"")"),"ಪ್ರವಾಸದ ಮೊದಲು ಮತ್ತು ನಂತರದ ಫೋಟೋಗಳನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ")</f>
+        <v>ಪ್ರವಾಸದ ಮೊದಲು ಮತ್ತು ನಂತರದ ಫೋಟೋಗಳನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ</v>
+      </c>
+      <c r="F1184" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1184, ""en"", ""ml"")"),"യാത്രയ്ക്ക് മുമ്പും ശേഷവുമുള്ള ഫോട്ടോകൾ അപ്‌ലോഡ് ചെയ്യുക")</f>
+        <v>യാത്രയ്ക്ക് മുമ്പും ശേഷവുമുള്ള ഫോട്ടോകൾ അപ്‌ലോഡ് ചെയ്യുക</v>
+      </c>
+      <c r="G1184" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1184, ""en"", ""te"")"),"ప్రయాణానికి ముందు మరియు తర్వాత ఫోటోలను అప్‌లోడ్ చేయండి")</f>
+        <v>ప్రయాణానికి ముందు మరియు తర్వాత ఫోటోలను అప్‌లోడ్ చేయండి</v>
+      </c>
     </row>
     <row r="1185">
-      <c r="A1185" s="4"/>
-      <c r="B1185" s="5"/>
-      <c r="C1185" s="6"/>
-      <c r="D1185" s="6"/>
-      <c r="E1185" s="6"/>
+      <c r="A1185" s="12" t="s">
+        <v>2843</v>
+      </c>
+      <c r="B1185" s="13" t="s">
+        <v>2843</v>
+      </c>
+      <c r="C1185" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1185, ""en"", ""ta"")"),"பதிவேற்றப்பட்டது")</f>
+        <v>பதிவேற்றப்பட்டது</v>
+      </c>
+      <c r="D1185" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1185, ""en"", ""hi"")"),"अपलोड किए गए")</f>
+        <v>अपलोड किए गए</v>
+      </c>
+      <c r="E1185" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1185, ""en"", ""kn"")"),"ಅಪ್‌ಲೋಡ್ ಮಾಡಲಾಗಿದೆ")</f>
+        <v>ಅಪ್‌ಲೋಡ್ ಮಾಡಲಾಗಿದೆ</v>
+      </c>
+      <c r="F1185" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1185, ""en"", ""ml"")"),"അപ്‌ലോഡ് ചെയ്‌തു")</f>
+        <v>അപ്‌ലോഡ് ചെയ്‌തു</v>
+      </c>
+      <c r="G1185" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1185, ""en"", ""te"")"),"అప్‌లోడ్ చేయబడింది")</f>
+        <v>అప్‌లోడ్ చేయబడింది</v>
+      </c>
     </row>
     <row r="1186">
-      <c r="A1186" s="4"/>
-      <c r="B1186" s="5"/>
-      <c r="C1186" s="6"/>
-      <c r="D1186" s="6"/>
-      <c r="E1186" s="6"/>
+      <c r="A1186" s="12" t="s">
+        <v>2844</v>
+      </c>
+      <c r="B1186" s="13" t="s">
+        <v>2845</v>
+      </c>
+      <c r="C1186" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1186, ""en"", ""ta"")"),"பயணத்திற்கு முந்தைய புகைப்படங்கள்")</f>
+        <v>பயணத்திற்கு முந்தைய புகைப்படங்கள்</v>
+      </c>
+      <c r="D1186" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1186, ""en"", ""hi"")"),"यात्रा से पहले की तस्वीरें")</f>
+        <v>यात्रा से पहले की तस्वीरें</v>
+      </c>
+      <c r="E1186" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1186, ""en"", ""kn"")"),"ಪ್ರವಾಸ ಪೂರ್ವ ಫೋಟೋಗಳು")</f>
+        <v>ಪ್ರವಾಸ ಪೂರ್ವ ಫೋಟೋಗಳು</v>
+      </c>
+      <c r="F1186" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1186, ""en"", ""ml"")"),"യാത്രയ്ക്ക് മുമ്പുള്ള ഫോട്ടോകൾ")</f>
+        <v>യാത്രയ്ക്ക് മുമ്പുള്ള ഫോട്ടോകൾ</v>
+      </c>
+      <c r="G1186" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1186, ""en"", ""te"")"),"ప్రయాణానికి ముందు ఫోటోలు")</f>
+        <v>ప్రయాణానికి ముందు ఫోటోలు</v>
+      </c>
     </row>
     <row r="1187">
-      <c r="A1187" s="4"/>
-      <c r="B1187" s="5"/>
-      <c r="C1187" s="6"/>
-      <c r="D1187" s="6"/>
-      <c r="E1187" s="6"/>
+      <c r="A1187" s="24" t="s">
+        <v>2846</v>
+      </c>
+      <c r="B1187" s="13" t="s">
+        <v>2847</v>
+      </c>
+      <c r="C1187" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1187, ""en"", ""ta"")"),"முன்")</f>
+        <v>முன்</v>
+      </c>
+      <c r="D1187" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1187, ""en"", ""hi"")"),"सामने")</f>
+        <v>सामने</v>
+      </c>
+      <c r="E1187" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1187, ""en"", ""kn"")"),"ಮುಂಭಾಗ")</f>
+        <v>ಮುಂಭಾಗ</v>
+      </c>
+      <c r="F1187" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1187, ""en"", ""ml"")"),"ഫ്രണ്ട്")</f>
+        <v>ഫ്രണ്ട്</v>
+      </c>
+      <c r="G1187" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1187, ""en"", ""te"")"),"ముందు")</f>
+        <v>ముందు</v>
+      </c>
     </row>
     <row r="1188">
-      <c r="A1188" s="4"/>
-      <c r="B1188" s="5"/>
-      <c r="C1188" s="6"/>
-      <c r="D1188" s="6"/>
-      <c r="E1188" s="6"/>
+      <c r="A1188" s="24" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B1188" s="13" t="s">
+        <v>2849</v>
+      </c>
+      <c r="C1188" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1188, ""en"", ""ta"")"),"பின்புறம்")</f>
+        <v>பின்புறம்</v>
+      </c>
+      <c r="D1188" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1188, ""en"", ""hi"")"),"पिछला")</f>
+        <v>पिछला</v>
+      </c>
+      <c r="E1188" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1188, ""en"", ""kn"")"),"ಹಿಂಭಾಗ")</f>
+        <v>ಹಿಂಭಾಗ</v>
+      </c>
+      <c r="F1188" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1188, ""en"", ""ml"")"),"പിൻഭാഗം")</f>
+        <v>പിൻഭാഗം</v>
+      </c>
+      <c r="G1188" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1188, ""en"", ""te"")"),"వెనుక")</f>
+        <v>వెనుక</v>
+      </c>
     </row>
     <row r="1189">
-      <c r="A1189" s="4"/>
-      <c r="B1189" s="5"/>
-      <c r="C1189" s="6"/>
-      <c r="D1189" s="6"/>
-      <c r="E1189" s="6"/>
+      <c r="A1189" s="24" t="s">
+        <v>2850</v>
+      </c>
+      <c r="B1189" s="13" t="s">
+        <v>2851</v>
+      </c>
+      <c r="C1189" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1189, ""en"", ""ta"")"),"இடது பக்கம்")</f>
+        <v>இடது பக்கம்</v>
+      </c>
+      <c r="D1189" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1189, ""en"", ""hi"")"),"बाईं तरफ")</f>
+        <v>बाईं तरफ</v>
+      </c>
+      <c r="E1189" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1189, ""en"", ""kn"")"),"ಎಡಭಾಗ")</f>
+        <v>ಎಡಭಾಗ</v>
+      </c>
+      <c r="F1189" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1189, ""en"", ""ml"")"),"ഇടതുവശം")</f>
+        <v>ഇടതുവശം</v>
+      </c>
+      <c r="G1189" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1189, ""en"", ""te"")"),"ఎడమ వైపు")</f>
+        <v>ఎడమ వైపు</v>
+      </c>
     </row>
     <row r="1190">
-      <c r="A1190" s="4"/>
-      <c r="B1190" s="5"/>
-      <c r="C1190" s="6"/>
-      <c r="D1190" s="6"/>
-      <c r="E1190" s="6"/>
+      <c r="A1190" s="24" t="s">
+        <v>2852</v>
+      </c>
+      <c r="B1190" s="13" t="s">
+        <v>2853</v>
+      </c>
+      <c r="C1190" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1190, ""en"", ""ta"")"),"வலது பக்கம்")</f>
+        <v>வலது பக்கம்</v>
+      </c>
+      <c r="D1190" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1190, ""en"", ""hi"")"),"दाहिनी ओर")</f>
+        <v>दाहिनी ओर</v>
+      </c>
+      <c r="E1190" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1190, ""en"", ""kn"")"),"ಬಲಭಾಗ")</f>
+        <v>ಬಲಭಾಗ</v>
+      </c>
+      <c r="F1190" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1190, ""en"", ""ml"")"),"വലതുവശം")</f>
+        <v>വലതുവശം</v>
+      </c>
+      <c r="G1190" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1190, ""en"", ""te"")"),"కుడి వైపు")</f>
+        <v>కుడి వైపు</v>
+      </c>
     </row>
     <row r="1191">
-      <c r="A1191" s="4"/>
-      <c r="B1191" s="5"/>
-      <c r="C1191" s="6"/>
-      <c r="D1191" s="6"/>
-      <c r="E1191" s="6"/>
+      <c r="A1191" s="12" t="s">
+        <v>2854</v>
+      </c>
+      <c r="B1191" s="13" t="s">
+        <v>2855</v>
+      </c>
+      <c r="C1191" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1191, ""en"", ""ta"")"),"பயணத்திற்கு முந்தைய பதிவை மீண்டும் பதிவேற்றவும்")</f>
+        <v>பயணத்திற்கு முந்தைய பதிவை மீண்டும் பதிவேற்றவும்</v>
+      </c>
+      <c r="D1191" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1191, ""en"", ""hi"")"),"यात्रा से पहले की सामग्री दोबारा अपलोड करें")</f>
+        <v>यात्रा से पहले की सामग्री दोबारा अपलोड करें</v>
+      </c>
+      <c r="E1191" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1191, ""en"", ""kn"")"),"ಪೂರ್ವ-ಪ್ರವಾಸವನ್ನು ಮರು-ಅಪ್‌ಲೋಡ್ ಮಾಡಿ")</f>
+        <v>ಪೂರ್ವ-ಪ್ರವಾಸವನ್ನು ಮರು-ಅಪ್‌ಲೋಡ್ ಮಾಡಿ</v>
+      </c>
+      <c r="F1191" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1191, ""en"", ""ml"")"),"യാത്രയ്ക്ക് മുമ്പുള്ള വിവരങ്ങൾ വീണ്ടും അപ്‌ലോഡ് ചെയ്യുക")</f>
+        <v>യാത്രയ്ക്ക് മുമ്പുള്ള വിവരങ്ങൾ വീണ്ടും അപ്‌ലോഡ് ചെയ്യുക</v>
+      </c>
+      <c r="G1191" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1191, ""en"", ""te"")"),"ప్రయాణానికి ముందు మళ్లీ అప్‌లోడ్ చేయండి")</f>
+        <v>ప్రయాణానికి ముందు మళ్లీ అప్‌లోడ్ చేయండి</v>
+      </c>
     </row>
     <row r="1192">
-      <c r="A1192" s="4"/>
-      <c r="B1192" s="5"/>
-      <c r="C1192" s="6"/>
-      <c r="D1192" s="6"/>
-      <c r="E1192" s="6"/>
+      <c r="A1192" s="12" t="s">
+        <v>2856</v>
+      </c>
+      <c r="B1192" s="13" t="s">
+        <v>2857</v>
+      </c>
+      <c r="C1192" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1192, ""en"", ""ta"")"),"பயணத்திற்கு முந்தைய புகைப்படங்களைப் பதிவேற்றவும்")</f>
+        <v>பயணத்திற்கு முந்தைய புகைப்படங்களைப் பதிவேற்றவும்</v>
+      </c>
+      <c r="D1192" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1192, ""en"", ""hi"")"),"यात्रा से पहले की तस्वीरें अपलोड करें")</f>
+        <v>यात्रा से पहले की तस्वीरें अपलोड करें</v>
+      </c>
+      <c r="E1192" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1192, ""en"", ""kn"")"),"ಪ್ರವಾಸ ಪೂರ್ವ ಫೋಟೋಗಳನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ")</f>
+        <v>ಪ್ರವಾಸ ಪೂರ್ವ ಫೋಟೋಗಳನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ</v>
+      </c>
+      <c r="F1192" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1192, ""en"", ""ml"")"),"യാത്രയ്ക്ക് മുമ്പുള്ള ഫോട്ടോകൾ അപ്‌ലോഡ് ചെയ്യുക")</f>
+        <v>യാത്രയ്ക്ക് മുമ്പുള്ള ഫോട്ടോകൾ അപ്‌ലോഡ് ചെയ്യുക</v>
+      </c>
+      <c r="G1192" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1192, ""en"", ""te"")"),"ప్రయాణానికి ముందు ఫోటోలను అప్‌లోడ్ చేయండి")</f>
+        <v>ప్రయాణానికి ముందు ఫోటోలను అప్‌లోడ్ చేయండి</v>
+      </c>
     </row>
     <row r="1193">
-      <c r="A1193" s="4"/>
-      <c r="B1193" s="5"/>
-      <c r="C1193" s="6"/>
-      <c r="D1193" s="6"/>
-      <c r="E1193" s="6"/>
+      <c r="A1193" s="23" t="s">
+        <v>2858</v>
+      </c>
+      <c r="B1193" s="13" t="s">
+        <v>2859</v>
+      </c>
+      <c r="C1193" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1193, ""en"", ""ta"")"),"பயணத்திற்குப் பிறகு மீண்டும் பதிவேற்றவும்")</f>
+        <v>பயணத்திற்குப் பிறகு மீண்டும் பதிவேற்றவும்</v>
+      </c>
+      <c r="D1193" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1193, ""en"", ""hi"")"),"यात्रा के बाद पुनः अपलोड करें")</f>
+        <v>यात्रा के बाद पुनः अपलोड करें</v>
+      </c>
+      <c r="E1193" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1193, ""en"", ""kn"")"),"ಪ್ರವಾಸದ ನಂತರದ ಮಾಹಿತಿಯನ್ನು ಮರು-ಅಪ್‌ಲೋಡ್ ಮಾಡಿ")</f>
+        <v>ಪ್ರವಾಸದ ನಂತರದ ಮಾಹಿತಿಯನ್ನು ಮರು-ಅಪ್‌ಲೋಡ್ ಮಾಡಿ</v>
+      </c>
+      <c r="F1193" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1193, ""en"", ""ml"")"),"യാത്രയ്ക്ക് ശേഷമുള്ള വിവരങ്ങൾ വീണ്ടും അപ്‌ലോഡ് ചെയ്യുക")</f>
+        <v>യാത്രയ്ക്ക് ശേഷമുള്ള വിവരങ്ങൾ വീണ്ടും അപ്‌ലോഡ് ചെയ്യുക</v>
+      </c>
+      <c r="G1193" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1193, ""en"", ""te"")"),"ప్రయాణం తర్వాత మళ్లీ అప్‌లోడ్ చేయండి")</f>
+        <v>ప్రయాణం తర్వాత మళ్లీ అప్‌లోడ్ చేయండి</v>
+      </c>
     </row>
     <row r="1194">
-      <c r="A1194" s="4"/>
-      <c r="B1194" s="5"/>
-      <c r="C1194" s="6"/>
-      <c r="D1194" s="6"/>
-      <c r="E1194" s="6"/>
+      <c r="A1194" s="12" t="s">
+        <v>2860</v>
+      </c>
+      <c r="B1194" s="13" t="s">
+        <v>2861</v>
+      </c>
+      <c r="C1194" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1194, ""en"", ""ta"")"),"பயணத்திற்குப் பிந்தைய புகைப்படங்களைப் பதிவேற்றவும்")</f>
+        <v>பயணத்திற்குப் பிந்தைய புகைப்படங்களைப் பதிவேற்றவும்</v>
+      </c>
+      <c r="D1194" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1194, ""en"", ""hi"")"),"यात्रा के बाद की तस्वीरें अपलोड करें")</f>
+        <v>यात्रा के बाद की तस्वीरें अपलोड करें</v>
+      </c>
+      <c r="E1194" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1194, ""en"", ""kn"")"),"ಪ್ರವಾಸದ ನಂತರದ ಫೋಟೋಗಳನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ")</f>
+        <v>ಪ್ರವಾಸದ ನಂತರದ ಫೋಟೋಗಳನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ</v>
+      </c>
+      <c r="F1194" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1194, ""en"", ""ml"")"),"യാത്രയ്ക്കു ശേഷമുള്ള ഫോട്ടോകൾ അപ്‌ലോഡ് ചെയ്യുക")</f>
+        <v>യാത്രയ്ക്കു ശേഷമുള്ള ഫോട്ടോകൾ അപ്‌ലോഡ് ചെയ്യുക</v>
+      </c>
+      <c r="G1194" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1194, ""en"", ""te"")"),"యాత్ర తర్వాత తీసిన ఫోటోలను అప్‌లోడ్ చేయండి")</f>
+        <v>యాత్ర తర్వాత తీసిన ఫోటోలను అప్‌లోడ్ చేయండి</v>
+      </c>
     </row>
     <row r="1195">
-      <c r="A1195" s="4"/>
-      <c r="B1195" s="5"/>
-      <c r="C1195" s="6"/>
-      <c r="D1195" s="6"/>
-      <c r="E1195" s="6"/>
+      <c r="A1195" s="12" t="s">
+        <v>2862</v>
+      </c>
+      <c r="B1195" s="13" t="s">
+        <v>2863</v>
+      </c>
+      <c r="C1195" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1195, ""en"", ""ta"")"),"கட்டணங்கள் மற்றும் செலவுகள்")</f>
+        <v>கட்டணங்கள் மற்றும் செலவுகள்</v>
+      </c>
+      <c r="D1195" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1195, ""en"", ""hi"")"),"बिल और खर्च")</f>
+        <v>बिल और खर्च</v>
+      </c>
+      <c r="E1195" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1195, ""en"", ""kn"")"),"ಬಿಲ್‌ಗಳು ಮತ್ತು ವೆಚ್ಚಗಳು")</f>
+        <v>ಬಿಲ್‌ಗಳು ಮತ್ತು ವೆಚ್ಚಗಳು</v>
+      </c>
+      <c r="F1195" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1195, ""en"", ""ml"")"),"ബില്ലുകളും ചെലവുകളും")</f>
+        <v>ബില്ലുകളും ചെലവുകളും</v>
+      </c>
+      <c r="G1195" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1195, ""en"", ""te"")"),"బిల్లులు &amp; ఖర్చులు")</f>
+        <v>బిల్లులు &amp; ఖర్చులు</v>
+      </c>
     </row>
     <row r="1196">
-      <c r="A1196" s="4"/>
-      <c r="B1196" s="5"/>
-      <c r="C1196" s="6"/>
-      <c r="D1196" s="6"/>
-      <c r="E1196" s="6"/>
+      <c r="A1196" s="12" t="s">
+        <v>2864</v>
+      </c>
+      <c r="B1196" s="13" t="s">
+        <v>2865</v>
+      </c>
+      <c r="C1196" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1196, ""en"", ""ta"")"),"பயணச் செலவுகள் மற்றும் ரசீதுகளைச் சேர்க்கவும்")</f>
+        <v>பயணச் செலவுகள் மற்றும் ரசீதுகளைச் சேர்க்கவும்</v>
+      </c>
+      <c r="D1196" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1196, ""en"", ""hi"")"),"यात्रा के खर्च और रसीदें जोड़ें")</f>
+        <v>यात्रा के खर्च और रसीदें जोड़ें</v>
+      </c>
+      <c r="E1196" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1196, ""en"", ""kn"")"),"ಪ್ರವಾಸ ವೆಚ್ಚಗಳು ಮತ್ತು ರಸೀದಿಗಳನ್ನು ಸೇರಿಸಿ")</f>
+        <v>ಪ್ರವಾಸ ವೆಚ್ಚಗಳು ಮತ್ತು ರಸೀದಿಗಳನ್ನು ಸೇರಿಸಿ</v>
+      </c>
+      <c r="F1196" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1196, ""en"", ""ml"")"),"യാത്രാ ചെലവുകളും രസീതുകളും ചേർക്കുക")</f>
+        <v>യാത്രാ ചെലവുകളും രസീതുകളും ചേർക്കുക</v>
+      </c>
+      <c r="G1196" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1196, ""en"", ""te"")"),"ప్రయాణ ఖర్చులు మరియు రసీదులను జోడించండి")</f>
+        <v>ప్రయాణ ఖర్చులు మరియు రసీదులను జోడించండి</v>
+      </c>
     </row>
     <row r="1197">
-      <c r="A1197" s="4"/>
-      <c r="B1197" s="5"/>
-      <c r="C1197" s="6"/>
-      <c r="D1197" s="6"/>
-      <c r="E1197" s="6"/>
+      <c r="A1197" s="12" t="s">
+        <v>2866</v>
+      </c>
+      <c r="B1197" s="13" t="s">
+        <v>2867</v>
+      </c>
+      <c r="C1197" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1197, ""en"", ""ta"")"),"இதுவரை மசோதாக்கள் எதுவும் சேர்க்கப்படவில்லை")</f>
+        <v>இதுவரை மசோதாக்கள் எதுவும் சேர்க்கப்படவில்லை</v>
+      </c>
+      <c r="D1197" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1197, ""en"", ""hi"")"),"अभी तक कोई बिल नहीं जोड़ा गया है")</f>
+        <v>अभी तक कोई बिल नहीं जोड़ा गया है</v>
+      </c>
+      <c r="E1197" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1197, ""en"", ""kn"")"),"ಇನ್ನೂ ಯಾವುದೇ ಬಿಲ್‌ಗಳನ್ನು ಸೇರಿಸಲಾಗಿಲ್ಲ.")</f>
+        <v>ಇನ್ನೂ ಯಾವುದೇ ಬಿಲ್‌ಗಳನ್ನು ಸೇರಿಸಲಾಗಿಲ್ಲ.</v>
+      </c>
+      <c r="F1197" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1197, ""en"", ""ml"")"),"ഇതുവരെ ബില്ലുകളൊന്നും ചേർത്തിട്ടില്ല.")</f>
+        <v>ഇതുവരെ ബില്ലുകളൊന്നും ചേർത്തിട്ടില്ല.</v>
+      </c>
+      <c r="G1197" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1197, ""en"", ""te"")"),"ఇంకా బిల్లులు జోడించబడలేదు")</f>
+        <v>ఇంకా బిల్లులు జోడించబడలేదు</v>
+      </c>
     </row>
     <row r="1198">
-      <c r="A1198" s="4"/>
-      <c r="B1198" s="5"/>
-      <c r="C1198" s="6"/>
-      <c r="D1198" s="6"/>
-      <c r="E1198" s="6"/>
+      <c r="A1198" s="12" t="s">
+        <v>2868</v>
+      </c>
+      <c r="B1198" s="13" t="s">
+        <v>2869</v>
+      </c>
+      <c r="C1198" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1198, ""en"", ""ta"")"),"ஒரு செலவைப் பதிவு செய்ய, கீழே உள்ள 'பில் சேர்க்கவும்' என்பதைத் தட்டவும்.")</f>
+        <v>ஒரு செலவைப் பதிவு செய்ய, கீழே உள்ள 'பில் சேர்க்கவும்' என்பதைத் தட்டவும்.</v>
+      </c>
+      <c r="D1198" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1198, ""en"", ""hi"")"),"खर्च दर्ज करने के लिए नीचे ""बिल जोड़ें"" पर टैप करें")</f>
+        <v>खर्च दर्ज करने के लिए नीचे "बिल जोड़ें" पर टैप करें</v>
+      </c>
+      <c r="E1198" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1198, ""en"", ""kn"")"),"ವೆಚ್ಚವನ್ನು ದಾಖಲಿಸಲು ಕೆಳಗೆ ""ಬಿಲ್ ಸೇರಿಸಿ"" ಟ್ಯಾಪ್ ಮಾಡಿ")</f>
+        <v>ವೆಚ್ಚವನ್ನು ದಾಖಲಿಸಲು ಕೆಳಗೆ "ಬಿಲ್ ಸೇರಿಸಿ" ಟ್ಯಾಪ್ ಮಾಡಿ</v>
+      </c>
+      <c r="F1198" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1198, ""en"", ""ml"")"),"ചെലവ് രേഖപ്പെടുത്താൻ താഴെയുള്ള ""ബിൽ ചേർക്കുക"" ടാപ്പ് ചെയ്യുക.")</f>
+        <v>ചെലവ് രേഖപ്പെടുത്താൻ താഴെയുള്ള "ബിൽ ചേർക്കുക" ടാപ്പ് ചെയ്യുക.</v>
+      </c>
+      <c r="G1198" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1198, ""en"", ""te"")"),"ఖర్చును నమోదు చేయడానికి దిగువన ఉన్న 'బిల్లును జోడించు'ను నొక్కండి")</f>
+        <v>ఖర్చును నమోదు చేయడానికి దిగువన ఉన్న 'బిల్లును జోడించు'ను నొక్కండి</v>
+      </c>
     </row>
     <row r="1199">
-      <c r="A1199" s="4"/>
-      <c r="B1199" s="5"/>
-      <c r="C1199" s="6"/>
-      <c r="D1199" s="6"/>
-      <c r="E1199" s="6"/>
+      <c r="A1199" s="12" t="s">
+        <v>2870</v>
+      </c>
+      <c r="B1199" s="13" t="s">
+        <v>2871</v>
+      </c>
+      <c r="C1199" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1199, ""en"", ""ta"")"),"பில்")</f>
+        <v>பில்</v>
+      </c>
+      <c r="D1199" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1199, ""en"", ""hi"")"),"बिल")</f>
+        <v>बिल</v>
+      </c>
+      <c r="E1199" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1199, ""en"", ""kn"")"),"ಬಿಲ್")</f>
+        <v>ಬಿಲ್</v>
+      </c>
+      <c r="F1199" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1199, ""en"", ""ml"")"),"ബിൽ")</f>
+        <v>ബിൽ</v>
+      </c>
+      <c r="G1199" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1199, ""en"", ""te"")"),"బిల్")</f>
+        <v>బిల్</v>
+      </c>
     </row>
     <row r="1200">
-      <c r="A1200" s="4"/>
-      <c r="B1200" s="5"/>
-      <c r="C1200" s="6"/>
-      <c r="D1200" s="6"/>
-      <c r="E1200" s="6"/>
+      <c r="A1200" s="12" t="s">
+        <v>2872</v>
+      </c>
+      <c r="B1200" s="13" t="s">
+        <v>2873</v>
+      </c>
+      <c r="C1200" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1200, ""en"", ""ta"")"),"சேர்க்கப்பட்டது")</f>
+        <v>சேர்க்கப்பட்டது</v>
+      </c>
+      <c r="D1200" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1200, ""en"", ""hi"")"),"जोड़ा")</f>
+        <v>जोड़ा</v>
+      </c>
+      <c r="E1200" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1200, ""en"", ""kn"")"),"ಸೇರಿಸಲಾಗಿದೆ")</f>
+        <v>ಸೇರಿಸಲಾಗಿದೆ</v>
+      </c>
+      <c r="F1200" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1200, ""en"", ""ml"")"),"ചേർത്തു")</f>
+        <v>ചേർത്തു</v>
+      </c>
+      <c r="G1200" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1200, ""en"", ""te"")"),"జోడించబడింది")</f>
+        <v>జోడించబడింది</v>
+      </c>
     </row>
     <row r="1201">
-      <c r="A1201" s="4"/>
-      <c r="B1201" s="5"/>
-      <c r="C1201" s="6"/>
-      <c r="D1201" s="6"/>
-      <c r="E1201" s="6"/>
+      <c r="A1201" s="12" t="s">
+        <v>2874</v>
+      </c>
+      <c r="B1201" s="13" t="s">
+        <v>2875</v>
+      </c>
+      <c r="C1201" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1201, ""en"", ""ta"")"),"பில்லைச் சேர்க்கவும்")</f>
+        <v>பில்லைச் சேர்க்கவும்</v>
+      </c>
+      <c r="D1201" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1201, ""en"", ""hi"")"),"बिल जोड़ें")</f>
+        <v>बिल जोड़ें</v>
+      </c>
+      <c r="E1201" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1201, ""en"", ""kn"")"),"ಬಿಲ್ ಸೇರಿಸಿ")</f>
+        <v>ಬಿಲ್ ಸೇರಿಸಿ</v>
+      </c>
+      <c r="F1201" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1201, ""en"", ""ml"")"),"ബിൽ ചേർക്കുക")</f>
+        <v>ബിൽ ചേർക്കുക</v>
+      </c>
+      <c r="G1201" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1201, ""en"", ""te"")"),"బిల్లును జోడించండి")</f>
+        <v>బిల్లును జోడించండి</v>
+      </c>
     </row>
     <row r="1202">
-      <c r="A1202" s="4"/>
-      <c r="B1202" s="5"/>
-      <c r="C1202" s="6"/>
-      <c r="D1202" s="6"/>
-      <c r="E1202" s="6"/>
+      <c r="A1202" s="12" t="s">
+        <v>2876</v>
+      </c>
+      <c r="B1202" s="13" t="s">
+        <v>2877</v>
+      </c>
+      <c r="C1202" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1202, ""en"", ""ta"")"),"பில் / செலவைச் சேர்க்கவும்")</f>
+        <v>பில் / செலவைச் சேர்க்கவும்</v>
+      </c>
+      <c r="D1202" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1202, ""en"", ""hi"")"),"बिल/खर्च जोड़ें")</f>
+        <v>बिल/खर्च जोड़ें</v>
+      </c>
+      <c r="E1202" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1202, ""en"", ""kn"")"),"ಬಿಲ್ / ವೆಚ್ಚವನ್ನು ಸೇರಿಸಿ")</f>
+        <v>ಬಿಲ್ / ವೆಚ್ಚವನ್ನು ಸೇರಿಸಿ</v>
+      </c>
+      <c r="F1202" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1202, ""en"", ""ml"")"),"ബിൽ / ചെലവ് ചേർക്കുക")</f>
+        <v>ബിൽ / ചെലവ് ചേർക്കുക</v>
+      </c>
+      <c r="G1202" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1202, ""en"", ""te"")"),"బిల్లు / ఖర్చును జోడించండి")</f>
+        <v>బిల్లు / ఖర్చును జోడించండి</v>
+      </c>
     </row>
     <row r="1203">
-      <c r="A1203" s="4"/>
-      <c r="B1203" s="5"/>
-      <c r="C1203" s="6"/>
-      <c r="D1203" s="6"/>
-      <c r="E1203" s="6"/>
+      <c r="A1203" s="12" t="s">
+        <v>2878</v>
+      </c>
+      <c r="B1203" s="13" t="s">
+        <v>2879</v>
+      </c>
+      <c r="C1203" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1203, ""en"", ""ta"")"),"உதாரணமாக எரிபொருள், சுங்கக் கட்டணம், வாகன நிறுத்தம்")</f>
+        <v>உதாரணமாக எரிபொருள், சுங்கக் கட்டணம், வாகன நிறுத்தம்</v>
+      </c>
+      <c r="D1203" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1203, ""en"", ""hi"")"),"उदाहरण के लिए: ईंधन, टोल, पार्किंग")</f>
+        <v>उदाहरण के लिए: ईंधन, टोल, पार्किंग</v>
+      </c>
+      <c r="E1203" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1203, ""en"", ""kn"")"),"ಉದಾ. ಇಂಧನ, ಟೋಲ್, ಪಾರ್ಕಿಂಗ್")</f>
+        <v>ಉದಾ. ಇಂಧನ, ಟೋಲ್, ಪಾರ್ಕಿಂಗ್</v>
+      </c>
+      <c r="F1203" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1203, ""en"", ""ml"")"),"ഉദാ. ഇന്ധനം, ടോൾ, പാർക്കിംഗ്")</f>
+        <v>ഉദാ. ഇന്ധനം, ടോൾ, പാർക്കിംഗ്</v>
+      </c>
+      <c r="G1203" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1203, ""en"", ""te"")"),"ఉదా. ఇంధనం, టోల్, పార్కింగ్")</f>
+        <v>ఉదా. ఇంధనం, టోల్, పార్కింగ్</v>
+      </c>
     </row>
     <row r="1204">
-      <c r="A1204" s="4"/>
-      <c r="B1204" s="5"/>
-      <c r="C1204" s="6"/>
-      <c r="D1204" s="6"/>
-      <c r="E1204" s="6"/>
+      <c r="A1204" s="12" t="s">
+        <v>463</v>
+      </c>
+      <c r="B1204" s="13" t="s">
+        <v>464</v>
+      </c>
+      <c r="C1204" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1204, ""en"", ""ta"")"),"தொகை")</f>
+        <v>தொகை</v>
+      </c>
+      <c r="D1204" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1204, ""en"", ""hi"")"),"मात्रा")</f>
+        <v>मात्रा</v>
+      </c>
+      <c r="E1204" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1204, ""en"", ""kn"")"),"ಮೊತ್ತ")</f>
+        <v>ಮೊತ್ತ</v>
+      </c>
+      <c r="F1204" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1204, ""en"", ""ml"")"),"തുക")</f>
+        <v>തുക</v>
+      </c>
+      <c r="G1204" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1204, ""en"", ""te"")"),"మొత్తం")</f>
+        <v>మొత్తం</v>
+      </c>
     </row>
     <row r="1205">
-      <c r="A1205" s="4"/>
-      <c r="B1205" s="5"/>
-      <c r="C1205" s="6"/>
-      <c r="D1205" s="6"/>
-      <c r="E1205" s="6"/>
+      <c r="A1205" s="12" t="s">
+        <v>2880</v>
+      </c>
+      <c r="B1205" s="13" t="s">
+        <v>2881</v>
+      </c>
+      <c r="C1205" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1205, ""en"", ""ta"")"),"ரசீது புகைப்படம்")</f>
+        <v>ரசீது புகைப்படம்</v>
+      </c>
+      <c r="D1205" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1205, ""en"", ""hi"")"),"रसीद की फोटो")</f>
+        <v>रसीद की फोटो</v>
+      </c>
+      <c r="E1205" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1205, ""en"", ""kn"")"),"ರಶೀದಿ ಫೋಟೋ")</f>
+        <v>ರಶೀದಿ ಫೋಟೋ</v>
+      </c>
+      <c r="F1205" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1205, ""en"", ""ml"")"),"രസീത് ഫോട്ടോ")</f>
+        <v>രസീത് ഫോട്ടോ</v>
+      </c>
+      <c r="G1205" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1205, ""en"", ""te"")"),"రసీదు ఫోటో")</f>
+        <v>రసీదు ఫోటో</v>
+      </c>
     </row>
     <row r="1206">
-      <c r="A1206" s="4"/>
-      <c r="B1206" s="5"/>
-      <c r="C1206" s="6"/>
-      <c r="D1206" s="6"/>
-      <c r="E1206" s="6"/>
+      <c r="A1206" s="12" t="s">
+        <v>2882</v>
+      </c>
+      <c r="B1206" s="13" t="s">
+        <v>2882</v>
+      </c>
+      <c r="C1206" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1206, ""en"", ""ta"")"),"விருப்பத்தேர்வு")</f>
+        <v>விருப்பத்தேர்வு</v>
+      </c>
+      <c r="D1206" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1206, ""en"", ""hi"")"),"वैकल्पिक")</f>
+        <v>वैकल्पिक</v>
+      </c>
+      <c r="E1206" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1206, ""en"", ""kn"")"),"ಐಚ್ಛಿಕ")</f>
+        <v>ಐಚ್ಛಿಕ</v>
+      </c>
+      <c r="F1206" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1206, ""en"", ""ml"")"),"ഓപ്ഷണൽ")</f>
+        <v>ഓപ്ഷണൽ</v>
+      </c>
+      <c r="G1206" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1206, ""en"", ""te"")"),"ఐచ్ఛికం")</f>
+        <v>ఐచ్ఛికం</v>
+      </c>
     </row>
     <row r="1207">
-      <c r="A1207" s="4"/>
-      <c r="B1207" s="5"/>
-      <c r="C1207" s="6"/>
-      <c r="D1207" s="6"/>
-      <c r="E1207" s="6"/>
+      <c r="A1207" s="12" t="s">
+        <v>2883</v>
+      </c>
+      <c r="B1207" s="13" t="s">
+        <v>2884</v>
+      </c>
+      <c r="C1207" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1207, ""en"", ""ta"")"),"சேர்ப்பது")</f>
+        <v>சேர்ப்பது</v>
+      </c>
+      <c r="D1207" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1207, ""en"", ""hi"")"),"जोड़ना")</f>
+        <v>जोड़ना</v>
+      </c>
+      <c r="E1207" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1207, ""en"", ""kn"")"),"ಸೇರಿಸುವುದು")</f>
+        <v>ಸೇರಿಸುವುದು</v>
+      </c>
+      <c r="F1207" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1207, ""en"", ""ml"")"),"ചേർക്കുന്നു")</f>
+        <v>ചേർക്കുന്നു</v>
+      </c>
+      <c r="G1207" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1207, ""en"", ""te"")"),"జోడింపు")</f>
+        <v>జోడింపు</v>
+      </c>
     </row>
     <row r="1208">
-      <c r="A1208" s="4"/>
-      <c r="B1208" s="5"/>
-      <c r="C1208" s="6"/>
-      <c r="D1208" s="6"/>
-      <c r="E1208" s="6"/>
+      <c r="A1208" s="12" t="s">
+        <v>2885</v>
+      </c>
+      <c r="B1208" s="25">
+        <v>99.99</v>
+      </c>
+      <c r="C1208" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1208, ""en"", ""ta"")"),"99.99")</f>
+        <v>99.99</v>
+      </c>
+      <c r="D1208" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1208, ""en"", ""hi"")"),"99.99")</f>
+        <v>99.99</v>
+      </c>
+      <c r="E1208" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1208, ""en"", ""kn"")"),"99.99 समान")</f>
+        <v>99.99 समान</v>
+      </c>
+      <c r="F1208" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1208, ""en"", ""ml"")"),"99.99 പിആർ")</f>
+        <v>99.99 പിആർ</v>
+      </c>
+      <c r="G1208" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1208, ""en"", ""te"")"),"99.99")</f>
+        <v>99.99</v>
+      </c>
     </row>
     <row r="1209">
-      <c r="A1209" s="4"/>
-      <c r="B1209" s="5"/>
-      <c r="C1209" s="6"/>
-      <c r="D1209" s="6"/>
-      <c r="E1209" s="6"/>
+      <c r="A1209" s="12" t="s">
+        <v>2886</v>
+      </c>
+      <c r="B1209" s="13" t="s">
+        <v>2887</v>
+      </c>
+      <c r="C1209" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1209, ""en"", ""ta"")"),"வாகனப் புகைப்படங்களைப் பதிவேற்றவும்")</f>
+        <v>வாகனப் புகைப்படங்களைப் பதிவேற்றவும்</v>
+      </c>
+      <c r="D1209" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1209, ""en"", ""hi"")"),"वाहन की तस्वीरें अपलोड करें")</f>
+        <v>वाहन की तस्वीरें अपलोड करें</v>
+      </c>
+      <c r="E1209" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1209, ""en"", ""kn"")"),"ವಾಹನ ಫೋಟೋಗಳನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ")</f>
+        <v>ವಾಹನ ಫೋಟೋಗಳನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ</v>
+      </c>
+      <c r="F1209" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1209, ""en"", ""ml"")"),"വാഹന ഫോട്ടോകൾ അപ്‌ലോഡ് ചെയ്യുക")</f>
+        <v>വാഹന ഫോട്ടോകൾ അപ്‌ലോഡ് ചെയ്യുക</v>
+      </c>
+      <c r="G1209" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1209, ""en"", ""te"")"),"వాహన ఫోటోలను అప్‌లోడ్ చేయండి")</f>
+        <v>వాహన ఫోటోలను అప్‌లోడ్ చేయండి</v>
+      </c>
     </row>
     <row r="1210">
-      <c r="A1210" s="4"/>
-      <c r="B1210" s="5"/>
-      <c r="C1210" s="6"/>
-      <c r="D1210" s="6"/>
-      <c r="E1210" s="6"/>
+      <c r="A1210" s="12" t="s">
+        <v>2888</v>
+      </c>
+      <c r="B1210" s="13" t="s">
+        <v>2889</v>
+      </c>
+      <c r="C1210" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1210, ""en"", ""ta"")"),"ரசீதுகள் மற்றும் செலவினங்களைப் பதிவேற்றவும்")</f>
+        <v>ரசீதுகள் மற்றும் செலவினங்களைப் பதிவேற்றவும்</v>
+      </c>
+      <c r="D1210" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1210, ""en"", ""hi"")"),"बिल और खर्च अपलोड करें")</f>
+        <v>बिल और खर्च अपलोड करें</v>
+      </c>
+      <c r="E1210" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1210, ""en"", ""kn"")"),"ಬಿಲ್‌ಗಳು ಮತ್ತು ವೆಚ್ಚಗಳನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ")</f>
+        <v>ಬಿಲ್‌ಗಳು ಮತ್ತು ವೆಚ್ಚಗಳನ್ನು ಅಪ್‌ಲೋಡ್ ಮಾಡಿ</v>
+      </c>
+      <c r="F1210" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1210, ""en"", ""ml"")"),"ബില്ലുകളും ചെലവുകളും അപ്‌ലോഡ് ചെയ്യുക")</f>
+        <v>ബില്ലുകളും ചെലവുകളും അപ്‌ലോഡ് ചെയ്യുക</v>
+      </c>
+      <c r="G1210" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1210, ""en"", ""te"")"),"బిల్లులు మరియు ఖర్చులను అప్‌లోడ్ చేయండి")</f>
+        <v>బిల్లులు మరియు ఖర్చులను అప్‌లోడ్ చేయండి</v>
+      </c>
     </row>
     <row r="1211">
-      <c r="A1211" s="4"/>
-      <c r="B1211" s="5"/>
-      <c r="C1211" s="6"/>
-      <c r="D1211" s="6"/>
-      <c r="E1211" s="6"/>
+      <c r="A1211" s="12" t="s">
+        <v>2890</v>
+      </c>
+      <c r="B1211" s="13" t="s">
+        <v>2810</v>
+      </c>
+      <c r="C1211" s="8" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1211, ""en"", ""ta"")"),"முழு முகவரியைக் காண்க")</f>
+        <v>முழு முகவரியைக் காண்க</v>
+      </c>
+      <c r="D1211" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1211, ""en"", ""hi"")"),"पूरा पता देखें")</f>
+        <v>पूरा पता देखें</v>
+      </c>
+      <c r="E1211" s="6" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1211, ""en"", ""kn"")"),"ಪೂರ್ಣ ವಿಳಾಸವನ್ನು ವೀಕ್ಷಿಸಿ")</f>
+        <v>ಪೂರ್ಣ ವಿಳಾಸವನ್ನು ವೀಕ್ಷಿಸಿ</v>
+      </c>
+      <c r="F1211" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1211, ""en"", ""ml"")"),"മുഴുവൻ വിലാസവും കാണുക")</f>
+        <v>മുഴുവൻ വിലാസവും കാണുക</v>
+      </c>
+      <c r="G1211" s="7" t="str">
+        <f>IFERROR(__xludf.DUMMYFUNCTION("GOOGLETRANSLATE(B1211, ""en"", ""te"")"),"పూర్తి చిరునామాను వీక్షించండి")</f>
+        <v>పూర్తి చిరునామాను వీక్షించండి</v>
+      </c>
     </row>
     <row r="1212">
       <c r="A1212" s="4"/>
@@ -41715,8 +42918,8 @@
       <c r="E1279" s="6"/>
     </row>
     <row r="1280">
-      <c r="A1280" s="4"/>
-      <c r="B1280" s="5"/>
+      <c r="A1280" s="11"/>
+      <c r="B1280" s="10"/>
       <c r="C1280" s="6"/>
       <c r="D1280" s="6"/>
       <c r="E1280" s="6"/>
@@ -41771,8 +42974,8 @@
       <c r="E1287" s="6"/>
     </row>
     <row r="1288">
-      <c r="A1288" s="11"/>
-      <c r="B1288" s="10"/>
+      <c r="A1288" s="4"/>
+      <c r="B1288" s="5"/>
       <c r="C1288" s="6"/>
       <c r="D1288" s="6"/>
       <c r="E1288" s="6"/>
@@ -42296,11 +43499,11 @@
       <c r="E1362" s="6"/>
     </row>
     <row r="1363">
-      <c r="A1363" s="4"/>
-      <c r="B1363" s="5"/>
-      <c r="C1363" s="6"/>
-      <c r="D1363" s="6"/>
-      <c r="E1363" s="6"/>
+      <c r="A1363" s="11"/>
+      <c r="B1363" s="17"/>
+      <c r="C1363" s="11"/>
+      <c r="D1363" s="11"/>
+      <c r="E1363" s="11"/>
     </row>
     <row r="1364">
       <c r="A1364" s="11"/>
@@ -47124,13 +48327,6 @@
       <c r="C2052" s="11"/>
       <c r="D2052" s="11"/>
       <c r="E2052" s="11"/>
-    </row>
-    <row r="2053">
-      <c r="A2053" s="11"/>
-      <c r="B2053" s="17"/>
-      <c r="C2053" s="11"/>
-      <c r="D2053" s="11"/>
-      <c r="E2053" s="11"/>
     </row>
   </sheetData>
   <dataValidations>
